--- a/dados_capes/capes_2021_2024_ia_antro_socio_cienciapolitica.xlsx
+++ b/dados_capes/capes_2021_2024_ia_antro_socio_cienciapolitica.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y72"/>
+  <dimension ref="A1:AE72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,70 +474,100 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>SUBCAMPOS</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>SUBCAMPO_IA_STRICTO</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>SUBCAMPO_ML</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>SUBCAMPO_DL</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>SUBCAMPO_LLM</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>SUBCAMPO_CORRELATOS</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>NM_ORIENTADOR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>NM_PROGRAMA</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>NM_ENTIDADE_ENSINO</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>SG_ENTIDADE_ENSINO</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NM_REGIAO</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SG_UF_IES</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>NM_UF_IES</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>NR_PAGINAS</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>NM_IDIOMA</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>NM_SUBAREA_CONHECIMENTO</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>NM_AREA_AVALIACAO</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>DS_URL_TEXTO_COMPLETO</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>ID_PRODUCAO_INTELECTUAL</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>ID_PESSOA_DISCENTE</t>
         </is>
@@ -594,73 +624,93 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>ROSE SATIKO GITIRANA HIKIJI</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>CIÊNCIA SOCIAL (ANTROPOLOGIA SOCIAL)</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>UNIVERSIDADE DE SÃO PAULO</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>USP</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SÃO PAULO</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="Y2" t="n">
         <v>374</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>ANTROPOLOGIA / ARQUEOLOGIA</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13950696</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>13950696</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="n">
         <v>1211062</v>
       </c>
     </row>
@@ -715,73 +765,93 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>EDUARDO BATALHA VIVEIROS DE CASTRO</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>ANTROPOLOGIA SOCIAL</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>UFRJ</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>ANTROPOLOGIA / ARQUEOLOGIA</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=10465666</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>10465666</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="AE3" t="n">
         <v>3048212</v>
       </c>
     </row>
@@ -836,73 +906,93 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>Aprendizado de máquina (ML); IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>LETICIA MARIA COSTA DA NOBREGA CESARINO</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>ANTROPOLOGIA SOCIAL</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DE SANTA CATARINA</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>UFSC</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SANTA CATARINA</t>
         </is>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="inlineStr">
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>ANTROPOLOGIA / ARQUEOLOGIA</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12295445</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>12295445</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="AE4" t="n">
         <v>3278660</v>
       </c>
     </row>
@@ -957,73 +1047,93 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>RAFAEL GUEDES MILHEIRA</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>ANTROPOLOGIA</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DE PELOTAS</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>UFPEL</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>RIO GRANDE DO SUL</t>
         </is>
       </c>
-      <c r="S5" t="n">
+      <c r="Y5" t="n">
         <v>149</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>ANTROPOLOGIA / ARQUEOLOGIA</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13994316</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>13994316</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="AE5" t="n">
         <v>2511313</v>
       </c>
     </row>
@@ -1078,73 +1188,93 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>Modelos de linguagem &amp; IA generativa</t>
+        </is>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>LAURA PEREZ GIL</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>ANTROPOLOGIA E ARQUEOLOGIA</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO PARANÁ</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>UFPR</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>PR</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>PARANÁ</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="Y6" t="n">
         <v>187</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>ANTROPOLOGIA / ARQUEOLOGIA</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16053501</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>16053501</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="AE6" t="n">
         <v>484110</v>
       </c>
     </row>
@@ -1199,73 +1329,93 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M7" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>LUIS GUSTAVO MELLO GROHMANN</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO RIO GRANDE DO SUL</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>UFRGS</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>RIO GRANDE DO SUL</t>
         </is>
       </c>
-      <c r="S7" t="n">
+      <c r="Y7" t="n">
         <v>250</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=10964912</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>10964912</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="AE7" t="n">
         <v>645294</v>
       </c>
     </row>
@@ -1320,73 +1470,93 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>Aprendizado de máquina (ML); IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M8" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>JOAO PAULO CANDIA VEIGA</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>UNIVERSIDADE DE SÃO PAULO</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>USP</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SÃO PAULO</t>
         </is>
       </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="inlineStr">
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12685308</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>12685308</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="AE8" t="n">
         <v>1150096</v>
       </c>
     </row>
@@ -1441,73 +1611,93 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>YI SHIN TANG</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>UNIVERSIDADE DE SÃO PAULO</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>USP</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SÃO PAULO</t>
         </is>
       </c>
-      <c r="S9" t="n">
+      <c r="Y9" t="n">
         <v>124</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>POLÍTICA INTERNACIONAL</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13498574</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>13498574</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="AE9" t="n">
         <v>816113</v>
       </c>
     </row>
@@ -1562,73 +1752,93 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>Aprendizado de máquina (ML)</t>
+        </is>
+      </c>
+      <c r="M10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>MARCUS ABILIO GOMES PEREIRA</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>UFMG</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>MINAS GERAIS</t>
         </is>
       </c>
-      <c r="S10" t="n">
+      <c r="Y10" t="n">
         <v>386</v>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15695371</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>15695371</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="AE10" t="n">
         <v>615797</v>
       </c>
     </row>
@@ -1683,73 +1893,93 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>DENILSON BANDEIRA COELHO</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>UNIVERSIDADE DE BRASÍLIA</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>UNB</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>CENTRO-OESTE</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>DF</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>DISTRITO FEDERAL</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="Y11" t="n">
         <v>301</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15771243</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>15771243</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="AE11" t="n">
         <v>1141673</v>
       </c>
     </row>
@@ -1804,73 +2034,93 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>Aprendizado de máquina (ML)</t>
+        </is>
+      </c>
+      <c r="M12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>ADRIANO NERVO CODATO</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO PARANÁ</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>UFPR</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>PR</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>PARANÁ</t>
         </is>
       </c>
-      <c r="S12" t="n">
+      <c r="Y12" t="n">
         <v>125</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16471651</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>16471651</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="AE12" t="n">
         <v>1993878</v>
       </c>
     </row>
@@ -1925,73 +2175,93 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M13" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>CLAUDIO RODRIGUES CORREA</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>ESTUDOS MARÍTIMOS</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>ESCOLA DE GUERRA NAVAL</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>EGN</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="S13" t="n">
+      <c r="Y13" t="n">
         <v>199</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16722764</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>16722764</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="AE13" t="n">
         <v>2757585</v>
       </c>
     </row>
@@ -2046,73 +2316,93 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>Aprendizado de máquina (ML)</t>
+        </is>
+      </c>
+      <c r="M14" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>DALSON BRITTO FIGUEIREDO FILHO</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DE PERNAMBUCO</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>UFPE</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>NORDESTE</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>PERNAMBUCO</t>
         </is>
       </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="inlineStr">
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=10455339</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>10455339</t>
         </is>
       </c>
-      <c r="Y14" t="n">
+      <c r="AE14" t="n">
         <v>3385936</v>
       </c>
     </row>
@@ -2167,73 +2457,93 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M15" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
           <t>BENJAMIN MIRANDA TABAK</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>POLÍTICAS PÚBLICAS E GOVERNO</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>FUNDACAO GETULIO VARGAS ( BRASÍLIA )</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>FGV/BSB</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>CENTRO-OESTE</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>DF</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>DISTRITO FEDERAL</t>
         </is>
       </c>
-      <c r="S15" t="n">
+      <c r="Y15" t="n">
         <v>133</v>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=10992403</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>10992403</t>
         </is>
       </c>
-      <c r="Y15" t="n">
+      <c r="AE15" t="n">
         <v>3576479</v>
       </c>
     </row>
@@ -2288,73 +2598,93 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M16" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
           <t>MARCOS AURELIO GUEDES DE OLIVEIRA</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DE PERNAMBUCO</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>UFPE</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>NORDESTE</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>PERNAMBUCO</t>
         </is>
       </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="inlineStr">
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=10456749</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>10456749</t>
         </is>
       </c>
-      <c r="Y16" t="n">
+      <c r="AE16" t="n">
         <v>3385997</v>
       </c>
     </row>
@@ -2409,73 +2739,93 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M17" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>CRISTINA SOREANU PECEQUILO</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>ECONOMIA POLÍTICA INTERNACIONAL</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>UFRJ</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="S17" t="n">
+      <c r="Y17" t="n">
         <v>162</v>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11515865</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>11515865</t>
         </is>
       </c>
-      <c r="Y17" t="n">
+      <c r="AE17" t="n">
         <v>3611866</v>
       </c>
     </row>
@@ -2530,73 +2880,93 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M18" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
           <t>JOSE MIGUEL QUEDI MARTINS</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>ESTUDOS ESTRATÉGICOS INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO RIO GRANDE DO SUL</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>UFRGS</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>RIO GRANDE DO SUL</t>
         </is>
       </c>
-      <c r="S18" t="n">
+      <c r="Y18" t="n">
         <v>170</v>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>POLÍTICA INTERNACIONAL</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11576624</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>11576624</t>
         </is>
       </c>
-      <c r="Y18" t="n">
+      <c r="AE18" t="n">
         <v>3859907</v>
       </c>
     </row>
@@ -2651,73 +3021,93 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>LUCIANA PAZINI PAPI</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO RIO GRANDE DO SUL</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>UFRGS</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>RIO GRANDE DO SUL</t>
         </is>
       </c>
-      <c r="S19" t="n">
+      <c r="Y19" t="n">
         <v>103</v>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13719515</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>13719515</t>
         </is>
       </c>
-      <c r="Y19" t="n">
+      <c r="AE19" t="n">
         <v>3894235</v>
       </c>
     </row>
@@ -2772,73 +3162,93 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M20" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" t="b">
+        <v>0</v>
+      </c>
+      <c r="O20" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
           <t>JOSE LUIS DA COSTA FIORI</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>ECONOMIA POLÍTICA INTERNACIONAL</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>UFRJ</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="S20" t="n">
+      <c r="Y20" t="n">
         <v>97</v>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12682786</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>12682786</t>
         </is>
       </c>
-      <c r="Y20" t="n">
+      <c r="AE20" t="n">
         <v>1385496</v>
       </c>
     </row>
@@ -2893,73 +3303,93 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+      <c r="N21" t="b">
+        <v>0</v>
+      </c>
+      <c r="O21" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
           <t>VANTUIL PEREIRA</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>POLÍTICAS PÚBLICAS EM DIREITOS HUMANOS</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>UFRJ</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="S21" t="n">
+      <c r="Y21" t="n">
         <v>129</v>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12441756</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>12441756</t>
         </is>
       </c>
-      <c r="Y21" t="n">
+      <c r="AE21" t="n">
         <v>3810911</v>
       </c>
     </row>
@@ -3014,73 +3444,93 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>Aprendizado de máquina (ML)</t>
+        </is>
+      </c>
+      <c r="M22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
+      </c>
+      <c r="O22" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
           <t>RODRIGO BARROS DE ALBUQUERQUE</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DE PERNAMBUCO</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>UFPE</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>NORDESTE</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>PERNAMBUCO</t>
         </is>
       </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="inlineStr">
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="inlineStr">
         <is>
           <t>INGLES</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14475475</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>14475475</t>
         </is>
       </c>
-      <c r="Y22" t="n">
+      <c r="AE22" t="n">
         <v>4028790</v>
       </c>
     </row>
@@ -3135,73 +3585,93 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
+          <t>IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M23" t="b">
+        <v>1</v>
+      </c>
+      <c r="N23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
           <t>BERNARDO OLIVEIRA BUTA</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>POLÍTICAS PÚBLICAS E GOVERNO</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>FUNDAÇÃO GETULIO VARGAS - BRASÍLIA</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>FGV-BSB</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>CENTRO-OESTE</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>DF</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>DISTRITO FEDERAL</t>
         </is>
       </c>
-      <c r="S23" t="n">
+      <c r="Y23" t="n">
         <v>108</v>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15961875</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>15961875</t>
         </is>
       </c>
-      <c r="Y23" t="n">
+      <c r="AE23" t="n">
         <v>4430849</v>
       </c>
     </row>
@@ -3256,73 +3726,93 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>Aprendizado de máquina (ML); Aprendizado profundo &amp; redes neurais</t>
+        </is>
+      </c>
+      <c r="M24" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" t="b">
+        <v>1</v>
+      </c>
+      <c r="O24" t="b">
+        <v>1</v>
+      </c>
+      <c r="P24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>0</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
           <t>HELCIMARA DE SOUZA TELLES</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>UFMG</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>MINAS GERAIS</t>
         </is>
       </c>
-      <c r="S24" t="n">
+      <c r="Y24" t="n">
         <v>115</v>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15204334</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>15204334</t>
         </is>
       </c>
-      <c r="Y24" t="n">
+      <c r="AE24" t="n">
         <v>3664850</v>
       </c>
     </row>
@@ -3377,73 +3867,93 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N25" t="b">
+        <v>0</v>
+      </c>
+      <c r="O25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
           <t>DANIELLE JACON AYRES PINTO</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DE SANTA CATARINA</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>UFSC</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>SANTA CATARINA</t>
         </is>
       </c>
-      <c r="S25" t="n">
+      <c r="Y25" t="n">
         <v>153</v>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>POLÍTICA INTERNACIONAL</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16197565</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>16197565</t>
         </is>
       </c>
-      <c r="Y25" t="n">
+      <c r="AE25" t="n">
         <v>4082614</v>
       </c>
     </row>
@@ -3498,73 +4008,93 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>0</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
           <t>MARCOS AURELIO GUEDES DE OLIVEIRA</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>CIÊNCIAS MILITARES</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>ESCOLA DE COMANDO E ESTADO-MAIOR DO EXÉRCITO</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>ECEME</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="S26" t="n">
+      <c r="Y26" t="n">
         <v>93</v>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15391626</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>15391626</t>
         </is>
       </c>
-      <c r="Y26" t="n">
+      <c r="AE26" t="n">
         <v>4003013</v>
       </c>
     </row>
@@ -3619,73 +4149,93 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M27" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
           <t>NATALIA DUS POIATTI LOMONACO</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>UNIVERSIDADE DE SÃO PAULO</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>USP</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>SÃO PAULO</t>
         </is>
       </c>
-      <c r="S27" t="n">
+      <c r="Y27" t="n">
         <v>78</v>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>INGLES</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>POLÍTICA INTERNACIONAL</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15665505</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>15665505</t>
         </is>
       </c>
-      <c r="Y27" t="n">
+      <c r="AE27" t="n">
         <v>4040126</v>
       </c>
     </row>
@@ -3740,73 +4290,93 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M28" t="b">
+        <v>1</v>
+      </c>
+      <c r="N28" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28" t="b">
+        <v>0</v>
+      </c>
+      <c r="P28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>0</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
           <t>RAPHAEL AMORIM MACHADO</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>POLÍTICAS PÚBLICAS E GOVERNO</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>FUNDAÇÃO GETULIO VARGAS - BRASÍLIA</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>FGV-BSB</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>CENTRO-OESTE</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>DF</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>DISTRITO FEDERAL</t>
         </is>
       </c>
-      <c r="S28" t="n">
+      <c r="Y28" t="n">
         <v>205</v>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15964806</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>15964806</t>
         </is>
       </c>
-      <c r="Y28" t="n">
+      <c r="AE28" t="n">
         <v>4549098</v>
       </c>
     </row>
@@ -3861,73 +4431,93 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t>IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M29" t="b">
+        <v>1</v>
+      </c>
+      <c r="N29" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
           <t>UALLACE MOREIRA LIMA</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DA BAHIA</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>UFBA</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>NORDESTE</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>BAHIA</t>
         </is>
       </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="inlineStr">
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>POLÍTICA INTERNACIONAL</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15964815</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>15964815</t>
         </is>
       </c>
-      <c r="Y29" t="n">
+      <c r="AE29" t="n">
         <v>3773478</v>
       </c>
     </row>
@@ -3982,73 +4572,93 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O30" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
           <t>AUGUSTO JUNIOR CLEMENTE</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>FUNDAÇÃO UNIVERSIDADE FEDERAL DO PAMPA</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>UNIPAMPA</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>RIO GRANDE DO SUL</t>
         </is>
       </c>
-      <c r="S30" t="n">
+      <c r="Y30" t="n">
         <v>106</v>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=10983519</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>10983519</t>
         </is>
       </c>
-      <c r="Y30" t="n">
+      <c r="AE30" t="n">
         <v>3479153</v>
       </c>
     </row>
@@ -4103,73 +4713,93 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M31" t="b">
+        <v>0</v>
+      </c>
+      <c r="N31" t="b">
+        <v>0</v>
+      </c>
+      <c r="O31" t="b">
+        <v>0</v>
+      </c>
+      <c r="P31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
           <t>FRANCIS ALBERT COTTA FORMIGA</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>SEGURANÇA PÚBLICA E CIDADANIA</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>UEMG</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>MINAS GERAIS</t>
         </is>
       </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="inlineStr">
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11453818</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>11453818</t>
         </is>
       </c>
-      <c r="Y31" t="n">
+      <c r="AE31" t="n">
         <v>3481208</v>
       </c>
     </row>
@@ -4224,73 +4854,93 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M32" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
           <t>AIRTON BODSTEIN DE BARROS</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>DEFESA E SEGURANÇA CIVIL</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL FLUMINENSE</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>UFF</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="S32" t="n">
+      <c r="Y32" t="n">
         <v>96</v>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11509111</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>11509111</t>
         </is>
       </c>
-      <c r="Y32" t="n">
+      <c r="AE32" t="n">
         <v>1554710</v>
       </c>
     </row>
@@ -4345,73 +4995,93 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O33" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
           <t>NIVAL NUNES DE ALMEIDA</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>ESTUDOS MARÍTIMOS</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>ESCOLA DE GUERRA NAVAL</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>EGN</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="S33" t="n">
+      <c r="Y33" t="n">
         <v>121</v>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11380785</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>11380785</t>
         </is>
       </c>
-      <c r="Y33" t="n">
+      <c r="AE33" t="n">
         <v>3619457</v>
       </c>
     </row>
@@ -4466,73 +5136,93 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
           <t>RODRIGO SANTAELLA GONCALVES</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>PLANEJAMENTO E POLITICAS PÚBLICAS</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>UNIVERSIDADE ESTADUAL DO CEARÁ</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>UECE</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>NORDESTE</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>CEARÁ</t>
         </is>
       </c>
-      <c r="S34" t="n">
+      <c r="Y34" t="n">
         <v>149</v>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11550911</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>11550911</t>
         </is>
       </c>
-      <c r="Y34" t="n">
+      <c r="AE34" t="n">
         <v>2353082</v>
       </c>
     </row>
@@ -4587,73 +5277,93 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M35" t="b">
+        <v>1</v>
+      </c>
+      <c r="N35" t="b">
+        <v>0</v>
+      </c>
+      <c r="O35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
           <t>TOMAZ OLIVEIRA PAOLIELLO</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>GOVERNANÇA GLOBAL E FORMULAÇÃO DE POLÍTICAS INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>PONTIFÍCIA UNIVERSIDADE CATÓLICA DE SÃO PAULO</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>PUC/SP</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>SÃO PAULO</t>
         </is>
       </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="inlineStr">
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>POLÍTICA INTERNACIONAL</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13677308</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>13677308</t>
         </is>
       </c>
-      <c r="Y35" t="n">
+      <c r="AE35" t="n">
         <v>3561400</v>
       </c>
     </row>
@@ -4708,73 +5418,93 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M36" t="b">
+        <v>0</v>
+      </c>
+      <c r="N36" t="b">
+        <v>0</v>
+      </c>
+      <c r="O36" t="b">
+        <v>0</v>
+      </c>
+      <c r="P36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
           <t>RAFAEL ZELESCO BARRETTO</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>ESTUDOS MARÍTIMOS</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>ESCOLA DE GUERRA NAVAL</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>EGN</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="S36" t="n">
+      <c r="Y36" t="n">
         <v>104</v>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12056351</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>12056351</t>
         </is>
       </c>
-      <c r="Y36" t="n">
+      <c r="AE36" t="n">
         <v>3619382</v>
       </c>
     </row>
@@ -4829,73 +5559,93 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M37" t="b">
+        <v>1</v>
+      </c>
+      <c r="N37" t="b">
+        <v>0</v>
+      </c>
+      <c r="O37" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
           <t>RODRIGO SANTAELLA GONCALVES</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>PLANEJAMENTO E POLITICAS PÚBLICAS</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>UNIVERSIDADE ESTADUAL DO CEARÁ</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>UECE</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>NORDESTE</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>CEARÁ</t>
         </is>
       </c>
-      <c r="S37" t="n">
+      <c r="Y37" t="n">
         <v>188</v>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13636640</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>13636640</t>
         </is>
       </c>
-      <c r="Y37" t="n">
+      <c r="AE37" t="n">
         <v>3673283</v>
       </c>
     </row>
@@ -4950,73 +5700,93 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M38" t="b">
+        <v>0</v>
+      </c>
+      <c r="N38" t="b">
+        <v>0</v>
+      </c>
+      <c r="O38" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
           <t>MICHELLE CARVALHO GALVAO DA SILVA PINTO BANDEIRA</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>SEGURANÇA DE AVIAÇÃO E AERONAVEGABILIDADE CONTINUADA</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>INSTITUTO TECNOLÓGICO DE AERONÁUTICA</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>ITA</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>SÃO PAULO</t>
         </is>
       </c>
-      <c r="S38" t="n">
+      <c r="Y38" t="n">
         <v>98</v>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14474457</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>14474457</t>
         </is>
       </c>
-      <c r="Y38" t="n">
+      <c r="AE38" t="n">
         <v>4007674</v>
       </c>
     </row>
@@ -5071,73 +5841,93 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M39" t="b">
+        <v>0</v>
+      </c>
+      <c r="N39" t="b">
+        <v>0</v>
+      </c>
+      <c r="O39" t="b">
+        <v>0</v>
+      </c>
+      <c r="P39" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
           <t>RONALDO VIEIRA CRUZ</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>SEGURANÇA DE AVIAÇÃO E AERONAVEGABILIDADE CONTINUADA</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>INSTITUTO TECNOLÓGICO DE AERONÁUTICA</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>ITA</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>SÃO PAULO</t>
         </is>
       </c>
-      <c r="S39" t="n">
+      <c r="Y39" t="n">
         <v>121</v>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14690798</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>14690798</t>
         </is>
       </c>
-      <c r="Y39" t="n">
+      <c r="AE39" t="n">
         <v>2753775</v>
       </c>
     </row>
@@ -5192,73 +5982,93 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
+          <t>Aprendizado de máquina (ML)</t>
+        </is>
+      </c>
+      <c r="M40" t="b">
+        <v>0</v>
+      </c>
+      <c r="N40" t="b">
+        <v>1</v>
+      </c>
+      <c r="O40" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>0</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
           <t>FLAVIA LUCIA CHEIN FERES</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>AVALIAÇÃO E MONITORAMENTO DE POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>FUNDAÇÃO ESCOLA NACIONAL DE ADMINISTRAÇÃO PÚBLICA</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>ENAP</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>CENTRO-OESTE</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>DF</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>DISTRITO FEDERAL</t>
         </is>
       </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="inlineStr">
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14385858</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>14385858</t>
         </is>
       </c>
-      <c r="Y40" t="n">
+      <c r="AE40" t="n">
         <v>444569</v>
       </c>
     </row>
@@ -5313,73 +6123,93 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
+          <t>Aprendizado de máquina (ML); Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M41" t="b">
+        <v>0</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
+      </c>
+      <c r="O41" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
           <t>FABIANO PERUZZO SCHWARTZ</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>PODER LEGISLATIVO</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>CENTRO DE FORMAÇÃO, TREINAMENTO E APERFEIÇOAMENTO</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>CEFOR</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>CENTRO-OESTE</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>DF</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>DISTRITO FEDERAL</t>
         </is>
       </c>
-      <c r="S41" t="n">
+      <c r="Y41" t="n">
         <v>81</v>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15145557</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>15145557</t>
         </is>
       </c>
-      <c r="Y41" t="n">
+      <c r="AE41" t="n">
         <v>3990725</v>
       </c>
     </row>
@@ -5434,73 +6264,93 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
+          <t>Aprendizado de máquina (ML)</t>
+        </is>
+      </c>
+      <c r="M42" t="b">
+        <v>0</v>
+      </c>
+      <c r="N42" t="b">
+        <v>1</v>
+      </c>
+      <c r="O42" t="b">
+        <v>0</v>
+      </c>
+      <c r="P42" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="b">
+        <v>0</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
           <t>VITOR AZEVEDO PEREIRA PONTUAL</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>AVALIAÇÃO E MONITORAMENTO DE POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>ESCOLA NACIONAL DE ADMINISTRAÇÃO PÚBLICA</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>ENAP</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>CENTRO-OESTE</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>DF</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>DISTRITO FEDERAL</t>
         </is>
       </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="inlineStr">
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="AC42" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16376007</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="AD42" t="inlineStr">
         <is>
           <t>16376007</t>
         </is>
       </c>
-      <c r="Y42" t="n">
+      <c r="AE42" t="n">
         <v>3441509</v>
       </c>
     </row>
@@ -5555,73 +6405,93 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M43" t="b">
+        <v>1</v>
+      </c>
+      <c r="N43" t="b">
+        <v>0</v>
+      </c>
+      <c r="O43" t="b">
+        <v>0</v>
+      </c>
+      <c r="P43" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="b">
+        <v>0</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
           <t>JOSE PEREIRA MASCARENHAS BISNETO</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>GESTÃO DE POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO RECÔNCAVO DA BAHIA</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>UFRB</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>NORDESTE</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>BAHIA</t>
         </is>
       </c>
-      <c r="S43" t="n">
+      <c r="Y43" t="n">
         <v>92</v>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="AC43" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16426209</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="AD43" t="inlineStr">
         <is>
           <t>16426209</t>
         </is>
       </c>
-      <c r="Y43" t="n">
+      <c r="AE43" t="n">
         <v>3938979</v>
       </c>
     </row>
@@ -5676,73 +6546,93 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
+          <t>Modelos de linguagem &amp; IA generativa</t>
+        </is>
+      </c>
+      <c r="M44" t="b">
+        <v>0</v>
+      </c>
+      <c r="N44" t="b">
+        <v>0</v>
+      </c>
+      <c r="O44" t="b">
+        <v>0</v>
+      </c>
+      <c r="P44" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="b">
+        <v>0</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
           <t>CRISTIANE BRUM BERNARDES</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>PODER LEGISLATIVO</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>CENTRO DE FORMAÇÃO, TREINAMENTO E APERFEIÇOAMENTO</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>CEFOR</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>CENTRO-OESTE</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>DF</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>DISTRITO FEDERAL</t>
         </is>
       </c>
-      <c r="S44" t="n">
+      <c r="Y44" t="n">
         <v>152</v>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16648671</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>16648671</t>
         </is>
       </c>
-      <c r="Y44" t="n">
+      <c r="AE44" t="n">
         <v>4338098</v>
       </c>
     </row>
@@ -5797,73 +6687,93 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
+          <t>Aprendizado de máquina (ML); IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M45" t="b">
+        <v>1</v>
+      </c>
+      <c r="N45" t="b">
+        <v>1</v>
+      </c>
+      <c r="O45" t="b">
+        <v>0</v>
+      </c>
+      <c r="P45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="b">
+        <v>0</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
           <t>FABIANO PERUZZO SCHWARTZ</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>PODER LEGISLATIVO</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>CENTRO DE FORMAÇÃO, TREINAMENTO E APERFEIÇOAMENTO</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>CEFOR</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>CENTRO-OESTE</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>DF</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>DISTRITO FEDERAL</t>
         </is>
       </c>
-      <c r="S45" t="n">
+      <c r="Y45" t="n">
         <v>134</v>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15217157</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>15217157</t>
         </is>
       </c>
-      <c r="Y45" t="n">
+      <c r="AE45" t="n">
         <v>3990787</v>
       </c>
     </row>
@@ -5918,73 +6828,93 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M46" t="b">
+        <v>1</v>
+      </c>
+      <c r="N46" t="b">
+        <v>0</v>
+      </c>
+      <c r="O46" t="b">
+        <v>0</v>
+      </c>
+      <c r="P46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="b">
+        <v>0</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
           <t>CLAUDIO RODRIGUES CORREA</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>ESTUDOS MARÍTIMOS</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>ESCOLA DE GUERRA NAVAL</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>EGN</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="inlineStr">
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16738179</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>16738179</t>
         </is>
       </c>
-      <c r="Y46" t="n">
+      <c r="AE46" t="n">
         <v>4225138</v>
       </c>
     </row>
@@ -6039,73 +6969,93 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M47" t="b">
+        <v>1</v>
+      </c>
+      <c r="N47" t="b">
+        <v>0</v>
+      </c>
+      <c r="O47" t="b">
+        <v>0</v>
+      </c>
+      <c r="P47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="b">
+        <v>0</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
           <t>MARCOS CORDEIRO PIRES</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>CIÊNCIAS SOCIAIS</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>UNIVERSIDADE ESTADUAL PAULISTA JÚLIO DE MESQUITA FILHO (MARÍLIA)</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>UNESP-MAR</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>SÃO PAULO</t>
         </is>
       </c>
-      <c r="S47" t="n">
+      <c r="Y47" t="n">
         <v>156</v>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11296907</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>11296907</t>
         </is>
       </c>
-      <c r="Y47" t="n">
+      <c r="AE47" t="n">
         <v>1994862</v>
       </c>
     </row>
@@ -6160,73 +7110,93 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
+          <t>IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M48" t="b">
+        <v>1</v>
+      </c>
+      <c r="N48" t="b">
+        <v>0</v>
+      </c>
+      <c r="O48" t="b">
+        <v>0</v>
+      </c>
+      <c r="P48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="b">
+        <v>1</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
           <t>MARIA TERESA MICELI KERBAUY</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>CIÊNCIAS SOCIAIS</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>UNIVERSIDADE ESTADUAL PAULISTA JÚLIO DE MESQUITA FILHO (ARARAQUARA)</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>UNESP-ARAR</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>SÃO PAULO</t>
         </is>
       </c>
-      <c r="S48" t="n">
+      <c r="Y48" t="n">
         <v>187</v>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12131172</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="AD48" t="inlineStr">
         <is>
           <t>12131172</t>
         </is>
       </c>
-      <c r="Y48" t="n">
+      <c r="AE48" t="n">
         <v>1010034</v>
       </c>
     </row>
@@ -6281,73 +7251,93 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
+          <t>Modelos de linguagem &amp; IA generativa</t>
+        </is>
+      </c>
+      <c r="M49" t="b">
+        <v>0</v>
+      </c>
+      <c r="N49" t="b">
+        <v>0</v>
+      </c>
+      <c r="O49" t="b">
+        <v>0</v>
+      </c>
+      <c r="P49" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q49" t="b">
+        <v>0</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
           <t>SANDRO RUDUIT GARCIA</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO RIO GRANDE DO SUL</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>UFRGS</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>RIO GRANDE DO SUL</t>
         </is>
       </c>
-      <c r="S49" t="n">
+      <c r="Y49" t="n">
         <v>559</v>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11646370</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="AD49" t="inlineStr">
         <is>
           <t>11646370</t>
         </is>
       </c>
-      <c r="Y49" t="n">
+      <c r="AE49" t="n">
         <v>628150</v>
       </c>
     </row>
@@ -6402,73 +7392,93 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M50" t="b">
+        <v>0</v>
+      </c>
+      <c r="N50" t="b">
+        <v>0</v>
+      </c>
+      <c r="O50" t="b">
+        <v>0</v>
+      </c>
+      <c r="P50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="b">
+        <v>1</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
           <t>ELAINE DA SILVEIRA LEITE</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DE PELOTAS</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>UFPEL</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>RIO GRANDE DO SUL</t>
         </is>
       </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="inlineStr">
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14897523</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="AD50" t="inlineStr">
         <is>
           <t>14897523</t>
         </is>
       </c>
-      <c r="Y50" t="n">
+      <c r="AE50" t="n">
         <v>1330676</v>
       </c>
     </row>
@@ -6523,73 +7533,93 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M51" t="b">
+        <v>0</v>
+      </c>
+      <c r="N51" t="b">
+        <v>0</v>
+      </c>
+      <c r="O51" t="b">
+        <v>0</v>
+      </c>
+      <c r="P51" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="b">
+        <v>1</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
           <t>GEOVANI JACO DE FREITAS</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>UNIVERSIDADE ESTADUAL DO CEARÁ</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>UECE</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>NORDESTE</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>CEARÁ</t>
         </is>
       </c>
-      <c r="S51" t="n">
+      <c r="Y51" t="n">
         <v>198</v>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14809587</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="AD51" t="inlineStr">
         <is>
           <t>14809587</t>
         </is>
       </c>
-      <c r="Y51" t="n">
+      <c r="AE51" t="n">
         <v>386811</v>
       </c>
     </row>
@@ -6644,73 +7674,93 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
+          <t>Aprendizado de máquina (ML); IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M52" t="b">
+        <v>1</v>
+      </c>
+      <c r="N52" t="b">
+        <v>1</v>
+      </c>
+      <c r="O52" t="b">
+        <v>0</v>
+      </c>
+      <c r="P52" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="b">
+        <v>1</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
           <t>GLAUCIA KRUSE VILLAS BOAS</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>SOCIOLOGIA E ANTROPOLOGIA</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>UFRJ</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="S52" t="n">
+      <c r="Y52" t="n">
         <v>229</v>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>OUTRAS SOCIOLOGIAS ESPECÍFICAS</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="AC52" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14195351</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="AD52" t="inlineStr">
         <is>
           <t>14195351</t>
         </is>
       </c>
-      <c r="Y52" t="n">
+      <c r="AE52" t="n">
         <v>1329593</v>
       </c>
     </row>
@@ -6765,73 +7815,93 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M53" t="b">
+        <v>1</v>
+      </c>
+      <c r="N53" t="b">
+        <v>0</v>
+      </c>
+      <c r="O53" t="b">
+        <v>0</v>
+      </c>
+      <c r="P53" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="b">
+        <v>0</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
           <t>MARIA APARECIDA DA CRUZ BRIDI</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO PARANÁ</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>UFPR</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>PR</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>PARANÁ</t>
         </is>
       </c>
-      <c r="S53" t="n">
+      <c r="Y53" t="n">
         <v>400</v>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15589542</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="AD53" t="inlineStr">
         <is>
           <t>15589542</t>
         </is>
       </c>
-      <c r="Y53" t="n">
+      <c r="AE53" t="n">
         <v>2675408</v>
       </c>
     </row>
@@ -6886,73 +7956,93 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M54" t="b">
+        <v>0</v>
+      </c>
+      <c r="N54" t="b">
+        <v>0</v>
+      </c>
+      <c r="O54" t="b">
+        <v>0</v>
+      </c>
+      <c r="P54" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="b">
+        <v>1</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
           <t>NOEMIA LAZZARESCHI</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>CIÊNCIAS SOCIAIS</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>PONTIFÍCIA UNIVERSIDADE CATÓLICA DE SÃO PAULO</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>PUCSP</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>SÃO PAULO</t>
         </is>
       </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="inlineStr">
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="AC54" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15793149</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="AD54" t="inlineStr">
         <is>
           <t>15793149</t>
         </is>
       </c>
-      <c r="Y54" t="n">
+      <c r="AE54" t="n">
         <v>2530079</v>
       </c>
     </row>
@@ -7007,73 +8097,93 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M55" t="b">
+        <v>0</v>
+      </c>
+      <c r="N55" t="b">
+        <v>0</v>
+      </c>
+      <c r="O55" t="b">
+        <v>0</v>
+      </c>
+      <c r="P55" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="b">
+        <v>1</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
           <t>MARIA APARECIDA DA CRUZ BRIDI</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO PARANÁ</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>UFPR</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>PR</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>PARANÁ</t>
         </is>
       </c>
-      <c r="S55" t="n">
+      <c r="Y55" t="n">
         <v>209</v>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="AC55" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15589576</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="AD55" t="inlineStr">
         <is>
           <t>15589576</t>
         </is>
       </c>
-      <c r="Y55" t="n">
+      <c r="AE55" t="n">
         <v>2675423</v>
       </c>
     </row>
@@ -7128,73 +8238,93 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M56" t="b">
+        <v>0</v>
+      </c>
+      <c r="N56" t="b">
+        <v>0</v>
+      </c>
+      <c r="O56" t="b">
+        <v>0</v>
+      </c>
+      <c r="P56" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="b">
+        <v>1</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
           <t>CESAR BARREIRA</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO CEARÁ</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>UFC</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>NORDESTE</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>CEARÁ</t>
         </is>
       </c>
-      <c r="S56" t="n">
+      <c r="Y56" t="n">
         <v>350</v>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="AC56" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16174984</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="AD56" t="inlineStr">
         <is>
           <t>16174984</t>
         </is>
       </c>
-      <c r="Y56" t="n">
+      <c r="AE56" t="n">
         <v>1177406</v>
       </c>
     </row>
@@ -7249,73 +8379,93 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M57" t="b">
+        <v>0</v>
+      </c>
+      <c r="N57" t="b">
+        <v>0</v>
+      </c>
+      <c r="O57" t="b">
+        <v>0</v>
+      </c>
+      <c r="P57" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="b">
+        <v>1</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
           <t>EDEMILSON CRUZ SANTANA JUNIOR</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO CEARÁ</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>UFC</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>NORDESTE</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>CEARÁ</t>
         </is>
       </c>
-      <c r="S57" t="n">
+      <c r="Y57" t="n">
         <v>381</v>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="AC57" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16175018</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="AD57" t="inlineStr">
         <is>
           <t>16175018</t>
         </is>
       </c>
-      <c r="Y57" t="n">
+      <c r="AE57" t="n">
         <v>1015048</v>
       </c>
     </row>
@@ -7370,73 +8520,93 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M58" t="b">
+        <v>0</v>
+      </c>
+      <c r="N58" t="b">
+        <v>0</v>
+      </c>
+      <c r="O58" t="b">
+        <v>0</v>
+      </c>
+      <c r="P58" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="b">
+        <v>1</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
           <t>RAPHAEL JONATHAS DA COSTA LIMA</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL FLUMINENSE</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>UFF</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="S58" t="n">
+      <c r="Y58" t="n">
         <v>107</v>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="AC58" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11436964</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="AD58" t="inlineStr">
         <is>
           <t>11436964</t>
         </is>
       </c>
-      <c r="Y58" t="n">
+      <c r="AE58" t="n">
         <v>2997668</v>
       </c>
     </row>
@@ -7491,73 +8661,93 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M59" t="b">
+        <v>0</v>
+      </c>
+      <c r="N59" t="b">
+        <v>0</v>
+      </c>
+      <c r="O59" t="b">
+        <v>0</v>
+      </c>
+      <c r="P59" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="b">
+        <v>1</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
           <t>SAMIRA FELDMAN MARZOCHI</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DE SÃO CARLOS</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>UFSCAR</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>SÃO PAULO</t>
         </is>
       </c>
-      <c r="S59" t="n">
+      <c r="Y59" t="n">
         <v>124</v>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="AC59" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11254402</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="AD59" t="inlineStr">
         <is>
           <t>11254402</t>
         </is>
       </c>
-      <c r="Y59" t="n">
+      <c r="AE59" t="n">
         <v>3328885</v>
       </c>
     </row>
@@ -7612,73 +8802,93 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M60" t="b">
+        <v>0</v>
+      </c>
+      <c r="N60" t="b">
+        <v>0</v>
+      </c>
+      <c r="O60" t="b">
+        <v>0</v>
+      </c>
+      <c r="P60" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="b">
+        <v>1</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
           <t>TANIA LUDMILA DIAS TOSTA</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DE GOIÁS</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>UFG</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>CENTRO-OESTE</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>GOIÁS</t>
         </is>
       </c>
-      <c r="S60" t="n">
+      <c r="Y60" t="n">
         <v>130</v>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="AC60" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13352420</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="AD60" t="inlineStr">
         <is>
           <t>13352420</t>
         </is>
       </c>
-      <c r="Y60" t="n">
+      <c r="AE60" t="n">
         <v>3615926</v>
       </c>
     </row>
@@ -7733,73 +8943,93 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
+          <t>Aprendizado profundo &amp; redes neurais; IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M61" t="b">
+        <v>1</v>
+      </c>
+      <c r="N61" t="b">
+        <v>0</v>
+      </c>
+      <c r="O61" t="b">
+        <v>1</v>
+      </c>
+      <c r="P61" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="b">
+        <v>0</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
           <t>EDEMILSON CRUZ SANTANA JUNIOR</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO CEARÁ</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>UFC</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>NORDESTE</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>CEARÁ</t>
         </is>
       </c>
-      <c r="S61" t="n">
+      <c r="Y61" t="n">
         <v>145</v>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="AC61" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13606356</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="AD61" t="inlineStr">
         <is>
           <t>13606356</t>
         </is>
       </c>
-      <c r="Y61" t="n">
+      <c r="AE61" t="n">
         <v>3608423</v>
       </c>
     </row>
@@ -7854,73 +9084,93 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
+          <t>Aprendizado de máquina (ML)</t>
+        </is>
+      </c>
+      <c r="M62" t="b">
+        <v>0</v>
+      </c>
+      <c r="N62" t="b">
+        <v>1</v>
+      </c>
+      <c r="O62" t="b">
+        <v>0</v>
+      </c>
+      <c r="P62" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="b">
+        <v>0</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
           <t>PEDRO ALCIDES ROBERTT NIZ</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DE PELOTAS</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>UFPEL</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>SUL</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>RIO GRANDE DO SUL</t>
         </is>
       </c>
-      <c r="S62" t="n">
+      <c r="Y62" t="n">
         <v>118</v>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="AC62" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11433364</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="AD62" t="inlineStr">
         <is>
           <t>11433364</t>
         </is>
       </c>
-      <c r="Y62" t="n">
+      <c r="AE62" t="n">
         <v>668986</v>
       </c>
     </row>
@@ -7975,73 +9225,93 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
+          <t>IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M63" t="b">
+        <v>1</v>
+      </c>
+      <c r="N63" t="b">
+        <v>0</v>
+      </c>
+      <c r="O63" t="b">
+        <v>0</v>
+      </c>
+      <c r="P63" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="b">
+        <v>1</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
           <t>EUGENIA DE SOUZA MELLO GUIMARAES MOTTA</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>UNIVERSIDADE DO ESTADO DO RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>UERJ</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="S63" t="n">
+      <c r="Y63" t="n">
         <v>84</v>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="AC63" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12141694</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="AD63" t="inlineStr">
         <is>
           <t>12141694</t>
         </is>
       </c>
-      <c r="Y63" t="n">
+      <c r="AE63" t="n">
         <v>3613835</v>
       </c>
     </row>
@@ -8096,73 +9366,93 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M64" t="b">
+        <v>1</v>
+      </c>
+      <c r="N64" t="b">
+        <v>0</v>
+      </c>
+      <c r="O64" t="b">
+        <v>0</v>
+      </c>
+      <c r="P64" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="b">
+        <v>0</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
           <t>RODRIGO SALLES PEREIRA DOS SANTOS</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>SOCIOLOGIA E ANTROPOLOGIA</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>UFRJ</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="S64" t="n">
+      <c r="Y64" t="n">
         <v>145</v>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>OUTRAS SOCIOLOGIAS ESPECÍFICAS</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="AC64" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12879895</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="AD64" t="inlineStr">
         <is>
           <t>12879895</t>
         </is>
       </c>
-      <c r="Y64" t="n">
+      <c r="AE64" t="n">
         <v>3055993</v>
       </c>
     </row>
@@ -8217,73 +9507,93 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M65" t="b">
+        <v>0</v>
+      </c>
+      <c r="N65" t="b">
+        <v>0</v>
+      </c>
+      <c r="O65" t="b">
+        <v>0</v>
+      </c>
+      <c r="P65" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="b">
+        <v>1</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
           <t>GONZALO ADRIAN ROJAS</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>CIÊNCIAS SOCIAIS</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DE CAMPINA GRANDE</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>UFCG</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>NORDESTE</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>PB</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>PARAÍBA</t>
         </is>
       </c>
-      <c r="S65" t="n">
+      <c r="Y65" t="n">
         <v>117</v>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="AC65" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12825916</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="AD65" t="inlineStr">
         <is>
           <t>12825916</t>
         </is>
       </c>
-      <c r="Y65" t="n">
+      <c r="AE65" t="n">
         <v>3876753</v>
       </c>
     </row>
@@ -8338,73 +9648,93 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M66" t="b">
+        <v>1</v>
+      </c>
+      <c r="N66" t="b">
+        <v>0</v>
+      </c>
+      <c r="O66" t="b">
+        <v>0</v>
+      </c>
+      <c r="P66" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="b">
+        <v>0</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
           <t>DIOGO SILVA CORREA</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>SOCIOLOGIA POLÍTICA</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>UNIVERSIDADE VILA VELHA</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>UVV</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="V66" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>ESPÍRITO SANTO</t>
         </is>
       </c>
-      <c r="S66" t="n">
+      <c r="Y66" t="n">
         <v>98</v>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="AB66" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="AC66" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14403191</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="AD66" t="inlineStr">
         <is>
           <t>14403191</t>
         </is>
       </c>
-      <c r="Y66" t="n">
+      <c r="AE66" t="n">
         <v>1636325</v>
       </c>
     </row>
@@ -8459,73 +9789,93 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M67" t="b">
+        <v>0</v>
+      </c>
+      <c r="N67" t="b">
+        <v>0</v>
+      </c>
+      <c r="O67" t="b">
+        <v>0</v>
+      </c>
+      <c r="P67" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="b">
+        <v>1</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
           <t>MARCOS CESAR ALVAREZ</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>UNIVERSIDADE DE SÃO PAULO</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>USP</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="V67" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>SÃO PAULO</t>
         </is>
       </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="inlineStr">
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="AC67" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13882903</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="AD67" t="inlineStr">
         <is>
           <t>13882903</t>
         </is>
       </c>
-      <c r="Y67" t="n">
+      <c r="AE67" t="n">
         <v>564924</v>
       </c>
     </row>
@@ -8580,73 +9930,93 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M68" t="b">
+        <v>1</v>
+      </c>
+      <c r="N68" t="b">
+        <v>0</v>
+      </c>
+      <c r="O68" t="b">
+        <v>0</v>
+      </c>
+      <c r="P68" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="b">
+        <v>0</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
           <t>PATRICIA REINHEIMER</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>CIÊNCIAS SOCIAIS</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL RURAL DO RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>UFRRJ</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="V68" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="S68" t="n">
+      <c r="Y68" t="n">
         <v>148</v>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="AC68" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15526518</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="AD68" t="inlineStr">
         <is>
           <t>15526518</t>
         </is>
       </c>
-      <c r="Y68" t="n">
+      <c r="AE68" t="n">
         <v>4121197</v>
       </c>
     </row>
@@ -8701,73 +10071,93 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M69" t="b">
+        <v>1</v>
+      </c>
+      <c r="N69" t="b">
+        <v>0</v>
+      </c>
+      <c r="O69" t="b">
+        <v>0</v>
+      </c>
+      <c r="P69" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="b">
+        <v>0</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
           <t>ALVARO AUGUSTO COMIN</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>UNIVERSIDADE DE SÃO PAULO</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>USP</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="V69" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>SÃO PAULO</t>
         </is>
       </c>
-      <c r="S69" t="n">
+      <c r="Y69" t="n">
         <v>253</v>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="AC69" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15426234</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="AD69" t="inlineStr">
         <is>
           <t>15426234</t>
         </is>
       </c>
-      <c r="Y69" t="n">
+      <c r="AE69" t="n">
         <v>3992079</v>
       </c>
     </row>
@@ -8822,73 +10212,93 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M70" t="b">
+        <v>0</v>
+      </c>
+      <c r="N70" t="b">
+        <v>0</v>
+      </c>
+      <c r="O70" t="b">
+        <v>0</v>
+      </c>
+      <c r="P70" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="b">
+        <v>1</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
           <t>ALEXSANDRO GALENO ARAUJO DANTAS</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>CIÊNCIAS SOCIAIS</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO RIO GRANDE DO NORTE</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>UFRN</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="V70" t="inlineStr">
         <is>
           <t>NORDESTE</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>RN</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>RIO GRANDE DO NORTE</t>
         </is>
       </c>
-      <c r="S70" t="n">
+      <c r="Y70" t="n">
         <v>76</v>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>SOCIOLOGIA DO DESENVOLVIMENTO</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="AC70" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15936517</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="AD70" t="inlineStr">
         <is>
           <t>15936517</t>
         </is>
       </c>
-      <c r="Y70" t="n">
+      <c r="AE70" t="n">
         <v>4322267</v>
       </c>
     </row>
@@ -8943,73 +10353,93 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Relacionado</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+        </is>
+      </c>
+      <c r="M71" t="b">
+        <v>0</v>
+      </c>
+      <c r="N71" t="b">
+        <v>0</v>
+      </c>
+      <c r="O71" t="b">
+        <v>0</v>
+      </c>
+      <c r="P71" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="b">
+        <v>1</v>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
           <t>EDEMILSON CRUZ SANTANA JUNIOR</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO CEARÁ</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>UFC</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="V71" t="inlineStr">
         <is>
           <t>NORDESTE</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="W71" t="inlineStr">
         <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>CEARÁ</t>
         </is>
       </c>
-      <c r="S71" t="n">
+      <c r="Y71" t="n">
         <v>89</v>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>NÃO SE APLICA</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
+      <c r="AC71" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16141494</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="AD71" t="inlineStr">
         <is>
           <t>16141494</t>
         </is>
       </c>
-      <c r="Y71" t="n">
+      <c r="AE71" t="n">
         <v>4046589</v>
       </c>
     </row>
@@ -9064,73 +10494,93 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>IA (sentido amplo) - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
+          <t>IA em sentido estrito</t>
+        </is>
+      </c>
+      <c r="M72" t="b">
+        <v>1</v>
+      </c>
+      <c r="N72" t="b">
+        <v>0</v>
+      </c>
+      <c r="O72" t="b">
+        <v>0</v>
+      </c>
+      <c r="P72" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="b">
+        <v>0</v>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
           <t>JOSE RICARDO GARCIA PEREIRA RAMALHO</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>SOCIOLOGIA E ANTROPOLOGIA</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>UNIVERSIDADE FEDERAL DO RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>UFRJ</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="V72" t="inlineStr">
         <is>
           <t>SUDESTE</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="W72" t="inlineStr">
         <is>
           <t>RJ</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>RIO DE JANEIRO</t>
         </is>
       </c>
-      <c r="S72" t="n">
+      <c r="Y72" t="n">
         <v>78</v>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>PORTUGUES</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>OUTRAS SOCIOLOGIAS ESPECÍFICAS</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="AC72" t="inlineStr">
         <is>
           <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16255791</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="AD72" t="inlineStr">
         <is>
           <t>16255791</t>
         </is>
       </c>
-      <c r="Y72" t="n">
+      <c r="AE72" t="n">
         <v>760300</v>
       </c>
     </row>

--- a/dados_capes/capes_2021_2024_ia_antro_socio_cienciapolitica.xlsx
+++ b/dados_capes/capes_2021_2024_ia_antro_socio_cienciapolitica.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE72"/>
+  <dimension ref="A1:AE70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1140,50 +1140,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ANTROPOLOGIA</t>
+          <t>CIÊNCIA POLÍTICA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MESTRADO</t>
+          <t>DOUTORADO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BARBARA CINTIA DE RIDDER BARROS</t>
+          <t>PAULO ROBERTO DA SILVA PINTO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>REIVINDICANDO O MATERNAR: DILEMAS, EMOÇÕES E UTOPIA NA EXPERIÊNCIA DA MATERNIDADE.</t>
+          <t>INTELIGÊNCIA ARTIFICIAL E O JUDICIÁRIO NO BRASIL: UMA ANÁLISE DOS DESAFIOS SOCIAIS E A VISÃO DOS JUÍZES (2017-2019)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>A MATERNIDADE É UM TEMA QUE TEM SE TORNADO CADA VEZ MAIS OBJETO DE REFLEXÃO CRÍTICA PELAS MULHERES-MÃES. ISSO DECORRE DOS SEUS PRÓPRIOS MOVIMENTOS PARA TRAZER QUESTÕES DA SUA EXPERIÊNCIA PESSOAL À DISCUSSÃO COLETIVA INTENCIONANDO PROMOVER MELHORES CONDIÇÕES PARA O SEU MATERNAR E PARA AS CRIANÇAS. ESSE TRABALHO DESENVOLVIDO AO LONGO DE SETE ANOS É RESULTADO DA MINHA EXPERIÊNCIA SOMADA ÀS DE DEZENAS DE MULHERES-MÃES ATIVAS NAS DISCUSSÕES SOCIAIS, DE GÊNERO, MATERNIDADE, EMOÇÕES, SAÚDE MENTAL MATERNA, ETC. O OBJETIVO É APRESENTAR COMO ATRAVÉS DE UMA MATERNIDADE CRÍTICA MULHERES-MÃES TÊM RESSIGNIFICADO AS PRÁTICAS DE CUIDADO E REIVINDICADO ASSIM O MATERNAR. POR FIM, PRETENDO ANALISAR COMO NOVAS COMPREENSÕES SOBRE A INFÂNCIA E AS RELAÇÕES TÊM RECONFIGURADO A MATERNIDADE PARA ESSE GRUPO E COMO ATRAVÉS DA ÉTICA DO AMOR MULHERES-MÃES VÊM ENTENDENDO UTOPICAMENTE SEU MATERNAR COMO POSSÍVEL TRANSFORMADOR DO CONTEXTO SOCIAL, POLÍTICO E CULTURAL.</t>
+          <t>A INTELIGÊNCIA ARTIFICIAL É UTILIZADA NOS MAIS VARIADOS CAMPOS E ATIVIDADES HUMANAS, TANTO NA PRODUÇÃO EM TODOS OS SETORES DA ECONOMIA, COMO NO SERVIÇO PÚBLICO, NO ENTRETENIMENTO E NAS TAREFAS DIÁRIAS E PESSOAIS, ENTREGANDO RESULTADOS COM MAIOR PRODUTIVIDADE E PRECISÃO, ASSIM COMO CUSTOS MENORES. DE IGUAL FORMA JÁ SÃO ENCONTRADAS NO JUDICIÁRIO VÁRIAS INICIATIVAS QUE UTILIZAM ESSE FERRAMENTAL NAS ATIVIDADES ROTINEIRAS. NO ENTANTO, DO SEU USO DECORREM DESAFIOS, IMPACTOS SOCIAIS E AMEAÇAS, TAIS COMO DESEMPREGO TECNOLÓGICO, SUBSTITUIÇÃO E COMPETIÇÃO COM HUMANOS, CONCENTRAÇÃO DE RENDA, EXCLUSÃO, CONTROLE E DISCRIMINAÇÃO SOCIAL E USO NA GUERRA, ENTRE OUTROS. TAIS DESAFIOS TRAZEM CONSEQUÊNCIAS EM DIVERSOS CAMPOS E SÃO CENTRAIS NA CIÊNCIA POLÍTICA, DIREITO E ÉTICA. PORTANTO, NO BRASIL, ONDE, EM REGRA QUALQUER CONFLITO É LEVADO A JUÍZO, É JUDICIALIZADO, ARGUMENTA-SE QUE OS JUÍZES SERÃO CHAMADOS À MANIFESTAÇÃO NOS AUTOS SOBRE LESÕES SOCIAIS CAUSADAS PELO USO DA INTELIGÊNCIA ARTIFICIAL. SENDO ASSIM, É NECESSÁRIO SABER SE OS JUÍZES CONHECEM AS AMEAÇAS DECORRENTES PARA A SOCIEDADE E SE CONSIDERAM IMPORTANTE ESTAR PREPARADOS PARA DECIDIR SOBRE AS TENDÊNCIAS, RISCOS E IMPACTOS QUE O TEMA APRESENTA? OU SEJA, COMO PERCEBEM E O QUANTO CONHECEM DE INTELIGÊNCIA ARTIFICIAL? MAS PARA ISSO, É NECESSÁRIO SABER O QUE E COMO PENSAM OS JUÍZES, POIS, COM AS SUAS FUNÇÕES AMPLIADAS E FORTALECIDAS, EM RAZÃO DA DEMOCRATIZAÇÃO EM 1985 E DA CONSTITUIÇÃO FEDERAL DE 1988, TORNARAM-SE ATORES DE SUMA IMPORTÂNCIA NA ESTRUTURA DE PODER DO PAÍS, DETERMINANTES NA SOCIEDADE. LOGO, PARA A COMPREENSÃO DO PAPEL DOS JUÍZES NO OBJETO DESTA TESE, O ESTUDO DE DIMENSÕES COMO EXPANSÃO JUDICIAL, CULTURA DOS JUÍZES, JUDICIALIZAÇÃO, ATIVISMO, DEMOCRACIA, DIREITOS FUNDAMENTAIS, INDEPENDÊNCIA, AUTONOMIA E ACCOUNTABILITY É IMPERATIVO. DESSA FORMA, NO CERNE DA INVESTIGAÇÃO DESTA TESE ESTÃO A INTELIGÊNCIA ARTIFICIAL E OS JUÍZES.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>MATERNITY HAS INCREASINGLY BECOME A SUBJECT OF CRITICAL REFLECTION AMONG WOMEN-MOTHERS. THIS ARISES FROM THEIR OWN MOVEMENTS TO BRING ISSUES FROM THEIR PERSONAL EXPERIENCE INTO COLLECTIVE DISCUSSION, INTENDING TO PROMOTE BETTER CONDITIONS FOR THEIR MOTHERING AND FOR CHILDREN. THIS WORK, DEVELOPED OVER SEVEN YEARS, IS THE RESULT OF MY EXPERIENCE COMBINED WITH THAT OF DOZENS OF ACTIVE WOMEN-MOTHERS ENGAGED IN SOCIAL, GENDER, MATERNITY, EMOTIONS, MATERNAL MENTAL HEALTH DISCUSSIONS, AND MORE. THE OBJECTIVE IS TO PRESENT HOW, THROUGH CRITICAL MATERNITY, WOMEN-MOTHERS HAVE REDEFINED CAREGIVING PRACTICES AND THUS ADVOCATED FOR MOTHERING. FINALLY, I AIM TO ANALYZE HOW NEW UNDERSTANDINGS OF CHILDHOOD HAVE RECONFIGURED MATERNITY FOR THIS GROUP AND HOW, THROUGH THE ETHIC OF LOVE, WOMEN-MOTHERS ARE UTOPICALLY UNDERSTANDING THEIR MOTHERING AS A POTENTIAL TRANSFORMER OF THE SOCIAL, POLITICAL, AND CULTURAL CONTEXT.</t>
+          <t>ARTIFICIAL INTELLIGENCE IS USED IN A WIDE RANGE OF FIELDS AND HUMAN ACTIVITIES, NOT ONLY FOR PRODUCTION IN ALL ECONOMIC FIELDS, BUT ALSO FOR THE PUBLIC SERVICE, FOR ENTERTAINMENT, AND FOR DAILY AND PRIVATE TASKS, DELIVERING GREATER PRODUCTIVITY AND PRECISION, AS WELL AS LOWER COSTS. IN A SIMILAR WAY, THE JUDICIARY IS ALREADY TAKING SEVERAL INITIATIVES FOR THE USE OF THIS TOOL IN ROUTINE ACTIVITIES, MANY IMPLEMENTED. NEVERTHELESS, ITS USE IMPOSES SEVERAL CHALLENGES, SOCIAL IMPACTS, AND THREATS, SUCH AS TECHNOLOGICAL UNEMPLOYMENT, SUBSTITUTION AND COMPETITION WITH HUMANS, CONCENTRATION OF INCOME, EXCLUSION, SOCIAL DISCRIMINATION AND CONTROL, ITS USE IN WAR, AMONG OTHERS. SUCH CHALLENGES HAVE CONSEQUENCES IN SEVERAL FIELDS AND ARE OF CENTRAL IMPORTANCE TO POLITICAL SCIENCE, LAW, AND ETHICS.THEREFORE, IN BRAZIL, WHERE, AS A RULE, ANY CONFLICT THAT IS TAKEN TO JUSTICES, IT´S JUDICIALIZED, IT IS ARGUED THAT THE JUDGES WILL BE CALLED UPON TO MANIFEST IN THE CASE FILE ON SOCIAL INJURIES CAUSED BY THE USE OF ARTIFICIAL INTELLIGENCE. THEREFORE, IS IT NECESSARY TO KNOW WHETHER JUDGES ARE AWARE OF THREATS TO SOCIETY AND WHETHER THEY CONSIDER RELEVANT BEING PREPARED TO DECIDE ABOUT THE TRENDS, RISKS, AND IMPACTS THIS ISSUE PRESENTS? IN OTHER WORDS, HOW DO THEY PERCEIVE AND HOW MUCH DO THEY KNOW ABOUT ARTIFICIAL INTELLIGENCE? IN ORDER TO UNDERSTAND THAT, IT IS NECESSARY TO KNOW HOW JUDGES THINK, SINCE THEIR EXPANDED AND STRENGTHENED FUNCTIONS, AS AN EFFECT OF THE DEMOCRATIZATION IN 1985 AND THE 1988 FEDERAL CONSTITUTION, TURNED THEM INTO ACTORS OF PARAMOUNT IMPORTANCE IN THE COUNTRY’S POWER STRUCTURE AND WITH A DETERMINANT ROLE IN SOCIETY. THEREFORE, TO UNDERSTAND THE ROLE OF JUDGES AS THE OBJECT OF THIS DISSERTATION, IN-DEPTH INTERVIEWS WERE CONDUCTED, AS WELL AS THE STUDY OF DIMENSIONS SUCH AS JUDICIAL EXPANSION, THE CULTURE OF JUDGES, JUDICIALIZATION, ACTIVISM, DEMOCRACY, FUNDAMENTAL AND HUMAN RIGHTS, INDEPENDENCE, AUTONOMY, AND ACCOUNTABILITY. THUS, AS THE CORE OF THIS DISSERTATION RESEARCH ARE ARTIFICIAL INTELLIGENCE AND JUDGES.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MATERNIDADE;ANTROPOLOGIA DAS EMOÇÕES;MATERNAR;UTOPIA</t>
+          <t>JUDICIÁRIO;JUÍZES;JUDICIALIZAÇÃO;POLÍTICA;TECNOLOGIAS DA INFORMAÇÃO E COMUNICAÇÃO;INTELIGÊNCIA ARTIFICIAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>MOTHERHOOD;ANTHROPOLOGY OF EMOTIONS;MOTHERING;UTOPIA</t>
+          <t>JUDICIARY;JUDGES;JUDICIALIZATION;POLITICS;INFORMATION AND COMMUNICATION TECHNOLOGY;ARTIFICIAL INTELLIGENCE</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1193,11 +1193,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Modelos de linguagem &amp; IA generativa</t>
+          <t>IA em sentido estrito</t>
         </is>
       </c>
       <c r="M6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -1206,29 +1206,29 @@
         <v>0</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>LAURA PEREZ GIL</t>
+          <t>LUIS GUSTAVO MELLO GROHMANN</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>ANTROPOLOGIA E ARQUEOLOGIA</t>
+          <t>CIÊNCIA POLÍTICA</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DO PARANÁ</t>
+          <t>UNIVERSIDADE FEDERAL DO RIO GRANDE DO SUL</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>UFPR</t>
+          <t>UFRGS</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1238,16 +1238,16 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>PARANÁ</t>
+          <t>RIO GRANDE DO SUL</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>187</v>
+        <v>250</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1261,21 +1261,21 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>ANTROPOLOGIA / ARQUEOLOGIA</t>
+          <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16053501</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=10964912</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>16053501</t>
+          <t>10964912</t>
         </is>
       </c>
       <c r="AE6" t="n">
-        <v>484110</v>
+        <v>645294</v>
       </c>
     </row>
     <row r="7">
@@ -1290,41 +1290,41 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
+          <t>2022-12-05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PAULO ROBERTO DA SILVA PINTO</t>
+          <t>THIAGO DE OLIVEIRA MEIRELES</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>INTELIGÊNCIA ARTIFICIAL E O JUDICIÁRIO NO BRASIL: UMA ANÁLISE DOS DESAFIOS SOCIAIS E A VISÃO DOS JUÍZES (2017-2019)</t>
+          <t>INTELIGÊNCIA ARTIFICIAL: IMPACTOS SOBRE O MERCADO DE TRABALHO E A DESIGUALDADE DE RENDA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>A INTELIGÊNCIA ARTIFICIAL É UTILIZADA NOS MAIS VARIADOS CAMPOS E ATIVIDADES HUMANAS, TANTO NA PRODUÇÃO EM TODOS OS SETORES DA ECONOMIA, COMO NO SERVIÇO PÚBLICO, NO ENTRETENIMENTO E NAS TAREFAS DIÁRIAS E PESSOAIS, ENTREGANDO RESULTADOS COM MAIOR PRODUTIVIDADE E PRECISÃO, ASSIM COMO CUSTOS MENORES. DE IGUAL FORMA JÁ SÃO ENCONTRADAS NO JUDICIÁRIO VÁRIAS INICIATIVAS QUE UTILIZAM ESSE FERRAMENTAL NAS ATIVIDADES ROTINEIRAS. NO ENTANTO, DO SEU USO DECORREM DESAFIOS, IMPACTOS SOCIAIS E AMEAÇAS, TAIS COMO DESEMPREGO TECNOLÓGICO, SUBSTITUIÇÃO E COMPETIÇÃO COM HUMANOS, CONCENTRAÇÃO DE RENDA, EXCLUSÃO, CONTROLE E DISCRIMINAÇÃO SOCIAL E USO NA GUERRA, ENTRE OUTROS. TAIS DESAFIOS TRAZEM CONSEQUÊNCIAS EM DIVERSOS CAMPOS E SÃO CENTRAIS NA CIÊNCIA POLÍTICA, DIREITO E ÉTICA. PORTANTO, NO BRASIL, ONDE, EM REGRA QUALQUER CONFLITO É LEVADO A JUÍZO, É JUDICIALIZADO, ARGUMENTA-SE QUE OS JUÍZES SERÃO CHAMADOS À MANIFESTAÇÃO NOS AUTOS SOBRE LESÕES SOCIAIS CAUSADAS PELO USO DA INTELIGÊNCIA ARTIFICIAL. SENDO ASSIM, É NECESSÁRIO SABER SE OS JUÍZES CONHECEM AS AMEAÇAS DECORRENTES PARA A SOCIEDADE E SE CONSIDERAM IMPORTANTE ESTAR PREPARADOS PARA DECIDIR SOBRE AS TENDÊNCIAS, RISCOS E IMPACTOS QUE O TEMA APRESENTA? OU SEJA, COMO PERCEBEM E O QUANTO CONHECEM DE INTELIGÊNCIA ARTIFICIAL? MAS PARA ISSO, É NECESSÁRIO SABER O QUE E COMO PENSAM OS JUÍZES, POIS, COM AS SUAS FUNÇÕES AMPLIADAS E FORTALECIDAS, EM RAZÃO DA DEMOCRATIZAÇÃO EM 1985 E DA CONSTITUIÇÃO FEDERAL DE 1988, TORNARAM-SE ATORES DE SUMA IMPORTÂNCIA NA ESTRUTURA DE PODER DO PAÍS, DETERMINANTES NA SOCIEDADE. LOGO, PARA A COMPREENSÃO DO PAPEL DOS JUÍZES NO OBJETO DESTA TESE, O ESTUDO DE DIMENSÕES COMO EXPANSÃO JUDICIAL, CULTURA DOS JUÍZES, JUDICIALIZAÇÃO, ATIVISMO, DEMOCRACIA, DIREITOS FUNDAMENTAIS, INDEPENDÊNCIA, AUTONOMIA E ACCOUNTABILITY É IMPERATIVO. DESSA FORMA, NO CERNE DA INVESTIGAÇÃO DESTA TESE ESTÃO A INTELIGÊNCIA ARTIFICIAL E OS JUÍZES.</t>
+          <t>A APROXIMAÇÃO DA INTELIGÊNCIA ARTIFICIAL DO COTIDIANO DE PESSOAS COMUNS PODE TRAZER IMPACTOS EM DIFERENTES ASPECTOS. UM DE GRANDE IMPORTÂNCIA ESTÁ RELACIONADO AO MERCADO DE TRABALHO E À SUBSTITUIÇÃO DE TRABALHADORES POR INTELIGÊNCIAS ARTIFICIAIS, O QUE PODERIA REDUZIR A PRESENÇA HUMANA NO MERCADO DE TRABALHO. A PARTIR DE DADOS DA RAIS AGREGADOS POR OCUPAÇÃO NO NÍVEL MUNICIPAL E OCUPAÇÃO COM A APLICAÇÃO DE UM ÍNDICE DE VULNERABILIDADE DAS OCUPAÇÕES QUANTO À INTELIGÊNCIA ARTIFICIAL, FOI REALIZADA UMA ANÁLISE SOBRE O MERCADO DE TRABALHO FORMAL BRASILEIRO. EM UM PRIMEIRO MOMENTO, FOI REALIZADA UMA ANÁLISE DESCRITIVA PARA IDENTIFICAÇÃO DE QUAIS AS OCUPAÇÕES MAIS VULNERÁVEIS E SUA IMPORTÂNCIA DENTRO DA FORÇA DE TRABALHO FORMAL NO BRASIL. OS PRIMEIROS RESULTADOS INDICAM QUE AS OCUPAÇÕES MAIS AMEAÇADAS ESTÃO ENTRE AQUELAS COM MAIOR DEMANDA POR ESCOLARIDADE E ESPECIALIZAÇÃO TÉCNICA, REPRESENTANDO UMA PARCELA PEQUENA DO MERCADO DE TRABALHO. POSTERIORMENTE, A PARTIR DE MÉTODOS DE PREDIÇÃO FOI POSSÍVEL MENSURAR O POSSÍVEL IMPACTO DA AMPLIAÇÃO DO USO DA INTELIGÊNCIA ARTIFICIAL SOBRE O NÍVEL DE EMPREGO E A DESIGUALDADE DE RENDA DO TRABALHO. FORAM APLICADOS O MODELO AUTORREGRESSIVO INTEGRADO DE MÉDIAS MÓVEIS) E UMA TÉCNICA DE MACHINE LEARNING (RANDOM FOREST), UTILIZANDO O ÍNDICE DE IMPACTO DE INTELIGÊNCIA ARTIFICIAL COMO PREDITOR. OS RESULTADOS INDICAM QUE O NÍVEL DE EMPREGO NO MERCADO DE TRABALHO FORMAL BRASILEIRO NÃO SERÁ IMPACTADO NEGATIVAMENTE PELA AMPLIAÇÃO DO USO DESSAS TECNOLOGIAS NOS CURTO E MÉDIO PRAZOS. POR OUTRO LADO, FOI ESTIMADO QUE O NÍVEL DE DESIGUALDADE NA RENDA DO TRABALHO TENDE A SE AMPLIAR UTILIZANDO O ÍNDICE DE GINI COMO MEDIDA.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ARTIFICIAL INTELLIGENCE IS USED IN A WIDE RANGE OF FIELDS AND HUMAN ACTIVITIES, NOT ONLY FOR PRODUCTION IN ALL ECONOMIC FIELDS, BUT ALSO FOR THE PUBLIC SERVICE, FOR ENTERTAINMENT, AND FOR DAILY AND PRIVATE TASKS, DELIVERING GREATER PRODUCTIVITY AND PRECISION, AS WELL AS LOWER COSTS. IN A SIMILAR WAY, THE JUDICIARY IS ALREADY TAKING SEVERAL INITIATIVES FOR THE USE OF THIS TOOL IN ROUTINE ACTIVITIES, MANY IMPLEMENTED. NEVERTHELESS, ITS USE IMPOSES SEVERAL CHALLENGES, SOCIAL IMPACTS, AND THREATS, SUCH AS TECHNOLOGICAL UNEMPLOYMENT, SUBSTITUTION AND COMPETITION WITH HUMANS, CONCENTRATION OF INCOME, EXCLUSION, SOCIAL DISCRIMINATION AND CONTROL, ITS USE IN WAR, AMONG OTHERS. SUCH CHALLENGES HAVE CONSEQUENCES IN SEVERAL FIELDS AND ARE OF CENTRAL IMPORTANCE TO POLITICAL SCIENCE, LAW, AND ETHICS.THEREFORE, IN BRAZIL, WHERE, AS A RULE, ANY CONFLICT THAT IS TAKEN TO JUSTICES, IT´S JUDICIALIZED, IT IS ARGUED THAT THE JUDGES WILL BE CALLED UPON TO MANIFEST IN THE CASE FILE ON SOCIAL INJURIES CAUSED BY THE USE OF ARTIFICIAL INTELLIGENCE. THEREFORE, IS IT NECESSARY TO KNOW WHETHER JUDGES ARE AWARE OF THREATS TO SOCIETY AND WHETHER THEY CONSIDER RELEVANT BEING PREPARED TO DECIDE ABOUT THE TRENDS, RISKS, AND IMPACTS THIS ISSUE PRESENTS? IN OTHER WORDS, HOW DO THEY PERCEIVE AND HOW MUCH DO THEY KNOW ABOUT ARTIFICIAL INTELLIGENCE? IN ORDER TO UNDERSTAND THAT, IT IS NECESSARY TO KNOW HOW JUDGES THINK, SINCE THEIR EXPANDED AND STRENGTHENED FUNCTIONS, AS AN EFFECT OF THE DEMOCRATIZATION IN 1985 AND THE 1988 FEDERAL CONSTITUTION, TURNED THEM INTO ACTORS OF PARAMOUNT IMPORTANCE IN THE COUNTRY’S POWER STRUCTURE AND WITH A DETERMINANT ROLE IN SOCIETY. THEREFORE, TO UNDERSTAND THE ROLE OF JUDGES AS THE OBJECT OF THIS DISSERTATION, IN-DEPTH INTERVIEWS WERE CONDUCTED, AS WELL AS THE STUDY OF DIMENSIONS SUCH AS JUDICIAL EXPANSION, THE CULTURE OF JUDGES, JUDICIALIZATION, ACTIVISM, DEMOCRACY, FUNDAMENTAL AND HUMAN RIGHTS, INDEPENDENCE, AUTONOMY, AND ACCOUNTABILITY. THUS, AS THE CORE OF THIS DISSERTATION RESEARCH ARE ARTIFICIAL INTELLIGENCE AND JUDGES.</t>
+          <t>THE APPROXIMATION OF ARTIFICIAL INTELLIGENCE TO THE DAILY LIVES OF ORDINARY PEOPLE CAN BRING IMPACTS IN DIFFERENT ASPECTS. AN IMPORTAND ONE IS RELATED TO THE LABOR MARKET AND THE REPLACEMENT OF WORKERS BY ARTIFICIAL INTELLIGENCE, WHICH COULD REDUCE THE HUMAN PRESENCE IN THE LABOR MARKET. FROM RAIS DATA AGGREGATED BY OCCUPATION AT THE MUNICIPAL LEVEL AND OCCUPATION WITH THE APPLICATION OF AN INDEX OF VULNERABILITY OF OCCUPATIONS REGARDING ARTIFICIAL INTELLIGENCE, AN ANALYSIS WAS CARRIED OUT ON THE BRAZILIAN FORMAL LABOR MARKET. AT FIRST, A DESCRIPTIVE ANALYSIS WAS CARRIED OUT TO IDENTIFY THE MOST VULNERABLE OCCUPATIONS AND THEIR IMPORTANCE FOR THE FORMAL WORKFORCE IN BRAZIL. THE FIRST RESULTS INDICATE THAT THE MOST THREATENED OCCUPATIONS ARE AMONG THOSE WITH THE HIGHEST DEMAND FOR SCHOOLING AND TECHNICAL SPECIALIZATION, REPRESENTING A SMALL PORTION OF THE LABOR MARKET. SUBSEQUENTLY, BASED ON PREDICTION METHODS, IT WAS POSSIBLE TO MEASURE THE POSSIBLE IMPACT OF THE EXPANSION OF THE USE OF ARTIFICIAL INTELLIGENCE ON THE LEVEL OF EMPLOYMENT AND INEQUALITY OF WORK INCOME. THE AUTOREGRESSIVE INTEGRATED MOVING AVERAGE MODEL (ARIMA) AND A MACHINE LEARNING TECHNIQUE (RANDOM FOREST) WERE APPLIED USING THE IMPACT INDEX OF ARTIFICIAL INTELLIGENCE AS PREDICTOR. THE RESULTS INDICATE THAT THE LEVEL OF EMPLOYMENT IN THE BRAZILIAN FORMAL LABOR MARKET WILL NOT BE NEGATIVELY IMPACTED BY THE EXPANSION OF THE USE OF THESE TECHNOLOGIES IN THE SHORT AND MEDIUM TERMS. ON THE OTHER HAND, IT WAS ESTIMATED THAT THE LEVEL OF INEQUALITY IN LABOR INCOME TENDS TO INCREASE USING THE GINI INDEX AS MEASURE.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>JUDICIÁRIO;JUÍZES;JUDICIALIZAÇÃO;POLÍTICA;TECNOLOGIAS DA INFORMAÇÃO E COMUNICAÇÃO;INTELIGÊNCIA ARTIFICIAL</t>
+          <t>INTELIGÊNCIA ARTIFICIAL;MERCADO DE TRABALHO;DESIGUALDADE;RIMA;RANDOM FOREST</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>JUDICIARY;JUDGES;JUDICIALIZATION;POLITICS;INFORMATION AND COMMUNICATION TECHNOLOGY;ARTIFICIAL INTELLIGENCE</t>
+          <t>RANDOM FOREST;ARIMA;ARTIFICIAL INTELLIGENCE;LABOR MARKET;INEQUALITY</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1334,14 +1334,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>IA em sentido estrito</t>
+          <t>Aprendizado de máquina (ML); IA em sentido estrito</t>
         </is>
       </c>
       <c r="M7" t="b">
         <v>1</v>
       </c>
       <c r="N7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="b">
         <v>0</v>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>LUIS GUSTAVO MELLO GROHMANN</t>
+          <t>JOAO PAULO CANDIA VEIGA</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1364,31 +1364,31 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DO RIO GRANDE DO SUL</t>
+          <t>UNIVERSIDADE DE SÃO PAULO</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>UFRGS</t>
+          <t>USP</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>SUL</t>
+          <t>SUDESTE</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>RIO GRANDE DO SUL</t>
+          <t>SÃO PAULO</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
@@ -1407,16 +1407,16 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=10964912</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12685308</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10964912</t>
+          <t>12685308</t>
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>645294</v>
+        <v>1150096</v>
       </c>
     </row>
     <row r="8">
@@ -1431,41 +1431,41 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2022-12-05</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>THIAGO DE OLIVEIRA MEIRELES</t>
+          <t>LUIZA GIMENEZ NONATO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>INTELIGÊNCIA ARTIFICIAL: IMPACTOS SOBRE O MERCADO DE TRABALHO E A DESIGUALDADE DE RENDA</t>
+          <t>RELAÇÕES DE PODER NA ERA DA INTELIGÊNCIA ARTIFICIAL (IA): A COMPETIÇÃO ESTRATÉGICA ENTRE ESTADOS UNIDOS E CHINA PELA LIDERANÇA DA IA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A APROXIMAÇÃO DA INTELIGÊNCIA ARTIFICIAL DO COTIDIANO DE PESSOAS COMUNS PODE TRAZER IMPACTOS EM DIFERENTES ASPECTOS. UM DE GRANDE IMPORTÂNCIA ESTÁ RELACIONADO AO MERCADO DE TRABALHO E À SUBSTITUIÇÃO DE TRABALHADORES POR INTELIGÊNCIAS ARTIFICIAIS, O QUE PODERIA REDUZIR A PRESENÇA HUMANA NO MERCADO DE TRABALHO. A PARTIR DE DADOS DA RAIS AGREGADOS POR OCUPAÇÃO NO NÍVEL MUNICIPAL E OCUPAÇÃO COM A APLICAÇÃO DE UM ÍNDICE DE VULNERABILIDADE DAS OCUPAÇÕES QUANTO À INTELIGÊNCIA ARTIFICIAL, FOI REALIZADA UMA ANÁLISE SOBRE O MERCADO DE TRABALHO FORMAL BRASILEIRO. EM UM PRIMEIRO MOMENTO, FOI REALIZADA UMA ANÁLISE DESCRITIVA PARA IDENTIFICAÇÃO DE QUAIS AS OCUPAÇÕES MAIS VULNERÁVEIS E SUA IMPORTÂNCIA DENTRO DA FORÇA DE TRABALHO FORMAL NO BRASIL. OS PRIMEIROS RESULTADOS INDICAM QUE AS OCUPAÇÕES MAIS AMEAÇADAS ESTÃO ENTRE AQUELAS COM MAIOR DEMANDA POR ESCOLARIDADE E ESPECIALIZAÇÃO TÉCNICA, REPRESENTANDO UMA PARCELA PEQUENA DO MERCADO DE TRABALHO. POSTERIORMENTE, A PARTIR DE MÉTODOS DE PREDIÇÃO FOI POSSÍVEL MENSURAR O POSSÍVEL IMPACTO DA AMPLIAÇÃO DO USO DA INTELIGÊNCIA ARTIFICIAL SOBRE O NÍVEL DE EMPREGO E A DESIGUALDADE DE RENDA DO TRABALHO. FORAM APLICADOS O MODELO AUTORREGRESSIVO INTEGRADO DE MÉDIAS MÓVEIS) E UMA TÉCNICA DE MACHINE LEARNING (RANDOM FOREST), UTILIZANDO O ÍNDICE DE IMPACTO DE INTELIGÊNCIA ARTIFICIAL COMO PREDITOR. OS RESULTADOS INDICAM QUE O NÍVEL DE EMPREGO NO MERCADO DE TRABALHO FORMAL BRASILEIRO NÃO SERÁ IMPACTADO NEGATIVAMENTE PELA AMPLIAÇÃO DO USO DESSAS TECNOLOGIAS NOS CURTO E MÉDIO PRAZOS. POR OUTRO LADO, FOI ESTIMADO QUE O NÍVEL DE DESIGUALDADE NA RENDA DO TRABALHO TENDE A SE AMPLIAR UTILIZANDO O ÍNDICE DE GINI COMO MEDIDA.</t>
+          <t>A INTELIGÊNCIA ARTIFICIAL (IA) TRANSFORMARÁ RADICALMENTE AS SOCIEDADES, SENDO FREQUENTEMENTE CARACTERIZADA COMO UMA DAS TECNOLOGIAS MAIS ESTRATÉGICAS DO SÉCULO XXI. AS DUAS NAÇÕES QUE ESTÃO NA VANGUARDA DESSA COMPETIÇÃO PELA IA SÃO OS EUA E A CHINA – E, PARA AMBOS OS ESTADOS, A BUSCA PELO DOMÍNIO TECNOLÓGICO EM IA ESTÁ OCORRENDO TANTO NA FRENTE COMERCIAL QUANTO NA MILITAR. PARTIMOS DE DUAS QUESTÕES PRINCIPAIS PARA INVESTIGAR A HIPÓTESE DISCUTIDA: NESSE CONTEXTO, PARTIMOS DE DUAS QUESTÕES PRINCIPAIS PARA ORIENTAR AS INVESTIGAÇÕES INICIAIS: A IA PODE SER ENTENDIDA COMO UM ELEMENTO DE PODER SEGUNDO AS TEORIAS DAS RELAÇÕES INTERNACIONAIS? É POSSÍVEL FALAR NA FORMAÇÃO DE UM REGIME INTERNACIONAL PARA A IA? EM NOSSA OPINIÃO, A RECENTE RIVALIDADE ENTRE OS EUA E A CHINA FOI MOTIVADA PELO DESEJO DE GARANTIR UMA POSIÇÃO COMPETITIVA NO SISTEMA INTERNACIONAL, JÁ QUE PEQUIM TOMOU A DECISÃO DE CONSTRUIR SUA LIDERANÇA EM IA. A CHINA TEM ESTABELECIDO SEUS PRÓPRIOS PADRÕES, PRINCÍPIOS, NORMAS E REGULAMENTOS PARA COMPETIR COM AS NAÇÕES OCIDENTAIS E, FINALMENTE, DOMINAR O DESENVOLVIMENTO ECONÔMICO E TECNOLÓGICO. ESSE COMPORTAMENTO LEVOU À COMPETIÇÃO HEGEMÔNICA ENTRE OS EUA E A CHINA, RESULTANDO EM DISPUTAS EM DIVERSAS FRENTES. COMO A LIDERANÇA GLOBAL EM IA EXIGIRÁ ATUAÇÃO PROATIVA NO ESTABELECIMENTO DE REGRAS E NORMAS PARA APLICATIVOS DE IA RESULTANDO NA CONSTRUÇÃO DE UM REGIME INTERNACIONAL, O ESTUDO DESTE TEMA SERVIRÁ A TRÊS PROPÓSITOS PRINCIPAIS. O PRIMEIRO É DISCUTIR O CONCEITO DE PODER, DISTRIBUIÇÃO DE PODER E HEGEMONIA PARA ENTENDER AS RELAÇÕES ENTRE POTÊNCIAS NA ERA DA INTELIGÊNCIA ARTIFICIAL A PARTIR DA COMPETIÇÃO ENTRE OS EUA E A CHINA. EM SEGUNDO LUGAR, APRESENTAR AS EVIDÊNCIAS E OS DESDOBRAMENTOS PRÁTICOS DE QUE A IA CONSISTE EM ELEMENTO DE DISPUTA DE PODER, DELINEAR AS ESTRATÉGIAS DE IA AMERICANAS E CHINESAS E A CONSTRUÇÃO DE LIDERANÇA, TENTANDO IDENTIFICAR COMO ESSAS NAÇÕES ESTÃO PROJETANDO PODER NO SISTEMA INTERNACIONAL A PARTIR DO DESENVOLVIMENTO DA IA. POR FIM, AVALIAR A PROBABILIDADE DE CONSTRUÇÃO DE UM REGIME INTERNACIONAL PARA IA, COM UMA ÚNICA ESTRUTURA DE PRINCÍPIOS E NORMAS.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>THE APPROXIMATION OF ARTIFICIAL INTELLIGENCE TO THE DAILY LIVES OF ORDINARY PEOPLE CAN BRING IMPACTS IN DIFFERENT ASPECTS. AN IMPORTAND ONE IS RELATED TO THE LABOR MARKET AND THE REPLACEMENT OF WORKERS BY ARTIFICIAL INTELLIGENCE, WHICH COULD REDUCE THE HUMAN PRESENCE IN THE LABOR MARKET. FROM RAIS DATA AGGREGATED BY OCCUPATION AT THE MUNICIPAL LEVEL AND OCCUPATION WITH THE APPLICATION OF AN INDEX OF VULNERABILITY OF OCCUPATIONS REGARDING ARTIFICIAL INTELLIGENCE, AN ANALYSIS WAS CARRIED OUT ON THE BRAZILIAN FORMAL LABOR MARKET. AT FIRST, A DESCRIPTIVE ANALYSIS WAS CARRIED OUT TO IDENTIFY THE MOST VULNERABLE OCCUPATIONS AND THEIR IMPORTANCE FOR THE FORMAL WORKFORCE IN BRAZIL. THE FIRST RESULTS INDICATE THAT THE MOST THREATENED OCCUPATIONS ARE AMONG THOSE WITH THE HIGHEST DEMAND FOR SCHOOLING AND TECHNICAL SPECIALIZATION, REPRESENTING A SMALL PORTION OF THE LABOR MARKET. SUBSEQUENTLY, BASED ON PREDICTION METHODS, IT WAS POSSIBLE TO MEASURE THE POSSIBLE IMPACT OF THE EXPANSION OF THE USE OF ARTIFICIAL INTELLIGENCE ON THE LEVEL OF EMPLOYMENT AND INEQUALITY OF WORK INCOME. THE AUTOREGRESSIVE INTEGRATED MOVING AVERAGE MODEL (ARIMA) AND A MACHINE LEARNING TECHNIQUE (RANDOM FOREST) WERE APPLIED USING THE IMPACT INDEX OF ARTIFICIAL INTELLIGENCE AS PREDICTOR. THE RESULTS INDICATE THAT THE LEVEL OF EMPLOYMENT IN THE BRAZILIAN FORMAL LABOR MARKET WILL NOT BE NEGATIVELY IMPACTED BY THE EXPANSION OF THE USE OF THESE TECHNOLOGIES IN THE SHORT AND MEDIUM TERMS. ON THE OTHER HAND, IT WAS ESTIMATED THAT THE LEVEL OF INEQUALITY IN LABOR INCOME TENDS TO INCREASE USING THE GINI INDEX AS MEASURE.</t>
+          <t>AI IS POISED TO RADICALLY TRANSFORM SOCIETIES, OFTEN BEING CHARACTERIZED AS ONE OF THE MOST STRATEGIC TECHNOLOGIES OF THE 21ST CENTURY. THE TWO NATIONS AT THE FOREFRONT OF THIS COMPETITION FOR AI ARE THE US AND CHINA – AND FOR BOTH STATES, THE QUEST FOR TECHNOLOGICAL DOMINANCE IN AI IS TAKING PLACE ON BOTH THE COMMERCIAL AND MILITARY FRONTS. WE START FROM TWO MAIN QUESTIONS TO INVESTIGATE THE HYPOTHESIS DISCUSSED: IN THIS CONTEXT, WE START FROM TWO MAIN QUESTIONS TO GUIDE THE INITIAL INVESTIGATIONS: CAN AI BE UNDERSTOOD AS AN ELEMENT OF POWER ACCORDING TO THEORIES OF INTERNATIONAL RELATIONS? IS IT POSSIBLE TO TALK ABOUT THE FORMATION OF AN INTERNATIONAL REGIME FOR AI? IN OUR OPINION, THE RECENT RIVALRY BETWEEN THE US AND CHINA WAS MOTIVATED BY THE DESIRE TO SECURE A COMPETITIVE POSITION IN THE INTERNATIONAL SYSTEM, AS BEIJING MADE THE DECISION TO BUILD ON ITS LEADERSHIP IN AI. CHINA HAS ESTABLISHED ITS OWN STANDARDS, PRINCIPLES, NORMS AND REGULATIONS TO COMPETE WITH WESTERN NATIONS AND ULTIMATELY DOMINATE ECONOMIC AND TECHNOLOGICAL DEVELOPMENT. THIS BEHAVIOR LED TO HEGEMONIC COMPETITION BETWEEN THE US AND CHINA, RESULTING IN DISPUTES ON SEVERAL FRONTS. AS GLOBAL LEADERSHIP IN AI WILL REQUIRE PROACTIVE ACTION IN ESTABLISHING RULES AND NORMS FOR AI APPLICATIONS RESULTING IN THE CONSTRUCTION OF AN INTERNATIONAL REGIME, STUDYING THIS TOPIC WILL SERVE THREE MAIN PURPOSES. THE FIRST IS TO DISCUSS THE CONCEPT OF POWER, DISTRIBUTION OF POWER AND HEGEMONY TO UNDERSTAND THE RELATIONS BETWEEN POWERS IN THE AGE OF ARTIFICIAL INTELLIGENCE FROM THE COMPETITION BETWEEN THE US AND CHINA. SECONDLY, TO PRESENT THE EVIDENCE AND PRACTICAL DEVELOPMENTS THAT AI IS AN ELEMENT OF POWER DISPUTE, OUTLINE AMERICAN AND CHINESE AI STRATEGIES AND LEADERSHIP CONSTRUCTION, TRYING TO IDENTIFY HOW THESE NATIONS ARE PROJECTING POWER IN THE INTERNATIONAL SYSTEM FROM OF AI DEVELOPMENT. FINALLY, ASSESS THE LIKELIHOOD OF BUILDING AN INTERNATIONAL AI REGIME, WITH A SINGLE FRAMEWORK OF PRINCIPLES AND NORMS.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>INTELIGÊNCIA ARTIFICIAL;MERCADO DE TRABALHO;DESIGUALDADE;RIMA;RANDOM FOREST</t>
+          <t>INTELIGÊNCIA ARTIFICIAL;PODER;HEGEMONIA;ESTADOS UNIDOS;CHINA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>RANDOM FOREST;ARIMA;ARTIFICIAL INTELLIGENCE;LABOR MARKET;INEQUALITY</t>
+          <t>ARTIFICIAL INTELLIGENCE;POWER;HEGEMONY;UNITED STATES;CHINA</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1475,14 +1475,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Aprendizado de máquina (ML); IA em sentido estrito</t>
+          <t>IA em sentido estrito</t>
         </is>
       </c>
       <c r="M8" t="b">
         <v>1</v>
       </c>
       <c r="N8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>JOAO PAULO CANDIA VEIGA</t>
+          <t>YI SHIN TANG</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CIÊNCIA POLÍTICA</t>
+          <t>RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>POLÍTICA INTERNACIONAL</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1548,16 +1548,16 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12685308</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13498574</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>12685308</t>
+          <t>13498574</t>
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>1150096</v>
+        <v>816113</v>
       </c>
     </row>
     <row r="9">
@@ -1572,41 +1572,41 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LUIZA GIMENEZ NONATO</t>
+          <t>JULIAO GONCALVES AMARAL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RELAÇÕES DE PODER NA ERA DA INTELIGÊNCIA ARTIFICIAL (IA): A COMPETIÇÃO ESTRATÉGICA ENTRE ESTADOS UNIDOS E CHINA PELA LIDERANÇA DA IA</t>
+          <t>SUJEITO COLETIVO, LUTAS LGBTQIA+ E A ESQUERDA CONTEMPORÂNEA: UMA ANÁLISE DE CONTEÚDO DA NOÇÃO DE SUJEITO UNIVERSAL CONTINGENTE NOS ESTUDOS SOBRE OS MOVIMENTOS SOCIAIS LGBTQIA+.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>A INTELIGÊNCIA ARTIFICIAL (IA) TRANSFORMARÁ RADICALMENTE AS SOCIEDADES, SENDO FREQUENTEMENTE CARACTERIZADA COMO UMA DAS TECNOLOGIAS MAIS ESTRATÉGICAS DO SÉCULO XXI. AS DUAS NAÇÕES QUE ESTÃO NA VANGUARDA DESSA COMPETIÇÃO PELA IA SÃO OS EUA E A CHINA – E, PARA AMBOS OS ESTADOS, A BUSCA PELO DOMÍNIO TECNOLÓGICO EM IA ESTÁ OCORRENDO TANTO NA FRENTE COMERCIAL QUANTO NA MILITAR. PARTIMOS DE DUAS QUESTÕES PRINCIPAIS PARA INVESTIGAR A HIPÓTESE DISCUTIDA: NESSE CONTEXTO, PARTIMOS DE DUAS QUESTÕES PRINCIPAIS PARA ORIENTAR AS INVESTIGAÇÕES INICIAIS: A IA PODE SER ENTENDIDA COMO UM ELEMENTO DE PODER SEGUNDO AS TEORIAS DAS RELAÇÕES INTERNACIONAIS? É POSSÍVEL FALAR NA FORMAÇÃO DE UM REGIME INTERNACIONAL PARA A IA? EM NOSSA OPINIÃO, A RECENTE RIVALIDADE ENTRE OS EUA E A CHINA FOI MOTIVADA PELO DESEJO DE GARANTIR UMA POSIÇÃO COMPETITIVA NO SISTEMA INTERNACIONAL, JÁ QUE PEQUIM TOMOU A DECISÃO DE CONSTRUIR SUA LIDERANÇA EM IA. A CHINA TEM ESTABELECIDO SEUS PRÓPRIOS PADRÕES, PRINCÍPIOS, NORMAS E REGULAMENTOS PARA COMPETIR COM AS NAÇÕES OCIDENTAIS E, FINALMENTE, DOMINAR O DESENVOLVIMENTO ECONÔMICO E TECNOLÓGICO. ESSE COMPORTAMENTO LEVOU À COMPETIÇÃO HEGEMÔNICA ENTRE OS EUA E A CHINA, RESULTANDO EM DISPUTAS EM DIVERSAS FRENTES. COMO A LIDERANÇA GLOBAL EM IA EXIGIRÁ ATUAÇÃO PROATIVA NO ESTABELECIMENTO DE REGRAS E NORMAS PARA APLICATIVOS DE IA RESULTANDO NA CONSTRUÇÃO DE UM REGIME INTERNACIONAL, O ESTUDO DESTE TEMA SERVIRÁ A TRÊS PROPÓSITOS PRINCIPAIS. O PRIMEIRO É DISCUTIR O CONCEITO DE PODER, DISTRIBUIÇÃO DE PODER E HEGEMONIA PARA ENTENDER AS RELAÇÕES ENTRE POTÊNCIAS NA ERA DA INTELIGÊNCIA ARTIFICIAL A PARTIR DA COMPETIÇÃO ENTRE OS EUA E A CHINA. EM SEGUNDO LUGAR, APRESENTAR AS EVIDÊNCIAS E OS DESDOBRAMENTOS PRÁTICOS DE QUE A IA CONSISTE EM ELEMENTO DE DISPUTA DE PODER, DELINEAR AS ESTRATÉGIAS DE IA AMERICANAS E CHINESAS E A CONSTRUÇÃO DE LIDERANÇA, TENTANDO IDENTIFICAR COMO ESSAS NAÇÕES ESTÃO PROJETANDO PODER NO SISTEMA INTERNACIONAL A PARTIR DO DESENVOLVIMENTO DA IA. POR FIM, AVALIAR A PROBABILIDADE DE CONSTRUÇÃO DE UM REGIME INTERNACIONAL PARA IA, COM UMA ÚNICA ESTRUTURA DE PRINCÍPIOS E NORMAS.</t>
+          <t>A PESQUISA EM QUESTÃO BUSCA MAPEAR A PRODUÇÃO ACADÊMICA SOBRE OS MOVIMENTOS SOCIAIS LGBTQIA+ NO BRASIL, COM O INTUITO DE COMPREENDER COMO OS ESTUDIOSOS TÊM ABORDADO A CONSTRUÇÃO DE UM SUJEITO COLETIVO UNIVERSAL CONTINGENTE. A PARTIR DO PRESSUPOSTO DA FRAGMENTAÇÃO DO SUJEITO COLETIVO EM AÇÕES PELA DIVERSIDADE SEXUAL, A ANÁLISE FOCALIZA A NOÇÃO DE UNIVERSALIDADE CONTINGENTE, DISCUTIDA POR BUTLER, LACLAU E ŽIŽEK, QUE PROPÕEM A UNIVERSALIDADE COMO CHAVE PARA ENTENDER A POLÍTICA DEMOCRÁTICA RADICAL E A AÇÃO DOS MOVIMENTOS SOCIAIS. AS TRANSFORMAÇÕES POLÍTICAS OCORRIDAS NO BRASIL NA SEGUNDA DÉCADA DO SÉCULO XXI, ESPECIALMENTE APÓS JUNHO DE 2013, EXEMPLIFICAM A POSSIBILIDADE DE ARTICULAÇÃO DE SUJEITOS UNIVERSAIS ATRAVÉS DE DISPUTAS HEGEMÔNICAS, UNIFICANDO A ESQUERDA EM TORNO DE OBJETIVOS COMUNS. A PARTIR DE LACLAU, BUTLER E ŽIŽEK, E DA TEORIA DA IDENTIDADE COLETIVA DE MELUCCI, ENTENDEMOS A IDENTIDADE COLETIVA NÃO COMO UM ENTE FIXO, MAS COMO ALGO A SER RECONSTRUÍDO INTERPRETATIVAMENTE. A TEORIA QUEER E A TEORIA INTERSECCIONAL CRITICAM AS CONCEPÇÕES TRADICIONAIS DE IDENTIDADE E PROMOVEM UMA POLÍTICA DE IDENTIDADES EM CONSTANTE TRANSFORMAÇÃO, DESTACANDO A COMPLEXIDADE DAS OPRESSÕES INTERSECCIONAIS. METODOLOGICAMENTE, A PESQUISA É BIBLIOGRÁFICA E DOCUMENTAL, ANALISANDO PUBLICAÇÕES SOBRE MOVIMENTOS LGBTQIA+ NO BRASIL ENTRE 2000 E 2022. UTILIZA A ANÁLISE DE CONTEÚDO CATEGORIAL PARA EXAMINAR COMO O CONCEITO DE SUJEITO COLETIVO É MOBILIZADO NOS ESTUDOS SELECIONADOS. FERRAMENTAS DE MACHINE LEARNING AUXILIARAM NA COLETA E NA ANÁLISE DOS DADOS, AJUDANDO A IDENTIFICAR PADRÕES RELEVANTES. OS DADOS REVELAM UMA DIVERSIDADE DE INSTITUIÇÕES COM PUBLICAÇÕES DE ARTIGOS SOBRE O MOVIMENTO E PREDOMINÂNCIA DAS ÁREAS DE PSICOLOGIA, SOCIOLOGIA E ANTROPOLOGIA. ESTUDOS EMPÍRICOS MOSTRAM UMA TENDÊNCIA DE ARTICULAÇÃO DO MOVIMENTO LGBTQIA+ COM OUTRAS LUTAS SOCIAIS, REFLETINDO A DIVERSIDADE DE SUJEITOS ENVOLVIDOS. AS PARADAS DO ORGULHO LGBTQIA+ DESTACAM-SE COMO UM REPERTÓRIO CENTRAL DE AÇÃO E VISIBILIDADE. OS DADOS MOSTRAM TAMBÉM QUE A RELAÇÃO ENTRE MOVIMENTOS LGBTQIA+ E INSTITUIÇÕES POLÍTICAS É COMPLEXA, ENVOLVENDO TANTO PARCERIAS QUANTO ANTAGONISMOS SIGNIFICATIVOS. A ANÁLISE EVIDENCIA UMA MENOR PRESENÇA DA TEORIA QUEER E UMA MAIOR MOBILIZAÇÃO DO PENSAMENTO INTERSECCIONAL (PRINCIPALMENTE A PARTIR DO ANO DE 2017) USADO PARA ANALISAR DIVERSAS DIMENSÕES DO MOVIMENTO, COMO OPRESSÃO E IDENTIDADE. A INTERNET EMERGE COMO UM FATOR CRUCIAL NA CONSTRUÇÃO DO SUJEITO COLETIVO E NA ATUAÇÃO DOS MILITANTES, DESTACANDO SUA IMPORTÂNCIA PARA O RECONHECIMENTO DE IDENTIDADES E PARA A FORMAÇÃO DE ALIANÇAS ENTRE MOVIMENTOS SOCIAIS. CONCLUI-SE QUE AS MUDANÇAS NAS CONCEPÇÕES DE IDENTIDADE, PROVOCADAS POR TEORIAS QUEER E INTERSECCIONAIS E PELA MOBILIZAÇÃO ONLINE, ABREM CAMINHO PARA A CONSTRUÇÃO DE UMA UNIVERSALIDADE CONTINGENTE. A PESQUISA CONTRIBUI PARA A COMPREENSÃO DAS DINÂMICAS INTERNAS DOS MOVIMENTOS LGBTQIA+ BRASILEIROS E DAS ESTRATÉGIAS DE ARTICULAÇÃO DA ESQUERDA FRENTE ÀS MUDANÇAS POLÍTICAS NO PAÍS.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AI IS POISED TO RADICALLY TRANSFORM SOCIETIES, OFTEN BEING CHARACTERIZED AS ONE OF THE MOST STRATEGIC TECHNOLOGIES OF THE 21ST CENTURY. THE TWO NATIONS AT THE FOREFRONT OF THIS COMPETITION FOR AI ARE THE US AND CHINA – AND FOR BOTH STATES, THE QUEST FOR TECHNOLOGICAL DOMINANCE IN AI IS TAKING PLACE ON BOTH THE COMMERCIAL AND MILITARY FRONTS. WE START FROM TWO MAIN QUESTIONS TO INVESTIGATE THE HYPOTHESIS DISCUSSED: IN THIS CONTEXT, WE START FROM TWO MAIN QUESTIONS TO GUIDE THE INITIAL INVESTIGATIONS: CAN AI BE UNDERSTOOD AS AN ELEMENT OF POWER ACCORDING TO THEORIES OF INTERNATIONAL RELATIONS? IS IT POSSIBLE TO TALK ABOUT THE FORMATION OF AN INTERNATIONAL REGIME FOR AI? IN OUR OPINION, THE RECENT RIVALRY BETWEEN THE US AND CHINA WAS MOTIVATED BY THE DESIRE TO SECURE A COMPETITIVE POSITION IN THE INTERNATIONAL SYSTEM, AS BEIJING MADE THE DECISION TO BUILD ON ITS LEADERSHIP IN AI. CHINA HAS ESTABLISHED ITS OWN STANDARDS, PRINCIPLES, NORMS AND REGULATIONS TO COMPETE WITH WESTERN NATIONS AND ULTIMATELY DOMINATE ECONOMIC AND TECHNOLOGICAL DEVELOPMENT. THIS BEHAVIOR LED TO HEGEMONIC COMPETITION BETWEEN THE US AND CHINA, RESULTING IN DISPUTES ON SEVERAL FRONTS. AS GLOBAL LEADERSHIP IN AI WILL REQUIRE PROACTIVE ACTION IN ESTABLISHING RULES AND NORMS FOR AI APPLICATIONS RESULTING IN THE CONSTRUCTION OF AN INTERNATIONAL REGIME, STUDYING THIS TOPIC WILL SERVE THREE MAIN PURPOSES. THE FIRST IS TO DISCUSS THE CONCEPT OF POWER, DISTRIBUTION OF POWER AND HEGEMONY TO UNDERSTAND THE RELATIONS BETWEEN POWERS IN THE AGE OF ARTIFICIAL INTELLIGENCE FROM THE COMPETITION BETWEEN THE US AND CHINA. SECONDLY, TO PRESENT THE EVIDENCE AND PRACTICAL DEVELOPMENTS THAT AI IS AN ELEMENT OF POWER DISPUTE, OUTLINE AMERICAN AND CHINESE AI STRATEGIES AND LEADERSHIP CONSTRUCTION, TRYING TO IDENTIFY HOW THESE NATIONS ARE PROJECTING POWER IN THE INTERNATIONAL SYSTEM FROM OF AI DEVELOPMENT. FINALLY, ASSESS THE LIKELIHOOD OF BUILDING AN INTERNATIONAL AI REGIME, WITH A SINGLE FRAMEWORK OF PRINCIPLES AND NORMS.</t>
+          <t>THE RESEARCH IN QUESTION AIMS TO MAP ACADEMIC PRODUCTION ON LGBTQIA+ SOCIAL MOVEMENTS IN BRAZIL, WITH THE GOAL OF UNDERSTANDING HOW SCHOLARS HAVE APPROACHED THE CONSTRUCTION OF A CONTINGENT UNIVERSAL COLLECTIVE SUBJECT. BASED ON THE ASSUMPTION OF THE FRAGMENTATION OF THE COLLECTIVE SUBJECT IN ACTIONS FOR SEXUAL DIVERSITY, THE ANALYSIS FOCUSES ON THE NOTION OF CONTINGENT UNIVERSALITY, DISCUSSED BY BUTLER, LACLAU, AND ŽIŽEK, WHO PROPOSE UNIVERSALITY AS A KEY TO UNDERSTANDING RADICAL DEMOCRATIC POLITICS AND THE ACTIONS OF SOCIAL MOVEMENTS. THE POLITICAL TRANSFORMATIONS THAT OCCURRED IN BRAZIL IN THE SECOND DECADE OF THE 21ST CENTURY, ESPECIALLY AFTER JUNE 2013, EXEMPLIFY THE POSSIBILITY OF ARTICULATING UNIVERSAL SUBJECTS THROUGH HEGEMONIC DISPUTES, UNIFYING THE LEFT AROUND COMMON GOALS. DRAWING FROM LACLAU, BUTLER, AND ŽIŽEK, AS WELL AS MELUCCI'S THEORY OF COLLECTIVE IDENTITY, WE UNDERSTAND COLLECTIVE IDENTITY NOT AS A FIXED ENTITY BUT AS SOMETHING TO BE INTERPRETATIVELY RECONSTRUCTED. QUEER THEORY AND INTERSECTIONAL THEORY CRITICIZE TRADITIONAL CONCEPTIONS OF IDENTITY AND PROMOTE A POLITICS OF CONSTANTLY TRANSFORMING IDENTITIES, HIGHLIGHTING THE COMPLEXITY OF INTERSECTIONAL OPPRESSIONS. METHODOLOGICALLY, THE RESEARCH IS BIBLIOGRAPHIC AND DOCUMENTAL, ANALYZING PUBLICATIONS ON LGBTQIA+ MOVEMENTS IN BRAZIL BETWEEN 2000 AND 2022. IT EMPLOYS CATEGORICAL CONTENT ANALYSIS TO EXAMINE HOW THE CONCEPT OF COLLECTIVE SUBJECT IS MOBILIZED IN THE SELECTED STUDIES. MACHINE LEARNING TOOLS AIDED IN THE COLLECTION AND ANALYSIS OF DATA, HELPING TO IDENTIFY RELEVANT PATTERNS. THE DATA REVEAL A DIVERSITY OF INSTITUTIONS PUBLISHING ARTICLES ON THE MOVEMENT AND A PREDOMINANCE OF THE FIELDS OF PSYCHOLOGY, SOCIOLOGY, AND ANTHROPOLOGY. EMPIRICAL STUDIES SHOW A TREND OF ARTICULATION OF THE LGBTQIA+ MOVEMENT WITH OTHER SOCIAL STRUGGLES, REFLECTING THE DIVERSITY OF SUBJECTS INVOLVED. LGBTQIA+ PRIDE PARADES STAND OUT AS A CENTRAL REPERTOIRE OF ACTION AND VISIBILITY. THE DATA ALSO SHOW THAT THE RELATIONSHIP BETWEEN LGBTQIA+ MOVEMENTS AND POLITICAL INSTITUTIONS IS COMPLEX, INVOLVING BOTH PARTNERSHIPS AND SIGNIFICANT ANTAGONISMS. THE ANALYSIS HIGHLIGHTS A LESSER PRESENCE OF QUEER THEORY AND A GREATER MOBILIZATION OF INTERSECTIONAL THOUGHT (MAINLY SINCE 2017) USED TO ANALYZE VARIOUS DIMENSIONS OF THE MOVEMENT, SUCH AS OPPRESSION AND IDENTITY. THE INTERNET EMERGES AS A CRUCIAL FACTOR IN THE CONSTRUCTION OF THE COLLECTIVE SUBJECT AND THE ACTIONS OF ACTIVISTS, HIGHLIGHTING ITS IMPORTANCE FOR THE RECOGNITION OF IDENTITIES AND THE FORMATION OF ALLIANCES BETWEEN SOCIAL MOVEMENTS. IT IS CONCLUDED THAT CHANGES IN CONCEPTIONS OF IDENTITY, DRIVEN BY QUEER AND INTERSECTIONAL THEORIES AND ONLINE MOBILIZATION, PAVE THE WAY FOR THE CONSTRUCTION OF A CONTINGENT UNIVERSALITY. THE RESEARCH CONTRIBUTES TO THE UNDERSTANDING OF THE INTERNAL DYNAMICS OF BRAZILIAN LGBTQIA+ MOVEMENTS AND THE ARTICULATION STRATEGIES OF THE LEFT IN THE FACE OF POLITICAL CHANGES IN THE COUNTRY.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>INTELIGÊNCIA ARTIFICIAL;PODER;HEGEMONIA;ESTADOS UNIDOS;CHINA</t>
+          <t>MOVIMENTO LGBTQIA+;MOVIMENTOS SOCIAIS;SUJEITO COLETIVO;UNIVERSALIDADE;INTERSECCIONALIDADE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ARTIFICIAL INTELLIGENCE;POWER;HEGEMONY;UNITED STATES;CHINA</t>
+          <t>LGBTQIA+ MOVEMENT;SOCIAL MOVEMENTS;COLLECTIVE SUBJECT;UNIVERSALITY;INTERSECTIONALITY</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1616,15 +1616,15 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>IA em sentido estrito</t>
+          <t>Aprendizado de máquina (ML)</t>
         </is>
       </c>
       <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" t="b">
         <v>1</v>
       </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
       <c r="O9" t="b">
         <v>0</v>
       </c>
@@ -1636,22 +1636,22 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>YI SHIN TANG</t>
+          <t>MARCUS ABILIO GOMES PEREIRA</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>RELAÇÕES INTERNACIONAIS</t>
+          <t>CIÊNCIA POLÍTICA</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DE SÃO PAULO</t>
+          <t>UNIVERSIDADE FEDERAL DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>USP</t>
+          <t>UFMG</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1661,16 +1661,16 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>SÃO PAULO</t>
+          <t>MINAS GERAIS</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>124</v>
+        <v>386</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>POLÍTICA INTERNACIONAL</t>
+          <t>NÃO SE APLICA</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1689,16 +1689,16 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13498574</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15695371</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>13498574</t>
+          <t>15695371</t>
         </is>
       </c>
       <c r="AE9" t="n">
-        <v>816113</v>
+        <v>615797</v>
       </c>
     </row>
     <row r="10">
@@ -1717,67 +1717,67 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JULIAO GONCALVES AMARAL</t>
+          <t>LEANDRO ALVES CARNEIRO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SUJEITO COLETIVO, LUTAS LGBTQIA+ E A ESQUERDA CONTEMPORÂNEA: UMA ANÁLISE DE CONTEÚDO DA NOÇÃO DE SUJEITO UNIVERSAL CONTINGENTE NOS ESTUDOS SOBRE OS MOVIMENTOS SOCIAIS LGBTQIA+.</t>
+          <t>A CONSTRUÇÃO DAS REGRAS REGULATÓRIAS: LÓGICAS DAS CONSULTAS PÚBLICAS NORMATIVAS DA ANATEL.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A PESQUISA EM QUESTÃO BUSCA MAPEAR A PRODUÇÃO ACADÊMICA SOBRE OS MOVIMENTOS SOCIAIS LGBTQIA+ NO BRASIL, COM O INTUITO DE COMPREENDER COMO OS ESTUDIOSOS TÊM ABORDADO A CONSTRUÇÃO DE UM SUJEITO COLETIVO UNIVERSAL CONTINGENTE. A PARTIR DO PRESSUPOSTO DA FRAGMENTAÇÃO DO SUJEITO COLETIVO EM AÇÕES PELA DIVERSIDADE SEXUAL, A ANÁLISE FOCALIZA A NOÇÃO DE UNIVERSALIDADE CONTINGENTE, DISCUTIDA POR BUTLER, LACLAU E ŽIŽEK, QUE PROPÕEM A UNIVERSALIDADE COMO CHAVE PARA ENTENDER A POLÍTICA DEMOCRÁTICA RADICAL E A AÇÃO DOS MOVIMENTOS SOCIAIS. AS TRANSFORMAÇÕES POLÍTICAS OCORRIDAS NO BRASIL NA SEGUNDA DÉCADA DO SÉCULO XXI, ESPECIALMENTE APÓS JUNHO DE 2013, EXEMPLIFICAM A POSSIBILIDADE DE ARTICULAÇÃO DE SUJEITOS UNIVERSAIS ATRAVÉS DE DISPUTAS HEGEMÔNICAS, UNIFICANDO A ESQUERDA EM TORNO DE OBJETIVOS COMUNS. A PARTIR DE LACLAU, BUTLER E ŽIŽEK, E DA TEORIA DA IDENTIDADE COLETIVA DE MELUCCI, ENTENDEMOS A IDENTIDADE COLETIVA NÃO COMO UM ENTE FIXO, MAS COMO ALGO A SER RECONSTRUÍDO INTERPRETATIVAMENTE. A TEORIA QUEER E A TEORIA INTERSECCIONAL CRITICAM AS CONCEPÇÕES TRADICIONAIS DE IDENTIDADE E PROMOVEM UMA POLÍTICA DE IDENTIDADES EM CONSTANTE TRANSFORMAÇÃO, DESTACANDO A COMPLEXIDADE DAS OPRESSÕES INTERSECCIONAIS. METODOLOGICAMENTE, A PESQUISA É BIBLIOGRÁFICA E DOCUMENTAL, ANALISANDO PUBLICAÇÕES SOBRE MOVIMENTOS LGBTQIA+ NO BRASIL ENTRE 2000 E 2022. UTILIZA A ANÁLISE DE CONTEÚDO CATEGORIAL PARA EXAMINAR COMO O CONCEITO DE SUJEITO COLETIVO É MOBILIZADO NOS ESTUDOS SELECIONADOS. FERRAMENTAS DE MACHINE LEARNING AUXILIARAM NA COLETA E NA ANÁLISE DOS DADOS, AJUDANDO A IDENTIFICAR PADRÕES RELEVANTES. OS DADOS REVELAM UMA DIVERSIDADE DE INSTITUIÇÕES COM PUBLICAÇÕES DE ARTIGOS SOBRE O MOVIMENTO E PREDOMINÂNCIA DAS ÁREAS DE PSICOLOGIA, SOCIOLOGIA E ANTROPOLOGIA. ESTUDOS EMPÍRICOS MOSTRAM UMA TENDÊNCIA DE ARTICULAÇÃO DO MOVIMENTO LGBTQIA+ COM OUTRAS LUTAS SOCIAIS, REFLETINDO A DIVERSIDADE DE SUJEITOS ENVOLVIDOS. AS PARADAS DO ORGULHO LGBTQIA+ DESTACAM-SE COMO UM REPERTÓRIO CENTRAL DE AÇÃO E VISIBILIDADE. OS DADOS MOSTRAM TAMBÉM QUE A RELAÇÃO ENTRE MOVIMENTOS LGBTQIA+ E INSTITUIÇÕES POLÍTICAS É COMPLEXA, ENVOLVENDO TANTO PARCERIAS QUANTO ANTAGONISMOS SIGNIFICATIVOS. A ANÁLISE EVIDENCIA UMA MENOR PRESENÇA DA TEORIA QUEER E UMA MAIOR MOBILIZAÇÃO DO PENSAMENTO INTERSECCIONAL (PRINCIPALMENTE A PARTIR DO ANO DE 2017) USADO PARA ANALISAR DIVERSAS DIMENSÕES DO MOVIMENTO, COMO OPRESSÃO E IDENTIDADE. A INTERNET EMERGE COMO UM FATOR CRUCIAL NA CONSTRUÇÃO DO SUJEITO COLETIVO E NA ATUAÇÃO DOS MILITANTES, DESTACANDO SUA IMPORTÂNCIA PARA O RECONHECIMENTO DE IDENTIDADES E PARA A FORMAÇÃO DE ALIANÇAS ENTRE MOVIMENTOS SOCIAIS. CONCLUI-SE QUE AS MUDANÇAS NAS CONCEPÇÕES DE IDENTIDADE, PROVOCADAS POR TEORIAS QUEER E INTERSECCIONAIS E PELA MOBILIZAÇÃO ONLINE, ABREM CAMINHO PARA A CONSTRUÇÃO DE UMA UNIVERSALIDADE CONTINGENTE. A PESQUISA CONTRIBUI PARA A COMPREENSÃO DAS DINÂMICAS INTERNAS DOS MOVIMENTOS LGBTQIA+ BRASILEIROS E DAS ESTRATÉGIAS DE ARTICULAÇÃO DA ESQUERDA FRENTE ÀS MUDANÇAS POLÍTICAS NO PAÍS.</t>
+          <t>A PRESENTE TESE TEM COMO OBJETO, A PARTIR DA EXPERIÊNCIA DA ANATEL, COMPREENDER O RESULTADO DOS PROCESSOS NORMATIVOS APÓS A FASE DE CONSULTA PÚBLICA, COMO O ARQUIVAMENTO, OU APROVAÇÃO COM VARIADOS GRAUS DE MODIFICAÇÃO. A METODOLOGIA DE PESQUISA UTILIZA TÉCNICAS DE PROCESSAMENTO DE LINGUAGEM NATURAL PARA EXTRAIR EVIDÊNCIAS A PARTIR DAS MINUTAS NORMATIVAS, DAS CONTRIBUIÇÕES RECEBIDAS, DO REGULAMENTO FINAL APROVADO E DE INFORMAÇÕES DO CONTEXTO INSTITUCIONAL. A PARTIR DE MAIS DE 20 ANOS DE REGULAMENTAÇÃO, O ESTUDO REVELA APRENDIZADOS DA AGÊNCIA AO LONGO DO TEMPO E AS MÚLTIPLAS LÓGICAS QUE REGEM A FASE DE CONSULTA PÚBLICA. ENTRE OS ACHADOS EMPÍRICOS, DESTACA-SE QUE A ACEITAÇÃO DE CONTRIBUIÇÕES É MODULADA POR DIVERSOS FATORES, COMO A MATURIDADE DA MINUTA INICIAL, A SALIÊNCIA DO TEMA PARA DETERMINADOS ATORES, A URGÊNCIA NA REGULAMENTAÇÃO E AS ARENAS ALTERNATIVAS, INCLUSIVE RODADAS ANTERIORES DE DEBATE. POR FIM, SÃO IDENTIFICADOS DILEMAS E TENSÕES DO PROCESSO DE CONSULTA PÚBLICA, BEM COMO SÃO SUGERIDAS FORMAS PARA SEU EQUACIONAMENTO.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>THE RESEARCH IN QUESTION AIMS TO MAP ACADEMIC PRODUCTION ON LGBTQIA+ SOCIAL MOVEMENTS IN BRAZIL, WITH THE GOAL OF UNDERSTANDING HOW SCHOLARS HAVE APPROACHED THE CONSTRUCTION OF A CONTINGENT UNIVERSAL COLLECTIVE SUBJECT. BASED ON THE ASSUMPTION OF THE FRAGMENTATION OF THE COLLECTIVE SUBJECT IN ACTIONS FOR SEXUAL DIVERSITY, THE ANALYSIS FOCUSES ON THE NOTION OF CONTINGENT UNIVERSALITY, DISCUSSED BY BUTLER, LACLAU, AND ŽIŽEK, WHO PROPOSE UNIVERSALITY AS A KEY TO UNDERSTANDING RADICAL DEMOCRATIC POLITICS AND THE ACTIONS OF SOCIAL MOVEMENTS. THE POLITICAL TRANSFORMATIONS THAT OCCURRED IN BRAZIL IN THE SECOND DECADE OF THE 21ST CENTURY, ESPECIALLY AFTER JUNE 2013, EXEMPLIFY THE POSSIBILITY OF ARTICULATING UNIVERSAL SUBJECTS THROUGH HEGEMONIC DISPUTES, UNIFYING THE LEFT AROUND COMMON GOALS. DRAWING FROM LACLAU, BUTLER, AND ŽIŽEK, AS WELL AS MELUCCI'S THEORY OF COLLECTIVE IDENTITY, WE UNDERSTAND COLLECTIVE IDENTITY NOT AS A FIXED ENTITY BUT AS SOMETHING TO BE INTERPRETATIVELY RECONSTRUCTED. QUEER THEORY AND INTERSECTIONAL THEORY CRITICIZE TRADITIONAL CONCEPTIONS OF IDENTITY AND PROMOTE A POLITICS OF CONSTANTLY TRANSFORMING IDENTITIES, HIGHLIGHTING THE COMPLEXITY OF INTERSECTIONAL OPPRESSIONS. METHODOLOGICALLY, THE RESEARCH IS BIBLIOGRAPHIC AND DOCUMENTAL, ANALYZING PUBLICATIONS ON LGBTQIA+ MOVEMENTS IN BRAZIL BETWEEN 2000 AND 2022. IT EMPLOYS CATEGORICAL CONTENT ANALYSIS TO EXAMINE HOW THE CONCEPT OF COLLECTIVE SUBJECT IS MOBILIZED IN THE SELECTED STUDIES. MACHINE LEARNING TOOLS AIDED IN THE COLLECTION AND ANALYSIS OF DATA, HELPING TO IDENTIFY RELEVANT PATTERNS. THE DATA REVEAL A DIVERSITY OF INSTITUTIONS PUBLISHING ARTICLES ON THE MOVEMENT AND A PREDOMINANCE OF THE FIELDS OF PSYCHOLOGY, SOCIOLOGY, AND ANTHROPOLOGY. EMPIRICAL STUDIES SHOW A TREND OF ARTICULATION OF THE LGBTQIA+ MOVEMENT WITH OTHER SOCIAL STRUGGLES, REFLECTING THE DIVERSITY OF SUBJECTS INVOLVED. LGBTQIA+ PRIDE PARADES STAND OUT AS A CENTRAL REPERTOIRE OF ACTION AND VISIBILITY. THE DATA ALSO SHOW THAT THE RELATIONSHIP BETWEEN LGBTQIA+ MOVEMENTS AND POLITICAL INSTITUTIONS IS COMPLEX, INVOLVING BOTH PARTNERSHIPS AND SIGNIFICANT ANTAGONISMS. THE ANALYSIS HIGHLIGHTS A LESSER PRESENCE OF QUEER THEORY AND A GREATER MOBILIZATION OF INTERSECTIONAL THOUGHT (MAINLY SINCE 2017) USED TO ANALYZE VARIOUS DIMENSIONS OF THE MOVEMENT, SUCH AS OPPRESSION AND IDENTITY. THE INTERNET EMERGES AS A CRUCIAL FACTOR IN THE CONSTRUCTION OF THE COLLECTIVE SUBJECT AND THE ACTIONS OF ACTIVISTS, HIGHLIGHTING ITS IMPORTANCE FOR THE RECOGNITION OF IDENTITIES AND THE FORMATION OF ALLIANCES BETWEEN SOCIAL MOVEMENTS. IT IS CONCLUDED THAT CHANGES IN CONCEPTIONS OF IDENTITY, DRIVEN BY QUEER AND INTERSECTIONAL THEORIES AND ONLINE MOBILIZATION, PAVE THE WAY FOR THE CONSTRUCTION OF A CONTINGENT UNIVERSALITY. THE RESEARCH CONTRIBUTES TO THE UNDERSTANDING OF THE INTERNAL DYNAMICS OF BRAZILIAN LGBTQIA+ MOVEMENTS AND THE ARTICULATION STRATEGIES OF THE LEFT IN THE FACE OF POLITICAL CHANGES IN THE COUNTRY.</t>
+          <t>BASED ON ANATEL'S EXPERIENCE, THE PURPOSE OF THIS THESIS IS TO UNDERSTAND THE OUTCOME OF NORMATIVE PROCESSES AFTER THE NOTICE-AND-COMMENT PHASE, SUCH AS CLOSURE, OR APPROVAL WITH DIFFERENT DEGREES OF MODIFICATION. THE RESEARCH METHODOLOGY USES NATURAL LANGUAGE PROCESSING (NLP) TO EXTRACT EVIDENCE FROM THE DRAFT REGULATION, THE CONTRIBUTIONS RECEIVED, THE FINAL RULE AND THE INSTITUTIONAL CONTEXT. BASED ON MORE THAN 20 YEARS OF REGULATION, THE STUDY REVEALS AGENCY'S LEARNINGS OVER TIME AND THE MULTIPLE LOGICS THAT GOVERN THE PUBLIC CONSULTATION PHASE. AMONG THE EMPIRICAL FINDINGS, IT IS WORTH NOTING THAT THE ACCEPTANCE OF CONTRIBUTIONS IS MODULATED BY SEVERAL FACTORS, SUCH AS THE MATURITY OF THE INITIAL DRAFT, THE SALIENCE OF THE TOPIC FOR CERTAIN STAKEHOLDERS, THE URGENCY OF REGULATION AND ALTERNATIVE ARENAS, INCLUDING PREVIOUS DEBATE ROUNDS. FINALLY, THE STUDY IDENTIFIES DILEMMAS AND TENSIONS IN THE NOTICE-AND-COMMENT PROCESS AND SUGGESTS MEANS TO ADDRESS THEM.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MOVIMENTO LGBTQIA+;MOVIMENTOS SOCIAIS;SUJEITO COLETIVO;UNIVERSALIDADE;INTERSECCIONALIDADE</t>
+          <t>REGULAÇÃO;CONSULTA PÚBLICA;REGULAMENTAÇÃO;PROCESSAMENTO DE LINGUAGEM NATURAL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>LGBTQIA+ MOVEMENT;SOCIAL MOVEMENTS;COLLECTIVE SUBJECT;UNIVERSALITY;INTERSECTIONALITY</t>
+          <t>REGULATION;NOTICE-AND-COMMENT;RULEMAKING;NATURAL LANGUAGE PROCESSING</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Aprendizado de máquina (ML)</t>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M10" t="b">
         <v>0</v>
       </c>
       <c r="N10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="b">
         <v>1</v>
       </c>
-      <c r="O10" t="b">
-        <v>0</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>0</v>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>MARCUS ABILIO GOMES PEREIRA</t>
+          <t>DENILSON BANDEIRA COELHO</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1787,31 +1787,31 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DE MINAS GERAIS</t>
+          <t>UNIVERSIDADE DE BRASÍLIA</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>UFMG</t>
+          <t>UNB</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>SUDESTE</t>
+          <t>CENTRO-OESTE</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>MINAS GERAIS</t>
+          <t>DISTRITO FEDERAL</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>386</v>
+        <v>301</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
@@ -1830,16 +1830,16 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15695371</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15771243</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>15695371</t>
+          <t>15771243</t>
         </is>
       </c>
       <c r="AE10" t="n">
-        <v>615797</v>
+        <v>1141673</v>
       </c>
     </row>
     <row r="11">
@@ -1858,54 +1858,54 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LEANDRO ALVES CARNEIRO</t>
+          <t>NILTON GARCIA SAINZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>A CONSTRUÇÃO DAS REGRAS REGULATÓRIAS: LÓGICAS DAS CONSULTAS PÚBLICAS NORMATIVAS DA ANATEL.</t>
+          <t>PADRÕES DE CARREIRA E AMBIÇÃO POLÍTICA DOS REPRESENTANTES NACIONAIS EM SISTEMAS MULTINÍVEL: OS CASOS DE BRASIL E CHILE EM PERSPECTIVA COMPARADA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>A PRESENTE TESE TEM COMO OBJETO, A PARTIR DA EXPERIÊNCIA DA ANATEL, COMPREENDER O RESULTADO DOS PROCESSOS NORMATIVOS APÓS A FASE DE CONSULTA PÚBLICA, COMO O ARQUIVAMENTO, OU APROVAÇÃO COM VARIADOS GRAUS DE MODIFICAÇÃO. A METODOLOGIA DE PESQUISA UTILIZA TÉCNICAS DE PROCESSAMENTO DE LINGUAGEM NATURAL PARA EXTRAIR EVIDÊNCIAS A PARTIR DAS MINUTAS NORMATIVAS, DAS CONTRIBUIÇÕES RECEBIDAS, DO REGULAMENTO FINAL APROVADO E DE INFORMAÇÕES DO CONTEXTO INSTITUCIONAL. A PARTIR DE MAIS DE 20 ANOS DE REGULAMENTAÇÃO, O ESTUDO REVELA APRENDIZADOS DA AGÊNCIA AO LONGO DO TEMPO E AS MÚLTIPLAS LÓGICAS QUE REGEM A FASE DE CONSULTA PÚBLICA. ENTRE OS ACHADOS EMPÍRICOS, DESTACA-SE QUE A ACEITAÇÃO DE CONTRIBUIÇÕES É MODULADA POR DIVERSOS FATORES, COMO A MATURIDADE DA MINUTA INICIAL, A SALIÊNCIA DO TEMA PARA DETERMINADOS ATORES, A URGÊNCIA NA REGULAMENTAÇÃO E AS ARENAS ALTERNATIVAS, INCLUSIVE RODADAS ANTERIORES DE DEBATE. POR FIM, SÃO IDENTIFICADOS DILEMAS E TENSÕES DO PROCESSO DE CONSULTA PÚBLICA, BEM COMO SÃO SUGERIDAS FORMAS PARA SEU EQUACIONAMENTO.</t>
+          <t>ESTA TESE INVESTIGA AS ESTRUTURAS DE OPORTUNIDADE E OS PADRÕES DE AMBIÇÃO POLÍTICA DE PARLAMENTARES BRASILEIROS E CHILENOS, EXPLORANDO COMO OS DESENHOS INSTITUCIONAIS E OS FATORES SOCIAIS MOLDAM SUAS TRAJETÓRIAS POLÍTICAS. ESTRUTURADA EM TRÊS CAPÍTULOS INDEPENDENTES NO FORMATO DE ARTIGOS ACADÊMICOS, A PESQUISA ADOTA UMA ABORDAGEM COMPARATIVA E QUANTITATIVA, UTILIZANDO TÉCNICAS DE MACHINE LEARNING E MODELAGEM ESTATÍSTICA PARA ANALISAR AS DECISÕES ELEITORAIS E OS PADRÕES DE AMBIÇÃO POLÍTICA NESSES DOIS CONTEXTOS. O PRIMEIRO CAPÍTULO APRESENTA UMA REVISÃO DA LITERATURA SOBRE AMBIÇÃO POLÍTICA, REALIZANDO UMA ANÁLISE BIBLIOMÉTRICA QUE MAPEIA O DESENVOLVIMENTO DO CAMPO NO CONTEXTO GLOBAL E SUL-AMERICANO. A PARTIR DA IDENTIFICAÇÃO DE DUAS PRINCIPAIS CORRENTES TEÓRICAS – O NEOINSTITUCIONALISMO DE ESCOLHA RACIONAL E A SOCIOLOGIA POLÍTICA NORTE-AMERICANA –, O CAPÍTULO DISCUTE A FRAGMENTAÇÃO TEÓRICA EXISTENTE E PROPÕE UMA ABORDAGEM MAIS INTEGRATIVA PARA OS ESTUDOS SOBRE CARREIRAS POLÍTICAS. O SEGUNDO CAPÍTULO EXAMINA AS ESCOLHAS ELEITORAIS DOS DEPUTADOS BRASILEIROS E CHILENOS, ANALISANDO COMO DIFERENTES ESTRUTURAS DE OPORTUNIDADE E REFORMAS POLÍTICAS RECENTES INFLUENCIAM SUAS DECISÕES DE CARREIRA. CONSIDERANDO AS ELEIÇÕES DE 2021 NO CHILE E 2022 NO BRASIL, A PESQUISA IDENTIFICA AS DINÂMICAS INSTITUCIONAIS QUE MOLDAM ESTRATÉGIAS POLÍTICAS NOS DOIS PAÍSES, CONTRASTANDO A ESTRUTURA HIERÁRQUICA E CENTRALIZADA DO CHILE COM A FLUIDEZ E A MOBILIDADE POLÍTICA NO BRASIL. O TERCEIRO CAPÍTULO PROPÕE UMA CLASSIFICAÇÃO EMPÍRICA DOS PADRÕES DE AMBIÇÃO POLÍTICA, APLICANDO ALGORITMOS DE RECONHECIMENTO DE PADRÕES PARA INTERPRETAR AS TRAJETÓRIAS DE CARREIRA DOS PARLAMENTARES AO LONGO DO PERÍODO ANALISADO. A PARTIR DESSA TIPOLOGIA, O ESTUDO INVESTIGA O IMPACTO DO GÊNERO NA AMBIÇÃO POLÍTICA, EXAMINANDO SE O GÊNERO DOS PARLAMENTARES É UM FATOR DETERMINANTE NOS PADRÕES DE PROGRESSÃO DE CARREIRA. OS RESULTADOS DEMONSTRAM QUE, EMBORA AS DEPUTADAS BRASILEIRAS APRESENTEM MAIOR AMBIÇÃO ASCENDENTE QUE SEUS COLEGAS HOMENS, ENCONTRAM BARREIRAS INSTITUCIONAIS E PARTIDÁRIAS QUE RESTRINGEM SUA ASCENSÃO AO NÍVEL FEDERAL. NO CHILE, POR OUTRO LADO, A RIGIDEZ INSTITUCIONAL DO SISTEMA POLÍTICO GERA TRAJETÓRIAS MAIS PREVISÍVEIS, REDUZINDO DIFERENÇAS DE GÊNERO NA AMBIÇÃO POLÍTICA. POR MEIO DESSA ANÁLISE COMPARADA, A TESE CONTRIBUI PARA O DEBATE SOBRE COMO DIFERENTES DESENHOS INSTITUCIONAIS ESTRUTURAM OPORTUNIDADES POLÍTICAS E MOLDAM PADRÕES DE CARREIRA PARLAMENTAR. OS ACHADOS INDICAM QUE, EMBORA AS REGRAS DO JOGO POLÍTICO INFLUENCIEM SIGNIFICATIVAMENTE AS ESTRATÉGIAS INDIVIDUAIS DOS PARLAMENTARES, A INTERAÇÃO ENTRE INSTITUIÇÕES, GÊNERO E ESTRUTURA PARTIDÁRIA PODE GERAR DESIGUALDADES NA PROGRESSÃO POLÍTICA, AFETANDO A COMPETITIVIDADE E A REPRESENTATIVIDADE NOS ESPAÇOS DE PODER.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BASED ON ANATEL'S EXPERIENCE, THE PURPOSE OF THIS THESIS IS TO UNDERSTAND THE OUTCOME OF NORMATIVE PROCESSES AFTER THE NOTICE-AND-COMMENT PHASE, SUCH AS CLOSURE, OR APPROVAL WITH DIFFERENT DEGREES OF MODIFICATION. THE RESEARCH METHODOLOGY USES NATURAL LANGUAGE PROCESSING (NLP) TO EXTRACT EVIDENCE FROM THE DRAFT REGULATION, THE CONTRIBUTIONS RECEIVED, THE FINAL RULE AND THE INSTITUTIONAL CONTEXT. BASED ON MORE THAN 20 YEARS OF REGULATION, THE STUDY REVEALS AGENCY'S LEARNINGS OVER TIME AND THE MULTIPLE LOGICS THAT GOVERN THE PUBLIC CONSULTATION PHASE. AMONG THE EMPIRICAL FINDINGS, IT IS WORTH NOTING THAT THE ACCEPTANCE OF CONTRIBUTIONS IS MODULATED BY SEVERAL FACTORS, SUCH AS THE MATURITY OF THE INITIAL DRAFT, THE SALIENCE OF THE TOPIC FOR CERTAIN STAKEHOLDERS, THE URGENCY OF REGULATION AND ALTERNATIVE ARENAS, INCLUDING PREVIOUS DEBATE ROUNDS. FINALLY, THE STUDY IDENTIFIES DILEMMAS AND TENSIONS IN THE NOTICE-AND-COMMENT PROCESS AND SUGGESTS MEANS TO ADDRESS THEM.</t>
+          <t>THIS THESIS INVESTIGATES THE STRUCTURES OF OPPORTUNITY AND PATTERNS OF POLITICAL AMBITION AMONG BRAZILIAN AND CHILEAN LEGISLATORS, EXPLORING HOW INSTITUTIONAL DESIGNS AND SOCIAL DYNAMICS SHAPE THEIR POLITICAL TRAJECTORIES. STRUCTURED INTO THREE INDEPENDENT CHAPTERS IN THE FORMAT OF ACADEMIC ARTICLES, THIS RESEARCH ADOPTS A COMPARATIVE AND QUANTITATIVE APPROACH, EMPLOYING MACHINE LEARNING TECHNIQUES AND STATISTICAL MODELING TO ANALYZE ELECTORAL DECISIONS AND PATTERNS OF POLITICAL AMBITION IN BOTH CONTEXTS. THE FIRST CHAPTER PRESENTS A LITERATURE REVIEW ON POLITICAL AMBITION, CONDUCTING A BIBLIOMETRIC ANALYSIS TO MAP THE DEVELOPMENT OF RESEARCH ON THE TOPIC IN BOTH GLOBAL AND SOUTH AMERICAN CONTEXTS. BY IDENTIFYING TWO DOMINANT THEORETICAL TRADITIONS— RATIONAL CHOICE NEO-INSTITUTIONALISM AND AMERICAN POLITICAL SOCIOLOGY—THE CHAPTER DISCUSSES THE EPISTEMOLOGICAL DIVISION IN THE FIELD AND PROPOSES A MORE INTEGRATIVE APPROACH TO THE STUDY OF POLITICAL CAREERS. THE SECOND CHAPTER EXAMINES THE ELECTORAL CHOICES OF BRAZILIAN AND CHILEAN LEGISLATORS, ANALYZING HOW DIFFERENT OPPORTUNITY STRUCTURES AND RECENT POLITICAL REFORMS INFLUENCE THEIR CAREER DECISIONS. CONSIDERING THE 2021 CHILEAN AND 2022 BRAZILIAN ELECTIONS, THE STUDY IDENTIFIES INSTITUTIONAL DYNAMICS SHAPING POLITICAL STRATEGIES, CONTRASTING CHILE’S HIERARCHICAL AND CENTRALIZED STRUCTURE WITH BRAZIL’S MORE FLUID AND MOBILE POLITICAL CAREERS. THE THIRD CHAPTER PROPOSES AN EMPIRICAL CLASSIFICATION OF POLITICAL AMBITION PATTERNS, APPLYING PATTERN RECOGNITION ALGORITHMS TO INTERPRET CAREER TRAJECTORIES OVER TIME. USING THIS TYPOLOGY, THE STUDY INVESTIGATES THE ROLE OF GENDER IN SHAPING POLITICAL AMBITION, ASSESSING WHETHER GENDER IS A DETERMINANT FACTOR IN CAREER PROGRESSION PATTERNS. THE FINDINGS REVEAL THAT ALTHOUGH BRAZILIAN FEMALE LEGISLATORS EXHIBIT GREATER PROGRESSIVE AMBITION THAN THEIR MALE COUNTERPARTS, THEY FACE INSTITUTIONAL AND PARTISAN BARRIERS THAT RESTRICT THEIR ASCENSION TO THE FEDERAL LEVEL. IN CHILE, BY CONTRAST, THE RIGIDITY OF THE POLITICAL SYSTEM RESULTS IN MORE PREDICTABLE CAREER PATHS, MINIMIZING GENDER DIFFERENCES IN POLITICAL AMBITION. THIS THESIS CONTRIBUTES TO THE BROADER DEBATE ON HOW INSTITUTIONAL DESIGNS STRUCTURE POLITICAL OPPORTUNITIES AND SHAPE PARLIAMENTARY CAREER PATTERNS. THE FINDINGS SUGGEST THAT, WHILE FORMAL POLITICAL RULES SIGNIFICANTLY INFLUENCE INDIVIDUAL STRATEGIES, THE INTERACTION BETWEEN INSTITUTIONS, GENDER, AND PARTY STRUCTURES CREATES BARRIERS TO EQUAL POLITICAL PROGRESSION, AFFECTING COMPETITIVENESS AND REPRESENTATIONAL EQUITY IN POSITIONS OF POWER. BY INTEGRATING INSTITUTIONAL AND SOCIETAL PERSPECTIVES, THIS RESEARCH ENHANCES THE UNDERSTANDING OF HOW POLITICAL CAREERS EVOLVE IN DISTINCT INSTITUTIONAL ENVIRONMENTS AND PROVIDES EMPIRICAL INSIGHTS FOR DISCUSSIONS ON INSTITUTIONAL REFORMS AIMED AT REDUCING GENDER DISPARITIES IN POLITICAL REPRESENTATION.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>REGULAÇÃO;CONSULTA PÚBLICA;REGULAMENTAÇÃO;PROCESSAMENTO DE LINGUAGEM NATURAL</t>
+          <t>AMBIÇÃO POLÍTICA;CARREIRAS PARLAMENTARES;RECONHECIMENTO DE PADRÕES;COMPARAÇÃO BRASIL-CHILE;SISTEMAS ELEITORAIS</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>REGULATION;NOTICE-AND-COMMENT;RULEMAKING;NATURAL LANGUAGE PROCESSING</t>
+          <t>POLITICAL AMBITION;POLITICAL CAREER;PATTERN RECOGNITION;BRAZIL-CHILE COMPARISON;ELECTORAL SYSTEMS</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Correlato</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>Aprendizado de máquina (ML)</t>
         </is>
       </c>
       <c r="M11" t="b">
         <v>0</v>
       </c>
       <c r="N11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="b">
         <v>0</v>
@@ -1914,11 +1914,11 @@
         <v>0</v>
       </c>
       <c r="Q11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>DENILSON BANDEIRA COELHO</t>
+          <t>ADRIANO NERVO CODATO</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1928,31 +1928,31 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DE BRASÍLIA</t>
+          <t>UNIVERSIDADE FEDERAL DO PARANÁ</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>UNB</t>
+          <t>UFPR</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>CENTRO-OESTE</t>
+          <t>SUL</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>DISTRITO FEDERAL</t>
+          <t>PARANÁ</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>301</v>
+        <v>125</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
@@ -1971,16 +1971,16 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15771243</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16471651</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>15771243</t>
+          <t>16471651</t>
         </is>
       </c>
       <c r="AE11" t="n">
-        <v>1141673</v>
+        <v>1993878</v>
       </c>
     </row>
     <row r="12">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DOUTORADO</t>
+          <t>DOUTORADO PROFISSIONAL</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1999,37 +1999,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NILTON GARCIA SAINZ</t>
+          <t>GISELLI CHRISTINA LEAL NICHOLS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PADRÕES DE CARREIRA E AMBIÇÃO POLÍTICA DOS REPRESENTANTES NACIONAIS EM SISTEMAS MULTINÍVEL: OS CASOS DE BRASIL E CHILE EM PERSPECTIVA COMPARADA</t>
+          <t>GUERRA COGNITIVA NAS REDES SOCIAIS: ANÁLISE DAS AMEAÇAS E PROPOSTAS PARA POLÍTICAS PÚBLICAS DO MINISTÉRIO DA DEFESA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ESTA TESE INVESTIGA AS ESTRUTURAS DE OPORTUNIDADE E OS PADRÕES DE AMBIÇÃO POLÍTICA DE PARLAMENTARES BRASILEIROS E CHILENOS, EXPLORANDO COMO OS DESENHOS INSTITUCIONAIS E OS FATORES SOCIAIS MOLDAM SUAS TRAJETÓRIAS POLÍTICAS. ESTRUTURADA EM TRÊS CAPÍTULOS INDEPENDENTES NO FORMATO DE ARTIGOS ACADÊMICOS, A PESQUISA ADOTA UMA ABORDAGEM COMPARATIVA E QUANTITATIVA, UTILIZANDO TÉCNICAS DE MACHINE LEARNING E MODELAGEM ESTATÍSTICA PARA ANALISAR AS DECISÕES ELEITORAIS E OS PADRÕES DE AMBIÇÃO POLÍTICA NESSES DOIS CONTEXTOS. O PRIMEIRO CAPÍTULO APRESENTA UMA REVISÃO DA LITERATURA SOBRE AMBIÇÃO POLÍTICA, REALIZANDO UMA ANÁLISE BIBLIOMÉTRICA QUE MAPEIA O DESENVOLVIMENTO DO CAMPO NO CONTEXTO GLOBAL E SUL-AMERICANO. A PARTIR DA IDENTIFICAÇÃO DE DUAS PRINCIPAIS CORRENTES TEÓRICAS – O NEOINSTITUCIONALISMO DE ESCOLHA RACIONAL E A SOCIOLOGIA POLÍTICA NORTE-AMERICANA –, O CAPÍTULO DISCUTE A FRAGMENTAÇÃO TEÓRICA EXISTENTE E PROPÕE UMA ABORDAGEM MAIS INTEGRATIVA PARA OS ESTUDOS SOBRE CARREIRAS POLÍTICAS. O SEGUNDO CAPÍTULO EXAMINA AS ESCOLHAS ELEITORAIS DOS DEPUTADOS BRASILEIROS E CHILENOS, ANALISANDO COMO DIFERENTES ESTRUTURAS DE OPORTUNIDADE E REFORMAS POLÍTICAS RECENTES INFLUENCIAM SUAS DECISÕES DE CARREIRA. CONSIDERANDO AS ELEIÇÕES DE 2021 NO CHILE E 2022 NO BRASIL, A PESQUISA IDENTIFICA AS DINÂMICAS INSTITUCIONAIS QUE MOLDAM ESTRATÉGIAS POLÍTICAS NOS DOIS PAÍSES, CONTRASTANDO A ESTRUTURA HIERÁRQUICA E CENTRALIZADA DO CHILE COM A FLUIDEZ E A MOBILIDADE POLÍTICA NO BRASIL. O TERCEIRO CAPÍTULO PROPÕE UMA CLASSIFICAÇÃO EMPÍRICA DOS PADRÕES DE AMBIÇÃO POLÍTICA, APLICANDO ALGORITMOS DE RECONHECIMENTO DE PADRÕES PARA INTERPRETAR AS TRAJETÓRIAS DE CARREIRA DOS PARLAMENTARES AO LONGO DO PERÍODO ANALISADO. A PARTIR DESSA TIPOLOGIA, O ESTUDO INVESTIGA O IMPACTO DO GÊNERO NA AMBIÇÃO POLÍTICA, EXAMINANDO SE O GÊNERO DOS PARLAMENTARES É UM FATOR DETERMINANTE NOS PADRÕES DE PROGRESSÃO DE CARREIRA. OS RESULTADOS DEMONSTRAM QUE, EMBORA AS DEPUTADAS BRASILEIRAS APRESENTEM MAIOR AMBIÇÃO ASCENDENTE QUE SEUS COLEGAS HOMENS, ENCONTRAM BARREIRAS INSTITUCIONAIS E PARTIDÁRIAS QUE RESTRINGEM SUA ASCENSÃO AO NÍVEL FEDERAL. NO CHILE, POR OUTRO LADO, A RIGIDEZ INSTITUCIONAL DO SISTEMA POLÍTICO GERA TRAJETÓRIAS MAIS PREVISÍVEIS, REDUZINDO DIFERENÇAS DE GÊNERO NA AMBIÇÃO POLÍTICA. POR MEIO DESSA ANÁLISE COMPARADA, A TESE CONTRIBUI PARA O DEBATE SOBRE COMO DIFERENTES DESENHOS INSTITUCIONAIS ESTRUTURAM OPORTUNIDADES POLÍTICAS E MOLDAM PADRÕES DE CARREIRA PARLAMENTAR. OS ACHADOS INDICAM QUE, EMBORA AS REGRAS DO JOGO POLÍTICO INFLUENCIEM SIGNIFICATIVAMENTE AS ESTRATÉGIAS INDIVIDUAIS DOS PARLAMENTARES, A INTERAÇÃO ENTRE INSTITUIÇÕES, GÊNERO E ESTRUTURA PARTIDÁRIA PODE GERAR DESIGUALDADES NA PROGRESSÃO POLÍTICA, AFETANDO A COMPETITIVIDADE E A REPRESENTATIVIDADE NOS ESPAÇOS DE PODER.</t>
+          <t>A GUERRA COGNITIVA É UM FENÔMENO EM CRESCIMENTO, CONDUZIDO NO DOMÍNIO DA MENTE HUMANA, QUE ESTÁ REVOLUCIONANDO A FORMA COMO AS INFORMAÇÕES SÃO COMPARTILHADAS E INTERPRETADAS NAS REDES SOCIAIS. A DISSEMINAÇÃO DA DESINFORMAÇÃO E FAKE NEWS, IMPULSIONADA POR TECNOLOGIAS AVANÇADAS COMO INTELIGÊNCIA ARTIFICIAL (IA), ALGORITMOS E BIG DATA, INTENSIFICA A COMPLEXIDADE DESSAS ESTRATÉGIAS, COM O PROPÓSITO DE MANIPULAR O PENSAMENTO E O COMPORTAMENTO DOS INDIVÍDUOS. A ANÁLISE DESTE NOVO TIPO DE GUERRA E SUAS IMPLICAÇÕES GLOBAIS ORIENTA ESTE ESTUDO, CUJO OBJETIVO É FORNECER SUBSÍDIOS PARA A FORMULAÇÃO DE POLÍTICAS PÚBLICAS PELO MINISTÉRIO DA DEFESA (MD) CONTRA AS AMEAÇAS À EXPRESSÃO PSICOSSOCIAL DO PODER NACIONAL DECORRENTES DA GUERRA COGNITIVA NAS REDES SOCIAIS. PARA ALCANÇAR ESSE OBJETIVO, FOI EMPREGADA UMA ABORDAGEM DE TRIANGULAÇÃO DE MÉTODOS QUALITATIVOS, INCLUINDO PESQUISA BIBLIOGRÁFICA, REVISÃO DA LITERATURA, MÉTODO EX-POST FACTO, ANÁLISE COMPARATIVA E SURVEY. ESTA PESQUISA SE DESTACA NÃO APENAS POR SUA INOVAÇÃO COM O TEMA, MAS TAMBÉM PELA COMPLEXIDADE EVIDENCIADA POR MEIO DA INTEGRAÇÃO DE CONHECIMENTOS DE DIVERSAS ÁREAS. OS RESULTADOS DEMONSTRAM QUE A MANIPULAÇÃO DA INFORMAÇÃO E DAS PERCEPÇÕES PÚBLICAS NAS REDES SOCIAIS É UMA ARMA CENTRAL DA GUERRA COGNITIVA, EXPLORANDO FRAGILIDADES DO CÉREBRO PARA INFLUENCIAR EMOÇÕES E COMPORTAMENTOS, E DESESTABILIZAR SOCIEDADES DEMOCRÁTICAS. EVENTOS RECENTES NO BRASIL ILUSTRAM COMO ESSA DINÂMICA SE DESENVOLVE, DESTACANDO VULNERABILIDADES SIGNIFICATIVAS NA EXPRESSÃO PSICOSSOCIAL DO PODER NACIONAL. DIANTE DA CRESCENTE INFLUÊNCIA DA GUERRA COGNITIVA NAS REDES SOCIAIS E DE SUAS IMPLICAÇÕES GLOBAIS, ESTE ESTUDO OFERECE IMPORTANTES CONTRIBUIÇÕES PARA A FORMULAÇÃO DE POLÍTICAS PÚBLICAS DE DEFESA NACIONAL. ALÉM DISSO, SUAS RECOMENDAÇÕES APRESENTAM UMA APLICABILIDADE CONCRETA, DELINEANDO UM CONJUNTO DE MEDIDAS EXECUTÁVEIS.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>THIS THESIS INVESTIGATES THE STRUCTURES OF OPPORTUNITY AND PATTERNS OF POLITICAL AMBITION AMONG BRAZILIAN AND CHILEAN LEGISLATORS, EXPLORING HOW INSTITUTIONAL DESIGNS AND SOCIAL DYNAMICS SHAPE THEIR POLITICAL TRAJECTORIES. STRUCTURED INTO THREE INDEPENDENT CHAPTERS IN THE FORMAT OF ACADEMIC ARTICLES, THIS RESEARCH ADOPTS A COMPARATIVE AND QUANTITATIVE APPROACH, EMPLOYING MACHINE LEARNING TECHNIQUES AND STATISTICAL MODELING TO ANALYZE ELECTORAL DECISIONS AND PATTERNS OF POLITICAL AMBITION IN BOTH CONTEXTS. THE FIRST CHAPTER PRESENTS A LITERATURE REVIEW ON POLITICAL AMBITION, CONDUCTING A BIBLIOMETRIC ANALYSIS TO MAP THE DEVELOPMENT OF RESEARCH ON THE TOPIC IN BOTH GLOBAL AND SOUTH AMERICAN CONTEXTS. BY IDENTIFYING TWO DOMINANT THEORETICAL TRADITIONS— RATIONAL CHOICE NEO-INSTITUTIONALISM AND AMERICAN POLITICAL SOCIOLOGY—THE CHAPTER DISCUSSES THE EPISTEMOLOGICAL DIVISION IN THE FIELD AND PROPOSES A MORE INTEGRATIVE APPROACH TO THE STUDY OF POLITICAL CAREERS. THE SECOND CHAPTER EXAMINES THE ELECTORAL CHOICES OF BRAZILIAN AND CHILEAN LEGISLATORS, ANALYZING HOW DIFFERENT OPPORTUNITY STRUCTURES AND RECENT POLITICAL REFORMS INFLUENCE THEIR CAREER DECISIONS. CONSIDERING THE 2021 CHILEAN AND 2022 BRAZILIAN ELECTIONS, THE STUDY IDENTIFIES INSTITUTIONAL DYNAMICS SHAPING POLITICAL STRATEGIES, CONTRASTING CHILE’S HIERARCHICAL AND CENTRALIZED STRUCTURE WITH BRAZIL’S MORE FLUID AND MOBILE POLITICAL CAREERS. THE THIRD CHAPTER PROPOSES AN EMPIRICAL CLASSIFICATION OF POLITICAL AMBITION PATTERNS, APPLYING PATTERN RECOGNITION ALGORITHMS TO INTERPRET CAREER TRAJECTORIES OVER TIME. USING THIS TYPOLOGY, THE STUDY INVESTIGATES THE ROLE OF GENDER IN SHAPING POLITICAL AMBITION, ASSESSING WHETHER GENDER IS A DETERMINANT FACTOR IN CAREER PROGRESSION PATTERNS. THE FINDINGS REVEAL THAT ALTHOUGH BRAZILIAN FEMALE LEGISLATORS EXHIBIT GREATER PROGRESSIVE AMBITION THAN THEIR MALE COUNTERPARTS, THEY FACE INSTITUTIONAL AND PARTISAN BARRIERS THAT RESTRICT THEIR ASCENSION TO THE FEDERAL LEVEL. IN CHILE, BY CONTRAST, THE RIGIDITY OF THE POLITICAL SYSTEM RESULTS IN MORE PREDICTABLE CAREER PATHS, MINIMIZING GENDER DIFFERENCES IN POLITICAL AMBITION. THIS THESIS CONTRIBUTES TO THE BROADER DEBATE ON HOW INSTITUTIONAL DESIGNS STRUCTURE POLITICAL OPPORTUNITIES AND SHAPE PARLIAMENTARY CAREER PATTERNS. THE FINDINGS SUGGEST THAT, WHILE FORMAL POLITICAL RULES SIGNIFICANTLY INFLUENCE INDIVIDUAL STRATEGIES, THE INTERACTION BETWEEN INSTITUTIONS, GENDER, AND PARTY STRUCTURES CREATES BARRIERS TO EQUAL POLITICAL PROGRESSION, AFFECTING COMPETITIVENESS AND REPRESENTATIONAL EQUITY IN POSITIONS OF POWER. BY INTEGRATING INSTITUTIONAL AND SOCIETAL PERSPECTIVES, THIS RESEARCH ENHANCES THE UNDERSTANDING OF HOW POLITICAL CAREERS EVOLVE IN DISTINCT INSTITUTIONAL ENVIRONMENTS AND PROVIDES EMPIRICAL INSIGHTS FOR DISCUSSIONS ON INSTITUTIONAL REFORMS AIMED AT REDUCING GENDER DISPARITIES IN POLITICAL REPRESENTATION.</t>
+          <t>COGNITIVE WARFARE IS A GROWING PHENOMENON, CONDUCTED IN THE DOMAIN OF THE HUMAN MIND, THAT IS REVOLUTIONIZING THE WAY INFORMATION IS SHARED AND INTERPRETED ON SOCIAL NETWORKS. THE DISSEMINATION OF DISINFORMATION AND FAKE NEWS, DRIVEN BY ADVANCED TECHNOLOGIES SUCH AS ARTIFICIAL INTELLIGENCE (AI), ALGORITHMS, AND BIG DATA, INTENSIFIES THE COMPLEXITY OF THESE STRATEGIES, WITH THE PURPOSE OF MANIPULATING THE THOUGHTS AND BEHAVIOR OF INDIVIDUALS. THE ANALYSIS OF THIS NEW TYPE OF WARFARE AND ITS GLOBAL IMPLICATIONS GUIDES THIS STUDY, WHOSE OBJECTIVE IS TO PROVIDE SUBSIDIES FOR THE FORMULATION OF PUBLIC POLICIES BY THE MINISTRY OF DEFENSE (MD) AGAINST THREATS TO THE PSYCHOSOCIAL EXPRESSION OF NATIONAL POWER RESULTING FROM COGNITIVE WARFARE ON SOCIAL NETWORKS. TO ACHIEVE THIS OBJECTIVE, A TRIANGULATION APPROACH OF QUALITATIVE METHODS WAS EMPLOYED, INCLUDING BIBLIOGRAPHICAL RESEARCH, LITERATURE REVIEW, EX- POST FACTO METHOD, COMPARATIVE ANALYSIS, AND SURVEY. THIS RESEARCH STANDS OUT NOT ONLY FOR ITS INNOVATION WITH THE THEME BUT ALSO FOR THE COMPLEXITY EVIDENCED THROUGH THE INTEGRATION OF KNOWLEDGE FROM VARIOUS AREAS. THE RESULTS DEMONSTRATE THAT THE MANIPULATION OF INFORMATION AND PUBLIC PERCEPTIONS ON SOCIAL NETWORKS IS A CENTRAL WEAPON OF COGNITIVE WARFARE, EXPLOITING BRAIN VULNERABILITIES TO INFLUENCE EMOTIONS AND BEHAVIORS AND DESTABILIZE DEMOCRATIC SOCIETIES. RECENT EVENTS IN BRAZIL ILLUSTRATE HOW THIS DYNAMIC DEVELOPS, HIGHLIGHTING SIGNIFICANT VULNERABILITIES IN THE PSYCHOSOCIAL EXPRESSION OF NATIONAL POWER. GIVEN THE GROWING INFLUENCE OF COGNITIVE WARFARE ON SOCIAL NETWORKS AND ITS GLOBAL IMPLICATIONS, THIS STUDY OFFERS IMPORTANT CONTRIBUTIONS TO THE FORMULATION OF NATIONAL DEFENSE PUBLIC POLICIES. IN ADDITION, ITS RECOMMENDATIONS PRESENT A CONCRETE APPLICABILITY, OUTLINING A SET OF EXECUTABLE MEASURES.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AMBIÇÃO POLÍTICA;CARREIRAS PARLAMENTARES;RECONHECIMENTO DE PADRÕES;COMPARAÇÃO BRASIL-CHILE;SISTEMAS ELEITORAIS</t>
+          <t>GUERRA COGNITIVA;REDES SOCIAIS;DESINFORMAÇÃO;DEFESA NACIONAL;POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>POLITICAL AMBITION;POLITICAL CAREER;PATTERN RECOGNITION;BRAZIL-CHILE COMPARISON;ELECTORAL SYSTEMS</t>
+          <t>COGNITIVE WARFARE;SOCIAL NETWORKS;DISINFORMATION;NATIONAL DEFENSE;PUBLIC POLICIES</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2039,61 +2039,61 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Aprendizado de máquina (ML)</t>
+          <t>IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="b">
         <v>1</v>
       </c>
-      <c r="O12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="b">
-        <v>0</v>
-      </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>ADRIANO NERVO CODATO</t>
+          <t>CLAUDIO RODRIGUES CORREA</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CIÊNCIA POLÍTICA</t>
+          <t>ESTUDOS MARÍTIMOS</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DO PARANÁ</t>
+          <t>ESCOLA DE GUERRA NAVAL</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>UFPR</t>
+          <t>EGN</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>SUL</t>
+          <t>SUDESTE</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>PARANÁ</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>125</v>
+        <v>199</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16471651</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16722764</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>16471651</t>
+          <t>16722764</t>
         </is>
       </c>
       <c r="AE12" t="n">
-        <v>1993878</v>
+        <v>2757585</v>
       </c>
     </row>
     <row r="13">
@@ -2132,45 +2132,45 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DOUTORADO PROFISSIONAL</t>
+          <t>MESTRADO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2021-02-15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GISELLI CHRISTINA LEAL NICHOLS</t>
+          <t>DANILO GONCALVES DOS SANTOS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GUERRA COGNITIVA NAS REDES SOCIAIS: ANÁLISE DAS AMEAÇAS E PROPOSTAS PARA POLÍTICAS PÚBLICAS DO MINISTÉRIO DA DEFESA</t>
+          <t>TEM QUE SER ASSIM! UM ESTUDO DE INSTRUMENTOS DETERMINANTES DE CONFORMIDADE DA BUROCRACIA PERNAMBUCANA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>A GUERRA COGNITIVA É UM FENÔMENO EM CRESCIMENTO, CONDUZIDO NO DOMÍNIO DA MENTE HUMANA, QUE ESTÁ REVOLUCIONANDO A FORMA COMO AS INFORMAÇÕES SÃO COMPARTILHADAS E INTERPRETADAS NAS REDES SOCIAIS. A DISSEMINAÇÃO DA DESINFORMAÇÃO E FAKE NEWS, IMPULSIONADA POR TECNOLOGIAS AVANÇADAS COMO INTELIGÊNCIA ARTIFICIAL (IA), ALGORITMOS E BIG DATA, INTENSIFICA A COMPLEXIDADE DESSAS ESTRATÉGIAS, COM O PROPÓSITO DE MANIPULAR O PENSAMENTO E O COMPORTAMENTO DOS INDIVÍDUOS. A ANÁLISE DESTE NOVO TIPO DE GUERRA E SUAS IMPLICAÇÕES GLOBAIS ORIENTA ESTE ESTUDO, CUJO OBJETIVO É FORNECER SUBSÍDIOS PARA A FORMULAÇÃO DE POLÍTICAS PÚBLICAS PELO MINISTÉRIO DA DEFESA (MD) CONTRA AS AMEAÇAS À EXPRESSÃO PSICOSSOCIAL DO PODER NACIONAL DECORRENTES DA GUERRA COGNITIVA NAS REDES SOCIAIS. PARA ALCANÇAR ESSE OBJETIVO, FOI EMPREGADA UMA ABORDAGEM DE TRIANGULAÇÃO DE MÉTODOS QUALITATIVOS, INCLUINDO PESQUISA BIBLIOGRÁFICA, REVISÃO DA LITERATURA, MÉTODO EX-POST FACTO, ANÁLISE COMPARATIVA E SURVEY. ESTA PESQUISA SE DESTACA NÃO APENAS POR SUA INOVAÇÃO COM O TEMA, MAS TAMBÉM PELA COMPLEXIDADE EVIDENCIADA POR MEIO DA INTEGRAÇÃO DE CONHECIMENTOS DE DIVERSAS ÁREAS. OS RESULTADOS DEMONSTRAM QUE A MANIPULAÇÃO DA INFORMAÇÃO E DAS PERCEPÇÕES PÚBLICAS NAS REDES SOCIAIS É UMA ARMA CENTRAL DA GUERRA COGNITIVA, EXPLORANDO FRAGILIDADES DO CÉREBRO PARA INFLUENCIAR EMOÇÕES E COMPORTAMENTOS, E DESESTABILIZAR SOCIEDADES DEMOCRÁTICAS. EVENTOS RECENTES NO BRASIL ILUSTRAM COMO ESSA DINÂMICA SE DESENVOLVE, DESTACANDO VULNERABILIDADES SIGNIFICATIVAS NA EXPRESSÃO PSICOSSOCIAL DO PODER NACIONAL. DIANTE DA CRESCENTE INFLUÊNCIA DA GUERRA COGNITIVA NAS REDES SOCIAIS E DE SUAS IMPLICAÇÕES GLOBAIS, ESTE ESTUDO OFERECE IMPORTANTES CONTRIBUIÇÕES PARA A FORMULAÇÃO DE POLÍTICAS PÚBLICAS DE DEFESA NACIONAL. ALÉM DISSO, SUAS RECOMENDAÇÕES APRESENTAM UMA APLICABILIDADE CONCRETA, DELINEANDO UM CONJUNTO DE MEDIDAS EXECUTÁVEIS.</t>
+          <t>ESSA DISSERTAÇÃO FEZ UMA ANÁLISE EXPLORATÓRIA EM TORNO DE AGÊNCIAS DO PODER EXECUTIVO DO GOVERNO DO ESTADO DE PERNAMBUCO, SEU PRINCIPAL OBJETIVO FOI A IDENTIFICAÇÃO DE FERRAMENTAS VOLTADAS À CONFORMIDADE DOS BUROCRATAS. IDENTIFICÁ-LAS TEM FUNÇÃO NA CATEGORIZAÇÃO DAS ORGANIZAÇÕES EM UMA TIPOLOGIA ORIGINAL CUJAS BASES SÃO ESTUDOS SOBRE MODELOS BUROCRÁTICOS GERENCIAIS. A TIPOLOGIA OBSERVA DUAS DIMENSÕES, X E Y. X DIZ RESPEITO AO QUE ESTÁ DESCRITO SOBRE OS SERVIÇOS A SEREM DESEMPENHADOS, E Y, INSTRUMENTOS VOLTADOS PARA QUE AS AÇÕES DOS AGENTES SEJAM MAIS PRÓXIMAS OU IDÊNTICAS AO QUE ESTÁ ESCRITO. PARA FAZER A IDENTIFICAÇÃO DESSES INSTRUMENTOS, CONSEQUENTEMENTE, OBSERVAR AS DIMENSÕES, FOI ELABORADO UM FRAMEWORK DE MINERAÇÃO DE TEXTO, UM CONJUNTO DE TÉCNICAS COMPUTACIONAIS PENSADAS PARA A IDENTIFICAÇÃO DE TRECHOS ÚTEIS E RELEVANTES (DE ACORDO COM O OBJETIVO) PRESENTES EM UM BANCO DE DADOS TEXTUAIS E NÃO ESTRUTURADOS. FOI ESCOLHIDA A TÉCNICA POR TRÊS MOTIVOS, PRIMEIRO A SUA CLARA UTILIDADE PARA A IDENTIFICAÇÃO DE TRECHOS EM DOCUMENTOS OFICIAIS QUE INSTITUCIONALIZAM AS FERRAMENTAS BUSCADAS, SEGUNDO POR SE TRATAR DE UMA TÉCNICA DE MACHINE LEARNING QUE POSSIBILITA O SEU INCREMENTO CONSTANTE, E POR FIM, SER APLICÁVEL COM SOFTWARES GRATUITOS E QUE PERMITEM REPLICABILIDADE DE MANEIRA SIMPLES, COMO O FOXIT PDF E O RSTUDIO. PERNAMBUCO FOI ESCOLHIDO COMO CASO PARA A APLICAÇÃO DO FRAMEWORK PORQUE SEU SISTEMA DE AVALIAÇÃO DE DESEMPENHO, PARA AS ENTIDADES SUBMETIDAS A ELE, GARANTE QUE TAIS INSTRUMENTOS POSSAM SER IDENTIFICADOS EM UM GRUPO MAIS ESPECÍFICO DE DOCUMENTOS. OS RESULTADOS ENCONTRADOS, PARA AS 20 ORGANIZAÇÕES OBSERVADAS, INDICAM QUE A MAIORIA DELAS SÃO DO TIPO 2B E APENAS DUAS DO TIPO 1A (RESPECTIVAMENTE, SERIA UMA “ORGANIZAÇÃO IDEAL” OU PRÓXIMO A ISSO, E O PIOR TIPO, UMA “ORGANIZAÇÃO CAÓTICA E FRACA”), MAS, MESMO ASSIM, APENAS DUAS ORGANIZAÇÕES NÃO APRESENTARAM FALTA DE INSTRUMENTOS SIGNIFICATIVOS. DEVIDO À COMPLEXIDADE TEÓRICA EM DESENVOLVER UMA TIPOLOGIA E UM FRAMEWORK DE APLICAÇÃO PARA A MESMA, OS DOIS PRIMEIROS CAPÍTULOS SÃO REVISÕES DE LITERATURA FOCADAS EM BUROCRACIAS, MODELOS GERENCIAIS E COMO OBSERVAR SUAS CARACTERÍSTICAS, POR FIM O TERCEIRO CAPÍTULO MOSTRA A APLICABILIDADE E RESULTADOS NO CASO PERNAMBUCO. EM SUMA, ESSE TRABALHO COM BASE NUMA REVISÃO DE LITERATURA CRIA UMA TIPOLOGIA FOCADA EM ORGANIZAÇÕES BUROCRÁTICAS E SEUS INSTRUMENTOS FORMAIS VOLTADOS A CONFORMIDADE E PERFORMANCE, ENTÃO DESENVOLVE UM FRAMEWORK PARA A IDENTIFICAÇÃO DESSAS E APLICAÇÃO DA TIPOLOGIA, EM SEGUIDA O COLOCA EM PRÁTICA AO ANALISAR ENTIDADES DO GOVERNO ESTADUAL DE PERNAMBUCO.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>COGNITIVE WARFARE IS A GROWING PHENOMENON, CONDUCTED IN THE DOMAIN OF THE HUMAN MIND, THAT IS REVOLUTIONIZING THE WAY INFORMATION IS SHARED AND INTERPRETED ON SOCIAL NETWORKS. THE DISSEMINATION OF DISINFORMATION AND FAKE NEWS, DRIVEN BY ADVANCED TECHNOLOGIES SUCH AS ARTIFICIAL INTELLIGENCE (AI), ALGORITHMS, AND BIG DATA, INTENSIFIES THE COMPLEXITY OF THESE STRATEGIES, WITH THE PURPOSE OF MANIPULATING THE THOUGHTS AND BEHAVIOR OF INDIVIDUALS. THE ANALYSIS OF THIS NEW TYPE OF WARFARE AND ITS GLOBAL IMPLICATIONS GUIDES THIS STUDY, WHOSE OBJECTIVE IS TO PROVIDE SUBSIDIES FOR THE FORMULATION OF PUBLIC POLICIES BY THE MINISTRY OF DEFENSE (MD) AGAINST THREATS TO THE PSYCHOSOCIAL EXPRESSION OF NATIONAL POWER RESULTING FROM COGNITIVE WARFARE ON SOCIAL NETWORKS. TO ACHIEVE THIS OBJECTIVE, A TRIANGULATION APPROACH OF QUALITATIVE METHODS WAS EMPLOYED, INCLUDING BIBLIOGRAPHICAL RESEARCH, LITERATURE REVIEW, EX- POST FACTO METHOD, COMPARATIVE ANALYSIS, AND SURVEY. THIS RESEARCH STANDS OUT NOT ONLY FOR ITS INNOVATION WITH THE THEME BUT ALSO FOR THE COMPLEXITY EVIDENCED THROUGH THE INTEGRATION OF KNOWLEDGE FROM VARIOUS AREAS. THE RESULTS DEMONSTRATE THAT THE MANIPULATION OF INFORMATION AND PUBLIC PERCEPTIONS ON SOCIAL NETWORKS IS A CENTRAL WEAPON OF COGNITIVE WARFARE, EXPLOITING BRAIN VULNERABILITIES TO INFLUENCE EMOTIONS AND BEHAVIORS AND DESTABILIZE DEMOCRATIC SOCIETIES. RECENT EVENTS IN BRAZIL ILLUSTRATE HOW THIS DYNAMIC DEVELOPS, HIGHLIGHTING SIGNIFICANT VULNERABILITIES IN THE PSYCHOSOCIAL EXPRESSION OF NATIONAL POWER. GIVEN THE GROWING INFLUENCE OF COGNITIVE WARFARE ON SOCIAL NETWORKS AND ITS GLOBAL IMPLICATIONS, THIS STUDY OFFERS IMPORTANT CONTRIBUTIONS TO THE FORMULATION OF NATIONAL DEFENSE PUBLIC POLICIES. IN ADDITION, ITS RECOMMENDATIONS PRESENT A CONCRETE APPLICABILITY, OUTLINING A SET OF EXECUTABLE MEASURES.</t>
+          <t>THIS DISSERTATION MADE AN EXPLORATORY ANALYSIS AROUND AGENCIES OF THE EXECUTIVE BRANCH OF THE GOVERNMENT OF THE STATE OF PERNAMBUCO, ITS MAIN OBJECTIVE WAS THE IDENTIFICATION OF TOOLS AIMED AT THE COMPLIANCE OF BUREAUCRATS. IDENTIFYING THEM HAS A ROLE IN THE CATEGORIZATION OF ORGANIZATIONS INTO AN ORIGINAL TYPOLOGY WHOSE BASES ARE STUDIES ON MANAGEMENT BUREAUCRATIC MODELS. THE TYPOLOGY OBSERVES TWO DIMENSIONS, X AND Y. X RELATES TO WHAT IS DESCRIBED ABOUT THE SERVICES TO BE PERFORMED, AND Y, INSTRUMENTS AIMED AT THE ACTIONS OF THE AGENTS ARE CLOSER OR IDENTICAL TO WHAT IS WRITTEN. TO MAKE THE IDENTIFICATION OF THESE INSTRUMENTS, CONSEQUENTLY, OBSERVE THE DIMENSIONS, A TEXT MINING FRAMEWORK WAS ELABORATED, A SET OF COMPUTATIONAL TECHNIQUES DESIGNED TO IDENTIFY USEFUL AND RELEVANT EXCERPTS (ACCORDING TO THE OBJECTIVE) PRESENT IN A TEXTUAL AND UNSTRUCTURED DATABASE. THE TECHNIQUE WAS CHOSEN FOR THREE REASONS, FIRST ITS CLEAR USEFULNESS FOR THE IDENTIFICATION OF EXCERPTS IN OFFICIAL DOCUMENTS THAT INSTITUTIONALIZE THE TOOLS SOUGHT, SECOND BECAUSE IT IS A MACHINE LEARNING TECHNIQUE THAT ALLOWS ITS CONSTANT INCREMENT, AND FINALLY, BE APPLICABLE WITH FREE SOFTWARE AND THAT ALLOW REPLICATION IN A SIMPLE WAY, SUCH AS FOXIT PDF AND RSTUDIO. PERNAMBUCO WAS CHOSEN AS A CASE FOR THE APPLICATION OF THE FRAMEWORK BECAUSE ITS PERFORMANCE EVALUATION SYSTEM, FOR THE ENTITIES SUBMITTED TO IT, ENSURES THAT SUCH INSTRUMENTS CAN BE IDENTIFIED IN A MORE SPECIFIC GROUP OF DOCUMENTS. THE RESULTS FOUND, FOR THE 20 ORGANIZATIONS OBSERVED, INDICATE THAT MOST OF THEM ARE TYPE 2B AND ONLY TWO TYPE 1A (RESPECTIVELY, IT WOULD BE AN "IDEAL ORGANIZATION" OR CLOSE TO IT, AND THE WORST TYPE, A "CHAOTIC AND WEAK ORGANIZATION"), BUT EVEN SO, ONLY TWO ORGANIZATIONS DID NOT PRESENT A LACK OF SIGNIFICANT INSTRUMENTS. DUE TO THE THEORETICAL COMPLEXITY IN DEVELOPING A TYPOLOGY AND AN APPLICATION FRAMEWORK FOR IT, THE FIRST TWO CHAPTERS ARE LITERATURE REVIEWS FOCUSED ON BUREAUCRACIES, MANAGEMENT MODELS AND HOW TO OBSERVE THEIR CHARACTERISTICS, FINALLY THE THIRD CHAPTER SHOWS THE APPLICABILITY AND RESULTS IN THE PERNAMBUCO CASE. IN SHORT, THIS WORK BASED ON A LITERATURE REVIEW CREATES A TYPOLOGY FOCUSED ON BUREAUCRATIC ORGANIZATIONS AND THEIR FORMAL INSTRUMENTS FOCUSED ON COMPLIANCE AND PERFORMANCE, THEN DEVELOPS A FRAMEWORK FOR THE IDENTIFICATION OF THESE AND APPLICATION OF THE TYPOLOGY, THEN PUTS IT INTO PRACTICE WHEN ANALYZING ENTITIES OF THE STATE GOVERNMENT OF PERNAMBUCO.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>GUERRA COGNITIVA;REDES SOCIAIS;DESINFORMAÇÃO;DEFESA NACIONAL;POLÍTICAS PÚBLICAS</t>
+          <t>BUROCRACIA;MODELOS GERENCIAIS;FERRAMENTAS INSTITUCIONAIS;MINERAÇÃO DE TEXTO.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>COGNITIVE WARFARE;SOCIAL NETWORKS;DISINFORMATION;NATIONAL DEFENSE;PUBLIC POLICIES</t>
+          <t>BUREAUCRACY;MANAGEMENT MODELS;INSTITUTIONAL TOOLS;TEXT MINING.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2180,15 +2180,15 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>Aprendizado de máquina (ML)</t>
         </is>
       </c>
       <c r="M13" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" t="b">
         <v>1</v>
       </c>
-      <c r="N13" t="b">
-        <v>0</v>
-      </c>
       <c r="O13" t="b">
         <v>0</v>
       </c>
@@ -2196,45 +2196,45 @@
         <v>0</v>
       </c>
       <c r="Q13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>CLAUDIO RODRIGUES CORREA</t>
+          <t>DALSON BRITTO FIGUEIREDO FILHO</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>ESTUDOS MARÍTIMOS</t>
+          <t>CIÊNCIA POLÍTICA</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>ESCOLA DE GUERRA NAVAL</t>
+          <t>UNIVERSIDADE FEDERAL DE PERNAMBUCO</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>EGN</t>
+          <t>UFPE</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>SUDESTE</t>
+          <t>NORDESTE</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>PERNAMBUCO</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
@@ -2253,16 +2253,16 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16722764</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=10455339</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>16722764</t>
+          <t>10455339</t>
         </is>
       </c>
       <c r="AE13" t="n">
-        <v>2757585</v>
+        <v>3385936</v>
       </c>
     </row>
     <row r="14">
@@ -2281,37 +2281,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DANILO GONCALVES DOS SANTOS</t>
+          <t>GUILHERME DE ALBUQUERQUE SANTOS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TEM QUE SER ASSIM! UM ESTUDO DE INSTRUMENTOS DETERMINANTES DE CONFORMIDADE DA BUROCRACIA PERNAMBUCANA</t>
+          <t>O USO DA TECNOLOGIA NA FORMULAÇÃO DE POLÍTICAS PÚBLICAS VOLTADAS À PREVENÇÃO E AO COMBATE À VIOLÊNCIA CONTRA A MULHER</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ESSA DISSERTAÇÃO FEZ UMA ANÁLISE EXPLORATÓRIA EM TORNO DE AGÊNCIAS DO PODER EXECUTIVO DO GOVERNO DO ESTADO DE PERNAMBUCO, SEU PRINCIPAL OBJETIVO FOI A IDENTIFICAÇÃO DE FERRAMENTAS VOLTADAS À CONFORMIDADE DOS BUROCRATAS. IDENTIFICÁ-LAS TEM FUNÇÃO NA CATEGORIZAÇÃO DAS ORGANIZAÇÕES EM UMA TIPOLOGIA ORIGINAL CUJAS BASES SÃO ESTUDOS SOBRE MODELOS BUROCRÁTICOS GERENCIAIS. A TIPOLOGIA OBSERVA DUAS DIMENSÕES, X E Y. X DIZ RESPEITO AO QUE ESTÁ DESCRITO SOBRE OS SERVIÇOS A SEREM DESEMPENHADOS, E Y, INSTRUMENTOS VOLTADOS PARA QUE AS AÇÕES DOS AGENTES SEJAM MAIS PRÓXIMAS OU IDÊNTICAS AO QUE ESTÁ ESCRITO. PARA FAZER A IDENTIFICAÇÃO DESSES INSTRUMENTOS, CONSEQUENTEMENTE, OBSERVAR AS DIMENSÕES, FOI ELABORADO UM FRAMEWORK DE MINERAÇÃO DE TEXTO, UM CONJUNTO DE TÉCNICAS COMPUTACIONAIS PENSADAS PARA A IDENTIFICAÇÃO DE TRECHOS ÚTEIS E RELEVANTES (DE ACORDO COM O OBJETIVO) PRESENTES EM UM BANCO DE DADOS TEXTUAIS E NÃO ESTRUTURADOS. FOI ESCOLHIDA A TÉCNICA POR TRÊS MOTIVOS, PRIMEIRO A SUA CLARA UTILIDADE PARA A IDENTIFICAÇÃO DE TRECHOS EM DOCUMENTOS OFICIAIS QUE INSTITUCIONALIZAM AS FERRAMENTAS BUSCADAS, SEGUNDO POR SE TRATAR DE UMA TÉCNICA DE MACHINE LEARNING QUE POSSIBILITA O SEU INCREMENTO CONSTANTE, E POR FIM, SER APLICÁVEL COM SOFTWARES GRATUITOS E QUE PERMITEM REPLICABILIDADE DE MANEIRA SIMPLES, COMO O FOXIT PDF E O RSTUDIO. PERNAMBUCO FOI ESCOLHIDO COMO CASO PARA A APLICAÇÃO DO FRAMEWORK PORQUE SEU SISTEMA DE AVALIAÇÃO DE DESEMPENHO, PARA AS ENTIDADES SUBMETIDAS A ELE, GARANTE QUE TAIS INSTRUMENTOS POSSAM SER IDENTIFICADOS EM UM GRUPO MAIS ESPECÍFICO DE DOCUMENTOS. OS RESULTADOS ENCONTRADOS, PARA AS 20 ORGANIZAÇÕES OBSERVADAS, INDICAM QUE A MAIORIA DELAS SÃO DO TIPO 2B E APENAS DUAS DO TIPO 1A (RESPECTIVAMENTE, SERIA UMA “ORGANIZAÇÃO IDEAL” OU PRÓXIMO A ISSO, E O PIOR TIPO, UMA “ORGANIZAÇÃO CAÓTICA E FRACA”), MAS, MESMO ASSIM, APENAS DUAS ORGANIZAÇÕES NÃO APRESENTARAM FALTA DE INSTRUMENTOS SIGNIFICATIVOS. DEVIDO À COMPLEXIDADE TEÓRICA EM DESENVOLVER UMA TIPOLOGIA E UM FRAMEWORK DE APLICAÇÃO PARA A MESMA, OS DOIS PRIMEIROS CAPÍTULOS SÃO REVISÕES DE LITERATURA FOCADAS EM BUROCRACIAS, MODELOS GERENCIAIS E COMO OBSERVAR SUAS CARACTERÍSTICAS, POR FIM O TERCEIRO CAPÍTULO MOSTRA A APLICABILIDADE E RESULTADOS NO CASO PERNAMBUCO. EM SUMA, ESSE TRABALHO COM BASE NUMA REVISÃO DE LITERATURA CRIA UMA TIPOLOGIA FOCADA EM ORGANIZAÇÕES BUROCRÁTICAS E SEUS INSTRUMENTOS FORMAIS VOLTADOS A CONFORMIDADE E PERFORMANCE, ENTÃO DESENVOLVE UM FRAMEWORK PARA A IDENTIFICAÇÃO DESSAS E APLICAÇÃO DA TIPOLOGIA, EM SEGUIDA O COLOCA EM PRÁTICA AO ANALISAR ENTIDADES DO GOVERNO ESTADUAL DE PERNAMBUCO.</t>
+          <t>OS ELEVADOS NÚMEROS DA VIOLÊNCIA CONTRA A MULHER NO PAÍS REFORÇAM A IMPORTÂNCIA DE SE LANÇAR MÃO DE INSTRUMENTOS MAIS EFETIVOS DE PREVENÇÃO, PROTEÇÃO E REPRESSÃO, RECLAMANDO POLÍTICAS PÚBLICAS MAIS ASSERTIVAS. NESSE VIÉS, A TECNOLOGIA SE AFIGURA INSTRUMENTO PODEROSO DE MUDANÇA SOCIAL, DE PRESTAÇÃO DE SERVIÇOS REMOTOS PELO ESTADO E DE APOIO NA FORMULAÇÃO DE POLÍTICAS PÚBLICAS E NA TOMADA DE DECISÃO, SOBRETUDO PARA IDENTIFICAR EVENTUAL NECESSIDADE DE MUDANÇA NO CURSO DAS AÇÕES E PROJETOS DESTINADOS À PROTEÇÃO DA MULHER. DIANTE DISSO, O ESTUDO SE PROPÕE A VERIFICAR A IMPORTÂNCIA DO USO DA TECNOLOGIA NO MAPEAMENTO DOS DADOS ENVOLVENDO A VIOLÊNCIA CONTRA A MULHER, DE MODO A SERVIR DE SUPORTE PARA A PARAMETRIZAÇÃO DE POLÍTICAS PÚBLICAS EFETIVAS NO COMBATE E MITIGAÇÃO DA SUA OCORRÊNCIA, BEM ASSIM DE MANEIRA A OFERTAR INSTRUMENTOS REMOTOS DE AUXÍLIO ÀS VÍTIMAS. PARA O DESENVOLVIMENTO DA PESQUISA, FORAM UTILIZADOS, DE MANEIRA CONJUGADA, OS MÉTODOS DEDUTIVO E INDUTIVO, COM ANÁLISE DA LEGISLAÇÃO INCIDENTE, DOS INSTRUMENTOS TECNOLÓGICOS E FERRAMENTAS DISPONÍVEIS, ASSIM COMO DOS DADOS ENVOLVENDO A VIOLÊNCIA DESSE JAEZ NO BRASIL E NO MUNDO. QUANTO AOS MÉTODOS DE PROCEDIMENTO, FORAM UTILIZADOS O HERMENÊUTICO, O HISTÓRICO, O JURÍDICO E O COMPARATIVO. AO LONGO DO ESTUDO, VERIFICOU-SE QUE AS FERRAMENTAS TECNOLÓGICAS ANALISADAS CONTRIBUEM SOBREMANEIRA NO COMBATE À VIOLÊNCIA CONTRA A MULHER, REVELANDO-SE FUNDAMENTAL PARA O PODER PÚBLICO AO ANALISAR OS DADOS COLETADOS DE MANEIRA MAIS ESTRUTURADA, RESULTANDO EM POLÍTICAS MAIS AJUSTADAS ÀS NECESSIDADES, INCLUSIVE PODENDO LEVAR EM CONTA CRITÉRIOS REGIONAIS E LOCAIS E OUTRAS INFORMAÇÕES QUE POSSAM VIR A INFLUENCIAR A ELEIÇÃO DOS PROJETOS E AÇÕES VOLTADOS ÀS MULHERES. A PAR DISSO, POSSUI O CONDÃO DE OFERTAR CANAIS REMOTOS DE PRESTAÇÃO DE SERVIÇOS PÚBLICOS, COMO OS DA ÁREA DE SAÚDE E DA SEGURANÇA PÚBLICA, DEIXANDO DE EXIGIR A PRESENÇA FÍSICA DAS VÍTIMAS, NÃO RARAS VEZES IMPOSSIBILITADAS DE COMPARECER, SOBRETUDO PELA VIGILÂNCIA OSTENSIVA DOS AGRESSORES, SITUAÇÃO VERTIGINOSAMENTE INCREMENTADA DURANTE A PANDEMIA DO COVID-19. RESTRIÇÕES À SITUAÇÃO FÁTICA MARCANTE REFLETEM IGUALMENTE NA DIFICULDADE EM SE ENCONTRAR DADOS COMPILADOS DA VIOLÊNCIA CONTRA A MULHER NO MUNDO. APÓS AS ANÁLISES, COMO CONTRIBUIÇÃO, FORAM APRESENTADAS SUGESTÕES PARA O PODER PÚBLICO, CONSISTENTES EM FERRAMENTAS E PROJETOS QUE PODERIAM SER IMPLEMENTADOS E INICIATIVAS JÁ DESENVOLVIDAS, NO ÂMBITO PÚBLICO E PRIVADO, PASSÍVEIS DE APROVEITAMENTO.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>THIS DISSERTATION MADE AN EXPLORATORY ANALYSIS AROUND AGENCIES OF THE EXECUTIVE BRANCH OF THE GOVERNMENT OF THE STATE OF PERNAMBUCO, ITS MAIN OBJECTIVE WAS THE IDENTIFICATION OF TOOLS AIMED AT THE COMPLIANCE OF BUREAUCRATS. IDENTIFYING THEM HAS A ROLE IN THE CATEGORIZATION OF ORGANIZATIONS INTO AN ORIGINAL TYPOLOGY WHOSE BASES ARE STUDIES ON MANAGEMENT BUREAUCRATIC MODELS. THE TYPOLOGY OBSERVES TWO DIMENSIONS, X AND Y. X RELATES TO WHAT IS DESCRIBED ABOUT THE SERVICES TO BE PERFORMED, AND Y, INSTRUMENTS AIMED AT THE ACTIONS OF THE AGENTS ARE CLOSER OR IDENTICAL TO WHAT IS WRITTEN. TO MAKE THE IDENTIFICATION OF THESE INSTRUMENTS, CONSEQUENTLY, OBSERVE THE DIMENSIONS, A TEXT MINING FRAMEWORK WAS ELABORATED, A SET OF COMPUTATIONAL TECHNIQUES DESIGNED TO IDENTIFY USEFUL AND RELEVANT EXCERPTS (ACCORDING TO THE OBJECTIVE) PRESENT IN A TEXTUAL AND UNSTRUCTURED DATABASE. THE TECHNIQUE WAS CHOSEN FOR THREE REASONS, FIRST ITS CLEAR USEFULNESS FOR THE IDENTIFICATION OF EXCERPTS IN OFFICIAL DOCUMENTS THAT INSTITUTIONALIZE THE TOOLS SOUGHT, SECOND BECAUSE IT IS A MACHINE LEARNING TECHNIQUE THAT ALLOWS ITS CONSTANT INCREMENT, AND FINALLY, BE APPLICABLE WITH FREE SOFTWARE AND THAT ALLOW REPLICATION IN A SIMPLE WAY, SUCH AS FOXIT PDF AND RSTUDIO. PERNAMBUCO WAS CHOSEN AS A CASE FOR THE APPLICATION OF THE FRAMEWORK BECAUSE ITS PERFORMANCE EVALUATION SYSTEM, FOR THE ENTITIES SUBMITTED TO IT, ENSURES THAT SUCH INSTRUMENTS CAN BE IDENTIFIED IN A MORE SPECIFIC GROUP OF DOCUMENTS. THE RESULTS FOUND, FOR THE 20 ORGANIZATIONS OBSERVED, INDICATE THAT MOST OF THEM ARE TYPE 2B AND ONLY TWO TYPE 1A (RESPECTIVELY, IT WOULD BE AN "IDEAL ORGANIZATION" OR CLOSE TO IT, AND THE WORST TYPE, A "CHAOTIC AND WEAK ORGANIZATION"), BUT EVEN SO, ONLY TWO ORGANIZATIONS DID NOT PRESENT A LACK OF SIGNIFICANT INSTRUMENTS. DUE TO THE THEORETICAL COMPLEXITY IN DEVELOPING A TYPOLOGY AND AN APPLICATION FRAMEWORK FOR IT, THE FIRST TWO CHAPTERS ARE LITERATURE REVIEWS FOCUSED ON BUREAUCRACIES, MANAGEMENT MODELS AND HOW TO OBSERVE THEIR CHARACTERISTICS, FINALLY THE THIRD CHAPTER SHOWS THE APPLICABILITY AND RESULTS IN THE PERNAMBUCO CASE. IN SHORT, THIS WORK BASED ON A LITERATURE REVIEW CREATES A TYPOLOGY FOCUSED ON BUREAUCRATIC ORGANIZATIONS AND THEIR FORMAL INSTRUMENTS FOCUSED ON COMPLIANCE AND PERFORMANCE, THEN DEVELOPS A FRAMEWORK FOR THE IDENTIFICATION OF THESE AND APPLICATION OF THE TYPOLOGY, THEN PUTS IT INTO PRACTICE WHEN ANALYZING ENTITIES OF THE STATE GOVERNMENT OF PERNAMBUCO.</t>
+          <t>THE FRIGHTENING NUMBERS OF VIOLENCE AGAINST WOMEN IN THE COUNTRY REINFORCE THE IMPORTANCE OF USING MORE EFFECTIVE INSTRUMENTS OF PREVENTION, PROTECTION AND REPRESSION, DEMANDING MORE ASSERTIVE PUBLIC POLICIES. IN THIS BIAS, TECHNOLOGY APPEARS TO BE A POWERFUL INSTRUMENT FOR SOCIAL CHANGE, FOR THE PROVISION OF REMOTE SERVICES BY THE STATE AND FOR SUPPORT IN THE FORMULATION OF PUBLIC POLICIES AND DECISION-MAKING, ESPECIALLY TO IDENTIFY ANY NEED FOR CHANGE IN THE COURSE OF ACTIONS AND PROJECTS AIMED AT PROTECTION OF THE WOMAN. THEREFORE, THE STUDY AIMS TO VERIFY THE IMPORTANCE OF USING TECHNOLOGY IN MAPPING DATA INVOLVING VIOLENCE AGAINST WOMEN, IN ORDER TO SUPPORT THE PARAMETERIZATION OF EFFECTIVE PUBLIC POLICIES TO COMBAT AND MITIGATE THEIR OCCURRENCE, AS WELL AS IN ORDER TO OFFER REMOTE INSTRUMENTS OF ASSISTANCE TO VICTIMS. FOR THE DEVELOPMENT OF THE RESEARCH, THE DEDUCTIVE AND INDUCTIVE METHODS WERE USED IN CONJUNCTION, WITH ANALYSIS OF THE INCIDENT LEGISLATION, THE TECHNOLOGICAL INSTRUMENTS AND TOOLS AVAILABLE, AS WELL AS THE DATA INVOLVING THIS VIOLENCE IN BRAZIL AND IN THE WORLD. AS FOR THE PROCEDURAL METHODS, THE HERMENEUTIC, HISTORICAL JURIDICAL AND COMPARATIVE METHODS WERE USED. THROUGHOUT THE STUDY, IT WAS FOUND THAT THE TECHNOLOGICAL TOOLS ANALYZED CONTRIBUTE GREATLY TO THE FIGHT AGAINST VIOLENCE AGAINST WOMEN, PROVING TO BE FUNDAMENTAL FOR THE PUBLIC POWER WHEN ANALYZING THE DATA COLLECTED IN A MORE STRUCTURED WAY, RESULTING IN POLICIES MORE ADJUSTED TO THE NEEDS, INCLUDING TAKING INTO ACCOUNT REGIONAL AND LOCAL CRITERIA AND OTHER INFORMATION THAT MAY INFLUENCE THE ELECTION OF PROJECTS AND ACTIONS AIMED AT WOMEN. IN ADDITION, IT HAS THE ABILITY TO OFFER REMOTE CHANNELS FOR THE PROVISION OF PUBLIC SERVICES, SUCH AS THOSE IN THE AREA OF HEALTH AND PUBLIC SECURITY, FAILING TO REQUIRE THE PHYSICAL PRESENCE OF THE VICTIMS, WHO ARE OFTEN UNABLE TO ATTEND, ESPECIALLY DUE TO THE OVERT SURVEILLANCE OF THE AGGRESSORS. A SITUATION THAT WAS DRAMATICALLY INCREASED DURING THE COVID-19 PANDEMIC. THE MOST STRIKING RESTRICTIONS RELATE TO THE DIFFICULTY IN FINDING COMPILED DATA ON VIOLENCE AGAINST WOMEN IN THE WORLD. AS A CONTRIBUTION, SUGGESTIONS WERE MADE TO THE PUBLIC POWER, CONSISTING OF TOOLS AND PROJECTS THAT COULD BE IMPLEMENTED AND INITIATIVES ALREADY DEVELOPED, IN THE PUBLIC AND PRIVATE SPHERES, THAT CAN BE USED.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BUROCRACIA;MODELOS GERENCIAIS;FERRAMENTAS INSTITUCIONAIS;MINERAÇÃO DE TEXTO.</t>
+          <t>VIOLÊNCIA CONTRA A MULHER;TECNOLOGIA;INTELIGÊNCIA ARTIFICIAL;MINERAÇÃO DE DADOS;POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>BUREAUCRACY;MANAGEMENT MODELS;INSTITUTIONAL TOOLS;TEXT MINING.</t>
+          <t>VIOLENCE AGAINST WOMEN;TECHNOLOGY;ARTIFICIAL INTELLIGENCE;DATA MINING;PUBLIC POLICY</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2321,61 +2321,61 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Aprendizado de máquina (ML)</t>
+          <t>IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="b">
         <v>1</v>
       </c>
-      <c r="O14" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>0</v>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>DALSON BRITTO FIGUEIREDO FILHO</t>
+          <t>BENJAMIN MIRANDA TABAK</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CIÊNCIA POLÍTICA</t>
+          <t>POLÍTICAS PÚBLICAS E GOVERNO</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DE PERNAMBUCO</t>
+          <t>FUNDACAO GETULIO VARGAS ( BRASÍLIA )</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>UFPE</t>
+          <t>FGV/BSB</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>NORDESTE</t>
+          <t>CENTRO-OESTE</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>PERNAMBUCO</t>
+          <t>DISTRITO FEDERAL</t>
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2394,16 +2394,16 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=10455339</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=10992403</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>10455339</t>
+          <t>10992403</t>
         </is>
       </c>
       <c r="AE14" t="n">
-        <v>3385936</v>
+        <v>3576479</v>
       </c>
     </row>
     <row r="15">
@@ -2422,37 +2422,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2021-06-11</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GUILHERME DE ALBUQUERQUE SANTOS</t>
+          <t>NATHALIA VIVIANI BITTENCOURT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>O USO DA TECNOLOGIA NA FORMULAÇÃO DE POLÍTICAS PÚBLICAS VOLTADAS À PREVENÇÃO E AO COMBATE À VIOLÊNCIA CONTRA A MULHER</t>
+          <t>O RETORNO DA COMPETIÇÃO DE GRANDES POTÊNCIAS E AS FORÇAS ARMADAS NA ERA DA INTELIGÊNCIA ARTIFICIAL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>OS ELEVADOS NÚMEROS DA VIOLÊNCIA CONTRA A MULHER NO PAÍS REFORÇAM A IMPORTÂNCIA DE SE LANÇAR MÃO DE INSTRUMENTOS MAIS EFETIVOS DE PREVENÇÃO, PROTEÇÃO E REPRESSÃO, RECLAMANDO POLÍTICAS PÚBLICAS MAIS ASSERTIVAS. NESSE VIÉS, A TECNOLOGIA SE AFIGURA INSTRUMENTO PODEROSO DE MUDANÇA SOCIAL, DE PRESTAÇÃO DE SERVIÇOS REMOTOS PELO ESTADO E DE APOIO NA FORMULAÇÃO DE POLÍTICAS PÚBLICAS E NA TOMADA DE DECISÃO, SOBRETUDO PARA IDENTIFICAR EVENTUAL NECESSIDADE DE MUDANÇA NO CURSO DAS AÇÕES E PROJETOS DESTINADOS À PROTEÇÃO DA MULHER. DIANTE DISSO, O ESTUDO SE PROPÕE A VERIFICAR A IMPORTÂNCIA DO USO DA TECNOLOGIA NO MAPEAMENTO DOS DADOS ENVOLVENDO A VIOLÊNCIA CONTRA A MULHER, DE MODO A SERVIR DE SUPORTE PARA A PARAMETRIZAÇÃO DE POLÍTICAS PÚBLICAS EFETIVAS NO COMBATE E MITIGAÇÃO DA SUA OCORRÊNCIA, BEM ASSIM DE MANEIRA A OFERTAR INSTRUMENTOS REMOTOS DE AUXÍLIO ÀS VÍTIMAS. PARA O DESENVOLVIMENTO DA PESQUISA, FORAM UTILIZADOS, DE MANEIRA CONJUGADA, OS MÉTODOS DEDUTIVO E INDUTIVO, COM ANÁLISE DA LEGISLAÇÃO INCIDENTE, DOS INSTRUMENTOS TECNOLÓGICOS E FERRAMENTAS DISPONÍVEIS, ASSIM COMO DOS DADOS ENVOLVENDO A VIOLÊNCIA DESSE JAEZ NO BRASIL E NO MUNDO. QUANTO AOS MÉTODOS DE PROCEDIMENTO, FORAM UTILIZADOS O HERMENÊUTICO, O HISTÓRICO, O JURÍDICO E O COMPARATIVO. AO LONGO DO ESTUDO, VERIFICOU-SE QUE AS FERRAMENTAS TECNOLÓGICAS ANALISADAS CONTRIBUEM SOBREMANEIRA NO COMBATE À VIOLÊNCIA CONTRA A MULHER, REVELANDO-SE FUNDAMENTAL PARA O PODER PÚBLICO AO ANALISAR OS DADOS COLETADOS DE MANEIRA MAIS ESTRUTURADA, RESULTANDO EM POLÍTICAS MAIS AJUSTADAS ÀS NECESSIDADES, INCLUSIVE PODENDO LEVAR EM CONTA CRITÉRIOS REGIONAIS E LOCAIS E OUTRAS INFORMAÇÕES QUE POSSAM VIR A INFLUENCIAR A ELEIÇÃO DOS PROJETOS E AÇÕES VOLTADOS ÀS MULHERES. A PAR DISSO, POSSUI O CONDÃO DE OFERTAR CANAIS REMOTOS DE PRESTAÇÃO DE SERVIÇOS PÚBLICOS, COMO OS DA ÁREA DE SAÚDE E DA SEGURANÇA PÚBLICA, DEIXANDO DE EXIGIR A PRESENÇA FÍSICA DAS VÍTIMAS, NÃO RARAS VEZES IMPOSSIBILITADAS DE COMPARECER, SOBRETUDO PELA VIGILÂNCIA OSTENSIVA DOS AGRESSORES, SITUAÇÃO VERTIGINOSAMENTE INCREMENTADA DURANTE A PANDEMIA DO COVID-19. RESTRIÇÕES À SITUAÇÃO FÁTICA MARCANTE REFLETEM IGUALMENTE NA DIFICULDADE EM SE ENCONTRAR DADOS COMPILADOS DA VIOLÊNCIA CONTRA A MULHER NO MUNDO. APÓS AS ANÁLISES, COMO CONTRIBUIÇÃO, FORAM APRESENTADAS SUGESTÕES PARA O PODER PÚBLICO, CONSISTENTES EM FERRAMENTAS E PROJETOS QUE PODERIAM SER IMPLEMENTADOS E INICIATIVAS JÁ DESENVOLVIDAS, NO ÂMBITO PÚBLICO E PRIVADO, PASSÍVEIS DE APROVEITAMENTO.</t>
+          <t>O PRESENTE TRABALHO DEBRUÇA-SE SOBRE A SEGUINTE QUESTÃO: DE QUE FORMA A INTELIGÊNCIA ARTIFICIAL ESTÁ INSERIDA NO CAMPO ESTRATÉGICO MILITAR DOS EUA E DA CHINA? COM EFEITO, ESSA TECNOLOGIA TEM PROVOCADO UMA MIRÍADE DE TRANSFORMAÇÕES SOCIAIS, DESDE A MUDANÇAS EM PADRÕES DE CONSUMO À AUTONOMIA DE ARTEFATOS MILITARES. EM TERMOS DAS DINÂMICAS DAS RELAÇÕES INTERNACIONAIS CONTEMPORÂNEAS, NOTA-SE UM RETORNO DA COMPETIÇÃO ENTRE GRANDES POTÊNCIAS, NO QUAL A BUSCA PELO SEU PIONEIRISMO CIENTÍFICO, CAPITAL HUMANO QUALIFICADO E TENSÕES NO ÂMBITO GEOPOLÍTICO E COMERCIAL TÊM TIDO DESTAQUE ESPECIAL ENTRE OS EUA E A CHINA. NO QUE CONCERNE AO SETOR MILITAR, OS AVANÇOS DA COMPUTAÇÃO E A VELOCIDADE NA QUAL ESSA TECNOLOGIA PROCESSA GRANDES VOLUMES DE DADOS TÊM CONFERIDO MAIS EFETIVIDADE E PRECISÃO PARA A INDÚSTRIA DE DEFESA. ASSIM, O PRESENTE ESTUDO EXPLORATÓRIO BUSCA IDENTIFICAR DE QUE FORMA ESSA TECNOLOGIA EMERGENTE ESTÁ SITUADA NO ÂMBITO ESTRATÉGICO MILITAR DO HEGEMON, OS EUA, E DA CHINA, CUJO PODER ECONÔMICO E MODERNIZAÇÃO DAS FORÇAS ARMADAS MERECEM ATENÇÃO NOS ESTUDOS DE SEGURANÇA INTERNACIONAIS. EM TERMOS METODOLÓGICOS, A EXECUÇÃO DESTA PESQUISA SERÁ PAUTADA PELA ABORDAGEM ESSENCIALMENTE DESCRITIVA, CUJO CARÁTER EXPLORATÓRIO TEM COMO PRINCIPAL FERRAMENTA DE COLETA DE DADOS A PESQUISA DOCUMENTAL E BIBLIOGRÁFICA. A ANÁLISE DESTES SERÁ EFETUADA COM O USO DA ESTATÍSTICA DESCRITIVA E ANÁLISE DE DOCUMENTOS. DESSA FORMA, ACREDITA-SE QUE A PRESENTE PESQUISA PODERÁ CONTRIBUIR COM A COMPREENSÃO DA EXPANSÃO DESSA TECNOLOGIA EMERGENTE NO ÂMBITO ESTRATÉGICO DOS ESTADOS, SOBRETUDO NO QUE TANGE AO SETOR DAS FORÇAS ARMADAS, BEM COMO NA LITERATURA DAS RELAÇÕES INTERNACIONAIS, PARA AMPLIAR AS DISCUSSÕES TEÓRICAS E POLÍTICAS SOBRE ESSE FENÔMENO CORRENTE.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>THE FRIGHTENING NUMBERS OF VIOLENCE AGAINST WOMEN IN THE COUNTRY REINFORCE THE IMPORTANCE OF USING MORE EFFECTIVE INSTRUMENTS OF PREVENTION, PROTECTION AND REPRESSION, DEMANDING MORE ASSERTIVE PUBLIC POLICIES. IN THIS BIAS, TECHNOLOGY APPEARS TO BE A POWERFUL INSTRUMENT FOR SOCIAL CHANGE, FOR THE PROVISION OF REMOTE SERVICES BY THE STATE AND FOR SUPPORT IN THE FORMULATION OF PUBLIC POLICIES AND DECISION-MAKING, ESPECIALLY TO IDENTIFY ANY NEED FOR CHANGE IN THE COURSE OF ACTIONS AND PROJECTS AIMED AT PROTECTION OF THE WOMAN. THEREFORE, THE STUDY AIMS TO VERIFY THE IMPORTANCE OF USING TECHNOLOGY IN MAPPING DATA INVOLVING VIOLENCE AGAINST WOMEN, IN ORDER TO SUPPORT THE PARAMETERIZATION OF EFFECTIVE PUBLIC POLICIES TO COMBAT AND MITIGATE THEIR OCCURRENCE, AS WELL AS IN ORDER TO OFFER REMOTE INSTRUMENTS OF ASSISTANCE TO VICTIMS. FOR THE DEVELOPMENT OF THE RESEARCH, THE DEDUCTIVE AND INDUCTIVE METHODS WERE USED IN CONJUNCTION, WITH ANALYSIS OF THE INCIDENT LEGISLATION, THE TECHNOLOGICAL INSTRUMENTS AND TOOLS AVAILABLE, AS WELL AS THE DATA INVOLVING THIS VIOLENCE IN BRAZIL AND IN THE WORLD. AS FOR THE PROCEDURAL METHODS, THE HERMENEUTIC, HISTORICAL JURIDICAL AND COMPARATIVE METHODS WERE USED. THROUGHOUT THE STUDY, IT WAS FOUND THAT THE TECHNOLOGICAL TOOLS ANALYZED CONTRIBUTE GREATLY TO THE FIGHT AGAINST VIOLENCE AGAINST WOMEN, PROVING TO BE FUNDAMENTAL FOR THE PUBLIC POWER WHEN ANALYZING THE DATA COLLECTED IN A MORE STRUCTURED WAY, RESULTING IN POLICIES MORE ADJUSTED TO THE NEEDS, INCLUDING TAKING INTO ACCOUNT REGIONAL AND LOCAL CRITERIA AND OTHER INFORMATION THAT MAY INFLUENCE THE ELECTION OF PROJECTS AND ACTIONS AIMED AT WOMEN. IN ADDITION, IT HAS THE ABILITY TO OFFER REMOTE CHANNELS FOR THE PROVISION OF PUBLIC SERVICES, SUCH AS THOSE IN THE AREA OF HEALTH AND PUBLIC SECURITY, FAILING TO REQUIRE THE PHYSICAL PRESENCE OF THE VICTIMS, WHO ARE OFTEN UNABLE TO ATTEND, ESPECIALLY DUE TO THE OVERT SURVEILLANCE OF THE AGGRESSORS. A SITUATION THAT WAS DRAMATICALLY INCREASED DURING THE COVID-19 PANDEMIC. THE MOST STRIKING RESTRICTIONS RELATE TO THE DIFFICULTY IN FINDING COMPILED DATA ON VIOLENCE AGAINST WOMEN IN THE WORLD. AS A CONTRIBUTION, SUGGESTIONS WERE MADE TO THE PUBLIC POWER, CONSISTING OF TOOLS AND PROJECTS THAT COULD BE IMPLEMENTED AND INITIATIVES ALREADY DEVELOPED, IN THE PUBLIC AND PRIVATE SPHERES, THAT CAN BE USED.</t>
+          <t>THE PRESENT WORK DEALS WITH THE FOLLOWING QUESTION: HOW IS ARTIFICIAL INTELLIGENCE INSERTED IN THE STRATEGIC MILITARY FIELD OF THE USA AND CHINA? INDEED, THIS TECHNOLOGY HAS BROUGHT ABOUT A MYRIAD OF SOCIAL TRANSFORMATIONS, FROM CHANGES IN CONSUMPTION PATTERNS TO THE AUTONOMY OF MILITARY ARTIFACTS. IN TERMS OF THE DYNAMICS OF CONTEMPORARY INTERNATIONAL RELATIONS, THERE IS A RETURN TO COMPETITION BETWEEN GREAT POWERS, IN WHICH THE SEARCH FOR THEIR SCIENTIFIC PIONEERING SPIRIT, QUALIFIED HUMAN CAPITAL AND TENSIONS IN THE GEOPOLITICAL AND COMMERCIAL SPHERES HAVE BEEN ESPECIALLY PROMINENT BETWEEN THE USA AND CHINA. WITH REGARD TO THE MILITARY SECTOR, ADVANCES IN COMPUTING AND THE SPEED AT WHICH THIS TECHNOLOGY PROCESSES LARGE VOLUMES OF DATA HAVE MADE THE DEFENSE INDUSTRY MORE EFFECTIVE AND ACCURATE. THUS, THE PRESENT EXPLORATORY STUDY SEEKS TO IDENTIFY HOW THIS EMERGING TECHNOLOGY IS SITUATED WITHIN THE MILITARY STRATEGIC SCOPE OF THE HEGEMON, THE USA, AND CHINA, WHOSE ECONOMIC POWER AND MODERNIZATION OF THE ARMED FORCES DESERVE ATTENTION IN INTERNATIONAL SECURITY STUDIES. IN METHODOLOGICAL TERMS, THE EXECUTION OF THIS RESEARCH WILL BE GUIDED BY THE ESSENTIALLY DESCRIPTIVE APPROACH, WHOSE EXPLORATORY CHARACTER HAS AS ITS MAIN DATA COLLECTION TOOL THE DOCUMENTARY AND BIBLIOGRAPHIC RESEARCH. THE ANALYSIS OF THESE WILL BE CARRIED OUT USING DESCRIPTIVE STATISTICS AND DOCUMENT ANALYSIS. THUS, IT IS BELIEVED THAT THE PRESENT RESEARCH CAN CONTRIBUTE TO THE UNDERSTANDING OF THE EXPANSION OF THIS EMERGING TECHNOLOGY IN THE STRATEGIC SCOPE OF THE STATES, ESPECIALLY WITH REGARD TO THE ARMED FORCES SECTOR, AS WELL AS IN THE LITERATURE ON INTERNATIONAL RELATIONS, TO BROADEN THE THEORETICAL AND POLICIES ON THIS CURRENT PHENOMENON</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>VIOLÊNCIA CONTRA A MULHER;TECNOLOGIA;INTELIGÊNCIA ARTIFICIAL;MINERAÇÃO DE DADOS;POLÍTICAS PÚBLICAS</t>
+          <t>INTELIGÊNCIA ARTIFICIAL;RELAÇÕES CHINA-EUA;FORÇAS ARMADAS;INDÚSTRIA DE DEFESA;ATIVOS ESTRATÉGICOS</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>VIOLENCE AGAINST WOMEN;TECHNOLOGY;ARTIFICIAL INTELLIGENCE;DATA MINING;PUBLIC POLICY</t>
+          <t>ARTIFICIAL INTELLIGENCE;CHINA-US RELATIONS;ARMED FORCES;DEFENSE INDUSTRY;STRATEGIC ASSETS</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>IA em sentido estrito</t>
         </is>
       </c>
       <c r="M15" t="b">
@@ -2478,45 +2478,45 @@
         <v>0</v>
       </c>
       <c r="Q15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>BENJAMIN MIRANDA TABAK</t>
+          <t>MARCOS AURELIO GUEDES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>POLÍTICAS PÚBLICAS E GOVERNO</t>
+          <t>CIÊNCIA POLÍTICA</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>FUNDACAO GETULIO VARGAS ( BRASÍLIA )</t>
+          <t>UNIVERSIDADE FEDERAL DE PERNAMBUCO</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>FGV/BSB</t>
+          <t>UFPE</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>CENTRO-OESTE</t>
+          <t>NORDESTE</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>DISTRITO FEDERAL</t>
+          <t>PERNAMBUCO</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>POLÍTICAS PÚBLICAS</t>
+          <t>NÃO SE APLICA</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2535,16 +2535,16 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=10992403</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=10456749</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>10992403</t>
+          <t>10456749</t>
         </is>
       </c>
       <c r="AE15" t="n">
-        <v>3576479</v>
+        <v>3385997</v>
       </c>
     </row>
     <row r="16">
@@ -2559,105 +2559,105 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2022-02-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NATHALIA VIVIANI BITTENCOURT</t>
+          <t>FRANCISCO LUIZ MARZINOTTO JUNIOR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>O RETORNO DA COMPETIÇÃO DE GRANDES POTÊNCIAS E AS FORÇAS ARMADAS NA ERA DA INTELIGÊNCIA ARTIFICIAL</t>
+          <t>ESTADOS E MERCADOS NA ERA DO BIG DATA: OLIGOPOLIZAÇÃO DAS BIG TECHS E A POLÍTICA NORTE-AMERICANA NOS GOVERNOS OBAMA E TRUMP (2009-2021)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>O PRESENTE TRABALHO DEBRUÇA-SE SOBRE A SEGUINTE QUESTÃO: DE QUE FORMA A INTELIGÊNCIA ARTIFICIAL ESTÁ INSERIDA NO CAMPO ESTRATÉGICO MILITAR DOS EUA E DA CHINA? COM EFEITO, ESSA TECNOLOGIA TEM PROVOCADO UMA MIRÍADE DE TRANSFORMAÇÕES SOCIAIS, DESDE A MUDANÇAS EM PADRÕES DE CONSUMO À AUTONOMIA DE ARTEFATOS MILITARES. EM TERMOS DAS DINÂMICAS DAS RELAÇÕES INTERNACIONAIS CONTEMPORÂNEAS, NOTA-SE UM RETORNO DA COMPETIÇÃO ENTRE GRANDES POTÊNCIAS, NO QUAL A BUSCA PELO SEU PIONEIRISMO CIENTÍFICO, CAPITAL HUMANO QUALIFICADO E TENSÕES NO ÂMBITO GEOPOLÍTICO E COMERCIAL TÊM TIDO DESTAQUE ESPECIAL ENTRE OS EUA E A CHINA. NO QUE CONCERNE AO SETOR MILITAR, OS AVANÇOS DA COMPUTAÇÃO E A VELOCIDADE NA QUAL ESSA TECNOLOGIA PROCESSA GRANDES VOLUMES DE DADOS TÊM CONFERIDO MAIS EFETIVIDADE E PRECISÃO PARA A INDÚSTRIA DE DEFESA. ASSIM, O PRESENTE ESTUDO EXPLORATÓRIO BUSCA IDENTIFICAR DE QUE FORMA ESSA TECNOLOGIA EMERGENTE ESTÁ SITUADA NO ÂMBITO ESTRATÉGICO MILITAR DO HEGEMON, OS EUA, E DA CHINA, CUJO PODER ECONÔMICO E MODERNIZAÇÃO DAS FORÇAS ARMADAS MERECEM ATENÇÃO NOS ESTUDOS DE SEGURANÇA INTERNACIONAIS. EM TERMOS METODOLÓGICOS, A EXECUÇÃO DESTA PESQUISA SERÁ PAUTADA PELA ABORDAGEM ESSENCIALMENTE DESCRITIVA, CUJO CARÁTER EXPLORATÓRIO TEM COMO PRINCIPAL FERRAMENTA DE COLETA DE DADOS A PESQUISA DOCUMENTAL E BIBLIOGRÁFICA. A ANÁLISE DESTES SERÁ EFETUADA COM O USO DA ESTATÍSTICA DESCRITIVA E ANÁLISE DE DOCUMENTOS. DESSA FORMA, ACREDITA-SE QUE A PRESENTE PESQUISA PODERÁ CONTRIBUIR COM A COMPREENSÃO DA EXPANSÃO DESSA TECNOLOGIA EMERGENTE NO ÂMBITO ESTRATÉGICO DOS ESTADOS, SOBRETUDO NO QUE TANGE AO SETOR DAS FORÇAS ARMADAS, BEM COMO NA LITERATURA DAS RELAÇÕES INTERNACIONAIS, PARA AMPLIAR AS DISCUSSÕES TEÓRICAS E POLÍTICAS SOBRE ESSE FENÔMENO CORRENTE.</t>
+          <t>O SÉCULO XX FOI MARCADO PELO DESENVOLVIMENTO DAS TECNOLOGIAS DA INFORMAÇÃO E COMUNICAÇÕES, GRANDE PARTE FINANCIADAS COM RECURSOS PÚBLICOS. DENTRE ELAS, A INTERNET ORIGINOU-SE NOS EUA COMO UMA RESPOSTA GEOPOLÍTICA AO AVANÇO TECNOLÓGICO SOVIÉTICO. EM MEADOS DO FIM DA GUERRA FRIA, A ASCENSÃO DO NEOLIBERALISMO ECONÔMICO FEZ COM QUE A INICIATIVA PRIVADA GANHASSE INFLUÊNCIA NO SETOR, ABRINDO ESPAÇO PARA A DESREGULAMENTAÇÃO FINANCEIRA E PRIVATIZAÇÃO DE TECNOLOGIAS. APÓS A ABERTURA COMERCIAL DA INTERNET, A PRESSÃO COMPETITIVA PELOS MERCADOS DA “NOVA ECONOMIA” PROPORCIONOU O SURGIMENTO DE EMPRESAS INOVADORAS E O AVANÇO GLOBAL DA INTERNET, FAZENDO-NOS ENTRAR NA ERA DO BIG DATA, UMA ÉPOCA DE PRODUÇÃO DE DADOS EM MASSA. NOS ÚLTIMOS ANOS, UM OLIGOPÓLIO CONSTITUIU-SE NOS EUA PARA EXPLORAR ECONOMICAMENTE ESSES RECURSOS DIGITAIS, QUE SE DILATOU DURANTE O GOVERNO OBAMA. APÓS A EXPANSÃO ECONÔMICA, A ERA TRUMP SUSCITOU PROBLEMÁTICAS SOBRE O PODER POLÍTICO DAS CHAMADAS BIG TECHS, MARCANDO O INÍCIO DE TENTATIVAS DE CONTENÇÃO PELO CHEFE DO EXECUTIVO E LEGISLATIVO. ENTRE AS INICIATIVAS, TRUMP BUSCOU MINAR O PODER CORPORATIVO ATRAVÉS DE ORDENS EXECUTIVAS, ENQUANTO O CONGRESSO ABRIU UMA INVESTIGAÇÃO ANTITRUSTE DESTINADA A QUEBRAR OS MONOPÓLIOS DIGITAIS PARA “PROTEGER O MERCADO DE TRANSGRESSÕES”. NO ENTANTO, ESSAS TENTATIVAS DE CONTENÇÃO SÃO, DE FATO, INICIATIVAS VOLTADAS APENAS PARA PROTEÇÃO DO “LIVRE MERCADO”? A HIPÓTESE DA DISSERTAÇÃO PARTE DA PREMISSA DE QUE AS TENTATIVAS DE CONTER AS BIG TECHS NA ERA TRUMP NÃO BUSCAM APENAS A DEFESA DO “LIVRE MERCADO”, MAS SIM, SUPÕE-SE QUE SEJAM INICIATIVAS PARA REPARAR AS CONSEQUÊNCIAS DESSE LIVRE MERCADO QUE LEVOU À OLIGOPOLIZAÇÃO E CENTRALIZAÇÃO DE PODER ESTRUTURAL NAS EMPRESAS. ASSIM, O OBJETIVO DO TRABALHO É ANALISAR AS RELAÇÕES ENTRE AS BIG TECHS E A POLÍTICA NORTE-AMERICANA NOS GOVERNOS OBAMA (PERÍODO DE EXPANSÃO) E NA ERA TRUMP (TENTATIVAS DE CONTENÇÃO). É UTILIZADO O MÉTODO HIPOTÉTICO-DEDUTIVO, CONGREGANDO A ANÁLISE QUALITATIVA DE DOCUMENTOS OFICIAIS E LITERATURA, ALÉM DA UTILIZAÇÃO DE INDICADORES QUANTITATIVOS.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>THE PRESENT WORK DEALS WITH THE FOLLOWING QUESTION: HOW IS ARTIFICIAL INTELLIGENCE INSERTED IN THE STRATEGIC MILITARY FIELD OF THE USA AND CHINA? INDEED, THIS TECHNOLOGY HAS BROUGHT ABOUT A MYRIAD OF SOCIAL TRANSFORMATIONS, FROM CHANGES IN CONSUMPTION PATTERNS TO THE AUTONOMY OF MILITARY ARTIFACTS. IN TERMS OF THE DYNAMICS OF CONTEMPORARY INTERNATIONAL RELATIONS, THERE IS A RETURN TO COMPETITION BETWEEN GREAT POWERS, IN WHICH THE SEARCH FOR THEIR SCIENTIFIC PIONEERING SPIRIT, QUALIFIED HUMAN CAPITAL AND TENSIONS IN THE GEOPOLITICAL AND COMMERCIAL SPHERES HAVE BEEN ESPECIALLY PROMINENT BETWEEN THE USA AND CHINA. WITH REGARD TO THE MILITARY SECTOR, ADVANCES IN COMPUTING AND THE SPEED AT WHICH THIS TECHNOLOGY PROCESSES LARGE VOLUMES OF DATA HAVE MADE THE DEFENSE INDUSTRY MORE EFFECTIVE AND ACCURATE. THUS, THE PRESENT EXPLORATORY STUDY SEEKS TO IDENTIFY HOW THIS EMERGING TECHNOLOGY IS SITUATED WITHIN THE MILITARY STRATEGIC SCOPE OF THE HEGEMON, THE USA, AND CHINA, WHOSE ECONOMIC POWER AND MODERNIZATION OF THE ARMED FORCES DESERVE ATTENTION IN INTERNATIONAL SECURITY STUDIES. IN METHODOLOGICAL TERMS, THE EXECUTION OF THIS RESEARCH WILL BE GUIDED BY THE ESSENTIALLY DESCRIPTIVE APPROACH, WHOSE EXPLORATORY CHARACTER HAS AS ITS MAIN DATA COLLECTION TOOL THE DOCUMENTARY AND BIBLIOGRAPHIC RESEARCH. THE ANALYSIS OF THESE WILL BE CARRIED OUT USING DESCRIPTIVE STATISTICS AND DOCUMENT ANALYSIS. THUS, IT IS BELIEVED THAT THE PRESENT RESEARCH CAN CONTRIBUTE TO THE UNDERSTANDING OF THE EXPANSION OF THIS EMERGING TECHNOLOGY IN THE STRATEGIC SCOPE OF THE STATES, ESPECIALLY WITH REGARD TO THE ARMED FORCES SECTOR, AS WELL AS IN THE LITERATURE ON INTERNATIONAL RELATIONS, TO BROADEN THE THEORETICAL AND POLICIES ON THIS CURRENT PHENOMENON</t>
+          <t>THE 20TH CENTURY WAS MARKED BY THE DEVELOPMENT OF INFORMATION AND COMMUNICATION TECHNOLOGIES, LARGELY FINANCED WITH PUBLIC RESOURCES. AMONG THEM, THE INTERNET ORIGINATED IN THE US AS A GEOPOLITICAL RESPONSE TO SOVIET TECHNOLOGICAL ADVANCEMENT. IN THE MIDDLE OF THE END OF THE COLD WAR, THE RISE OF ECONOMIC NEOLIBERALISM MADE THE PRIVATE SECTOR GAIN INFLUENCE IN THE SECTOR, OPENING SPACE FOR FINANCIAL DEREGULATION AND PRIVATIZATION OF TECHNOLOGIES. AFTER THE COMMERCIAL OPENING OF THE INTERNET, THE COMPETITIVE PRESSURE BY THE MARKETS OF THE “NEW ECONOMY” PROVIDED THE EMERGENCE OF INNOVATIVE COMPANIES AND THE GLOBAL ADVANCEMENT OF THE INTERNET, MAKING US ENTER THE ERA OF BIG DATA, AN ERA OF MASS DATA PRODUCTION. IN RECENT YEARS, AN OLIGOPOLY WAS FORMED IN THE US TO ECONOMICALLY EXPLOIT THESE DIGITAL RESOURCES, WHICH EXPANDED DURING THE OBAMA ADMINISTRATION. AFTER THE ECONOMIC EXPANSION, THE TRUMP ERA RAISED QUESTIONS ABOUT THE POLITICAL POWER OF THE SO-CALLED BIG TECHS, MARKING THE BEGINNING OF CONTAINMENT ATTEMPTS BY THE HEAD OF THE EXECUTIVE AND LEGISLATIVE. AMONG THE INITIATIVES, TRUMP SOUGHT TO UNDERMINE CORPORATE POWER THROUGH EXECUTIVE ORDERS, WHILE CONGRESS OPENED AN ANTITRUST INVESTIGATION AIMED AT BREAKING DIGITAL MONOPOLIES TO "PROTECT THE MARKET FROM TRANSGRESSIONS". HOWEVER, ARE THESE ATTEMPTS AT CONTAINMENT, IN FACT, INITIATIVES AIMED ONLY AT PROTECTING THE “FREE MARKET”? THE HYPOTHESIS OF THE DISSERTATION STARTS FROM THE PREMISE THAT THE ATTEMPTS TO CONTAIN BIG TECHS IN THE TRUMP ERA DO NOT SEEK ONLY THE DEFENSE OF THE “FREE MARKET”, BUT RATHER, IT IS ASSUMED THAT THEY ARE INITIATIVES TO REPAIR THE CONSEQUENCES OF THIS FREE MARKET THAT LED TO OLIGOPOLIZATION AND CENTRALIZATION OF STRUCTURAL POWER IN COMPANIES. THUS, THE OBJECTIVE OF THE WORK IS TO ANALYZE THE RELATIONSHIP BETWEEN BIG TECHS AND US POLICY IN THE OBAMA ADMINISTRATIONS (EXPANSION PERIOD) AND IN THE TRUMP ERA (CONTAINMENT ATTEMPTS). THE HYPOTHETICAL-DEDUCTIVE METHOD IS USED, BRINGING TOGETHER THE QUALITATIVE ANALYSIS OF OFFICIAL DOCUMENTS AND LITERATURE, IN ADDITION TO THE USE OF QUANTITATIVE INDICATORS.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>INTELIGÊNCIA ARTIFICIAL;RELAÇÕES CHINA-EUA;FORÇAS ARMADAS;INDÚSTRIA DE DEFESA;ATIVOS ESTRATÉGICOS</t>
+          <t>BIG DATA;BIG TECHS;ECONOMIA POLÍTICA INTERNACIONAL;ESTADOS UNIDOS;TECNOLOGIAS DA INFORMAÇÃO E COMUNICAÇÕES</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>ARTIFICIAL INTELLIGENCE;CHINA-US RELATIONS;ARMED FORCES;DEFENSE INDUSTRY;STRATEGIC ASSETS</t>
+          <t>BIG DATA;BIG TECHS;INTERNATIONAL POLITICAL ECONOMY;UNITED STATES;INFORMATION AND COMMUNICATION TECHNOLOGIES</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>IA em sentido estrito</t>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M16" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="b">
         <v>1</v>
       </c>
-      <c r="N16" t="b">
-        <v>0</v>
-      </c>
-      <c r="O16" t="b">
-        <v>0</v>
-      </c>
-      <c r="P16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>0</v>
-      </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>MARCOS AURELIO GUEDES DE OLIVEIRA</t>
+          <t>CRISTINA SOREANU PECEQUILO</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CIÊNCIA POLÍTICA</t>
+          <t>ECONOMIA POLÍTICA INTERNACIONAL</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DE PERNAMBUCO</t>
+          <t>UNIVERSIDADE FEDERAL DO RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>UFPE</t>
+          <t>UFRJ</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>NORDESTE</t>
+          <t>SUDESTE</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>PERNAMBUCO</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
@@ -2676,16 +2676,16 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=10456749</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11515865</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>10456749</t>
+          <t>11515865</t>
         </is>
       </c>
       <c r="AE16" t="n">
-        <v>3385997</v>
+        <v>3611866</v>
       </c>
     </row>
     <row r="17">
@@ -2704,51 +2704,51 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2022-02-02</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FRANCISCO LUIZ MARZINOTTO JUNIOR</t>
+          <t>WELBER SILVEIRA NORONHA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ESTADOS E MERCADOS NA ERA DO BIG DATA: OLIGOPOLIZAÇÃO DAS BIG TECHS E A POLÍTICA NORTE-AMERICANA NOS GOVERNOS OBAMA E TRUMP (2009-2021)</t>
+          <t>DRONE MULTIDOMÍNIO: CONCILIANDO MODERNIZAÇÃO E TRANSFORMAÇÃO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>O SÉCULO XX FOI MARCADO PELO DESENVOLVIMENTO DAS TECNOLOGIAS DA INFORMAÇÃO E COMUNICAÇÕES, GRANDE PARTE FINANCIADAS COM RECURSOS PÚBLICOS. DENTRE ELAS, A INTERNET ORIGINOU-SE NOS EUA COMO UMA RESPOSTA GEOPOLÍTICA AO AVANÇO TECNOLÓGICO SOVIÉTICO. EM MEADOS DO FIM DA GUERRA FRIA, A ASCENSÃO DO NEOLIBERALISMO ECONÔMICO FEZ COM QUE A INICIATIVA PRIVADA GANHASSE INFLUÊNCIA NO SETOR, ABRINDO ESPAÇO PARA A DESREGULAMENTAÇÃO FINANCEIRA E PRIVATIZAÇÃO DE TECNOLOGIAS. APÓS A ABERTURA COMERCIAL DA INTERNET, A PRESSÃO COMPETITIVA PELOS MERCADOS DA “NOVA ECONOMIA” PROPORCIONOU O SURGIMENTO DE EMPRESAS INOVADORAS E O AVANÇO GLOBAL DA INTERNET, FAZENDO-NOS ENTRAR NA ERA DO BIG DATA, UMA ÉPOCA DE PRODUÇÃO DE DADOS EM MASSA. NOS ÚLTIMOS ANOS, UM OLIGOPÓLIO CONSTITUIU-SE NOS EUA PARA EXPLORAR ECONOMICAMENTE ESSES RECURSOS DIGITAIS, QUE SE DILATOU DURANTE O GOVERNO OBAMA. APÓS A EXPANSÃO ECONÔMICA, A ERA TRUMP SUSCITOU PROBLEMÁTICAS SOBRE O PODER POLÍTICO DAS CHAMADAS BIG TECHS, MARCANDO O INÍCIO DE TENTATIVAS DE CONTENÇÃO PELO CHEFE DO EXECUTIVO E LEGISLATIVO. ENTRE AS INICIATIVAS, TRUMP BUSCOU MINAR O PODER CORPORATIVO ATRAVÉS DE ORDENS EXECUTIVAS, ENQUANTO O CONGRESSO ABRIU UMA INVESTIGAÇÃO ANTITRUSTE DESTINADA A QUEBRAR OS MONOPÓLIOS DIGITAIS PARA “PROTEGER O MERCADO DE TRANSGRESSÕES”. NO ENTANTO, ESSAS TENTATIVAS DE CONTENÇÃO SÃO, DE FATO, INICIATIVAS VOLTADAS APENAS PARA PROTEÇÃO DO “LIVRE MERCADO”? A HIPÓTESE DA DISSERTAÇÃO PARTE DA PREMISSA DE QUE AS TENTATIVAS DE CONTER AS BIG TECHS NA ERA TRUMP NÃO BUSCAM APENAS A DEFESA DO “LIVRE MERCADO”, MAS SIM, SUPÕE-SE QUE SEJAM INICIATIVAS PARA REPARAR AS CONSEQUÊNCIAS DESSE LIVRE MERCADO QUE LEVOU À OLIGOPOLIZAÇÃO E CENTRALIZAÇÃO DE PODER ESTRUTURAL NAS EMPRESAS. ASSIM, O OBJETIVO DO TRABALHO É ANALISAR AS RELAÇÕES ENTRE AS BIG TECHS E A POLÍTICA NORTE-AMERICANA NOS GOVERNOS OBAMA (PERÍODO DE EXPANSÃO) E NA ERA TRUMP (TENTATIVAS DE CONTENÇÃO). É UTILIZADO O MÉTODO HIPOTÉTICO-DEDUTIVO, CONGREGANDO A ANÁLISE QUALITATIVA DE DOCUMENTOS OFICIAIS E LITERATURA, ALÉM DA UTILIZAÇÃO DE INDICADORES QUANTITATIVOS.</t>
+          <t>ESTE TRABALHO TRATA DOS FUNDAMENTOS RELACIONADOS AO PAPEL DO DRONE PARA A INDÚSTRIA E PARA A DEFESA. A HIPÓTESE PRINCIPAL DE TRABALHO É DE QUE O DRONE MULTIDOMÍNIO CONSTITUI-SE EM MÓVEL DE ENDOGENEIZAÇÃO DAS TECNOLOGIAS CRÍTICAS DA III E DA IV REVOLUÇÃO INDUSTRIAL. A HIPÓTESE SECUNDÁRIA É A DE QUE ELE É CAPAZ DE CONCILIAR AS TAREFAS DE MODERNIZAÇÃO E TRANSFORMAÇÃO, AO PERMITIR A CRIAÇÃO DE UMA AGENDA ECUMÊNICA ADEQUADA À PERSPECTIVA HOLÍSTICA DE TRANSFORMAÇÃO ADOTADA PELO BRASIL E A UM PERFIL DE FORÇA HÍBRIDO. O RELATÓRIO PARTE DO DEBATE ACERCA DA TRANSFORMAÇÃO E DO PAPEL DO DRONE NA IV REVOLUÇÃO INDUSTRIAL. A SEGUIR, DISCUTE-SE O PAPEL DAS CAPACIDADES, A TRANSFORMAÇÃO NO BRASIL E O MARCO LEGAL DA DEFESA, PARA ENTÃO TRATAR DO PAPEL DO DRONE NA TRANSFORMAÇÃO, NO COMBATE E ADAPTAÇÃO. PARA DAR PROFUNDIDADE E PERSPECTIVA, EFETUA-SE UM BREVE HISTÓRICO DO DRONE, ENFATIZANDO-SE AS MISSÕES ESTRATÉGICAS RELACIONADAS À GUERRA NUCLEAR, BEM COMO SUA UTILIZAÇÃO NA BATALHA DE BEKAA EM 1982. PROCURA-SE RELACIONAR ESTES DOIS ACÚMULOS COM A INTERVENIÊNCIA DO DRONE NA ALTERAÇÃO DE POLARIDADE, QUE CONVERTEU OS EUA NA ÚNICA SUPERPOTÊNCIA DO PLANTE. NA SEQUÊNCIA, DISCUTE-SE O CONCEITO “DRONE MULTIDOMÍNIO” E SUA FUNCIONALIDADE PARA ELABORAÇÃO DE POLÍTICAS ABRANGENTES E CONJUNTAS DE DEFESA. PROCURA-SE ESTABELECER VÍNCULO ENTRE O DRONE E O PROJETO NACIONAL, ATRAVÉS DO PAPEL DA INTELIGÊNCIA ARTIFICIAL, DA COMPUTAÇÃO QUÂNTICA, DA COMUNICAÇÃO QUÂNTICA E DA CONQUISTA ESPACIAL.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>THE 20TH CENTURY WAS MARKED BY THE DEVELOPMENT OF INFORMATION AND COMMUNICATION TECHNOLOGIES, LARGELY FINANCED WITH PUBLIC RESOURCES. AMONG THEM, THE INTERNET ORIGINATED IN THE US AS A GEOPOLITICAL RESPONSE TO SOVIET TECHNOLOGICAL ADVANCEMENT. IN THE MIDDLE OF THE END OF THE COLD WAR, THE RISE OF ECONOMIC NEOLIBERALISM MADE THE PRIVATE SECTOR GAIN INFLUENCE IN THE SECTOR, OPENING SPACE FOR FINANCIAL DEREGULATION AND PRIVATIZATION OF TECHNOLOGIES. AFTER THE COMMERCIAL OPENING OF THE INTERNET, THE COMPETITIVE PRESSURE BY THE MARKETS OF THE “NEW ECONOMY” PROVIDED THE EMERGENCE OF INNOVATIVE COMPANIES AND THE GLOBAL ADVANCEMENT OF THE INTERNET, MAKING US ENTER THE ERA OF BIG DATA, AN ERA OF MASS DATA PRODUCTION. IN RECENT YEARS, AN OLIGOPOLY WAS FORMED IN THE US TO ECONOMICALLY EXPLOIT THESE DIGITAL RESOURCES, WHICH EXPANDED DURING THE OBAMA ADMINISTRATION. AFTER THE ECONOMIC EXPANSION, THE TRUMP ERA RAISED QUESTIONS ABOUT THE POLITICAL POWER OF THE SO-CALLED BIG TECHS, MARKING THE BEGINNING OF CONTAINMENT ATTEMPTS BY THE HEAD OF THE EXECUTIVE AND LEGISLATIVE. AMONG THE INITIATIVES, TRUMP SOUGHT TO UNDERMINE CORPORATE POWER THROUGH EXECUTIVE ORDERS, WHILE CONGRESS OPENED AN ANTITRUST INVESTIGATION AIMED AT BREAKING DIGITAL MONOPOLIES TO "PROTECT THE MARKET FROM TRANSGRESSIONS". HOWEVER, ARE THESE ATTEMPTS AT CONTAINMENT, IN FACT, INITIATIVES AIMED ONLY AT PROTECTING THE “FREE MARKET”? THE HYPOTHESIS OF THE DISSERTATION STARTS FROM THE PREMISE THAT THE ATTEMPTS TO CONTAIN BIG TECHS IN THE TRUMP ERA DO NOT SEEK ONLY THE DEFENSE OF THE “FREE MARKET”, BUT RATHER, IT IS ASSUMED THAT THEY ARE INITIATIVES TO REPAIR THE CONSEQUENCES OF THIS FREE MARKET THAT LED TO OLIGOPOLIZATION AND CENTRALIZATION OF STRUCTURAL POWER IN COMPANIES. THUS, THE OBJECTIVE OF THE WORK IS TO ANALYZE THE RELATIONSHIP BETWEEN BIG TECHS AND US POLICY IN THE OBAMA ADMINISTRATIONS (EXPANSION PERIOD) AND IN THE TRUMP ERA (CONTAINMENT ATTEMPTS). THE HYPOTHETICAL-DEDUCTIVE METHOD IS USED, BRINGING TOGETHER THE QUALITATIVE ANALYSIS OF OFFICIAL DOCUMENTS AND LITERATURE, IN ADDITION TO THE USE OF QUANTITATIVE INDICATORS.</t>
+          <t>THIS DISSERTATION DEALS WITH THE FUNDAMENTALS RELATED TO THE ROLE OF THE DRONE FOR INDUSTRY AND DEFENSE. THE MAIN HYPOTHESIS IS THAT THE MULTI-DOMAIN DRONE CONSTITUTES A MOBILE FOR THE ENDOGENIZATION OF CRITICAL TECHNOLOGIES OF THE III AND IV INDUSTRIAL REVOLUTION. THE SECONDARY HYPOTHESIS IS THAT IT IS CAPABLE OF RECONCILING THE TASKS OF MODERNIZATION AND TRANSFORMATION, BY ALLOWING THE CREATION OF AN ECUMENICAL AGENDA SUITED TO THE HOLISTIC PERSPECTIVE OF TRANSFORMATION ADOPTED BY BRAZIL AND TO A HYBRID FORCE PROFILE. THE REPORT STARTS FROM THE DEBATE ABOUT TRANSFORMATION AND THE ROLE OF THE DRONE IN THE IV INDUSTRIAL REVOLUTION. NEXT, IT DISCUSSES THE ROLE OF CAPABILITIES, TRANSFORMATION IN BRAZIL AND THE LEGAL FRAMEWORK FOR DEFENSE, AND THEN DISCUSSES THE ROLE OF THE DRONE IN TRANSFORMATION, COMBAT AND ADAPTATION. TO GIVE DEPTH AND PERSPECTIVE, A BRIEF HISTORY OF THE DRONE IS CARRIED OUT, EMPHASIZING THE STRATEGIC MISSIONS RELATED TO NUCLEAR WAR, AS WELL AS ITS USE IN THE BATTLE OF BEKAA IN 1982. IT SEEKS TO RELATE THESE TWO ACCUMULATIONS WITH THE INTERVENTION OF THE DRONE IN THE POLARITY SHIFT, WHICH MADE THE US THE ONLY SUPERPOWER ON THE PLANET. NEXT, THE “MULTI-DOMAIN DRONE” CONCEPT AND ITS FUNCTIONALITY FOR THE ELABORATION OF COMPREHENSIVE AND JOINT DEFENSE POLICIES ARE DISCUSSED. IT SEEKS TO ESTABLISH A LINK BETWEEN THE DRONE AND THE NATIONAL PROJECT, THROUGH THE ROLE OF ARTIFICIAL INTELLIGENCE, QUANTUM COMPUTING, QUANTUM COMMUNICATION, AND SPACE CONQUEST.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>BIG DATA;BIG TECHS;ECONOMIA POLÍTICA INTERNACIONAL;ESTADOS UNIDOS;TECNOLOGIAS DA INFORMAÇÃO E COMUNICAÇÕES</t>
+          <t>DRONE;REVOLUÇÃO INDUSTRIAL;MODERNIZAÇÃO E TRANSFORMAÇÃO MILITAR;INTELIGÊNCIA ARTIFICIAL;CIBERNÉTICA;CONQUISTA ESPACIAL</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>BIG DATA;BIG TECHS;INTERNATIONAL POLITICAL ECONOMY;UNITED STATES;INFORMATION AND COMMUNICATION TECHNOLOGIES</t>
+          <t>DRONE;INDUSTRIAL REVOLUTION.;MILITARY MODERNIZATION AND TRANSFORMATION;ARTIFICIAL INTELLIGENCE;CYBERNETICS;SPACE CONQUEST.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Correlato</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>IA em sentido estrito</t>
         </is>
       </c>
       <c r="M17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
@@ -2760,45 +2760,45 @@
         <v>0</v>
       </c>
       <c r="Q17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>CRISTINA SOREANU PECEQUILO</t>
+          <t>JOSE MIGUEL QUEDI MARTINS</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>ECONOMIA POLÍTICA INTERNACIONAL</t>
+          <t>ESTUDOS ESTRATÉGICOS INTERNACIONAIS</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DO RIO DE JANEIRO</t>
+          <t>UNIVERSIDADE FEDERAL DO RIO GRANDE DO SUL</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>UFRJ</t>
+          <t>UFRGS</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>SUDESTE</t>
+          <t>SUL</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>RIO GRANDE DO SUL</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>POLÍTICA INTERNACIONAL</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2817,16 +2817,16 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11515865</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11576624</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>11515865</t>
+          <t>11576624</t>
         </is>
       </c>
       <c r="AE17" t="n">
-        <v>3611866</v>
+        <v>3859907</v>
       </c>
     </row>
     <row r="18">
@@ -2841,76 +2841,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>WELBER SILVEIRA NORONHA</t>
+          <t>ISIS PARIS MAIA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DRONE MULTIDOMÍNIO: CONCILIANDO MODERNIZAÇÃO E TRANSFORMAÇÃO</t>
+          <t>POLÍTICAS DIRECIONADAS DE ENFRENTAMENTO À POBREZA NA CHINA: UMA ANÁLISE DOS ARRANJOS DE IMPLEMENTAÇÃO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ESTE TRABALHO TRATA DOS FUNDAMENTOS RELACIONADOS AO PAPEL DO DRONE PARA A INDÚSTRIA E PARA A DEFESA. A HIPÓTESE PRINCIPAL DE TRABALHO É DE QUE O DRONE MULTIDOMÍNIO CONSTITUI-SE EM MÓVEL DE ENDOGENEIZAÇÃO DAS TECNOLOGIAS CRÍTICAS DA III E DA IV REVOLUÇÃO INDUSTRIAL. A HIPÓTESE SECUNDÁRIA É A DE QUE ELE É CAPAZ DE CONCILIAR AS TAREFAS DE MODERNIZAÇÃO E TRANSFORMAÇÃO, AO PERMITIR A CRIAÇÃO DE UMA AGENDA ECUMÊNICA ADEQUADA À PERSPECTIVA HOLÍSTICA DE TRANSFORMAÇÃO ADOTADA PELO BRASIL E A UM PERFIL DE FORÇA HÍBRIDO. O RELATÓRIO PARTE DO DEBATE ACERCA DA TRANSFORMAÇÃO E DO PAPEL DO DRONE NA IV REVOLUÇÃO INDUSTRIAL. A SEGUIR, DISCUTE-SE O PAPEL DAS CAPACIDADES, A TRANSFORMAÇÃO NO BRASIL E O MARCO LEGAL DA DEFESA, PARA ENTÃO TRATAR DO PAPEL DO DRONE NA TRANSFORMAÇÃO, NO COMBATE E ADAPTAÇÃO. PARA DAR PROFUNDIDADE E PERSPECTIVA, EFETUA-SE UM BREVE HISTÓRICO DO DRONE, ENFATIZANDO-SE AS MISSÕES ESTRATÉGICAS RELACIONADAS À GUERRA NUCLEAR, BEM COMO SUA UTILIZAÇÃO NA BATALHA DE BEKAA EM 1982. PROCURA-SE RELACIONAR ESTES DOIS ACÚMULOS COM A INTERVENIÊNCIA DO DRONE NA ALTERAÇÃO DE POLARIDADE, QUE CONVERTEU OS EUA NA ÚNICA SUPERPOTÊNCIA DO PLANTE. NA SEQUÊNCIA, DISCUTE-SE O CONCEITO “DRONE MULTIDOMÍNIO” E SUA FUNCIONALIDADE PARA ELABORAÇÃO DE POLÍTICAS ABRANGENTES E CONJUNTAS DE DEFESA. PROCURA-SE ESTABELECER VÍNCULO ENTRE O DRONE E O PROJETO NACIONAL, ATRAVÉS DO PAPEL DA INTELIGÊNCIA ARTIFICIAL, DA COMPUTAÇÃO QUÂNTICA, DA COMUNICAÇÃO QUÂNTICA E DA CONQUISTA ESPACIAL.</t>
+          <t>O OBJETIVO DA PESQUISA FOI DESCREVER AS CONFIGURAÇÕES DAS RELAÇÕES VERTICAIS ENTRE OS ATORES GOVERNAMENTAIS ENVOLVIDOS NOS PROCESSOS DE IMPLEMENTAÇÃO DAS POLÍTICAS PÚBLICAS DIRECIONADAS (PPD), OCORRIDAS DURANTE O 13O PLANO QUINQUENAL (2016-2020) NA CHINA. EMBORA AS PRIMEIRAS POLÍTICAS DE ENFRENTAMENTO À POBREZA REMONTEM À DÉCADA DE 1980, AS PPD FORAM RESPONSÁVEIS POR ATENDER AS ÚLTIMAS 43 MILHÕES DE PESSOAS, DO TOTAL DE 850 MILHÕES RETIRADAS DESSA SITUAÇÃO DESDE A POLÍTICA DE REFORMA E ABERTURA INICIADA EM 1978. PARA ALÉM DO DESENVOLVIMENTO COMO PROPULSOR DA MOBILIDADE SOCIAL, CABE DISCUTIR AS SINGULARIDADES POLÍTICO-INSTITUCIONAIS DO ESTADO CHINÊS, BEM COMO OS MECANISMOS INTERGOVERNAMENTAIS PARA IMPLANTAÇÃO DAS POLÍTICAS PÚBLICAS, EM ESPECÍFICO AS PPD. DO PONTO DE VISTA METODOLÓGICO, TRATA-SE DE UMA PESQUISA EXPLORATÓRIA, EM QUE FOI EMPREENDIDA REVISÃO BIBLIOGRÁFICA, ANÁLISE DOCUMENTAL E ENTREVISTA. PODE-SE CONCLUIR QUE A CHINA É UM ESTADO UNITÁRIO MULTIÉTNICO DE ORIENTAÇÃO SOCIALISTA COM COMPLEXOS MECANISMOS DE INTERGOVERNABILIDADE, DESCENTRALIZAÇÃO E AUTONOMIA SUBNACIONAL. ASSIM, DESTACAM-SE AS INOVAÇÕES INSTITUCIONAIS, NO QUE TANGE A LIBERDADE DE ADAPTAÇÃO DAS AÇÕES GOVERNAMENTAIS EM ÂMBITO SUBNACIONAL; POLÍTICO, NO QUE DIZ RESPEITO AO PAPEL DO DESEMPENHADO NA PROMOÇÃO MERITOCRÁTICA DOS QUADROS GOVERNAMENTAIS; E TÉCNICAS, NO QUE SE REFERE À UTILIZAÇÃO DE NOVAS FERRAMENTAS, COMO É O CASO DO BIG DATA. O ACHADO PRINCIPAL É QUE A AUTONOMIA DECISÓRIA DAS UNIDADES SUBNACIONAIS, CRUCIAL PARA QUE OS ARRANJOS VERTICAIS SE ADAPTEM ÀS POLÍTICAS PÚBLICAS À REALIDADE LOCAL, SE DÁ MANTENDO A OBSERVÂNCIA ÀS DIRETRIZES NACIONAIS EM FUNÇÃO DA AVALIAÇÃO E PROMOÇÃO DOS QUADROS PARTIDÁRIOS.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>THIS DISSERTATION DEALS WITH THE FUNDAMENTALS RELATED TO THE ROLE OF THE DRONE FOR INDUSTRY AND DEFENSE. THE MAIN HYPOTHESIS IS THAT THE MULTI-DOMAIN DRONE CONSTITUTES A MOBILE FOR THE ENDOGENIZATION OF CRITICAL TECHNOLOGIES OF THE III AND IV INDUSTRIAL REVOLUTION. THE SECONDARY HYPOTHESIS IS THAT IT IS CAPABLE OF RECONCILING THE TASKS OF MODERNIZATION AND TRANSFORMATION, BY ALLOWING THE CREATION OF AN ECUMENICAL AGENDA SUITED TO THE HOLISTIC PERSPECTIVE OF TRANSFORMATION ADOPTED BY BRAZIL AND TO A HYBRID FORCE PROFILE. THE REPORT STARTS FROM THE DEBATE ABOUT TRANSFORMATION AND THE ROLE OF THE DRONE IN THE IV INDUSTRIAL REVOLUTION. NEXT, IT DISCUSSES THE ROLE OF CAPABILITIES, TRANSFORMATION IN BRAZIL AND THE LEGAL FRAMEWORK FOR DEFENSE, AND THEN DISCUSSES THE ROLE OF THE DRONE IN TRANSFORMATION, COMBAT AND ADAPTATION. TO GIVE DEPTH AND PERSPECTIVE, A BRIEF HISTORY OF THE DRONE IS CARRIED OUT, EMPHASIZING THE STRATEGIC MISSIONS RELATED TO NUCLEAR WAR, AS WELL AS ITS USE IN THE BATTLE OF BEKAA IN 1982. IT SEEKS TO RELATE THESE TWO ACCUMULATIONS WITH THE INTERVENTION OF THE DRONE IN THE POLARITY SHIFT, WHICH MADE THE US THE ONLY SUPERPOWER ON THE PLANET. NEXT, THE “MULTI-DOMAIN DRONE” CONCEPT AND ITS FUNCTIONALITY FOR THE ELABORATION OF COMPREHENSIVE AND JOINT DEFENSE POLICIES ARE DISCUSSED. IT SEEKS TO ESTABLISH A LINK BETWEEN THE DRONE AND THE NATIONAL PROJECT, THROUGH THE ROLE OF ARTIFICIAL INTELLIGENCE, QUANTUM COMPUTING, QUANTUM COMMUNICATION, AND SPACE CONQUEST.</t>
+          <t>THE OBJECTIVE OF THIS RESEARCH WAS TO DESCRIBE THE CONFIGURATIONS OF THE VERTICAL RELATIONSHIPS BETWEEN THE GOVERNMENT ACTORS INVOLVED IN THE IMPLEMENTATION PROCESSES OF THE TARGETED POVERTY ALLEVIATION (TPA), WHICH OCCURRED DURING THE 13 TH FIVE YEAR PLAN (2016-2020) IN CHINA. ALTHOUGH THE FIRST POLICIES TO COMBAT POVERTY DATE BACK TO THE 1980S, THE TPAS WERE RESPONSIBLE FOR SERVING THE LAST 43 MILLION PEOPLE, OUT OF A TOTAL OF 850 MILLION REMOVED FROM THIS SITUATION SINCE THE OPENING REFORM POLICY STARTED IN 1978. BEYOND DEVELOPMENT AS A DRIVER OF SOCIAL MOBILITY, IT IS WORTH DISCUSSING THE POLITICAL-INSTITUTIONAL SINGULARITIES OF THE CHINESE STATE, AS WELL AS THE INTERGOVERNMENTAL MECHANISMS FOR THE IMPLEMENTATION OF PUBLIC POLICIES, SPECIFICALLY THE TPA. FROM THE METHODOLOGICAL POINT OF VIEW, THIS IS AN EXPLORATORY RESEARCH, IN WHICH A BIBLIOGRAPHIC REVIEW, A DOCUMENT ANALYSIS AND AN INTERVIEW WERE MADE. IT CAN BE CONCLUDED THAT CHINA IS A MULTIETHNIC UNITARY STATE OF SOCIALIST ORIENTATION WITH COMPLEX MECHANISMS OF INTERGOVERNABILITY, DECENTRALIZATION AND SUBNATIONAL AUTONOMY. THUS, IT IS IMPORTANT TO HIGHLIGHT 1) INSTITUTIONAL INNOVATIONS, CONCERNING THE FREEDOM TO ADAPT GOVERNMENT ACTIONS TO SUBNATIONAL LEVEL; 2) POLITICAL INNOVATIONS, WITH REGARD TO THE ROLE PLAYED BY THE MERITOCRATIC PROMOTION OF GOVERNMENT STAFF; AND 3) TECHNICAL INNOVATIONS, WITH REGARD TO THE USE OF NEW TOOLS, SUCH AS BIG DATA. THE MAIN FINDING IS THAT THE DECISION-MAKING AUTONOMY OF SUBNATIONAL UNITS, WHICH IS CRUCIAL FOR VERTICAL ARRANGEMENTS TO ADAPT PUBLIC POLICIES TO LOCAL REALITY, IS ACHIEVED BY MAINTAINING COMPLIANCE WITH NATIONAL GUIDELINES DUE TO THE EVALUATION AND PROMOTION OF PARTY CADRES.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>DRONE;REVOLUÇÃO INDUSTRIAL;MODERNIZAÇÃO E TRANSFORMAÇÃO MILITAR;INTELIGÊNCIA ARTIFICIAL;CIBERNÉTICA;CONQUISTA ESPACIAL</t>
+          <t>CHINA;POLÍTICAS PÚBLICAS;POBREZA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>DRONE;INDUSTRIAL REVOLUTION.;MILITARY MODERNIZATION AND TRANSFORMATION;ARTIFICIAL INTELLIGENCE;CYBERNETICS;SPACE CONQUEST.</t>
+          <t>CHINA;PUBLIC POLICY;POVERTY</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>IA em sentido estrito</t>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M18" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="b">
         <v>1</v>
       </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" t="b">
-        <v>0</v>
-      </c>
-      <c r="P18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>0</v>
-      </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>JOSE MIGUEL QUEDI MARTINS</t>
+          <t>LUCIANA PAZINI PAPI</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>ESTUDOS ESTRATÉGICOS INTERNACIONAIS</t>
+          <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>170</v>
+        <v>103</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>POLÍTICA INTERNACIONAL</t>
+          <t>NÃO SE APLICA</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2958,16 +2958,16 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11576624</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13719515</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>11576624</t>
+          <t>13719515</t>
         </is>
       </c>
       <c r="AE18" t="n">
-        <v>3859907</v>
+        <v>3894235</v>
       </c>
     </row>
     <row r="19">
@@ -2986,37 +2986,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ISIS PARIS MAIA</t>
+          <t>MARCUS VINICIUS DA SILVA TAVARES</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>POLÍTICAS DIRECIONADAS DE ENFRENTAMENTO À POBREZA NA CHINA: UMA ANÁLISE DOS ARRANJOS DE IMPLEMENTAÇÃO</t>
+          <t>5G – CONEXÃO PARA UM NOVO MUNDO: UMA ANÁLISE TRANSVERSAL DO CASO EUA VS HUAWEI</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>O OBJETIVO DA PESQUISA FOI DESCREVER AS CONFIGURAÇÕES DAS RELAÇÕES VERTICAIS ENTRE OS ATORES GOVERNAMENTAIS ENVOLVIDOS NOS PROCESSOS DE IMPLEMENTAÇÃO DAS POLÍTICAS PÚBLICAS DIRECIONADAS (PPD), OCORRIDAS DURANTE O 13O PLANO QUINQUENAL (2016-2020) NA CHINA. EMBORA AS PRIMEIRAS POLÍTICAS DE ENFRENTAMENTO À POBREZA REMONTEM À DÉCADA DE 1980, AS PPD FORAM RESPONSÁVEIS POR ATENDER AS ÚLTIMAS 43 MILHÕES DE PESSOAS, DO TOTAL DE 850 MILHÕES RETIRADAS DESSA SITUAÇÃO DESDE A POLÍTICA DE REFORMA E ABERTURA INICIADA EM 1978. PARA ALÉM DO DESENVOLVIMENTO COMO PROPULSOR DA MOBILIDADE SOCIAL, CABE DISCUTIR AS SINGULARIDADES POLÍTICO-INSTITUCIONAIS DO ESTADO CHINÊS, BEM COMO OS MECANISMOS INTERGOVERNAMENTAIS PARA IMPLANTAÇÃO DAS POLÍTICAS PÚBLICAS, EM ESPECÍFICO AS PPD. DO PONTO DE VISTA METODOLÓGICO, TRATA-SE DE UMA PESQUISA EXPLORATÓRIA, EM QUE FOI EMPREENDIDA REVISÃO BIBLIOGRÁFICA, ANÁLISE DOCUMENTAL E ENTREVISTA. PODE-SE CONCLUIR QUE A CHINA É UM ESTADO UNITÁRIO MULTIÉTNICO DE ORIENTAÇÃO SOCIALISTA COM COMPLEXOS MECANISMOS DE INTERGOVERNABILIDADE, DESCENTRALIZAÇÃO E AUTONOMIA SUBNACIONAL. ASSIM, DESTACAM-SE AS INOVAÇÕES INSTITUCIONAIS, NO QUE TANGE A LIBERDADE DE ADAPTAÇÃO DAS AÇÕES GOVERNAMENTAIS EM ÂMBITO SUBNACIONAL; POLÍTICO, NO QUE DIZ RESPEITO AO PAPEL DO DESEMPENHADO NA PROMOÇÃO MERITOCRÁTICA DOS QUADROS GOVERNAMENTAIS; E TÉCNICAS, NO QUE SE REFERE À UTILIZAÇÃO DE NOVAS FERRAMENTAS, COMO É O CASO DO BIG DATA. O ACHADO PRINCIPAL É QUE A AUTONOMIA DECISÓRIA DAS UNIDADES SUBNACIONAIS, CRUCIAL PARA QUE OS ARRANJOS VERTICAIS SE ADAPTEM ÀS POLÍTICAS PÚBLICAS À REALIDADE LOCAL, SE DÁ MANTENDO A OBSERVÂNCIA ÀS DIRETRIZES NACIONAIS EM FUNÇÃO DA AVALIAÇÃO E PROMOÇÃO DOS QUADROS PARTIDÁRIOS.</t>
+          <t>DESDE O ANO DE 2019, A TECNOLOGIA 5G VEM GANHANDO CADA VEZ MAIS ESPAÇO NOS NOTICIÁRIOS ECONÔMICOS E POLÍTICOS, BEM COMO NOS ESTUDOS ACADÊMICOS. TAL FATO NÃO SÓ É DEVIDO A SUA IMPORTÂNCIA NO ROMPER DE UMA NOVA ERA DAS TECNOLOGIAS DA INFORMAÇÃO E COMUNICAÇÃO QUE É FUNDAMENTAL PARA UM NOVO PARADIGMA INDUSTRIAL. MAS SE DEVE SOBRETUDO AS SANÇÕES IMPOSTAS PELOS EUA À HUAWEI, SOB A ALEGAÇÃO DE ESPIONAGEM EM CONJUNTO COM O ESTADO CHINÊS. TAIS ACUSAÇÕES LEVAM A INDAGAÇÕES QUANTOS AOS INTERESSES POR TRÁS DAS SANÇÕES ESTADUNIDENSES. AO MESMO TEMPO EM QUE NOSSOS OLHOS SE VOLTAM COM FACILIDADE E ENCANTO ÀS APLICABILIDADES QUE NOS SÃO ANUNCIADAS NA AUTOMAÇÃO DAS INDÚSTRIAS, VEÍCULOS SEM CONDUTORES E CASAS E CIDADES INTELIGENTES; AS APLICABILIDADES MILITARES SÃO IGUALMENTE VASTAS E CAPAZES DE INFLUENCIAR DE FORMA AINDA IMENSURÁVEL O TABULEIRO DO PODER GLOBAL. DENTRO DESSE CENÁRIO, O PRESENTE TRABALHO OBJETIVA INVESTIGAR AS APLICABILIDADES ECONÔMICAS E MILITARES DA TECNOLOGIA 5G E COMO AS MESMAS SE CORRELACIONAM NO CAMPO DO CONFLITO GEOPOLÍTICO ENTRE CHINA E EUA NUM CONTEXTO DE DISPUTA HEGEMÔNICA.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>THE OBJECTIVE OF THIS RESEARCH WAS TO DESCRIBE THE CONFIGURATIONS OF THE VERTICAL RELATIONSHIPS BETWEEN THE GOVERNMENT ACTORS INVOLVED IN THE IMPLEMENTATION PROCESSES OF THE TARGETED POVERTY ALLEVIATION (TPA), WHICH OCCURRED DURING THE 13 TH FIVE YEAR PLAN (2016-2020) IN CHINA. ALTHOUGH THE FIRST POLICIES TO COMBAT POVERTY DATE BACK TO THE 1980S, THE TPAS WERE RESPONSIBLE FOR SERVING THE LAST 43 MILLION PEOPLE, OUT OF A TOTAL OF 850 MILLION REMOVED FROM THIS SITUATION SINCE THE OPENING REFORM POLICY STARTED IN 1978. BEYOND DEVELOPMENT AS A DRIVER OF SOCIAL MOBILITY, IT IS WORTH DISCUSSING THE POLITICAL-INSTITUTIONAL SINGULARITIES OF THE CHINESE STATE, AS WELL AS THE INTERGOVERNMENTAL MECHANISMS FOR THE IMPLEMENTATION OF PUBLIC POLICIES, SPECIFICALLY THE TPA. FROM THE METHODOLOGICAL POINT OF VIEW, THIS IS AN EXPLORATORY RESEARCH, IN WHICH A BIBLIOGRAPHIC REVIEW, A DOCUMENT ANALYSIS AND AN INTERVIEW WERE MADE. IT CAN BE CONCLUDED THAT CHINA IS A MULTIETHNIC UNITARY STATE OF SOCIALIST ORIENTATION WITH COMPLEX MECHANISMS OF INTERGOVERNABILITY, DECENTRALIZATION AND SUBNATIONAL AUTONOMY. THUS, IT IS IMPORTANT TO HIGHLIGHT 1) INSTITUTIONAL INNOVATIONS, CONCERNING THE FREEDOM TO ADAPT GOVERNMENT ACTIONS TO SUBNATIONAL LEVEL; 2) POLITICAL INNOVATIONS, WITH REGARD TO THE ROLE PLAYED BY THE MERITOCRATIC PROMOTION OF GOVERNMENT STAFF; AND 3) TECHNICAL INNOVATIONS, WITH REGARD TO THE USE OF NEW TOOLS, SUCH AS BIG DATA. THE MAIN FINDING IS THAT THE DECISION-MAKING AUTONOMY OF SUBNATIONAL UNITS, WHICH IS CRUCIAL FOR VERTICAL ARRANGEMENTS TO ADAPT PUBLIC POLICIES TO LOCAL REALITY, IS ACHIEVED BY MAINTAINING COMPLIANCE WITH NATIONAL GUIDELINES DUE TO THE EVALUATION AND PROMOTION OF PARTY CADRES.</t>
+          <t>SINCE 2019, 5G TECHNOLOGY HAS BEEN GETTING MORE ATTENTION IN ECONOMIC AND POLITICAL CIRCLES, AS WELL AS IN ACADEMIA. PART OF THE REASON FOR THIS IS THAT 5G TECHNOLOGY IS AN ESSENTIAL ELEMENT OF THE NEW AGE OF INFORMATION AND COMMUNICATION TECHNOLOGY (ICT), LEADING TO THE EMERGENCE OF A NEW INDUSTRIAL PARADIGM. BUT THE MAIN REASON FOR ALL THE ATTENTION CONCERNING 5G TECHNOLOGY IS THE SANCTIONS IMPOSED BY THE US ON THE CHINESE ICT FIRM HUAWEI, UNDER THE ALLEGATION OF ESPIONAGE IN COOPERATION WITH THE CHINESE STATE. THESE ACCUSATIONS BRING QUESTIONS CONCERNING THE REAL INTERESTS BEHIND THE AMERICAN SANCTIONS. AT THE SAME TIME THAT OUR EYES EASILY FOCUS ON THE INTERESTING AND APPEALING CIVILIAN APPLICATIONS OF 5G TECHNOLOGY, SUCH AS IN THE AUTOMATION OF INDUSTRIES, DRIVER-LESS VEHICLES, AND INTELLIGENT HOUSES AND CITIES, THE MILITARY APPLICATIONS OF 5G ARE EQUALLY VAST AND CAPABLE OF INFLUENCING IN AN IMMEASURABLE MANNER THE GLOBAL POWER BOARD AS IT IS NOW DRAWN. IN THIS SCENARIO, THE PRESENT WORK INVESTIGATES THE ECONOMIC AND MILITARY APPLICATIONS OF 5G TECHNOLOGY AND THE WAY THESE TECHNOLOGIES ARE CORRELATED IN THE LARGER GEOPOLITICAL CONFLICT BETWEEN CHINA AND THE USA.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CHINA;POLÍTICAS PÚBLICAS;POBREZA</t>
+          <t>HUAWEI;CHINA;EUA;GEOPOLÍTICA 5G;CIBERSEGURANÇA;HEGEMONIA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>CHINA;PUBLIC POLICY;POVERTY</t>
+          <t>HUAWEI;CHINA;USA;5G GEOPOLITICS;CYBERSECURITY;HEGEMONY</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3046,41 +3046,41 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>LUCIANA PAZINI PAPI</t>
+          <t>JOSE LUIS DA COSTA FIORI</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>POLÍTICAS PÚBLICAS</t>
+          <t>ECONOMIA POLÍTICA INTERNACIONAL</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DO RIO GRANDE DO SUL</t>
+          <t>UNIVERSIDADE FEDERAL DO RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>UFRGS</t>
+          <t>UFRJ</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>SUL</t>
+          <t>SUDESTE</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>RIO GRANDE DO SUL</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -3099,16 +3099,16 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13719515</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12682786</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>13719515</t>
+          <t>12682786</t>
         </is>
       </c>
       <c r="AE19" t="n">
-        <v>3894235</v>
+        <v>1385496</v>
       </c>
     </row>
     <row r="20">
@@ -3127,51 +3127,51 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2023-02-13</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MARCUS VINICIUS DA SILVA TAVARES</t>
+          <t>REJANE BARBOSA DE SOUSA NOGUEIRA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>5G – CONEXÃO PARA UM NOVO MUNDO: UMA ANÁLISE TRANSVERSAL DO CASO EUA VS HUAWEI</t>
+          <t>OBSERVANDO O PROJETO ESCOLA SEM PARTIDO EM UMA PERSPECTIVA CRÍTICA CONTRA-HEGEMÔNICA NO CONTEXTO DOS ATAQUES A UMA ESCOLA FEDERAL DO RIO DE JANEIRO, O COLÉGIO PEDRO II</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DESDE O ANO DE 2019, A TECNOLOGIA 5G VEM GANHANDO CADA VEZ MAIS ESPAÇO NOS NOTICIÁRIOS ECONÔMICOS E POLÍTICOS, BEM COMO NOS ESTUDOS ACADÊMICOS. TAL FATO NÃO SÓ É DEVIDO A SUA IMPORTÂNCIA NO ROMPER DE UMA NOVA ERA DAS TECNOLOGIAS DA INFORMAÇÃO E COMUNICAÇÃO QUE É FUNDAMENTAL PARA UM NOVO PARADIGMA INDUSTRIAL. MAS SE DEVE SOBRETUDO AS SANÇÕES IMPOSTAS PELOS EUA À HUAWEI, SOB A ALEGAÇÃO DE ESPIONAGEM EM CONJUNTO COM O ESTADO CHINÊS. TAIS ACUSAÇÕES LEVAM A INDAGAÇÕES QUANTOS AOS INTERESSES POR TRÁS DAS SANÇÕES ESTADUNIDENSES. AO MESMO TEMPO EM QUE NOSSOS OLHOS SE VOLTAM COM FACILIDADE E ENCANTO ÀS APLICABILIDADES QUE NOS SÃO ANUNCIADAS NA AUTOMAÇÃO DAS INDÚSTRIAS, VEÍCULOS SEM CONDUTORES E CASAS E CIDADES INTELIGENTES; AS APLICABILIDADES MILITARES SÃO IGUALMENTE VASTAS E CAPAZES DE INFLUENCIAR DE FORMA AINDA IMENSURÁVEL O TABULEIRO DO PODER GLOBAL. DENTRO DESSE CENÁRIO, O PRESENTE TRABALHO OBJETIVA INVESTIGAR AS APLICABILIDADES ECONÔMICAS E MILITARES DA TECNOLOGIA 5G E COMO AS MESMAS SE CORRELACIONAM NO CAMPO DO CONFLITO GEOPOLÍTICO ENTRE CHINA E EUA NUM CONTEXTO DE DISPUTA HEGEMÔNICA.</t>
+          <t>ESTA DISSERTAÇÃO PROCURA REFLETIR SOBRE A ADESÃO AO DISCURSO REACIONÁRIO DO MOVIMENTO ESCOLA SEM PARTIDO (ESP). TAMBÉM PRETENDE ANALISAR O DISCURSO DE ÓDIO VOLTADO CONTRA A EDUCAÇÃO, AVALIANDO EM QUAL MEDIDA ESTE SE CONSTITUI NUM PROJETO CONSERVADOR E EXCLUDENTE DE DIREITOS A PARTIR DO CASO DO COLÉGIO PEDRO II, ESCOLA PÚBLICA FEDERAL DE EXCELÊNCIA EM ENSINO BÁSICO. ATRAVÉS DA ANÁLISE DE COMO SE CONSTITUI O ESP, DE SUA HISTÓRIA E FORMA DE OPERAR, BUSCAMOS COMPREENDER COMO ESTE DISCURSO SE PROPAGA NA SOCIEDADE E COM QUAL INTENÇÃO. PRETENDE COMPREENDER SE ESTE SE CONFIGURA EM DISCURSO HEGEMÔNICO OU SIMPLES CONSTRUÇÃO DE TIRANIA. TAMBÉM PRETENDE COMPREENDER COMO DISCURSO DE ÓDIO E DE PÂNICO MORAL É APREENDIDO PELA AUDIÊNCIA: AS CONSEQUÊNCIAS, OS SENTIMENTOS ENVOLVIDOS, QUE HISTÓRIA SOBRE A SOCIEDADE BRASILEIRA ESTES CONTAM. PRETENDE ENTENDER COMO AS TRANSFORMAÇÕES PROMOVIDAS PELAS REDES SOCIAIS DIGITAIS NESSE NOVO ESPAÇO DE EXISTÊNCIA INCIVIL, CRIADO A PARTIR DA TECNOLOGIA, VEM DETERMINANDO AS RELAÇÕES SOCIAIS. DEBATER SOBRE TURBOCAPITALISMO, HEGEMONIA E NEOCOLONIALISMO A PARTIR DO ADVENTO DA INTELIGÊNCIA ARTIFICIAL NO NOVO BIOS VIRTUAL. PRETENDE INVESTIGAR SE O DISCURSO DO ESCOLA SEM PARTIDO SE TRADUZ EM DISCURSO FASCISTA E EM QUAL MEDIDA ISTO CORROBORA COM A DISPUTA PELA HEGEMONIA DA PAUTA NEOCONSERVADORA NA SOCIEDADE BRASILEIRA, ANALISANDO DE QUAL FORMA OS DISCURSOS DA EXTREMA DIREITA SÃO CONSTRUÍDOS, ECOADOS VIA REDES SOCIAIS E O NÍVEL DE ACEITAÇÃO/ADESÃO PELA SOCIEDADE. COMPROVAR QUE O MOVIMENTO ESCOLA SEM PARTIDO SE CONTRAPÕE À GARANTIA DE DIREITOS FUNDAMENTAIS E A SERVIÇO DA HEGEMONIA REGRESSIVA NEOLIBERAL. QUANTO AOS PROCEDIMENTOS METODOLÓGICOS, FORAM ESTES DE DUAS NATUREZAS: QUANTITATIVA E QUALITATIVA. A PESQUISA QUANTITATIVA FOI REALIZADA ATRAVÉS DA ANÁLISE DE REDES SOCIAIS (ARS) DA PÁGINA INSTITUCIONAL E DAS REDES SOCIAIS DIGITAIS DO MOVIMENTO ESCOLA SEM PARTIDO, DO “PAIS DO COLÉGIO PEDRO II CONTRA A IDEOLOGIA DE GÊNERO E A DOUTRINAÇÃO DOS ALUNOS” E DO SINDICATO DOS SERVIDORES DO COLÉGIO PEDRO II. A PESQUISA QUALITATIVA FOI GERADA A PARTIR DA ANÁLISE DE CONTEÚDO (DE DOCUMENTOS, VÍDEOS, ÁUDIOS E ENTREVISTAS), DA PESQUISA BIBLIOGRÁFICA (O COLÉGIO PEDRO II, O PROJETO ESCOLA SEM PARTIDO, O SINDSCOPE), DA PESQUISA HISTÓRICA E DOCUMENTAL (LEVANTAMENTO DE DOCUMENTOS OFICIAIS, LIVROS, REVISTAS, JORNAIS, PETIÇÕES, OFÍCIOS, NOTAS PÚBLICAS, SENTENÇAS JUDICIAIS) E DUAS ENTREVISTAS COM SERVIDORES DO COLÉGIO PEDRO II.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SINCE 2019, 5G TECHNOLOGY HAS BEEN GETTING MORE ATTENTION IN ECONOMIC AND POLITICAL CIRCLES, AS WELL AS IN ACADEMIA. PART OF THE REASON FOR THIS IS THAT 5G TECHNOLOGY IS AN ESSENTIAL ELEMENT OF THE NEW AGE OF INFORMATION AND COMMUNICATION TECHNOLOGY (ICT), LEADING TO THE EMERGENCE OF A NEW INDUSTRIAL PARADIGM. BUT THE MAIN REASON FOR ALL THE ATTENTION CONCERNING 5G TECHNOLOGY IS THE SANCTIONS IMPOSED BY THE US ON THE CHINESE ICT FIRM HUAWEI, UNDER THE ALLEGATION OF ESPIONAGE IN COOPERATION WITH THE CHINESE STATE. THESE ACCUSATIONS BRING QUESTIONS CONCERNING THE REAL INTERESTS BEHIND THE AMERICAN SANCTIONS. AT THE SAME TIME THAT OUR EYES EASILY FOCUS ON THE INTERESTING AND APPEALING CIVILIAN APPLICATIONS OF 5G TECHNOLOGY, SUCH AS IN THE AUTOMATION OF INDUSTRIES, DRIVER-LESS VEHICLES, AND INTELLIGENT HOUSES AND CITIES, THE MILITARY APPLICATIONS OF 5G ARE EQUALLY VAST AND CAPABLE OF INFLUENCING IN AN IMMEASURABLE MANNER THE GLOBAL POWER BOARD AS IT IS NOW DRAWN. IN THIS SCENARIO, THE PRESENT WORK INVESTIGATES THE ECONOMIC AND MILITARY APPLICATIONS OF 5G TECHNOLOGY AND THE WAY THESE TECHNOLOGIES ARE CORRELATED IN THE LARGER GEOPOLITICAL CONFLICT BETWEEN CHINA AND THE USA.</t>
+          <t>THIS MASTER’S DEGREE DISSERTATION HAS AS PURPOSE TO REFLECT ABOUT THE ADHERENCE TO THE REACTIONARY DISCOURSE OF THE SCHOOL WITHOUT PARTY (ESP) MOVEMENT. ALSO AIMS AT ANALYSING HATE SPEECH AGAINST EDUCATION, ASSESSING TO WHAT EXTENT THIS CONSTITUTES A CONSERVATIVE AND EXCLUSIONARY PROJECT OF RIGHTS FROM THE CASE OF COLÉGIO PEDRO II, FEDERAL PUBLIC SCHOOL OF EXCELLENCE IN BASIC EDUCATION. THROUGH THE ANALYSIS OF HOW ESP IS CONSTITUTED, ITS HISTORY AND ITS MODUS OPERANDI, WE SEEK TO UNDERSTAND HOW THIS DISCOURSE SPREADS THROUGH SOCIETY, AND WITH WHICH INTENT. INTENDS TO UNDERSTAND WHETHER THIS IS CONFIGURED IN HEGEMONIC DISCOURSE OR SIMPLY BUILDING TYRANNY. IT ALSO AIMS AT UNDERSTANDING HOW HATE SPEECH AND MORAL PANIC IS APPREHENDED BY THE PUBLIC, THE CONSEQUENCES, THE FEELINGS INVOLVED, THE HISTORY OF THE BRAZILIAN SOCIETY THEY RELATE. PROPOSES TO UNDERSTAND HOW THE TRANSFORMATIONS PROMOTED BY DIGITAL SOCIAL NETWORKS IN THIS NEW SPACE OF UNCIVIL EXISTENCE, CREATED FROM TECHNOLOGY, HAS BEEN DETERMINING SOCIAL RELATIONS. DISCUSSES TURBO CAPITALISM, HEGEMONY AND COLONIALISM FROM THE ADVENT OF ARTIFICIAL INTELLIGENCE IN THE NEW VIRTUAL BIOS. IT INTENDS TO INVESTIGATE WHETHER THE DISCOURSE OF THE SCHOOL WITHOUT PARTY (ESP) TRANSLATES INTO FASCIST DISCOURSE AND TO WHAT EXTENT THIS CORROBORATES THE DISPUTE OVER THE HEGEMONY OF THE NEOCONSERVATIVE AGENDA IN BRAZILIAN SOCIETY ANALYSING HOW THE DISCOURSES OF THE EXTREME RIGHT ARE BUILT, RELAYED BY SOCIAL NETWORKS AND THE LEVEL OF ACCEPTANCE/ADHERENCE OF SOCIETY. SHOW THAT THE SCHOOL WITHOUT PARTY IS OPPOSED TO THE GUARANTEE OF FUNDAMENTAL RIGHTS AND THAT THIS IS A PROJECT AT THE SERVICE OF REGRESSIVE NEOLIBERAL HEGEMONY. AS FOR THE METHODOLOGICAL PROCEDURES, THEY WERE OF TWO NATURES: QUANTITATIVE AND QUALITATIVE. THE QUANTITATIVE RESEARCH WAS CONDUCTED THROUGH THE ANALYSIS OF THE SOCIAL NETWORKS OF THE INSTITUTIONAL PAGE AND THE DIGITAL SOCIAL NETWORKS OF THE SCHOOL WITHOUT PARTY (ESP) MOVEMENT AS WELL AS THE "PARENTS OF THE COLÉGIO PEDRO II AGAINST THE IDEOLOGY OF GENDER AND INDOCTRINATION OF STUDENTS" AND THE UNION OF EMPLOYEES OF THE COLLEGE PEDRO II. THE QUALITATIVE RESEARCH WAS GENERATED FROM CONTENT ANALYSIS (DOCUMENTS, VIDEOS, AUDIOS AND INTERVIEWS), BIBLIOGRAPHICAL RESEARCH (THE COLÉGIO PEDRO II, THE PROJECT SCHOOL WITHOUT PARTY AND SINDSCOPE), HISTORICAL AND DOCUMENTARY RESEARCH (SURVEY OF OFFICIAL DOCUMENTS, BOOKS, MAGAZINES, NEWSPAPERS, PETITIONS, LETTERS, PUBLIC NOTES, COURT SENTENCES) AND TWO INTERVIEWS WITH EMPLOYEES OF COLÉGIO PEDRO II.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>HUAWEI;CHINA;EUA;GEOPOLÍTICA 5G;CIBERSEGURANÇA;HEGEMONIA</t>
+          <t>ESCOLA SEM PARTIDO;COLÉGIO PEDRO II;EDUCAÇÃO;NEOCONSERVADORISMO;NEOLIBERALISMO;TURBOCAPITALISMO;BIOS VIRTUAL;COMUNICAÇÃO;DISCURSO;INTELIGÊNCIA ARTIFICIAL.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>HUAWEI;CHINA;USA;5G GEOPOLITICS;CYBERSECURITY;HEGEMONY</t>
+          <t>SCHOOL WITHOUT PARTY;COLÉGIO PEDRO II;EDUCATION;NEOCONSERVATISM;NEOLIBERALISM;TURBOCAPITALISM;VIRTUAL BIOS;COMMUNICATION;DISCOURSE;ARTIFICIAL INTELLIGENCE.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Correlato</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>IA em sentido estrito</t>
         </is>
       </c>
       <c r="M20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
@@ -3183,16 +3183,16 @@
         <v>0</v>
       </c>
       <c r="Q20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>JOSE LUIS DA COSTA FIORI</t>
+          <t>VANTUIL PEREIRA</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>ECONOMIA POLÍTICA INTERNACIONAL</t>
+          <t>POLÍTICAS PÚBLICAS EM DIREITOS HUMANOS</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -3240,16 +3240,16 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12682786</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12441756</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>12682786</t>
+          <t>12441756</t>
         </is>
       </c>
       <c r="AE20" t="n">
-        <v>1385496</v>
+        <v>3810911</v>
       </c>
     </row>
     <row r="21">
@@ -3264,41 +3264,41 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>REJANE BARBOSA DE SOUSA NOGUEIRA</t>
+          <t>CHRISTIAN DE ALMEIDA BRANDAO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OBSERVANDO O PROJETO ESCOLA SEM PARTIDO EM UMA PERSPECTIVA CRÍTICA CONTRA-HEGEMÔNICA NO CONTEXTO DOS ATAQUES A UMA ESCOLA FEDERAL DO RIO DE JANEIRO, O COLÉGIO PEDRO II</t>
+          <t>GREEN INFLUENCE, ECONOMIC REALITIES, AND POLITICAL LANDSCAPES: UNDERSTANDING CARBON TAX DETERMINANTS IN EUROPE USING MACHINE LEARNING</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ESTA DISSERTAÇÃO PROCURA REFLETIR SOBRE A ADESÃO AO DISCURSO REACIONÁRIO DO MOVIMENTO ESCOLA SEM PARTIDO (ESP). TAMBÉM PRETENDE ANALISAR O DISCURSO DE ÓDIO VOLTADO CONTRA A EDUCAÇÃO, AVALIANDO EM QUAL MEDIDA ESTE SE CONSTITUI NUM PROJETO CONSERVADOR E EXCLUDENTE DE DIREITOS A PARTIR DO CASO DO COLÉGIO PEDRO II, ESCOLA PÚBLICA FEDERAL DE EXCELÊNCIA EM ENSINO BÁSICO. ATRAVÉS DA ANÁLISE DE COMO SE CONSTITUI O ESP, DE SUA HISTÓRIA E FORMA DE OPERAR, BUSCAMOS COMPREENDER COMO ESTE DISCURSO SE PROPAGA NA SOCIEDADE E COM QUAL INTENÇÃO. PRETENDE COMPREENDER SE ESTE SE CONFIGURA EM DISCURSO HEGEMÔNICO OU SIMPLES CONSTRUÇÃO DE TIRANIA. TAMBÉM PRETENDE COMPREENDER COMO DISCURSO DE ÓDIO E DE PÂNICO MORAL É APREENDIDO PELA AUDIÊNCIA: AS CONSEQUÊNCIAS, OS SENTIMENTOS ENVOLVIDOS, QUE HISTÓRIA SOBRE A SOCIEDADE BRASILEIRA ESTES CONTAM. PRETENDE ENTENDER COMO AS TRANSFORMAÇÕES PROMOVIDAS PELAS REDES SOCIAIS DIGITAIS NESSE NOVO ESPAÇO DE EXISTÊNCIA INCIVIL, CRIADO A PARTIR DA TECNOLOGIA, VEM DETERMINANDO AS RELAÇÕES SOCIAIS. DEBATER SOBRE TURBOCAPITALISMO, HEGEMONIA E NEOCOLONIALISMO A PARTIR DO ADVENTO DA INTELIGÊNCIA ARTIFICIAL NO NOVO BIOS VIRTUAL. PRETENDE INVESTIGAR SE O DISCURSO DO ESCOLA SEM PARTIDO SE TRADUZ EM DISCURSO FASCISTA E EM QUAL MEDIDA ISTO CORROBORA COM A DISPUTA PELA HEGEMONIA DA PAUTA NEOCONSERVADORA NA SOCIEDADE BRASILEIRA, ANALISANDO DE QUAL FORMA OS DISCURSOS DA EXTREMA DIREITA SÃO CONSTRUÍDOS, ECOADOS VIA REDES SOCIAIS E O NÍVEL DE ACEITAÇÃO/ADESÃO PELA SOCIEDADE. COMPROVAR QUE O MOVIMENTO ESCOLA SEM PARTIDO SE CONTRAPÕE À GARANTIA DE DIREITOS FUNDAMENTAIS E A SERVIÇO DA HEGEMONIA REGRESSIVA NEOLIBERAL. QUANTO AOS PROCEDIMENTOS METODOLÓGICOS, FORAM ESTES DE DUAS NATUREZAS: QUANTITATIVA E QUALITATIVA. A PESQUISA QUANTITATIVA FOI REALIZADA ATRAVÉS DA ANÁLISE DE REDES SOCIAIS (ARS) DA PÁGINA INSTITUCIONAL E DAS REDES SOCIAIS DIGITAIS DO MOVIMENTO ESCOLA SEM PARTIDO, DO “PAIS DO COLÉGIO PEDRO II CONTRA A IDEOLOGIA DE GÊNERO E A DOUTRINAÇÃO DOS ALUNOS” E DO SINDICATO DOS SERVIDORES DO COLÉGIO PEDRO II. A PESQUISA QUALITATIVA FOI GERADA A PARTIR DA ANÁLISE DE CONTEÚDO (DE DOCUMENTOS, VÍDEOS, ÁUDIOS E ENTREVISTAS), DA PESQUISA BIBLIOGRÁFICA (O COLÉGIO PEDRO II, O PROJETO ESCOLA SEM PARTIDO, O SINDSCOPE), DA PESQUISA HISTÓRICA E DOCUMENTAL (LEVANTAMENTO DE DOCUMENTOS OFICIAIS, LIVROS, REVISTAS, JORNAIS, PETIÇÕES, OFÍCIOS, NOTAS PÚBLICAS, SENTENÇAS JUDICIAIS) E DUAS ENTREVISTAS COM SERVIDORES DO COLÉGIO PEDRO II.</t>
+          <t>ESTA PESQUISA DESENVOLVE ÁRVORES DE CLASSIFICAÇÃO, UM MÉTODO DE APRENDIZAGEM DE MÁQUINA, PARA INTERPRETAR E PREVER A IMPLEMENTAÇÃO E VARIAÇÃO DE IMPOSTOS SOBRE CARBONO NA EUROPA. À MEDIDA QUE A TEMPERATURA DO PLANETA AQUECE E OS IMPACTOS DAS MUDANÇAS CLIMÁTICAS AUMENTAM, MAIS GOVERNOS ADOTAM MEDIDAS DE PRECIFICAÇÃO DE CARBONO PARA REDUZIR AS EMISSÕES. OS IMPOSTOS SOBRE CARBONO SÃO NOTÁVEIS POR SUA SIMPLICIDADE DE INTRODUÇÃO, CAPACIDADE DE GERAR RECEITAS E COMPROVADA EFICÁCIA NA REDUÇÃO DE EMISSÕES. APESAR DE SEUS MÉRITOS, ATÉ 2020, APENAS 21 PAÍSES EM TODO O MUNDO HAVIAM IMPLEMENTADO IMPOSTOS SOBRE CARBONO, SENDO 15 NA EUROPA, MUITOS COM TAXAS RELATIVAMENTE BAIXAS. PARA MELHOR COMPREENDER ESSE CENÁRIO COMPLEXO, AS ÁRVORES DE CLASSIFICAÇÃO SÃO UTILIZADAS PARA INVESTIGAR DUAS HIPÓTESES RELACIONADAS AOS EFEITOS DA IDEOLOGIA DO GABINETE E À INFLUÊNCIA DOS PARTIDOS VERDES NA IMPLEMENTAÇÃO E VARIAÇÃO DE PREÇOS DO IMPOSTO SOBRE O CARBONO. AO INCORPORAR CARACTERÍSTICAS IDEOLÓGICAS NOS MODELOS, ESSA PESQUISA RECONHECE QUE OS IMPOSTOS SOBRE CARBONO ESTÃO INSERIDOS EM UM CONTEXTO POLÍTICO, E QUE AS RECOMENDAÇÕES DE ECONOMISTAS E AMBIENTALISTAS TEM IMPACTO LIMITADO. OS MODELOS RELACIONADOS À VARIAÇÃO DE PREÇOS DESTACARAM A IMPORTÂNCIA DO DESEMPENHO DOS PARTIDOS VERDES NAS ELEIÇÕES, EMBORA SUA PRESENÇA NO GOVERNO NÃO IMPEDISSE REDUÇÕES DE PREÇOS. SURPREENDENTEMENTE, NENHUM GOVERNO COM UMA PARCELA SIGNIFICATIVA DE VOTOS PARA OS PARTIDOS VERDES E SEM UMA DÍVIDA GOVERNAMENTAL MUITO BAIXA REDUZIU OS IMPOSTOS SOBRE CARBONO. ALÉM DISSO, OS MODELOS INDICARAM QUE SER UM GOVERNO DE DIREITA NÃO IMPEDIU AUMENTOS DE PREÇO, E RECEITAS VINCULADAS FORAM ASSOCIADAS A AUMENTOS NOS IMPOSTOS SOBRE CARBONO. POR OUTRO LADO, O MODELO DE ÁRVORE DE DECISÃO PARA A IMPLEMENTAÇÃO DO IMPOSTO DESTACOU A IMPORTÂNCIA DA DIVISÃO ESQUERDA-DIREITA EM PAÍSES COM UM PIB PER CAPITA (PPC) INFERIOR A 39 MIL DÓLARES. EM NAÇÕES MAIS RICAS, A CRIAÇÃO DE IMPOSTOS SOBRE CARBONO FOI ASSOCIADA A UM SISTEMA DEMOCRÁTICO LIBERAL ROBUSTO, AUSÊNCIA DE UMA ENORME DÍVIDA GOVERNAMENTAL, OCORRÊNCIA DE DESASTRES NATURAIS DURANTE O MANDATO DO GOVERNO E UMA NÃO DEPENDÊNCIA COMPLETA DE COMBUSTÍVEIS FÓSSEIS PARA O CONSUMO DE ENERGIA. AS CARACTERÍSTICAS IDEOLÓGICAS MOSTRARAM-SE RELEVANTES PARA TODOS OS MODELOS, REFORÇANDO A IMPORTÂNCIA DAS CONSIDERAÇÕES POLÍTICAS NA PESQUISA DE POLÍTICAS CLIMÁTICAS.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>THIS MASTER’S DEGREE DISSERTATION HAS AS PURPOSE TO REFLECT ABOUT THE ADHERENCE TO THE REACTIONARY DISCOURSE OF THE SCHOOL WITHOUT PARTY (ESP) MOVEMENT. ALSO AIMS AT ANALYSING HATE SPEECH AGAINST EDUCATION, ASSESSING TO WHAT EXTENT THIS CONSTITUTES A CONSERVATIVE AND EXCLUSIONARY PROJECT OF RIGHTS FROM THE CASE OF COLÉGIO PEDRO II, FEDERAL PUBLIC SCHOOL OF EXCELLENCE IN BASIC EDUCATION. THROUGH THE ANALYSIS OF HOW ESP IS CONSTITUTED, ITS HISTORY AND ITS MODUS OPERANDI, WE SEEK TO UNDERSTAND HOW THIS DISCOURSE SPREADS THROUGH SOCIETY, AND WITH WHICH INTENT. INTENDS TO UNDERSTAND WHETHER THIS IS CONFIGURED IN HEGEMONIC DISCOURSE OR SIMPLY BUILDING TYRANNY. IT ALSO AIMS AT UNDERSTANDING HOW HATE SPEECH AND MORAL PANIC IS APPREHENDED BY THE PUBLIC, THE CONSEQUENCES, THE FEELINGS INVOLVED, THE HISTORY OF THE BRAZILIAN SOCIETY THEY RELATE. PROPOSES TO UNDERSTAND HOW THE TRANSFORMATIONS PROMOTED BY DIGITAL SOCIAL NETWORKS IN THIS NEW SPACE OF UNCIVIL EXISTENCE, CREATED FROM TECHNOLOGY, HAS BEEN DETERMINING SOCIAL RELATIONS. DISCUSSES TURBO CAPITALISM, HEGEMONY AND COLONIALISM FROM THE ADVENT OF ARTIFICIAL INTELLIGENCE IN THE NEW VIRTUAL BIOS. IT INTENDS TO INVESTIGATE WHETHER THE DISCOURSE OF THE SCHOOL WITHOUT PARTY (ESP) TRANSLATES INTO FASCIST DISCOURSE AND TO WHAT EXTENT THIS CORROBORATES THE DISPUTE OVER THE HEGEMONY OF THE NEOCONSERVATIVE AGENDA IN BRAZILIAN SOCIETY ANALYSING HOW THE DISCOURSES OF THE EXTREME RIGHT ARE BUILT, RELAYED BY SOCIAL NETWORKS AND THE LEVEL OF ACCEPTANCE/ADHERENCE OF SOCIETY. SHOW THAT THE SCHOOL WITHOUT PARTY IS OPPOSED TO THE GUARANTEE OF FUNDAMENTAL RIGHTS AND THAT THIS IS A PROJECT AT THE SERVICE OF REGRESSIVE NEOLIBERAL HEGEMONY. AS FOR THE METHODOLOGICAL PROCEDURES, THEY WERE OF TWO NATURES: QUANTITATIVE AND QUALITATIVE. THE QUANTITATIVE RESEARCH WAS CONDUCTED THROUGH THE ANALYSIS OF THE SOCIAL NETWORKS OF THE INSTITUTIONAL PAGE AND THE DIGITAL SOCIAL NETWORKS OF THE SCHOOL WITHOUT PARTY (ESP) MOVEMENT AS WELL AS THE "PARENTS OF THE COLÉGIO PEDRO II AGAINST THE IDEOLOGY OF GENDER AND INDOCTRINATION OF STUDENTS" AND THE UNION OF EMPLOYEES OF THE COLLEGE PEDRO II. THE QUALITATIVE RESEARCH WAS GENERATED FROM CONTENT ANALYSIS (DOCUMENTS, VIDEOS, AUDIOS AND INTERVIEWS), BIBLIOGRAPHICAL RESEARCH (THE COLÉGIO PEDRO II, THE PROJECT SCHOOL WITHOUT PARTY AND SINDSCOPE), HISTORICAL AND DOCUMENTARY RESEARCH (SURVEY OF OFFICIAL DOCUMENTS, BOOKS, MAGAZINES, NEWSPAPERS, PETITIONS, LETTERS, PUBLIC NOTES, COURT SENTENCES) AND TWO INTERVIEWS WITH EMPLOYEES OF COLÉGIO PEDRO II.</t>
+          <t>THIS RESEARCH DEVELOPS CLASSIFICATION TREES, A MACHINE LEARNING METHOD, TO INTERPRET AND PREDICT THE IMPLEMENTATION AND VARIATION OF CARBON TAXES IN EUROPE. AS OUR PLANET’S TEMPERATURE INCREASES AND THE EFFECTS OF CLIMATE CHANGE INTENSIFY, AN INCREASING NUMBER OF GOVERNMENTS ARE IMPLEMENTING CARBON PRICING MEASURES TO REDUCE EMISSIONS. CARBON TAXES ARE AN INTERESTING MECHANISM, AS THEY ARE SIMPLE TO INTRODUCE, GENERATE REVENUE, AND HAVE BEEN PROVEN TO REDUCE EMISSIONS. DESPITE THESE MERITS, AS OF 2020, ONLY 21 COUNTRIES WORLDWIDE HAVE IMPLEMENTED CARBON TAXES, WITH 15 OF THOSE SITUATED IN EUROPE, AND MANY OF THESE TAXES FEATURE COMPARATIVELY LOW RATES. TO BETTER UNDERSTAND THIS INTRICATE LANDSCAPE, THE CLASSIFICATION TREES ARE UTILIZED TO INVESTIGATE TWO HYPOTHESES CONCERNING THE EFFECTS OF CABINET IDEOLOGY AND THE INFLUENCE OF GREEN PARTIES ON CARBON TAX IMPLEMENTATION AND PRICE VARIATION. BY INCORPORATING IDEOLOGICAL FEATURES INTO THE MODELS, THIS RESEARCH RECOGNIZES THAT CARBON TAXES DO NOT EXIST IN A POLITICAL VACUUM, AND THAT THE ADVICE OF ECONOMISTS AND ENVIRONMENTALISTS ONLY GOES SO FAR. THE TWO MODELS RELATED TO THE PRICE VARIATION DEMONSTRATED THE IMPORTANCE OF THE GREEN PARTIES PERFORMANCE IN THE ELECTION, ALTHOUGH THEIR PRESENCE IN CABINET DOES NOT PREVENT PRICE DECREASES. INTERESTINGLY, NO CABINET THAT EXPERIENCED A SUBSTANTIAL VOTE SHARE FOR GREEN PARTIES AND DID NOT HAVE VERY LOW GOVERNMENT DEBT DECREASE THEIR CARBON TAXES. THE MODELS ALSO INDICATED THAT BEING A RIGHT-WING CABINET DOES NOT PREVENT PRICE INCREASES, AND THAT EARMARK REVENUES ARE ASSOCIATED WITH CARBON TAX INCREASES. ON THE OTHER HAND, THE DECISION TREE MODEL FOR THE TAX’S IMPLEMENTATION DEMONSTRATED THE IMPORTANCE OF THE LEFT-RIGHT CLEAVAGE WHEN THE GDP PER CAPITA (PPP) IS LOWER THAN 39 THOUSAND DOLLARS. IN WEALTHIER COUNTRIES, THE CREATION OF A CARBON TAX WAS ASSOCIATED WITH A STRONG LIBERAL DEMOCRATIC SYSTEM, THE ABSENCE OF A CRIPPLING DEBT BURDEN, THE OCCURRENCE OF A NATURAL DISASTER DURING THE CABINET'S TENURE, AND NOT BEING COMPLETELY RELYING ON FOSSIL FUELS FOR ENERGY CONSUMPTION. THE IDEOLOGICAL FEATURES WERE DEEMED RELEVANT TO THE THREE MODELS, FURTHER DEMONSTRATING THE IMPORTANCE OF POLITICAL CONSIDERATIONS IN THE REALM OF CLIMATE POLICY RESEARCH.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ESCOLA SEM PARTIDO;COLÉGIO PEDRO II;EDUCAÇÃO;NEOCONSERVADORISMO;NEOLIBERALISMO;TURBOCAPITALISMO;BIOS VIRTUAL;COMUNICAÇÃO;DISCURSO;INTELIGÊNCIA ARTIFICIAL.</t>
+          <t>REGULAMENTAÇÕES AMBIENTAIS;MODELO DECISÓRIO;TRIBUTAÇÃO DE EMISSÕES;CLIVAGEM IDEOLÓGICA.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>SCHOOL WITHOUT PARTY;COLÉGIO PEDRO II;EDUCATION;NEOCONSERVATISM;NEOLIBERALISM;TURBOCAPITALISM;VIRTUAL BIOS;COMMUNICATION;DISCOURSE;ARTIFICIAL INTELLIGENCE.</t>
+          <t>ENVIRONMENTAL REGULATIONS;DECISION-MAKING MODEL;EMISSION TAXATION;IDEOLOGICAL CLEAVAGE.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3308,15 +3308,15 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>IA em sentido estrito</t>
+          <t>Aprendizado de máquina (ML)</t>
         </is>
       </c>
       <c r="M21" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" t="b">
         <v>1</v>
       </c>
-      <c r="N21" t="b">
-        <v>0</v>
-      </c>
       <c r="O21" t="b">
         <v>0</v>
       </c>
@@ -3328,45 +3328,45 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>VANTUIL PEREIRA</t>
+          <t>RODRIGO BARROS DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>POLÍTICAS PÚBLICAS EM DIREITOS HUMANOS</t>
+          <t>CIÊNCIA POLÍTICA</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DO RIO DE JANEIRO</t>
+          <t>UNIVERSIDADE FEDERAL DE PERNAMBUCO</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>UFRJ</t>
+          <t>UFPE</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>SUDESTE</t>
+          <t>NORDESTE</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>PERNAMBUCO</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>PORTUGUES</t>
+          <t>INGLES</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3381,16 +3381,16 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12441756</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14475475</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>12441756</t>
+          <t>14475475</t>
         </is>
       </c>
       <c r="AE21" t="n">
-        <v>3810911</v>
+        <v>4028790</v>
       </c>
     </row>
     <row r="22">
@@ -3409,37 +3409,37 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CHRISTIAN DE ALMEIDA BRANDAO</t>
+          <t>GUILHERME OTAVIANO SOARES</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GREEN INFLUENCE, ECONOMIC REALITIES, AND POLITICAL LANDSCAPES: UNDERSTANDING CARBON TAX DETERMINANTS IN EUROPE USING MACHINE LEARNING</t>
+          <t>ACEITAÇÃO DO USO DE INTELIGÊNCIA ARTIFICIAL NA POLÍTICA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ESTA PESQUISA DESENVOLVE ÁRVORES DE CLASSIFICAÇÃO, UM MÉTODO DE APRENDIZAGEM DE MÁQUINA, PARA INTERPRETAR E PREVER A IMPLEMENTAÇÃO E VARIAÇÃO DE IMPOSTOS SOBRE CARBONO NA EUROPA. À MEDIDA QUE A TEMPERATURA DO PLANETA AQUECE E OS IMPACTOS DAS MUDANÇAS CLIMÁTICAS AUMENTAM, MAIS GOVERNOS ADOTAM MEDIDAS DE PRECIFICAÇÃO DE CARBONO PARA REDUZIR AS EMISSÕES. OS IMPOSTOS SOBRE CARBONO SÃO NOTÁVEIS POR SUA SIMPLICIDADE DE INTRODUÇÃO, CAPACIDADE DE GERAR RECEITAS E COMPROVADA EFICÁCIA NA REDUÇÃO DE EMISSÕES. APESAR DE SEUS MÉRITOS, ATÉ 2020, APENAS 21 PAÍSES EM TODO O MUNDO HAVIAM IMPLEMENTADO IMPOSTOS SOBRE CARBONO, SENDO 15 NA EUROPA, MUITOS COM TAXAS RELATIVAMENTE BAIXAS. PARA MELHOR COMPREENDER ESSE CENÁRIO COMPLEXO, AS ÁRVORES DE CLASSIFICAÇÃO SÃO UTILIZADAS PARA INVESTIGAR DUAS HIPÓTESES RELACIONADAS AOS EFEITOS DA IDEOLOGIA DO GABINETE E À INFLUÊNCIA DOS PARTIDOS VERDES NA IMPLEMENTAÇÃO E VARIAÇÃO DE PREÇOS DO IMPOSTO SOBRE O CARBONO. AO INCORPORAR CARACTERÍSTICAS IDEOLÓGICAS NOS MODELOS, ESSA PESQUISA RECONHECE QUE OS IMPOSTOS SOBRE CARBONO ESTÃO INSERIDOS EM UM CONTEXTO POLÍTICO, E QUE AS RECOMENDAÇÕES DE ECONOMISTAS E AMBIENTALISTAS TEM IMPACTO LIMITADO. OS MODELOS RELACIONADOS À VARIAÇÃO DE PREÇOS DESTACARAM A IMPORTÂNCIA DO DESEMPENHO DOS PARTIDOS VERDES NAS ELEIÇÕES, EMBORA SUA PRESENÇA NO GOVERNO NÃO IMPEDISSE REDUÇÕES DE PREÇOS. SURPREENDENTEMENTE, NENHUM GOVERNO COM UMA PARCELA SIGNIFICATIVA DE VOTOS PARA OS PARTIDOS VERDES E SEM UMA DÍVIDA GOVERNAMENTAL MUITO BAIXA REDUZIU OS IMPOSTOS SOBRE CARBONO. ALÉM DISSO, OS MODELOS INDICARAM QUE SER UM GOVERNO DE DIREITA NÃO IMPEDIU AUMENTOS DE PREÇO, E RECEITAS VINCULADAS FORAM ASSOCIADAS A AUMENTOS NOS IMPOSTOS SOBRE CARBONO. POR OUTRO LADO, O MODELO DE ÁRVORE DE DECISÃO PARA A IMPLEMENTAÇÃO DO IMPOSTO DESTACOU A IMPORTÂNCIA DA DIVISÃO ESQUERDA-DIREITA EM PAÍSES COM UM PIB PER CAPITA (PPC) INFERIOR A 39 MIL DÓLARES. EM NAÇÕES MAIS RICAS, A CRIAÇÃO DE IMPOSTOS SOBRE CARBONO FOI ASSOCIADA A UM SISTEMA DEMOCRÁTICO LIBERAL ROBUSTO, AUSÊNCIA DE UMA ENORME DÍVIDA GOVERNAMENTAL, OCORRÊNCIA DE DESASTRES NATURAIS DURANTE O MANDATO DO GOVERNO E UMA NÃO DEPENDÊNCIA COMPLETA DE COMBUSTÍVEIS FÓSSEIS PARA O CONSUMO DE ENERGIA. AS CARACTERÍSTICAS IDEOLÓGICAS MOSTRARAM-SE RELEVANTES PARA TODOS OS MODELOS, REFORÇANDO A IMPORTÂNCIA DAS CONSIDERAÇÕES POLÍTICAS NA PESQUISA DE POLÍTICAS CLIMÁTICAS.</t>
+          <t>O TRABALHO EXAMINA A ACEITAÇÃO DO USO DE INTELIGÊNCIA ARTIFICIAL (IA) NA POLÍTICA, FOCANDO ESPECIALMENTE NOS IMPACTOS DESSA TECNOLOGIA EM PROCESSOS LEGISLATIVOS E NA FORMULAÇÃO DE POLÍTICAS PÚBLICAS. O USO DA IA NA POLÍTICA PROMETE UMA REVOLUÇÃO EM TERMOS DE EFICIÊNCIA ADMINISTRATIVA, COM APLICAÇÕES QUE VARIAM DESDE A AUTOMAÇÃO DE PROCESSOS ATÉ A ANÁLISE DE GRANDES VOLUMES DE DADOS, OFERECENDO POTENCIAL PARA DECISÕES MAIS EMBASADAS E RESPOSTAS RÁPIDAS A DEMANDAS SOCIAIS. CONTUDO, ESSA ADOÇÃO APRESENTA DESAFIOS ÉTICOS E PRÁTICOS, LEVANTANDO QUESTIONAMENTOS SOBRE A PRESERVAÇÃO DOS PRINCÍPIOS DEMOCRÁTICOS. O PRINCIPAL OBJETIVO DA PESQUISA É INVESTIGAR A ACEITAÇÃO DA IA NO CAMPO POLÍTICO, EXPLORANDO A FAMILIARIDADE E AS PERCEPÇÕES DE PARLAMENTARES BRASILEIROS SOBRE O USO DESSA TECNOLOGIA EM SUAS ATIVIDADES LEGISLATIVAS. A PESQUISA BUSCA ENTENDER COMO ESSES AGENTES ASSIMILAM E AVALIAM A ADOÇÃO DA IA INVESTIGANDO SE A CONSIDERAM UM RECURSO VÁLIDO PARA AMPLIAR A REPRESENTATIVIDADE E A EFICIÊNCIA DA GOVERNANÇA, OU SE EXISTEM PREOCUPAÇÕES QUE RESTRINGEM SEU USO. A JUSTIFICATIVA PARA A PESQUISA RESIDE NA CRESCENTE IMPORTÂNCIA DA IA NA SOCIEDADE E NOS IMPACTOS POTENCIAIS DE SEU USO POLÍTICO, ESPECIALMENTE EM UM CONTEXTO DE POLARIZAÇÃO E DESINFORMAÇÃO, PODENDO CAUSAR IMPACTOS À DEMOCRACIA. ALÉM DE UMA PESQUISA BIBLIOGRÁFICA ACERCA DO TEMA, FOI REALIZADA UMA PESQUISA QUALITATIVA, CENTRADA EM ENTREVISTAS SEMIESTRUTURADAS REALIZADAS COM LEGISLADORES EM NÍVEIS MUNICIPAL, ESTADUAL E FEDERAL. AS ENTREVISTAS FORAM GRAVADAS, TRANSCRITAS, CODIFICADAS E SUBMETIDAS A ANÁLISE TEMÁTICA PARA IDENTIFICAR PADRÕES DE RESPOSTA. AS ENTREVISTAS FORAM CONDUZIDAS ATÉ O PONTO DE SATURAÇÃO TEÓRICA, PERMITINDO UM ENTENDIMENTO ROBUSTO SOBRE AS PERCEPÇÕES E RESISTÊNCIAS DOS PARLAMENTARES EM RELAÇÃO AO USO DA IA. OS RESULTADOS INDICAM UMA ACEITAÇÃO MODERADA DA IA, COM OS LEGISLADORES RECONHECENDO O POTENCIAL DA TECNOLOGIA PARA MELHORAR PROCESSOS LEGISLATIVOS, MAS EXPRESSANDO PREOCUPAÇÕES QUANTO AO IMPACTO SOBRE SUA AUTONOMIA E SOBRE OS VALORES DEMOCRÁTICOS. EMBORA ALGUNS VEJAM A IA COMO UM RECURSO PROMISSOR PARA UMA POLÍTICA MAIS EFICIENTE, EXISTE UM RECEIO QUANTO À POSSIBILIDADE DE MANIPULAÇÃO E FALTA DE SUPERVISÃO HUMANA. A PESQUISA SUGERE QUE A PLENA ACEITAÇÃO DA IA NA POLÍTICA EXIGE UM CONJUNTO DE REGULAMENTAÇÕES QUE GARANTAM A TRANSPARÊNCIA, O CONTROLE DEMOCRÁTICO E A PROTEÇÃO CONTRA VIESES, APONTANDO PARA A NECESSIDADE DE UMA MUDANÇA CULTURAL E NORMATIVA QUE POSSIBILITE O USO ÉTICO E RESPONSÁVEL DESSA TECNOLOGIA.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>THIS RESEARCH DEVELOPS CLASSIFICATION TREES, A MACHINE LEARNING METHOD, TO INTERPRET AND PREDICT THE IMPLEMENTATION AND VARIATION OF CARBON TAXES IN EUROPE. AS OUR PLANET’S TEMPERATURE INCREASES AND THE EFFECTS OF CLIMATE CHANGE INTENSIFY, AN INCREASING NUMBER OF GOVERNMENTS ARE IMPLEMENTING CARBON PRICING MEASURES TO REDUCE EMISSIONS. CARBON TAXES ARE AN INTERESTING MECHANISM, AS THEY ARE SIMPLE TO INTRODUCE, GENERATE REVENUE, AND HAVE BEEN PROVEN TO REDUCE EMISSIONS. DESPITE THESE MERITS, AS OF 2020, ONLY 21 COUNTRIES WORLDWIDE HAVE IMPLEMENTED CARBON TAXES, WITH 15 OF THOSE SITUATED IN EUROPE, AND MANY OF THESE TAXES FEATURE COMPARATIVELY LOW RATES. TO BETTER UNDERSTAND THIS INTRICATE LANDSCAPE, THE CLASSIFICATION TREES ARE UTILIZED TO INVESTIGATE TWO HYPOTHESES CONCERNING THE EFFECTS OF CABINET IDEOLOGY AND THE INFLUENCE OF GREEN PARTIES ON CARBON TAX IMPLEMENTATION AND PRICE VARIATION. BY INCORPORATING IDEOLOGICAL FEATURES INTO THE MODELS, THIS RESEARCH RECOGNIZES THAT CARBON TAXES DO NOT EXIST IN A POLITICAL VACUUM, AND THAT THE ADVICE OF ECONOMISTS AND ENVIRONMENTALISTS ONLY GOES SO FAR. THE TWO MODELS RELATED TO THE PRICE VARIATION DEMONSTRATED THE IMPORTANCE OF THE GREEN PARTIES PERFORMANCE IN THE ELECTION, ALTHOUGH THEIR PRESENCE IN CABINET DOES NOT PREVENT PRICE DECREASES. INTERESTINGLY, NO CABINET THAT EXPERIENCED A SUBSTANTIAL VOTE SHARE FOR GREEN PARTIES AND DID NOT HAVE VERY LOW GOVERNMENT DEBT DECREASE THEIR CARBON TAXES. THE MODELS ALSO INDICATED THAT BEING A RIGHT-WING CABINET DOES NOT PREVENT PRICE INCREASES, AND THAT EARMARK REVENUES ARE ASSOCIATED WITH CARBON TAX INCREASES. ON THE OTHER HAND, THE DECISION TREE MODEL FOR THE TAX’S IMPLEMENTATION DEMONSTRATED THE IMPORTANCE OF THE LEFT-RIGHT CLEAVAGE WHEN THE GDP PER CAPITA (PPP) IS LOWER THAN 39 THOUSAND DOLLARS. IN WEALTHIER COUNTRIES, THE CREATION OF A CARBON TAX WAS ASSOCIATED WITH A STRONG LIBERAL DEMOCRATIC SYSTEM, THE ABSENCE OF A CRIPPLING DEBT BURDEN, THE OCCURRENCE OF A NATURAL DISASTER DURING THE CABINET'S TENURE, AND NOT BEING COMPLETELY RELYING ON FOSSIL FUELS FOR ENERGY CONSUMPTION. THE IDEOLOGICAL FEATURES WERE DEEMED RELEVANT TO THE THREE MODELS, FURTHER DEMONSTRATING THE IMPORTANCE OF POLITICAL CONSIDERATIONS IN THE REALM OF CLIMATE POLICY RESEARCH.</t>
+          <t>THIS STUDY EXAMINES THE ACCEPTANCE OF ARTIFICIAL INTELLIGENCE (AI) USE IN POLITICS, FOCUSING PARTICULARLY ON THE IMPACT OF THIS TECHNOLOGY ON LEGISLATIVE PROCESSES AND PUBLIC POLICY FORMULATION. THE USE OF AI IN POLITICS PROMISES A REVOLUTION IN ADMINISTRATIVE EFFICIENCY, WITH APPLICATIONS RANGING FROM PROCESS AUTOMATION TO THE ANALYSIS OF LARGE DATASETS, OFFERING THE POTENTIAL FOR MORE INFORMED DECISIONS AND RAPID RESPONSES TO SOCIAL DEMANDS. HOWEVER, THIS ADOPTION PRESENTS ETHICAL AND PRACTICAL CHALLENGES, RAISING QUESTIONS ABOUT PRESERVING DEMOCRATIC PRINCIPLES. THE MAIN OBJECTIVE OF THIS RESEARCH IS TO INVESTIGATE THE ACCEPTANCE OF AI IN THE POLITICAL FIELD, EXPLORING BRAZILIAN LEGISLATORS' FAMILIARITY WITH AND PERCEPTIONS OF THIS TECHNOLOGY IN THEIR LEGISLATIVE ACTIVITIES. THE RESEARCH AIMS TO UNDERSTAND HOW THESE AGENTS ASSIMILATE AND EVALUATE AI ADOPTION, INVESTIGATING WHETHER THEY CONSIDER IT A VALID RESOURCE TO ENHANCE REPRESENTATIVENESS AND GOVERNANCE EFFICIENCY OR IF CONCERNS EXIST THAT LIMIT ITS USE. THE RESEARCH JUSTIFICATION LIES IN THE GROWING IMPORTANCE OF AI IN SOCIETY AND ITS POTENTIAL POLITICAL IMPACTS, ESPECIALLY IN THE CONTEXT OF POLARIZATION AND MISINFORMATION, WHICH MAY AFFECT DEMOCRACY. IN ADDITION TO A BIBLIOGRAPHIC REVIEW ON THE SUBJECT, THE STUDY UTILIZED A QUALITATIVE METHODOLOGY CENTERED ON SEMI-STRUCTURED INTERVIEWS WITH LEGISLATORS AT MUNICIPAL, STATE, AND FEDERAL LEVELS. THE INTERVIEWS WERE RECORDED, TRANSCRIBED, CODED, AND SUBJECTED TO THEMATIC ANALYSIS TO IDENTIFY RESPONSE PATTERNS. INTERVIEWS WERE CONDUCTED UNTIL REACHING THEORETICAL SATURATION, ENABLING A ROBUST UNDERSTANDING OF THE PERCEPTIONS AND RESISTANCE OF LEGISLATORS REGARDING AI USE. THE RESULTS INDICATE A MODERATE ACCEPTANCE OF AI, WITH LEGISLATORS RECOGNIZING THE TECHNOLOGY'S POTENTIAL TO IMPROVE LEGISLATIVE PROCESSES WHILE EXPRESSING CONCERNS ABOUT ITS IMPACT ON THEIR AUTONOMY AND DEMOCRATIC VALUES. ALTHOUGH SOME SEE AI AS A PROMISING RESOURCE FOR MORE EFFICIENT POLITICS, THERE ARE CONCERNS ABOUT POTENTIAL MANIPULATION AND LACK OF HUMAN OVERSIGHT. THE RESEARCH SUGGESTS THAT FULL ACCEPTANCE OF AI IN POLITICS REQUIRES A SET OF REGULATIONS THAT ENSURE TRANSPARENCY, DEMOCRATIC CONTROL, AND PROTECTION AGAINST BIAS, HIGHLIGHTING THE NEED FOR A CULTURAL AND NORMATIVE SHIFT TO ENABLE THE ETHICAL AND RESPONSIBLE USE OF THIS TECHNOLOGY.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>REGULAMENTAÇÕES AMBIENTAIS;MODELO DECISÓRIO;TRIBUTAÇÃO DE EMISSÕES;CLIVAGEM IDEOLÓGICA.</t>
+          <t>INTELIGÊNCIA ARTIFICIAL NA POLÍTICA;ACEITAÇÃO TECNOLÓGICA;COMPORTAMENTO POLÍTICO</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>ENVIRONMENTAL REGULATIONS;DECISION-MAKING MODEL;EMISSION TAXATION;IDEOLOGICAL CLEAVAGE.</t>
+          <t>ARTIFICIAL INTELLIGENCE IN POLITICS;TECHNOLOGICAL ACCEPTANCE;POLITICAL BEHAVIOR</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3449,70 +3449,70 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Aprendizado de máquina (ML)</t>
+          <t>IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="b">
         <v>1</v>
       </c>
-      <c r="O22" t="b">
-        <v>0</v>
-      </c>
-      <c r="P22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>0</v>
-      </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>RODRIGO BARROS DE ALBUQUERQUE</t>
+          <t>BERNARDO OLIVEIRA BUTA</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>CIÊNCIA POLÍTICA</t>
+          <t>POLÍTICAS PÚBLICAS E GOVERNO</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DE PERNAMBUCO</t>
+          <t>FUNDAÇÃO GETULIO VARGAS - BRASÍLIA</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>UFPE</t>
+          <t>FGV-BSB</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>NORDESTE</t>
+          <t>CENTRO-OESTE</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>PERNAMBUCO</t>
+          <t>DISTRITO FEDERAL</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>INGLES</t>
+          <t>PORTUGUES</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3522,16 +3522,16 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14475475</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15961875</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>14475475</t>
+          <t>15961875</t>
         </is>
       </c>
       <c r="AE22" t="n">
-        <v>4028790</v>
+        <v>4430849</v>
       </c>
     </row>
     <row r="23">
@@ -3550,37 +3550,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GUILHERME OTAVIANO SOARES</t>
+          <t>JOAO CARDOSO LARA CAMARGOS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ACEITAÇÃO DO USO DE INTELIGÊNCIA ARTIFICIAL NA POLÍTICA</t>
+          <t>O PODER DA CRENÇA: TREINAMENTO INDIRETO E OS EFEITOS DA CRENÇA QUE BOLSONARO FOI ENVIADO POR DEUS (2018-2022)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>O TRABALHO EXAMINA A ACEITAÇÃO DO USO DE INTELIGÊNCIA ARTIFICIAL (IA) NA POLÍTICA, FOCANDO ESPECIALMENTE NOS IMPACTOS DESSA TECNOLOGIA EM PROCESSOS LEGISLATIVOS E NA FORMULAÇÃO DE POLÍTICAS PÚBLICAS. O USO DA IA NA POLÍTICA PROMETE UMA REVOLUÇÃO EM TERMOS DE EFICIÊNCIA ADMINISTRATIVA, COM APLICAÇÕES QUE VARIAM DESDE A AUTOMAÇÃO DE PROCESSOS ATÉ A ANÁLISE DE GRANDES VOLUMES DE DADOS, OFERECENDO POTENCIAL PARA DECISÕES MAIS EMBASADAS E RESPOSTAS RÁPIDAS A DEMANDAS SOCIAIS. CONTUDO, ESSA ADOÇÃO APRESENTA DESAFIOS ÉTICOS E PRÁTICOS, LEVANTANDO QUESTIONAMENTOS SOBRE A PRESERVAÇÃO DOS PRINCÍPIOS DEMOCRÁTICOS. O PRINCIPAL OBJETIVO DA PESQUISA É INVESTIGAR A ACEITAÇÃO DA IA NO CAMPO POLÍTICO, EXPLORANDO A FAMILIARIDADE E AS PERCEPÇÕES DE PARLAMENTARES BRASILEIROS SOBRE O USO DESSA TECNOLOGIA EM SUAS ATIVIDADES LEGISLATIVAS. A PESQUISA BUSCA ENTENDER COMO ESSES AGENTES ASSIMILAM E AVALIAM A ADOÇÃO DA IA INVESTIGANDO SE A CONSIDERAM UM RECURSO VÁLIDO PARA AMPLIAR A REPRESENTATIVIDADE E A EFICIÊNCIA DA GOVERNANÇA, OU SE EXISTEM PREOCUPAÇÕES QUE RESTRINGEM SEU USO. A JUSTIFICATIVA PARA A PESQUISA RESIDE NA CRESCENTE IMPORTÂNCIA DA IA NA SOCIEDADE E NOS IMPACTOS POTENCIAIS DE SEU USO POLÍTICO, ESPECIALMENTE EM UM CONTEXTO DE POLARIZAÇÃO E DESINFORMAÇÃO, PODENDO CAUSAR IMPACTOS À DEMOCRACIA. ALÉM DE UMA PESQUISA BIBLIOGRÁFICA ACERCA DO TEMA, FOI REALIZADA UMA PESQUISA QUALITATIVA, CENTRADA EM ENTREVISTAS SEMIESTRUTURADAS REALIZADAS COM LEGISLADORES EM NÍVEIS MUNICIPAL, ESTADUAL E FEDERAL. AS ENTREVISTAS FORAM GRAVADAS, TRANSCRITAS, CODIFICADAS E SUBMETIDAS A ANÁLISE TEMÁTICA PARA IDENTIFICAR PADRÕES DE RESPOSTA. AS ENTREVISTAS FORAM CONDUZIDAS ATÉ O PONTO DE SATURAÇÃO TEÓRICA, PERMITINDO UM ENTENDIMENTO ROBUSTO SOBRE AS PERCEPÇÕES E RESISTÊNCIAS DOS PARLAMENTARES EM RELAÇÃO AO USO DA IA. OS RESULTADOS INDICAM UMA ACEITAÇÃO MODERADA DA IA, COM OS LEGISLADORES RECONHECENDO O POTENCIAL DA TECNOLOGIA PARA MELHORAR PROCESSOS LEGISLATIVOS, MAS EXPRESSANDO PREOCUPAÇÕES QUANTO AO IMPACTO SOBRE SUA AUTONOMIA E SOBRE OS VALORES DEMOCRÁTICOS. EMBORA ALGUNS VEJAM A IA COMO UM RECURSO PROMISSOR PARA UMA POLÍTICA MAIS EFICIENTE, EXISTE UM RECEIO QUANTO À POSSIBILIDADE DE MANIPULAÇÃO E FALTA DE SUPERVISÃO HUMANA. A PESQUISA SUGERE QUE A PLENA ACEITAÇÃO DA IA NA POLÍTICA EXIGE UM CONJUNTO DE REGULAMENTAÇÕES QUE GARANTAM A TRANSPARÊNCIA, O CONTROLE DEMOCRÁTICO E A PROTEÇÃO CONTRA VIESES, APONTANDO PARA A NECESSIDADE DE UMA MUDANÇA CULTURAL E NORMATIVA QUE POSSIBILITE O USO ÉTICO E RESPONSÁVEL DESSA TECNOLOGIA.</t>
+          <t>ESTE TRABALHO EXAMINA A INFLUÊNCIA DA CRENÇA DE QUE JAIR BOLSONARO FOI DIVINAMENTE ESCOLHIDO NO COMPORTAMENTO POLÍTICO DE SEUS APOIADORES, PARTICULARMENTE ENTRE OS EVANGÉLICOS, DE 2018 A 2022. A PESQUISA ABORDA DUAS QUESTÕES PRINCIPAIS: POR QUE ALGUNS INDIVÍDUOS PASSARAM A ACREDITAR QUE DEUS ENVIOU BOLSONARO, E COMO ESSA CRENÇA AFETOU A AVALIAÇÃO QUE ESSES INDIVÍDUOS FAZEM DE SEU GOVERNO? PARA RESPONDER A ESSAS PERGUNTAS, FORAM TESTADAS TRÊS HIPÓTESES, FOCANDO NA DISSEMINAÇÃO DESSA CRENÇA POR MEIO DAS REDES SOCIAIS, ESPECIALMENTE O WHATSAPP, E SEU IMPACTO NO COMPORTAMENTO POLÍTICO E NA AVALIAÇÃO DO GOVERNO ENTRE OS EVANGÉLICOS. PARA TANTO, O ESTUDO UTILIZA UMA ABORDAGEM QUANTITATIVA, ANALISANDO MAIS DE MEIO MILHÃO DE MENSAGENS DE 310 GRUPOS PÚBLICOS DE WHATSAPP QUE APOIAM BOLSONARO. FOI DESENVOLVIDA UMA METODOLOGIA INOVADORA QUE COMBINA MODELOS DE REDES NEURAIS PROFUNDAS PARA CLASSIFICAÇÃO DE TEXTO E ANÁLISE DE SENTIMENTOS. ALÉM DISSO, FORAM UTILIZADOS MODELOS DE REGRESSÃO PARA EXPLORAR A RELAÇÃO ENTRE A CRENÇA E A AVALIAÇÃO DO GOVERNO, COM BASE EM UMA AMOSTRA REPRESENTATIVA DE MINAS GERAIS. OS RESULTADOS INDICAM QUE A CRENÇA EM BOLSONARO COMO UM ENVIADO DIVINO DESEMPENHOU UM PAPEL SIGNIFICATIVO NA MANUTENÇÃO DO APOIO ENTRE SEUS SEGUIDORES, MESMO EM MEIO A CRÍTICAS DURANTE A PANDEMIA. ESSA CRENÇA ATUOU COMO UM MEDIADOR, LEVANDO A AVALIAÇÕES MAIS FAVORÁVEIS DO GOVERNO ENTRE OS EVANGÉLICOS.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>THIS STUDY EXAMINES THE ACCEPTANCE OF ARTIFICIAL INTELLIGENCE (AI) USE IN POLITICS, FOCUSING PARTICULARLY ON THE IMPACT OF THIS TECHNOLOGY ON LEGISLATIVE PROCESSES AND PUBLIC POLICY FORMULATION. THE USE OF AI IN POLITICS PROMISES A REVOLUTION IN ADMINISTRATIVE EFFICIENCY, WITH APPLICATIONS RANGING FROM PROCESS AUTOMATION TO THE ANALYSIS OF LARGE DATASETS, OFFERING THE POTENTIAL FOR MORE INFORMED DECISIONS AND RAPID RESPONSES TO SOCIAL DEMANDS. HOWEVER, THIS ADOPTION PRESENTS ETHICAL AND PRACTICAL CHALLENGES, RAISING QUESTIONS ABOUT PRESERVING DEMOCRATIC PRINCIPLES. THE MAIN OBJECTIVE OF THIS RESEARCH IS TO INVESTIGATE THE ACCEPTANCE OF AI IN THE POLITICAL FIELD, EXPLORING BRAZILIAN LEGISLATORS' FAMILIARITY WITH AND PERCEPTIONS OF THIS TECHNOLOGY IN THEIR LEGISLATIVE ACTIVITIES. THE RESEARCH AIMS TO UNDERSTAND HOW THESE AGENTS ASSIMILATE AND EVALUATE AI ADOPTION, INVESTIGATING WHETHER THEY CONSIDER IT A VALID RESOURCE TO ENHANCE REPRESENTATIVENESS AND GOVERNANCE EFFICIENCY OR IF CONCERNS EXIST THAT LIMIT ITS USE. THE RESEARCH JUSTIFICATION LIES IN THE GROWING IMPORTANCE OF AI IN SOCIETY AND ITS POTENTIAL POLITICAL IMPACTS, ESPECIALLY IN THE CONTEXT OF POLARIZATION AND MISINFORMATION, WHICH MAY AFFECT DEMOCRACY. IN ADDITION TO A BIBLIOGRAPHIC REVIEW ON THE SUBJECT, THE STUDY UTILIZED A QUALITATIVE METHODOLOGY CENTERED ON SEMI-STRUCTURED INTERVIEWS WITH LEGISLATORS AT MUNICIPAL, STATE, AND FEDERAL LEVELS. THE INTERVIEWS WERE RECORDED, TRANSCRIBED, CODED, AND SUBJECTED TO THEMATIC ANALYSIS TO IDENTIFY RESPONSE PATTERNS. INTERVIEWS WERE CONDUCTED UNTIL REACHING THEORETICAL SATURATION, ENABLING A ROBUST UNDERSTANDING OF THE PERCEPTIONS AND RESISTANCE OF LEGISLATORS REGARDING AI USE. THE RESULTS INDICATE A MODERATE ACCEPTANCE OF AI, WITH LEGISLATORS RECOGNIZING THE TECHNOLOGY'S POTENTIAL TO IMPROVE LEGISLATIVE PROCESSES WHILE EXPRESSING CONCERNS ABOUT ITS IMPACT ON THEIR AUTONOMY AND DEMOCRATIC VALUES. ALTHOUGH SOME SEE AI AS A PROMISING RESOURCE FOR MORE EFFICIENT POLITICS, THERE ARE CONCERNS ABOUT POTENTIAL MANIPULATION AND LACK OF HUMAN OVERSIGHT. THE RESEARCH SUGGESTS THAT FULL ACCEPTANCE OF AI IN POLITICS REQUIRES A SET OF REGULATIONS THAT ENSURE TRANSPARENCY, DEMOCRATIC CONTROL, AND PROTECTION AGAINST BIAS, HIGHLIGHTING THE NEED FOR A CULTURAL AND NORMATIVE SHIFT TO ENABLE THE ETHICAL AND RESPONSIBLE USE OF THIS TECHNOLOGY.</t>
+          <t>THIS WORK EXAMINES THE INFLUENCE OF THE BELIEF THAT JAIR BOLSONARO WAS DIVINELY APPOINTED ON THE POLITICAL BEHAVIOR OF HIS SUPPORTERS, PARTICULARLY AMONG EVANGELICALS, FROM 2018 TO 2022. THE RESEARCH ADDRESSES TWO KEY QUESTIONS: WHY DID SOME INDIVIDUALS COME TO BELIEVE THAT GOD SENT BOLSONARO, AND HOW DID THIS BELIEF AFFECT THEIR EVALUATION OF HIS GOVERNMENT? TO ANSWER THESE QUESTIONS, THREE HYPOTHESES WERE TESTED, FOCUSING ON THE DISSEMINATION OF THIS BELIEF THROUGH SOCIAL MEDIA, PARTICULARLY WHATSAPP, AND ITS IMPACT ON POLITICAL BEHAVIOR AND GOVERNMENT EVALUATION AMONG EVANGELICALS. TO DO SO THE STUDY EMPLOYS A QUANTITATIVE APPROACH, ANALYZING OVER HALF A MILLION MESSAGES FROM 310 PUBLIC WHATSAPP GROUPS SUPPORTING BOLSONARO. A NOVEL METHODOLOGY WAS DEVELOPED COMBINING DEEP NEURAL NETWORK MODELS FOR TEXT CLASSIFICATION AND SENTIMENT ANALYSIS. ADDITIONALLY, REGRESSION MODELS WERE USED TO EXPLORE THE RELATIONSHIP BETWEEN BELIEF AND GOVERNMENT EVALUATION, BASED ON A REPRESENTATIVE SAMPLE FROM MINAS GERAIS. THE FINDINGS INDICATE THAT THE BELIEF IN BOLSONARO AS A DIVINE ENVOY PLAYED A SIGNIFICANT ROLE IN MAINTAINING SUPPORT AMONG HIS FOLLOWERS, EVEN AMID CRITICISM DURING THE PANDEMIC. THIS BELIEF WAS A MEDIATOR, LEADING TO MORE FAVORABLE GOVERNMENT EVALUATIONS AMONG EVANGELICALS.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>INTELIGÊNCIA ARTIFICIAL NA POLÍTICA;ACEITAÇÃO TECNOLÓGICA;COMPORTAMENTO POLÍTICO</t>
+          <t>PSICOLOGIA POLÍTICA;EVANGÉLICOS;APRENDIZADO DE MÁQUINA;JAIR BOLSONARO;CRENÇAS</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>ARTIFICIAL INTELLIGENCE IN POLITICS;TECHNOLOGICAL ACCEPTANCE;POLITICAL BEHAVIOR</t>
+          <t>POLITICAL PSYCHOLOGY;EVANGELICALS;MACHINE LEARNING;JAIR BOLSONARO;BELIEFS</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3590,61 +3590,61 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>Aprendizado de máquina (ML); Aprendizado profundo &amp; redes neurais</t>
         </is>
       </c>
       <c r="M23" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" t="b">
         <v>1</v>
       </c>
-      <c r="N23" t="b">
-        <v>0</v>
-      </c>
       <c r="O23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="b">
         <v>0</v>
       </c>
       <c r="Q23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>BERNARDO OLIVEIRA BUTA</t>
+          <t>HELCIMARA DE SOUZA TELLES</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>POLÍTICAS PÚBLICAS E GOVERNO</t>
+          <t>CIÊNCIA POLÍTICA</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO GETULIO VARGAS - BRASÍLIA</t>
+          <t>UNIVERSIDADE FEDERAL DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>FGV-BSB</t>
+          <t>UFMG</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>CENTRO-OESTE</t>
+          <t>SUDESTE</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>DISTRITO FEDERAL</t>
+          <t>MINAS GERAIS</t>
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>POLÍTICAS PÚBLICAS</t>
+          <t>NÃO SE APLICA</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3663,16 +3663,16 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15961875</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15204334</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>15961875</t>
+          <t>15204334</t>
         </is>
       </c>
       <c r="AE23" t="n">
-        <v>4430849</v>
+        <v>3664850</v>
       </c>
     </row>
     <row r="24">
@@ -3691,37 +3691,37 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>JOAO CARDOSO LARA CAMARGOS</t>
+          <t>LAURA BEATRIZ DE ALMEIDA CEZAR ORTELLADO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>O PODER DA CRENÇA: TREINAMENTO INDIRETO E OS EFEITOS DA CRENÇA QUE BOLSONARO FOI ENVIADO POR DEUS (2018-2022)</t>
+          <t>A CRISE DA DEMOCRACIA NO REGIME DA INFORMAÇÃO: A RACIONALIDADE NEOLIBERAL OBSERVADA A PARTIR DOS CASOS BREXIT E BOLSONARO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ESTE TRABALHO EXAMINA A INFLUÊNCIA DA CRENÇA DE QUE JAIR BOLSONARO FOI DIVINAMENTE ESCOLHIDO NO COMPORTAMENTO POLÍTICO DE SEUS APOIADORES, PARTICULARMENTE ENTRE OS EVANGÉLICOS, DE 2018 A 2022. A PESQUISA ABORDA DUAS QUESTÕES PRINCIPAIS: POR QUE ALGUNS INDIVÍDUOS PASSARAM A ACREDITAR QUE DEUS ENVIOU BOLSONARO, E COMO ESSA CRENÇA AFETOU A AVALIAÇÃO QUE ESSES INDIVÍDUOS FAZEM DE SEU GOVERNO? PARA RESPONDER A ESSAS PERGUNTAS, FORAM TESTADAS TRÊS HIPÓTESES, FOCANDO NA DISSEMINAÇÃO DESSA CRENÇA POR MEIO DAS REDES SOCIAIS, ESPECIALMENTE O WHATSAPP, E SEU IMPACTO NO COMPORTAMENTO POLÍTICO E NA AVALIAÇÃO DO GOVERNO ENTRE OS EVANGÉLICOS. PARA TANTO, O ESTUDO UTILIZA UMA ABORDAGEM QUANTITATIVA, ANALISANDO MAIS DE MEIO MILHÃO DE MENSAGENS DE 310 GRUPOS PÚBLICOS DE WHATSAPP QUE APOIAM BOLSONARO. FOI DESENVOLVIDA UMA METODOLOGIA INOVADORA QUE COMBINA MODELOS DE REDES NEURAIS PROFUNDAS PARA CLASSIFICAÇÃO DE TEXTO E ANÁLISE DE SENTIMENTOS. ALÉM DISSO, FORAM UTILIZADOS MODELOS DE REGRESSÃO PARA EXPLORAR A RELAÇÃO ENTRE A CRENÇA E A AVALIAÇÃO DO GOVERNO, COM BASE EM UMA AMOSTRA REPRESENTATIVA DE MINAS GERAIS. OS RESULTADOS INDICAM QUE A CRENÇA EM BOLSONARO COMO UM ENVIADO DIVINO DESEMPENHOU UM PAPEL SIGNIFICATIVO NA MANUTENÇÃO DO APOIO ENTRE SEUS SEGUIDORES, MESMO EM MEIO A CRÍTICAS DURANTE A PANDEMIA. ESSA CRENÇA ATUOU COMO UM MEDIADOR, LEVANDO A AVALIAÇÕES MAIS FAVORÁVEIS DO GOVERNO ENTRE OS EVANGÉLICOS.</t>
+          <t>A DEPENDÊNCIA CRIADA PELO AVANÇO NAS TECNOLOGIAS DE INFORMAÇÃO E COMUNICAÇÃO RESULTOU NA NECESSIDADE DE UTILIZAÇÃO DE APLICATIVOS E REDES SOCIAIS PARA AS MAIS SIMPLES TAREFAS DIÁRIAS, E, EM CONTRAPARTIDA, PASSOU A DEFINIR AS RELAÇÕES SOCIAIS POR MEIO DA INTERAÇÃO ONLINE, E MAIS EMINENTEMENTE, DITAR AS FORMAS DE COMPREENSÃO E DISCERNIMENTO DO INDIVÍDUO ATRAVÉS DA DISSEMINAÇÃO DE NARRATIVAS E DA DETERMINAÇÃO DE TÓPICOS DE DISCUSSÃO POLÍTICO-SOCIAIS. DESSA FORMA, PROPÕE-SE COMPREENDER COMO PROCESSOS DEMOCRÁTICOS, COM FOCO NAS ELEIÇÕES, ESTÃO SENDO AFETADOS PELA MANIPULAÇÃO DE INFORMAÇÕES ATRAVÉS DO MEIO DIGITAL. ATRAVÉS DE UMA REVISÃO BIBLIOGRÁFICA NARRATIVA, CONSTATOU-SE A EXISTÊNCIA DE UMA RACIONALIDADE: A RACIONALIDADE NEOLIBERAL. ESSA RACIONALIDADE TEM REESTRUTURADO A(S) SOCIEDADE(S) E, A PARTIR DISSO, CONSTRUÍDO UM NOVO TIPO DE INDIVÍDUO. ESSE NOVO INDIVÍDUO TEM SUAS EXPERIÊNCIAS CAPTURADAS POR MEIO DE INFRAESTRUTURAS DE COLETA E PROCESSAMENTO, E, OS DADOS GERADOS POR ESSE PROCESSO SÃO APROPRIADOS A FIM DE GERAR PERFIS PSICOMÉTRICOS. ESSES PERFIS PERMITEM A PREDIÇÃO PRECISA DO COMPORTAMENTO DO INDIVÍDUO. A PARTIR DESSA PREDIÇÃO, QUALQUER CONTEÚDO PODE SER MICRO-DIRECIONADO DE FORMA A SER O MAIS PERSUASIVO POSSÍVEL. SURGE DAÍ UMA NOVA FORMA DE DOMINAÇÃO NA QUAL INFORMAÇÕES E SEU PROCESSAMENTO POR ALGORITMOS E INTELIGÊNCIA ARTIFICIAL PODEM DETERMINAR DECISIVAMENTE PROCESSOS SOCIAIS, ECONÔMICOS E POLÍTICOS, O QUE DIRETAMENTE AFETA O SISTEMA DEMOCRÁTICO. A FIM DE MELHOR CARACTERIZAR ESSE FENÔMENO SÃO ANALISADOS DOIS CASOS: AS ELEIÇÕES QUE NOMEARAM JAIR BOLSONARO PRESIDENTE DA REPÚBLICA NO BRASIL EM 2018, E O PLEBISCITO QUE DETERMINOU A SAÍDA DO REINO UNIDO DA UNIÃO EUROPEIA (BREXIT) EM 2016. APESAR DE SUAS DIFERENÇAS, É POSSÍVEL PERCEBER QUE EXISTE UM ORDENAMENTO, PROCEDIMENTOS E NARRATIVAS ANÁLOGAS.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>THIS WORK EXAMINES THE INFLUENCE OF THE BELIEF THAT JAIR BOLSONARO WAS DIVINELY APPOINTED ON THE POLITICAL BEHAVIOR OF HIS SUPPORTERS, PARTICULARLY AMONG EVANGELICALS, FROM 2018 TO 2022. THE RESEARCH ADDRESSES TWO KEY QUESTIONS: WHY DID SOME INDIVIDUALS COME TO BELIEVE THAT GOD SENT BOLSONARO, AND HOW DID THIS BELIEF AFFECT THEIR EVALUATION OF HIS GOVERNMENT? TO ANSWER THESE QUESTIONS, THREE HYPOTHESES WERE TESTED, FOCUSING ON THE DISSEMINATION OF THIS BELIEF THROUGH SOCIAL MEDIA, PARTICULARLY WHATSAPP, AND ITS IMPACT ON POLITICAL BEHAVIOR AND GOVERNMENT EVALUATION AMONG EVANGELICALS. TO DO SO THE STUDY EMPLOYS A QUANTITATIVE APPROACH, ANALYZING OVER HALF A MILLION MESSAGES FROM 310 PUBLIC WHATSAPP GROUPS SUPPORTING BOLSONARO. A NOVEL METHODOLOGY WAS DEVELOPED COMBINING DEEP NEURAL NETWORK MODELS FOR TEXT CLASSIFICATION AND SENTIMENT ANALYSIS. ADDITIONALLY, REGRESSION MODELS WERE USED TO EXPLORE THE RELATIONSHIP BETWEEN BELIEF AND GOVERNMENT EVALUATION, BASED ON A REPRESENTATIVE SAMPLE FROM MINAS GERAIS. THE FINDINGS INDICATE THAT THE BELIEF IN BOLSONARO AS A DIVINE ENVOY PLAYED A SIGNIFICANT ROLE IN MAINTAINING SUPPORT AMONG HIS FOLLOWERS, EVEN AMID CRITICISM DURING THE PANDEMIC. THIS BELIEF WAS A MEDIATOR, LEADING TO MORE FAVORABLE GOVERNMENT EVALUATIONS AMONG EVANGELICALS.</t>
+          <t>THE DEPENDENCE CREATED BY ADVANCES IN INFORMATION AND COMMUNICATION TECHNOLOGIES RESULTED IN THE NEED TO USE APPS AND SOCIAL MEDIA FOR THE SIMPLEST DAILY TASKS, AND, IN RETURN, DEFINED SOCIAL RELATIONSHIPS THROUGH ONLINE INTERACTION, AND MORE EMINENTLY, DICTATED THE INDIVIDUAL'S WAYS OF UNDERSTANDING THROUGH THE DISSEMINATION OF NARRATIVES, AS WELL AS THE DEFINING OF POLITICAL-SOCIAL DISCUSSION TOPICS. THUS, THE AIM OF THIS RESEARCH IS TO UNDERSTAND HOW DEMOCRATIC PROCESSES, FOCUSING ON ELECTIONS, ARE BEING AFFECTED BY THE MANIPULATION OF INFORMATION THROUGH DIGITAL MEDIA. THROUGH A NARRATIVE BIBLIOGRAPHICAL REVIEW, THE EXISTENCE OF A RATIONALITY WAS VERIFIED: THE NEOLIBERAL RATIONALITY. THIS RATIONALITY HAS RESTRUCTURED SOCIETY(IES) AND BUILT A NEW TYPE OF INDIVIDUAL. THIS NEW INDIVIDUAL HAS THEIR EXPERIENCES CAPTURED THROUGH COLLECTION AND PROCESSING INFRASTRUCTURES, AND THE DATA GENERATED BY THIS PROCESS IS APPROPRIATED TO GENERATE PSYCHOMETRIC PROFILES. THESE PROFILES ALLOW ACCURATE PREDICTION OF AN INDIVIDUAL'S BEHAVIOR. BASED ON THIS PREDICTION, ANY CONTENT CAN BE MICRO-TARGETED TO BE AS PERSUASIVE AS POSSIBLE. THIS ESTABLISHES A NEW FORM OF DOMINATION IN WHICH INFORMATION AND ITS PROCESSING BY ALGORITHMS AND ARTIFICIAL INTELLIGENCE CAN DECISIVELY DETERMINE SOCIAL, ECONOMIC AND POLITICAL PROCESSES, WHICH DIRECTLY AFFECTS THE DEMOCRATIC SYSTEM. IN ORDER TO BETTER CHARACTERIZE THIS PHENOMENON, TWO CASES ARE ANALYZED: THE ELECTIONS THAT MADE JAIR BOLSONARO PRESIDENT OF THE REPUBLIC IN BRAZIL IN 2018, AND THE PLEBISCITE THAT DETERMINED THE UNITED KINGDOM'S EXIT FROM THE EUROPEAN UNION (BREXIT) IN 2016. DESPITE THEIR DIFFERENCES, IT?S POSSIBLE TO NOTICE SIMILARITIES IN ORDER, PROCEDURES AND NARRATIVES</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PSICOLOGIA POLÍTICA;EVANGÉLICOS;APRENDIZADO DE MÁQUINA;JAIR BOLSONARO;CRENÇAS</t>
+          <t>DEMOCRACIA;NEOLIBERALISMO;MODULAÇÃO DIGITAL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>POLITICAL PSYCHOLOGY;EVANGELICALS;MACHINE LEARNING;JAIR BOLSONARO;BELIEFS</t>
+          <t>DEMOCRACY;NEOLIBERALISM;DIGITAL MODULATION</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3731,17 +3731,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Aprendizado de máquina (ML); Aprendizado profundo &amp; redes neurais</t>
+          <t>IA em sentido estrito</t>
         </is>
       </c>
       <c r="M24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="b">
         <v>0</v>
@@ -3751,41 +3751,41 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>HELCIMARA DE SOUZA TELLES</t>
+          <t>DANIELLE JACON AYRES PINTO</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>CIÊNCIA POLÍTICA</t>
+          <t>RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DE MINAS GERAIS</t>
+          <t>UNIVERSIDADE FEDERAL DE SANTA CATARINA</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>UFMG</t>
+          <t>UFSC</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>SUDESTE</t>
+          <t>SUL</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>MINAS GERAIS</t>
+          <t>SANTA CATARINA</t>
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>POLÍTICA INTERNACIONAL</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3804,16 +3804,16 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15204334</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16197565</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>15204334</t>
+          <t>16197565</t>
         </is>
       </c>
       <c r="AE24" t="n">
-        <v>3664850</v>
+        <v>4082614</v>
       </c>
     </row>
     <row r="25">
@@ -3832,37 +3832,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LAURA BEATRIZ DE ALMEIDA CEZAR ORTELLADO</t>
+          <t>LUCAS CHRYSTELLO PEDERNEIRAS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>A CRISE DA DEMOCRACIA NO REGIME DA INFORMAÇÃO: A RACIONALIDADE NEOLIBERAL OBSERVADA A PARTIR DOS CASOS BREXIT E BOLSONARO</t>
+          <t>A GUERRA EM TRANSFORMAÇÃO: INTELIGÊNCIA ARTIFICIAL SOB A TEORIA DE CLAUSEWITZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>A DEPENDÊNCIA CRIADA PELO AVANÇO NAS TECNOLOGIAS DE INFORMAÇÃO E COMUNICAÇÃO RESULTOU NA NECESSIDADE DE UTILIZAÇÃO DE APLICATIVOS E REDES SOCIAIS PARA AS MAIS SIMPLES TAREFAS DIÁRIAS, E, EM CONTRAPARTIDA, PASSOU A DEFINIR AS RELAÇÕES SOCIAIS POR MEIO DA INTERAÇÃO ONLINE, E MAIS EMINENTEMENTE, DITAR AS FORMAS DE COMPREENSÃO E DISCERNIMENTO DO INDIVÍDUO ATRAVÉS DA DISSEMINAÇÃO DE NARRATIVAS E DA DETERMINAÇÃO DE TÓPICOS DE DISCUSSÃO POLÍTICO-SOCIAIS. DESSA FORMA, PROPÕE-SE COMPREENDER COMO PROCESSOS DEMOCRÁTICOS, COM FOCO NAS ELEIÇÕES, ESTÃO SENDO AFETADOS PELA MANIPULAÇÃO DE INFORMAÇÕES ATRAVÉS DO MEIO DIGITAL. ATRAVÉS DE UMA REVISÃO BIBLIOGRÁFICA NARRATIVA, CONSTATOU-SE A EXISTÊNCIA DE UMA RACIONALIDADE: A RACIONALIDADE NEOLIBERAL. ESSA RACIONALIDADE TEM REESTRUTURADO A(S) SOCIEDADE(S) E, A PARTIR DISSO, CONSTRUÍDO UM NOVO TIPO DE INDIVÍDUO. ESSE NOVO INDIVÍDUO TEM SUAS EXPERIÊNCIAS CAPTURADAS POR MEIO DE INFRAESTRUTURAS DE COLETA E PROCESSAMENTO, E, OS DADOS GERADOS POR ESSE PROCESSO SÃO APROPRIADOS A FIM DE GERAR PERFIS PSICOMÉTRICOS. ESSES PERFIS PERMITEM A PREDIÇÃO PRECISA DO COMPORTAMENTO DO INDIVÍDUO. A PARTIR DESSA PREDIÇÃO, QUALQUER CONTEÚDO PODE SER MICRO-DIRECIONADO DE FORMA A SER O MAIS PERSUASIVO POSSÍVEL. SURGE DAÍ UMA NOVA FORMA DE DOMINAÇÃO NA QUAL INFORMAÇÕES E SEU PROCESSAMENTO POR ALGORITMOS E INTELIGÊNCIA ARTIFICIAL PODEM DETERMINAR DECISIVAMENTE PROCESSOS SOCIAIS, ECONÔMICOS E POLÍTICOS, O QUE DIRETAMENTE AFETA O SISTEMA DEMOCRÁTICO. A FIM DE MELHOR CARACTERIZAR ESSE FENÔMENO SÃO ANALISADOS DOIS CASOS: AS ELEIÇÕES QUE NOMEARAM JAIR BOLSONARO PRESIDENTE DA REPÚBLICA NO BRASIL EM 2018, E O PLEBISCITO QUE DETERMINOU A SAÍDA DO REINO UNIDO DA UNIÃO EUROPEIA (BREXIT) EM 2016. APESAR DE SUAS DIFERENÇAS, É POSSÍVEL PERCEBER QUE EXISTE UM ORDENAMENTO, PROCEDIMENTOS E NARRATIVAS ANÁLOGAS.</t>
+          <t>INÚMERAS TECNOLOGIAS DE GRANDE COMPLEXIDADE TÊM SURGIDO NO CAMPO DA DEFESA. DE ACORDO COM A ORGANIZAÇÃO DO TRATADO DO ATLÂNTICO NORTE (OTAN) POR EXEMPLO, A INTELIGÊNCIA ARTIFICIAL (IA) É UMA DAS TECNOLOGIAS EMERGENTES E DISRUPTIVAS QUE TEM GANHADO DESTAQUE NOS DEBATES NAS CIÊNCIAS MILITARES. NESTE SENTIDO, A IA, NAS CIÊNCIAS MILITARES, É TRATADA COMO UMA FERRAMENTA TECNOLÓGICA DE APLICAÇÕES MULTIFACETADAS DE GRANDE IMPORTÂNCIA ESTRATÉGICA, DEVIDO À SUA CAPACIDADE DE ALTERAR E INFLUENCIAR AS DINÂMICAS DE UM CONFLITO ENTRE ATORES ESTATAIS OU NÃO-ESTATAIS, TORNANDO-SE UMA DAS FERRAMENTAS MAIS COMPETITIVAS NO ATUAL CENÁRIO GLOBAL. COM BASE NISTO, A PERGUNTA QUE GUIA ESTA DISSERTAÇÃO É: "A INTELIGÊNCIA ARTIFICIAL MILITAR É CAPAZ DE MUDAR A NATUREZA DA GUERRA, SEGUNDO OS PRINCÍPIOS DA TEORIA DE GUERRA DE CLAUSEWITZ?". A HIPÓTESE EMPREGADA É QUE A TEORIA DE CLAUSEWITZ MANTÉM SUA RELEVÂNCIA NOS ESTUDOS DAS CIÊNCIAS MILITARES, MESMO DIANTE DO SURGIMENTO DE TECNOLOGIAS EMERGENTES COMO A INTELIGÊNCIA ARTIFICIAL APLICADA AO MEIO MILITAR, AS QUAIS BUSCAM SUPERAR, ALTERAR E MINIMIZAR ELEMENTOS DA NATUREZA INTRÍNSECOS À GUERRA. O OBJETIVO GERAL DESTA PESQUISA, SE PROPÕE A INVESTIGAR SE IA MILITAR PODE TRANSFORMAR AS DINÂMICAS E CONCEITOS ESSENCIAIS DA GUERRA QUE FORAM ESTABELECIDOS POR CLAUSEWITZ. PORTANTO, OS OBJETIVOS ESPECÍFICOS QUE ORIENTAM ESTA DISSERTAÇÃO SÃO: (I) OS CONCEITOS DE FRICÇÃO, NÉVOA DA GUERRA, CENTRO DE GRAVIDADE E DA TRINDADE DE CLAUSEWITZ; (II) A COMPREENSÃO DA IA, DESDE SUA HISTÓRIA, CONCEITO E DESENVOLVIMENTO À SUA CONCENTRAÇÃO; (III) CONTEXTUALIZAR TANTO A IA, QUANTO CATEGORIZAR AS SUAS APLICAÇÕES NO CONTEXTO MILITAR; E POR FIM (IV) REALIZAR UMA ANÁLISE CRÍTICA DAS APLICAÇÕES DA IA MILITAR À LUZ DOS PRINCÍPIOS DA TEORIA DE GUERRA DE CLAUSEWITZ. ESTE ESTUDO DE CARÁTER QUALITATIVO CONSISTE NA ANÁLISE DOCUMENTAL E DE CONTEÚDO DANDO PRIORIDADE ÀS FONTES RECENTES (2019-2024) E NA APLICAÇÃO DE UMA REVISÃO BIBLIOGRÁFICA PARA UMA ANÁLISE CRÍTICA PROPOSTA, PERMITINDO UM SÓLIDO DEBATE INTRODUTÓRIO SOBRE AS APLICAÇÕES DA IA NO MEIO MILITAR.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>THE DEPENDENCE CREATED BY ADVANCES IN INFORMATION AND COMMUNICATION TECHNOLOGIES RESULTED IN THE NEED TO USE APPS AND SOCIAL MEDIA FOR THE SIMPLEST DAILY TASKS, AND, IN RETURN, DEFINED SOCIAL RELATIONSHIPS THROUGH ONLINE INTERACTION, AND MORE EMINENTLY, DICTATED THE INDIVIDUAL'S WAYS OF UNDERSTANDING THROUGH THE DISSEMINATION OF NARRATIVES, AS WELL AS THE DEFINING OF POLITICAL-SOCIAL DISCUSSION TOPICS. THUS, THE AIM OF THIS RESEARCH IS TO UNDERSTAND HOW DEMOCRATIC PROCESSES, FOCUSING ON ELECTIONS, ARE BEING AFFECTED BY THE MANIPULATION OF INFORMATION THROUGH DIGITAL MEDIA. THROUGH A NARRATIVE BIBLIOGRAPHICAL REVIEW, THE EXISTENCE OF A RATIONALITY WAS VERIFIED: THE NEOLIBERAL RATIONALITY. THIS RATIONALITY HAS RESTRUCTURED SOCIETY(IES) AND BUILT A NEW TYPE OF INDIVIDUAL. THIS NEW INDIVIDUAL HAS THEIR EXPERIENCES CAPTURED THROUGH COLLECTION AND PROCESSING INFRASTRUCTURES, AND THE DATA GENERATED BY THIS PROCESS IS APPROPRIATED TO GENERATE PSYCHOMETRIC PROFILES. THESE PROFILES ALLOW ACCURATE PREDICTION OF AN INDIVIDUAL'S BEHAVIOR. BASED ON THIS PREDICTION, ANY CONTENT CAN BE MICRO-TARGETED TO BE AS PERSUASIVE AS POSSIBLE. THIS ESTABLISHES A NEW FORM OF DOMINATION IN WHICH INFORMATION AND ITS PROCESSING BY ALGORITHMS AND ARTIFICIAL INTELLIGENCE CAN DECISIVELY DETERMINE SOCIAL, ECONOMIC AND POLITICAL PROCESSES, WHICH DIRECTLY AFFECTS THE DEMOCRATIC SYSTEM. IN ORDER TO BETTER CHARACTERIZE THIS PHENOMENON, TWO CASES ARE ANALYZED: THE ELECTIONS THAT MADE JAIR BOLSONARO PRESIDENT OF THE REPUBLIC IN BRAZIL IN 2018, AND THE PLEBISCITE THAT DETERMINED THE UNITED KINGDOM'S EXIT FROM THE EUROPEAN UNION (BREXIT) IN 2016. DESPITE THEIR DIFFERENCES, IT?S POSSIBLE TO NOTICE SIMILARITIES IN ORDER, PROCEDURES AND NARRATIVES</t>
+          <t>NUMEROUS HIGHLY COMPLEX TECHNOLOGIES HAVE EMERGED IN THE FIELD OF DEFENSE. ACCORDING TO THE NORTH ATLANTIC TREATY ORGANIZATION (NATO), FOR EXAMPLE, ARTIFICIAL INTELLIGENCE (AI) IS ONE OF THE EMERGING AND DISRUPTIVE TECHNOLOGIES THAT HAS GAINED PROMINENCE IN MILITARY SCIENCES DEBATES. IN THIS CONTEXT, AI IN MILITARY SCIENCES IS TREATED AS A TECHNOLOGICAL TOOL WITH MULTIFACETED APPLICATIONS OF GREAT STRATEGIC IMPORTANCE DUE TO ITS ABILITY TO ALTER AND INFLUENCE THE DYNAMICS OF CONFLICT BETWEEN STATE AND NON-STATE ACTORS, MAKING IT ONE OF THE MOST COMPETITIVE TOOLS IN THE CURRENT GLOBAL SCENARIO. BASED ON THIS, THE GUIDING QUESTION OF THIS DISSERTATION IS: "IS MILITARY ARTIFICIAL INTELLIGENCE CAPABLE OF CHANGING THE NATURE OF WAR ACCORDING TO THE PRINCIPLES OF CLAUSEWITZ'S THEORY OF WAR?" THE HYPOTHESIS EMPLOYED IS THAT CLAUSEWITZ'S THEORY MAINTAINS ITS RELEVANCE IN MILITARY SCIENCES STUDIES, EVEN IN THE FACE OF EMERGING TECHNOLOGIES LIKE ARTIFICIAL INTELLIGENCE APPLIED TO THE MILITARY DOMAIN, WHICH SEEK TO SURPASS, ALTER, AND MINIMIZE INTRINSIC ELEMENTS OF THE NATURE OF WAR. THE OVERALL OBJECTIVE OF THIS RESEARCH PROPOSES TO INVESTIGATE WHETHER MILITARY AI CAN TRANSFORM THE DYNAMICS AND ESSENTIAL CONCEPTS OF WAR THAT WERE ESTABLISHED BY CLAUSEWITZ. THEREFORE, THE SPECIFIC OBJECTIVES GUIDING THIS DISSERTATION ARE: (I) THE CONCEPTS OF FRICTION, FOG OF WAR, CENTER OF GRAVITY, AND CLAUSEWITZ'S TRINITY; (II) UNDERSTANDING AI, FROM ITS HISTORY, CONCEPT, AND DEVELOPMENT TO ITS CONCENTRATION; (III) CONTEXTUALIZING AI AND CATEGORIZING ITS APPLICATIONS IN THE MILITARY CONTEXT; AND FINALLY (IV) CONDUCTING A CRITICAL ANALYSIS OF MILITARY AI APPLICATIONS IN LIGHT OF CLAUSEWITZ'S PRINCIPLES OF WAR THEORY. THIS QUALITATIVE STUDY CONSISTS OF DOCUMENT AND CONTENT ANALYSIS, PRIORITIZING RECENT SOURCES (2019-2024), AND APPLYING A BIBLIOGRAPHIC REVIEW FOR THE PROPOSED CRITICAL ANALYSIS, ENABLING A SOLID INTRODUCTORY DEBATE ON THE APPLICATIONS OF AI IN THE MILITARY FIELD.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>DEMOCRACIA;NEOLIBERALISMO;MODULAÇÃO DIGITAL</t>
+          <t>CIÊNCIAS MILITARES;INTELIGÊNCIA ARTIFICIAL;CLAUSEWITZ;TEORIA DA GUERRA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>DEMOCRACY;NEOLIBERALISM;DIGITAL MODULATION</t>
+          <t>MILITARY SCIENCES;ARTIFICIAL INTELLIGENCE;CLAUSEWITZ;WAR THEORY</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3892,41 +3892,41 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>DANIELLE JACON AYRES PINTO</t>
+          <t>MARCOS AURELIO GUEDES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>RELAÇÕES INTERNACIONAIS</t>
+          <t>CIÊNCIAS MILITARES</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DE SANTA CATARINA</t>
+          <t>ESCOLA DE COMANDO E ESTADO-MAIOR DO EXÉRCITO</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>UFSC</t>
+          <t>ECEME</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>SUL</t>
+          <t>SUDESTE</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>SANTA CATARINA</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>153</v>
+        <v>93</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>POLÍTICA INTERNACIONAL</t>
+          <t>NÃO SE APLICA</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3945,16 +3945,16 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16197565</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15391626</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>16197565</t>
+          <t>15391626</t>
         </is>
       </c>
       <c r="AE25" t="n">
-        <v>4082614</v>
+        <v>4003013</v>
       </c>
     </row>
     <row r="26">
@@ -3973,82 +3973,82 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LUCAS CHRYSTELLO PEDERNEIRAS</t>
+          <t>MATHEUS MOREIRA ALVES ALMEIDA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>A GUERRA EM TRANSFORMAÇÃO: INTELIGÊNCIA ARTIFICIAL SOB A TEORIA DE CLAUSEWITZ</t>
+          <t>THE ROLE OF PRIVATE AUTHORITY IN GLOBAL GOVERNANCE FRAMEWORKS: THE CASE OF THE CLIMATE KNOWLEDGE INFRASTRUCTURE IN THE ERA OF BIG DATA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>INÚMERAS TECNOLOGIAS DE GRANDE COMPLEXIDADE TÊM SURGIDO NO CAMPO DA DEFESA. DE ACORDO COM A ORGANIZAÇÃO DO TRATADO DO ATLÂNTICO NORTE (OTAN) POR EXEMPLO, A INTELIGÊNCIA ARTIFICIAL (IA) É UMA DAS TECNOLOGIAS EMERGENTES E DISRUPTIVAS QUE TEM GANHADO DESTAQUE NOS DEBATES NAS CIÊNCIAS MILITARES. NESTE SENTIDO, A IA, NAS CIÊNCIAS MILITARES, É TRATADA COMO UMA FERRAMENTA TECNOLÓGICA DE APLICAÇÕES MULTIFACETADAS DE GRANDE IMPORTÂNCIA ESTRATÉGICA, DEVIDO À SUA CAPACIDADE DE ALTERAR E INFLUENCIAR AS DINÂMICAS DE UM CONFLITO ENTRE ATORES ESTATAIS OU NÃO-ESTATAIS, TORNANDO-SE UMA DAS FERRAMENTAS MAIS COMPETITIVAS NO ATUAL CENÁRIO GLOBAL. COM BASE NISTO, A PERGUNTA QUE GUIA ESTA DISSERTAÇÃO É: "A INTELIGÊNCIA ARTIFICIAL MILITAR É CAPAZ DE MUDAR A NATUREZA DA GUERRA, SEGUNDO OS PRINCÍPIOS DA TEORIA DE GUERRA DE CLAUSEWITZ?". A HIPÓTESE EMPREGADA É QUE A TEORIA DE CLAUSEWITZ MANTÉM SUA RELEVÂNCIA NOS ESTUDOS DAS CIÊNCIAS MILITARES, MESMO DIANTE DO SURGIMENTO DE TECNOLOGIAS EMERGENTES COMO A INTELIGÊNCIA ARTIFICIAL APLICADA AO MEIO MILITAR, AS QUAIS BUSCAM SUPERAR, ALTERAR E MINIMIZAR ELEMENTOS DA NATUREZA INTRÍNSECOS À GUERRA. O OBJETIVO GERAL DESTA PESQUISA, SE PROPÕE A INVESTIGAR SE IA MILITAR PODE TRANSFORMAR AS DINÂMICAS E CONCEITOS ESSENCIAIS DA GUERRA QUE FORAM ESTABELECIDOS POR CLAUSEWITZ. PORTANTO, OS OBJETIVOS ESPECÍFICOS QUE ORIENTAM ESTA DISSERTAÇÃO SÃO: (I) OS CONCEITOS DE FRICÇÃO, NÉVOA DA GUERRA, CENTRO DE GRAVIDADE E DA TRINDADE DE CLAUSEWITZ; (II) A COMPREENSÃO DA IA, DESDE SUA HISTÓRIA, CONCEITO E DESENVOLVIMENTO À SUA CONCENTRAÇÃO; (III) CONTEXTUALIZAR TANTO A IA, QUANTO CATEGORIZAR AS SUAS APLICAÇÕES NO CONTEXTO MILITAR; E POR FIM (IV) REALIZAR UMA ANÁLISE CRÍTICA DAS APLICAÇÕES DA IA MILITAR À LUZ DOS PRINCÍPIOS DA TEORIA DE GUERRA DE CLAUSEWITZ. ESTE ESTUDO DE CARÁTER QUALITATIVO CONSISTE NA ANÁLISE DOCUMENTAL E DE CONTEÚDO DANDO PRIORIDADE ÀS FONTES RECENTES (2019-2024) E NA APLICAÇÃO DE UMA REVISÃO BIBLIOGRÁFICA PARA UMA ANÁLISE CRÍTICA PROPOSTA, PERMITINDO UM SÓLIDO DEBATE INTRODUTÓRIO SOBRE AS APLICAÇÕES DA IA NO MEIO MILITAR.</t>
+          <t>AS MUDANÇAS CLIMÁTICAS SÃO VISTAS POR MUITOS AUTORES E ATIVISTAS COMO O MAIOR DESAFIO DO SÉCULO 21. DADO ÀS CONSEQUÊNCIAS NEFASTAS DO ASSUNTO SOBRE DIVERSOS ASPECTOS DA VIDA POLÍTICA, ECONÔMICA E SOCIAL NA TERRA, ESSE TEMA REQUER UMA ABORDAGEM MULTIFACETADA E INTERDISCIPLINAR PARA FAZER FRENTE TANTO ÀS SUAS CAUSAS QUANTO AOS SEUS EFEITOS. NESSE ESFORÇO, ESTE TRABALHO RECORRE AO DEBATE EM TORNO DA GOVERNANÇA GLOBAL E AO CONCEITO DE INFRAESTRUTURA DE CONHECIMENTO DO CLIMA, DUAS LITERATURAS INDEPENDENTES, PORÉM COMPLEMENTARES, QUE OFERECEM UMA ESTRUTUTRA ANALÍTICA PODEROSA PARA ANALISAR A ECONOMIA POLÍTICA EM TORNO DAS MUDANÇAS CLIMÁTICAS. O OBJETIVO DESTE TRABALHO É DUPLO: APRESENTAR UMA ARGUMENTAÇÃO TEÓRICA QUANTO ÀS RAZÕES PELAS QUAIS AMBAS AS LITERATURAS PODEM SE BENEFICIAR MUTUAMENTE DAS SUAS CONTRIBUIÇÕES E APRESENTAR COMO UMA COALIZÃO MULTISETORIAL CONTRA AS MUDANÇAS CLIMÁTICAS SE TORNOU POSSÍVEL ATRAVÉS SURGIMENTO DE NOVAS TECNOLOGIAS DIGITAIS. ATRAVÉS DE UM PROCESSO DE ANÁLISE ABDUTIVA, ESTA PESQUISA ARGUMENTA SOBRE A IMPORTÂNCIA DE ESTABELECER SÓLIDAS PARCERIAS PÚBLICO-PRIVADAS COM O INTUITO DE OFERECER PRODUTOS CLIMÁTICOS CONFIÁVEIS E PRECISOS, COMO PREVISÕES DO TEMPO E SERVIÇOS DE ALERTA DE CONDIÇÕES ADVERSAS.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>NUMEROUS HIGHLY COMPLEX TECHNOLOGIES HAVE EMERGED IN THE FIELD OF DEFENSE. ACCORDING TO THE NORTH ATLANTIC TREATY ORGANIZATION (NATO), FOR EXAMPLE, ARTIFICIAL INTELLIGENCE (AI) IS ONE OF THE EMERGING AND DISRUPTIVE TECHNOLOGIES THAT HAS GAINED PROMINENCE IN MILITARY SCIENCES DEBATES. IN THIS CONTEXT, AI IN MILITARY SCIENCES IS TREATED AS A TECHNOLOGICAL TOOL WITH MULTIFACETED APPLICATIONS OF GREAT STRATEGIC IMPORTANCE DUE TO ITS ABILITY TO ALTER AND INFLUENCE THE DYNAMICS OF CONFLICT BETWEEN STATE AND NON-STATE ACTORS, MAKING IT ONE OF THE MOST COMPETITIVE TOOLS IN THE CURRENT GLOBAL SCENARIO. BASED ON THIS, THE GUIDING QUESTION OF THIS DISSERTATION IS: "IS MILITARY ARTIFICIAL INTELLIGENCE CAPABLE OF CHANGING THE NATURE OF WAR ACCORDING TO THE PRINCIPLES OF CLAUSEWITZ'S THEORY OF WAR?" THE HYPOTHESIS EMPLOYED IS THAT CLAUSEWITZ'S THEORY MAINTAINS ITS RELEVANCE IN MILITARY SCIENCES STUDIES, EVEN IN THE FACE OF EMERGING TECHNOLOGIES LIKE ARTIFICIAL INTELLIGENCE APPLIED TO THE MILITARY DOMAIN, WHICH SEEK TO SURPASS, ALTER, AND MINIMIZE INTRINSIC ELEMENTS OF THE NATURE OF WAR. THE OVERALL OBJECTIVE OF THIS RESEARCH PROPOSES TO INVESTIGATE WHETHER MILITARY AI CAN TRANSFORM THE DYNAMICS AND ESSENTIAL CONCEPTS OF WAR THAT WERE ESTABLISHED BY CLAUSEWITZ. THEREFORE, THE SPECIFIC OBJECTIVES GUIDING THIS DISSERTATION ARE: (I) THE CONCEPTS OF FRICTION, FOG OF WAR, CENTER OF GRAVITY, AND CLAUSEWITZ'S TRINITY; (II) UNDERSTANDING AI, FROM ITS HISTORY, CONCEPT, AND DEVELOPMENT TO ITS CONCENTRATION; (III) CONTEXTUALIZING AI AND CATEGORIZING ITS APPLICATIONS IN THE MILITARY CONTEXT; AND FINALLY (IV) CONDUCTING A CRITICAL ANALYSIS OF MILITARY AI APPLICATIONS IN LIGHT OF CLAUSEWITZ'S PRINCIPLES OF WAR THEORY. THIS QUALITATIVE STUDY CONSISTS OF DOCUMENT AND CONTENT ANALYSIS, PRIORITIZING RECENT SOURCES (2019-2024), AND APPLYING A BIBLIOGRAPHIC REVIEW FOR THE PROPOSED CRITICAL ANALYSIS, ENABLING A SOLID INTRODUCTORY DEBATE ON THE APPLICATIONS OF AI IN THE MILITARY FIELD.</t>
+          <t>CLIMATE CHANGE IS REGARDED BY MANY SCHOLARS AND ACTIVISTS AS THE MOST PRESSING CHALLENGE OF THE TWENTY-FIRST CENTURY. GIVEN THE DIRE CONSEQUENCES OF THE ISSUE OVER MANY ASPECTS OF POLITICAL, ECONOMIC, AND SOCIAL LIFE ON EARTH, THIS SUBJECT REQUIRES A MULTIFACETED AND INTERDISCIPLINARY APPROACH TO TACKLE BOTH ITS CAUSES AND EFFECTS. IN THIS EFFORT, THIS WORK RESORTS TO THE DEBATE AROUND GLOBAL GOVERNANCE AND THE CONCEPT OF CLIMATE KNOWLEDGE INFRASTRUCTURE, TWO INDEPENDENT, YET COMPLIMENTARY LITERATURES THAT CAN OFFER A POWERFUL ANALYTICAL FRAMEWORK TO ASSESS THE POLITICAL ECONOMY AROUND CLIMATE CHANGE. THE GOAL OF THIS RESEARCH IS TWOFOLD: INTRODUCE THE THEORETICAL REASONING AS TO WHY BOTH LITERATURES CAN MUTUALLY BENEFIT FROM THEIR CONTRIBUTIONS AND LAY OUT HOW A MULTISTAKEHOLDER COALITION AGAINST CLIMATE CHANGE HAS BEEN ENABLED BY THE EMERGENCE OF NEW DIGITAL TECHNOLOGIES. THROUGH AN ABDUCTIVE ANALYSIS PROCESS, THIS RESEARCH ARGUES FOR THE IMPORTANCE OF ESTABLISHING SOLID PUBLIC-PRIVATE PARTNERSHIPS IN PROVIDING RELIABLE AND ACCURATE WEATHER AND CLIMATE PRODUCTS, SUCH AS WEATHER FORECASTS AND EARLY WARNING SERVICES.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CIÊNCIAS MILITARES;INTELIGÊNCIA ARTIFICIAL;CLAUSEWITZ;TEORIA DA GUERRA</t>
+          <t>MUDANÇAS CLIMÁTICAS;GOVERNANÇA GLOBAL;INFRAESTRUTURA DE CONHECIMENTO DO CLIMA;AUTORIDADE PRIVADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>MILITARY SCIENCES;ARTIFICIAL INTELLIGENCE;CLAUSEWITZ;WAR THEORY</t>
+          <t>CLIMATE CHANGE;GLOBAL GOVERNANCE;CLIMATE KNOWLEDGE INFRASTRUCTURE;PRIVATE AUTHORITY</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>IA em sentido estrito</t>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M26" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="b">
         <v>1</v>
       </c>
-      <c r="N26" t="b">
-        <v>0</v>
-      </c>
-      <c r="O26" t="b">
-        <v>0</v>
-      </c>
-      <c r="P26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="b">
-        <v>0</v>
-      </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>MARCOS AURELIO GUEDES DE OLIVEIRA</t>
+          <t>NATALIA DUS POIATTI LOMONACO</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>CIÊNCIAS MILITARES</t>
+          <t>RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>ESCOLA DE COMANDO E ESTADO-MAIOR DO EXÉRCITO</t>
+          <t>UNIVERSIDADE DE SÃO PAULO</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>ECEME</t>
+          <t>USP</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -4058,25 +4058,25 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>SÃO PAULO</t>
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>PORTUGUES</t>
+          <t>INGLES</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>POLÍTICA INTERNACIONAL</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -4086,16 +4086,16 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15391626</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15665505</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>15391626</t>
+          <t>15665505</t>
         </is>
       </c>
       <c r="AE26" t="n">
-        <v>4003013</v>
+        <v>4040126</v>
       </c>
     </row>
     <row r="27">
@@ -4114,51 +4114,51 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MATHEUS MOREIRA ALVES ALMEIDA</t>
+          <t>MICHELE GOEBEL PILLON</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>THE ROLE OF PRIVATE AUTHORITY IN GLOBAL GOVERNANCE FRAMEWORKS: THE CASE OF THE CLIMATE KNOWLEDGE INFRASTRUCTURE IN THE ERA OF BIG DATA</t>
+          <t>INOVAÇÃO, CAPACIDADE ESTATAL E POLÍTICAS PÚBLICAS: PERSPECTIVAS DOS ESTADOS BRASILEIROS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>AS MUDANÇAS CLIMÁTICAS SÃO VISTAS POR MUITOS AUTORES E ATIVISTAS COMO O MAIOR DESAFIO DO SÉCULO 21. DADO ÀS CONSEQUÊNCIAS NEFASTAS DO ASSUNTO SOBRE DIVERSOS ASPECTOS DA VIDA POLÍTICA, ECONÔMICA E SOCIAL NA TERRA, ESSE TEMA REQUER UMA ABORDAGEM MULTIFACETADA E INTERDISCIPLINAR PARA FAZER FRENTE TANTO ÀS SUAS CAUSAS QUANTO AOS SEUS EFEITOS. NESSE ESFORÇO, ESTE TRABALHO RECORRE AO DEBATE EM TORNO DA GOVERNANÇA GLOBAL E AO CONCEITO DE INFRAESTRUTURA DE CONHECIMENTO DO CLIMA, DUAS LITERATURAS INDEPENDENTES, PORÉM COMPLEMENTARES, QUE OFERECEM UMA ESTRUTUTRA ANALÍTICA PODEROSA PARA ANALISAR A ECONOMIA POLÍTICA EM TORNO DAS MUDANÇAS CLIMÁTICAS. O OBJETIVO DESTE TRABALHO É DUPLO: APRESENTAR UMA ARGUMENTAÇÃO TEÓRICA QUANTO ÀS RAZÕES PELAS QUAIS AMBAS AS LITERATURAS PODEM SE BENEFICIAR MUTUAMENTE DAS SUAS CONTRIBUIÇÕES E APRESENTAR COMO UMA COALIZÃO MULTISETORIAL CONTRA AS MUDANÇAS CLIMÁTICAS SE TORNOU POSSÍVEL ATRAVÉS SURGIMENTO DE NOVAS TECNOLOGIAS DIGITAIS. ATRAVÉS DE UM PROCESSO DE ANÁLISE ABDUTIVA, ESTA PESQUISA ARGUMENTA SOBRE A IMPORTÂNCIA DE ESTABELECER SÓLIDAS PARCERIAS PÚBLICO-PRIVADAS COM O INTUITO DE OFERECER PRODUTOS CLIMÁTICOS CONFIÁVEIS E PRECISOS, COMO PREVISÕES DO TEMPO E SERVIÇOS DE ALERTA DE CONDIÇÕES ADVERSAS.</t>
+          <t>A PESQUISA ADOTA UMA ABORDAGEM QUALITATIVA, UTILIZANDO ANÁLISE DE CONTEÚDO COMO METODOLOGIA PRINCIPAL, CONFORME PROPOSTA POR BARDIN. OS DADOS FORAM COLETADOS POR MEIO DE ENTREVISTAS SEMIESTRUTURADAS REALIZADAS COM SECRETÁRIOS ESTADUAIS DE CT&amp;I, DOS 27 ESTADOS BRASILEIROS, ABRANGENDO TODAS AS REGIÕES DO BRASIL. A ANÁLISE FOI ESTRUTURADA EM CINCO CATEGORIAS PRINCIPAIS: (1) COMPREENSÃO DA INOVAÇÃO E DO ÍNDICE DE INOVAÇÃO SUBNACIONAL, (2) INICIATIVAS DAS POLÍTICAS PÚBLICAS DE CT&amp;I NOS ESTADOS, (3) PERCEPÇÃO DOS SECRETÁRIOS DA POLÍTICA PÚBLICA DE CIÊNCIA TECNOLOGIA E INOVAÇÃO NO CICLO DAS DEMAIS POLÍTICAS PÚBLICAS DO ESTADO, (4) INOVAÇÃO E CAPACIDADE ESTATAL, E (5) USO DA INTELIGÊNCIA ARTIFICIAL NA POLÍTICA PÚBLICA DE CIÊNCIA, TECNOLOGIA E INOVAÇÃO. OS RESULTADOS REVELAM AVANÇOS SIGNIFICATIVOS NA ADOÇÃO DE POLÍTICAS PÚBLICAS DE CT&amp;I EM DIVERSAS REGIÕES, MAS TAMBÉM DESTACAM DESIGUALDADES REGIONAIS E DESAFIOS ESTRUTURAIS. AS INICIATIVAS VARIAM DESDE PROGRAMAS DE CAPACITAÇÃO E CRIAÇÃO DE HUBS DE INOVAÇÃO ATÉ A APLICAÇÃO DE INTELIGÊNCIA ARTIFICIAL PARA APRIMORAR SERVIÇOS PÚBLICOS. CONTUDO, LIMITAÇÕES COMO A FALTA DE RECURSOS, INFRAESTRUTURA INADEQUADA E DIFICULDADES NA ARTICULAÇÃO INTERSETORIAL AINDA PERSISTEM EM MUITOS ESTADOS. A PESQUISA CONTRIBUI PARA A LITERATURA SOBRE POLÍTICAS PÚBLICAS DE CT&amp;I AO EVIDENCIAR A IMPORTÂNCIA DE UM PLANEJAMENTO ESTRATÉGICO BASEADO EM INDICADORES REGIONAIS E NA TRANSVERSALIDADE ENTRE DIFERENTES SETORES GOVERNAMENTAIS. TAMBÉM REFORÇA A NECESSIDADE DE FORTALECER A CAPACIDADE ESTATAL PARA MAXIMIZAR OS BENEFÍCIOS DA INOVAÇÃO E PROMOVER MAIOR EQUIDADE REGIONAL. AS LIMITAÇÕES INCLUEM O FOCO EM PERCEPÇÕES DE GESTORES ESTADUAIS, O QUE PODE RESTRINGIR UMA ANÁLISE MAIS ABRANGENTE DOS IMPACTOS DIRETOS DAS POLÍTICAS IMPLEMENTADAS. CONTUDO, O ESTUDO OFERECE SUBSÍDIOS RELEVANTES PARA GESTORES, ACADÊMICOS E FORMULADORES DE POLÍTICAS INTERESSADOS EM COMPREENDER E APRIMORAR O PAPEL DA INOVAÇÃO COMO VETOR ESTRATÉGICO PARA O DESENVOLVIMENTO SOCIOECONÔMICO NO BRASIL.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CLIMATE CHANGE IS REGARDED BY MANY SCHOLARS AND ACTIVISTS AS THE MOST PRESSING CHALLENGE OF THE TWENTY-FIRST CENTURY. GIVEN THE DIRE CONSEQUENCES OF THE ISSUE OVER MANY ASPECTS OF POLITICAL, ECONOMIC, AND SOCIAL LIFE ON EARTH, THIS SUBJECT REQUIRES A MULTIFACETED AND INTERDISCIPLINARY APPROACH TO TACKLE BOTH ITS CAUSES AND EFFECTS. IN THIS EFFORT, THIS WORK RESORTS TO THE DEBATE AROUND GLOBAL GOVERNANCE AND THE CONCEPT OF CLIMATE KNOWLEDGE INFRASTRUCTURE, TWO INDEPENDENT, YET COMPLIMENTARY LITERATURES THAT CAN OFFER A POWERFUL ANALYTICAL FRAMEWORK TO ASSESS THE POLITICAL ECONOMY AROUND CLIMATE CHANGE. THE GOAL OF THIS RESEARCH IS TWOFOLD: INTRODUCE THE THEORETICAL REASONING AS TO WHY BOTH LITERATURES CAN MUTUALLY BENEFIT FROM THEIR CONTRIBUTIONS AND LAY OUT HOW A MULTISTAKEHOLDER COALITION AGAINST CLIMATE CHANGE HAS BEEN ENABLED BY THE EMERGENCE OF NEW DIGITAL TECHNOLOGIES. THROUGH AN ABDUCTIVE ANALYSIS PROCESS, THIS RESEARCH ARGUES FOR THE IMPORTANCE OF ESTABLISHING SOLID PUBLIC-PRIVATE PARTNERSHIPS IN PROVIDING RELIABLE AND ACCURATE WEATHER AND CLIMATE PRODUCTS, SUCH AS WEATHER FORECASTS AND EARLY WARNING SERVICES.</t>
+          <t>THE RESEARCH ADOPTS A QUALITATIVE APPROACH, USING CONTENT ANALYSIS AS THE MAIN METHODOLOGY, AS PROPOSED BY BARDIN. DATA WERE COLLECTED THROUGH SEMI-STRUCTURED INTERVIEWS CONDUCTED WITH STATE SECRETARIES OF SCIENCE, TECHNOLOGY, AND INNOVATION (ST&amp;I) FROM BRAZIL'S 27 STATES, COVERING ALL REGIONS OF THE COUNTRY. THE ANALYSIS WAS STRUCTURED INTO FIVE MAIN CATEGORIES: (1) UNDERSTANDING INNOVATION AND SUBNATIONAL INNOVATION INDEX, (2) PUBLIC POLICY INITIATIVES FOR SCIENCE, TECHNOLOGY AND INNOVATION (ST&amp;I) IN STATES, (3) PERCEPTION OF SECRETARIES OF PUBLIC POLICY FOR SCIENCE, TECHNOLOGY AND INNOVATION IN THE CYCLE OF OTHER PUBLIC POLICIES OF THE STATE, (4) INNOVATION AND STATE CAPACITY, AND (5) USE OF ARTIFICIAL INTELLIGENCE IN PUBLIC POLICY FOR SCIENCE, TECHNOLOGY AND INNOVATION. THE RESULTS REVEAL SIGNIFICANT PROGRESS IN THE ADOPTION OF ST&amp;I PUBLIC POLICIES ACROSS VARIOUS REGIONS BUT ALSO HIGHLIGHT REGIONAL INEQUALITIES AND STRUCTURAL CHALLENGES. INITIATIVES RANGE FROM TRAINING PROGRAMS AND THE CREATION OF INNOVATION HUBS TO THE APPLICATION OF ARTIFICIAL INTELLIGENCE TO ENHANCE PUBLIC SERVICES. HOWEVER, LIMITATIONS SUCH AS RESOURCE SHORTAGES, INADEQUATE INFRASTRUCTURE, AND DIFFICULTIES IN INTERSECTORAL COORDINATION PERSIST IN MANY STATES. THIS RESEARCH CONTRIBUTES TO THE LITERATURE ON ST&amp;I PUBLIC POLICIES BY EMPHASIZING THE IMPORTANCE OF STRATEGIC PLANNING BASED ON REGIONAL INDICATORS AND THE CROSS-SECTORAL INTEGRATION OF GOVERNMENT EFFORTS. IT ALSO REINFORCES THE NEED TO STRENGTHEN STATE CAPACITY TO MAXIMIZE THE BENEFITS OF INNOVATION AND PROMOTE GREATER REGIONAL EQUITY. LIMITATIONS INCLUDE THE FOCUS ON THE PERCEPTIONS OF STATE MANAGERS, WHICH MAY RESTRICT A MORE COMPREHENSIVE ANALYSIS OF THE DIRECT IMPACTS OF IMPLEMENTED POLICIES. NONETHELESS, THE STUDY PROVIDES VALUABLE INSIGHTS FOR MANAGERS, ACADEMICS, AND POLICYMAKERS INTERESTED IN UNDERSTANDING AND ENHANCING THE ROLE OF INNOVATION AS A STRATEGIC DRIVER FOR BRAZIL'S SOCIOECONOMIC DEVELOPMENT.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MUDANÇAS CLIMÁTICAS;GOVERNANÇA GLOBAL;INFRAESTRUTURA DE CONHECIMENTO DO CLIMA;AUTORIDADE PRIVADA</t>
+          <t>INOVAÇÃO E INDICADORES;POLÍTICA PÚBLICA DE CIÊNCIA;TECNOLOGIA E INOVAÇÃO;CAPACIDADE ESTATAL E INTELIGÊNCIA ARTIFICIAL EM POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>CLIMATE CHANGE;GLOBAL GOVERNANCE;CLIMATE KNOWLEDGE INFRASTRUCTURE;PRIVATE AUTHORITY</t>
+          <t>INNOVATION AND INDICATORS;PUBLIC POLICY FOR SCIENCE;TECHNOLOGY AND INNOVATION;STATE CAPACITY AND ARTIFICIAL INTELLIGENCE IN PUBLIC POLICIES</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Correlato</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>IA em sentido estrito</t>
         </is>
       </c>
       <c r="M27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
@@ -4170,54 +4170,54 @@
         <v>0</v>
       </c>
       <c r="Q27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>NATALIA DUS POIATTI LOMONACO</t>
+          <t>RAPHAEL AMORIM MACHADO</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>RELAÇÕES INTERNACIONAIS</t>
+          <t>POLÍTICAS PÚBLICAS E GOVERNO</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DE SÃO PAULO</t>
+          <t>FUNDAÇÃO GETULIO VARGAS - BRASÍLIA</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>USP</t>
+          <t>FGV-BSB</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>SUDESTE</t>
+          <t>CENTRO-OESTE</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>SÃO PAULO</t>
+          <t>DISTRITO FEDERAL</t>
         </is>
       </c>
       <c r="Y27" t="n">
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>INGLES</t>
+          <t>PORTUGUES</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>POLÍTICA INTERNACIONAL</t>
+          <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4227,16 +4227,16 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15665505</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15964806</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>15665505</t>
+          <t>15964806</t>
         </is>
       </c>
       <c r="AE27" t="n">
-        <v>4040126</v>
+        <v>4549098</v>
       </c>
     </row>
     <row r="28">
@@ -4255,37 +4255,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MICHELE GOEBEL PILLON</t>
+          <t>PEDRO VICTOR CARVALHO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>INOVAÇÃO, CAPACIDADE ESTATAL E POLÍTICAS PÚBLICAS: PERSPECTIVAS DOS ESTADOS BRASILEIROS</t>
+          <t>GLOBALIZAÇÃO DA PRODUÇÃO E DESENVOLVIMENTO TECNOLÓGICO: ASCENSÃO CHINESA E A DISPUTA NO SETOR DE TELECOMUNICAÇÕES</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>A PESQUISA ADOTA UMA ABORDAGEM QUALITATIVA, UTILIZANDO ANÁLISE DE CONTEÚDO COMO METODOLOGIA PRINCIPAL, CONFORME PROPOSTA POR BARDIN. OS DADOS FORAM COLETADOS POR MEIO DE ENTREVISTAS SEMIESTRUTURADAS REALIZADAS COM SECRETÁRIOS ESTADUAIS DE CT&amp;I, DOS 27 ESTADOS BRASILEIROS, ABRANGENDO TODAS AS REGIÕES DO BRASIL. A ANÁLISE FOI ESTRUTURADA EM CINCO CATEGORIAS PRINCIPAIS: (1) COMPREENSÃO DA INOVAÇÃO E DO ÍNDICE DE INOVAÇÃO SUBNACIONAL, (2) INICIATIVAS DAS POLÍTICAS PÚBLICAS DE CT&amp;I NOS ESTADOS, (3) PERCEPÇÃO DOS SECRETÁRIOS DA POLÍTICA PÚBLICA DE CIÊNCIA TECNOLOGIA E INOVAÇÃO NO CICLO DAS DEMAIS POLÍTICAS PÚBLICAS DO ESTADO, (4) INOVAÇÃO E CAPACIDADE ESTATAL, E (5) USO DA INTELIGÊNCIA ARTIFICIAL NA POLÍTICA PÚBLICA DE CIÊNCIA, TECNOLOGIA E INOVAÇÃO. OS RESULTADOS REVELAM AVANÇOS SIGNIFICATIVOS NA ADOÇÃO DE POLÍTICAS PÚBLICAS DE CT&amp;I EM DIVERSAS REGIÕES, MAS TAMBÉM DESTACAM DESIGUALDADES REGIONAIS E DESAFIOS ESTRUTURAIS. AS INICIATIVAS VARIAM DESDE PROGRAMAS DE CAPACITAÇÃO E CRIAÇÃO DE HUBS DE INOVAÇÃO ATÉ A APLICAÇÃO DE INTELIGÊNCIA ARTIFICIAL PARA APRIMORAR SERVIÇOS PÚBLICOS. CONTUDO, LIMITAÇÕES COMO A FALTA DE RECURSOS, INFRAESTRUTURA INADEQUADA E DIFICULDADES NA ARTICULAÇÃO INTERSETORIAL AINDA PERSISTEM EM MUITOS ESTADOS. A PESQUISA CONTRIBUI PARA A LITERATURA SOBRE POLÍTICAS PÚBLICAS DE CT&amp;I AO EVIDENCIAR A IMPORTÂNCIA DE UM PLANEJAMENTO ESTRATÉGICO BASEADO EM INDICADORES REGIONAIS E NA TRANSVERSALIDADE ENTRE DIFERENTES SETORES GOVERNAMENTAIS. TAMBÉM REFORÇA A NECESSIDADE DE FORTALECER A CAPACIDADE ESTATAL PARA MAXIMIZAR OS BENEFÍCIOS DA INOVAÇÃO E PROMOVER MAIOR EQUIDADE REGIONAL. AS LIMITAÇÕES INCLUEM O FOCO EM PERCEPÇÕES DE GESTORES ESTADUAIS, O QUE PODE RESTRINGIR UMA ANÁLISE MAIS ABRANGENTE DOS IMPACTOS DIRETOS DAS POLÍTICAS IMPLEMENTADAS. CONTUDO, O ESTUDO OFERECE SUBSÍDIOS RELEVANTES PARA GESTORES, ACADÊMICOS E FORMULADORES DE POLÍTICAS INTERESSADOS EM COMPREENDER E APRIMORAR O PAPEL DA INOVAÇÃO COMO VETOR ESTRATÉGICO PARA O DESENVOLVIMENTO SOCIOECONÔMICO NO BRASIL.</t>
+          <t>A REPÚBLICA POPULAR DA CHINA É UM CASO PARTICULAR PARA O ESTUDO DE TRAJETÓRIAS DE DESENVOLVIMENTO POR SE TRATAR DE UM ESTADO QUE, NOS ÚLTIMOS ANOS, CONSEGUIU AVANÇAR EM DIREÇÃO À FRONTEIRA TECNOLÓGICA EM DIFERENTES SEGMENTOS E POR APRESENTAR UMA ESTRUTURA POLÍTICA ESPECÍFICA E COMPLEXA. CONSIDERANDO O DESENVOLVIMENTO TECNOLÓGICO COMO UM IMPORTANTE VETOR DE TRANSFORMAÇÃO ECONÔMICA E DE PODER POLÍTICO PARA OS ESTADOS, OBSERVA-SE NOS ÚLTIMOS ANOS UMA DISPUTA SINO-ESTADUNIDENSE NO SETOR DE TELECOMUNICAÇÕES. NO CONTEXTO DESSA DISPUTA, A TRAJETÓRIA DE INTERNACIONALIZAÇÃO, A LIDERANÇA NA INDÚSTRIA DE EQUIPAMENTOS DE TELECOMUNICAÇÕES E AS SANÇÕES QUE A HUAWEI TECHNOLOGIES CO. TEM SOFRIDO FOMENTAM A DISCUSSÃO SOBRE A RELAÇÃO ENTRE ESTADO E MERCADO. PRINCIPALMENTE EM DECORRÊNCIA DE SUAS IMPLICAÇÕES GEOPOLÍTICAS QUE ENVOLVEM, DENTRE OUTROS FATORES, A REGULAÇÃO, A PADRONIZAÇÃO E O ACESSO A MERCADOS DESTINATÁRIOS DAS TECNOLOGIAS “5G” E “6G” E O CONTROLE DE TECNOLOGIAS SUBJACENTES E RELACIONADAS, INCLUINDO SEMICONDUTORES E INTELIGÊNCIA ARTIFICIAL. A PARTIR DE UMA REVISÃO DA LITERATURA, ESTA DISSERTAÇÃO TEM COMO OBJETIVO DISCUTIR A RELAÇÃO ENTRE O DESENVOLVIMENTO TECNOLÓGICO E A CAPACIDADE DE PODER DO ESTADO CHINÊS NO CONTEXTO DA GLOBALIZAÇÃO, COM ÊNFASE NO SETOR DE TELECOMUNICAÇÕES E NA DISPUTA TECNOLÓGICA SINO-ESTADUNIDENSE. A PESQUISA FOI DIVIDIDA EM TRÊS CAPÍTULOS. NO PRIMEIRO, FORAM DISCUTIDOS E ARTICULADOS TEORICAMENTE O “PODER ESTRUTURAL” COMO CATEGORIA ANALÍTICA DAS RELAÇÕES INTERNACIONAIS, AS RELAÇÕES ENTRE TECNOLOGIA E PODER E O PROCESSO DE GLOBALIZAÇÃO E FRAGMENTAÇÃO INTERNACIONAL DA PRODUÇÃO COMO VETORES DE MUDANÇA DA REALIDADE POLÍTICA DE ESTADOS E CORPORAÇÕES. NO SEGUNDO, FORAM ANALISADAS A TRAJETÓRIA DA INDÚSTRIA DE TELECOMUNICAÇÕES NA CHINA, O PAPEL DO SEU “SISTEMA NACIONAL DE INOVAÇÃO” NA AMPLIAÇÃO DAS CAPACIDADES TECNOLÓGICAS E A ESTRATÉGIA DE DESENVOLVIMENTO DOMÉSTICO E INTERNACIONALIZAÇÃO DA HUAWEI. NO TERCEIRO CAPÍTULO, FORAM MAPEADOS OS RECURSOS ENVOLVIDOS NA DISPUTA COMERCIAL-TECNOLÓGICA SINO-ESTADUNIDENSE COMO O “5G”, A INTELIGÊNCIA ARTIFICIAL E O BIG DATA NO CONTEXTO DE DATIFICAÇÃO E DIGITALIZAÇÃO DA ECONOMIA E AS SANÇÕES E RESPOSTAS DENTRO DO CONFLITO EM EXAME, PRINCIPALMENTE NOS PROCESSOS DE SECURITIZAÇÃO E PADRONIZAÇÃO DAS REDES. AO FIM, EVIDENCIOU-SE QUE A REPÚBLICA POPULAR DA CHINA ADOTOU POLÍTICAS DE ESTADO VOLTADAS AO DESENVOLVIMENTO DE SUA INDÚSTRIA DE ALTA TECNOLOGIA COM INVESTIMENTOS ESTRATÉGICOS EM P&amp;D E, CONSEQUENTEMENTE, NA PROMOÇÃO DO SEU SISTEMA NACIONAL DE INOVAÇÃO E DE CORPORAÇÕES NACIONAIS NO COMÉRCIO INTERNACIONAL. ESPECIFICAMENTE NO SETOR DE EQUIPAMENTOS DE TELECOMUNICAÇÕES, ESSE DESENVOLVIMENTO PROPORCIONOU AO PAÍS QUE UMA DE SUAS CORPORAÇÕES, A HUAWEI, ALCANÇASSE A LIDERANÇA GLOBAL NO SETOR, ASSUMINDO A MAIOR PARCELA DE RECEITAS EM SEU SEGMENTO, ADQUIRINDO CAPACIDADE DE RESPONDER ÀS SANÇÕES.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>THE RESEARCH ADOPTS A QUALITATIVE APPROACH, USING CONTENT ANALYSIS AS THE MAIN METHODOLOGY, AS PROPOSED BY BARDIN. DATA WERE COLLECTED THROUGH SEMI-STRUCTURED INTERVIEWS CONDUCTED WITH STATE SECRETARIES OF SCIENCE, TECHNOLOGY, AND INNOVATION (ST&amp;I) FROM BRAZIL'S 27 STATES, COVERING ALL REGIONS OF THE COUNTRY. THE ANALYSIS WAS STRUCTURED INTO FIVE MAIN CATEGORIES: (1) UNDERSTANDING INNOVATION AND SUBNATIONAL INNOVATION INDEX, (2) PUBLIC POLICY INITIATIVES FOR SCIENCE, TECHNOLOGY AND INNOVATION (ST&amp;I) IN STATES, (3) PERCEPTION OF SECRETARIES OF PUBLIC POLICY FOR SCIENCE, TECHNOLOGY AND INNOVATION IN THE CYCLE OF OTHER PUBLIC POLICIES OF THE STATE, (4) INNOVATION AND STATE CAPACITY, AND (5) USE OF ARTIFICIAL INTELLIGENCE IN PUBLIC POLICY FOR SCIENCE, TECHNOLOGY AND INNOVATION. THE RESULTS REVEAL SIGNIFICANT PROGRESS IN THE ADOPTION OF ST&amp;I PUBLIC POLICIES ACROSS VARIOUS REGIONS BUT ALSO HIGHLIGHT REGIONAL INEQUALITIES AND STRUCTURAL CHALLENGES. INITIATIVES RANGE FROM TRAINING PROGRAMS AND THE CREATION OF INNOVATION HUBS TO THE APPLICATION OF ARTIFICIAL INTELLIGENCE TO ENHANCE PUBLIC SERVICES. HOWEVER, LIMITATIONS SUCH AS RESOURCE SHORTAGES, INADEQUATE INFRASTRUCTURE, AND DIFFICULTIES IN INTERSECTORAL COORDINATION PERSIST IN MANY STATES. THIS RESEARCH CONTRIBUTES TO THE LITERATURE ON ST&amp;I PUBLIC POLICIES BY EMPHASIZING THE IMPORTANCE OF STRATEGIC PLANNING BASED ON REGIONAL INDICATORS AND THE CROSS-SECTORAL INTEGRATION OF GOVERNMENT EFFORTS. IT ALSO REINFORCES THE NEED TO STRENGTHEN STATE CAPACITY TO MAXIMIZE THE BENEFITS OF INNOVATION AND PROMOTE GREATER REGIONAL EQUITY. LIMITATIONS INCLUDE THE FOCUS ON THE PERCEPTIONS OF STATE MANAGERS, WHICH MAY RESTRICT A MORE COMPREHENSIVE ANALYSIS OF THE DIRECT IMPACTS OF IMPLEMENTED POLICIES. NONETHELESS, THE STUDY PROVIDES VALUABLE INSIGHTS FOR MANAGERS, ACADEMICS, AND POLICYMAKERS INTERESTED IN UNDERSTANDING AND ENHANCING THE ROLE OF INNOVATION AS A STRATEGIC DRIVER FOR BRAZIL'S SOCIOECONOMIC DEVELOPMENT.</t>
+          <t>THE PEOPLE'S REPUBLIC OF CHINA CONSTITUTES A DISTINC CASE FOR THE RESEARCH IN DEVELOPMENT STUDIES, AS IT HAS IN RECENT YEARS MOVED TOWARDS THE TECHNOLOGICAL FRONTIER ACROSS VARIOUS SECTORS AND POSSESSES A SPECIFIC AND COMPLEX POLITICAL STRUCTURE. GIVEN TECHNOLOGICAL DEVELOPMENT AS A CRUCIAL DRIVER OF ECONOMIC TRANSFORMATION AND POLITICAL POWER FOR STATES, THERE HAS BEEN OBSERVED IN RECENT YEARS A SINO-AMERICAN RIVALRY IN THE TELECOMMUNICATIONS SECTOR. AMIDST THIS RIVALRY, THE TRAJECTORY OF INTERNATIONALIZATION, LEADERSHIP IN THE TELECOMMUNICATIONS EQUIPMENT INDUSTRY, AND THE SANCTIONS FACED BY HUAWEI TECHNOLOGIES CO. FOSTER DISCUSSIONS ABOUT THE RELATIONS BETWEEN THE STATE AND THE MARKET. PRIMARILY DUE TO ITS GEOPOLITICAL IMPLICATIONS, WHICH INVOLVE, AMONG OTHER FACTORS, THE REGULATION, STANDARDIZATION, AND ACCESS TO TARGET MARKETS FOR 5G AND 6G TECHNOLOGIES, AS WELL AS THE CONTROL OF UNDERLYING AND RELATED TECHNOLOGIES, INCLUDING SEMICONDUCTORS AND ARTIFICIAL INTELLIGENCE. BASED ON A LITERATURE REVIEW, THIS DISSERTATION AIMS TO DISCUSS THE RELATIONS BETWEEN TECHNOLOGICAL DEVELOPMENT AND THE CHINESE STATE'S POWER CAPACITY IN THE CONTEXT OF GLOBALIZATION, WITH A FOCUS ON THE TELECOMMUNICATIONS SECTOR AND THE SINO-AMERICAN TECHNOLOGICAL DISPUTE. THE RESEARCH WAS DIVIDED INTO THREE CHAPTERS. THE FIRST CHAPTER DISCUSSED AND THEORETICALLY ARTICULATED THE CONCEPT OF "STRUCTURAL POWER" AS AN ANALYTICAL CATEGORY OF INTERNATIONAL RELATIONS, THE RELATIONS BETWEEN TECHNOLOGY AND POWER, AND THE PROCESS OF GLOBALIZATION AND INTERNATIONAL FRAGMENTATION OF PRODUCTION AS DRIVERS OF CHANGE IN THE POLITICAL REALITIES OF STATES AND CORPORATIONS. THE SECOND CHAPTER ANALYZED THE TRAJECTORY OF THE TELECOMMUNICATIONS INDUSTRY IN CHINA, THE ROLE OF ITS "NATIONAL INNOVATION SYSTEM" IN EXPANDING TECHNOLOGICAL CAPABILITIES, AND HUAWEI'S DOMESTIC DEVELOPMENT AND INTERNATIONALIZATION STRATEGY. THE THIRD CHAPTER MAPPED THE RESOURCES INVOLVED IN THE SINO-AMERICAN TRADE-TECH DISPUTE, SUCH AS "5G," ARTIFICIAL INTELLIGENCE, AND BIG DATA IN THE CONTEXT OF DATAFICATION AND DIGITALIZATION OF THE ECONOMY, AS WELL AS THE SANCTIONS AND RESPONSES WITHIN THE CONFLICT UNDER EXAMINATION, PARTICULARLY IN THE PROCESSES OF SECURITIZATION AND NETWORK STANDARDIZATION. IN CONCLUSION, IT WAS EVIDENT THAT THE PEOPLE'S REPUBLIC OF CHINA ADOPTED STATE POLICIES AIMED AT DEVELOPING ITS HIGH-TECH INDUSTRY THROUGH STRATEGIC INVESTMENTS IN R&amp;D, THEREBY PROMOTING ITS NATIONAL INNOVATION SYSTEM AND NATIONAL CORPORATIONS IN INTERNATIONAL TRADE. SPECIFICALLY IN THE TELECOMMUNICATIONS EQUIPMENT SECTOR, THIS DEVELOPMENT ENABLED ONE OF ITS CORPORATIONS, HUAWEI, TO ACHIEVE GLOBAL LEADERSHIP, CAPTURING THE LARGEST SHARE OF REVENUES IN ITS SEGMENT AND GAINING THE CAPABILITY TO RESPOND TO SANCTIONS.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>INOVAÇÃO E INDICADORES;POLÍTICA PÚBLICA DE CIÊNCIA;TECNOLOGIA E INOVAÇÃO;CAPACIDADE ESTATAL E INTELIGÊNCIA ARTIFICIAL EM POLÍTICAS PÚBLICAS</t>
+          <t>CHINA;DISPUTA TECNOLÓGICA;GLOBALIZAÇÃO;HUAWEI;PODER ESTRUTURAL;TELECOMUNICAÇÕES.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>INNOVATION AND INDICATORS;PUBLIC POLICY FOR SCIENCE;TECHNOLOGY AND INNOVATION;STATE CAPACITY AND ARTIFICIAL INTELLIGENCE IN PUBLIC POLICIES</t>
+          <t>CHINA;TECHNOLOGICAL COMPETITION;GLOBALIZATION;HUAWEI;STRUCTURAL POWER;TELECOMMUNICATIONS.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>IA em sentido estrito</t>
+          <t>IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M28" t="b">
@@ -4311,45 +4311,45 @@
         <v>0</v>
       </c>
       <c r="Q28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>RAPHAEL AMORIM MACHADO</t>
+          <t>UALLACE MOREIRA LIMA</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>POLÍTICAS PÚBLICAS E GOVERNO</t>
+          <t>RELAÇÕES INTERNACIONAIS</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO GETULIO VARGAS - BRASÍLIA</t>
+          <t>UNIVERSIDADE FEDERAL DA BAHIA</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>FGV-BSB</t>
+          <t>UFBA</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>CENTRO-OESTE</t>
+          <t>NORDESTE</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>DISTRITO FEDERAL</t>
+          <t>BAHIA</t>
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>POLÍTICAS PÚBLICAS</t>
+          <t>POLÍTICA INTERNACIONAL</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4368,16 +4368,16 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15964806</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15964815</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>15964806</t>
+          <t>15964815</t>
         </is>
       </c>
       <c r="AE28" t="n">
-        <v>4549098</v>
+        <v>3773478</v>
       </c>
     </row>
     <row r="29">
@@ -4388,59 +4388,59 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MESTRADO</t>
+          <t>MESTRADO PROFISSIONAL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2021-07-16</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PEDRO VICTOR CARVALHO</t>
+          <t>MARCIA REJANE CHITOLINA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GLOBALIZAÇÃO DA PRODUÇÃO E DESENVOLVIMENTO TECNOLÓGICO: ASCENSÃO CHINESA E A DISPUTA NO SETOR DE TELECOMUNICAÇÕES</t>
+          <t>CRITÉRIOS E INDICADORES DE GOVERNANÇA EM SMART CITIES: UMA REVISÃOSISTEMÁTICA DA LITERATURA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>A REPÚBLICA POPULAR DA CHINA É UM CASO PARTICULAR PARA O ESTUDO DE TRAJETÓRIAS DE DESENVOLVIMENTO POR SE TRATAR DE UM ESTADO QUE, NOS ÚLTIMOS ANOS, CONSEGUIU AVANÇAR EM DIREÇÃO À FRONTEIRA TECNOLÓGICA EM DIFERENTES SEGMENTOS E POR APRESENTAR UMA ESTRUTURA POLÍTICA ESPECÍFICA E COMPLEXA. CONSIDERANDO O DESENVOLVIMENTO TECNOLÓGICO COMO UM IMPORTANTE VETOR DE TRANSFORMAÇÃO ECONÔMICA E DE PODER POLÍTICO PARA OS ESTADOS, OBSERVA-SE NOS ÚLTIMOS ANOS UMA DISPUTA SINO-ESTADUNIDENSE NO SETOR DE TELECOMUNICAÇÕES. NO CONTEXTO DESSA DISPUTA, A TRAJETÓRIA DE INTERNACIONALIZAÇÃO, A LIDERANÇA NA INDÚSTRIA DE EQUIPAMENTOS DE TELECOMUNICAÇÕES E AS SANÇÕES QUE A HUAWEI TECHNOLOGIES CO. TEM SOFRIDO FOMENTAM A DISCUSSÃO SOBRE A RELAÇÃO ENTRE ESTADO E MERCADO. PRINCIPALMENTE EM DECORRÊNCIA DE SUAS IMPLICAÇÕES GEOPOLÍTICAS QUE ENVOLVEM, DENTRE OUTROS FATORES, A REGULAÇÃO, A PADRONIZAÇÃO E O ACESSO A MERCADOS DESTINATÁRIOS DAS TECNOLOGIAS “5G” E “6G” E O CONTROLE DE TECNOLOGIAS SUBJACENTES E RELACIONADAS, INCLUINDO SEMICONDUTORES E INTELIGÊNCIA ARTIFICIAL. A PARTIR DE UMA REVISÃO DA LITERATURA, ESTA DISSERTAÇÃO TEM COMO OBJETIVO DISCUTIR A RELAÇÃO ENTRE O DESENVOLVIMENTO TECNOLÓGICO E A CAPACIDADE DE PODER DO ESTADO CHINÊS NO CONTEXTO DA GLOBALIZAÇÃO, COM ÊNFASE NO SETOR DE TELECOMUNICAÇÕES E NA DISPUTA TECNOLÓGICA SINO-ESTADUNIDENSE. A PESQUISA FOI DIVIDIDA EM TRÊS CAPÍTULOS. NO PRIMEIRO, FORAM DISCUTIDOS E ARTICULADOS TEORICAMENTE O “PODER ESTRUTURAL” COMO CATEGORIA ANALÍTICA DAS RELAÇÕES INTERNACIONAIS, AS RELAÇÕES ENTRE TECNOLOGIA E PODER E O PROCESSO DE GLOBALIZAÇÃO E FRAGMENTAÇÃO INTERNACIONAL DA PRODUÇÃO COMO VETORES DE MUDANÇA DA REALIDADE POLÍTICA DE ESTADOS E CORPORAÇÕES. NO SEGUNDO, FORAM ANALISADAS A TRAJETÓRIA DA INDÚSTRIA DE TELECOMUNICAÇÕES NA CHINA, O PAPEL DO SEU “SISTEMA NACIONAL DE INOVAÇÃO” NA AMPLIAÇÃO DAS CAPACIDADES TECNOLÓGICAS E A ESTRATÉGIA DE DESENVOLVIMENTO DOMÉSTICO E INTERNACIONALIZAÇÃO DA HUAWEI. NO TERCEIRO CAPÍTULO, FORAM MAPEADOS OS RECURSOS ENVOLVIDOS NA DISPUTA COMERCIAL-TECNOLÓGICA SINO-ESTADUNIDENSE COMO O “5G”, A INTELIGÊNCIA ARTIFICIAL E O BIG DATA NO CONTEXTO DE DATIFICAÇÃO E DIGITALIZAÇÃO DA ECONOMIA E AS SANÇÕES E RESPOSTAS DENTRO DO CONFLITO EM EXAME, PRINCIPALMENTE NOS PROCESSOS DE SECURITIZAÇÃO E PADRONIZAÇÃO DAS REDES. AO FIM, EVIDENCIOU-SE QUE A REPÚBLICA POPULAR DA CHINA ADOTOU POLÍTICAS DE ESTADO VOLTADAS AO DESENVOLVIMENTO DE SUA INDÚSTRIA DE ALTA TECNOLOGIA COM INVESTIMENTOS ESTRATÉGICOS EM P&amp;D E, CONSEQUENTEMENTE, NA PROMOÇÃO DO SEU SISTEMA NACIONAL DE INOVAÇÃO E DE CORPORAÇÕES NACIONAIS NO COMÉRCIO INTERNACIONAL. ESPECIFICAMENTE NO SETOR DE EQUIPAMENTOS DE TELECOMUNICAÇÕES, ESSE DESENVOLVIMENTO PROPORCIONOU AO PAÍS QUE UMA DE SUAS CORPORAÇÕES, A HUAWEI, ALCANÇASSE A LIDERANÇA GLOBAL NO SETOR, ASSUMINDO A MAIOR PARCELA DE RECEITAS EM SEU SEGMENTO, ADQUIRINDO CAPACIDADE DE RESPONDER ÀS SANÇÕES.</t>
+          <t>INTRODUÇÃO: O FOCO DESTA DISSERTAÇÃO ESTÁ NO TEMA DAS SMART CITIES, ESPECIALMENTE SOB A DIMENSÃO DA GOVERNANÇA. SEU INTUITO É ELENCAR CRITÉRIOS E INDICADORES E POSSÍVEIS FORMAS DE MENSURAÇÃO DA GOVERNANÇA EM SMART CITIES, A PARTIR DA ANÁLISE DO CENÁRIO DAS INICIATIVAS E CONCEITOS IDENTIFICADOS NA LITERATURA. ASSIM, OS OBJETIVOS ESPECÍFICOS SÃO OS SEGUINTES: A)MAPEAR DE FORMA ABRANGENTE A PRODUÇÃO DE CONHECIMENTO QUE CARACTERIZA E DEFINE O ESTADO DA ARTE SOBRE SMART CITIES, POR MEIO DE MÉTODOS CIENTOMÉTRICOS SOBRE A REDE DE COLABORAÇÃO CIENTÍFICA, COCITAÇÃO DE REFERÊNCIAS, ACOPLAMENTO BIBLIOGRÁFICO E PALAVRAS-CHAVE; B) IDENTIFICAR E DEMONSTRAR CRITÉRIOS E INDICADORES PASSÍVEIS DE MENSURAÇÃO, DA DIMENSÃO DE GOVERNANÇA EM SMART CITIES, ENCONTRADOS NA LITERATURA CIENTÍFICA; C) A PARTIR DOS ACHADOS DA REVISÃO SISTEMÁTICA, ELABORAR UMA ESCALA DE CRITÉRIOS E INDICADORES SOBRE A DIMENSÃO DA GOVERNANÇA NAS SMART CITIES. MATERIAIS E MÉTODOS: POR MEIO DE UMA REVISÃO SISTEMÁTICA DA LITERATURA, ENTENDIDA COMO UM MÉTODO DE SÍNTESE DE EVIDÊNCIAS, ANALISOU-SE NOVE DOCUMENTOS DO TIPO ARTIGO CIENTÍFICO. AS PUBLICAÇÕES CONCENTRAM-SE ENTRE OS ANOS DE 2018 E 2020, INDEXADOS NA COLEÇÃO PRINCIPAL DA BASE WEB OF SCIENCE (WOS), BEM COMO INDICAÇÕES DE ESPECIALISTAS. ALIADA À REVISÃO SISTEMÁTICA, LANÇOU-SE MÃO DE UMA ABORDAGEM CIENTOMÉTRICA E BIBLIOMÉTRICA. ESTA ANÁLISE CONCENTROU-SE EM TRÊS CONCEITOS COMPLEMENTARES: O ACOPLAMENTO BIBLIOGRÁFICO DE FONTES, A COCITAÇÃO DE TEXTOS E A COOCORRÊNCIA DE TERMOS, A PARTIR DA ANÁLISE DO BANCO DE DADOS ORIGINAL DA WOS, COM 3.835 DOCUMENTOS. RESULTADOS: A REVISÃO SISTEMÁTICA DOS NOVE DOCUMENTOS IDENTIFICOU SEIS PRINCIPAIS DIMENSÕES, NAS QUAIS OS CRITÉRIOS E INDICADORES ESTÃO DISTRIBUÍDOS: DEMOCRACIA, ACCOUNTABILITY, GOVERNO, SERVIÇOS, GESTÃO E, TECNOLOGIA E INFRAESTRUTURA. JÁ COM A VISUALIZAÇÃO MAIS AMPLA SOBRE SMART CITIES, PELO OLHAR DA CIENTOMETRIA, FOI POSSÍVEL PERCEBER QUE A ÁREA SE ORGANIZA ESPECIALMENTE EM TORNO DE TEMAS COMO INTERNET OF THINGS (IOT), CONCEITUAÇÃO DAS SMARTS CITIES, CONCEITUAÇÃO E TECNOLOGIA (BIG DATA, TICS, INTERNET) E, GOVERNANÇA E POLÍTICAS PÚBLICAS. DISCUSSÃO: NA ANÁLISE DOS ESTUDOS, É POSSÍVEL CONCLUIR QUE: HÁ SOBREPOSIÇÕES DE INDICADORES, GERALMENTE ASSOCIADOS AO USO DOS SERVIÇOS PÚBLICOS, IMPLEMENTAÇÃO DE TECNOLOGIAS NA PRESTAÇÃO DE SERVIÇOS PÚBLICOS, TRANSPARÊNCIA DOS DADOS SOBRE AS ATIVIDADES DO GOVERNO E DOS SERVIÇOS PÚBLICOS, PARTICIPAÇÃO, ENTRE OUTROS. OS CRITÉRIOS E INDICADORES EXTRAÍDOS INCLUEM AINDA INFRAESTRUTURA FÍSICA, FATORES SOCIAIS E HUMANOS, TECNOLOGIAS, MONITORAMENTO DE RECURSOS E ATIVIDADES, DESENVOLVIMENTO SOCIOECONÔMICO, GESTÃO INOVADORA.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>THE PEOPLE'S REPUBLIC OF CHINA CONSTITUTES A DISTINC CASE FOR THE RESEARCH IN DEVELOPMENT STUDIES, AS IT HAS IN RECENT YEARS MOVED TOWARDS THE TECHNOLOGICAL FRONTIER ACROSS VARIOUS SECTORS AND POSSESSES A SPECIFIC AND COMPLEX POLITICAL STRUCTURE. GIVEN TECHNOLOGICAL DEVELOPMENT AS A CRUCIAL DRIVER OF ECONOMIC TRANSFORMATION AND POLITICAL POWER FOR STATES, THERE HAS BEEN OBSERVED IN RECENT YEARS A SINO-AMERICAN RIVALRY IN THE TELECOMMUNICATIONS SECTOR. AMIDST THIS RIVALRY, THE TRAJECTORY OF INTERNATIONALIZATION, LEADERSHIP IN THE TELECOMMUNICATIONS EQUIPMENT INDUSTRY, AND THE SANCTIONS FACED BY HUAWEI TECHNOLOGIES CO. FOSTER DISCUSSIONS ABOUT THE RELATIONS BETWEEN THE STATE AND THE MARKET. PRIMARILY DUE TO ITS GEOPOLITICAL IMPLICATIONS, WHICH INVOLVE, AMONG OTHER FACTORS, THE REGULATION, STANDARDIZATION, AND ACCESS TO TARGET MARKETS FOR 5G AND 6G TECHNOLOGIES, AS WELL AS THE CONTROL OF UNDERLYING AND RELATED TECHNOLOGIES, INCLUDING SEMICONDUCTORS AND ARTIFICIAL INTELLIGENCE. BASED ON A LITERATURE REVIEW, THIS DISSERTATION AIMS TO DISCUSS THE RELATIONS BETWEEN TECHNOLOGICAL DEVELOPMENT AND THE CHINESE STATE'S POWER CAPACITY IN THE CONTEXT OF GLOBALIZATION, WITH A FOCUS ON THE TELECOMMUNICATIONS SECTOR AND THE SINO-AMERICAN TECHNOLOGICAL DISPUTE. THE RESEARCH WAS DIVIDED INTO THREE CHAPTERS. THE FIRST CHAPTER DISCUSSED AND THEORETICALLY ARTICULATED THE CONCEPT OF "STRUCTURAL POWER" AS AN ANALYTICAL CATEGORY OF INTERNATIONAL RELATIONS, THE RELATIONS BETWEEN TECHNOLOGY AND POWER, AND THE PROCESS OF GLOBALIZATION AND INTERNATIONAL FRAGMENTATION OF PRODUCTION AS DRIVERS OF CHANGE IN THE POLITICAL REALITIES OF STATES AND CORPORATIONS. THE SECOND CHAPTER ANALYZED THE TRAJECTORY OF THE TELECOMMUNICATIONS INDUSTRY IN CHINA, THE ROLE OF ITS "NATIONAL INNOVATION SYSTEM" IN EXPANDING TECHNOLOGICAL CAPABILITIES, AND HUAWEI'S DOMESTIC DEVELOPMENT AND INTERNATIONALIZATION STRATEGY. THE THIRD CHAPTER MAPPED THE RESOURCES INVOLVED IN THE SINO-AMERICAN TRADE-TECH DISPUTE, SUCH AS "5G," ARTIFICIAL INTELLIGENCE, AND BIG DATA IN THE CONTEXT OF DATAFICATION AND DIGITALIZATION OF THE ECONOMY, AS WELL AS THE SANCTIONS AND RESPONSES WITHIN THE CONFLICT UNDER EXAMINATION, PARTICULARLY IN THE PROCESSES OF SECURITIZATION AND NETWORK STANDARDIZATION. IN CONCLUSION, IT WAS EVIDENT THAT THE PEOPLE'S REPUBLIC OF CHINA ADOPTED STATE POLICIES AIMED AT DEVELOPING ITS HIGH-TECH INDUSTRY THROUGH STRATEGIC INVESTMENTS IN R&amp;D, THEREBY PROMOTING ITS NATIONAL INNOVATION SYSTEM AND NATIONAL CORPORATIONS IN INTERNATIONAL TRADE. SPECIFICALLY IN THE TELECOMMUNICATIONS EQUIPMENT SECTOR, THIS DEVELOPMENT ENABLED ONE OF ITS CORPORATIONS, HUAWEI, TO ACHIEVE GLOBAL LEADERSHIP, CAPTURING THE LARGEST SHARE OF REVENUES IN ITS SEGMENT AND GAINING THE CAPABILITY TO RESPOND TO SANCTIONS.</t>
+          <t>INTRODUCTION: THE FOCUS OF THIS DISSERTATION IS ON THE THEME OF SMART CITIES, ESPECIALLY UNDER THE GOVERNANCE DIMENSION. ITS INTENT IS TO CAST REQUIREMENTS AND INDICATORS AND POSSIBLE WAYS OF MEASUREMENT IN SMART CITIES, THE ANALYSIS OF INITIATIVES AND CONCEPTS IDENTIFIED IN THE LITERATURE. THUS, THE SPECIFIC GOALS ARE THE FOLLOWING: A) WIDELY MAP THE PRODUCTION OF KNOWLEDGE WHICH CHARACTERIZE AND DEFINE THE STATE OF ART ABOUT SMART CITIES; B) IDENTIFY AND SHOW MEASURABLE REQUIREMENTS AND INDICATORS, FROM THE DIMENSION OF GOVERNANCE IN SMART CITIES, FOUND IN SCIENTIFIC LITERATURE. C) FROM THE FINDINGS IN THE SYSTEMATIC REVIEW CREATE A SCALE OF REQUIREMENTS AND INDICATORS ABOUT THE GOVERNANCE DIMENSION IN SMART CITIES. METHODS AND MATERIALS: THROUGH A SYSTEMATIC REVIEW OF THE LITERATURE, UNDERSTOOD AS A METHOD OF SYNTHESIS OF EVIDENCE, NINE DOCUMENTS OF THE SCIENTIFIC ARTICLE WERE ANALYZED. PUBLICATIONS ARE CONCENTRATED BETWEEN THE YEARS 2018 AND 2020, INDEXED TO THE MAIN BASE COLLECTION OF WEB OF SCIENCE (WOS), AS WELL AS EXPERT DEVICES. COMBINED WITH SYSTEMATIC REVIEW, A SCIENTOMETRIC AND BIBLIOMETRIC APPROACH WAS USED. THE ANALYSIS FOCUSED ON THREE COMPLEMENTARY CONCEPTS: THE BIBLIOGRAPHIC COUPLING OF SOURCES, THE CO-CITATION OF TEXTS AND CO-OCCURENCE OF TERMS, FROM THE ORIGINAL WOS DATABASE, WITH THEE THOUSAND EIGHT HUNDRED THIRTY-FIVE (3.835) DOCUMENTS. RESULTS: THE SYSTEMATIC REVIEW OF THE NINE DOCUMENTS IDENTIFIED SIX MAIN DIMENSIONS, IN WHICH THE REQUIREMENTS AND INDICATORS ARE DISTRIBUTED IN SIX DIMENSIONS: DEMOCRACY, ACCOUNTABILITY, GOVERNMENT, SERVICES AND MANAGEMENT AND TECHNOLOGY AND INFRASTRUCTURE. ALREADY, WITH A WIDELY VIEW ABOUT SMART CITIES, THROUGH THE EYES OF SCIENTOMETRICS, IT WAS POSSIBLE TO NOTICE THAT THE AREA IS ORGANIZED ESPECIALLY AROUND THEMES LIKE INTERNET OF THINGS (IOT), CONCEPTUALIZATION OF SMART CITIES, CONCEPTUALIZATION AND TECHNOLOGY (BIG DATA, TIC'S, INTERNET) AND, GOVERNANCE AND PUBLIC POLICY. DISCUSSION: IN THE ANALYSIS OF STUDIES, IT IS POSSIBLE TO CONCLUDE: THERE ARE OVERLAPPING INDICATORS, WHICH ARE ASSOCIATED WITH PUBLIC SERVICES USE, IMPLEMENTATION OF TECHNOLOGIES IN THE PROVISION OF PUBLIC SERVICES, TRANSPARENCY OF DATA ON GOVERNMENT AND PUBLIC SERVICE ACTIVITIES, PARTICIPATION, AMONG OTHERS. THE EXTRACTED REQUIREMENTS AND INDICATORS STILL INCLUDE PHYSICAL INFRASTRUCTURE, SOCIAL AND HUMAN FACTORS, TECHNOLOGIES, MONITORING OF RESOURCES AND ACTIVITIES, SOCIO ECONOMIC DEVELOPMENT, INNOVATIVE MANAGEMENT.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CHINA;DISPUTA TECNOLÓGICA;GLOBALIZAÇÃO;HUAWEI;PODER ESTRUTURAL;TELECOMUNICAÇÕES.</t>
+          <t>SMART CITIES;GOVERNANÇA;CRITÉRIOS;INDICADORES;REVISÃO SISTEMÁTICA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>CHINA;TECHNOLOGICAL COMPETITION;GLOBALIZATION;HUAWEI;STRUCTURAL POWER;TELECOMMUNICATIONS.</t>
+          <t>SMART CITIES;GOVERNANCE;REQUIREMENTS;INDICATORS;SYSTEMATIC REVIEW.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
@@ -4456,41 +4456,41 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>UALLACE MOREIRA LIMA</t>
+          <t>AUGUSTO JUNIOR CLEMENTE</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>RELAÇÕES INTERNACIONAIS</t>
+          <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DA BAHIA</t>
+          <t>FUNDAÇÃO UNIVERSIDADE FEDERAL DO PAMPA</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>UFBA</t>
+          <t>UNIPAMPA</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>NORDESTE</t>
+          <t>SUL</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>BAHIA</t>
+          <t>RIO GRANDE DO SUL</t>
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>POLÍTICA INTERNACIONAL</t>
+          <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4509,16 +4509,16 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15964815</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=10983519</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>15964815</t>
+          <t>10983519</t>
         </is>
       </c>
       <c r="AE29" t="n">
-        <v>3773478</v>
+        <v>3479153</v>
       </c>
     </row>
     <row r="30">
@@ -4537,37 +4537,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2021-07-16</t>
+          <t>2021-12-06</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MARCIA REJANE CHITOLINA</t>
+          <t>RICARDO MARI DE NOVAIS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CRITÉRIOS E INDICADORES DE GOVERNANÇA EM SMART CITIES: UMA REVISÃOSISTEMÁTICA DA LITERATURA</t>
+          <t>O USO DO BIG DATA PELA POLÍCIA MILITAR DE MINAS GERAIS NA PREVENÇÃO CRIMINAL</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>INTRODUÇÃO: O FOCO DESTA DISSERTAÇÃO ESTÁ NO TEMA DAS SMART CITIES, ESPECIALMENTE SOB A DIMENSÃO DA GOVERNANÇA. SEU INTUITO É ELENCAR CRITÉRIOS E INDICADORES E POSSÍVEIS FORMAS DE MENSURAÇÃO DA GOVERNANÇA EM SMART CITIES, A PARTIR DA ANÁLISE DO CENÁRIO DAS INICIATIVAS E CONCEITOS IDENTIFICADOS NA LITERATURA. ASSIM, OS OBJETIVOS ESPECÍFICOS SÃO OS SEGUINTES: A)MAPEAR DE FORMA ABRANGENTE A PRODUÇÃO DE CONHECIMENTO QUE CARACTERIZA E DEFINE O ESTADO DA ARTE SOBRE SMART CITIES, POR MEIO DE MÉTODOS CIENTOMÉTRICOS SOBRE A REDE DE COLABORAÇÃO CIENTÍFICA, COCITAÇÃO DE REFERÊNCIAS, ACOPLAMENTO BIBLIOGRÁFICO E PALAVRAS-CHAVE; B) IDENTIFICAR E DEMONSTRAR CRITÉRIOS E INDICADORES PASSÍVEIS DE MENSURAÇÃO, DA DIMENSÃO DE GOVERNANÇA EM SMART CITIES, ENCONTRADOS NA LITERATURA CIENTÍFICA; C) A PARTIR DOS ACHADOS DA REVISÃO SISTEMÁTICA, ELABORAR UMA ESCALA DE CRITÉRIOS E INDICADORES SOBRE A DIMENSÃO DA GOVERNANÇA NAS SMART CITIES. MATERIAIS E MÉTODOS: POR MEIO DE UMA REVISÃO SISTEMÁTICA DA LITERATURA, ENTENDIDA COMO UM MÉTODO DE SÍNTESE DE EVIDÊNCIAS, ANALISOU-SE NOVE DOCUMENTOS DO TIPO ARTIGO CIENTÍFICO. AS PUBLICAÇÕES CONCENTRAM-SE ENTRE OS ANOS DE 2018 E 2020, INDEXADOS NA COLEÇÃO PRINCIPAL DA BASE WEB OF SCIENCE (WOS), BEM COMO INDICAÇÕES DE ESPECIALISTAS. ALIADA À REVISÃO SISTEMÁTICA, LANÇOU-SE MÃO DE UMA ABORDAGEM CIENTOMÉTRICA E BIBLIOMÉTRICA. ESTA ANÁLISE CONCENTROU-SE EM TRÊS CONCEITOS COMPLEMENTARES: O ACOPLAMENTO BIBLIOGRÁFICO DE FONTES, A COCITAÇÃO DE TEXTOS E A COOCORRÊNCIA DE TERMOS, A PARTIR DA ANÁLISE DO BANCO DE DADOS ORIGINAL DA WOS, COM 3.835 DOCUMENTOS. RESULTADOS: A REVISÃO SISTEMÁTICA DOS NOVE DOCUMENTOS IDENTIFICOU SEIS PRINCIPAIS DIMENSÕES, NAS QUAIS OS CRITÉRIOS E INDICADORES ESTÃO DISTRIBUÍDOS: DEMOCRACIA, ACCOUNTABILITY, GOVERNO, SERVIÇOS, GESTÃO E, TECNOLOGIA E INFRAESTRUTURA. JÁ COM A VISUALIZAÇÃO MAIS AMPLA SOBRE SMART CITIES, PELO OLHAR DA CIENTOMETRIA, FOI POSSÍVEL PERCEBER QUE A ÁREA SE ORGANIZA ESPECIALMENTE EM TORNO DE TEMAS COMO INTERNET OF THINGS (IOT), CONCEITUAÇÃO DAS SMARTS CITIES, CONCEITUAÇÃO E TECNOLOGIA (BIG DATA, TICS, INTERNET) E, GOVERNANÇA E POLÍTICAS PÚBLICAS. DISCUSSÃO: NA ANÁLISE DOS ESTUDOS, É POSSÍVEL CONCLUIR QUE: HÁ SOBREPOSIÇÕES DE INDICADORES, GERALMENTE ASSOCIADOS AO USO DOS SERVIÇOS PÚBLICOS, IMPLEMENTAÇÃO DE TECNOLOGIAS NA PRESTAÇÃO DE SERVIÇOS PÚBLICOS, TRANSPARÊNCIA DOS DADOS SOBRE AS ATIVIDADES DO GOVERNO E DOS SERVIÇOS PÚBLICOS, PARTICIPAÇÃO, ENTRE OUTROS. OS CRITÉRIOS E INDICADORES EXTRAÍDOS INCLUEM AINDA INFRAESTRUTURA FÍSICA, FATORES SOCIAIS E HUMANOS, TECNOLOGIAS, MONITORAMENTO DE RECURSOS E ATIVIDADES, DESENVOLVIMENTO SOCIOECONÔMICO, GESTÃO INOVADORA.</t>
+          <t>O PRESENTE TRABALHO TEM POR OBJETIVO ANALISAR AS POSSIBILIDADES DA APLICAÇÃO DE FERRAMENTAS BASEADAS NA TECNOLOGIA BIG DATA PARA CUMPRIMENTO DAS ATRIBUIÇÕES CONSTITUCIONAIS DA POLÍCIA MILITAR DE MINAS GERAIS. A PESQUISA SE CARACTERIZA COMO QUALITATIVA, DE NATUREZA APLICADA. QUANTO AOS OBJETIVOS, TRATA-SE DE PESQUISA EXPLORATÓRIA E DESCRITIVA. FORAM UTILIZADOS OS PROCEDIMENTOS DE PESQUISA BIBLIOGRÁFICA, DOCUMENTAL E DE ESTUDO DE CASO, JÁ QUE SE BUSCOU FONTES SECUNDÁRIAS PARA ABORDAGEM EPISTEMOLÓGICA DO OBJETO, SUA CARACTERIZAÇÃO E EMPREGO NO CASO REAL DA POLÍCIA MILITAR DE MINAS GERAIS. PARA ENUMERAR POR MEIO DE UM ROL EXEMPLIFICATIVO AS POSSIBILIDADES DA APLICAÇÃO DE FERRAMENTAS BASEADAS NO BIG DATA NO CUMPRIMENTO DA ATRIBUIÇÃO CONSTITUCIONAL DA POLÍCIA MILITAR DE MINAS GERAIS, UTILIZOU-SE O CRITÉRIO PRAGMÁTICO, DE MANEIRA QUE AS FERRAMENTAS PROPOSTAS NÃO SEJAM INVIÁVEIS, SEJA PELO APORTE FINANCEIRO NECESSÁRIO, SEJA POR USO DE FERRAMENTAS CUJA TECNOLOGIA ESTÁ AINDA DISTANTE DA CAPACIDADE DE SER DESENVOLVIDA PELA PMMG. AS POSSIBILIDADES APRESENTADAS NÃO SÃO EXAURIENTES E FORAM ELABORADAS COM BASE NO QUE FOI PERCEBIDO E POSSÍVEL DE SER PROJETADO A RESPEITO DA CAPACIDADE TECNOLÓGICA DA PMMG A CURTO E MÉDIO PRAZO, COM O USO DE BANCO DE DADOS JÁ DISPONÍVEIS NA INSTITUIÇÃO E COM PROCEDIMENTOS ACESSÍVEIS. COMO RESULTADOS, FORAM APRESENTADAS 12 PROPOSTAS DE FERRAMENTAS DE NATUREZA PREVENTIVA QUE PODEM AUXILIAR A PMMG NO CUMPRIMENTO DA SUA ATRIBUIÇÃO CONSTITUCIONAL.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>INTRODUCTION: THE FOCUS OF THIS DISSERTATION IS ON THE THEME OF SMART CITIES, ESPECIALLY UNDER THE GOVERNANCE DIMENSION. ITS INTENT IS TO CAST REQUIREMENTS AND INDICATORS AND POSSIBLE WAYS OF MEASUREMENT IN SMART CITIES, THE ANALYSIS OF INITIATIVES AND CONCEPTS IDENTIFIED IN THE LITERATURE. THUS, THE SPECIFIC GOALS ARE THE FOLLOWING: A) WIDELY MAP THE PRODUCTION OF KNOWLEDGE WHICH CHARACTERIZE AND DEFINE THE STATE OF ART ABOUT SMART CITIES; B) IDENTIFY AND SHOW MEASURABLE REQUIREMENTS AND INDICATORS, FROM THE DIMENSION OF GOVERNANCE IN SMART CITIES, FOUND IN SCIENTIFIC LITERATURE. C) FROM THE FINDINGS IN THE SYSTEMATIC REVIEW CREATE A SCALE OF REQUIREMENTS AND INDICATORS ABOUT THE GOVERNANCE DIMENSION IN SMART CITIES. METHODS AND MATERIALS: THROUGH A SYSTEMATIC REVIEW OF THE LITERATURE, UNDERSTOOD AS A METHOD OF SYNTHESIS OF EVIDENCE, NINE DOCUMENTS OF THE SCIENTIFIC ARTICLE WERE ANALYZED. PUBLICATIONS ARE CONCENTRATED BETWEEN THE YEARS 2018 AND 2020, INDEXED TO THE MAIN BASE COLLECTION OF WEB OF SCIENCE (WOS), AS WELL AS EXPERT DEVICES. COMBINED WITH SYSTEMATIC REVIEW, A SCIENTOMETRIC AND BIBLIOMETRIC APPROACH WAS USED. THE ANALYSIS FOCUSED ON THREE COMPLEMENTARY CONCEPTS: THE BIBLIOGRAPHIC COUPLING OF SOURCES, THE CO-CITATION OF TEXTS AND CO-OCCURENCE OF TERMS, FROM THE ORIGINAL WOS DATABASE, WITH THEE THOUSAND EIGHT HUNDRED THIRTY-FIVE (3.835) DOCUMENTS. RESULTS: THE SYSTEMATIC REVIEW OF THE NINE DOCUMENTS IDENTIFIED SIX MAIN DIMENSIONS, IN WHICH THE REQUIREMENTS AND INDICATORS ARE DISTRIBUTED IN SIX DIMENSIONS: DEMOCRACY, ACCOUNTABILITY, GOVERNMENT, SERVICES AND MANAGEMENT AND TECHNOLOGY AND INFRASTRUCTURE. ALREADY, WITH A WIDELY VIEW ABOUT SMART CITIES, THROUGH THE EYES OF SCIENTOMETRICS, IT WAS POSSIBLE TO NOTICE THAT THE AREA IS ORGANIZED ESPECIALLY AROUND THEMES LIKE INTERNET OF THINGS (IOT), CONCEPTUALIZATION OF SMART CITIES, CONCEPTUALIZATION AND TECHNOLOGY (BIG DATA, TIC'S, INTERNET) AND, GOVERNANCE AND PUBLIC POLICY. DISCUSSION: IN THE ANALYSIS OF STUDIES, IT IS POSSIBLE TO CONCLUDE: THERE ARE OVERLAPPING INDICATORS, WHICH ARE ASSOCIATED WITH PUBLIC SERVICES USE, IMPLEMENTATION OF TECHNOLOGIES IN THE PROVISION OF PUBLIC SERVICES, TRANSPARENCY OF DATA ON GOVERNMENT AND PUBLIC SERVICE ACTIVITIES, PARTICIPATION, AMONG OTHERS. THE EXTRACTED REQUIREMENTS AND INDICATORS STILL INCLUDE PHYSICAL INFRASTRUCTURE, SOCIAL AND HUMAN FACTORS, TECHNOLOGIES, MONITORING OF RESOURCES AND ACTIVITIES, SOCIO ECONOMIC DEVELOPMENT, INNOVATIVE MANAGEMENT.</t>
+          <t>THIS WORK AIMS TO ANALYZE THE POSSIBILITIES OF APPLYING TOOLS BASED ON BIG DATA TECHNOLOGY TO FULFILL THE CONSTITUTIONAL ATTRIBUTIONS OF THE MILITARY POLICE OF MINAS GERAIS. THE RESEARCH IS CHARACTERIZED AS QUALITATIVE, APPLIED IN NATURE. AS FOR THE OBJECTIVES, IT IS EXPLORATORY AND DESCRIPTIVE RESEARCH. BIBLIOGRAPHIC, DOCUMENTAL, AND CASE STUDY RESEARCH PROCEDURES WERE USED SINCE SECONDARY SOURCES WERE SOUGHT FOR AN EPISTEMOLOGICAL APPROACH TO THE OBJECT, ITS CHARACTERIZATION, AND USE IN THE REAL CASE OF THE MILITARY POLICE OF MINAS GERAIS. TO ENUMERATE, THROUGH AN EXEMPLARY LIST, THE POSSIBILITIES OF APPLYING TOOLS BASED ON BIG DATA IN THE FULFILLMENT OF THE CONSTITUTIONAL ATTRIBUTION OF THE MILITARY POLICE OF MINAS GERAIS, THE PRAGMATIC CRITERION WAS USED, SO THAT IMPRACTICABLE POSSIBILITIES ARE NOT PRESENTED, EITHER BY THE CONTRIBUTION NECESSARY FINANCIAL RESOURCES, OR THROUGH THE USE OF TOOLS WHOSE TECHNOLOGY IS STILL FAR FROM THE CAPACITY TO BE DEVELOPED BY THE PMMG. THE POSSIBILITIES PRESENTED ARE NOT EXHAUSTIVE AND WERE ELABORATED BASED ON WHAT WAS PERCEIVED AND POSSIBLE TO BE PROJECTED REGARDING THE TECHNOLOGICAL CAPACITY OF PMMG IN THE SHORT AND MEDIUM-TERM, USING A DATABASE ALREADY AVAILABLE AT THE INSTITUTION AND WITH ACCESSIBLE PROCEDURES. AS A RESULT, 12 PROPOSALS FOR PREVENTIVE TOOLS THAT CAN HELP THE PMMG IN FULFILLING ITS CONSTITUTIONAL MISSION WERE PRESENTED.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SMART CITIES;GOVERNANÇA;CRITÉRIOS;INDICADORES;REVISÃO SISTEMÁTICA</t>
+          <t>BIG DATA;SEGURANÇA PÚBLICA;POLÍCIA MILITAR;ANÁLISE PREDITIVA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SMART CITIES;GOVERNANCE;REQUIREMENTS;INDICATORS;SYSTEMATIC REVIEW.</t>
+          <t>BIG DATA;PUBLIC SECURITY;MILITARY POLICE;PREDICTIVE ANALYSIS</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4597,41 +4597,41 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>AUGUSTO JUNIOR CLEMENTE</t>
+          <t>FRANCIS ALBERT COTTA FORMIGA</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>POLÍTICAS PÚBLICAS</t>
+          <t>SEGURANÇA PÚBLICA E CIDADANIA</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO UNIVERSIDADE FEDERAL DO PAMPA</t>
+          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>UNIPAMPA</t>
+          <t>UEMG</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>SUL</t>
+          <t>SUDESTE</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>RIO GRANDE DO SUL</t>
+          <t>MINAS GERAIS</t>
         </is>
       </c>
       <c r="Y30" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>POLÍTICAS PÚBLICAS</t>
+          <t>NÃO SE APLICA</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4650,16 +4650,16 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=10983519</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11453818</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>10983519</t>
+          <t>11453818</t>
         </is>
       </c>
       <c r="AE30" t="n">
-        <v>3479153</v>
+        <v>3481208</v>
       </c>
     </row>
     <row r="31">
@@ -4678,37 +4678,37 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2021-12-06</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RICARDO MARI DE NOVAIS</t>
+          <t>SAMIR BATISTA FERNANDES</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>O USO DO BIG DATA PELA POLÍCIA MILITAR DE MINAS GERAIS NA PREVENÇÃO CRIMINAL</t>
+          <t>DESCOBERTA DE CONHECIMENTO EM BANCO DE DADOS APLICADOS EM DEFESA CIVIL UTILIZANDO ÁRVORE DE DECISÃO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>O PRESENTE TRABALHO TEM POR OBJETIVO ANALISAR AS POSSIBILIDADES DA APLICAÇÃO DE FERRAMENTAS BASEADAS NA TECNOLOGIA BIG DATA PARA CUMPRIMENTO DAS ATRIBUIÇÕES CONSTITUCIONAIS DA POLÍCIA MILITAR DE MINAS GERAIS. A PESQUISA SE CARACTERIZA COMO QUALITATIVA, DE NATUREZA APLICADA. QUANTO AOS OBJETIVOS, TRATA-SE DE PESQUISA EXPLORATÓRIA E DESCRITIVA. FORAM UTILIZADOS OS PROCEDIMENTOS DE PESQUISA BIBLIOGRÁFICA, DOCUMENTAL E DE ESTUDO DE CASO, JÁ QUE SE BUSCOU FONTES SECUNDÁRIAS PARA ABORDAGEM EPISTEMOLÓGICA DO OBJETO, SUA CARACTERIZAÇÃO E EMPREGO NO CASO REAL DA POLÍCIA MILITAR DE MINAS GERAIS. PARA ENUMERAR POR MEIO DE UM ROL EXEMPLIFICATIVO AS POSSIBILIDADES DA APLICAÇÃO DE FERRAMENTAS BASEADAS NO BIG DATA NO CUMPRIMENTO DA ATRIBUIÇÃO CONSTITUCIONAL DA POLÍCIA MILITAR DE MINAS GERAIS, UTILIZOU-SE O CRITÉRIO PRAGMÁTICO, DE MANEIRA QUE AS FERRAMENTAS PROPOSTAS NÃO SEJAM INVIÁVEIS, SEJA PELO APORTE FINANCEIRO NECESSÁRIO, SEJA POR USO DE FERRAMENTAS CUJA TECNOLOGIA ESTÁ AINDA DISTANTE DA CAPACIDADE DE SER DESENVOLVIDA PELA PMMG. AS POSSIBILIDADES APRESENTADAS NÃO SÃO EXAURIENTES E FORAM ELABORADAS COM BASE NO QUE FOI PERCEBIDO E POSSÍVEL DE SER PROJETADO A RESPEITO DA CAPACIDADE TECNOLÓGICA DA PMMG A CURTO E MÉDIO PRAZO, COM O USO DE BANCO DE DADOS JÁ DISPONÍVEIS NA INSTITUIÇÃO E COM PROCEDIMENTOS ACESSÍVEIS. COMO RESULTADOS, FORAM APRESENTADAS 12 PROPOSTAS DE FERRAMENTAS DE NATUREZA PREVENTIVA QUE PODEM AUXILIAR A PMMG NO CUMPRIMENTO DA SUA ATRIBUIÇÃO CONSTITUCIONAL.</t>
+          <t>O PRESENTE ESTUDO OBJETIVOU EXTRAIR CONHECIMENTO EM BANCOS DE DADOS DE DEFESA CIVIL, PARA ISSO FOI SELECIONADO OS DADOS DA BASE DO PROGRAMA DE REGISTRO DE OCORRÊNCIAS DA SECRETARIA ESTADUAL DE DEFESA CIVIL DO RIO DE JANEIRO E TEVE COMO OBJETO DE ESTUDO OS REGISTROS DOS EVENTOS ATENDIDOS E AS SOLICITAÇÕES DE RECONHECIMENTO DE DESASTRES NO MUNÍCIPIO DE DUQUE DE CAXIAS, NA BAIXADA FLUMINENSE, NO ESTADO DO RIO DE JANEIRO ENTRE O PERÍODO DE 2013 A 2020. FOI UTILIZADA A FERRAMENTA POWER BI PARA DETECTAR ANOMALIAS, BEM COMO UTILIZAR O ALGORITMO DA MICROSOFT DECISION TREE PARA ELABORAÇÃO DE UMA ÁRVORE DE DECISÃO. A TAREFA DE CLASSIFICAÇÃO FOI EMPREGADA JUNTO COM A COLEÇÃO DE ALGORITMOS DO PROGRAMA WAIKATO ENVIRONMENT FOR KNOWLEDGE ANALYSIS PARA AVALIAR O CLASSIFICADOR. APÓS, FOI REALIZADA INTERPRETAÇÃO DA AVALIAÇÃO DOS RESULTADOS E GERADO UM GRUPO DE REGRAS. AO CONCLUIR O CICLO FOI POSSÍVEL OBTER NOVOS CONHECIMENTOS POR MEIO DE MINERAÇÃO DE DADOS QUE PODEM SER ÚTEIS E APLICADOS EM DEFESA CIVIL.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>THIS WORK AIMS TO ANALYZE THE POSSIBILITIES OF APPLYING TOOLS BASED ON BIG DATA TECHNOLOGY TO FULFILL THE CONSTITUTIONAL ATTRIBUTIONS OF THE MILITARY POLICE OF MINAS GERAIS. THE RESEARCH IS CHARACTERIZED AS QUALITATIVE, APPLIED IN NATURE. AS FOR THE OBJECTIVES, IT IS EXPLORATORY AND DESCRIPTIVE RESEARCH. BIBLIOGRAPHIC, DOCUMENTAL, AND CASE STUDY RESEARCH PROCEDURES WERE USED SINCE SECONDARY SOURCES WERE SOUGHT FOR AN EPISTEMOLOGICAL APPROACH TO THE OBJECT, ITS CHARACTERIZATION, AND USE IN THE REAL CASE OF THE MILITARY POLICE OF MINAS GERAIS. TO ENUMERATE, THROUGH AN EXEMPLARY LIST, THE POSSIBILITIES OF APPLYING TOOLS BASED ON BIG DATA IN THE FULFILLMENT OF THE CONSTITUTIONAL ATTRIBUTION OF THE MILITARY POLICE OF MINAS GERAIS, THE PRAGMATIC CRITERION WAS USED, SO THAT IMPRACTICABLE POSSIBILITIES ARE NOT PRESENTED, EITHER BY THE CONTRIBUTION NECESSARY FINANCIAL RESOURCES, OR THROUGH THE USE OF TOOLS WHOSE TECHNOLOGY IS STILL FAR FROM THE CAPACITY TO BE DEVELOPED BY THE PMMG. THE POSSIBILITIES PRESENTED ARE NOT EXHAUSTIVE AND WERE ELABORATED BASED ON WHAT WAS PERCEIVED AND POSSIBLE TO BE PROJECTED REGARDING THE TECHNOLOGICAL CAPACITY OF PMMG IN THE SHORT AND MEDIUM-TERM, USING A DATABASE ALREADY AVAILABLE AT THE INSTITUTION AND WITH ACCESSIBLE PROCEDURES. AS A RESULT, 12 PROPOSALS FOR PREVENTIVE TOOLS THAT CAN HELP THE PMMG IN FULFILLING ITS CONSTITUTIONAL MISSION WERE PRESENTED.</t>
+          <t>THE PRESENT STUDY AIMED TO EXTRACT KNOWLEDGE FROM A DATABASE OF CIVIL DEFENSE, FOR THIS THE DATA FROM THE BASE OF THE RECORD OF OCCURRENCES PROGRAM OF THE STATE SECRETARIAT OF CIVIL DEFENSE OF RIO DE JANEIRO WAS SELECTED AND HAD AS OBJECT OF STUDY THE RECORDS OF THE EVENTS ATTENDED AND REQUESTS FOR RECOGNITION OF DISASTERS IN THE MUNICIPALITY OF DUQUE DE CAXIAS, IN BAIXADA FLUMINENSE, IN THE STATE OF RIO DE JANEIRO BETWEEN THE PERIOD OF 2013 TO 2020. THE POWER BI TOOL WAS USED TO DETECT ANOMALIES, AS WELL AS TO USE THE ALGORITHM MICROSOFT'S DECISION TREE FOR THE ELABORATION OF A DECISION TREE. THE CLASSIFICATION TASK WAS USED TOGETHER WITH THE COLLECTION OF ALGORITHMS FROM THE WAIKATO ENVIRONMENT FOR KNOWLEDGE ANALYSIS PROGRAM TO EVALUATE THE CLASSIFIER. AFTERWARDS, INTERPRETATION OF THE EVALUATION OF THE RESULTS WAS CARRIED OUT AND A GROUP OF RULES WAS GENERATED. AT THE END OF THE CYCLE, IT WAS POSSIBLE TO DISCOVER NEW KNOWLEDGE THROUGH DATA MINING THAT CAN BE USEFUL AND APPLIED IN CIVIL DEFENSE.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>BIG DATA;SEGURANÇA PÚBLICA;POLÍCIA MILITAR;ANÁLISE PREDITIVA</t>
+          <t>DEFESA CIVIL;ARVORE DE DECISAO;MINERAÇÃO DE DADOS;POWER BI</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>BIG DATA;PUBLIC SECURITY;MILITARY POLICE;PREDICTIVE ANALYSIS</t>
+          <t>CIVIL DEFENSE, DECISION TREE, DATA MINING, POWER BI.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>FRANCIS ALBERT COTTA FORMIGA</t>
+          <t>AIRTON BODSTEIN DE BARROS</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>SEGURANÇA PÚBLICA E CIDADANIA</t>
+          <t>DEFESA E SEGURANÇA CIVIL</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>UNIVERSIDADE FEDERAL FLUMINENSE</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>UEMG</t>
+          <t>UFF</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -4763,16 +4763,16 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>MINAS GERAIS</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -4791,16 +4791,16 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11453818</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11509111</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>11453818</t>
+          <t>11509111</t>
         </is>
       </c>
       <c r="AE31" t="n">
-        <v>3481208</v>
+        <v>1554710</v>
       </c>
     </row>
     <row r="32">
@@ -4819,37 +4819,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SAMIR BATISTA FERNANDES</t>
+          <t>WALMOR CRISTINO LEITE JUNIOR</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>DESCOBERTA DE CONHECIMENTO EM BANCO DE DADOS APLICADOS EM DEFESA CIVIL UTILIZANDO ÁRVORE DE DECISÃO</t>
+          <t>MEDIDAS DE SEGURANÇA CIBERNÉTICA PARA O AMBIENTE MARÍTIMO: UMA ANÁLISE HÍBRIDA DE PROPOSTAS E TENDÊNCIAS NO CONTEXTO BRASILEIRO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>O PRESENTE ESTUDO OBJETIVOU EXTRAIR CONHECIMENTO EM BANCOS DE DADOS DE DEFESA CIVIL, PARA ISSO FOI SELECIONADO OS DADOS DA BASE DO PROGRAMA DE REGISTRO DE OCORRÊNCIAS DA SECRETARIA ESTADUAL DE DEFESA CIVIL DO RIO DE JANEIRO E TEVE COMO OBJETO DE ESTUDO OS REGISTROS DOS EVENTOS ATENDIDOS E AS SOLICITAÇÕES DE RECONHECIMENTO DE DESASTRES NO MUNÍCIPIO DE DUQUE DE CAXIAS, NA BAIXADA FLUMINENSE, NO ESTADO DO RIO DE JANEIRO ENTRE O PERÍODO DE 2013 A 2020. FOI UTILIZADA A FERRAMENTA POWER BI PARA DETECTAR ANOMALIAS, BEM COMO UTILIZAR O ALGORITMO DA MICROSOFT DECISION TREE PARA ELABORAÇÃO DE UMA ÁRVORE DE DECISÃO. A TAREFA DE CLASSIFICAÇÃO FOI EMPREGADA JUNTO COM A COLEÇÃO DE ALGORITMOS DO PROGRAMA WAIKATO ENVIRONMENT FOR KNOWLEDGE ANALYSIS PARA AVALIAR O CLASSIFICADOR. APÓS, FOI REALIZADA INTERPRETAÇÃO DA AVALIAÇÃO DOS RESULTADOS E GERADO UM GRUPO DE REGRAS. AO CONCLUIR O CICLO FOI POSSÍVEL OBTER NOVOS CONHECIMENTOS POR MEIO DE MINERAÇÃO DE DADOS QUE PODEM SER ÚTEIS E APLICADOS EM DEFESA CIVIL.</t>
+          <t>O PRESENTE ESTUDO APRESENTA A IMPORTÂNCIA DA SEGURANÇA CIBERNÉTICA NAS RELAÇÕES DE PODER NO CONTEXTO DAS RELAÇÕES INTERNACIONAIS E EM QUESTÕES DE SEGURANÇA MARÍTIMA, TRAZENDO À TONA A NECESSIDADE DE SE ENFRENTAR ESSA PROBLEMÁTICA. SÃO APRESENTADOS OS RISCOS E MEDIDAS MITIGATÓRIAS IDENTIFICADOS A PARTIR DE 2017, ATRAVÉS DE UMA REVISÃO SISTEMÁTICA NAS BASES DE DADOS SCOPUS, IEEE EXPLORE, ACM DIGITAL LIBRARY E GOOGLE SCHOLAR. ANALISAM-SE DADOS OBTIDOS ATRAVÉS DA MINERAÇÃO DE DADOS EM TEXTO EM DOCUMENTOS DE NÍVEL POLÍTICO BRASILEIROS E AMERICANOS. ALÉM DISSO, SÃO APRESENTADOS OS RESULTADOS DE UM QUESTIONÁRIO RESPONDIDO PELA SOCIEDADE CIVIL, PESQUISADORES E MILITARES BRASILEIROS, COM O OBJETIVO DE COLHER A PERCEPÇÃO DESSES GRUPOS SOBRE O ASSUNTO SEGURANÇA CIBERNÉTICA NO CONTEXTO BRASILEIRO. DESSA FORMA, SÃO OBTIDOS OS RESULTADOS QUE PERMITEM CONCLUIR QUE HÁ INDÍCIOS DE QUE UMA MAIOR PRESENÇA DO ASSUNTO EM DOCUMENTOS OFICIAIS DE NÍVEL POLÍTICO SE TRADUZ EM MAIORES ÍNDICES DE SEGURANÇA CIBERNÉTICA. TAMBÉM SE PERCEBE QUE A PRESENÇA DO TEMA EM DOCUMENTOS BRASILEIROS NÃO SE ENCONTRA EM NÍVEIS SATISFATÓRIOS, FATO REFORÇADO PELOS RESULTADOS DOS QUESTIONÁRIOS. NOTA-SE QUE O ASSUNTO VEM GANHANDO CADA VEZ MAIS IMPORTÂNCIA AO LONGO DOS ANOS E QUE AS MEDIDAS MITIGATÓRIAS IDENTIFICADAS APRESENTAM POTENCIAL PARA SEREM IMPLEMENTADAS NO BRASIL, COMO POLÍTICAS PÚBLICAS.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>THE PRESENT STUDY AIMED TO EXTRACT KNOWLEDGE FROM A DATABASE OF CIVIL DEFENSE, FOR THIS THE DATA FROM THE BASE OF THE RECORD OF OCCURRENCES PROGRAM OF THE STATE SECRETARIAT OF CIVIL DEFENSE OF RIO DE JANEIRO WAS SELECTED AND HAD AS OBJECT OF STUDY THE RECORDS OF THE EVENTS ATTENDED AND REQUESTS FOR RECOGNITION OF DISASTERS IN THE MUNICIPALITY OF DUQUE DE CAXIAS, IN BAIXADA FLUMINENSE, IN THE STATE OF RIO DE JANEIRO BETWEEN THE PERIOD OF 2013 TO 2020. THE POWER BI TOOL WAS USED TO DETECT ANOMALIES, AS WELL AS TO USE THE ALGORITHM MICROSOFT'S DECISION TREE FOR THE ELABORATION OF A DECISION TREE. THE CLASSIFICATION TASK WAS USED TOGETHER WITH THE COLLECTION OF ALGORITHMS FROM THE WAIKATO ENVIRONMENT FOR KNOWLEDGE ANALYSIS PROGRAM TO EVALUATE THE CLASSIFIER. AFTERWARDS, INTERPRETATION OF THE EVALUATION OF THE RESULTS WAS CARRIED OUT AND A GROUP OF RULES WAS GENERATED. AT THE END OF THE CYCLE, IT WAS POSSIBLE TO DISCOVER NEW KNOWLEDGE THROUGH DATA MINING THAT CAN BE USEFUL AND APPLIED IN CIVIL DEFENSE.</t>
+          <t>THIS STUDY PRESENTS THE IMPORTANCE OF CYBER SECURITY IN RELATIONS OF POWER, IN THE CONTEXT OF INTERNATIONAL RELATIONS AND IN MARITIME SECURITY ISSUES, BRINGING TO LIGHT THE NEED TO FACE THIS PROBLEM. THE RISKS AND MITIGATION MEASURES IDENTIFIED SINCE 2017 ARE PRESENTED THROUGH A SYSTEMATIC REVIEW IN SCOPUS, IEEE EXPLORE, ACM DIGITAL LIBRARY AND GOOGLE SCHOLAR DATABASES. DATA OBTAINED THROUGH DATA MINING IN BRAZILIAN AND AMERICAN POLITICAL DOCUMENTS ARE ANALYZED. IN ADDITION, THE RESULTS OF A QUESTIONNAIRE ANSWERED BY BRAZILIAN CIVIL SOCIETY, RESEARCHERS AND THE MILITARY ARE PRESENTED, WITH THE AIM OF GATHERING THE PERCEPTION OF THESE GROUPS, ON THE SUBJECT OF CYBERSECURITY IN THE BRAZILIAN CONTEXT. THUS, THE RESULTS OBTAINED ALLOW TO CONCLUDE THAT THERE ARE SIGNS THAT A GREATER PRESENCE OF THE SUBJECT IN OFFICIAL DOCUMENTS AT A POLITICAL LEVEL TRANSLATES INTO HIGHER LEVELS OF CYBER SECURITY. IT IS ALSO NOTICED THAT THE PRESENCE OF THE TOPIC IN BRAZILIAN DOCUMENTS IS NOT AT A SATISFACTORY LEVEL, A FACT REINFORCED BY THE RESULTS OF THE QUESTIONNAIRES. IT IS NOTED THAT THE SUBJECT HAS GAINED INCREASING IMPORTANCE OVER THE YEARS AND THAT THE IDENTIFIED MITIGATION MEASURES HAVE THE POTENTIAL TO BE IMPLEMENTED IN BRAZIL AS PUBLIC POLICIES.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>DEFESA CIVIL;ARVORE DE DECISAO;MINERAÇÃO DE DADOS;POWER BI</t>
+          <t>SEGURANÇA CIBERNÉTICA;POLÍTICAS PÚBLICAS;AMBIENTE MARÍTIMO</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>CIVIL DEFENSE, DECISION TREE, DATA MINING, POWER BI.</t>
+          <t>CYBER SECURITY;PUBLIC POLICY;MARITIME ENVIRONMENT</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4879,22 +4879,22 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>AIRTON BODSTEIN DE BARROS</t>
+          <t>NIVAL NUNES DE ALMEIDA</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>DEFESA E SEGURANÇA CIVIL</t>
+          <t>ESTUDOS MARÍTIMOS</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL FLUMINENSE</t>
+          <t>ESCOLA DE GUERRA NAVAL</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>UFF</t>
+          <t>EGN</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="Y32" t="n">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
@@ -4932,16 +4932,16 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11509111</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11380785</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>11509111</t>
+          <t>11380785</t>
         </is>
       </c>
       <c r="AE32" t="n">
-        <v>1554710</v>
+        <v>3619457</v>
       </c>
     </row>
     <row r="33">
@@ -4956,41 +4956,41 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>WALMOR CRISTINO LEITE JUNIOR</t>
+          <t>ANTONIO GUEDES CAVALCANTE JUNIOR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MEDIDAS DE SEGURANÇA CIBERNÉTICA PARA O AMBIENTE MARÍTIMO: UMA ANÁLISE HÍBRIDA DE PROPOSTAS E TENDÊNCIAS NO CONTEXTO BRASILEIRO</t>
+          <t>POLÍTICA DE FORMAÇÃO PROFISSIONAL DO IFCE PECÉM: PERCEPÇÕES DAS PARTES INTERESSADAS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>O PRESENTE ESTUDO APRESENTA A IMPORTÂNCIA DA SEGURANÇA CIBERNÉTICA NAS RELAÇÕES DE PODER NO CONTEXTO DAS RELAÇÕES INTERNACIONAIS E EM QUESTÕES DE SEGURANÇA MARÍTIMA, TRAZENDO À TONA A NECESSIDADE DE SE ENFRENTAR ESSA PROBLEMÁTICA. SÃO APRESENTADOS OS RISCOS E MEDIDAS MITIGATÓRIAS IDENTIFICADOS A PARTIR DE 2017, ATRAVÉS DE UMA REVISÃO SISTEMÁTICA NAS BASES DE DADOS SCOPUS, IEEE EXPLORE, ACM DIGITAL LIBRARY E GOOGLE SCHOLAR. ANALISAM-SE DADOS OBTIDOS ATRAVÉS DA MINERAÇÃO DE DADOS EM TEXTO EM DOCUMENTOS DE NÍVEL POLÍTICO BRASILEIROS E AMERICANOS. ALÉM DISSO, SÃO APRESENTADOS OS RESULTADOS DE UM QUESTIONÁRIO RESPONDIDO PELA SOCIEDADE CIVIL, PESQUISADORES E MILITARES BRASILEIROS, COM O OBJETIVO DE COLHER A PERCEPÇÃO DESSES GRUPOS SOBRE O ASSUNTO SEGURANÇA CIBERNÉTICA NO CONTEXTO BRASILEIRO. DESSA FORMA, SÃO OBTIDOS OS RESULTADOS QUE PERMITEM CONCLUIR QUE HÁ INDÍCIOS DE QUE UMA MAIOR PRESENÇA DO ASSUNTO EM DOCUMENTOS OFICIAIS DE NÍVEL POLÍTICO SE TRADUZ EM MAIORES ÍNDICES DE SEGURANÇA CIBERNÉTICA. TAMBÉM SE PERCEBE QUE A PRESENÇA DO TEMA EM DOCUMENTOS BRASILEIROS NÃO SE ENCONTRA EM NÍVEIS SATISFATÓRIOS, FATO REFORÇADO PELOS RESULTADOS DOS QUESTIONÁRIOS. NOTA-SE QUE O ASSUNTO VEM GANHANDO CADA VEZ MAIS IMPORTÂNCIA AO LONGO DOS ANOS E QUE AS MEDIDAS MITIGATÓRIAS IDENTIFICADAS APRESENTAM POTENCIAL PARA SEREM IMPLEMENTADAS NO BRASIL, COMO POLÍTICAS PÚBLICAS.</t>
+          <t>O ESTUDO DAS CIÊNCIAS POLÍTICAS PÚBLICAS NASCE COM A PUBLICAÇÃO DA OBRA INTITULADA THE POLICY SCIENCES DE HAROLD LASSWELL E DAVID LERNER, EM 1951. OS AUTORES DA OBRA POSSUÍAM VISÕES PRAGMÁTICAS ACERCA DA RESOLUTIVIDADE DOS PROBLEMAS SOCIAIS E, POR CONSEGUINTE, EMPRESTARAM TAIS CARACTERÍSTICAS À NOVA CIÊNCIA QUE NASCERA. O GOVERNO FEDERAL NORTE AMERICANO COMPROU A IDEIA DAS POLÍTICAS PÚBLICAS E, DURANTE O MANDATO PRESIDENCIAL DE RONALD REAGAN, PASSOU-SE A EXIGIR COMO FUNDAMENTO PARA O GASTO PÚBLICO QUE TODA E QUALQUER AÇÃO PÚBLICA ONEROSA NECESSITARIA DE UMA ANÁLISE A PRIORI ACERCA DOS ESPERADOS IMPACTOS SOCIAIS. LOGICAMENTE, AS CIÊNCIAS POLÍTICAS PÚBLICAS SE DESENVOLVERAM E NOVAS FORMAS DE SE ENXERGAREM AS SUAS APLICABILIDADES NA RESOLUÇÃO DOS PROBLEMAS PÚBLICOS SURGIRAM. ASSIM, A PARTIR DA DÉCADA DE 1980, NASCE A ABORDAGEM ARGUMENTATIVA, QUE ANALISA AS POLÍTICAS PÚBLICAS COM UM VIÉS MAIS CRÍTICO. NA DÉCADA DE 1990, OCORRE UMA DIVERSIFICAÇÃO TEÓRICA E METODOLÓGICA COM A CHAMADA “VIRADA ARGUMENTATIVA”. OUTRA FORMA DE SE ANALISAR AS POLÍTICAS PÚBLICAS É QUANTO AOS ATORES ENVOLVIDOS NA SUA ELABORAÇÃO E/OU IMPLEMENTAÇÃO. QUANDO SE CONSIDERA QUE APENAS OS AGENTES PÚBLICOS ESTÃO ENVOLVIDOS NESSE PROCESSO, ESTÁ-SE DIANTE DA ABORDAGEM ESTADOCÊNTRICA; QUANDO SE CONSIDERA QUE, ALÉM DOS ATORES GOVERNAMENTAIS, EXISTE UMA GAMA DE OUTROS PARTICIPANTES OU INTERESSADOS NA FORMULAÇÃO DE DETERMINADA POLÍTICA PÚBLICA, ESTÁ A SE ADOTAR A ABORDAGEM MULTICÊNTRICA DE POLÍTICAS PÚBLICAS. DA LEITURA DE SECCHI (2013), INFERE-SE QUE A ABORDAGEM MULTICÊNTRICA ADOTA UM ENFOQUE MENOS POSITIVISTA E, PORTANTO, INTERPRETATIVO/ARGUMENTATIVO DAS POLÍTICAS PÚBLICAS. A PARTIR DOS CONHECIMENTOS DESSE CAMPO DE ESTUDO, ANALISOU-SE A POLÍTICA PÚBLICA DE FORMAÇÃO PROFISSIONAL DO IFCE CAMPUS PECÉM. POR SER UMA POLÍTICA PÚBLICA DE FORMAÇÃO PROFISSIONAL, FOI NECESSÁRIO A CONSTRUÇÃO DE UM ARCABOUÇO TEÓRICO ACERCA DESSE CAMPO DE ESTUDO. VERIFICOU-SE QUE O PROCESSO DE FORMAÇÃO PROFISSIONAL BRASILEIRO NASCEU COM A CHEGADA DOS PORTUGUESES AQUI. DE LÁ PARA CÁ, A FORMAÇÃO PROFISSIONAL PARA O TRABALHO PASSOU POR DIVERSAS MUTAÇÕES. NUM INÍCIO, O TRABALHO MANUAL FOI DIRECIONADO EXCLUSIVAMENTE AOS ÍNDIOS E ESCRAVOS IMPORTADOS DA ÁFRICA, OCASIONANDO UMA NÍTIDA SEPARAÇÃO SOCIAL POR MEIO DO TRABALHO. ESSE PROCESSO DE ESTIGMATIZAÇÃO DO TRABALHO MANUAL ENRAIZOU-SE NA CULTURA BRASILEIRA – TRABALHO MANUAL PASSOU A SER COISA DE NEGRO E DE ÍNDIO E, AQUELES QUE PRETENDIA DEIXAR EVIDENTE SUA POSIÇÃO SOCIAL SE AFASTAVAM DAS ATIVIDADES LABORAIS QUE UTILIZAVAM AS MÃOS. ALÉM DO MAIS, O PROCESSO DE APRENDIZAGEM PROFISSIONAL SE DAVA SEM NENHUMA SISTEMATIZAÇÃO E, GERALMENTE, OCORRIA NO PRÓPRIO LOCAL DE TRABALHO DURANTE A SUA EXECUÇÃO. ERA TRABALHANDO QUE SE APRENDIA A TRABALHAR. COM A CHEGADA DA FAMÍLIA REAL PORTUGUESA AO BRASIL, EM 1808, EM NADA SE MUDA A CONCEPÇÃO ACERCA DE QUEM REALIZAVA OS TRABALHOS MANUAIS, POIS CONTINUAVAM SENDO EXECUTADOS POR ESCRAVOS E ÍNDIOS. CONTUDO, NASCE A CONCEPÇÃO DE SISTEMATIZAÇÃO DO ENSINO PROFISSIONAL BRASILEIRO COM A CRIAÇÃO DO COLÉGIO DAS FÁBRICAS, EM 1808, CONSIDERADO O PRIMEIRO ESTABELECIMENTO IMPLANTADO PELO PODER PÚBLICO NO PAÍS. DURANTE O BRASIL IMPERIAL POUCAS MUDANÇAS ACONTECERAM E SE LIMITARAM A OFERTAR ENSINO PROFISSIONAL OBRIGATÓRIO AOS ÓRFÃOS E DESAMPARADOS, COMO UMA FORMA DE ASSISTENCIALISMO REPARATÓRIO. JÁ, NO INÍCIO DO SÉCULO XX, NASCE O ENSINO PROFISSIONAL SISTEMATIZADO E A NÍVEL NACIONAL, COM A CRIAÇÃO DAS ESCOLAS DE APRENDIZES E ARTÍFICES, EM 1909, PELO PRESIDENTE DA REPÚBLICA NILO PEÇANHA. A EDUCAÇÃO PROFISSIONAL BRASILEIRA EVOLUIU BASTANTE AO LONGO DO SÉCULO XX, PASSOU POR VÁRIAS ALTERAÇÕES DE DENOMINAÇÃO INSTITUCIONAL ATÉ CHEGAR NO QUE É CONHECIDA COMO A REDE FEDERAL DE EDUCAÇÃO PROFISSIONAL, DA QUAL FAZ PARTE O INSTITUTO FEDERAL DO CEARÁ, QUE POSSUI MAIS DE 30 CAMPI, ENTRE ELES O IFCE CAMPUS PECÉM, OBJETO DE ESTUDO DESTA PESQUISA. O IFCE CAMPUS PECÉM ESTÁ LOCALIZADO NA DIVISA DOS MUNICÍPIOS DE CAUCAIA E SÃO GONÇALO DO AMARANTE, MAIS ESPECIFICAMENTE NA ÁREA DO COMPLEXO INDUSTRIAL E PORTUÁRIO DO PECÉM – CIPP. O MOTIVO DA SUA IMPLANTAÇÃO É EXATAMENTE A FORMAÇÃO PROFISSIONAL DA MÃO DE OBRA DEMANDADA PELAS EMPRESAS QUE COMPÕEM O CIPP. NASCEU A PARTIR DO ACORDO DE COOPERAÇÃO ENTRE O GOVERNO DO ESTADO DO CEARÁ E O IFCE, PARA FUNCIONAR COMO CENTRO DE TREINAMENTO DO TRABALHADOR CEARENSE – CTTC. FOI INAUGURADO EM 2015 E COMEÇOU A FUNCIONAR EM 2016. NO INÍCIO, OFERTOU CURSOS DE CURTA DURAÇÃO E APLICABILIDADE PRÁTICA, CHAMADOS FIC – FORMAÇÃO INICIAL E CONTINUADA. NO ANO DE 2018, ABRIU SEUS PRIMEIROS CURSOS DE FORMAÇÃO TÉCNICA: ELETROMECÂNICA E AUTOMAÇÃO INDUSTRIAL. ATUALMENTE, POSSUI CINCO CURSOS TÉCNICOS: ELETROMECÂNICA, AUTOMAÇÃO INDUSTRIAL, QUÍMICA INDUSTRIAL, ELETROTÉCNICA E SEGURANÇA DO TRABALHO. ESTE TRABALHO, PORTANTO, VISOU IDENTIFICAR, A PARTIR DE QUESTIONÁRIOS E ENTREVISTAS, QUAIS AS PERCEPÇÕES DAS SUAS PARTES INTERESSADAS, ALUNOS, EGRESSOS, SERVIDORES, REITORIA DO IFCE, DIRETORIA DA AECIPP – ASSOCIAÇÃO DAS EMPRESAS DO CIPP E A GESTÃO DO CIPP.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>THIS STUDY PRESENTS THE IMPORTANCE OF CYBER SECURITY IN RELATIONS OF POWER, IN THE CONTEXT OF INTERNATIONAL RELATIONS AND IN MARITIME SECURITY ISSUES, BRINGING TO LIGHT THE NEED TO FACE THIS PROBLEM. THE RISKS AND MITIGATION MEASURES IDENTIFIED SINCE 2017 ARE PRESENTED THROUGH A SYSTEMATIC REVIEW IN SCOPUS, IEEE EXPLORE, ACM DIGITAL LIBRARY AND GOOGLE SCHOLAR DATABASES. DATA OBTAINED THROUGH DATA MINING IN BRAZILIAN AND AMERICAN POLITICAL DOCUMENTS ARE ANALYZED. IN ADDITION, THE RESULTS OF A QUESTIONNAIRE ANSWERED BY BRAZILIAN CIVIL SOCIETY, RESEARCHERS AND THE MILITARY ARE PRESENTED, WITH THE AIM OF GATHERING THE PERCEPTION OF THESE GROUPS, ON THE SUBJECT OF CYBERSECURITY IN THE BRAZILIAN CONTEXT. THUS, THE RESULTS OBTAINED ALLOW TO CONCLUDE THAT THERE ARE SIGNS THAT A GREATER PRESENCE OF THE SUBJECT IN OFFICIAL DOCUMENTS AT A POLITICAL LEVEL TRANSLATES INTO HIGHER LEVELS OF CYBER SECURITY. IT IS ALSO NOTICED THAT THE PRESENCE OF THE TOPIC IN BRAZILIAN DOCUMENTS IS NOT AT A SATISFACTORY LEVEL, A FACT REINFORCED BY THE RESULTS OF THE QUESTIONNAIRES. IT IS NOTED THAT THE SUBJECT HAS GAINED INCREASING IMPORTANCE OVER THE YEARS AND THAT THE IDENTIFIED MITIGATION MEASURES HAVE THE POTENTIAL TO BE IMPLEMENTED IN BRAZIL AS PUBLIC POLICIES.</t>
+          <t>THE STUDY OF PUBLIC POLICY SCIENCES WAS BORN WITH THE PUBLICATION OF THE WORK ENTITLED THE POLICY SCIENCES BY HAROLD LASSWELL AND DAVID LERNER, IN 1951. THE AUTHORS OF THE WORK HAD PRAGMATIC VISIONS ABOUT THE RESOLUTION OF SOCIAL PROBLEMS AND, THEREFORE, LENT SUCH CHARACTERISTICS TO THE NEW SCIENCE. WHO WAS BORN THE US FEDERAL GOVERNMENT BOUGHT THE IDEA OF PUBLIC POLICIES AND, DURING RONALD REAGAN'S PRESIDENTIAL TERM, IT BEGAN TO DEMAND AS A BASIS FOR PUBLIC SPENDING THAT ANY AND ALL ONEROUS PUBLIC ACTION WOULD REQUIRE AN A PRIORI ANALYSIS OF THE EXPECTED SOCIAL IMPACTS. LOGICALLY, PUBLIC POLICY SCIENCES HAVE DEVELOPED AND NEW WAYS OF SEEING THEIR APPLICABILITY IN SOLVING PUBLIC PROBLEMS HAVE EMERGED. THUS, FROM THE 1980S ONWARDS, THE ARGUMENTATIVE APPROACH WAS BORN, WHICH ANALYZES PUBLIC POLICIES WITH A MORE CRITICAL BIAS. IN THE 1990S, THERE WAS A THEORETICAL AND METHODOLOGICAL DIVERSIFICATION WITH THE SO-CALLED “ARGUMENTATIVE TURN”. ANOTHER WAY OF ANALYZING PUBLIC POLICIES IS REGARDING THE ACTORS INVOLVED IN THEIR ELABORATION AND/OR IMPLEMENTATION. WHEN WE CONSIDER THAT ONLY PUBLIC AGENTS ARE INVOLVED IN THIS PROCESS, WE ARE FACED WITH THE STATE-CENTRIC APPROACH; WHEN ONE CONSIDERS THAT, IN ADDITION TO GOVERNMENT ACTORS, THERE IS A RANGE OF OTHER PARTICIPANTS OR STAKEHOLDERS IN THE FORMULATION OF A GIVEN PUBLIC POLICY, A MULTICENTRIC APPROACH TO PUBLIC POLICIES IS BEING ADOPTED. FROM A READING OF SECCHI (2013), IT IS INFERRED THAT THE MULTICENTRIC APPROACH ADOPTS A LESS POSITIVIST APPROACH AND, THEREFORE, AN INTERPRETATIVE/ARGUMENTATIVE APPROACH TO PUBLIC POLICIES. BASED ON THE KNOWLEDGE OF THIS FIELD OF STUDY, THE PUBLIC POLICY FOR PROFESSIONAL TRAINING OF THE IFCE CAMPUS PECÉM WAS ANALYZED. AS IT IS A PUBLIC POLICY FOR PROFESSIONAL TRAINING, IT WAS NECESSARY TO BUILD A THEORETICAL FRAMEWORK ABOUT THIS FIELD OF STUDY. IT WAS FOUND THAT THE BRAZILIAN PROFESSIONAL TRAINING PROCESS WAS BORN WITH THE ARRIVAL OF THE PORTUGUESE HERE. SINCE THEN, PROFESSIONAL TRAINING FOR WORK HAS UNDERGONE SEVERAL CHANGES. IN THE BEGINNING, MANUAL WORK WAS DIRECTED EXCLUSIVELY TO INDIANS AND SLAVES IMPORTED FROM AFRICA, CAUSING A CLEAR SOCIAL SEPARATION THROUGH WORK. THIS PROCESS OF STIGMATIZATION OF MANUAL WORK WAS ROOTED IN BRAZILIAN CULTURE – MANUAL WORK BECAME A THING FOR BLACKS AND INDIANS, AND THOSE WHO INTENDED TO MAKE THEIR SOCIAL POSITION EVIDENT MOVED AWAY FROM WORK ACTIVITIES THAT USED THEIR HANDS. FURTHERMORE, THE PROFESSIONAL LEARNING PROCESS TOOK PLACE WITHOUT ANY SYSTEMATIZATION AND GENERALLY TOOK PLACE IN THE WORKPLACE DURING ITS EXECUTION. IT WAS BY WORKING THAT YOU LEARNED TO WORK. WITH THE ARRIVAL OF THE PORTUGUESE ROYAL FAMILY IN BRAZIL, IN 1808, THE CONCEPTION ABOUT WHO CARRIED OUT MANUAL WORK REMAINED UNCHANGED, AS THEY CONTINUED TO BE PERFORMED BY SLAVES AND INDIANS. HOWEVER, THE CONCEPT OF SYSTEMATIZATION OF BRAZILIAN PROFESSIONAL EDUCATION WAS BORN WITH THE CREATION OF THE COLÉGIO DAS FÁBRICAS, IN 1808, CONSIDERED THE FIRST ESTABLISHMENT IMPLEMENTED BY THE GOVERNMENT IN THE COUNTRY. DURING IMPERIAL BRAZIL, FEW CHANGES TOOK PLACE AND THEY WERE LIMITED TO OFFERING MANDATORY PROFESSIONAL EDUCATION TO ORPHANS AND THE HELPLESS, AS A FORM OF REPARATORY ASSISTANCE. AT THE BEGINNING OF THE 20TH CENTURY, SYSTEMATIZED PROFESSIONAL EDUCATION WAS BORN AT A NATIONAL LEVEL, WITH THE CREATION OF THE SCHOOLS FOR APPRENTICES AND CRAFTSMEN, IN 1909, BY THE PRESIDENT OF THE REPUBLIC NILO PEÇANHA. BRAZILIAN PROFESSIONAL EDUCATION HAS EVOLVED A LOT THROUGHOUT THE 20TH CENTURY, HAS UNDERGONE SEVERAL CHANGES OF INSTITUTIONAL NAME UNTIL REACHING WHAT IS KNOWN AS THE FEDERAL NETWORK OF PROFESSIONAL EDUCATION, WHICH INCLUDES THE FEDERAL INSTITUTE OF CEARÁ, WHICH HAS MORE THAN 30 CAMPUSES, AMONG THEM THE IFCE CAMPUS PECÉM, OBJECT OF STUDY OF THIS RESEARCH. THE IFCE CAMPUS PECÉM IS LOCATED ON THE BORDER OF THE MUNICIPALITIES OF CAUCAIA AND SÃO GONÇALO DO AMARANTE, MORE SPECIFICALLY IN THE AREA OF THE INDUSTRIAL AND PORT COMPLEX OF PECÉM – CIPP. THE REASON FOR ITS IMPLEMENTATION IS PRECISELY THE PROFESSIONAL TRAINING OF THE WORKFORCE DEMANDED BY THE COMPANIES THAT MAKE UP THE CIPP. IT WAS BORN FROM THE COOPERATION AGREEMENT BETWEEN THE GOVERNMENT OF THE STATE OF CEARÁ AND IFCE, TO FUNCTION AS A TRAINING CENTER FOR CEARÁ WORKERS - CTTC. IT WAS OPENED IN 2015 AND STARTED OPERATING IN 2016. AT THE BEGINNING, IT OFFERED SHORT-TERM COURSES WITH PRACTICAL APPLICABILITY, CALLED FIC – INITIAL AND CONTINUED TRAINING. IN 2018, IT OPENED ITS FIRST TECHNICAL TRAINING COURSES: ELECTROMECHANICS AND INDUSTRIAL AUTOMATION. CURRENTLY, IT HAS FIVE TECHNICAL COURSES: ELECTROMECHANICS, INDUSTRIAL AUTOMATION, INDUSTRIAL CHEMISTRY, ELECTROTECHNICS AND OCCUPATIONAL SAFETY. THIS WORK, THEREFORE, AIMED TO IDENTIFY, FROM QUESTIONNAIRES AND INTERVIEWS, WHICH ARE THE PERCEPTIONS OF ITS STAKEHOLDERS, STUDENTS, GRADUATES, SERVERS, RECTORY OF IFCE, BOARD OF AECIPP – ASSOCIATION OF CIPP COMPANIES AND THE MANAGEMENT OF THE CIPP.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SEGURANÇA CIBERNÉTICA;POLÍTICAS PÚBLICAS;AMBIENTE MARÍTIMO</t>
+          <t>POLÍTICAS PÚBLICAS;EDUCAÇÃO PROFISSIONAL;INSTITUTO FEDERAL DO CEARÁ</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>CYBER SECURITY;PUBLIC POLICY;MARITIME ENVIRONMENT</t>
+          <t>PUBLIC POLICIES;PROFESSIONAL EDUCATION;FEDERAL INSTITUTE OF CEARÁ</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -5020,41 +5020,41 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>NIVAL NUNES DE ALMEIDA</t>
+          <t>RODRIGO SANTAELLA GONCALVES</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>ESTUDOS MARÍTIMOS</t>
+          <t>PLANEJAMENTO E POLITICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>ESCOLA DE GUERRA NAVAL</t>
+          <t>UNIVERSIDADE ESTADUAL DO CEARÁ</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>EGN</t>
+          <t>UECE</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>SUDESTE</t>
+          <t>NORDESTE</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>CEARÁ</t>
         </is>
       </c>
       <c r="Y33" t="n">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -5073,16 +5073,16 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11380785</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11550911</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>11380785</t>
+          <t>11550911</t>
         </is>
       </c>
       <c r="AE33" t="n">
-        <v>3619457</v>
+        <v>2353082</v>
       </c>
     </row>
     <row r="34">
@@ -5101,51 +5101,51 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ANTONIO GUEDES CAVALCANTE JUNIOR</t>
+          <t>CAUE BETTINI PAES LEME</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>POLÍTICA DE FORMAÇÃO PROFISSIONAL DO IFCE PECÉM: PERCEPÇÕES DAS PARTES INTERESSADAS</t>
+          <t>LEGISLAÇÕES E MAPEAMENTO DE ACESSIBILIDADE NA CIDADE DE SÃO PAULO POR MEIO DE APLICATIVOS DIGITAIS E PLATAFORMAS COLABORATIVAS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>O ESTUDO DAS CIÊNCIAS POLÍTICAS PÚBLICAS NASCE COM A PUBLICAÇÃO DA OBRA INTITULADA THE POLICY SCIENCES DE HAROLD LASSWELL E DAVID LERNER, EM 1951. OS AUTORES DA OBRA POSSUÍAM VISÕES PRAGMÁTICAS ACERCA DA RESOLUTIVIDADE DOS PROBLEMAS SOCIAIS E, POR CONSEGUINTE, EMPRESTARAM TAIS CARACTERÍSTICAS À NOVA CIÊNCIA QUE NASCERA. O GOVERNO FEDERAL NORTE AMERICANO COMPROU A IDEIA DAS POLÍTICAS PÚBLICAS E, DURANTE O MANDATO PRESIDENCIAL DE RONALD REAGAN, PASSOU-SE A EXIGIR COMO FUNDAMENTO PARA O GASTO PÚBLICO QUE TODA E QUALQUER AÇÃO PÚBLICA ONEROSA NECESSITARIA DE UMA ANÁLISE A PRIORI ACERCA DOS ESPERADOS IMPACTOS SOCIAIS. LOGICAMENTE, AS CIÊNCIAS POLÍTICAS PÚBLICAS SE DESENVOLVERAM E NOVAS FORMAS DE SE ENXERGAREM AS SUAS APLICABILIDADES NA RESOLUÇÃO DOS PROBLEMAS PÚBLICOS SURGIRAM. ASSIM, A PARTIR DA DÉCADA DE 1980, NASCE A ABORDAGEM ARGUMENTATIVA, QUE ANALISA AS POLÍTICAS PÚBLICAS COM UM VIÉS MAIS CRÍTICO. NA DÉCADA DE 1990, OCORRE UMA DIVERSIFICAÇÃO TEÓRICA E METODOLÓGICA COM A CHAMADA “VIRADA ARGUMENTATIVA”. OUTRA FORMA DE SE ANALISAR AS POLÍTICAS PÚBLICAS É QUANTO AOS ATORES ENVOLVIDOS NA SUA ELABORAÇÃO E/OU IMPLEMENTAÇÃO. QUANDO SE CONSIDERA QUE APENAS OS AGENTES PÚBLICOS ESTÃO ENVOLVIDOS NESSE PROCESSO, ESTÁ-SE DIANTE DA ABORDAGEM ESTADOCÊNTRICA; QUANDO SE CONSIDERA QUE, ALÉM DOS ATORES GOVERNAMENTAIS, EXISTE UMA GAMA DE OUTROS PARTICIPANTES OU INTERESSADOS NA FORMULAÇÃO DE DETERMINADA POLÍTICA PÚBLICA, ESTÁ A SE ADOTAR A ABORDAGEM MULTICÊNTRICA DE POLÍTICAS PÚBLICAS. DA LEITURA DE SECCHI (2013), INFERE-SE QUE A ABORDAGEM MULTICÊNTRICA ADOTA UM ENFOQUE MENOS POSITIVISTA E, PORTANTO, INTERPRETATIVO/ARGUMENTATIVO DAS POLÍTICAS PÚBLICAS. A PARTIR DOS CONHECIMENTOS DESSE CAMPO DE ESTUDO, ANALISOU-SE A POLÍTICA PÚBLICA DE FORMAÇÃO PROFISSIONAL DO IFCE CAMPUS PECÉM. POR SER UMA POLÍTICA PÚBLICA DE FORMAÇÃO PROFISSIONAL, FOI NECESSÁRIO A CONSTRUÇÃO DE UM ARCABOUÇO TEÓRICO ACERCA DESSE CAMPO DE ESTUDO. VERIFICOU-SE QUE O PROCESSO DE FORMAÇÃO PROFISSIONAL BRASILEIRO NASCEU COM A CHEGADA DOS PORTUGUESES AQUI. DE LÁ PARA CÁ, A FORMAÇÃO PROFISSIONAL PARA O TRABALHO PASSOU POR DIVERSAS MUTAÇÕES. NUM INÍCIO, O TRABALHO MANUAL FOI DIRECIONADO EXCLUSIVAMENTE AOS ÍNDIOS E ESCRAVOS IMPORTADOS DA ÁFRICA, OCASIONANDO UMA NÍTIDA SEPARAÇÃO SOCIAL POR MEIO DO TRABALHO. ESSE PROCESSO DE ESTIGMATIZAÇÃO DO TRABALHO MANUAL ENRAIZOU-SE NA CULTURA BRASILEIRA – TRABALHO MANUAL PASSOU A SER COISA DE NEGRO E DE ÍNDIO E, AQUELES QUE PRETENDIA DEIXAR EVIDENTE SUA POSIÇÃO SOCIAL SE AFASTAVAM DAS ATIVIDADES LABORAIS QUE UTILIZAVAM AS MÃOS. ALÉM DO MAIS, O PROCESSO DE APRENDIZAGEM PROFISSIONAL SE DAVA SEM NENHUMA SISTEMATIZAÇÃO E, GERALMENTE, OCORRIA NO PRÓPRIO LOCAL DE TRABALHO DURANTE A SUA EXECUÇÃO. ERA TRABALHANDO QUE SE APRENDIA A TRABALHAR. COM A CHEGADA DA FAMÍLIA REAL PORTUGUESA AO BRASIL, EM 1808, EM NADA SE MUDA A CONCEPÇÃO ACERCA DE QUEM REALIZAVA OS TRABALHOS MANUAIS, POIS CONTINUAVAM SENDO EXECUTADOS POR ESCRAVOS E ÍNDIOS. CONTUDO, NASCE A CONCEPÇÃO DE SISTEMATIZAÇÃO DO ENSINO PROFISSIONAL BRASILEIRO COM A CRIAÇÃO DO COLÉGIO DAS FÁBRICAS, EM 1808, CONSIDERADO O PRIMEIRO ESTABELECIMENTO IMPLANTADO PELO PODER PÚBLICO NO PAÍS. DURANTE O BRASIL IMPERIAL POUCAS MUDANÇAS ACONTECERAM E SE LIMITARAM A OFERTAR ENSINO PROFISSIONAL OBRIGATÓRIO AOS ÓRFÃOS E DESAMPARADOS, COMO UMA FORMA DE ASSISTENCIALISMO REPARATÓRIO. JÁ, NO INÍCIO DO SÉCULO XX, NASCE O ENSINO PROFISSIONAL SISTEMATIZADO E A NÍVEL NACIONAL, COM A CRIAÇÃO DAS ESCOLAS DE APRENDIZES E ARTÍFICES, EM 1909, PELO PRESIDENTE DA REPÚBLICA NILO PEÇANHA. A EDUCAÇÃO PROFISSIONAL BRASILEIRA EVOLUIU BASTANTE AO LONGO DO SÉCULO XX, PASSOU POR VÁRIAS ALTERAÇÕES DE DENOMINAÇÃO INSTITUCIONAL ATÉ CHEGAR NO QUE É CONHECIDA COMO A REDE FEDERAL DE EDUCAÇÃO PROFISSIONAL, DA QUAL FAZ PARTE O INSTITUTO FEDERAL DO CEARÁ, QUE POSSUI MAIS DE 30 CAMPI, ENTRE ELES O IFCE CAMPUS PECÉM, OBJETO DE ESTUDO DESTA PESQUISA. O IFCE CAMPUS PECÉM ESTÁ LOCALIZADO NA DIVISA DOS MUNICÍPIOS DE CAUCAIA E SÃO GONÇALO DO AMARANTE, MAIS ESPECIFICAMENTE NA ÁREA DO COMPLEXO INDUSTRIAL E PORTUÁRIO DO PECÉM – CIPP. O MOTIVO DA SUA IMPLANTAÇÃO É EXATAMENTE A FORMAÇÃO PROFISSIONAL DA MÃO DE OBRA DEMANDADA PELAS EMPRESAS QUE COMPÕEM O CIPP. NASCEU A PARTIR DO ACORDO DE COOPERAÇÃO ENTRE O GOVERNO DO ESTADO DO CEARÁ E O IFCE, PARA FUNCIONAR COMO CENTRO DE TREINAMENTO DO TRABALHADOR CEARENSE – CTTC. FOI INAUGURADO EM 2015 E COMEÇOU A FUNCIONAR EM 2016. NO INÍCIO, OFERTOU CURSOS DE CURTA DURAÇÃO E APLICABILIDADE PRÁTICA, CHAMADOS FIC – FORMAÇÃO INICIAL E CONTINUADA. NO ANO DE 2018, ABRIU SEUS PRIMEIROS CURSOS DE FORMAÇÃO TÉCNICA: ELETROMECÂNICA E AUTOMAÇÃO INDUSTRIAL. ATUALMENTE, POSSUI CINCO CURSOS TÉCNICOS: ELETROMECÂNICA, AUTOMAÇÃO INDUSTRIAL, QUÍMICA INDUSTRIAL, ELETROTÉCNICA E SEGURANÇA DO TRABALHO. ESTE TRABALHO, PORTANTO, VISOU IDENTIFICAR, A PARTIR DE QUESTIONÁRIOS E ENTREVISTAS, QUAIS AS PERCEPÇÕES DAS SUAS PARTES INTERESSADAS, ALUNOS, EGRESSOS, SERVIDORES, REITORIA DO IFCE, DIRETORIA DA AECIPP – ASSOCIAÇÃO DAS EMPRESAS DO CIPP E A GESTÃO DO CIPP.</t>
+          <t>ESTE POLICY PAPER TEM COMO OBJETIVO SUGERIR A IMPLEMENTAÇÃO DE MECANISMOS DE COLETA DE DADOS SOBRE CONDIÇÕES DE ACESSIBILIDADE DE CALÇADAS E PASSEIOS PÚBLICOS NA CIDADE DE SÃO PAULO. TOMANDO COMO MODELO A EXPERIÊNCIA DO PROJECT SIDEWALK, JÁ ATIVO EM CIDADES DOS EUA E MÉXICO, ESPERAMOS QUE ESSA INICIATIVA POSSA SER REPRODUZIDA EM SÃO PAULO E CONTE COM PARTICIPAÇÃO POPULAR VOLUNTÁRIA E INTELIGÊNCIA ARTIFICIAL PARA COLETAR DADOS QUE POSSAM SER UTILIZADOS NA CRIAÇÃO DE POLÍTICAS PÚBLICAS, QUE MELHOREM AS CONDIÇÕES DAS CALÇADAS NAS CIDADES AO REDOR DO MUNDO, PRINCIPALMENTE EM SÃO PAULO.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>THE STUDY OF PUBLIC POLICY SCIENCES WAS BORN WITH THE PUBLICATION OF THE WORK ENTITLED THE POLICY SCIENCES BY HAROLD LASSWELL AND DAVID LERNER, IN 1951. THE AUTHORS OF THE WORK HAD PRAGMATIC VISIONS ABOUT THE RESOLUTION OF SOCIAL PROBLEMS AND, THEREFORE, LENT SUCH CHARACTERISTICS TO THE NEW SCIENCE. WHO WAS BORN THE US FEDERAL GOVERNMENT BOUGHT THE IDEA OF PUBLIC POLICIES AND, DURING RONALD REAGAN'S PRESIDENTIAL TERM, IT BEGAN TO DEMAND AS A BASIS FOR PUBLIC SPENDING THAT ANY AND ALL ONEROUS PUBLIC ACTION WOULD REQUIRE AN A PRIORI ANALYSIS OF THE EXPECTED SOCIAL IMPACTS. LOGICALLY, PUBLIC POLICY SCIENCES HAVE DEVELOPED AND NEW WAYS OF SEEING THEIR APPLICABILITY IN SOLVING PUBLIC PROBLEMS HAVE EMERGED. THUS, FROM THE 1980S ONWARDS, THE ARGUMENTATIVE APPROACH WAS BORN, WHICH ANALYZES PUBLIC POLICIES WITH A MORE CRITICAL BIAS. IN THE 1990S, THERE WAS A THEORETICAL AND METHODOLOGICAL DIVERSIFICATION WITH THE SO-CALLED “ARGUMENTATIVE TURN”. ANOTHER WAY OF ANALYZING PUBLIC POLICIES IS REGARDING THE ACTORS INVOLVED IN THEIR ELABORATION AND/OR IMPLEMENTATION. WHEN WE CONSIDER THAT ONLY PUBLIC AGENTS ARE INVOLVED IN THIS PROCESS, WE ARE FACED WITH THE STATE-CENTRIC APPROACH; WHEN ONE CONSIDERS THAT, IN ADDITION TO GOVERNMENT ACTORS, THERE IS A RANGE OF OTHER PARTICIPANTS OR STAKEHOLDERS IN THE FORMULATION OF A GIVEN PUBLIC POLICY, A MULTICENTRIC APPROACH TO PUBLIC POLICIES IS BEING ADOPTED. FROM A READING OF SECCHI (2013), IT IS INFERRED THAT THE MULTICENTRIC APPROACH ADOPTS A LESS POSITIVIST APPROACH AND, THEREFORE, AN INTERPRETATIVE/ARGUMENTATIVE APPROACH TO PUBLIC POLICIES. BASED ON THE KNOWLEDGE OF THIS FIELD OF STUDY, THE PUBLIC POLICY FOR PROFESSIONAL TRAINING OF THE IFCE CAMPUS PECÉM WAS ANALYZED. AS IT IS A PUBLIC POLICY FOR PROFESSIONAL TRAINING, IT WAS NECESSARY TO BUILD A THEORETICAL FRAMEWORK ABOUT THIS FIELD OF STUDY. IT WAS FOUND THAT THE BRAZILIAN PROFESSIONAL TRAINING PROCESS WAS BORN WITH THE ARRIVAL OF THE PORTUGUESE HERE. SINCE THEN, PROFESSIONAL TRAINING FOR WORK HAS UNDERGONE SEVERAL CHANGES. IN THE BEGINNING, MANUAL WORK WAS DIRECTED EXCLUSIVELY TO INDIANS AND SLAVES IMPORTED FROM AFRICA, CAUSING A CLEAR SOCIAL SEPARATION THROUGH WORK. THIS PROCESS OF STIGMATIZATION OF MANUAL WORK WAS ROOTED IN BRAZILIAN CULTURE – MANUAL WORK BECAME A THING FOR BLACKS AND INDIANS, AND THOSE WHO INTENDED TO MAKE THEIR SOCIAL POSITION EVIDENT MOVED AWAY FROM WORK ACTIVITIES THAT USED THEIR HANDS. FURTHERMORE, THE PROFESSIONAL LEARNING PROCESS TOOK PLACE WITHOUT ANY SYSTEMATIZATION AND GENERALLY TOOK PLACE IN THE WORKPLACE DURING ITS EXECUTION. IT WAS BY WORKING THAT YOU LEARNED TO WORK. WITH THE ARRIVAL OF THE PORTUGUESE ROYAL FAMILY IN BRAZIL, IN 1808, THE CONCEPTION ABOUT WHO CARRIED OUT MANUAL WORK REMAINED UNCHANGED, AS THEY CONTINUED TO BE PERFORMED BY SLAVES AND INDIANS. HOWEVER, THE CONCEPT OF SYSTEMATIZATION OF BRAZILIAN PROFESSIONAL EDUCATION WAS BORN WITH THE CREATION OF THE COLÉGIO DAS FÁBRICAS, IN 1808, CONSIDERED THE FIRST ESTABLISHMENT IMPLEMENTED BY THE GOVERNMENT IN THE COUNTRY. DURING IMPERIAL BRAZIL, FEW CHANGES TOOK PLACE AND THEY WERE LIMITED TO OFFERING MANDATORY PROFESSIONAL EDUCATION TO ORPHANS AND THE HELPLESS, AS A FORM OF REPARATORY ASSISTANCE. AT THE BEGINNING OF THE 20TH CENTURY, SYSTEMATIZED PROFESSIONAL EDUCATION WAS BORN AT A NATIONAL LEVEL, WITH THE CREATION OF THE SCHOOLS FOR APPRENTICES AND CRAFTSMEN, IN 1909, BY THE PRESIDENT OF THE REPUBLIC NILO PEÇANHA. BRAZILIAN PROFESSIONAL EDUCATION HAS EVOLVED A LOT THROUGHOUT THE 20TH CENTURY, HAS UNDERGONE SEVERAL CHANGES OF INSTITUTIONAL NAME UNTIL REACHING WHAT IS KNOWN AS THE FEDERAL NETWORK OF PROFESSIONAL EDUCATION, WHICH INCLUDES THE FEDERAL INSTITUTE OF CEARÁ, WHICH HAS MORE THAN 30 CAMPUSES, AMONG THEM THE IFCE CAMPUS PECÉM, OBJECT OF STUDY OF THIS RESEARCH. THE IFCE CAMPUS PECÉM IS LOCATED ON THE BORDER OF THE MUNICIPALITIES OF CAUCAIA AND SÃO GONÇALO DO AMARANTE, MORE SPECIFICALLY IN THE AREA OF THE INDUSTRIAL AND PORT COMPLEX OF PECÉM – CIPP. THE REASON FOR ITS IMPLEMENTATION IS PRECISELY THE PROFESSIONAL TRAINING OF THE WORKFORCE DEMANDED BY THE COMPANIES THAT MAKE UP THE CIPP. IT WAS BORN FROM THE COOPERATION AGREEMENT BETWEEN THE GOVERNMENT OF THE STATE OF CEARÁ AND IFCE, TO FUNCTION AS A TRAINING CENTER FOR CEARÁ WORKERS - CTTC. IT WAS OPENED IN 2015 AND STARTED OPERATING IN 2016. AT THE BEGINNING, IT OFFERED SHORT-TERM COURSES WITH PRACTICAL APPLICABILITY, CALLED FIC – INITIAL AND CONTINUED TRAINING. IN 2018, IT OPENED ITS FIRST TECHNICAL TRAINING COURSES: ELECTROMECHANICS AND INDUSTRIAL AUTOMATION. CURRENTLY, IT HAS FIVE TECHNICAL COURSES: ELECTROMECHANICS, INDUSTRIAL AUTOMATION, INDUSTRIAL CHEMISTRY, ELECTROTECHNICS AND OCCUPATIONAL SAFETY. THIS WORK, THEREFORE, AIMED TO IDENTIFY, FROM QUESTIONNAIRES AND INTERVIEWS, WHICH ARE THE PERCEPTIONS OF ITS STAKEHOLDERS, STUDENTS, GRADUATES, SERVERS, RECTORY OF IFCE, BOARD OF AECIPP – ASSOCIATION OF CIPP COMPANIES AND THE MANAGEMENT OF THE CIPP.</t>
+          <t>THIS POLICY PAPER AIMS TO SUGGEST THE IMPLEMENTATION OF DATA COLLECTION MECHANISMS ON ACCESSIBILITY CONDITIONS OF SIDEWALKS IN THE CITY OF SÃO PAULO. TAKING AS A MODEL THE EXPERIENCE OF PROJECT SIDEWALK, ALREADY ACTIVE IN CITIES IN THE U.S. AND MEXICO, WE HOPE THAT THIS INITIATIVE CAN BE REPRODUCED IN SÃO PAULO AND, WITH THE USE OF VOLUNTARY POPULAR PARTICIPATION AND ARTIFICIAL INTELLIGENCE, TO COLLECT DATA THAT CAN BE USED IN THE CREATION OF PUBLIC POLICIES THAT IMPROVE THE CONDITIONS OF SIDEWALKS IN CITIES AROUND THE WORLD, ESPECIALLY IN SÃO PAULO.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>POLÍTICAS PÚBLICAS;EDUCAÇÃO PROFISSIONAL;INSTITUTO FEDERAL DO CEARÁ</t>
+          <t>DEFICIÊNCIA;CALÇADAS;ACESSIBILIDADE;POLÍTICA PÚBLICA.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>PUBLIC POLICIES;PROFESSIONAL EDUCATION;FEDERAL INSTITUTE OF CEARÁ</t>
+          <t>DISABILITY;SIDEWALKS;ACCESSIBILITY;PUBLIC POLICY</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Correlato</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>IA em sentido estrito</t>
         </is>
       </c>
       <c r="M34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" t="b">
         <v>0</v>
@@ -5157,45 +5157,45 @@
         <v>0</v>
       </c>
       <c r="Q34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>RODRIGO SANTAELLA GONCALVES</t>
+          <t>TOMAZ OLIVEIRA PAOLIELLO</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>PLANEJAMENTO E POLITICAS PÚBLICAS</t>
+          <t>GOVERNANÇA GLOBAL E FORMULAÇÃO DE POLÍTICAS INTERNACIONAIS</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DO CEARÁ</t>
+          <t>PONTIFÍCIA UNIVERSIDADE CATÓLICA DE SÃO PAULO</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>UECE</t>
+          <t>PUC/SP</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>NORDESTE</t>
+          <t>SUDESTE</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>CEARÁ</t>
+          <t>SÃO PAULO</t>
         </is>
       </c>
       <c r="Y34" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>POLÍTICAS PÚBLICAS</t>
+          <t>POLÍTICA INTERNACIONAL</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5214,16 +5214,16 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11550911</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13677308</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>11550911</t>
+          <t>13677308</t>
         </is>
       </c>
       <c r="AE34" t="n">
-        <v>2353082</v>
+        <v>3561400</v>
       </c>
     </row>
     <row r="35">
@@ -5242,82 +5242,82 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
+          <t>2022-07-09</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CAUE BETTINI PAES LEME</t>
+          <t>ELISA FRIAS VILLELA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>LEGISLAÇÕES E MAPEAMENTO DE ACESSIBILIDADE NA CIDADE DE SÃO PAULO POR MEIO DE APLICATIVOS DIGITAIS E PLATAFORMAS COLABORATIVAS</t>
+          <t>EMBARCAÇÕES AUTÔNOMAS DE SURPERFÍCIES E A SEGURANÇA DO TRAFEGO AQUAVIÁRIO EM ÁGUAS SOB JURISDIÇÃO NACIONAL BRASILEIRA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ESTE POLICY PAPER TEM COMO OBJETIVO SUGERIR A IMPLEMENTAÇÃO DE MECANISMOS DE COLETA DE DADOS SOBRE CONDIÇÕES DE ACESSIBILIDADE DE CALÇADAS E PASSEIOS PÚBLICOS NA CIDADE DE SÃO PAULO. TOMANDO COMO MODELO A EXPERIÊNCIA DO PROJECT SIDEWALK, JÁ ATIVO EM CIDADES DOS EUA E MÉXICO, ESPERAMOS QUE ESSA INICIATIVA POSSA SER REPRODUZIDA EM SÃO PAULO E CONTE COM PARTICIPAÇÃO POPULAR VOLUNTÁRIA E INTELIGÊNCIA ARTIFICIAL PARA COLETAR DADOS QUE POSSAM SER UTILIZADOS NA CRIAÇÃO DE POLÍTICAS PÚBLICAS, QUE MELHOREM AS CONDIÇÕES DAS CALÇADAS NAS CIDADES AO REDOR DO MUNDO, PRINCIPALMENTE EM SÃO PAULO.</t>
+          <t>ATUALMENTE ESTÁ EM DESENVOLVIMENTO UMA NOVA CATEGORIA DE NAVIOS MERCANTES, OS AUTÔNOMOS. TAIS NAVIOS POSSUEM DIVERSOS NIVÉIS DE AUTOMAÇÃO, QUE ORIGINAM INSEGURANÇAS EM RELAÇÃO Á SUA REGULAÇÃO E EM ESPECIAL AS NORMAS QUE PROMOVEM SEGURANÇA DE TRÁFEGO AQUAVIÁRIO. OS NAVIOS NÃO TRIPULADOS ALTERAM AS REGRAS RELATIVAS À SEGURANÇA DA NAVEGAÇÃO E AO PAPLE DO SER HUMANO NO SETOR DO TRANSPORTES MARÍTIMOS. ASSIM, DEVIDO ÀS CARCTERÍSTICAS MARÍTIMAS NACIONAIS TORNA-SE NECESSÁRIO QUE O BRASIL SE DEDIQUE AS NECESSIDADES DE ADEQUAÇÃO DA LEGISLAÇÃO NACIONAL EM RELAÇÃO ÁS OPERAÇÕES MASS NA AJB. O OBJETIVO CENTRAL DO TRABALHO É ABORDAR E ANALISAR ALGUMAS NORMAS REGULADORAS INTERNACIONAIS E AS NORMAS NACIONAIS RELATIVAS A SEGURANÇA DA NAVEGAÇÃO ILUSTRANDO A IMPORTÃNCIA DO CONHECIMENTO E A INCLUSÃO DOS NAVIOS AUTÔNOMOS NA REGULAÇÃO INTERNA. PROPÕE-SE ASSIM, APRESENTAR QUIAS ASPECTOS, DEVEM SER LEVADOS EM CONSIDERAÇÃO PELO LEGISLADOR BRASILEIRO AO PRETENDER REGULAR AS OPERAÇÕES MASS NA AJB.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>THIS POLICY PAPER AIMS TO SUGGEST THE IMPLEMENTATION OF DATA COLLECTION MECHANISMS ON ACCESSIBILITY CONDITIONS OF SIDEWALKS IN THE CITY OF SÃO PAULO. TAKING AS A MODEL THE EXPERIENCE OF PROJECT SIDEWALK, ALREADY ACTIVE IN CITIES IN THE U.S. AND MEXICO, WE HOPE THAT THIS INITIATIVE CAN BE REPRODUCED IN SÃO PAULO AND, WITH THE USE OF VOLUNTARY POPULAR PARTICIPATION AND ARTIFICIAL INTELLIGENCE, TO COLLECT DATA THAT CAN BE USED IN THE CREATION OF PUBLIC POLICIES THAT IMPROVE THE CONDITIONS OF SIDEWALKS IN CITIES AROUND THE WORLD, ESPECIALLY IN SÃO PAULO.</t>
+          <t>CURRENTLY A NEW CATEGORIE OF MERCHANT SHIPS IS UNDER DEVELOPEMENT, THE AUTONOMOUS. SUCH SHIPS HAVE SEVERAL LEVELS OF AUTOMATION, WITCH CAUSE INSECURITIES IN RELATION TO THEIR REGULATION AND IN PARTICULAR THE STANDARTS THAT PROMOTE THE SAFETY OF WATERWAY TRAFFIC. UNMANNED SHIPS CHANGE THE RULES ON THE SAFETY OF NAVIGATION AND THE ROLE OF MAN IN THE MARITIME TRANSPORT SECTOR. THUS, DUE TO NACIONAL MARITIME CHARACTERISTICS, ITSELF NECESSARY THAT BRAZIL DEDICADE ITSELF TO THE NEEDS OF ADAPTATION OF NATIONAL LEGISLATION IN RELATION TO MASS OPERATIONS IN AJB. THE MAIN OBJECTIVE OF THE WORK IS TO ADRESS AND ANALYZE SOME INTERNATIONAL REGULATORY STANDARTS AND NATIONAL STANDARTS ON NAVIGATION SAFETY ILLUSTRAING THE IMPORTANCE OF KNOWLEGED AND THE INCLUSION OF AUTONOMOUS SHIPS IN INTERNATIONAL REGULATION. THUS, IT IS PROPOSED TO PRESENT WHICH ASPECTS SHOULD BE TAKEN INTO ACCOUNT BY THE BRAZILIAN LEGISLATOR TO REGULATE MASS OPERATION IN AJB.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>DEFICIÊNCIA;CALÇADAS;ACESSIBILIDADE;POLÍTICA PÚBLICA.</t>
+          <t>SEGURANÇA DA NAVEGAÇÃO;OPERAÇÕES COM EMBARCAÇÃO AUTÔNOMAS;MASS;IMO;REGULAMENTAÇÃO INTERNACIONAL;REGULAMENTAÇÃO NACIONAL</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>DISABILITY;SIDEWALKS;ACCESSIBILITY;PUBLIC POLICY</t>
+          <t>SAFETY OF NAVIGATION;OPERATIONS WITH AUTONOMOUS VESSELS;MASS;IMO;INTERNATIONAL REGULATIONS;NATIONAL REGULATIONS.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>IA em sentido estrito</t>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M35" t="b">
+        <v>0</v>
+      </c>
+      <c r="N35" t="b">
+        <v>0</v>
+      </c>
+      <c r="O35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="b">
         <v>1</v>
       </c>
-      <c r="N35" t="b">
-        <v>0</v>
-      </c>
-      <c r="O35" t="b">
-        <v>0</v>
-      </c>
-      <c r="P35" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="b">
-        <v>0</v>
-      </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>TOMAZ OLIVEIRA PAOLIELLO</t>
+          <t>RAFAEL ZELESCO BARRETTO</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>GOVERNANÇA GLOBAL E FORMULAÇÃO DE POLÍTICAS INTERNACIONAIS</t>
+          <t>ESTUDOS MARÍTIMOS</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>PONTIFÍCIA UNIVERSIDADE CATÓLICA DE SÃO PAULO</t>
+          <t>ESCOLA DE GUERRA NAVAL</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>PUC/SP</t>
+          <t>EGN</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -5327,16 +5327,16 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>SÃO PAULO</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>POLÍTICA INTERNACIONAL</t>
+          <t>NÃO SE APLICA</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5355,16 +5355,16 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13677308</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12056351</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>13677308</t>
+          <t>12056351</t>
         </is>
       </c>
       <c r="AE35" t="n">
-        <v>3561400</v>
+        <v>3619382</v>
       </c>
     </row>
     <row r="36">
@@ -5383,51 +5383,51 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ELISA FRIAS VILLELA</t>
+          <t>LIVIA OHANA BEZERRA GOMES</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>EMBARCAÇÕES AUTÔNOMAS DE SURPERFÍCIES E A SEGURANÇA DO TRAFEGO AQUAVIÁRIO EM ÁGUAS SOB JURISDIÇÃO NACIONAL BRASILEIRA</t>
+          <t>OS IMPACTOS DO USO DE MECANISMOS DE INTELIGÊNCIA ARTIFICIAL E ROBOTIZAÇÃO PARA A GESTÃO DO ACERVO PROCESSUAL DO TRIBUNAL DE JUSTIÇA DO ESTADO DO CEARÁ.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ATUALMENTE ESTÁ EM DESENVOLVIMENTO UMA NOVA CATEGORIA DE NAVIOS MERCANTES, OS AUTÔNOMOS. TAIS NAVIOS POSSUEM DIVERSOS NIVÉIS DE AUTOMAÇÃO, QUE ORIGINAM INSEGURANÇAS EM RELAÇÃO Á SUA REGULAÇÃO E EM ESPECIAL AS NORMAS QUE PROMOVEM SEGURANÇA DE TRÁFEGO AQUAVIÁRIO. OS NAVIOS NÃO TRIPULADOS ALTERAM AS REGRAS RELATIVAS À SEGURANÇA DA NAVEGAÇÃO E AO PAPLE DO SER HUMANO NO SETOR DO TRANSPORTES MARÍTIMOS. ASSIM, DEVIDO ÀS CARCTERÍSTICAS MARÍTIMAS NACIONAIS TORNA-SE NECESSÁRIO QUE O BRASIL SE DEDIQUE AS NECESSIDADES DE ADEQUAÇÃO DA LEGISLAÇÃO NACIONAL EM RELAÇÃO ÁS OPERAÇÕES MASS NA AJB. O OBJETIVO CENTRAL DO TRABALHO É ABORDAR E ANALISAR ALGUMAS NORMAS REGULADORAS INTERNACIONAIS E AS NORMAS NACIONAIS RELATIVAS A SEGURANÇA DA NAVEGAÇÃO ILUSTRANDO A IMPORTÃNCIA DO CONHECIMENTO E A INCLUSÃO DOS NAVIOS AUTÔNOMOS NA REGULAÇÃO INTERNA. PROPÕE-SE ASSIM, APRESENTAR QUIAS ASPECTOS, DEVEM SER LEVADOS EM CONSIDERAÇÃO PELO LEGISLADOR BRASILEIRO AO PRETENDER REGULAR AS OPERAÇÕES MASS NA AJB.</t>
+          <t>O AUMENTO DEMOGRÁFICO, A PRODUÇÃO E CONSUMO EM MASSA E O AVANÇO TECNOLÓGICO, QUE FACILITOU O ACESSO À INFORMAÇÃO E A CRIAÇÃO DE SOFTWARES QUE VIABILIZAM O AJUIZAMENTO MASSIVO DE AÇÕES NOS ESCRITÓRIOS DE ADVOCATÍCIA, SÃO FATORES QUE, SOMADOS, CONTRIBUEM PARA O ACÚMULO DE PROCESSOS NAS UNIDADES JURISDICIONAIS E PARA O ATRASO DA ENTREGA DA PRESTAÇÃO JURISDICIONAL. É CERTO QUE A MOROSIDADE JUDICIAL GERA INSEGURANÇA JURÍDICA, DESCRENÇA NAS INSTITUIÇÕES DE JUSTIÇA E AFASTA INVESTIDORES, DE MODO QUE A INOBSERVÂNCIA DO DIREITO CONSTITUCIONALMENTE ASSEGURADO À DURAÇÃO RAZOÁVEL DO PROCESSO PROMOVE REPERCUSSÕES SUBSTANCIAIS NAS SEARAS SOCIAIS E ECONÔMICAS. A FIM DE DEBELAR ESSA PROBLEMÁTICA, BUSCA-SE, NO PRESENTE TRABALHO, INVESTIGAR OS IMPACTOS DA UTILIZAÇÃO DE MECANISMOS DE INTELIGÊNCIA ARTIFICIAL E ROBOTIZAÇÃO PARA A GESTÃO DO ACERVO PROCESSUAL DO TRIBUNAL DE JUSTIÇA DO ESTADO DO CEARÁ – TJ-CE, NO QUE TANGE À PRODUTIVIDADE E CELERIDADE NA TRAMITAÇÃO DOS PROCESSOS EM CURSO NA REFERIDA CORTE. PARA ISSO, EMPREENDEU-SE PESQUISA DE CARÁTER QUALITATIVO, RECORRENDO-SE À CONSULTA A LIVROS, ARTIGOS CIENTÍFICOS E NOTÍCIAS VEICULADAS NO SÍTIO ELETRÔNICO DA INSTITUIÇÃO EM APREÇO, BEM COMO A ENTREVISTAS COM OS ATORES SOCIAIS ENVOLVIDOS COM A UTILIZAÇÃO DESSES RECURSOS NO ÂMBITO DO TJ-CE, PARA, AO FINAL, CONCLUIR PELA AVALIAÇÃO POSITIVA DO USO DESSAS TECNOLOGIAS PARA O INCREMENTO DA PRODUTIVIDADE, CELERIDADE PROCESSUAL E, AINDA, DA QUALIDADE DE VIDA DO SERVIDOR PÚBLICO.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>CURRENTLY A NEW CATEGORIE OF MERCHANT SHIPS IS UNDER DEVELOPEMENT, THE AUTONOMOUS. SUCH SHIPS HAVE SEVERAL LEVELS OF AUTOMATION, WITCH CAUSE INSECURITIES IN RELATION TO THEIR REGULATION AND IN PARTICULAR THE STANDARTS THAT PROMOTE THE SAFETY OF WATERWAY TRAFFIC. UNMANNED SHIPS CHANGE THE RULES ON THE SAFETY OF NAVIGATION AND THE ROLE OF MAN IN THE MARITIME TRANSPORT SECTOR. THUS, DUE TO NACIONAL MARITIME CHARACTERISTICS, ITSELF NECESSARY THAT BRAZIL DEDICADE ITSELF TO THE NEEDS OF ADAPTATION OF NATIONAL LEGISLATION IN RELATION TO MASS OPERATIONS IN AJB. THE MAIN OBJECTIVE OF THE WORK IS TO ADRESS AND ANALYZE SOME INTERNATIONAL REGULATORY STANDARTS AND NATIONAL STANDARTS ON NAVIGATION SAFETY ILLUSTRAING THE IMPORTANCE OF KNOWLEGED AND THE INCLUSION OF AUTONOMOUS SHIPS IN INTERNATIONAL REGULATION. THUS, IT IS PROPOSED TO PRESENT WHICH ASPECTS SHOULD BE TAKEN INTO ACCOUNT BY THE BRAZILIAN LEGISLATOR TO REGULATE MASS OPERATION IN AJB.</t>
+          <t>THE DEMOGRAPHIC INCREASE, PRODUCTION, CONSUMPTION AND THE TECHNOLOGICAL ADVANCE, WHICH FACILITATED THE ACCESS TO INFORMATION AND THE CREATION OF SOFTWARE THAT MAKES POSSIBLE THE MASSIVE FILING OF ACTIONS IN LAW OFFICES, ARE FACTORS THAT, WHEN ADDED, CONTRIBUTE TO THE ACCUMULATION OF PROCESSES IN THE JURISDICTIONAL UNITS AND FOR THE DELAY IN THE DISPATCH OF THE JURISDICTIONAL PROVISION. IT IS TRUE THAT JUDICIAL DELAYS GENERATE LEGAL UNCERTAINTY, DISBELIEF IN JUSTICE INSTITUTIONS AND ALIENATE INVESTORS, SO THAT FAILURE TO OBSERVE THE CONSTITUTIONAL RIGHTS IN RELATION TO A REASONABLE DURATION OF PROCEEDINGS HAS SUBSTANTIAL REPERCUSSIONS IN SOCIAL AND ECONOMIC AREAS. IN ORDER TO OVERCOME THIS PROBLEM, THE CURRENT WORK SEEKS TO INVESTIGATE THE IMPACTS OF THE USE OF ARTIFICIAL INTELLIGENCE AND ROBOT MECHANISMS FOR THE MANAGEMENT OF THE PROCEDURAL COLLECTION OF THE COURT OF JUSTICE OF THE STATE OF CEARÁ - TJ-CE, WITH REGARD TO THE PRODUCTIVITY AND SPEED IN THE PROCESSING OF ONGOING PROCESSES IN SAID COURT. FOR THIS, A QUALITATIVE RESEARCH WAS CARRIED OUT, RESORTING TO CONSULTING BOOKS, SCIENTIFIC ARTICLES AND NEWS PUBLISHED ON THE WEBSITE OF THE INSTITUTION IN QUESTION, AS WELL AS INTERVIEWS WITH THE SOCIAL ACTORS INVOLVED WITH THE USE OF THESE RESOURCES WITHIN THE SCOPE OF THE TJ -CE, TO, IN THE END, CONCLUDE BY THE POSITIVE EVALUATION OF THE USE OF THESE TECHNOLOGIES TO INCREASE PRODUCTIVITY, PROCEDURAL SPEED AND, ALSO, THE QUALITY OF LIFE OF PUBLIC SERVANTS.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SEGURANÇA DA NAVEGAÇÃO;OPERAÇÕES COM EMBARCAÇÃO AUTÔNOMAS;MASS;IMO;REGULAMENTAÇÃO INTERNACIONAL;REGULAMENTAÇÃO NACIONAL</t>
+          <t>INTELIGÊNCIA ARTIFICIAL;ROBOTIZAÇÃO;POLÍTICAS PÚBLICAS;PODER JUDICIÁRIO;CELERIDADE PROCESSUAL</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>SAFETY OF NAVIGATION;OPERATIONS WITH AUTONOMOUS VESSELS;MASS;IMO;INTERNATIONAL REGULATIONS;NATIONAL REGULATIONS.</t>
+          <t>ARTIFICIAL INTELLIGENCE;ROBOTIZATION;PUBLIC POLICY;JUDICIAL POWER;PROCEDURAL SPEED</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Correlato</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>IA em sentido estrito</t>
         </is>
       </c>
       <c r="M36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="b">
         <v>0</v>
@@ -5439,45 +5439,45 @@
         <v>0</v>
       </c>
       <c r="Q36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>RAFAEL ZELESCO BARRETTO</t>
+          <t>RODRIGO SANTAELLA GONCALVES</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>ESTUDOS MARÍTIMOS</t>
+          <t>PLANEJAMENTO E POLITICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>ESCOLA DE GUERRA NAVAL</t>
+          <t>UNIVERSIDADE ESTADUAL DO CEARÁ</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>EGN</t>
+          <t>UECE</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>SUDESTE</t>
+          <t>NORDESTE</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>CEARÁ</t>
         </is>
       </c>
       <c r="Y36" t="n">
-        <v>104</v>
+        <v>188</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5496,16 +5496,16 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12056351</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13636640</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>12056351</t>
+          <t>13636640</t>
         </is>
       </c>
       <c r="AE36" t="n">
-        <v>3619382</v>
+        <v>3673283</v>
       </c>
     </row>
     <row r="37">
@@ -5520,105 +5520,105 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LIVIA OHANA BEZERRA GOMES</t>
+          <t>ANDERSON MATOS DE CASTRO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>OS IMPACTOS DO USO DE MECANISMOS DE INTELIGÊNCIA ARTIFICIAL E ROBOTIZAÇÃO PARA A GESTÃO DO ACERVO PROCESSUAL DO TRIBUNAL DE JUSTIÇA DO ESTADO DO CEARÁ.</t>
+          <t>MODELO DE TREINAMENTO PARA MITIGAÇÃO DA CONFUSÃO ENTRE MODOS DE CONTROLE DE TRAÇÃO PARA PILOTOS EM TRANSIÇÃO DE AERONAVES</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>O AUMENTO DEMOGRÁFICO, A PRODUÇÃO E CONSUMO EM MASSA E O AVANÇO TECNOLÓGICO, QUE FACILITOU O ACESSO À INFORMAÇÃO E A CRIAÇÃO DE SOFTWARES QUE VIABILIZAM O AJUIZAMENTO MASSIVO DE AÇÕES NOS ESCRITÓRIOS DE ADVOCATÍCIA, SÃO FATORES QUE, SOMADOS, CONTRIBUEM PARA O ACÚMULO DE PROCESSOS NAS UNIDADES JURISDICIONAIS E PARA O ATRASO DA ENTREGA DA PRESTAÇÃO JURISDICIONAL. É CERTO QUE A MOROSIDADE JUDICIAL GERA INSEGURANÇA JURÍDICA, DESCRENÇA NAS INSTITUIÇÕES DE JUSTIÇA E AFASTA INVESTIDORES, DE MODO QUE A INOBSERVÂNCIA DO DIREITO CONSTITUCIONALMENTE ASSEGURADO À DURAÇÃO RAZOÁVEL DO PROCESSO PROMOVE REPERCUSSÕES SUBSTANCIAIS NAS SEARAS SOCIAIS E ECONÔMICAS. A FIM DE DEBELAR ESSA PROBLEMÁTICA, BUSCA-SE, NO PRESENTE TRABALHO, INVESTIGAR OS IMPACTOS DA UTILIZAÇÃO DE MECANISMOS DE INTELIGÊNCIA ARTIFICIAL E ROBOTIZAÇÃO PARA A GESTÃO DO ACERVO PROCESSUAL DO TRIBUNAL DE JUSTIÇA DO ESTADO DO CEARÁ – TJ-CE, NO QUE TANGE À PRODUTIVIDADE E CELERIDADE NA TRAMITAÇÃO DOS PROCESSOS EM CURSO NA REFERIDA CORTE. PARA ISSO, EMPREENDEU-SE PESQUISA DE CARÁTER QUALITATIVO, RECORRENDO-SE À CONSULTA A LIVROS, ARTIGOS CIENTÍFICOS E NOTÍCIAS VEICULADAS NO SÍTIO ELETRÔNICO DA INSTITUIÇÃO EM APREÇO, BEM COMO A ENTREVISTAS COM OS ATORES SOCIAIS ENVOLVIDOS COM A UTILIZAÇÃO DESSES RECURSOS NO ÂMBITO DO TJ-CE, PARA, AO FINAL, CONCLUIR PELA AVALIAÇÃO POSITIVA DO USO DESSAS TECNOLOGIAS PARA O INCREMENTO DA PRODUTIVIDADE, CELERIDADE PROCESSUAL E, AINDA, DA QUALIDADE DE VIDA DO SERVIDOR PÚBLICO.</t>
+          <t>O DESENVOLVIMENTO DOS PRIMEIROS PILOTOS AUTOMÁTICOS NA DÉCADA DE 1930 PODE SER CONSIDERADO O PRIMEIRO PASSO DE AUTOMAÇÃO EM AVIÕES. DIVERSOS SETORES DA INDÚSTRIA EXPERIMENTARAM CONSIDERÁVEIS TRANSFORMAÇÕES, ESPECIALMENTE O SETOR DE TRANSPORTE AÉREO COMERCIAL POR MEIO DE TECNOLOGIA QUE AUTOMATIZA PROCEDIMENTOS NO COCKPIT. EMBORA A AUTOMAÇÃO TENHA TRAZIDO CONSIDERÁVEIS BENEFÍCIOS ÀS OPERAÇÕES E PARA O CONTROLE DE SISTEMAS DE INTERAÇÃO HOMEM-MÁQUINA, EXISTE UMA CRESCENTE EVIDÊNCIA EMPÍRICA APONTANDO PARA ALGUNS EFEITOS NEGATIVOS, ESPECIALMENTE EM RELAÇÃO AO DESEMPENHO DO MONITORAMENTO HUMANO. EM FUNÇÃO DO EXPOSTO, A PRESENTE PESQUISA BUSCA RESPONDER A SEGUINTE PERGUNTA: COMO MITIGAR A CONFUSÃO DE MODOS DE CONTROLE DE TRAÇÃO A QUE PILOTOS DE LINHA AÉREA ESTÃO SUJEITOS AO MIGRAREM PARA UMA NOVA AERONAVE? ESTA DISSERTAÇÃO TEM COMO OBJETIVO PROPOR UM MODELO DE TREINAMENTO PARA PILOTOS EM TRANSIÇÃO DE AERONAVES COMERCIAIS, DE MODO QUE SEJA POSSÍVEL MITIGAR OS EFEITOS ADVERSOS DA AUTOMAÇÃO. PARA TANTO, ESTE TRABALHO APLICOU UM QUESTIONÁRIO SEMIESTRUTURADO, UTILIZADO PARA IDENTIFICAR ERROS COMUNS PARA CADA TIPO DE TRANSIÇÃO. COMO RESULTADOS, OBTEVE-SE AS SEGUINTES RESPOSTAS MAIS PRESENTES AS SITUAÇÕES PASSÍVEIS DE GERAR CONFUSÃO, NESSA ORDEM: “INTERPRETAÇÃO DOS MODOS APRESENTADOS NO FMA DA AERONAVE”, “GERENCIAMENTO DA NAVEGAÇÃO VERTICAL”, “SEQUÊNCIA DE AÇÕES DURANTE A ARREMETIDA”, “PRIORIZAÇÃO DE PERFIL DE DESCIDA X PRIORIZAÇÃO DE MANUTENÇÃO DE VELOCIDADE” E “POSICIONAMENTO INCORRETO DAS MANETES DE TRAÇÃO NA ARREMETIDA”. PARA AS RECOMENDAÇÕES DOS PILOTOS COM A FINALIDADE DE MITIGAR AS CIRCUNSTÂNCIAS DE CONFUSÃO, IDENTIFICOU-SE: “MAIS HORAS DE TREINAMENTO EM SIMULADOR” E “MAIS HORAS DE TREINAMENTO TEÓRICO”. A PARTIR DOS RESULTADOS, UM MODELO CONCEITUAL FOI DESENVOLVIDO A FIM DE ADICIONAR ELEMENTOS IMPORTANTES AO TREINAMENTO, TAIS COMO: AVALIAÇÃO DO BACKGROUND DOS PILOTOS, GUIA DE ERROS COMUNS E MAPA DE COMPETÊNCIAS DA ESTRUTURA ATUAL DO PROGRAMA DE TREINAMENTO – PROPOSTA DE PRODUTO DESTA DISSERTAÇÃO. AS INFORMAÇÕES OBTIDAS NESSA PESQUISA PODEM SER UTILIZADAS POR COMPANHIAS AÉREAS PARA A IDENTIFICAÇÃO DE SITUAÇÕES CAUSADORES DE CONFUSÕES DE MODO E APLICAÇÃO DE MEDIDAS MITIGADORAS DOS EFEITOS ADVERSOS DA AUTOMAÇÃO.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>THE DEMOGRAPHIC INCREASE, PRODUCTION, CONSUMPTION AND THE TECHNOLOGICAL ADVANCE, WHICH FACILITATED THE ACCESS TO INFORMATION AND THE CREATION OF SOFTWARE THAT MAKES POSSIBLE THE MASSIVE FILING OF ACTIONS IN LAW OFFICES, ARE FACTORS THAT, WHEN ADDED, CONTRIBUTE TO THE ACCUMULATION OF PROCESSES IN THE JURISDICTIONAL UNITS AND FOR THE DELAY IN THE DISPATCH OF THE JURISDICTIONAL PROVISION. IT IS TRUE THAT JUDICIAL DELAYS GENERATE LEGAL UNCERTAINTY, DISBELIEF IN JUSTICE INSTITUTIONS AND ALIENATE INVESTORS, SO THAT FAILURE TO OBSERVE THE CONSTITUTIONAL RIGHTS IN RELATION TO A REASONABLE DURATION OF PROCEEDINGS HAS SUBSTANTIAL REPERCUSSIONS IN SOCIAL AND ECONOMIC AREAS. IN ORDER TO OVERCOME THIS PROBLEM, THE CURRENT WORK SEEKS TO INVESTIGATE THE IMPACTS OF THE USE OF ARTIFICIAL INTELLIGENCE AND ROBOT MECHANISMS FOR THE MANAGEMENT OF THE PROCEDURAL COLLECTION OF THE COURT OF JUSTICE OF THE STATE OF CEARÁ - TJ-CE, WITH REGARD TO THE PRODUCTIVITY AND SPEED IN THE PROCESSING OF ONGOING PROCESSES IN SAID COURT. FOR THIS, A QUALITATIVE RESEARCH WAS CARRIED OUT, RESORTING TO CONSULTING BOOKS, SCIENTIFIC ARTICLES AND NEWS PUBLISHED ON THE WEBSITE OF THE INSTITUTION IN QUESTION, AS WELL AS INTERVIEWS WITH THE SOCIAL ACTORS INVOLVED WITH THE USE OF THESE RESOURCES WITHIN THE SCOPE OF THE TJ -CE, TO, IN THE END, CONCLUDE BY THE POSITIVE EVALUATION OF THE USE OF THESE TECHNOLOGIES TO INCREASE PRODUCTIVITY, PROCEDURAL SPEED AND, ALSO, THE QUALITY OF LIFE OF PUBLIC SERVANTS.</t>
+          <t>THE DEVELOPMENT OF THE FIRST AUTOPILOTS IN THE 1930S CAN BE CONSIDERED THE INITIAL STEP IN AIRCRAFT AUTOMATION. VARIOUS INDUSTRY SECTORS UNDERWENT SIGNIFICANT TRANSFORMATIONS, ESPECIALLY THE COMMERCIAL AVIATION SECTOR THROUGH TECHNOLOGY THAT AUTOMATES PROCEDURES IN THE COCKPIT. WHILE AUTOMATION HAS BROUGHT CONSIDERABLE BENEFITS TO OPERATIONS AND THE CONTROL OF HUMAN-MACHINE INTERACTION SYSTEMS, THERE IS GROWING EMPIRICAL EVIDENCE POINTING TO SOME NEGATIVE EFFECTS, ESPECIALLY CONCERNING HUMAN MONITORING PERFORMANCE. IN LIGHT OF THIS, THE PRESENT RESEARCH SEEKS TO ANSWER THE FOLLOWING QUESTION: HOW TO MITIGATE THE CONFUSION OF ENGINE THRUST MODES TO WHICH AIRLINE PILOTS ARE SUBJECTED WHEN TRANSITIONING TO A NEW AIRCRAFT? THIS DISSERTATION AIMS TO PROPOSE A TRAINING MODEL FOR PILOTS TRANSITIONING BETWEEN COMMERCIAL AIRCRAFT, ALLOWING FOR THE MITIGATION OF ADVERSE EFFECTS OF AUTOMATION. TO ACHIEVE THIS, THIS WORK APPLIED A SEMI-STRUCTURED QUESTIONNAIRE, USED TO IDENTIFY COMMON ERRORS FOR EACH TYPE OF TRANSITION. THE MOST PREVALENT RESPONSES TO SITUATIONS PRONE TO CONFUSION WERE OBTAINED IN THE FOLLOWING ORDER: "INTERPRETATION OF MODES PRESENTED IN THE AIRCRAFT'S FMA (FLIGHT MODE ANNUNCIATOR)," "MANAGEMENT OF VERTICAL NAVIGATION," "SEQUENCE OF ACTIONS DURING A GO-AROUND," "DESCENT PROFILE PRIORITIZATION VS. SPEED MAINTENANCE PRIORITIZATION," AND "INCORRECT POSITIONING OF THRUST LEVERS DURING A GO-AROUND." FOR PILOT RECOMMENDATIONS TO MITIGATE CONFUSING CIRCUMSTANCES, THE FOLLOWING WERE IDENTIFIED: "MORE SIMULATOR TRAINING HOURS" AND "MORE THEORETICAL TRAINING HOURS." BASED ON THE RESULTS, A CONCEPTUAL MODEL WAS DEVELOPED TO ADD IMPORTANT ELEMENTS TO TRAINING, SUCH AS: PILOT BACKGROUND ASSESSMENT, COMMON ERRORS GUIDE, AND COMPETENCY MAP OF THE CURRENT TRAINING PROGRAM STRUCTURE—A PROPOSED PRODUCT OF THIS DISSERTATION. THE INFORMATION OBTAINED IN THIS RESEARCH CAN BE USED BY AIRLINES TO IDENTIFY SITUATIONS CAUSING MODE CONFUSION AND IMPLEMENT MEASURES TO MITIGATE THE ADVERSE EFFECTS OF AUTOMATION.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>INTELIGÊNCIA ARTIFICIAL;ROBOTIZAÇÃO;POLÍTICAS PÚBLICAS;PODER JUDICIÁRIO;CELERIDADE PROCESSUAL</t>
+          <t>TREINAMENTO DO PILOTO;AUTOMAÇÃO;FATORES HUMANOS;PILOTO AUTOMÁTICO;PROGRAMAS DE TREINAMENTO;SEGURANÇA DO VOO;SIMULADORES DE VOO;MONITORAMENTO;ENGENHARIA DE AERONÁUTICA.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>ARTIFICIAL INTELLIGENCE;ROBOTIZATION;PUBLIC POLICY;JUDICIAL POWER;PROCEDURAL SPEED</t>
+          <t>TREINAMENTO DO PILOTO;AUTOMAÇÃO;FATORES HUMANOS;PILOTO AUTOMÁTICO;PROGRAMAS DE TREINAMENTO;SEGURANÇA DO VOO;SIMULADORES DE VOO;MONITORAMENTO;ENGENHARIA DE AERONÁUTICA.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>IA em sentido estrito</t>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M37" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37" t="b">
+        <v>0</v>
+      </c>
+      <c r="O37" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="b">
         <v>1</v>
       </c>
-      <c r="N37" t="b">
-        <v>0</v>
-      </c>
-      <c r="O37" t="b">
-        <v>0</v>
-      </c>
-      <c r="P37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="b">
-        <v>0</v>
-      </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>RODRIGO SANTAELLA GONCALVES</t>
+          <t>MICHELLE CARVALHO GALVAO DA SILVA PINTO BANDEIRA</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>PLANEJAMENTO E POLITICAS PÚBLICAS</t>
+          <t>SEGURANÇA DE AVIAÇÃO E AERONAVEGABILIDADE CONTINUADA</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DO CEARÁ</t>
+          <t>INSTITUTO TECNOLÓGICO DE AERONÁUTICA</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>UECE</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>NORDESTE</t>
+          <t>SUDESTE</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>CEARÁ</t>
+          <t>SÃO PAULO</t>
         </is>
       </c>
       <c r="Y37" t="n">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>POLÍTICAS PÚBLICAS</t>
+          <t>NÃO SE APLICA</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5637,16 +5637,16 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13636640</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14474457</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>13636640</t>
+          <t>14474457</t>
         </is>
       </c>
       <c r="AE37" t="n">
-        <v>3673283</v>
+        <v>4007674</v>
       </c>
     </row>
     <row r="38">
@@ -5665,37 +5665,37 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ANDERSON MATOS DE CASTRO</t>
+          <t>FABIANO VARGAS FREITAS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MODELO DE TREINAMENTO PARA MITIGAÇÃO DA CONFUSÃO ENTRE MODOS DE CONTROLE DE TRAÇÃO PARA PILOTOS EM TRANSIÇÃO DE AERONAVES</t>
+          <t>PROPOSTA DE PLANO ESTRATÉGICO DE IMPLEMENTAÇÃO DE PROGRAMA DE TREINAMENTO DE PILOTOS EM ÂMBITO NACIONAL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>O DESENVOLVIMENTO DOS PRIMEIROS PILOTOS AUTOMÁTICOS NA DÉCADA DE 1930 PODE SER CONSIDERADO O PRIMEIRO PASSO DE AUTOMAÇÃO EM AVIÕES. DIVERSOS SETORES DA INDÚSTRIA EXPERIMENTARAM CONSIDERÁVEIS TRANSFORMAÇÕES, ESPECIALMENTE O SETOR DE TRANSPORTE AÉREO COMERCIAL POR MEIO DE TECNOLOGIA QUE AUTOMATIZA PROCEDIMENTOS NO COCKPIT. EMBORA A AUTOMAÇÃO TENHA TRAZIDO CONSIDERÁVEIS BENEFÍCIOS ÀS OPERAÇÕES E PARA O CONTROLE DE SISTEMAS DE INTERAÇÃO HOMEM-MÁQUINA, EXISTE UMA CRESCENTE EVIDÊNCIA EMPÍRICA APONTANDO PARA ALGUNS EFEITOS NEGATIVOS, ESPECIALMENTE EM RELAÇÃO AO DESEMPENHO DO MONITORAMENTO HUMANO. EM FUNÇÃO DO EXPOSTO, A PRESENTE PESQUISA BUSCA RESPONDER A SEGUINTE PERGUNTA: COMO MITIGAR A CONFUSÃO DE MODOS DE CONTROLE DE TRAÇÃO A QUE PILOTOS DE LINHA AÉREA ESTÃO SUJEITOS AO MIGRAREM PARA UMA NOVA AERONAVE? ESTA DISSERTAÇÃO TEM COMO OBJETIVO PROPOR UM MODELO DE TREINAMENTO PARA PILOTOS EM TRANSIÇÃO DE AERONAVES COMERCIAIS, DE MODO QUE SEJA POSSÍVEL MITIGAR OS EFEITOS ADVERSOS DA AUTOMAÇÃO. PARA TANTO, ESTE TRABALHO APLICOU UM QUESTIONÁRIO SEMIESTRUTURADO, UTILIZADO PARA IDENTIFICAR ERROS COMUNS PARA CADA TIPO DE TRANSIÇÃO. COMO RESULTADOS, OBTEVE-SE AS SEGUINTES RESPOSTAS MAIS PRESENTES AS SITUAÇÕES PASSÍVEIS DE GERAR CONFUSÃO, NESSA ORDEM: “INTERPRETAÇÃO DOS MODOS APRESENTADOS NO FMA DA AERONAVE”, “GERENCIAMENTO DA NAVEGAÇÃO VERTICAL”, “SEQUÊNCIA DE AÇÕES DURANTE A ARREMETIDA”, “PRIORIZAÇÃO DE PERFIL DE DESCIDA X PRIORIZAÇÃO DE MANUTENÇÃO DE VELOCIDADE” E “POSICIONAMENTO INCORRETO DAS MANETES DE TRAÇÃO NA ARREMETIDA”. PARA AS RECOMENDAÇÕES DOS PILOTOS COM A FINALIDADE DE MITIGAR AS CIRCUNSTÂNCIAS DE CONFUSÃO, IDENTIFICOU-SE: “MAIS HORAS DE TREINAMENTO EM SIMULADOR” E “MAIS HORAS DE TREINAMENTO TEÓRICO”. A PARTIR DOS RESULTADOS, UM MODELO CONCEITUAL FOI DESENVOLVIDO A FIM DE ADICIONAR ELEMENTOS IMPORTANTES AO TREINAMENTO, TAIS COMO: AVALIAÇÃO DO BACKGROUND DOS PILOTOS, GUIA DE ERROS COMUNS E MAPA DE COMPETÊNCIAS DA ESTRUTURA ATUAL DO PROGRAMA DE TREINAMENTO – PROPOSTA DE PRODUTO DESTA DISSERTAÇÃO. AS INFORMAÇÕES OBTIDAS NESSA PESQUISA PODEM SER UTILIZADAS POR COMPANHIAS AÉREAS PARA A IDENTIFICAÇÃO DE SITUAÇÕES CAUSADORES DE CONFUSÕES DE MODO E APLICAÇÃO DE MEDIDAS MITIGADORAS DOS EFEITOS ADVERSOS DA AUTOMAÇÃO.</t>
+          <t>OS TREINAMENTOS TRADICIONAIS DE PILOTOS, FUNDAMENTADOS NO INCREMENTO DE PRÁTICAS BASEADAS EM REPETIÇÃO DE MANOBRAS, PERMANECERAM INALTERADOS DESDE O ADVENTO DOS SIMULADORES DE VOO, COM A CRENÇA DE QUE “ONE SIZE FITS ALL”. DURANTE O MESMO PERÍODO, AVANÇOS TECNOLÓGICOS NO PROJETO DE AERONAVES, INCLUINDO O DESENVOLVIMENTO EM AUTOMAÇÃO, SISTEMA DE INTEGRAÇÃO, CONFIABILIDADE E MUDANÇAS NO AMBIENTE OPERACIONAL, CONTRIBUÍRAM PARA MELHORIA CONTÍNUA DA SEGURANÇA NA AVIAÇÃO, MAS TAMBÉM REVELARAM NOVOS DESAFIOS. DIANTE DISSO, TORNA-SE NECESSÁRIA A ADOÇÃO DE MÉTODOS ADEQUADOS PARA A MUDANÇA DE PADRÃO NO TREINAMENTO DE PILOTOS, PARTINDO DA ABORDAGEM DE “TICK BOX” PARA AS BOAS PRÁTICAS ADOTADAS PELA INDÚSTRIA AERONÁUTICA. ESSA ABORDAGEM PODE CONTRIBUIR PARA MELHORIA DO DESEMPENHO DOS PILOTOS NAS OPERAÇÕES AÉREAS, POR MEIO DE UM PROGRAMA DE TREINAMENTO MAIS EFICIENTE E FLEXÍVEL. NESSE SENTIDO, O OBJETIVO DESTE TRABALHO É PROPOR UM PLANO PARA IMPLEMENTAÇÃO DE PROGRAMA DE TREINAMENTO DE PILOTOS NO ÂMBITO NACIONAL, VISANDO ATENDER AOS REQUISITOS DE CERTIFICAÇÃO, AO MESMO TEMPO QUE SEJA VIÁVEL PARA OS OPERADORES AÉREOS E PARA OS CENTROS DE TREINAMENTO DE AVIAÇÃO CIVIL. UMA DAS AFIRMAÇÕES MAIS COERENTES ENCONTRADAS NESSE ESTUDO FOI: “TRAIN THE WAY YOU OPERATE AND OPERATE THE WAY YOU TRAIN”. A PRESENTE PESQUISA CARACTERIZA-SE COMO DESCRITIVA E COMPARATIVA, COMPLEMENTADA POR EXPLORATÓRIA COM PROCEDIMENTO BIBLIOGRÁFICO E DOCUMENTAL, A PARTIR DO ESTUDO DAS NORMAS NACIONAIS E INTERNACIONAIS NO ÂMBITO DA AVIAÇÃO CIVIL, ABORDANDO AS METODOLOGIAS DE TREINAMENTO A SEGUIR: ADVANCED QUALIFICATION PROGRAM (AQP), ALTERNATIVE TRAINING AND QUALIFICATION PROGRAMME (ATQP), EVIDENCE-BASED TRAINING (EBT) E COMPETENCY-BASED TRAINING AND ASSESSMENT (CBTA). A PARTIR DAS PRINCIPAIS CARACTERÍSTICAS DAS METODOLOGIAS ABORDADAS, DESENVOLVEU-SE UM QUESTIONÁRIO COM A ESCALA DE LIKERT, RESPONDIDO POR MEIO DE ENTREVISTAS ESTRUTURADAS E ABERTAS PELO COMITÊ AVALIATIVO. FOI UTILIZADA A ANÁLISE SWOT (STRENGTHS, WEAKNESSES, OPPORTUNITIES AND THREATS) PARA COMPILAR OS RESULTADOS DAS ENTREVISTAS, RESULTANDO NA PROPOSIÇÃO DE UM PLANO ESTRATÉGICO PARA IMPLEMENTAÇÃO DO PROGRAMA DE TREINAMENTO DE PILOTOS EM ÂMBITO NACIONAL. DESSA MANEIRA, APONTAM-SE OS ASPECTOS MAIS RELEVANTES DE CADA METODOLOGIA DE TREINAMENTO, ADOTANDO UMA ABORDAGEM MAIS MODERNA E EFICIENTE, VISANDO AO AUMENTO DO NÍVEL DE SEGURANÇA OPERACIONAL.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>THE DEVELOPMENT OF THE FIRST AUTOPILOTS IN THE 1930S CAN BE CONSIDERED THE INITIAL STEP IN AIRCRAFT AUTOMATION. VARIOUS INDUSTRY SECTORS UNDERWENT SIGNIFICANT TRANSFORMATIONS, ESPECIALLY THE COMMERCIAL AVIATION SECTOR THROUGH TECHNOLOGY THAT AUTOMATES PROCEDURES IN THE COCKPIT. WHILE AUTOMATION HAS BROUGHT CONSIDERABLE BENEFITS TO OPERATIONS AND THE CONTROL OF HUMAN-MACHINE INTERACTION SYSTEMS, THERE IS GROWING EMPIRICAL EVIDENCE POINTING TO SOME NEGATIVE EFFECTS, ESPECIALLY CONCERNING HUMAN MONITORING PERFORMANCE. IN LIGHT OF THIS, THE PRESENT RESEARCH SEEKS TO ANSWER THE FOLLOWING QUESTION: HOW TO MITIGATE THE CONFUSION OF ENGINE THRUST MODES TO WHICH AIRLINE PILOTS ARE SUBJECTED WHEN TRANSITIONING TO A NEW AIRCRAFT? THIS DISSERTATION AIMS TO PROPOSE A TRAINING MODEL FOR PILOTS TRANSITIONING BETWEEN COMMERCIAL AIRCRAFT, ALLOWING FOR THE MITIGATION OF ADVERSE EFFECTS OF AUTOMATION. TO ACHIEVE THIS, THIS WORK APPLIED A SEMI-STRUCTURED QUESTIONNAIRE, USED TO IDENTIFY COMMON ERRORS FOR EACH TYPE OF TRANSITION. THE MOST PREVALENT RESPONSES TO SITUATIONS PRONE TO CONFUSION WERE OBTAINED IN THE FOLLOWING ORDER: "INTERPRETATION OF MODES PRESENTED IN THE AIRCRAFT'S FMA (FLIGHT MODE ANNUNCIATOR)," "MANAGEMENT OF VERTICAL NAVIGATION," "SEQUENCE OF ACTIONS DURING A GO-AROUND," "DESCENT PROFILE PRIORITIZATION VS. SPEED MAINTENANCE PRIORITIZATION," AND "INCORRECT POSITIONING OF THRUST LEVERS DURING A GO-AROUND." FOR PILOT RECOMMENDATIONS TO MITIGATE CONFUSING CIRCUMSTANCES, THE FOLLOWING WERE IDENTIFIED: "MORE SIMULATOR TRAINING HOURS" AND "MORE THEORETICAL TRAINING HOURS." BASED ON THE RESULTS, A CONCEPTUAL MODEL WAS DEVELOPED TO ADD IMPORTANT ELEMENTS TO TRAINING, SUCH AS: PILOT BACKGROUND ASSESSMENT, COMMON ERRORS GUIDE, AND COMPETENCY MAP OF THE CURRENT TRAINING PROGRAM STRUCTURE—A PROPOSED PRODUCT OF THIS DISSERTATION. THE INFORMATION OBTAINED IN THIS RESEARCH CAN BE USED BY AIRLINES TO IDENTIFY SITUATIONS CAUSING MODE CONFUSION AND IMPLEMENT MEASURES TO MITIGATE THE ADVERSE EFFECTS OF AUTOMATION.</t>
+          <t>TRADITIONAL PILOT TRAINING, WHICH RELIES ON REPETITION-BASED ENHANCEMENT OF MANEUVER PRACTICES, HAS REMAINED UNCHANGED SINCE THE INTRODUCTION OF FLIGHT SIMULATORS, GUIDED BY THE BELIEF THAT “ONE SIZE FITS ALL.” MEANWHILE, TECHNOLOGICAL ADVANCEMENTS IN AIRCRAFT DESIGN, INCLUDING AUTOMATION DEVELOPMENT, INTEGRATION SYSTEMS, RELIABILITY, AND CHANGES IN THE OPERATIONAL ENVIRONMENT, HAVE CONTRIBUTED TO CONTINUOUS IMPROVEMENTS IN AVIATION SAFETY WHILE ALSO REVEALING NEW CHALLENGES. CONSIDERING THIS, ADOPTING APPROPRIATE METHODS TO SHIFT THE PATTERN IN PILOT TRAINING FROM A “TICK BOX” APPROACH TO INDUSTRY-ADOPTED BEST PRACTICES BECOMES IMPERATIVE. THIS APPROACH CAN CONTRIBUTE TO ENHANCING PILOT PERFORMANCE IN AERIAL OPERATIONS THROUGH A MORE EFFICIENT AND FLEXIBLE TRAINING PROGRAM. THEREFORE, THE OBJECTIVE OF THIS WORK IS TO PROPOSE A PLAN FOR IMPLEMENTING A PILOT TRAINING PROGRAM ON A NATIONAL SCALE, AIMING TO MEET CERTIFICATION REQUIREMENTS WHILE REMAINING FEASIBLE FOR AIR OPERATORS AND CIVIL AVIATION TRAINING CENTERS. ONE OF THE MOST COHERENT STATEMENTS FOUND IN THIS STUDY WAS: “TRAIN THE WAY YOU OPERATE AND OPERATE THE WAY YOU TRAIN.” THIS RESEARCH IS CHARACTERIZED AS DESCRIPTIVE AND COMPARATIVE, SUPPLEMENTED BY EXPLORATORY PROCEDURES INVOLVING BIBLIOGRAPHIC AND DOCUMENTARY STUDIES OF NATIONAL AND INTERNATIONAL CIVIL AVIATION STANDARDS. THE STUDY COVERS THE FOLLOWING TRAINING METHODOLOGIES: ADVANCED QUALIFICATION PROGRAM (AQP), ALTERNATIVE TRAINING AND QUALIFICATION PROGRAMME (ATQP), EVIDENCE-BASED TRAINING (EBT), AND COMPETENCY-BASED TRAINING AND ASSESSMENT (CBTA). FROM THE MAIN CHARACTERISTICS OF THE ADDRESSED METHODOLOGIES, A QUESTIONNAIRE WAS DEVELOPED USING THE LIKERT SCALE, ANSWERED THROUGH STRUCTURED AND OPEN INTERVIEWS CONDUCTED BY THE EVALUATION COMMITTEE. THE SWOT ANALYSIS (STRENGTHS, WEAKNESSES, OPPORTUNITIES, AND THREATS) WAS EMPLOYED TO COMPILE THE INTERVIEW RESULTS, RESULTING IN THE PROPOSAL OF A STRATEGIC PLAN FOR THE IMPLEMENTATION OF A NATIONWIDE PILOT TRAINING PROGRAM. IN THIS WAY, THE MOST RELEVANT ASPECTS OF EACH TRAINING METHODOLOGY ARE HIGHLIGHTED, ADOPTING A MORE MODERN AND EFFICIENT APPROACH, AIMING TO INCREASE THE LEVEL OF AVIATION SAFETY.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TREINAMENTO DO PILOTO;AUTOMAÇÃO;FATORES HUMANOS;PILOTO AUTOMÁTICO;PROGRAMAS DE TREINAMENTO;SEGURANÇA DO VOO;SIMULADORES DE VOO;MONITORAMENTO;ENGENHARIA DE AERONÁUTICA.</t>
+          <t>TREINAMENTO DO PILOTO;PLANEJAMENTO ESTRATÉGICO;SEGURANÇA OPERACIONAL;TREINAMENTO DE VOO;FATORES HUMANOS;PREVENÇÃO DE ACIDENTES;ENGENHARIA AERONÁUTICA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>TREINAMENTO DO PILOTO;AUTOMAÇÃO;FATORES HUMANOS;PILOTO AUTOMÁTICO;PROGRAMAS DE TREINAMENTO;SEGURANÇA DO VOO;SIMULADORES DE VOO;MONITORAMENTO;ENGENHARIA DE AERONÁUTICA.</t>
+          <t>TREINAMENTO DO PILOTO;PLANEJAMENTO ESTRATÉGICO;SEGURANÇA OPERACIONAL;TREINAMENTO DE VOO;FATORES HUMANOS;PREVENÇÃO DE ACIDENTES;ENGENHARIA AERONÁUTICA</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>MICHELLE CARVALHO GALVAO DA SILVA PINTO BANDEIRA</t>
+          <t>RONALDO VIEIRA CRUZ</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y38" t="n">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -5778,16 +5778,16 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14474457</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14690798</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>14474457</t>
+          <t>14690798</t>
         </is>
       </c>
       <c r="AE38" t="n">
-        <v>4007674</v>
+        <v>2753775</v>
       </c>
     </row>
     <row r="39">
@@ -5806,54 +5806,54 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FABIANO VARGAS FREITAS</t>
+          <t>GUTEMBERG ASSUNCAO VIEIRA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PROPOSTA DE PLANO ESTRATÉGICO DE IMPLEMENTAÇÃO DE PROGRAMA DE TREINAMENTO DE PILOTOS EM ÂMBITO NACIONAL</t>
+          <t>USO DE APRENDIZADO DE MÁQUINA NA AVALIAÇÃO DE POLÍTICAS PÚBLICAS: UMA REVISÃO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>OS TREINAMENTOS TRADICIONAIS DE PILOTOS, FUNDAMENTADOS NO INCREMENTO DE PRÁTICAS BASEADAS EM REPETIÇÃO DE MANOBRAS, PERMANECERAM INALTERADOS DESDE O ADVENTO DOS SIMULADORES DE VOO, COM A CRENÇA DE QUE “ONE SIZE FITS ALL”. DURANTE O MESMO PERÍODO, AVANÇOS TECNOLÓGICOS NO PROJETO DE AERONAVES, INCLUINDO O DESENVOLVIMENTO EM AUTOMAÇÃO, SISTEMA DE INTEGRAÇÃO, CONFIABILIDADE E MUDANÇAS NO AMBIENTE OPERACIONAL, CONTRIBUÍRAM PARA MELHORIA CONTÍNUA DA SEGURANÇA NA AVIAÇÃO, MAS TAMBÉM REVELARAM NOVOS DESAFIOS. DIANTE DISSO, TORNA-SE NECESSÁRIA A ADOÇÃO DE MÉTODOS ADEQUADOS PARA A MUDANÇA DE PADRÃO NO TREINAMENTO DE PILOTOS, PARTINDO DA ABORDAGEM DE “TICK BOX” PARA AS BOAS PRÁTICAS ADOTADAS PELA INDÚSTRIA AERONÁUTICA. ESSA ABORDAGEM PODE CONTRIBUIR PARA MELHORIA DO DESEMPENHO DOS PILOTOS NAS OPERAÇÕES AÉREAS, POR MEIO DE UM PROGRAMA DE TREINAMENTO MAIS EFICIENTE E FLEXÍVEL. NESSE SENTIDO, O OBJETIVO DESTE TRABALHO É PROPOR UM PLANO PARA IMPLEMENTAÇÃO DE PROGRAMA DE TREINAMENTO DE PILOTOS NO ÂMBITO NACIONAL, VISANDO ATENDER AOS REQUISITOS DE CERTIFICAÇÃO, AO MESMO TEMPO QUE SEJA VIÁVEL PARA OS OPERADORES AÉREOS E PARA OS CENTROS DE TREINAMENTO DE AVIAÇÃO CIVIL. UMA DAS AFIRMAÇÕES MAIS COERENTES ENCONTRADAS NESSE ESTUDO FOI: “TRAIN THE WAY YOU OPERATE AND OPERATE THE WAY YOU TRAIN”. A PRESENTE PESQUISA CARACTERIZA-SE COMO DESCRITIVA E COMPARATIVA, COMPLEMENTADA POR EXPLORATÓRIA COM PROCEDIMENTO BIBLIOGRÁFICO E DOCUMENTAL, A PARTIR DO ESTUDO DAS NORMAS NACIONAIS E INTERNACIONAIS NO ÂMBITO DA AVIAÇÃO CIVIL, ABORDANDO AS METODOLOGIAS DE TREINAMENTO A SEGUIR: ADVANCED QUALIFICATION PROGRAM (AQP), ALTERNATIVE TRAINING AND QUALIFICATION PROGRAMME (ATQP), EVIDENCE-BASED TRAINING (EBT) E COMPETENCY-BASED TRAINING AND ASSESSMENT (CBTA). A PARTIR DAS PRINCIPAIS CARACTERÍSTICAS DAS METODOLOGIAS ABORDADAS, DESENVOLVEU-SE UM QUESTIONÁRIO COM A ESCALA DE LIKERT, RESPONDIDO POR MEIO DE ENTREVISTAS ESTRUTURADAS E ABERTAS PELO COMITÊ AVALIATIVO. FOI UTILIZADA A ANÁLISE SWOT (STRENGTHS, WEAKNESSES, OPPORTUNITIES AND THREATS) PARA COMPILAR OS RESULTADOS DAS ENTREVISTAS, RESULTANDO NA PROPOSIÇÃO DE UM PLANO ESTRATÉGICO PARA IMPLEMENTAÇÃO DO PROGRAMA DE TREINAMENTO DE PILOTOS EM ÂMBITO NACIONAL. DESSA MANEIRA, APONTAM-SE OS ASPECTOS MAIS RELEVANTES DE CADA METODOLOGIA DE TREINAMENTO, ADOTANDO UMA ABORDAGEM MAIS MODERNA E EFICIENTE, VISANDO AO AUMENTO DO NÍVEL DE SEGURANÇA OPERACIONAL.</t>
+          <t>CADA VEZ MAIS O APRENDIZADO DE MÁQUINA TEM SIDO APLICADO PARA DESEMPENHAR ATIVIDADES QUE REQUERIAM A EXECUÇÃO POR SERES HUMANOS, INCLUSIVE NO ÂMBITO GOVERNAMENTAL. NESSE CONTEXTO, QUESTIONA-SE COMO OCORRE A UTILIZAÇÃO DESSE TIPO DE FERRAMENTA NA AVALIAÇÃO DE POLÍTICAS PÚBLICAS E SOBRE QUAIS INTERVENÇÕES JÁ FORAM APLICADAS. DITO ISSO, O OBJETIVO DESTA DISSERTAÇÃO É O MAPEAMENTO DE EVIDÊNCIAS DE USO DE APRENDIZADO DE MÁQUINA NA AVALIAÇÃO DE POLÍTICAS PÚBLICAS COM A FINALIDADE DE SER UTILIZADO COMO FONTE DE REFERÊNCIA POR PESQUISADORES, PROFISSIONAIS E OUTROS INTERESSADOS NO ASSUNTO. FOI UTILIZADA A METODOLOGIA DE REVISÃO DE ESCOPO COM IMPLEMENTAÇÃO DE REVISÃO CEGADA PARA REDUÇÃO DE VIÉS NA SELEÇÃO DOS ESTUDOS. AO FINAL FORAM ESCOLHIDOS 64 ESTUDOS PARA MAPEAMENTO, AGRUPAMENTO, SUMARIZAÇÃO E REPORTE NAS PERSPECTIVAS DE MÉTODOS DE APRENDIZADO DE MÁQUINA EMPREGADOS, OBJETOS AVALIADOS E CARACTERÍSTICAS GERAIS DAS PUBLICAÇÕES. CONFIRMOU-SE QUE SE TRATA DE UMA ÁREA DE APLICAÇÃO RECENTE EM TERMOS DE PUBLICAÇÃO, COM A MAIORIA DOS ESTUDOS CONCENTRADOS NOS ÚLTIMOS CINCO ANOS, E NÃO ABRANGE AÇÕES DA MAIORIA DAS ÁREAS GOVERNAMENTAIS. NÃO FOI IDENTIFICADO ESTUDO NO BRASIL DENTRO DO ESCOPO DEFINIDO E ESTRATÉGIA DE BUSCA IMPLEMENTADA, DESTACANDO-SE A OPORTUNIDADE DE PESQUISA APLICADA NO TEMA. OS MÉTODOS DE APRENDIZADO DE MÁQUINA FORAM CODIFICADOS QUANTO AO OBJETIVO DE APLICAÇÃO, RESULTANDO EM NOVE FORMAS DE APLICAÇÃO. TODOS OS DADOS MAPEADOS, CODIFICAÇÕES CRIADAS, BEM COMO OUTRAS MENÇÕES ÀS TECNOLOGIAS EMPREGADAS FORAM INCLUÍDOS NO TEXTO E NOS APÊNDICES PARA REFERÊNCIAS FUTURAS.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>TRADITIONAL PILOT TRAINING, WHICH RELIES ON REPETITION-BASED ENHANCEMENT OF MANEUVER PRACTICES, HAS REMAINED UNCHANGED SINCE THE INTRODUCTION OF FLIGHT SIMULATORS, GUIDED BY THE BELIEF THAT “ONE SIZE FITS ALL.” MEANWHILE, TECHNOLOGICAL ADVANCEMENTS IN AIRCRAFT DESIGN, INCLUDING AUTOMATION DEVELOPMENT, INTEGRATION SYSTEMS, RELIABILITY, AND CHANGES IN THE OPERATIONAL ENVIRONMENT, HAVE CONTRIBUTED TO CONTINUOUS IMPROVEMENTS IN AVIATION SAFETY WHILE ALSO REVEALING NEW CHALLENGES. CONSIDERING THIS, ADOPTING APPROPRIATE METHODS TO SHIFT THE PATTERN IN PILOT TRAINING FROM A “TICK BOX” APPROACH TO INDUSTRY-ADOPTED BEST PRACTICES BECOMES IMPERATIVE. THIS APPROACH CAN CONTRIBUTE TO ENHANCING PILOT PERFORMANCE IN AERIAL OPERATIONS THROUGH A MORE EFFICIENT AND FLEXIBLE TRAINING PROGRAM. THEREFORE, THE OBJECTIVE OF THIS WORK IS TO PROPOSE A PLAN FOR IMPLEMENTING A PILOT TRAINING PROGRAM ON A NATIONAL SCALE, AIMING TO MEET CERTIFICATION REQUIREMENTS WHILE REMAINING FEASIBLE FOR AIR OPERATORS AND CIVIL AVIATION TRAINING CENTERS. ONE OF THE MOST COHERENT STATEMENTS FOUND IN THIS STUDY WAS: “TRAIN THE WAY YOU OPERATE AND OPERATE THE WAY YOU TRAIN.” THIS RESEARCH IS CHARACTERIZED AS DESCRIPTIVE AND COMPARATIVE, SUPPLEMENTED BY EXPLORATORY PROCEDURES INVOLVING BIBLIOGRAPHIC AND DOCUMENTARY STUDIES OF NATIONAL AND INTERNATIONAL CIVIL AVIATION STANDARDS. THE STUDY COVERS THE FOLLOWING TRAINING METHODOLOGIES: ADVANCED QUALIFICATION PROGRAM (AQP), ALTERNATIVE TRAINING AND QUALIFICATION PROGRAMME (ATQP), EVIDENCE-BASED TRAINING (EBT), AND COMPETENCY-BASED TRAINING AND ASSESSMENT (CBTA). FROM THE MAIN CHARACTERISTICS OF THE ADDRESSED METHODOLOGIES, A QUESTIONNAIRE WAS DEVELOPED USING THE LIKERT SCALE, ANSWERED THROUGH STRUCTURED AND OPEN INTERVIEWS CONDUCTED BY THE EVALUATION COMMITTEE. THE SWOT ANALYSIS (STRENGTHS, WEAKNESSES, OPPORTUNITIES, AND THREATS) WAS EMPLOYED TO COMPILE THE INTERVIEW RESULTS, RESULTING IN THE PROPOSAL OF A STRATEGIC PLAN FOR THE IMPLEMENTATION OF A NATIONWIDE PILOT TRAINING PROGRAM. IN THIS WAY, THE MOST RELEVANT ASPECTS OF EACH TRAINING METHODOLOGY ARE HIGHLIGHTED, ADOPTING A MORE MODERN AND EFFICIENT APPROACH, AIMING TO INCREASE THE LEVEL OF AVIATION SAFETY.</t>
+          <t>MACHINE LEARNING HAS INCREASINGLY BEEN APPLIED TO PERFORM ACTIVITIES THAT REQUIRED HUMAN BEINGS TO PERFORM THEM, INCLUDING GOVERNMENT SERVICES. IN THIS CONTEXT, IT IS QUESTIONED HOW THIS TYPE OF TOOL IS USED IN THE EVALUATION OF PUBLIC POLICIES AND IN WHICH INTERVENTIONS HAVE ALREADY BEEN APPLIED. THEREFORE, THE OBJECTIVE OF THIS DISSERTATION IS TO MAP EVIDENCE OF THE USE OF MACHINE LEARNING IN THE EVALUATION OF PUBLIC POLICIES IN ORDER TO BE USED AS A REFERENCE SOURCE BY RESEARCHERS, PROFESSIONALS AND OTHERS INTERESTED IN THE SUBJECT. THE SCOPE REVIEW METHODOLOGY WAS USED AND BLINDED REVIEW WAS APPLIED TO REDUCE BIAS IN THE SELECTION OF STUDIES. IN THE END, 64 STUDIES WERE CHOSEN FOR MAPPING, GROUPING, SUMMARIZING AND REPORTING FROM THE PERSPECTIVES OF MACHINE LEARNING METHODS EMPLOYED, EVALUATED OBJECTS AND GENERAL CHARACTERISTICS OF THE PUBLICATIONS. IT WAS CONFIRMED THAT THIS IS A RECENT AREA OF APPLICATION IN TERMS OF PUBLICATION, MOSTLY OF THE THEM PUBLISHED IN THE LAST FIVE YEARS, AND DOES NOT COVER ACTIONS IN MOST GOVERNMENT AREAS. NO STUDY WAS IDENTIFIED IN BRAZIL WITHIN THE DEFINED SCOPE AND SEARCH STRATEGY, HIGHLIGHTING THE OPPORTUNITY FOR APPLIED RESEARCH ON THE TOPIC. THE MACHINE LEARNING METHODS WERE CODED ACCORDING TO THE APPLICATION OBJECTIVE, RESULTING IN NINE WAYS OF APPLICATION. ALL MAPPED DATA, CODING CREATED, AS WELL AS OTHER MENTIONS TO THE TECHNOLOGIES EMPLOYED WERE INCLUDED IN THE TEXT AND IN THE APPENDICES FOR FUTURE REFERENCE.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>TREINAMENTO DO PILOTO;PLANEJAMENTO ESTRATÉGICO;SEGURANÇA OPERACIONAL;TREINAMENTO DE VOO;FATORES HUMANOS;PREVENÇÃO DE ACIDENTES;ENGENHARIA AERONÁUTICA</t>
+          <t>AVALIAÇÃO DE POLÍTICA PÚBLICA;APRENDIZADO DE MÁQUINA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>TREINAMENTO DO PILOTO;PLANEJAMENTO ESTRATÉGICO;SEGURANÇA OPERACIONAL;TREINAMENTO DE VOO;FATORES HUMANOS;PREVENÇÃO DE ACIDENTES;ENGENHARIA AERONÁUTICA</t>
+          <t>PUBLIC POLICY EVALUATION;MACHINE LEARNING</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Correlato</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>Aprendizado de máquina (ML)</t>
         </is>
       </c>
       <c r="M39" t="b">
         <v>0</v>
       </c>
       <c r="N39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" t="b">
         <v>0</v>
@@ -5862,45 +5862,45 @@
         <v>0</v>
       </c>
       <c r="Q39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>RONALDO VIEIRA CRUZ</t>
+          <t>FLAVIA LUCIA CHEIN FERES</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>SEGURANÇA DE AVIAÇÃO E AERONAVEGABILIDADE CONTINUADA</t>
+          <t>AVALIAÇÃO E MONITORAMENTO DE POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>INSTITUTO TECNOLÓGICO DE AERONÁUTICA</t>
+          <t>FUNDAÇÃO ESCOLA NACIONAL DE ADMINISTRAÇÃO PÚBLICA</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>ENAP</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>SUDESTE</t>
+          <t>CENTRO-OESTE</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>SÃO PAULO</t>
+          <t>DISTRITO FEDERAL</t>
         </is>
       </c>
       <c r="Y39" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5919,16 +5919,16 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14690798</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14385858</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>14690798</t>
+          <t>14385858</t>
         </is>
       </c>
       <c r="AE39" t="n">
-        <v>2753775</v>
+        <v>444569</v>
       </c>
     </row>
     <row r="40">
@@ -5943,41 +5943,41 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GUTEMBERG ASSUNCAO VIEIRA</t>
+          <t>CARLOS RAFAEL DE AGUIAR NERY</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>USO DE APRENDIZADO DE MÁQUINA NA AVALIAÇÃO DE POLÍTICAS PÚBLICAS: UMA REVISÃO</t>
+          <t>INSTRUMENTO DE RECOMENDAÇÃO AUTOMÁTICA DE AÇÕES PARLAMENTARES COM BASE EM PREFERÊNCIAS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CADA VEZ MAIS O APRENDIZADO DE MÁQUINA TEM SIDO APLICADO PARA DESEMPENHAR ATIVIDADES QUE REQUERIAM A EXECUÇÃO POR SERES HUMANOS, INCLUSIVE NO ÂMBITO GOVERNAMENTAL. NESSE CONTEXTO, QUESTIONA-SE COMO OCORRE A UTILIZAÇÃO DESSE TIPO DE FERRAMENTA NA AVALIAÇÃO DE POLÍTICAS PÚBLICAS E SOBRE QUAIS INTERVENÇÕES JÁ FORAM APLICADAS. DITO ISSO, O OBJETIVO DESTA DISSERTAÇÃO É O MAPEAMENTO DE EVIDÊNCIAS DE USO DE APRENDIZADO DE MÁQUINA NA AVALIAÇÃO DE POLÍTICAS PÚBLICAS COM A FINALIDADE DE SER UTILIZADO COMO FONTE DE REFERÊNCIA POR PESQUISADORES, PROFISSIONAIS E OUTROS INTERESSADOS NO ASSUNTO. FOI UTILIZADA A METODOLOGIA DE REVISÃO DE ESCOPO COM IMPLEMENTAÇÃO DE REVISÃO CEGADA PARA REDUÇÃO DE VIÉS NA SELEÇÃO DOS ESTUDOS. AO FINAL FORAM ESCOLHIDOS 64 ESTUDOS PARA MAPEAMENTO, AGRUPAMENTO, SUMARIZAÇÃO E REPORTE NAS PERSPECTIVAS DE MÉTODOS DE APRENDIZADO DE MÁQUINA EMPREGADOS, OBJETOS AVALIADOS E CARACTERÍSTICAS GERAIS DAS PUBLICAÇÕES. CONFIRMOU-SE QUE SE TRATA DE UMA ÁREA DE APLICAÇÃO RECENTE EM TERMOS DE PUBLICAÇÃO, COM A MAIORIA DOS ESTUDOS CONCENTRADOS NOS ÚLTIMOS CINCO ANOS, E NÃO ABRANGE AÇÕES DA MAIORIA DAS ÁREAS GOVERNAMENTAIS. NÃO FOI IDENTIFICADO ESTUDO NO BRASIL DENTRO DO ESCOPO DEFINIDO E ESTRATÉGIA DE BUSCA IMPLEMENTADA, DESTACANDO-SE A OPORTUNIDADE DE PESQUISA APLICADA NO TEMA. OS MÉTODOS DE APRENDIZADO DE MÁQUINA FORAM CODIFICADOS QUANTO AO OBJETIVO DE APLICAÇÃO, RESULTANDO EM NOVE FORMAS DE APLICAÇÃO. TODOS OS DADOS MAPEADOS, CODIFICAÇÕES CRIADAS, BEM COMO OUTRAS MENÇÕES ÀS TECNOLOGIAS EMPREGADAS FORAM INCLUÍDOS NO TEXTO E NOS APÊNDICES PARA REFERÊNCIAS FUTURAS.</t>
+          <t>A SOBRECARGA E DIVERSIDADE DE PROPOSIÇÕES LEGISLATIVAS EM TRAMITAÇÃO NO SENADO FEDERAL DIFICULTAM O TRABALHO DOS GABINETES PARLAMENTARES. AS EQUIPES RESPONSÁVEIS POR ASSESSORAR DIRETAMENTE OS SENADORES MUITAS VEZES ENFRENTAM DESAFIOS DECORRENTES DO VOLUME DIÁRIO DE MATÉRIAS E DA COMPLEXIDADE DE TEMAS. NESSE CONTEXTO, ESTE TRABALHO PROPÕE A CRIAÇÃO DE UM SISTEMA AUTOMÁTICO DE RECOMENDAÇÃO DE AÇÕES LEGISLATIVAS, CONSIDERANDO O HISTÓRICO E AS PREFERÊNCIAS INDIVIDUAIS DOS SENADORES. OS DADOS FORAM COLETADOS E TRATADOS A PARTIR DO PORTAL DE DADOS ABERTOS DO SENADO FEDERAL. PARA ATRIBUIÇÃO DOS INTERESSES DE CADA SENADOR PELAS MATÉRIAS, FORAM UTILIZADOS ALGORITMOS DE MACHINE LEARNING. PARA IDENTIFICAÇÃO DA SIMILARIDADE ENTRE AS PROPOSIÇÕES LEGISLATIVAS, FORAM UTILIZADOS OS ALGORITMOS DE SIMILARIDADE DE COSSENO E BEST MATCH 25, PRÓPRIOS PARA PROCESSAMENTO DE LINGUAGEM NATURAL. APÓS IMPLEMENTAÇÃO, O SISTEMA FOI APRESENTADO A 80 GABINETES PARLAMENTARES E OS RESULTADOS INDICARAM QUE A FERRAMENTA DESENVOLVIDA É VALIOSA PARA O ASSESSORAMENTO LEGISLATIVO, REDUZINDO SIGNIFICATIVAMENTE O ESFORÇO NA LOCALIZAÇÃO DE MATÉRIAS DE INTERESSE PARA OS PARLAMENTARES.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>MACHINE LEARNING HAS INCREASINGLY BEEN APPLIED TO PERFORM ACTIVITIES THAT REQUIRED HUMAN BEINGS TO PERFORM THEM, INCLUDING GOVERNMENT SERVICES. IN THIS CONTEXT, IT IS QUESTIONED HOW THIS TYPE OF TOOL IS USED IN THE EVALUATION OF PUBLIC POLICIES AND IN WHICH INTERVENTIONS HAVE ALREADY BEEN APPLIED. THEREFORE, THE OBJECTIVE OF THIS DISSERTATION IS TO MAP EVIDENCE OF THE USE OF MACHINE LEARNING IN THE EVALUATION OF PUBLIC POLICIES IN ORDER TO BE USED AS A REFERENCE SOURCE BY RESEARCHERS, PROFESSIONALS AND OTHERS INTERESTED IN THE SUBJECT. THE SCOPE REVIEW METHODOLOGY WAS USED AND BLINDED REVIEW WAS APPLIED TO REDUCE BIAS IN THE SELECTION OF STUDIES. IN THE END, 64 STUDIES WERE CHOSEN FOR MAPPING, GROUPING, SUMMARIZING AND REPORTING FROM THE PERSPECTIVES OF MACHINE LEARNING METHODS EMPLOYED, EVALUATED OBJECTS AND GENERAL CHARACTERISTICS OF THE PUBLICATIONS. IT WAS CONFIRMED THAT THIS IS A RECENT AREA OF APPLICATION IN TERMS OF PUBLICATION, MOSTLY OF THE THEM PUBLISHED IN THE LAST FIVE YEARS, AND DOES NOT COVER ACTIONS IN MOST GOVERNMENT AREAS. NO STUDY WAS IDENTIFIED IN BRAZIL WITHIN THE DEFINED SCOPE AND SEARCH STRATEGY, HIGHLIGHTING THE OPPORTUNITY FOR APPLIED RESEARCH ON THE TOPIC. THE MACHINE LEARNING METHODS WERE CODED ACCORDING TO THE APPLICATION OBJECTIVE, RESULTING IN NINE WAYS OF APPLICATION. ALL MAPPED DATA, CODING CREATED, AS WELL AS OTHER MENTIONS TO THE TECHNOLOGIES EMPLOYED WERE INCLUDED IN THE TEXT AND IN THE APPENDICES FOR FUTURE REFERENCE.</t>
+          <t>THE OVERLOAD AND DIVERSITY OF LEGISLATIVE PROPOSALS IN PROGRESS AT THE FEDERAL SENATE COMPLICATE THE WORK OF PARLIAMENTARY OFFICES. THE TEAMS RESPONSIBLE FOR DIRECTLY ASSISTING SENATORS OFTEN FACE CHALLENGES STEMMING FROM THE DAILY VOLUME OF BILLS OF LAW AND THE COMPLEXITY OF TOPICS. IN THIS CONTEXT, THIS WORK PROPOSES THE DEVELOPMENT OF AN AUTOMATIC SYSTEM FOR RECOMMENDING LEGISLATIVE ACTIONS, TAKING INTO ACCOUNT THE HISTORICAL DATA AND INDIVIDUAL PREFERENCES OF SENATORS. DATA WERE COLLECTED AND PROCESSED FROM THE FEDERAL SENATE’S OPEN DATA PORTAL. MACHINE LEARNING ALGORITHMS WERE EMPLOYED TO ASSIGN EACH SENATOR’S INTERESTS TO THE PROPOSED LAWS. COSINE SIMILARITY AND BEST MATCH 25 ALGORITHMS, SPECIFICALLY DESIGNED FOR NATURAL LANGUAGE PROCESSING, WERE USED TO IDENTIFY SIMILARITY AMONG LEGISLATIVE PROPOSALS. FOLLOWING IMPLEMENTATION, THE SYSTEM WAS PRESENTED TO 80 PARLIAMENTARY OFFICES, AND THE RESULTS INDICATED THAT THE DEVELOPED TOOL IS VALUABLE FOR LEGISLATIVE SUPPORT, SIGNIFICANTLY REDUCING THE EFFORT INVOLVED IN LOCATING SUBJECTS OF INTEREST TO SENATORS.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>AVALIAÇÃO DE POLÍTICA PÚBLICA;APRENDIZADO DE MÁQUINA</t>
+          <t>PODER LEGISLATIVO;SISTEMA DE RECOMENDAÇÃO;DADOS ABERTOS;AÇÕES LEGISLATIVAS;ATUAÇÃO PARLAMENTAR</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>PUBLIC POLICY EVALUATION;MACHINE LEARNING</t>
+          <t>LEGISLATIVE POWER;RECOMMENDATION SYSTEM;OPEN DATA;LEGISLATIVE ACTIONS;PARLIAMENTARY ACTIVITY</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Aprendizado de máquina (ML)</t>
+          <t>Aprendizado de máquina (ML); Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M40" t="b">
@@ -6003,26 +6003,26 @@
         <v>0</v>
       </c>
       <c r="Q40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>FLAVIA LUCIA CHEIN FERES</t>
+          <t>FABIANO PERUZZO SCHWARTZ</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>AVALIAÇÃO E MONITORAMENTO DE POLÍTICAS PÚBLICAS</t>
+          <t>PODER LEGISLATIVO</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO ESCOLA NACIONAL DE ADMINISTRAÇÃO PÚBLICA</t>
+          <t>CENTRO DE FORMAÇÃO, TREINAMENTO E APERFEIÇOAMENTO</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>ENAP</t>
+          <t>CEFOR</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>POLÍTICAS PÚBLICAS</t>
+          <t>NÃO SE APLICA</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -6060,16 +6060,16 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14385858</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15145557</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>14385858</t>
+          <t>15145557</t>
         </is>
       </c>
       <c r="AE40" t="n">
-        <v>444569</v>
+        <v>3990725</v>
       </c>
     </row>
     <row r="41">
@@ -6088,37 +6088,37 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CARLOS RAFAEL DE AGUIAR NERY</t>
+          <t>JULIA DINIZ CALATRONE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>INSTRUMENTO DE RECOMENDAÇÃO AUTOMÁTICA DE AÇÕES PARLAMENTARES COM BASE EM PREFERÊNCIAS</t>
+          <t>MODELO PREDITIVO DA QUALIDADE DE MEDICAMENTOS NO BRASIL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>A SOBRECARGA E DIVERSIDADE DE PROPOSIÇÕES LEGISLATIVAS EM TRAMITAÇÃO NO SENADO FEDERAL DIFICULTAM O TRABALHO DOS GABINETES PARLAMENTARES. AS EQUIPES RESPONSÁVEIS POR ASSESSORAR DIRETAMENTE OS SENADORES MUITAS VEZES ENFRENTAM DESAFIOS DECORRENTES DO VOLUME DIÁRIO DE MATÉRIAS E DA COMPLEXIDADE DE TEMAS. NESSE CONTEXTO, ESTE TRABALHO PROPÕE A CRIAÇÃO DE UM SISTEMA AUTOMÁTICO DE RECOMENDAÇÃO DE AÇÕES LEGISLATIVAS, CONSIDERANDO O HISTÓRICO E AS PREFERÊNCIAS INDIVIDUAIS DOS SENADORES. OS DADOS FORAM COLETADOS E TRATADOS A PARTIR DO PORTAL DE DADOS ABERTOS DO SENADO FEDERAL. PARA ATRIBUIÇÃO DOS INTERESSES DE CADA SENADOR PELAS MATÉRIAS, FORAM UTILIZADOS ALGORITMOS DE MACHINE LEARNING. PARA IDENTIFICAÇÃO DA SIMILARIDADE ENTRE AS PROPOSIÇÕES LEGISLATIVAS, FORAM UTILIZADOS OS ALGORITMOS DE SIMILARIDADE DE COSSENO E BEST MATCH 25, PRÓPRIOS PARA PROCESSAMENTO DE LINGUAGEM NATURAL. APÓS IMPLEMENTAÇÃO, O SISTEMA FOI APRESENTADO A 80 GABINETES PARLAMENTARES E OS RESULTADOS INDICARAM QUE A FERRAMENTA DESENVOLVIDA É VALIOSA PARA O ASSESSORAMENTO LEGISLATIVO, REDUZINDO SIGNIFICATIVAMENTE O ESFORÇO NA LOCALIZAÇÃO DE MATÉRIAS DE INTERESSE PARA OS PARLAMENTARES.</t>
+          <t>MEDICAMENTOS QUE NÃO ATENDEM A PADRÕES MÍNIMOS DE QUALIDADE, CHAMADOS SUBSTANDARD SÃO UM GRANDE PROBLEMA DE SAÚDE PÚBLICA, PONDO EM RISCO A SAÚDE DOS CONSUMIDORES. AS AGÊNCIAS REGULADORAS NEM SEMPRE POSSUEM CAPACIDADE OPERACIONAL PARA VERIFICAR TODAS AS ATIVIDADES DE PRODUÇÃO FARMACÊUTICA, E DEVEM ATUAR BASEADAS NO RISCO SANITÁRIO. O RISCO SANITÁRIO PARA DIRECIONAMENTO DAS AÇÕES DE FISCALIZAÇÃO COMUMENTE É DETERMINADO DE FORMA EMPÍRICA. APESAR DESSA ABORDAGEM TER UMA PERFORMANCE TRADICIONALMENTE ACEITÁVEL, É NECESSÁRIO BUSCAR MODELOS QUE OTIMIZEM CUSTO E EFETIVIDADE, MINIMIZADO ASSIM A CHANCE DE QUE UM MEDICAMENTO SUBSTANDARD SEJA COMERCIALIZADO. ESTE TRABALHO FAZ USO DE DADOS COLETADOS DE FORMA ESTRUTURADA NO AMBIENTE REGULATÓRIO DA ANVISA PARA PREVER MEDICAMENTOS SUBSTANDARD POR MEIO DE MODELOS DE MACHINE LEARNING. ESSA ABORDAGEM INOVADORA NA ÁREA DA REGULAÇÃO SANITÁRIA ABRE OPORTUNIDADES PARA A REFORMULAÇÃO DE PROCESSOS DE TRABALHO DE FISCALIZAÇÃO E TAMBÉM PARA A REVISÃO DA POLÍTICA DE GERENCIAMENTO DE DADOS INSTITUCIONAL. NO TRABALHO FORAM UTILIZADOS OS MODELOS LASSO, RIDGE E ELASTIC NET PARA CLASSIFICAÇÃO, APLICADOS POR MEIO DO SOFTWARE R. AS MÉTRICAS DE DESEMPENHO EMPREGADAS FORAM ACURÁCIA E ROC AUC. TODOS OS MODELOS ATINGIRAM RESULTADOS SEMELHANTES DE ACURÁCIA DE APROXIMADAMENTE 99%. O MODELO LASSO SE MOSTROU O MAIS ADEQUADO PARA A APLICAÇÃO PRÁTICA, POR TER O MELHOR DESEMPENHO DE ROC AUC COM UM VALOR DE 0,99, E USANDO O MENOR NÚMERO DE VARIÁVEIS.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>THE OVERLOAD AND DIVERSITY OF LEGISLATIVE PROPOSALS IN PROGRESS AT THE FEDERAL SENATE COMPLICATE THE WORK OF PARLIAMENTARY OFFICES. THE TEAMS RESPONSIBLE FOR DIRECTLY ASSISTING SENATORS OFTEN FACE CHALLENGES STEMMING FROM THE DAILY VOLUME OF BILLS OF LAW AND THE COMPLEXITY OF TOPICS. IN THIS CONTEXT, THIS WORK PROPOSES THE DEVELOPMENT OF AN AUTOMATIC SYSTEM FOR RECOMMENDING LEGISLATIVE ACTIONS, TAKING INTO ACCOUNT THE HISTORICAL DATA AND INDIVIDUAL PREFERENCES OF SENATORS. DATA WERE COLLECTED AND PROCESSED FROM THE FEDERAL SENATE’S OPEN DATA PORTAL. MACHINE LEARNING ALGORITHMS WERE EMPLOYED TO ASSIGN EACH SENATOR’S INTERESTS TO THE PROPOSED LAWS. COSINE SIMILARITY AND BEST MATCH 25 ALGORITHMS, SPECIFICALLY DESIGNED FOR NATURAL LANGUAGE PROCESSING, WERE USED TO IDENTIFY SIMILARITY AMONG LEGISLATIVE PROPOSALS. FOLLOWING IMPLEMENTATION, THE SYSTEM WAS PRESENTED TO 80 PARLIAMENTARY OFFICES, AND THE RESULTS INDICATED THAT THE DEVELOPED TOOL IS VALUABLE FOR LEGISLATIVE SUPPORT, SIGNIFICANTLY REDUCING THE EFFORT INVOLVED IN LOCATING SUBJECTS OF INTEREST TO SENATORS.</t>
+          <t>SUBSTANDARD MEDICINES POSE A SIGNIFICANT PUBLIC HEALTH CHALLENGE. REGULATORY AGENCIES LACK THE OPERATIONAL CAPACITY TO VERIFY ALL PHARMACEUTICAL PRODUCTION ACTIVITIES AND THEREFORE MUST OPERATE IN A RISK-BASED MANNER. DETERMINING THE APPROPRIATE RISK LEVEL FOR GUIDING ENFORCEMENT ACTIONS WITHIN REGULATED MARKETS OFTEN RELIES ON EMPIRICAL METHODS. DESPITE THE HISTORICAL EFFECTIVENESS OF THIS APPROACH, THERE IS A NEED TO EXPLORE MODELS THAT ENHANCE COST-EFFICIENCY AND OVERALL EFFECTIVENESS. ANVISA SYSTEMATICALLY COLLECTS STRUCTURED DATA THROUGH ITS REGULATORY ACTIONS. THIS DATA HAS BEEN LEVERAGED TO PREDICT SUBSTANDARD MEDICINES USING MACHINE LEARNING MODELS. THIS PIONEERING APPROACH WITHIN THE FIELD CREATES OPPORTUNITIES TO REFORMULATE ENFORCEMENT WORK PROCESSES AND REVISE INSTITUTIONAL DATA MANAGEMENT POLICIES. IN THIS STUDY, LASSO, RIDGE AND ELASTIC NET MODELS WERE EMPLOYED FOR CLASSIFICATION, UTILIZING THE SOFTWARE R. ACCURACY AND ROC AUC WERE EMPLOYED AS PERFORMANCE METRICS. ALL MODELS YIELDED SIMILAR ACCURACY RATES OF APPROXIMATELY 99%. THE LASSO MODEL PROVED TO BE THE MOST SUITABLE FOR PRACTICAL APPLICATION, EXHIBITING THE HIGHEST ROC AUC PERFORMANCE AT 0.99, WHILE UTILIZING THE FEWEST VARIABLES.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PODER LEGISLATIVO;SISTEMA DE RECOMENDAÇÃO;DADOS ABERTOS;AÇÕES LEGISLATIVAS;ATUAÇÃO PARLAMENTAR</t>
+          <t>SUBSTANDARD;FALSIFIED;MEDICATIONS;MACHINE LEARNING;PREDICTIVE MODEL</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>LEGISLATIVE POWER;RECOMMENDATION SYSTEM;OPEN DATA;LEGISLATIVE ACTIONS;PARLIAMENTARY ACTIVITY</t>
+          <t>SUBSTANDARD;FALSIFIED;MEDICINES;MACHINE LEARNING;PREDICTIVE MODEL</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Aprendizado de máquina (ML); Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>Aprendizado de máquina (ML)</t>
         </is>
       </c>
       <c r="M41" t="b">
@@ -6144,26 +6144,26 @@
         <v>0</v>
       </c>
       <c r="Q41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>FABIANO PERUZZO SCHWARTZ</t>
+          <t>VITOR AZEVEDO PEREIRA PONTUAL</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>PODER LEGISLATIVO</t>
+          <t>AVALIAÇÃO E MONITORAMENTO DE POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMAÇÃO, TREINAMENTO E APERFEIÇOAMENTO</t>
+          <t>ESCOLA NACIONAL DE ADMINISTRAÇÃO PÚBLICA</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>CEFOR</t>
+          <t>ENAP</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -6182,7 +6182,7 @@
         </is>
       </c>
       <c r="Y41" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -6201,16 +6201,16 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15145557</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16376007</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>15145557</t>
+          <t>16376007</t>
         </is>
       </c>
       <c r="AE41" t="n">
-        <v>3990725</v>
+        <v>3441509</v>
       </c>
     </row>
     <row r="42">
@@ -6229,37 +6229,37 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>JULIA DINIZ CALATRONE</t>
+          <t>LUIZ MORAES DE ALMEIDA JUNIOR</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MODELO PREDITIVO DA QUALIDADE DE MEDICAMENTOS NO BRASIL</t>
+          <t>CHATBOT: UM PROTÓTIPO DE ASSISTENTE VIRTUAL COMO FERRAMENTA DE EDUCAÇÃO FISCAL NA SECRETARIA DA FAZENDA DA BAHIA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>MEDICAMENTOS QUE NÃO ATENDEM A PADRÕES MÍNIMOS DE QUALIDADE, CHAMADOS SUBSTANDARD SÃO UM GRANDE PROBLEMA DE SAÚDE PÚBLICA, PONDO EM RISCO A SAÚDE DOS CONSUMIDORES. AS AGÊNCIAS REGULADORAS NEM SEMPRE POSSUEM CAPACIDADE OPERACIONAL PARA VERIFICAR TODAS AS ATIVIDADES DE PRODUÇÃO FARMACÊUTICA, E DEVEM ATUAR BASEADAS NO RISCO SANITÁRIO. O RISCO SANITÁRIO PARA DIRECIONAMENTO DAS AÇÕES DE FISCALIZAÇÃO COMUMENTE É DETERMINADO DE FORMA EMPÍRICA. APESAR DESSA ABORDAGEM TER UMA PERFORMANCE TRADICIONALMENTE ACEITÁVEL, É NECESSÁRIO BUSCAR MODELOS QUE OTIMIZEM CUSTO E EFETIVIDADE, MINIMIZADO ASSIM A CHANCE DE QUE UM MEDICAMENTO SUBSTANDARD SEJA COMERCIALIZADO. ESTE TRABALHO FAZ USO DE DADOS COLETADOS DE FORMA ESTRUTURADA NO AMBIENTE REGULATÓRIO DA ANVISA PARA PREVER MEDICAMENTOS SUBSTANDARD POR MEIO DE MODELOS DE MACHINE LEARNING. ESSA ABORDAGEM INOVADORA NA ÁREA DA REGULAÇÃO SANITÁRIA ABRE OPORTUNIDADES PARA A REFORMULAÇÃO DE PROCESSOS DE TRABALHO DE FISCALIZAÇÃO E TAMBÉM PARA A REVISÃO DA POLÍTICA DE GERENCIAMENTO DE DADOS INSTITUCIONAL. NO TRABALHO FORAM UTILIZADOS OS MODELOS LASSO, RIDGE E ELASTIC NET PARA CLASSIFICAÇÃO, APLICADOS POR MEIO DO SOFTWARE R. AS MÉTRICAS DE DESEMPENHO EMPREGADAS FORAM ACURÁCIA E ROC AUC. TODOS OS MODELOS ATINGIRAM RESULTADOS SEMELHANTES DE ACURÁCIA DE APROXIMADAMENTE 99%. O MODELO LASSO SE MOSTROU O MAIS ADEQUADO PARA A APLICAÇÃO PRÁTICA, POR TER O MELHOR DESEMPENHO DE ROC AUC COM UM VALOR DE 0,99, E USANDO O MENOR NÚMERO DE VARIÁVEIS.</t>
+          <t>PARA AMPLIAR O ACESSO A INFORMAÇÃO, A ADMINISTRAÇÃO PÚBLICA PRECISA DISPOR DE INSTRUMENTOS CAPAZES DE INFORMAR DE MANEIRA EFICIENTE E SIMPLIFICADA, VISANDO APROXIMAR CADA VEZ MAIS O CIDADÃO DAS INSTITUIÇÕES. NESTE SENTIDO, A PESQUISA OBJETIVOU DESENVOLVER UM PROTÓTIPO DE ASSISTENTE VIRTUAL (CHATBOT) PARA AUXILIAR A EDUCAÇÃO FISCAL NO SENTIDO DE PROMOVER O CONHECIMENTO E A CONSCIENTIZAÇÃO DOS CIDADÃOS PARA ALÉM DAS QUESTÕES TRIBUTÁRIAS. O CHATBOT PROPOSTO É UM SOFTWARE DE INTELIGÊNCIA ARTIFICIAL BASEADO EM REGRAS, DESENVOLVIDO EM PROGRAMA GRATUITO E ACESSÍVEL PELO CELULAR QUE FUNCIONA INTEGRADO AO APLICATIVO DE MENSAGENS TELEGRAM, INTERAGINDO COM OS USUÁRIOS DE FORMA NATURAL PARA INFORMAR E ESCLARECER DÚVIDAS. AS METODOLOGIAS APLICADAS FORAM A PESQUISA BIBLIOGRÁFICA, VISANDO ESCLARECER CONCEITOS RELACIONADOS A EDUCAÇÃO FISCAL, INTELIGÊNCIA ARTIFICIAL E CHATBOT; E A PESQUISA DOCUMENTAL, QUE ANALISOU O CONTEÚDO DOS RELATÓRIOS DAS CENTRAIS DE ATENDIMENTO “CALL CENTER” E “FALE CONOSCO” DA SECRETARIA DA FAZENDA DO ESTADO DA BAHIA. OS RESULTADOS INDICAM QUE, EMBORA ALGUMAS ÁREAS DO GOVERNO JÁ ESTEJAM UTILIZANDO A INTELIGÊNCIA ARTIFICIAL PARA MELHORAR A ARRECADAÇÃO DE IMPOSTOS, AGILIZAR A PRESTAÇÃO DE SERVIÇOS E APRIMORAR SEUS PROCESSOS, AS INICIATIVAS RELACIONADAS À EDUCAÇÃO FISCAL AINDA ENFRENTAM DESAFIOS COMO O EXCESSO DE TECNICISMO, ABORDAGENS INADEQUADAS E FALTA DE PRIORIDADE SOBRE OUTRAS DEMANDAS SOCIAIS. O ESTUDO SINALIZA QUE A TECNOLOGIA CHATBOT AINDA PRECISA SUPERAR O DESAFIO DA ACESSIBILIDADE E EXCLUSÃO DIGITAL DAS PESSOAS SOCIALMENTE VULNERÁVEIS SEM ACESSO A REDE DE INTERNET. POR OUTRO LADO, O PROTÓTIPO DO CHATBOT TEM O POTENCIAL DE DEMOCRATIZAR O CONHECIMENTO, USANDO LINGUAGEM ACESSÍVEL ALCANÇANDO UM PÚBLICO FAMILIARIZADO COM CONTEÚDO DIGITAL COM EXPLICAÇÕES CLARAS E CONCISAS SOBRE CONCEITOS TRIBUTÁRIOS COMPLEXOS.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SUBSTANDARD MEDICINES POSE A SIGNIFICANT PUBLIC HEALTH CHALLENGE. REGULATORY AGENCIES LACK THE OPERATIONAL CAPACITY TO VERIFY ALL PHARMACEUTICAL PRODUCTION ACTIVITIES AND THEREFORE MUST OPERATE IN A RISK-BASED MANNER. DETERMINING THE APPROPRIATE RISK LEVEL FOR GUIDING ENFORCEMENT ACTIONS WITHIN REGULATED MARKETS OFTEN RELIES ON EMPIRICAL METHODS. DESPITE THE HISTORICAL EFFECTIVENESS OF THIS APPROACH, THERE IS A NEED TO EXPLORE MODELS THAT ENHANCE COST-EFFICIENCY AND OVERALL EFFECTIVENESS. ANVISA SYSTEMATICALLY COLLECTS STRUCTURED DATA THROUGH ITS REGULATORY ACTIONS. THIS DATA HAS BEEN LEVERAGED TO PREDICT SUBSTANDARD MEDICINES USING MACHINE LEARNING MODELS. THIS PIONEERING APPROACH WITHIN THE FIELD CREATES OPPORTUNITIES TO REFORMULATE ENFORCEMENT WORK PROCESSES AND REVISE INSTITUTIONAL DATA MANAGEMENT POLICIES. IN THIS STUDY, LASSO, RIDGE AND ELASTIC NET MODELS WERE EMPLOYED FOR CLASSIFICATION, UTILIZING THE SOFTWARE R. ACCURACY AND ROC AUC WERE EMPLOYED AS PERFORMANCE METRICS. ALL MODELS YIELDED SIMILAR ACCURACY RATES OF APPROXIMATELY 99%. THE LASSO MODEL PROVED TO BE THE MOST SUITABLE FOR PRACTICAL APPLICATION, EXHIBITING THE HIGHEST ROC AUC PERFORMANCE AT 0.99, WHILE UTILIZING THE FEWEST VARIABLES.</t>
+          <t>CHATBOT: A VIRTUAL ASSISTANT PROTOTYPE AS A TAX EDUCATION TOOL AT THE BAHIA FINANCE DEPARTMENT TO EXPAND ACCESS TO INFORMATION, THE PUBLIC ADMINISTRATION NEEDS TO HAVE INSTRUMENTS CAPABLE OF PROVIDING INFORMATION IN AN EFFICIENT AND SIMPLIFIED MANNER, AIMING TO BRING CITIZENS INCREASINGLY CLOSER TO INSTITUTIONS. IN THIS SENSE, THE RESEARCH AIMED TO DEVELOP A VIRTUAL ASSISTANT PROTOTYPE (CHATBOT) TO ASSIST TAX EDUCATION IN ORDER TO PROMOTE KNOWLEDGE AND AWARENESS AMONG CITIZENS BEYOND TAX ISSUES. THE PROPOSED CHATBOT IS A RULES-BASED ARTIFICIAL INTELLIGENCE SOFTWARE, DEVELOPED IN A FREE PROGRAM ACCESSIBLE BY CELL PHONE THAT WORKS INTEGRATED WITH THE TELEGRAM MESSAGING APPLICATION, INTERACTING WITH USERS IN A NATURAL WAY TO INFORM AND CLARIFY DOUBTS. THE METHODOLOGIES APPLIED WERE BIBLIOGRAPHICAL RESEARCH, AIMING TO CLARIFY CONCEPTS RELATED TO TAX EDUCATION, ARTIFICIAL INTELLIGENCE AND CHATBOT; AND DOCUMENTARY RESEARCH, WHICH ANALYZED THE CONTENT OF REPORTS FROM THE “CALL CENTER” AND “FALE CONOSCO” CUSTOMER SERVICE CENTERS OF THE BAHIA STATE FINANCE DEPARTMENT. THE RESULTS INDICATE THAT, ALTHOUGH SOME AREAS OF THE GOVERNMENT ARE ALREADY USING ARTIFICIAL INTELLIGENCE TO IMPROVE TAX COLLECTION, SPEED UP THE PROVISION OF SERVICES AND IMPROVE THEIR PROCESSES, INITIATIVES RELATED TO TAX EDUCATION STILL FACE CHALLENGES SUCH AS EXCESSIVE TECHNICALITY, INADEQUATE APPROACHES AND LACK OF PRIORITY OVER OTHER SOCIAL DEMANDS. THE STUDY INDICATES THAT CHATBOT TECHNOLOGY STILL NEEDS TO OVERCOME THE CHALLENGE OF ACCESSIBILITY AND DIGITAL EXCLUSION FOR SOCIALLY VULNERABLE PEOPLE WITHOUT ACCESS TO THE INTERNET. ON THE OTHER HAND, THE CHATBOT PROTOTYPE HAS THE POTENTIAL TO DEMOCRATIZE KNOWLEDGE, USING ACCESSIBLE LANGUAGE, REACHING AN AUDIENCE FAMILIAR WITH DIGITAL CONTENT WITH CLEAR AND CONCISE EXPLANATIONS OF COMPLEX TAX CONCEPTS.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SUBSTANDARD;FALSIFIED;MEDICATIONS;MACHINE LEARNING;PREDICTIVE MODEL</t>
+          <t>EDUCAÇÃO TRIBUTÁRIA;INTELIGÊNCIA ARTIFICIAL;CONSCIÊNCIA SOCIAL;PARTICIPAÇÃO CIDADÃ</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>SUBSTANDARD;FALSIFIED;MEDICINES;MACHINE LEARNING;PREDICTIVE MODEL</t>
+          <t>TAX EDUCATION;ARTIFICIAL INTELLIGENCE;SOCIAL CONSCIOUSNESS;CITIZEN PARTICIPATION</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -6269,14 +6269,14 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Aprendizado de máquina (ML)</t>
+          <t>IA em sentido estrito</t>
         </is>
       </c>
       <c r="M42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="b">
         <v>0</v>
@@ -6289,41 +6289,41 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>VITOR AZEVEDO PEREIRA PONTUAL</t>
+          <t>JOSE PEREIRA MASCARENHAS BISNETO</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>AVALIAÇÃO E MONITORAMENTO DE POLÍTICAS PÚBLICAS</t>
+          <t>GESTÃO DE POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>ESCOLA NACIONAL DE ADMINISTRAÇÃO PÚBLICA</t>
+          <t>UNIVERSIDADE FEDERAL DO RECÔNCAVO DA BAHIA</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>ENAP</t>
+          <t>UFRB</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>CENTRO-OESTE</t>
+          <t>NORDESTE</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>DISTRITO FEDERAL</t>
+          <t>BAHIA</t>
         </is>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -6342,16 +6342,16 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16376007</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16426209</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>16376007</t>
+          <t>16426209</t>
         </is>
       </c>
       <c r="AE42" t="n">
-        <v>3441509</v>
+        <v>3938979</v>
       </c>
     </row>
     <row r="43">
@@ -6370,37 +6370,37 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LUIZ MORAES DE ALMEIDA JUNIOR</t>
+          <t>ROBERTA GUERRA HOLDER BELFORT CAMPOS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CHATBOT: UM PROTÓTIPO DE ASSISTENTE VIRTUAL COMO FERRAMENTA DE EDUCAÇÃO FISCAL NA SECRETARIA DA FAZENDA DA BAHIA</t>
+          <t>DO PLENÁRIO AO FEED: ANÁLISE DOS PERFIS DOS SENADORES DA 57.ª LEGISLATURA NO INSTAGRAM</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>PARA AMPLIAR O ACESSO A INFORMAÇÃO, A ADMINISTRAÇÃO PÚBLICA PRECISA DISPOR DE INSTRUMENTOS CAPAZES DE INFORMAR DE MANEIRA EFICIENTE E SIMPLIFICADA, VISANDO APROXIMAR CADA VEZ MAIS O CIDADÃO DAS INSTITUIÇÕES. NESTE SENTIDO, A PESQUISA OBJETIVOU DESENVOLVER UM PROTÓTIPO DE ASSISTENTE VIRTUAL (CHATBOT) PARA AUXILIAR A EDUCAÇÃO FISCAL NO SENTIDO DE PROMOVER O CONHECIMENTO E A CONSCIENTIZAÇÃO DOS CIDADÃOS PARA ALÉM DAS QUESTÕES TRIBUTÁRIAS. O CHATBOT PROPOSTO É UM SOFTWARE DE INTELIGÊNCIA ARTIFICIAL BASEADO EM REGRAS, DESENVOLVIDO EM PROGRAMA GRATUITO E ACESSÍVEL PELO CELULAR QUE FUNCIONA INTEGRADO AO APLICATIVO DE MENSAGENS TELEGRAM, INTERAGINDO COM OS USUÁRIOS DE FORMA NATURAL PARA INFORMAR E ESCLARECER DÚVIDAS. AS METODOLOGIAS APLICADAS FORAM A PESQUISA BIBLIOGRÁFICA, VISANDO ESCLARECER CONCEITOS RELACIONADOS A EDUCAÇÃO FISCAL, INTELIGÊNCIA ARTIFICIAL E CHATBOT; E A PESQUISA DOCUMENTAL, QUE ANALISOU O CONTEÚDO DOS RELATÓRIOS DAS CENTRAIS DE ATENDIMENTO “CALL CENTER” E “FALE CONOSCO” DA SECRETARIA DA FAZENDA DO ESTADO DA BAHIA. OS RESULTADOS INDICAM QUE, EMBORA ALGUMAS ÁREAS DO GOVERNO JÁ ESTEJAM UTILIZANDO A INTELIGÊNCIA ARTIFICIAL PARA MELHORAR A ARRECADAÇÃO DE IMPOSTOS, AGILIZAR A PRESTAÇÃO DE SERVIÇOS E APRIMORAR SEUS PROCESSOS, AS INICIATIVAS RELACIONADAS À EDUCAÇÃO FISCAL AINDA ENFRENTAM DESAFIOS COMO O EXCESSO DE TECNICISMO, ABORDAGENS INADEQUADAS E FALTA DE PRIORIDADE SOBRE OUTRAS DEMANDAS SOCIAIS. O ESTUDO SINALIZA QUE A TECNOLOGIA CHATBOT AINDA PRECISA SUPERAR O DESAFIO DA ACESSIBILIDADE E EXCLUSÃO DIGITAL DAS PESSOAS SOCIALMENTE VULNERÁVEIS SEM ACESSO A REDE DE INTERNET. POR OUTRO LADO, O PROTÓTIPO DO CHATBOT TEM O POTENCIAL DE DEMOCRATIZAR O CONHECIMENTO, USANDO LINGUAGEM ACESSÍVEL ALCANÇANDO UM PÚBLICO FAMILIARIZADO COM CONTEÚDO DIGITAL COM EXPLICAÇÕES CLARAS E CONCISAS SOBRE CONCEITOS TRIBUTÁRIOS COMPLEXOS.</t>
+          <t>O TRABALHO BUSCA ESTUDAR A CONSTRUÇÃO DE IDENTIDADE POLÍTICA E AS ESTRATÉGIAS COMUNICATIVAS DESENVOLVIDAS PELOS SENADORES DA REPÚBLICA DA 57ª LEGISLATURA NA REDE SOCIAL INSTAGRAM, DURANTE TODO O ANO DE 2023, A PARTIR DE ANÁLISE LEXICAL AUTOMATIZADA DAS POSTAGENS REALIZADA PELO PROGRAMA IRAMUTEQ CONJUGADA COM ANÁLISE NO CHATGPT. A PESQUISA FUNDAMENTA-SE NOS CONCEITOS DE REPRESENTAÇÃO SIMBÓLICA, REIVINDICAÇÃO REPRESENTATIVA E CONEXÃO ELEITORAL, EXPLORANDO COMO ESTES MOLDAM AS ESTRATÉGIAS COMUNICATIVAS E A CONSTRUÇÃO DE IDENTIDADE DOS PARLAMENTARES, EVIDENCIANDO A INTERAÇÃO ENTRE POLÍTICOS E CIDADÃOS NAS REDES SOCIAIS. ENTRE OS RESULTADOS, OBSERVAM-SE DIFERENTES E PERSONALIZADAS ESTRATÉGIAS UTILIZADAS POR ESSES ATORES POLÍTICOS, COMO A DESVINCULAÇÃO PARTIDÁRIA, O FOCO REGIONAL, A COMBINAÇÃO ENTRE O PÚBLICO E O PRIVADO; O ANTAGONISMO POLÍTICO, ALÉM DE DIFERENÇAS NA COMUNICAÇÃO COM RELAÇÃO AO GÊNERO DO PARLAMENTAR. ADICIONALMENTE, OBSERVOU-SE QUE A “PERFORMANCE DE ATAQUE” E AS PAUTAS DE CONFLITO, UTILIZADAS PRINCIPALMENTE POR PARLAMENTARES DE DIREITA, SÃO AS ESTRATÉGIAS QUE MAIS ALCANÇAM ENGAJAMENTO NO INSTAGRAM.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CHATBOT: A VIRTUAL ASSISTANT PROTOTYPE AS A TAX EDUCATION TOOL AT THE BAHIA FINANCE DEPARTMENT TO EXPAND ACCESS TO INFORMATION, THE PUBLIC ADMINISTRATION NEEDS TO HAVE INSTRUMENTS CAPABLE OF PROVIDING INFORMATION IN AN EFFICIENT AND SIMPLIFIED MANNER, AIMING TO BRING CITIZENS INCREASINGLY CLOSER TO INSTITUTIONS. IN THIS SENSE, THE RESEARCH AIMED TO DEVELOP A VIRTUAL ASSISTANT PROTOTYPE (CHATBOT) TO ASSIST TAX EDUCATION IN ORDER TO PROMOTE KNOWLEDGE AND AWARENESS AMONG CITIZENS BEYOND TAX ISSUES. THE PROPOSED CHATBOT IS A RULES-BASED ARTIFICIAL INTELLIGENCE SOFTWARE, DEVELOPED IN A FREE PROGRAM ACCESSIBLE BY CELL PHONE THAT WORKS INTEGRATED WITH THE TELEGRAM MESSAGING APPLICATION, INTERACTING WITH USERS IN A NATURAL WAY TO INFORM AND CLARIFY DOUBTS. THE METHODOLOGIES APPLIED WERE BIBLIOGRAPHICAL RESEARCH, AIMING TO CLARIFY CONCEPTS RELATED TO TAX EDUCATION, ARTIFICIAL INTELLIGENCE AND CHATBOT; AND DOCUMENTARY RESEARCH, WHICH ANALYZED THE CONTENT OF REPORTS FROM THE “CALL CENTER” AND “FALE CONOSCO” CUSTOMER SERVICE CENTERS OF THE BAHIA STATE FINANCE DEPARTMENT. THE RESULTS INDICATE THAT, ALTHOUGH SOME AREAS OF THE GOVERNMENT ARE ALREADY USING ARTIFICIAL INTELLIGENCE TO IMPROVE TAX COLLECTION, SPEED UP THE PROVISION OF SERVICES AND IMPROVE THEIR PROCESSES, INITIATIVES RELATED TO TAX EDUCATION STILL FACE CHALLENGES SUCH AS EXCESSIVE TECHNICALITY, INADEQUATE APPROACHES AND LACK OF PRIORITY OVER OTHER SOCIAL DEMANDS. THE STUDY INDICATES THAT CHATBOT TECHNOLOGY STILL NEEDS TO OVERCOME THE CHALLENGE OF ACCESSIBILITY AND DIGITAL EXCLUSION FOR SOCIALLY VULNERABLE PEOPLE WITHOUT ACCESS TO THE INTERNET. ON THE OTHER HAND, THE CHATBOT PROTOTYPE HAS THE POTENTIAL TO DEMOCRATIZE KNOWLEDGE, USING ACCESSIBLE LANGUAGE, REACHING AN AUDIENCE FAMILIAR WITH DIGITAL CONTENT WITH CLEAR AND CONCISE EXPLANATIONS OF COMPLEX TAX CONCEPTS.</t>
+          <t>THIS STUDY AIMS TO EXPLORE THE CONSTRUCTION OF POLITICAL IDENTITY AND COMMUNICATIVE STRATEGIES DEVELOPED BY SENATORS OF THE 57TH LEGISLATURE IN BRAZIL, USING THE SOCIAL NETWORK INSTAGRAM, THROUGHOUT THE YEAR 2023. THIS EXPLORATION IS CONDUCTED THROUGH AUTOMATED LEXICAL ANALYSIS OF POSTS USING THE IRAMUTEQ PROGRAM, COMBINED WITH ANALYSIS IN CHATGPT. THE RESEARCH IS BASED ON THE CONCEPTS OF SYMBOLIC REPRESENTATION, REPRESENTATIVE CLAIM AND ELECTORAL CONNECTION, EXPLORING HOW THESE SHAPE THE COMMUNICATIVE STRATEGIES AND IDENTITY CONSTRUCTION OF THE PARLIAMENTARIANS, HIGHLIGHTING THE INTERACTION BETWEEN POLITICIANS AND CITIZENS ON SOCIAL MEDIA. THE FINDINGS REVEAL A RANGE OF DISTINCT AND PERSONALIZED STRATEGIES EMPLOYED BY THESE POLITICAL ACTORS ON THIS PLATFORM. THESE STRATEGIES INCLUDE DISASSOCIATION FROM PARTY LINES, A FOCUS ON REGIONAL ISSUES, AND A BLEND OF PUBLIC AND PRIVATE PERSONAS. VARIATIONS IN COMMUNICATION STYLES ARE NOTED IN RELATION TO THE GENDER OF THE PARLIAMENTARIANS. ADDITIONALLY, IT WAS OBSERVED THAT “ATTACK PERFORMANCES” AND CONFLICT-DRIVEN AGENDAS, MAINLY USED BY RIGHT-WING PARLIAMENTARIANS, ARE THE STRATEGIES THAT GENERATE THE HIGHEST ENGAGEMENT ON INSTAGRAM.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>EDUCAÇÃO TRIBUTÁRIA;INTELIGÊNCIA ARTIFICIAL;CONSCIÊNCIA SOCIAL;PARTICIPAÇÃO CIDADÃ</t>
+          <t>PODER LEGISLATIVO;PARLAMENTO DIGITAL;INSTAGRAM;MANDATOS DIGITAIS;COMUNICAÇÃO POLÍTICA;SENADO FEDERAL</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>TAX EDUCATION;ARTIFICIAL INTELLIGENCE;SOCIAL CONSCIOUSNESS;CITIZEN PARTICIPATION</t>
+          <t>DIGITAL PARLIAMENT;INSTAGRAM;DIGITAL MANDATES;POLITICAL COMMUNICATION;FEDERAL SENATE</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -6410,61 +6410,61 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>IA em sentido estrito</t>
+          <t>Modelos de linguagem &amp; IA generativa</t>
         </is>
       </c>
       <c r="M43" t="b">
+        <v>0</v>
+      </c>
+      <c r="N43" t="b">
+        <v>0</v>
+      </c>
+      <c r="O43" t="b">
+        <v>0</v>
+      </c>
+      <c r="P43" t="b">
         <v>1</v>
       </c>
-      <c r="N43" t="b">
-        <v>0</v>
-      </c>
-      <c r="O43" t="b">
-        <v>0</v>
-      </c>
-      <c r="P43" t="b">
-        <v>0</v>
-      </c>
       <c r="Q43" t="b">
         <v>0</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>JOSE PEREIRA MASCARENHAS BISNETO</t>
+          <t>CRISTIANE BRUM BERNARDES</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>GESTÃO DE POLÍTICAS PÚBLICAS</t>
+          <t>PODER LEGISLATIVO</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DO RECÔNCAVO DA BAHIA</t>
+          <t>CENTRO DE FORMAÇÃO, TREINAMENTO E APERFEIÇOAMENTO</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>UFRB</t>
+          <t>CEFOR</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>NORDESTE</t>
+          <t>CENTRO-OESTE</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>BAHIA</t>
+          <t>DISTRITO FEDERAL</t>
         </is>
       </c>
       <c r="Y43" t="n">
-        <v>92</v>
+        <v>152</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>POLÍTICAS PÚBLICAS</t>
+          <t>NÃO SE APLICA</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -6483,16 +6483,16 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16426209</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16648671</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>16426209</t>
+          <t>16648671</t>
         </is>
       </c>
       <c r="AE43" t="n">
-        <v>3938979</v>
+        <v>4338098</v>
       </c>
     </row>
     <row r="44">
@@ -6511,37 +6511,37 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ROBERTA GUERRA HOLDER BELFORT CAMPOS</t>
+          <t>RUBENS VASCONCELLOS TERRA NETO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>DO PLENÁRIO AO FEED: ANÁLISE DOS PERFIS DOS SENADORES DA 57.ª LEGISLATURA NO INSTAGRAM</t>
+          <t>APRENDIZAGEM DE MÁQUINA NO COMBATE AO SOBREPREÇO DAS COMPRAS PÚBLICAS: ANÁLISE DE PESQUISAS DE PREÇOS DE CONTRATAÇÕES DO SENADO FEDERAL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>O TRABALHO BUSCA ESTUDAR A CONSTRUÇÃO DE IDENTIDADE POLÍTICA E AS ESTRATÉGIAS COMUNICATIVAS DESENVOLVIDAS PELOS SENADORES DA REPÚBLICA DA 57ª LEGISLATURA NA REDE SOCIAL INSTAGRAM, DURANTE TODO O ANO DE 2023, A PARTIR DE ANÁLISE LEXICAL AUTOMATIZADA DAS POSTAGENS REALIZADA PELO PROGRAMA IRAMUTEQ CONJUGADA COM ANÁLISE NO CHATGPT. A PESQUISA FUNDAMENTA-SE NOS CONCEITOS DE REPRESENTAÇÃO SIMBÓLICA, REIVINDICAÇÃO REPRESENTATIVA E CONEXÃO ELEITORAL, EXPLORANDO COMO ESTES MOLDAM AS ESTRATÉGIAS COMUNICATIVAS E A CONSTRUÇÃO DE IDENTIDADE DOS PARLAMENTARES, EVIDENCIANDO A INTERAÇÃO ENTRE POLÍTICOS E CIDADÃOS NAS REDES SOCIAIS. ENTRE OS RESULTADOS, OBSERVAM-SE DIFERENTES E PERSONALIZADAS ESTRATÉGIAS UTILIZADAS POR ESSES ATORES POLÍTICOS, COMO A DESVINCULAÇÃO PARTIDÁRIA, O FOCO REGIONAL, A COMBINAÇÃO ENTRE O PÚBLICO E O PRIVADO; O ANTAGONISMO POLÍTICO, ALÉM DE DIFERENÇAS NA COMUNICAÇÃO COM RELAÇÃO AO GÊNERO DO PARLAMENTAR. ADICIONALMENTE, OBSERVOU-SE QUE A “PERFORMANCE DE ATAQUE” E AS PAUTAS DE CONFLITO, UTILIZADAS PRINCIPALMENTE POR PARLAMENTARES DE DIREITA, SÃO AS ESTRATÉGIAS QUE MAIS ALCANÇAM ENGAJAMENTO NO INSTAGRAM.</t>
+          <t>QUANDO O ASSUNTO É COMPRAS PÚBLICAS, O CAMINHO DA LEGALIDADE EXIGE A REALIZAÇÃO DE PROCESSO LICITATÓRIO. A PESQUISA DE PREÇOS É UM DOS PRINCIPAIS ARTEFATOS QUE COMPÕEM O PROCESSO LICITATÓRIO, E TEM COMO FINALIDADE ESTIMAR O MONTANTE DE DINHEIRO QUE PODERÁ SER GASTO NA AVENÇA. A AFERIÇÃO DESSE MONTANTE TEM COMO OBJETIVOS A RESERVA DO VALOR NO ORÇAMENTO E O BALIZAMENTO DE PREÇOS PARA GARANTIR QUE A ADMINISTRAÇÃO PÚBLICA ESTEJA PAGANDO UM PREÇO JUSTO E COMPATÍVEL COM O DE MERCADO. O PRESENTE ESTUDO RELATA PESQUISA DE MESTRADO QUE SE DEDICOU A EXPLORAR E PROCESSAR OS DADOS DE CONTRATAÇÕES PÚBLICAS NOS ANOS DE 2022 E 2023. O PRINCIPAL OBJETIVO CONSISTIU NO DESENVOLVIMENTO DE UMA APLICAÇÃO COM UTILIZAÇÃO DE ALGORITMOS BASEADOS EM APRENDIZAGEM DE MÁQUINA (MACHINE LEARNING), CAPAZES DE INDICAR, A PARTIR DE ESTIMATIVAS DE PROBABILIDADE, POSSÍVEIS INDÍCIOS DE SOBREPREÇOS DURANTE A FASE DE PESQUISA DE PREÇOS EM CONTRATAÇÕES. A CONSTRUÇÃO DA BASE DE DADOS EMPREGADA NO DESENVOLVIMENTO SE UTILIZOU DOS DADOS ABERTOS DE COMPRAS GOVERNAMENTAIS QUE MANTÊM REGISTRO DAS COMPRAS E CONTRATAÇÕES FIRMADAS PELO PODER EXECUTIVO E POR TODAS AS INSTITUIÇÕES QUE UTILIZAM O SISTEMA COMPRASNET. OS DADOS RECUPERADOS SÃO REFERENTES AO PERÍODO DE JANEIRO/2022 ATÉ OUTUBRO/2023 E ESTÃO DISPONÍVEIS EM REPOSITÓRIO PÚBLICO. UM PRIMEIRO PROTÓTIPO DE DETECÇÃO DE SOBREPREÇO DE COMPRAS FOI DESENVOLVIDO COM BASE NA BIBLIOTECA DENOMINADA PYTHON OUTLIER DETECTION (PYOD), QUE APRESENTA DIVERSOS ALGORITMOS DE DETECÇÃO DE ANOMALIA NÃO-SUPERVISIONADOS. PARA A ESCOLHA DOS ALGORITMOS, DEFINIÇÃO DOS PARÂMETROS E SELEÇÃO DO MODELO FORAM FEITOS TESTES EM ATÉ OITO CATEGORIAS DE MATERIAIS. OPTOU-SE POR UTILIZAR NO MODELO O ALGORITMO COPULA-BASED OUTLIER DETECTION (COPOD). PARA AVALIAÇÃO FINAL FORAM UTILIZADAS 13 CATEGORIAS E O MÉTODO DE VALIDAÇÃO CRUZADA CHAMADO DE LEAVEONEOUT (LOOCV).COM BASE NOS RESULTADOS DA PESQUISA, PODEMOS CONCLUIR QUE O MODELO DE DETECÇÃO DE SOBREPREÇO ALCANÇOU UM RECALL MÉDIO DE 99,54% E UMA ACURÁCIA DE 90,68%. ESSES NÚMEROS INDICAM QUE O MODELO É ALTAMENTE SENSÍVEL NA IDENTIFICAÇÃO DE CASOS DE SOBREPREÇO, MINIMIZANDO A OCORRÊNCIA DE FALSOS NEGATIVOS. ALÉM DISSO, EM UMA PESQUISA COM GESTORES DO SENADO FEDERAL, ELES AVALIARAM O SISTEMA COMO ÚTIL NA MAIORIA DAS SITUAÇÕES E RESSALTARAM QUE ELE PODE REDUZIR O ESFORÇO NECESSÁRIO PARA PESQUISAS DE PREÇOS EM ATÉ 50%. ESSA CONSTATAÇÃO SUGERE QUE O SISTEMA TEM POTENCIAL PARA SER INCORPORADO AOS PROCESSOS DE COMPRA NO FUTURO.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>THIS STUDY AIMS TO EXPLORE THE CONSTRUCTION OF POLITICAL IDENTITY AND COMMUNICATIVE STRATEGIES DEVELOPED BY SENATORS OF THE 57TH LEGISLATURE IN BRAZIL, USING THE SOCIAL NETWORK INSTAGRAM, THROUGHOUT THE YEAR 2023. THIS EXPLORATION IS CONDUCTED THROUGH AUTOMATED LEXICAL ANALYSIS OF POSTS USING THE IRAMUTEQ PROGRAM, COMBINED WITH ANALYSIS IN CHATGPT. THE RESEARCH IS BASED ON THE CONCEPTS OF SYMBOLIC REPRESENTATION, REPRESENTATIVE CLAIM AND ELECTORAL CONNECTION, EXPLORING HOW THESE SHAPE THE COMMUNICATIVE STRATEGIES AND IDENTITY CONSTRUCTION OF THE PARLIAMENTARIANS, HIGHLIGHTING THE INTERACTION BETWEEN POLITICIANS AND CITIZENS ON SOCIAL MEDIA. THE FINDINGS REVEAL A RANGE OF DISTINCT AND PERSONALIZED STRATEGIES EMPLOYED BY THESE POLITICAL ACTORS ON THIS PLATFORM. THESE STRATEGIES INCLUDE DISASSOCIATION FROM PARTY LINES, A FOCUS ON REGIONAL ISSUES, AND A BLEND OF PUBLIC AND PRIVATE PERSONAS. VARIATIONS IN COMMUNICATION STYLES ARE NOTED IN RELATION TO THE GENDER OF THE PARLIAMENTARIANS. ADDITIONALLY, IT WAS OBSERVED THAT “ATTACK PERFORMANCES” AND CONFLICT-DRIVEN AGENDAS, MAINLY USED BY RIGHT-WING PARLIAMENTARIANS, ARE THE STRATEGIES THAT GENERATE THE HIGHEST ENGAGEMENT ON INSTAGRAM.</t>
+          <t>WHEN IT COMES TO PUBLIC ACQUISITIONS, THE PATH TO LEGALITY REQUIRES A BIDDING PROCESS. PRICE RESEARCH IS ONE OF THE MAIN ARTIFACTS THAT MAKE UP THE BIDDING PROCESS, AND AIMS TO ESTIMATE THE AMOUNT OF MONEY THAT CAN BE SPENT ON THE CONTRACT. THE PURPOSE OF MEASURING THIS AMOUNT IS TO RESERVE THE AMOUNT IN THE BUDGET AND SET PRICES TO ENSURE THAT THE PUBLIC ADMINISTRATION IS PAYING A FAIR PRICE COMPATIBLE WITH THE MARKET. THE PRESENT STUDY REPORTS A MASTER’S RESEARCH THAT WAS DEDICATED TO EXPLORING AND PROCESSING PUBLIC CONTRACTING DATA IN THE YEARS 2022 AND 2023. THE MAIN OBJECTIVE WAS TO DEVELOPMENT OF AN APPLICATION USING ALGORITHMS BASED ON MACHINE LEARNING, CAPABLE OF INDICATING, BASED ON PROBABILITY ESTIMATES, POSSIBLE SIGNS OF OVERPRICING DURING THE PRICE RESEARCH PHASE IN ACQUISITIONS. THE CONSTRUCTION OF THE DATABASE USED IN THE DEVELOPMENT USED OPEN DATA FROM GOVERNMENT PURCHASES THAT MAINTAIN RECORDS OF PURCHASES AND CONTRACTS SIGNED BY THE POWER EXECUTIVE AND BY ALL INSTITUTIONS THAT USE THE COMPRASNET SYSTEM. THE RECOVERED DATA REFER TO THE PERIOD FROM JANUARY/2022 TO OCTOBER/2023 AND ARE AVAILABLE IN A PUBLIC REPOSITORY. A FIRST PROTOTYPE FOR DETECTING OVERPRICING IN PURCHASES WAS DEVELOPED BASED ON THE LIBRARY CALLED PYTHON OUTLIER DETECTION (PYOD), WHICH PRESENTS SEVERAL ALGORITHMS UNSUPERVISED ANOMALY DETECTION. TO CHOOSE THE ALGORITHMS, DEFINE THE PARAMETERS AND MODEL SELECTION TESTS WERE CARRIED OUT ON UP TO EIGHT MATERIAL CATEGORIES. IT WAS CHOSEN FOR USING THE COPULA-BASED OUTLIER DETECTION (COPOD) ALGORITHM IN THE MODEL. BASED ON THE RESEARCH RESULTS, WE CAN CONCLUDE THAT THE OVERPRICING DETECTION MODEL ACHIEVED AN AVERAGE RECALL OF 99.54% AND AN ACCURACY OF 90.68%. THESE NUMBERS INDICATE THAT THE MODEL IS HIGHLY SENSITIVE IN IDENTIFYING OVERPRICING CASES, MINIMIZING FALSE NEGATIVES. ADDITIONALLY, IN A SURVEY WITH MANAGERS FROM THE FEDERAL SENATE, THEY ASSESSED THE SYSTEM AS USEFUL IN MOST SITUATIONS AND HIGHLIGHTED ITS POTENTIAL TO REDUCE THE EFFORT REQUIRED FOR PRICE RESEARCH BY UP TO 50%. THIS FINDING SUGGESTS THAT THE SYSTEM COULD BE INCORPORATED INTO ACQUISITION PROCESSES IN THE FUTURE.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>PODER LEGISLATIVO;PARLAMENTO DIGITAL;INSTAGRAM;MANDATOS DIGITAIS;COMUNICAÇÃO POLÍTICA;SENADO FEDERAL</t>
+          <t>INTELIGÊNCIA ARTIFICIAL;SETOR PÚBLICO;PROCESSO DE CONTRATAÇÃO;SENADO FEDERAL;PODER LEGISLATIVO</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>DIGITAL PARLIAMENT;INSTAGRAM;DIGITAL MANDATES;POLITICAL COMMUNICATION;FEDERAL SENATE</t>
+          <t>ARTIFICIAL INTELLIGENCE;PUBLIC SECTOR;ACQUISITION PROCESS;BRAZILIAN FEDERAL SENATE;LEGISLATIVE BRANCH</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -6551,27 +6551,27 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Modelos de linguagem &amp; IA generativa</t>
+          <t>Aprendizado de máquina (ML); IA em sentido estrito</t>
         </is>
       </c>
       <c r="M44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" t="b">
         <v>0</v>
       </c>
       <c r="P44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="b">
         <v>0</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>CRISTIANE BRUM BERNARDES</t>
+          <t>FABIANO PERUZZO SCHWARTZ</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -6605,7 +6605,7 @@
         </is>
       </c>
       <c r="Y44" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -6624,16 +6624,16 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16648671</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15217157</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>16648671</t>
+          <t>15217157</t>
         </is>
       </c>
       <c r="AE44" t="n">
-        <v>4338098</v>
+        <v>3990787</v>
       </c>
     </row>
     <row r="45">
@@ -6652,37 +6652,37 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RUBENS VASCONCELLOS TERRA NETO</t>
+          <t>SIMONE ALVES RAMOS DE MELO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>APRENDIZAGEM DE MÁQUINA NO COMBATE AO SOBREPREÇO DAS COMPRAS PÚBLICAS: ANÁLISE DE PESQUISAS DE PREÇOS DE CONTRATAÇÕES DO SENADO FEDERAL</t>
+          <t>CARACTERÍSTICAS DE UM SIMULADOR DE RISCOS EMERGENTES APLICADO EM TERMINAIS PORTUÁRIOS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>QUANDO O ASSUNTO É COMPRAS PÚBLICAS, O CAMINHO DA LEGALIDADE EXIGE A REALIZAÇÃO DE PROCESSO LICITATÓRIO. A PESQUISA DE PREÇOS É UM DOS PRINCIPAIS ARTEFATOS QUE COMPÕEM O PROCESSO LICITATÓRIO, E TEM COMO FINALIDADE ESTIMAR O MONTANTE DE DINHEIRO QUE PODERÁ SER GASTO NA AVENÇA. A AFERIÇÃO DESSE MONTANTE TEM COMO OBJETIVOS A RESERVA DO VALOR NO ORÇAMENTO E O BALIZAMENTO DE PREÇOS PARA GARANTIR QUE A ADMINISTRAÇÃO PÚBLICA ESTEJA PAGANDO UM PREÇO JUSTO E COMPATÍVEL COM O DE MERCADO. O PRESENTE ESTUDO RELATA PESQUISA DE MESTRADO QUE SE DEDICOU A EXPLORAR E PROCESSAR OS DADOS DE CONTRATAÇÕES PÚBLICAS NOS ANOS DE 2022 E 2023. O PRINCIPAL OBJETIVO CONSISTIU NO DESENVOLVIMENTO DE UMA APLICAÇÃO COM UTILIZAÇÃO DE ALGORITMOS BASEADOS EM APRENDIZAGEM DE MÁQUINA (MACHINE LEARNING), CAPAZES DE INDICAR, A PARTIR DE ESTIMATIVAS DE PROBABILIDADE, POSSÍVEIS INDÍCIOS DE SOBREPREÇOS DURANTE A FASE DE PESQUISA DE PREÇOS EM CONTRATAÇÕES. A CONSTRUÇÃO DA BASE DE DADOS EMPREGADA NO DESENVOLVIMENTO SE UTILIZOU DOS DADOS ABERTOS DE COMPRAS GOVERNAMENTAIS QUE MANTÊM REGISTRO DAS COMPRAS E CONTRATAÇÕES FIRMADAS PELO PODER EXECUTIVO E POR TODAS AS INSTITUIÇÕES QUE UTILIZAM O SISTEMA COMPRASNET. OS DADOS RECUPERADOS SÃO REFERENTES AO PERÍODO DE JANEIRO/2022 ATÉ OUTUBRO/2023 E ESTÃO DISPONÍVEIS EM REPOSITÓRIO PÚBLICO. UM PRIMEIRO PROTÓTIPO DE DETECÇÃO DE SOBREPREÇO DE COMPRAS FOI DESENVOLVIDO COM BASE NA BIBLIOTECA DENOMINADA PYTHON OUTLIER DETECTION (PYOD), QUE APRESENTA DIVERSOS ALGORITMOS DE DETECÇÃO DE ANOMALIA NÃO-SUPERVISIONADOS. PARA A ESCOLHA DOS ALGORITMOS, DEFINIÇÃO DOS PARÂMETROS E SELEÇÃO DO MODELO FORAM FEITOS TESTES EM ATÉ OITO CATEGORIAS DE MATERIAIS. OPTOU-SE POR UTILIZAR NO MODELO O ALGORITMO COPULA-BASED OUTLIER DETECTION (COPOD). PARA AVALIAÇÃO FINAL FORAM UTILIZADAS 13 CATEGORIAS E O MÉTODO DE VALIDAÇÃO CRUZADA CHAMADO DE LEAVEONEOUT (LOOCV).COM BASE NOS RESULTADOS DA PESQUISA, PODEMOS CONCLUIR QUE O MODELO DE DETECÇÃO DE SOBREPREÇO ALCANÇOU UM RECALL MÉDIO DE 99,54% E UMA ACURÁCIA DE 90,68%. ESSES NÚMEROS INDICAM QUE O MODELO É ALTAMENTE SENSÍVEL NA IDENTIFICAÇÃO DE CASOS DE SOBREPREÇO, MINIMIZANDO A OCORRÊNCIA DE FALSOS NEGATIVOS. ALÉM DISSO, EM UMA PESQUISA COM GESTORES DO SENADO FEDERAL, ELES AVALIARAM O SISTEMA COMO ÚTIL NA MAIORIA DAS SITUAÇÕES E RESSALTARAM QUE ELE PODE REDUZIR O ESFORÇO NECESSÁRIO PARA PESQUISAS DE PREÇOS EM ATÉ 50%. ESSA CONSTATAÇÃO SUGERE QUE O SISTEMA TEM POTENCIAL PARA SER INCORPORADO AOS PROCESSOS DE COMPRA NO FUTURO.</t>
+          <t>O PRESENTE RELATÓRIO TÉCNICO TEM COMO TEMA DE PESQUISA O SIMULADOR DOS EFEITOS DOS RISCOS EMERGENTES EM TERMINAIS PORTUÁRIOS BRASILEIROS. FUNDAMENTA-SE NO CAMPO TEÓRICO E CONCEITUAL DO GERENCIAMENTO DE RISCOS EMERGENTES, QUE INCLUI RISCOS NOVOS E EM CONSTANTE EVOLUÇÃO. ABRANGE TEMAS COMO SEGURANÇA MARÍTIMA, SEGURANÇA PORTUÁRIA, E A REGULAMENTAÇÃO INTERNACIONAL E NACIONAL NO ÂMBITO DA INTERNATIONAL MARITIME ORGANIZATION (IMO), MARINHA DO BRASIL, MINISTÉRIO DE PORTOS E AEROPORTOS E AGÊNCIA NACIONAL DE TRANSPORTES AQUAVIÁRIOS (ANTAQ). O OBJETIVO GERAL DA PESQUISA CONSISTE EM APRESENTAR AS CARACTERÍSTICAS DE UM SIMULADOR DE RISCOS EMERGENTES APLICADO EM TERMINAIS PORTUÁRIOS. A METODOLOGIA ADOTADA INCLUI A ANÁLISE DOS CASOS DOS TERMINAIS PORTUÁRIOS DE VILA VELHA (TVV) E DE GRÃOS DO MARANHÃO (TEGRAM), UMA ABORDAGEM EXPLORATÓRIA E DESCRITIVA, COM ANÁLISE DOCUMENTAL DE RELATÓRIOS DA ANTAQ, ÓRGÃOS REGULADORES E DOCUMENTOS CORPORATIVOS DOS TERMINAIS. DADOS EMPÍRICOS FORAM COLETADOS POR MEIO DE ENTREVISTAS SEMIESTRUTURADAS E QUESTIONÁRIOS APLICADOS A PROFISSIONAIS DOS TERMINAIS, ABRANGENDO ÁREAS COMO SEGURANÇA, MEIO AMBIENTE, TECNOLOGIA DA INFORMAÇÃO, OPERAÇÕES E SEGUROS. A PESQUISA CONCLUI QUE O USO DE TECNOLOGIAS ESPECIALIZADAS PARA O GERENCIAMENTO DE RISCOS EMERGENTES EM TERMINAIS PORTUÁRIOS É FUNDAMENTAL, TRAZENDO INOVAÇÕES QUE PROMETEM MELHORIAS SIGNIFICATIVAS NA SEGURANÇA E EFICIÊNCIA DAS OPERAÇÕES. A COMBINAÇÃO DE INTELIGÊNCIA ARTIFICIAL E PLATAFORMAS CONECTADAS É INDICADA PARA UMA GESTÃO ESTRATÉGICA ROBUSTA. ENTRETANTO, É NECESSÁRIO ASSEGURAR QUE ESSAS FERRAMENTAS SEJAM ACESSÍVEIS E FÁCEIS DE USAR POR TODOS OS USUÁRIOS. ESTA PESQUISA SE DESTACA NO QUE TANGE À INOVAÇÃO E A APLICABILIDADE POR APONTAR QUE O INVESTIMENTO EM TECNOLOGIAS AVANÇADAS, REVELOU-SE ESSENCIAL PARA ENFRENTAR OS DESAFIOS CRESCENTES NO GERENCIAMENTO DE RISCOS NOS PORTOS BRASILEIROS, TRAZENDO BENEFÍCIOS SIGNIFICATIVOS PARA A ADMINISTRAÇÃO PORTUÁRIA DO PAÍS.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>WHEN IT COMES TO PUBLIC ACQUISITIONS, THE PATH TO LEGALITY REQUIRES A BIDDING PROCESS. PRICE RESEARCH IS ONE OF THE MAIN ARTIFACTS THAT MAKE UP THE BIDDING PROCESS, AND AIMS TO ESTIMATE THE AMOUNT OF MONEY THAT CAN BE SPENT ON THE CONTRACT. THE PURPOSE OF MEASURING THIS AMOUNT IS TO RESERVE THE AMOUNT IN THE BUDGET AND SET PRICES TO ENSURE THAT THE PUBLIC ADMINISTRATION IS PAYING A FAIR PRICE COMPATIBLE WITH THE MARKET. THE PRESENT STUDY REPORTS A MASTER’S RESEARCH THAT WAS DEDICATED TO EXPLORING AND PROCESSING PUBLIC CONTRACTING DATA IN THE YEARS 2022 AND 2023. THE MAIN OBJECTIVE WAS TO DEVELOPMENT OF AN APPLICATION USING ALGORITHMS BASED ON MACHINE LEARNING, CAPABLE OF INDICATING, BASED ON PROBABILITY ESTIMATES, POSSIBLE SIGNS OF OVERPRICING DURING THE PRICE RESEARCH PHASE IN ACQUISITIONS. THE CONSTRUCTION OF THE DATABASE USED IN THE DEVELOPMENT USED OPEN DATA FROM GOVERNMENT PURCHASES THAT MAINTAIN RECORDS OF PURCHASES AND CONTRACTS SIGNED BY THE POWER EXECUTIVE AND BY ALL INSTITUTIONS THAT USE THE COMPRASNET SYSTEM. THE RECOVERED DATA REFER TO THE PERIOD FROM JANUARY/2022 TO OCTOBER/2023 AND ARE AVAILABLE IN A PUBLIC REPOSITORY. A FIRST PROTOTYPE FOR DETECTING OVERPRICING IN PURCHASES WAS DEVELOPED BASED ON THE LIBRARY CALLED PYTHON OUTLIER DETECTION (PYOD), WHICH PRESENTS SEVERAL ALGORITHMS UNSUPERVISED ANOMALY DETECTION. TO CHOOSE THE ALGORITHMS, DEFINE THE PARAMETERS AND MODEL SELECTION TESTS WERE CARRIED OUT ON UP TO EIGHT MATERIAL CATEGORIES. IT WAS CHOSEN FOR USING THE COPULA-BASED OUTLIER DETECTION (COPOD) ALGORITHM IN THE MODEL. BASED ON THE RESEARCH RESULTS, WE CAN CONCLUDE THAT THE OVERPRICING DETECTION MODEL ACHIEVED AN AVERAGE RECALL OF 99.54% AND AN ACCURACY OF 90.68%. THESE NUMBERS INDICATE THAT THE MODEL IS HIGHLY SENSITIVE IN IDENTIFYING OVERPRICING CASES, MINIMIZING FALSE NEGATIVES. ADDITIONALLY, IN A SURVEY WITH MANAGERS FROM THE FEDERAL SENATE, THEY ASSESSED THE SYSTEM AS USEFUL IN MOST SITUATIONS AND HIGHLIGHTED ITS POTENTIAL TO REDUCE THE EFFORT REQUIRED FOR PRICE RESEARCH BY UP TO 50%. THIS FINDING SUGGESTS THAT THE SYSTEM COULD BE INCORPORATED INTO ACQUISITION PROCESSES IN THE FUTURE.</t>
+          <t>THE PRESENT TECHNICAL REPORT RESEARCH THEME IS THE SIMULATOR OF THE EFFECTS OF EMERGING RISKS IN BRAZILIAN PORT TERMINALS. IT IS ALSO GROUNDED IN THE THEORETICAL AND CONCEPTUAL FIELD OF EMERGING RISK MANAGEMENT, WHICH INCLUDES NEW AND CONSTANTLY EVOLVING RISKS. ADDITIONALLY, IT COVERS TOPICS SUCH AS MARITIME SECURITY, PORT SECURITY, AND INTERNATIONAL AND NATIONAL REGULATIONS WITHIN THE SCOPE OF THE INTERNATIONAL MARITIME ORGANIZATION (IMO), THE BRAZILIAN NAVY, THE MINISTRY OF PORTS AND AIRPORTS, AND THE NATIONAL WATERWAY TRANSPORTATION AGENCY (ANTAQ). THE MAIN OBJECTIVE WAS TO MODEL A SIMULATOR THAT COULD ESTIMATE AND MITIGATE THE EFFECTS OF EMERGING RISKS, WITH CASE STUDIES OF THE VILA VELHA TERMINAL (TVV) AND THE MARANHÃO GRAINS TERMINAL (TEGRAM). THE METHODOLOGY ADOPTED INCLUDES AN EXPLORATORY AND DESCRIPTIVE APPROACH, WITH DOCUMENTAL ANALYSIS OF REPORTS FROM ANTAQ, REGULATORY BODIES, AND CORPORATE DOCUMENTS FROM THE TERMINALS. EMPIRICAL DATA WAS COLLECTED THROUGH SEMI-STRUCTURED INTERVIEWS AND QUESTIONNAIRES ADMINISTERED TO TERMINAL PROFESSIONALS, COVERING AREAS SUCH AS SECURITY, ENVIRONMENT, INFORMATION TECHNOLOGY, OPERATIONS, AND INSURANCE. THE RESEARCH CONCLUDES THAT THE USE OF SPECIALIZED TECHNOLOGIES FOR MANAGING EMERGING RISKS IN PORT TERMINALS IS FUNDAMENTAL, BRINGING INNOVATIONS THAT PROMISE SIGNIFICANT IMPROVEMENTS IN THE SAFETY AND EFFICIENCY OF OPERATIONS. THE COMBINATION OF ARTIFICIAL INTELLIGENCE AND CONNECTED PLATFORMS IS INDICATIVE OF ROBUST STRATEGIC MANAGEMENT. HOWEVER, IT IS NECESSARY TO ENSURE THAT THESE TOOLS ARE ACCESSIBLE AND EASY TO USE FOR ALL USERS. THIS RESEARCH STANDS OUT IN TERMS OF INNOVATION AND APPLICABILITY BY POINTING OUT THAT INVESTMENT IN ADVANCED TECHNOLOGIES HAS PROVEN TO BE ESSENTIAL IN FACING THE GROWING CHALLENGES IN RISK MANAGEMENT AT BRAZILIAN PORTS, BRINGING SIGNIFICANT BENEFITS TO THE COUNTRY'S PORT ADMINISTRATION</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>INTELIGÊNCIA ARTIFICIAL;SETOR PÚBLICO;PROCESSO DE CONTRATAÇÃO;SENADO FEDERAL;PODER LEGISLATIVO</t>
+          <t>GESTÃO DE RISCOS;RISCOS EMERGENTES;TERMINAIS PORTUÁRIOS;SEGURANÇA PORTUÁRIA;TECNOLOGIA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>ARTIFICIAL INTELLIGENCE;PUBLIC SECTOR;ACQUISITION PROCESS;BRAZILIAN FEDERAL SENATE;LEGISLATIVE BRANCH</t>
+          <t>RISK MANAGEMENT;EMERGING RISKS;PORT TERMINALS;PORT SECURITY;TECHNOLOGY</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -6692,14 +6692,14 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Aprendizado de máquina (ML); IA em sentido estrito</t>
+          <t>IA em sentido estrito</t>
         </is>
       </c>
       <c r="M45" t="b">
         <v>1</v>
       </c>
       <c r="N45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="b">
         <v>0</v>
@@ -6712,41 +6712,41 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>FABIANO PERUZZO SCHWARTZ</t>
+          <t>CLAUDIO RODRIGUES CORREA</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>PODER LEGISLATIVO</t>
+          <t>ESTUDOS MARÍTIMOS</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMAÇÃO, TREINAMENTO E APERFEIÇOAMENTO</t>
+          <t>ESCOLA DE GUERRA NAVAL</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>CEFOR</t>
+          <t>EGN</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>CENTRO-OESTE</t>
+          <t>SUDESTE</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>DISTRITO FEDERAL</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="Y45" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -6765,65 +6765,65 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15217157</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16738179</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>15217157</t>
+          <t>16738179</t>
         </is>
       </c>
       <c r="AE45" t="n">
-        <v>3990787</v>
+        <v>4225138</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CIÊNCIA POLÍTICA</t>
+          <t>SOCIOLOGIA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MESTRADO PROFISSIONAL</t>
+          <t>DOUTORADO</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SIMONE ALVES RAMOS DE MELO</t>
+          <t>THAIS CAROLINE LACERDA MATTOS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CARACTERÍSTICAS DE UM SIMULADOR DE RISCOS EMERGENTES APLICADO EM TERMINAIS PORTUÁRIOS</t>
+          <t>“UMA ERA SEM PRECEDENTES” E A GRANDE ESTRATÉGIA DO SONHO CHINÊS DE REJUVENESCIMENTO DA NAÇÃO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>O PRESENTE RELATÓRIO TÉCNICO TEM COMO TEMA DE PESQUISA O SIMULADOR DOS EFEITOS DOS RISCOS EMERGENTES EM TERMINAIS PORTUÁRIOS BRASILEIROS. FUNDAMENTA-SE NO CAMPO TEÓRICO E CONCEITUAL DO GERENCIAMENTO DE RISCOS EMERGENTES, QUE INCLUI RISCOS NOVOS E EM CONSTANTE EVOLUÇÃO. ABRANGE TEMAS COMO SEGURANÇA MARÍTIMA, SEGURANÇA PORTUÁRIA, E A REGULAMENTAÇÃO INTERNACIONAL E NACIONAL NO ÂMBITO DA INTERNATIONAL MARITIME ORGANIZATION (IMO), MARINHA DO BRASIL, MINISTÉRIO DE PORTOS E AEROPORTOS E AGÊNCIA NACIONAL DE TRANSPORTES AQUAVIÁRIOS (ANTAQ). O OBJETIVO GERAL DA PESQUISA CONSISTE EM APRESENTAR AS CARACTERÍSTICAS DE UM SIMULADOR DE RISCOS EMERGENTES APLICADO EM TERMINAIS PORTUÁRIOS. A METODOLOGIA ADOTADA INCLUI A ANÁLISE DOS CASOS DOS TERMINAIS PORTUÁRIOS DE VILA VELHA (TVV) E DE GRÃOS DO MARANHÃO (TEGRAM), UMA ABORDAGEM EXPLORATÓRIA E DESCRITIVA, COM ANÁLISE DOCUMENTAL DE RELATÓRIOS DA ANTAQ, ÓRGÃOS REGULADORES E DOCUMENTOS CORPORATIVOS DOS TERMINAIS. DADOS EMPÍRICOS FORAM COLETADOS POR MEIO DE ENTREVISTAS SEMIESTRUTURADAS E QUESTIONÁRIOS APLICADOS A PROFISSIONAIS DOS TERMINAIS, ABRANGENDO ÁREAS COMO SEGURANÇA, MEIO AMBIENTE, TECNOLOGIA DA INFORMAÇÃO, OPERAÇÕES E SEGUROS. A PESQUISA CONCLUI QUE O USO DE TECNOLOGIAS ESPECIALIZADAS PARA O GERENCIAMENTO DE RISCOS EMERGENTES EM TERMINAIS PORTUÁRIOS É FUNDAMENTAL, TRAZENDO INOVAÇÕES QUE PROMETEM MELHORIAS SIGNIFICATIVAS NA SEGURANÇA E EFICIÊNCIA DAS OPERAÇÕES. A COMBINAÇÃO DE INTELIGÊNCIA ARTIFICIAL E PLATAFORMAS CONECTADAS É INDICADA PARA UMA GESTÃO ESTRATÉGICA ROBUSTA. ENTRETANTO, É NECESSÁRIO ASSEGURAR QUE ESSAS FERRAMENTAS SEJAM ACESSÍVEIS E FÁCEIS DE USAR POR TODOS OS USUÁRIOS. ESTA PESQUISA SE DESTACA NO QUE TANGE À INOVAÇÃO E A APLICABILIDADE POR APONTAR QUE O INVESTIMENTO EM TECNOLOGIAS AVANÇADAS, REVELOU-SE ESSENCIAL PARA ENFRENTAR OS DESAFIOS CRESCENTES NO GERENCIAMENTO DE RISCOS NOS PORTOS BRASILEIROS, TRAZENDO BENEFÍCIOS SIGNIFICATIVOS PARA A ADMINISTRAÇÃO PORTUÁRIA DO PAÍS.</t>
+          <t>NOS ÚLTIMOS ANOS, TÊM SIDO COMUNS, NA MÍDIA ESTATAL, CONGRESSOS E DOCUMENTOS OFICIAIS EMITIDOS PELO PCC DE QUE A CHINA ESTÁ PASSANDO POR “UMA ERA SEM PRECEDENTES” ¿¿¿¿¿¿¿¿¿. O ENFRENTAMENTO DOS DESAFIOS DA NOVA ERA IMPLICARIA UMA NOVA FORMULAÇÃO TEÓRICA DO PARTIDO E DA HISTÓRIA DO DESENVOLVIMENTO DO MARXISMO, COM CONSEQUÊNCIAS PRÁTICAS NA ECONOMIA, GOVERNANÇA INSTITUCIONAL, SOCIEDADE E POLÍTICA EXTERNA DA CHINA, CONFLUINDO NA RESOLUÇÃO DA CONTRADIÇÃO ATUAL, QUAL SEJA, O DESENVOLVIMENTO DESEQUILIBRADO E INADEQUADO FRENTE ÀS CRESCENTES NECESSIDADES DO POVO PARA UMA VIDA MELHOR. FRENTE A ISSO, A PRESENTE TESE TEM POR OBJETIVO ANALISAR OS ELEMENTOS DISTINTIVOS DA ADMINISTRAÇÃO DE XI JINPING EM RELAÇÃO AOS SEUS PRECEDENTES, COM RELAÇÃO TANTO À SUPERESTRUTURA QUANTO ÀS FORÇAS PRODUTIVAS. NUM PRIMEIRO MOMENTO, NOS CONCENTRAREMOS NA QUESTÃO DA IDEOLOGIA POLÍTICA E SOCIAL, TENDO POR BASE A ANÁLISE CONTEUDISTA DO DISCURSO POLÍTICO, EM QUE OCORRE UM FORTE RESGATE DAS TRADIÇÕES HISTÓRICAS DO PAÍS, MESCLADA PELO REAVIVAMENTO DAS POSTURAS MAOISTAS. NUM SEGUNDO MOMENTO, NOS DEBRUÇAREMOS SOBRE A CONSTRUÇÃO DE FONTES DE PODER ESTRUTURAL DA CHINA, TAL COMO DEFINE SUSAN STRANGE, COMO A EVOLUÇÃO DE SUA CAPACIDADE DEFENSIVA, A CONSOLIDAÇÃO DE UM MODERNO PARQUE INDUSTRIAL, A INTERNACIONALIZAÇÃO DO RMB E DA CRIAÇÃO DE BANCOS MULTILATERAIS DE DESENVOLVIMENTO E, POR FIM, PELA FORMAÇÃO TÉCNICO-CIENTÍFICA E OS AVANÇOS EM SEGMENTOS DE PONTA, TAIS COMO TELECOMUNICAÇÕES E INTELIGÊNCIA ARTIFICIAL.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>THE PRESENT TECHNICAL REPORT RESEARCH THEME IS THE SIMULATOR OF THE EFFECTS OF EMERGING RISKS IN BRAZILIAN PORT TERMINALS. IT IS ALSO GROUNDED IN THE THEORETICAL AND CONCEPTUAL FIELD OF EMERGING RISK MANAGEMENT, WHICH INCLUDES NEW AND CONSTANTLY EVOLVING RISKS. ADDITIONALLY, IT COVERS TOPICS SUCH AS MARITIME SECURITY, PORT SECURITY, AND INTERNATIONAL AND NATIONAL REGULATIONS WITHIN THE SCOPE OF THE INTERNATIONAL MARITIME ORGANIZATION (IMO), THE BRAZILIAN NAVY, THE MINISTRY OF PORTS AND AIRPORTS, AND THE NATIONAL WATERWAY TRANSPORTATION AGENCY (ANTAQ). THE MAIN OBJECTIVE WAS TO MODEL A SIMULATOR THAT COULD ESTIMATE AND MITIGATE THE EFFECTS OF EMERGING RISKS, WITH CASE STUDIES OF THE VILA VELHA TERMINAL (TVV) AND THE MARANHÃO GRAINS TERMINAL (TEGRAM). THE METHODOLOGY ADOPTED INCLUDES AN EXPLORATORY AND DESCRIPTIVE APPROACH, WITH DOCUMENTAL ANALYSIS OF REPORTS FROM ANTAQ, REGULATORY BODIES, AND CORPORATE DOCUMENTS FROM THE TERMINALS. EMPIRICAL DATA WAS COLLECTED THROUGH SEMI-STRUCTURED INTERVIEWS AND QUESTIONNAIRES ADMINISTERED TO TERMINAL PROFESSIONALS, COVERING AREAS SUCH AS SECURITY, ENVIRONMENT, INFORMATION TECHNOLOGY, OPERATIONS, AND INSURANCE. THE RESEARCH CONCLUDES THAT THE USE OF SPECIALIZED TECHNOLOGIES FOR MANAGING EMERGING RISKS IN PORT TERMINALS IS FUNDAMENTAL, BRINGING INNOVATIONS THAT PROMISE SIGNIFICANT IMPROVEMENTS IN THE SAFETY AND EFFICIENCY OF OPERATIONS. THE COMBINATION OF ARTIFICIAL INTELLIGENCE AND CONNECTED PLATFORMS IS INDICATIVE OF ROBUST STRATEGIC MANAGEMENT. HOWEVER, IT IS NECESSARY TO ENSURE THAT THESE TOOLS ARE ACCESSIBLE AND EASY TO USE FOR ALL USERS. THIS RESEARCH STANDS OUT IN TERMS OF INNOVATION AND APPLICABILITY BY POINTING OUT THAT INVESTMENT IN ADVANCED TECHNOLOGIES HAS PROVEN TO BE ESSENTIAL IN FACING THE GROWING CHALLENGES IN RISK MANAGEMENT AT BRAZILIAN PORTS, BRINGING SIGNIFICANT BENEFITS TO THE COUNTRY'S PORT ADMINISTRATION</t>
+          <t>IN RECENT YEARS, STATE MEDIA HAS REPORTED CONGRESSES AND OFFICIAL DOCUMENTS ISSUED BY THE CCP THAT CHINA IS EXPERIENCING “AN UNPRECEDENTED ERA” ¿¿¿¿¿¿¿¿¿. FACING THE CHALLENGES OF THE NEW AGE WOULD IMPLY A NEW THEORETICAL FORMULATION OF THE PARTY AND THE HISTORY OF THE DEVELOPMENT OF MARXISM WITH PRACTICAL CONSEQUENCES FOR CHINA'S ECONOMY, INSTITUTIONAL GOVERNANCE, SOCIETY AND FOREIGN POLICY, CONVERGING IN RESOLVING THE CURRENT CONTRADICTION, NAMELY, UNBALANCED AND INADEQUATE DEVELOPMENT IN THE FACE OF THE GROWING NEEDS OF THE PEOPLE FOR A BETTER LIFE. FACED WITH IT, THIS THESIS AIMS TO ANALYZE THE DISTINCTIVE ELEMENTS OF XI JINPING'S ADMINISTRATION IN RELATION TO ITS PRECEDENTS, BOTH IN RELATION TO THE SUPERSTRUCTURE AND ALSO WITH PRODUCTIVE FORCES. AT FIRST, WE FOCUS ON THE ISSUE OF POLITICAL AND SOCIAL IDEOLOGY, BASED ON THE CONTENT ANALYSIS OF POLITICAL DISCOURSE, IN WHICH THERE IS A STRONG RESCUE OF THE COUNTRY'S HISTORICAL TRADITIONS, WHICH IS MIXED BY THE REVIVAL OF MAOIST POSITIONS. IN A SECOND MOMENT, WE FOCUS ON THE CONSTRUCTION OF STRUCTURAL POWER SOURCES IN CHINA, AS DEFINED BY SUSAN STRANGE, AS THE EVOLUTION OF ITS DEFENSE CAPACITY, THE CONSOLIDATION OF A MODERN INDUSTRIAL PARK, THE INTERNATIONALIZATION OF THE RMB AND THE CREATION OF MULTILATERAL BANKS DEVELOPMENT AND, FINALLY, TECHNICAL-SCIENTIFIC TRAINING AND ADVANCES IN CUTTING-EDGE SEGMENTS, SUCH AS TELECOMMUNICATIONS AND ARTIFICIAL INTELLIGENCE.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>GESTÃO DE RISCOS;RISCOS EMERGENTES;TERMINAIS PORTUÁRIOS;SEGURANÇA PORTUÁRIA;TECNOLOGIA</t>
+          <t>UMA ERA SEM PRECEDENTES. XI JINPING. SINICIZAÇÃO DO MARXISMO. PODER ESTRUTURAL. IDEOLOGIA.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>RISK MANAGEMENT;EMERGING RISKS;PORT TERMINALS;PORT SECURITY;TECHNOLOGY</t>
+          <t>AN UNPRECEDENTED ERA. SINICIZATION OF MARXISM. XI JINPING. SINICIZATION OF MARXISM. STRUCTURAL POWER. IDEOLOGY.</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -6853,22 +6853,22 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>CLAUDIO RODRIGUES CORREA</t>
+          <t>MARCOS CORDEIRO PIRES</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>ESTUDOS MARÍTIMOS</t>
+          <t>CIÊNCIAS SOCIAIS</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>ESCOLA DE GUERRA NAVAL</t>
+          <t>UNIVERSIDADE ESTADUAL PAULISTA JÚLIO DE MESQUITA FILHO (MARÍLIA)</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>EGN</t>
+          <t>UNESP-MAR</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -6878,16 +6878,16 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>SÃO PAULO</t>
         </is>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -6901,21 +6901,21 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>CIÊNCIA POLÍTICA E RELAÇÕES INTERNACIONAIS</t>
+          <t>SOCIOLOGIA</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16738179</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11296907</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>16738179</t>
+          <t>11296907</t>
         </is>
       </c>
       <c r="AE46" t="n">
-        <v>4225138</v>
+        <v>1994862</v>
       </c>
     </row>
     <row r="47">
@@ -6930,41 +6930,41 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>THAIS CAROLINE LACERDA MATTOS</t>
+          <t>OSWALDO SOULE JUNIOR</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>“UMA ERA SEM PRECEDENTES” E A GRANDE ESTRATÉGIA DO SONHO CHINÊS DE REJUVENESCIMENTO DA NAÇÃO</t>
+          <t>TECNOLOGIAS DIGITAIS NAS TESES DOS PROGRAMAS DE PÓS GRADUAÇÃO EM CIÊNCIAS SOCIAIS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>NOS ÚLTIMOS ANOS, TÊM SIDO COMUNS, NA MÍDIA ESTATAL, CONGRESSOS E DOCUMENTOS OFICIAIS EMITIDOS PELO PCC DE QUE A CHINA ESTÁ PASSANDO POR “UMA ERA SEM PRECEDENTES” ¿¿¿¿¿¿¿¿¿. O ENFRENTAMENTO DOS DESAFIOS DA NOVA ERA IMPLICARIA UMA NOVA FORMULAÇÃO TEÓRICA DO PARTIDO E DA HISTÓRIA DO DESENVOLVIMENTO DO MARXISMO, COM CONSEQUÊNCIAS PRÁTICAS NA ECONOMIA, GOVERNANÇA INSTITUCIONAL, SOCIEDADE E POLÍTICA EXTERNA DA CHINA, CONFLUINDO NA RESOLUÇÃO DA CONTRADIÇÃO ATUAL, QUAL SEJA, O DESENVOLVIMENTO DESEQUILIBRADO E INADEQUADO FRENTE ÀS CRESCENTES NECESSIDADES DO POVO PARA UMA VIDA MELHOR. FRENTE A ISSO, A PRESENTE TESE TEM POR OBJETIVO ANALISAR OS ELEMENTOS DISTINTIVOS DA ADMINISTRAÇÃO DE XI JINPING EM RELAÇÃO AOS SEUS PRECEDENTES, COM RELAÇÃO TANTO À SUPERESTRUTURA QUANTO ÀS FORÇAS PRODUTIVAS. NUM PRIMEIRO MOMENTO, NOS CONCENTRAREMOS NA QUESTÃO DA IDEOLOGIA POLÍTICA E SOCIAL, TENDO POR BASE A ANÁLISE CONTEUDISTA DO DISCURSO POLÍTICO, EM QUE OCORRE UM FORTE RESGATE DAS TRADIÇÕES HISTÓRICAS DO PAÍS, MESCLADA PELO REAVIVAMENTO DAS POSTURAS MAOISTAS. NUM SEGUNDO MOMENTO, NOS DEBRUÇAREMOS SOBRE A CONSTRUÇÃO DE FONTES DE PODER ESTRUTURAL DA CHINA, TAL COMO DEFINE SUSAN STRANGE, COMO A EVOLUÇÃO DE SUA CAPACIDADE DEFENSIVA, A CONSOLIDAÇÃO DE UM MODERNO PARQUE INDUSTRIAL, A INTERNACIONALIZAÇÃO DO RMB E DA CRIAÇÃO DE BANCOS MULTILATERAIS DE DESENVOLVIMENTO E, POR FIM, PELA FORMAÇÃO TÉCNICO-CIENTÍFICA E OS AVANÇOS EM SEGMENTOS DE PONTA, TAIS COMO TELECOMUNICAÇÕES E INTELIGÊNCIA ARTIFICIAL.</t>
+          <t>A SOCIEDADE ATUAL É CADA VEZ MAIS MULTICONECTADA ATRAVÉS DO USO CRESCENTE DAS TECNOLOGIAS DIGITAIS, AQUI CONSIDERADA COMO TODA TECNOLOGIA BASEADA EM ESTRUTURAS DIGITAIS, COM BASE BINÁRIA. ESSA CONECTIVIDADE GERA UM VOLUME DE DADOS MUITO GRANDE, DAS MAIS VARIADAS FORMAS E A ALTÍSSIMA VELOCIDADE. A ESSE AMBIENTE DEU-SE O NOME DE BIG DATA. O USO DO BIG DATA ASSOCIADO AS TECNOLOGIAS DIGITAIS, EM ESPECIAL A DE INTELIGÊNCIA ARTIFICIAL, VEM MOLDANDO O COMPORTAMENTO DA SOCIEDADE. O ARGUMENTO DA TESE É DE QUE O USO DAS TECNOLOGIAS DIGITAIS, COM DESTAQUE AS QUE FAZEM USO DA INTELIGÊNCIA ARTIFICIAL, SÃO FERRAMENTAS QUE PODEM APRIMORAR AS PESQUISAS EM CIÊNCIAS SOCIAIS, MAS QUE SÃO UTILIZADAS DE FORMA INCOMPLETA NAS PESQUISAS DE DOUTORADO EM CIÊNCIAS SOCIAIS DOS PROGRAMAS DE PÓS-GRADUAÇÃO STRICTO SENSU. A PESQUISA TEVE POR OBJETIVO IDENTIFICAR COMO AS TECNOLOGIAS DIGITAIS FORAM INCORPORADAS AOS ESTUDOS DE PÓS-GRADUAÇÃO STRICTO SENSU EM CIÊNCIAS SOCIAIS, NO NÍVEL DE DOUTORADO, NAS UNIVERSIDADES QUE ATUAM NO ESTADO DE SÃO PAULO, BEM COMO, IDENTIFICAR NOVAS HABILIDADES E CONHECIMENTOS NECESSÁRIOS AOS PESQUISADORES EM CIÊNCIAS SOCIAIS. PARA ALCANÇAR ESSES OBJETIVOS, FEZ-SE, EM UMA PRIMEIRA ETAPA, UMA PESQUISA BIBLIOGRÁFICA PARA A COMPREENSÃO DO TEMA E, EM UMA SEGUNDA ETAPA, DE UMA PESQUISA DOCUMENTACIONAL EM TESES EM CIÊNCIAS SOCIAIS DAS UNIVERSIDADES QUE ATUAM NO ESTADO DE SÃO PAULO, ENTRE OS ANOS 2017 E 2022, COM O OBJETIVO DE IDENTIFICAR COMO ESSE TEMA TEM SIDO TRATADO, SEJA UTILIZANDO ESSAS TECNOLOGIAS COMO RECURSO OU COMO OBJETO DE PESQUISA, AO ESTUDAR OS SEU IMPACTOS NA SOCIEDADE. OS DADOS COLETADOS APONTAM PARA POUCOS ESTUDOS QUE FAZEM USO DAS TECNOLOGIAS DIGITAIS MAIS ATUAIS OU REALIZAM ESTUDOS SOBRE OS SEUS IMPACTOS. PARA O CIENTISTA SOCIAL RECAI O DESAFIO DE COMPREENDER COMO ESTAS TECNOLOGIAS AFETAM SUAS PESQUISAS, SEJA COMO FERRAMENTA DE APOIO, SEJA COMO O ESTUDO DE SEUS IMPACTOS NA SOCIEDADE.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>IN RECENT YEARS, STATE MEDIA HAS REPORTED CONGRESSES AND OFFICIAL DOCUMENTS ISSUED BY THE CCP THAT CHINA IS EXPERIENCING “AN UNPRECEDENTED ERA” ¿¿¿¿¿¿¿¿¿. FACING THE CHALLENGES OF THE NEW AGE WOULD IMPLY A NEW THEORETICAL FORMULATION OF THE PARTY AND THE HISTORY OF THE DEVELOPMENT OF MARXISM WITH PRACTICAL CONSEQUENCES FOR CHINA'S ECONOMY, INSTITUTIONAL GOVERNANCE, SOCIETY AND FOREIGN POLICY, CONVERGING IN RESOLVING THE CURRENT CONTRADICTION, NAMELY, UNBALANCED AND INADEQUATE DEVELOPMENT IN THE FACE OF THE GROWING NEEDS OF THE PEOPLE FOR A BETTER LIFE. FACED WITH IT, THIS THESIS AIMS TO ANALYZE THE DISTINCTIVE ELEMENTS OF XI JINPING'S ADMINISTRATION IN RELATION TO ITS PRECEDENTS, BOTH IN RELATION TO THE SUPERSTRUCTURE AND ALSO WITH PRODUCTIVE FORCES. AT FIRST, WE FOCUS ON THE ISSUE OF POLITICAL AND SOCIAL IDEOLOGY, BASED ON THE CONTENT ANALYSIS OF POLITICAL DISCOURSE, IN WHICH THERE IS A STRONG RESCUE OF THE COUNTRY'S HISTORICAL TRADITIONS, WHICH IS MIXED BY THE REVIVAL OF MAOIST POSITIONS. IN A SECOND MOMENT, WE FOCUS ON THE CONSTRUCTION OF STRUCTURAL POWER SOURCES IN CHINA, AS DEFINED BY SUSAN STRANGE, AS THE EVOLUTION OF ITS DEFENSE CAPACITY, THE CONSOLIDATION OF A MODERN INDUSTRIAL PARK, THE INTERNATIONALIZATION OF THE RMB AND THE CREATION OF MULTILATERAL BANKS DEVELOPMENT AND, FINALLY, TECHNICAL-SCIENTIFIC TRAINING AND ADVANCES IN CUTTING-EDGE SEGMENTS, SUCH AS TELECOMMUNICATIONS AND ARTIFICIAL INTELLIGENCE.</t>
+          <t>MODERN SOCIETY IS INCREASINGLY MULTI CONNECTED THROUGH DIGITAL TECHNOLOGIES, WHICH IN THIS THESIS ARE CONSIDERED AS ANY TECHNOLOGY BASED ON DIGITAL STRUCTURES AND WITH A BINARY BASE. THIS CONNECTIVITY GENERATES A VAST VOLUME OF DATA, IN THE MOST VARIED FORMS AND AT A VERY HIGH SPEED. THIS ENVIRONMENT IS CALLED BIG DATA. THE USE OF BIG DATA ASSOCIATED WITH DIGITAL TECHNOLOGIES, ESPECIALLY ARTIFICIAL INTELLIGENCE, HAS BEEN SHAPING SOCIETY'S BEHAVIOR. THIS THESIS ARGUES THAT DIGITAL TECHNOLOGIES, ESPECIALLY THOSE THAT MAKE USE OF ARTIFICIAL INTELLIGENCE, ARE TOOLS THAT CAN IMPROVE RESEARCH IN SOCIAL SCIENCES, BUT THAT ARE STILL UNDERUSED IN DOCTORAL RESEARCH IN SOCIAL SCIENCES PROGRAMS. THIS RESEARCH AIMED TO IDENTIFY HOW DIGITAL TECHNOLOGIES WERE INCORPORATED INTO SOCIAL SCIENCES DOCTORAL RESEARCH, IN UNIVERSITIES BASED IN THE STATE OF SÃO PAULO, AS WELL AS TO IDENTIFY NEW SKILLS AND KNOWLEDGE NEEDED BY RESEARCHERS IN SOCIAL SCIENCES. TO ACHIEVE THESE OBJECTIVES, IN THE FIRST STEP, BIBLIOGRAPHICAL RESEARCH WAS CONDUCTED, TO ELABORATE AN OVERVIEW OF THE THEME. IN THE SECOND STEP, A DOCUMENTAL ANALYSIS OF SOCIAL SCIENCES THESES WAS CARRIED OUT TO IDENTIFY HOW THIS TOPIC HAS BEEN ADDRESSED, WHETHER USING THESE TECHNOLOGIES AS A RESOURCE OR AS A RESEARCH OBJECT, WHEN STUDYING THEIR IMPACTS ON SOCIETY. THE ANALYZED THESE INCLUDED THOSE DEFENDED FROM 2017 TO 2022 AND THAT WERE DEVELOPED IN UNIVERSITIES BASED IN THE STATE OF SÃO PAULO. THE RESULTS SHOW THAT FEW OF THESE RESEARCH MAKE USE OF THE MOST CURRENT DIGITAL TECHNOLOGIES OR ASSESS THEIR IMPACTS ON SOCIETY. FOR SOCIAL SCIENTISTS, THERE IS A CHALLENGE TO UNDERSTANDING HOW THESE TECHNOLOGIES AFFECT THEIR RESEARCH, EITHER AS A SUPPORT TOOL OR AS A STUDY OF THEIR IMPACTS ON SOCIETY.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>UMA ERA SEM PRECEDENTES. XI JINPING. SINICIZAÇÃO DO MARXISMO. PODER ESTRUTURAL. IDEOLOGIA.</t>
+          <t>BIG DATA;CIÊNCIAS SOCIAIS;INTELIGÊNCIA ARTIFICIAL;TECNOLOGIAS DIGITAIS</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>AN UNPRECEDENTED ERA. SINICIZATION OF MARXISM. XI JINPING. SINICIZATION OF MARXISM. STRUCTURAL POWER. IDEOLOGY.</t>
+          <t>BIG DATA;SOCIAL SCIENCES;ARTIFICIAL INTELLIGENCE;DIGITAL TECHNOLOGIES.</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>IA em sentido estrito</t>
+          <t>IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M47" t="b">
@@ -6990,11 +6990,11 @@
         <v>0</v>
       </c>
       <c r="Q47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>MARCOS CORDEIRO PIRES</t>
+          <t>MARIA TERESA MICELI KERBAUY</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL PAULISTA JÚLIO DE MESQUITA FILHO (MARÍLIA)</t>
+          <t>UNIVERSIDADE ESTADUAL PAULISTA JÚLIO DE MESQUITA FILHO (ARARAQUARA)</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>UNESP-MAR</t>
+          <t>UNESP-ARAR</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="Y47" t="n">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
@@ -7047,16 +7047,16 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11296907</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12131172</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>11296907</t>
+          <t>12131172</t>
         </is>
       </c>
       <c r="AE47" t="n">
-        <v>1994862</v>
+        <v>1010034</v>
       </c>
     </row>
     <row r="48">
@@ -7071,55 +7071,55 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2022-10-24</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OSWALDO SOULE JUNIOR</t>
+          <t>JULIO MARINHO FERREIRA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TECNOLOGIAS DIGITAIS NAS TESES DOS PROGRAMAS DE PÓS GRADUAÇÃO EM CIÊNCIAS SOCIAIS</t>
+          <t>LECTOR DIGITALIS: A PRÁTICA BOOKTUBE, A CRIAÇÃO DE PÚBLICOS LEITORES NA INTERNET E A SUA RELAÇÃO COM O CAPITALISMO DE VIGILÂNCIA NA PRODUÇÃO DE SOCIABILIDADES LABORAIS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>A SOCIEDADE ATUAL É CADA VEZ MAIS MULTICONECTADA ATRAVÉS DO USO CRESCENTE DAS TECNOLOGIAS DIGITAIS, AQUI CONSIDERADA COMO TODA TECNOLOGIA BASEADA EM ESTRUTURAS DIGITAIS, COM BASE BINÁRIA. ESSA CONECTIVIDADE GERA UM VOLUME DE DADOS MUITO GRANDE, DAS MAIS VARIADAS FORMAS E A ALTÍSSIMA VELOCIDADE. A ESSE AMBIENTE DEU-SE O NOME DE BIG DATA. O USO DO BIG DATA ASSOCIADO AS TECNOLOGIAS DIGITAIS, EM ESPECIAL A DE INTELIGÊNCIA ARTIFICIAL, VEM MOLDANDO O COMPORTAMENTO DA SOCIEDADE. O ARGUMENTO DA TESE É DE QUE O USO DAS TECNOLOGIAS DIGITAIS, COM DESTAQUE AS QUE FAZEM USO DA INTELIGÊNCIA ARTIFICIAL, SÃO FERRAMENTAS QUE PODEM APRIMORAR AS PESQUISAS EM CIÊNCIAS SOCIAIS, MAS QUE SÃO UTILIZADAS DE FORMA INCOMPLETA NAS PESQUISAS DE DOUTORADO EM CIÊNCIAS SOCIAIS DOS PROGRAMAS DE PÓS-GRADUAÇÃO STRICTO SENSU. A PESQUISA TEVE POR OBJETIVO IDENTIFICAR COMO AS TECNOLOGIAS DIGITAIS FORAM INCORPORADAS AOS ESTUDOS DE PÓS-GRADUAÇÃO STRICTO SENSU EM CIÊNCIAS SOCIAIS, NO NÍVEL DE DOUTORADO, NAS UNIVERSIDADES QUE ATUAM NO ESTADO DE SÃO PAULO, BEM COMO, IDENTIFICAR NOVAS HABILIDADES E CONHECIMENTOS NECESSÁRIOS AOS PESQUISADORES EM CIÊNCIAS SOCIAIS. PARA ALCANÇAR ESSES OBJETIVOS, FEZ-SE, EM UMA PRIMEIRA ETAPA, UMA PESQUISA BIBLIOGRÁFICA PARA A COMPREENSÃO DO TEMA E, EM UMA SEGUNDA ETAPA, DE UMA PESQUISA DOCUMENTACIONAL EM TESES EM CIÊNCIAS SOCIAIS DAS UNIVERSIDADES QUE ATUAM NO ESTADO DE SÃO PAULO, ENTRE OS ANOS 2017 E 2022, COM O OBJETIVO DE IDENTIFICAR COMO ESSE TEMA TEM SIDO TRATADO, SEJA UTILIZANDO ESSAS TECNOLOGIAS COMO RECURSO OU COMO OBJETO DE PESQUISA, AO ESTUDAR OS SEU IMPACTOS NA SOCIEDADE. OS DADOS COLETADOS APONTAM PARA POUCOS ESTUDOS QUE FAZEM USO DAS TECNOLOGIAS DIGITAIS MAIS ATUAIS OU REALIZAM ESTUDOS SOBRE OS SEUS IMPACTOS. PARA O CIENTISTA SOCIAL RECAI O DESAFIO DE COMPREENDER COMO ESTAS TECNOLOGIAS AFETAM SUAS PESQUISAS, SEJA COMO FERRAMENTA DE APOIO, SEJA COMO O ESTUDO DE SEUS IMPACTOS NA SOCIEDADE.</t>
+          <t>A PRESENTE TESE DEBRUÇA-SE EM ANALISAR O PAPEL DE UM APARATO TECNOLÓGICO ALTAMENTE COMPLEXO QUE SE MOSTRA PRESENTE EM COMPUTADORES E SEUS SIMILARES, TAIS QUAIS SMARTPHONES, LAPTOPS ETC., EM PRODUZIR SUBJETIVIDADES LEITORAS, TENDO NA PLATAFORMA E MÍDIA SOCIAL DIGITAL YOUTUBE COMO UMA ESPÉCIE DE VETOR À PRODUÇÃO DESSAS AÇÕES. DESSE MODO, ATRAVÉS DE CRIADORES/AS DE CONTEÚDO SOBRE LIVROS E DERIVATIVOS NO REFERIDO YOUTUBE, OS/AS BOOKTUBERS, QUE SE MOSTRAM COMO UMA FORMA VARIANTE DE INFLUENCIADORES DIGITAIS, SE FAZ NECESSÁRIO UMA MIRADA SOCIOLÓGICA ACERCA DO ENTENDIMENTO DESSA PRÁTICA, QUE PODE SER, TANTO AMADORA QUANTO ESPECIALIZADA, E SUA RELAÇÃO COM O MODELO DE UMA SOCIEDADE INFORMATIZADA. E AO MESMO TEMPO, CONTROLADA POR FERRAMENTAS INTERATIVAS, QUE, PODERIAM IMPOR CERTOS ASPECTOS PROBLEMÁTICOS COMO REGULAGEM ALGORÍTMICA, EXPOSIÇÃO DO PRIVADO, CONTROLE, MANIPULAÇÃO DE DADOS E VIGILÂNCIA. NESSE SENTIDO, TENDO NOS LIVROS COMO SUAS FERRAMENTAS PARA PRODUÇÃO DE RESENHAS AMADORAS, CRÍTICAS LITERÁRIAS, OPINIÕES E TAMBÉM COMENTÁRIOS DIVERSOS, ESSAS PESSOAS QUE AGEM, NA MAIOR PARTE DE SEU TEMPO, COMO INFLUENCIADORES DIGITAIS PARA UMA GAMA DE SEGUIDORES E TAMBÉM CURIOSOS ACABAM TORNANDO-SE INDIVÍDUOS QUE PODEM GESTAR A SUA PRÓPRIA IMAGEM EM FUNÇÃO DO DIGITAL. E AO INFLUENCIAR DIGITALMENTE LEITORES A RESPEITO DE CERTAS OBRAS LITERÁRIAS, CRIARIAM VÍNCULOS DE SOCIABILIDADES QUE SE APRESENTAM COMO ELEMENTOS FUNDANTES PARA UMA RELAÇÃO LABORAL LATENTE NO DIGITAL, MAS NÃO APENAS, JÁ QUE ESSE MESMO ATO DE INFLUENCIAR PRESSUPÕE UMA GAMA DE RELAÇÕES QUE PODEM IR ALÉM DA CATEGORIA TRABALHO. DESSE MODO, A PESQUISA SE FIA NA PERCEPÇÃO TEÓRICA DO DIGITAL COMO UM TERRITÓRIO ESTÉTICO E PROBLEMÁTICO, SOMADA À UMA RETÓRICA DE ESPAÇO DE PROGRESSO SOCIAL E TAMBÉM DE LIBERDADE, ALÉM DA INTERAÇÃO E DE SUA RELAÇÃO COM INSTITUIÇÕES SOCIAIS, PRINCIPALMENTE O TRABALHO RECONFIGURADO – UMA DAS MARCAS DA GESTÃO LABORAL ATUAL. EM SEGUIDA, A PARTIR DE UMA PESQUISA TEÓRICA E EMPÍRICA EXECUTADA ATRAVÉS DE ENTREVISTAS, DE ACOMPANHAMENTOS, DE COLETA DE DADOS E DE PERCEPÇÕES MÚLTIPLAS SOMADAS ÀS ANÁLISES DESSES/AS CRIADORES/AS DE CONTEÚDO SOBRE LIVROS NO YT UM DEBATE ACABA SENDO PROPOSTO E DESMEMBRADO AO LONGO DOS CAPÍTULOS. ONDE O FOCO ANALÍTICO VISA PERCEBER SE BIG DATA, ALGORITMOS, BIG TECH, CAPITALISMO DE VIGILÂNCIA (ZUBOFF, 2021) E A CRIAÇÃO DE REPUTAÇÃO ATRAVÉS DA EXPOSIÇÃO DE SI, FUNDIDAS EM PROL DE UMA INTERAÇÃO DIGITAL TORNADA OBRIGATÓRIA NA SOCIEDADE, PODERIAM APRESENTAR, ELEMENTOS PARA UMA INVESTIGAÇÃO SOCIOLÓGICA SOBRE AS CAUSAS E OS EFEITOS SOBRE INDIVÍDUOS QUE PRECISAM ESTAR NESSE AMPLO TERRITÓRIO DIGITAL, PRIMEIRO COMO UMA FORMA DE EXISTÊNCIA REDEFINIDA, E DEPOIS COMO UMA PRODUTORA DE TRABALHO EM CONTEXTOS DE CRISES SOCIAIS, POLÍTICAS, SANITÁRIAS ETC.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>MODERN SOCIETY IS INCREASINGLY MULTI CONNECTED THROUGH DIGITAL TECHNOLOGIES, WHICH IN THIS THESIS ARE CONSIDERED AS ANY TECHNOLOGY BASED ON DIGITAL STRUCTURES AND WITH A BINARY BASE. THIS CONNECTIVITY GENERATES A VAST VOLUME OF DATA, IN THE MOST VARIED FORMS AND AT A VERY HIGH SPEED. THIS ENVIRONMENT IS CALLED BIG DATA. THE USE OF BIG DATA ASSOCIATED WITH DIGITAL TECHNOLOGIES, ESPECIALLY ARTIFICIAL INTELLIGENCE, HAS BEEN SHAPING SOCIETY'S BEHAVIOR. THIS THESIS ARGUES THAT DIGITAL TECHNOLOGIES, ESPECIALLY THOSE THAT MAKE USE OF ARTIFICIAL INTELLIGENCE, ARE TOOLS THAT CAN IMPROVE RESEARCH IN SOCIAL SCIENCES, BUT THAT ARE STILL UNDERUSED IN DOCTORAL RESEARCH IN SOCIAL SCIENCES PROGRAMS. THIS RESEARCH AIMED TO IDENTIFY HOW DIGITAL TECHNOLOGIES WERE INCORPORATED INTO SOCIAL SCIENCES DOCTORAL RESEARCH, IN UNIVERSITIES BASED IN THE STATE OF SÃO PAULO, AS WELL AS TO IDENTIFY NEW SKILLS AND KNOWLEDGE NEEDED BY RESEARCHERS IN SOCIAL SCIENCES. TO ACHIEVE THESE OBJECTIVES, IN THE FIRST STEP, BIBLIOGRAPHICAL RESEARCH WAS CONDUCTED, TO ELABORATE AN OVERVIEW OF THE THEME. IN THE SECOND STEP, A DOCUMENTAL ANALYSIS OF SOCIAL SCIENCES THESES WAS CARRIED OUT TO IDENTIFY HOW THIS TOPIC HAS BEEN ADDRESSED, WHETHER USING THESE TECHNOLOGIES AS A RESOURCE OR AS A RESEARCH OBJECT, WHEN STUDYING THEIR IMPACTS ON SOCIETY. THE ANALYZED THESE INCLUDED THOSE DEFENDED FROM 2017 TO 2022 AND THAT WERE DEVELOPED IN UNIVERSITIES BASED IN THE STATE OF SÃO PAULO. THE RESULTS SHOW THAT FEW OF THESE RESEARCH MAKE USE OF THE MOST CURRENT DIGITAL TECHNOLOGIES OR ASSESS THEIR IMPACTS ON SOCIETY. FOR SOCIAL SCIENTISTS, THERE IS A CHALLENGE TO UNDERSTANDING HOW THESE TECHNOLOGIES AFFECT THEIR RESEARCH, EITHER AS A SUPPORT TOOL OR AS A STUDY OF THEIR IMPACTS ON SOCIETY.</t>
+          <t>THIS THESIS FOCUSES ON ANALYZING THE ROLE OF A HIGHLY COMPLEX TECHNOLOGICAL APPARATUS THAT IS PRESENT IN COMPUTERS AND THEIR SIMILAR ONES, SUCH AS SMARTPHONES, LAPTOPS, ETC., IN PRODUCING READER SUBJECTIVITIES, HAVING YOUTUBE AS A KIND OF PLATFORM AND DIGITAL SOCIAL MEDIA. OF VECTOR TO THE PRODUCTION OF THESE ACTIONS. IN THIS WAY, THROUGH CREATORS OF CONTENT ABOUT BOOKS AND DERIVATIVES ON THE AFOREMENTIONED YOUTUBE, THE BOOKTUBERS, WHO SHOW THEMSELVES AS A VARIANT FORM OF DIGITAL INFLUENCERS, IT IS NECESSARY TO TAKE A SOCIOLOGICAL LOOK AT THE UNDERSTANDING OF THIS PRACTICE, WHICH CAN BE, BOTH AMATEUR AND SPECIALIZED, AND ITS RELATION TO THE MODEL OF A COMPUTERIZED SOCIETY. AND AT THE SAME TIME, CONTROLLED BY INTERACTIVE TOOLS, WHICH COULD IMPOSE CERTAIN PROBLEMATIC ASPECTS SUCH AS ALGORITHMIC REGULATION, EXPOSURE OF THE PRIVATE, CONTROL, DATA MANIPULATION AND SURVEILLANCE. IN THIS SENSE, HAVING BOOKS AS THEIR TOOLS FOR PRODUCING AMATEUR REVIEWS, LITERARY CRITICISM, OPINIONS AND ALSO VARIOUS COMMENTS, THESE PEOPLE WHO ACT, MOST OF THEIR TIME, AS DIGITAL INFLUENCERS FOR A RANGE OF FOLLOWERS AND ALSO CURIOUS PEOPLE END UP BECOMING IF INDIVIDUALS WHO CAN MANAGE THEIR OWN IMAGE IN TERMS OF DIGITAL. AND BY DIGITALLY INFLUENCING READERS ABOUT CERTAIN LITERARY WORKS, THEY WOULD CREATE SOCIABILITY LINKS THAT ARE PRESENTED AS FOUNDING ELEMENTS FOR A LATENT LABOR RELATIONSHIP IN DIGITAL, BUT NOT ONLY, SINCE THIS SAME ACT OF INFLUENCING PRESUPPOSES A RANGE OF RELATIONSHIPS THAT CAN GO BEYOND OF THE JOB CATEGORY. IN THIS WAY, THE RESEARCH IS BASED ON THE THEORETICAL PERCEPTION OF THE DIGITAL AS AN AESTHETIC AND PROBLEMATIC TERRITORY, ADDED TO A RHETORIC OF SPACE OF SOCIAL PROGRESS AND ALSO OF FREEDOM, IN ADDITION TO THE INTERACTION AND ITS RELATIONSHIP WITH SOCIAL INSTITUTIONS, MAINLY THE RECONFIGURED WORK – THE HALLMARKS OF CURRENT LABOR MANAGEMENT. THEN, FROM A THEORETICAL AND EMPIRICAL RESEARCH CARRIED OUT THROUGH INTERVIEWS, FOLLOW-UPS, DATA COLLECTION AND MULTIPLE PERCEPTIONS ADDED TO THE ANALYZES OF THESE CREATORS OF CONTENT ABOUT BOOKS ON YT, A DEBATE ENDS UP BEING PROPOSED AND BROKEN DOWN TO THE THROUGHOUT THE CHAPTERS. WHERE THE ANALYTICAL FOCUS AIMS TO UNDERSTAND IF BIG DATA, ALGORITHMS, BIG TECH, SURVEILLANCE CAPITALISM (ZUBOFF, 2021) AND THE CREATION OF REPUTATION THROUGH SELF-EXPOSURE, MERGED IN FAVOR OF A DIGITAL INTERACTION MADE MANDATORY IN SOCIETY, COULD PRESENT, ELEMENTS FOR A SOCIOLOGICAL INVESTIGATION INTO THE CAUSES AND EFFECTS ON INDIVIDUALS WHO NEED TO BE IN THIS VAST DIGITAL TERRITORY, FIRST AS A REDEFINED FORM OF EXISTENCE, AND THEN AS A PRODUCER OF WORK IN CONTEXTS OF SOCIAL, POLITICAL, HEALTH CRISES, ETC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>BIG DATA;CIÊNCIAS SOCIAIS;INTELIGÊNCIA ARTIFICIAL;TECNOLOGIAS DIGITAIS</t>
+          <t>SOCIOLOGIA;DIGITAL;LIVROS. BOOKTUBERS;CAPITALISMO DE VIGILÂNCIA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>BIG DATA;SOCIAL SCIENCES;ARTIFICIAL INTELLIGENCE;DIGITAL TECHNOLOGIES.</t>
+          <t>SOCIOLOGY;DIGITAL;BOOKS;BOOKTUBERS;SURVEILLANCE CAPITALISM</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" t="b">
         <v>0</v>
@@ -7135,41 +7135,41 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>MARIA TERESA MICELI KERBAUY</t>
+          <t>ELAINE DA SILVEIRA LEITE</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>CIÊNCIAS SOCIAIS</t>
+          <t>SOCIOLOGIA</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL PAULISTA JÚLIO DE MESQUITA FILHO (ARARAQUARA)</t>
+          <t>UNIVERSIDADE FEDERAL DE PELOTAS</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>UNESP-ARAR</t>
+          <t>UFPEL</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>SUDESTE</t>
+          <t>SUL</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>SÃO PAULO</t>
+          <t>RIO GRANDE DO SUL</t>
         </is>
       </c>
       <c r="Y48" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
@@ -7188,16 +7188,16 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12131172</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14897523</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>12131172</t>
+          <t>14897523</t>
         </is>
       </c>
       <c r="AE48" t="n">
-        <v>1010034</v>
+        <v>1330676</v>
       </c>
     </row>
     <row r="49">
@@ -7212,51 +7212,51 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ROBSON ROCHA DE SOUZA JUNIOR</t>
+          <t>PEDRO JORGE CHAVES MOURAO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GOVERNANÇA INOVATIVA : A RELAÇÃO ESTADO-EMPRESAS NA IMPLEMENTAÇÃO DO PROSOFT PELO BNDES</t>
+          <t>REPÚBLICA DO ÓDIO: ETNOGRAFIA DIGITAL FUNDAMENTADA EM DADOS DOS GRUPOS BOLSONARISTAS NO WHATSAPP</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>O PRESENTE ESTUDO TEM O PROPÓSITO DE ANALISAR COMO A GOVERNANÇA INOVATIVA, FORMADA PELA ARTICULAÇÃO ENTRE A INTERVENÇÃO ESTRATÉGICA DO ESTADO NO PROCESSO INOVATIVO E O PLANEJAMENTO ESTRATÉGICO DAS EMPRESAS, INTERFERE NAS COMPETÊNCIAS INOVATIVAS DE ESFORÇO E DE DESEMPENHO DAS EMPRESAS. A PESQUISA DISCUTE O SUPOSTO MAIS GERAL DE QUE QUANTO MAIS ARROJADA E TRANSFORMADORA FOR A GOVERNANÇA INOVATIVA, TANTO MAIOR TENDE A SER O EFEITO POSITIVO NO CONJUNTO DAS COMPETÊNCIAS INOVATIVAS DAS EMPRESAS FOMENTADAS. O CONTEXTO EMPÍRICO DA ANÁLISE SE REFERE À PARCERIA FORMADA PELO BANCO NACIONAL DE DESENVOLVIMENTO SOCIAL (BNDES) COM QUATRO EMPRESAS DO SETOR DE SOFTWARE E SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO (SSTI) NO ÂMBITO DO PROGRAMA PARA O DESENVOLVIMENTO DA INDÚSTRIA NACIONAL DE SOFTWARE E SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO (PROSOFT) (1997-2017): TOTVS, LINX, SINQIA E LIQ. LOGO, O ESTUDO TEM O OBJETIVO MAIS PRECISO DE ANALISAR COMO A GOVERNANÇA INOVATIVA ENTRE A INTERVENÇÃO ESTRATÉGICA ADOTADA PELO BNDES NO PROSOFT E O PLANEJAMENTO ESTRATÉGICO DAQUELAS QUATRO EMPRESAS (TOTVS, LINX, SINQIA E LIQ) INTERFERIU NA COMPETÊNCIA INOVATIVA DAS EMPRESAS. PARA TANTO, FOI FUNDAMENTAL: A) DESCREVER E ANALISAR O TIPO DE INTERVENÇÃO ESTRATÉGICA ADOTADO PELO BNDES NO PROSOFT; B) ANALISAR O TIPO DE PLANEJAMENTO ESTRATÉGICO QUE AS EMPRESAS BENEFICIADAS PELO BNDES NO PROSOFT ADOTARAM NA ORGANIZAÇÃO DE SUAS COMPETÊNCIAS INOVATIVAS; C) ANALISAR A VARIAÇÃO DAS COMPETÊNCIAS INOVATIVAS DAS EMPRESAS BENEFICIADAS A PARTIR DE SUA RELAÇÃO COM O BNDES NO PROSOFT; D) CONTRASTAR E TIPIFICAR OS DIFERENTES RESULTADOS VERIFICADOS NA VARIAÇÃO DAS COMPETÊNCIAS INOVATIVAS DAS EMPRESAS BENEFICIADAS PELO BNDES NO PROSOFT. O MODELO DE ANÁLISE QUE ORIENTOU A INVESTIGAÇÃO FOI CONSTRUÍDO A PARTIR DE UM DEBATE TEÓRICO QUE LEVOU EM CONSIDERAÇÃO UMA SÉRIE DE CONTRIBUIÇÕES QUE ANALISARAM O PAPEL DO ESTADO E DAS EMPRESAS NO PROCESSO INOVATIVO, O QUE COLOCOU EM RELEVO A IMPORTÂNCIA DESSAS DUAS FORMAS DE GESTÃO, SOBRETUDO EM SISTEMAS DE INOVAÇÃO EM ESTÁGIO DE CONSOLIDAÇÃO, COMO É O CASO DO SETOR DE SSTI NO BRASIL. A PESQUISA TEM CARÁTER LONGITUDINAL, FOI CONSTRUÍDA A PARTIR DE FONTES SECUNDÁRIAS (DOCUMENTOS DO BNDES E DAS QUATRO EMPRESAS ANALISADAS, BEM COMO ENTREVISTAS REALIZADAS POR SEUS GESTORES NA IMPRENSA) E FONTES PRIMÁRIAS (ENTREVISTAS COM FUNCIONÁRIOS DAS EMPRESAS ANALISADAS) E ADOTOU, COMO PROCEDIMENTO ANALÍTICO, TANTO A ANÁLISE DE CONTEÚDO, QUANTO A ESTATÍSTICA DESCRITIVA. APESAR DE AS EMPRESAS TEREM ACESSADO O MESMO PROGRAMA DE FOMENTO, CONSTATOU-SE QUE ESSAS EMPRESAS APRESENTARAM RESPOSTAS VARIADAS EM FUNÇÃO DE SEU PLANEJAMENTO ESTRATÉGICO E DAS COMPETÊNCIAS INOVATIVAS CONSOLIDADAS EM SUA TRAJETÓRIA NO SETOR DE SSTI NACIONAL, O QUE LHES PERMITIU ACESSAR COM MAIOR OU MENOR QUALIFICAÇÃO AS OPORTUNIDADES DO PROSOFT E INCREMENTAR, QUANTITATIVA E QUALITATIVAMENTE, SUAS COMPETÊNCIAS INOVATIVAS DE ESFORÇO. NO QUE SE REFERE ÀS COMPETÊNCIAS INOVATIVAS DE DESEMPENHO, NÃO FOI POSSÍVEL DETECTAR A MESMA RELAÇÃO.</t>
+          <t>A PESQUISA TEVE COMO OBJETIVO COMPREENDER O UNIVERSO SIMBÓLICO DOS MILITANTES BOLSONARISTAS EM 59 GRUPOS PÚBLICOS DE WHATSAPP DURANTE A CAMPANHA ELEITORAL DE 2018 NO BRASIL. A INVESTIGAÇÃO OBSERVOU E ANALISOU PRÁTICAS POLÍTICAS E REPRESENTAÇÕES DISCURSIVAS ALIADAS A TÉCNICAS DE MINERAÇÃO DE DADOS E PROCESSAMENTO COMPUTACIONAL DE TEXTOS. O ESTUDO ANALISOU 59 GRUPOS PÚBLICOS DE WHATSAPP QUE COMPARTILHAVAM IDENTIDADE BOLSONARISTA, VISANDO COMPREENDER A RELAÇÃO CONSTRUÍDA NO ESPAÇO DIGITAL, A DEFESA DA IDEOLOGIA BOLSONARISTA E AS REPRESENTAÇÕES FEITAS SOBRE MINORIAS, COMO MULHERES, NEGROS, GAYS E INDÍGENAS. A PESQUISA RESULTOU NA CONSTRUÇÃO DE UM NOVA FERRAMENTA SOCIOTÉCNICA QUE AVALIA OS ASPECTOS SIMBÓLICOS QUE EVIDENCIAM AS REPRESENTAÇÕES SOCIAIS ENTRE MILITANTES VIRTUAIS. O ESTUDO REVELOU A CONSTRUÇÃO DA IDENTIDADE POR MEIO DA OPOSIÇÃO A UM CONJUNTO DE INIMIGOS COMUNS IMAGINÁRIOS E IMAGINADOS, RESULTANDO NA ELABORAÇÃO DE UMA NOVA FORMA ESPECÍFICA DE IDENTIDADE POLÍTICA: O BOLSONARISMO.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>THIS STUDY AIMS TO ANALYZE HOW THE INNOVATIVE GOVERNANCE, FORMED BY THE ARTICULATION BETWEEN THE STRATEGIC INTERVENTION OF THE STATE IN THE INNOVATIVE PROCESS AND THE STRATEGIC PLANNING OH THE COMPANIES, INTERFERES IN THE INNOVATIVE COMPETENCES OF EFFORT AND PERFORMANCE OF THE COMPANIES. THE RESEARCH ASSUMES THAT THE BOLDER AND TRANSFORMER IS THE INNOVATIVE GOVERNANCE, BIGGER TENDS TO BE THE POSITIVE EFFECT ON THE SET OF THE COMPETENCES OF THE FOSTERED COMPANIES. THE EMPIRICAL CONTEXT OF THE ANALYSIS REFERS TO THE PARTNERSHIP FORMED BY THE BANCO NACIONAL DE DESENVOLVIMENTO SOCIAL (BNDES) AND FOUR COMPANIES OF THE SOFTWARE AND INFORMATION TECHNOLOGY SERVICE INDUSTRY (S&amp;ITS) UNDER THE PROGRAMA PARA O DESENVOLVIMENTO DA INDÚSTRIA NACIONAL DE SOFTWARE E SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO (PROSOFT) (1997-2017): TOTVS, LINX, SINQIA E LIQ. THEREFORE, THE STUDY HAS THE MOST PRECISE OBJECTIVE OF ANALYZING HOW THE INNOVATIVE GOVERNANCE BETWEEN THE STRATEGIC INTERVENTION ADOPTED BY THE BNDES IN PROSOFT AND THE STRATEGIC PLANNING OF THOSE FOUR COMPANIES (TOTVS, LINX, SINQIA E LIQ) HAS INTERFERED IN THE INNOVATIVE COMPETENCES OF THE COMPANIES. FOR THAT, IT WAS FUNDAMENTAL: A) TO DESCRIBE AND TO ANALYZE THE TYPE OF STRATEGIC INTERVENTION ADOPTED BY BNDES IN PROSOFT; B) TO ANALYZE THE TYPE OF STRATEGIC PLANNING THAT THE FOSTERED COMPANIES HAVE ADOPTED IN THE ORGANIZATION OF THEIR INNOVATIVE COMPETENCES; C) TO ANALYZE THE VARIATION OF THE INNOVATIVE COMPETENCES OF THE FOSTERED COMPANIES FROM THEIR RELATION WITH BNDES IN PROSOFT; D) TO CONTRAST AND TO TYPIFY THE DIFFERENT RESULTS RECORDED IN THE VARIATION OF THE INNOVATIVE COMPETENCES OF THE FOSTERED COMPANIES BY THE BNDES IN PROSOFT. THE ANALYZES MODEL THAT DIRECTED THE INVESTIGATION WAS BUILT FROM A THEORETICAL DEBATE THAT HAS TAKEN INTO ACCOUNT A RANGE OF CONTRIBUTIONS THAT HAVE ANALYZED THE ROLE OF THE STATE AND OF THE COMPANIES IN THE INNOVATIVE PROCESS, WHICH HAS HIGHLIGHTED THE IMPORTANCE OF THESE TWO FORMS OF MANAGEMENT, ESPECIALLY IN INNOVATION SYSTEMS IN CONSOLIDATION STAGE, AS IS THE CASE OF THE S&amp;ITS INDUSTRY IN BRAZIL. THE RESEARCH IS LONGITUDINAL, WAS BUILT FROM SECONDARY (DOCUMENTS OF BNDES AND OF THE FOUR COMPANIES ANALYZED, AS WELL AS INTERVIEW OF THEIR MANAGERS IN THE PRESS) AND PRIMARY (INTERVIEWS WITH EMPLOYEES OF THE COMPANIES ANALYZED) SOURCES, AND HAS ADOPTED, AS ANALYTICAL PROCEDURE, BOTH THE CONTENT ANALYZE AND THE DESCRIPTIVE STATISTIC. ALTHOUGH THE COMPANIES HAVE ACCESSED THE SAME FOSTERED PROGRAM, IT WAS FOUND THAT THESE COMPANIES PRESENT DIFFERENT REPLIES IN ORDER TO THEIR STRATEGIC PLANNING AND TO THE INNOVATIVE COMPETENCIES CONSOLIDATED IN THEIR PATH IN THE NATIONAL S&amp;ITS INDUSTRY, WHICH ALLOWED THEM TO ACCESS PROSOFT OPPORTUNITIES IN A MORE OR LESS QUALIFIED WAY, AND INCREMENT, IN QUANTITATIVE AND QUALITATIVE TERMS, THEIR INNOVATIVE COMPETENCES OF EFFORT. IN RELATION TO THE INNOVATIVE COMPETENCES OF PERFORMANCE, WAS NOT POSSIBLE TO DETECT THE SAME RELATION.</t>
+          <t>THE RESEARCH AIMED TO UNDERSTAND THE SYMBOLIC UNIVERSE OF BOLSONARIST MILITANTS IN 59 PUBLIC WHATSAPP GROUPS DURING THE 2018 ELECTION CAMPAIGN IN BRAZIL. THE INVESTIGATION OBSERVED AND ANALYZED POLITICAL PRACTICES AND DISCURSIVE REPRESENTATIONS COMBINED WITH DATA MINING TECHNIQUES AND COMPUTATIONAL TEXT PROCESSING. THE STUDY ANALYZED 59 PUBLIC WHATSAPP GROUPS THAT SHARED BOLSONARIST IDENTITY, AIMING TO UNDERSTAND THE RELATIONSHIP BUILT IN THE DIGITAL SPACE, THE DEFENSE OF BOLSONARISTA IDEOLOGY AND THE REPRESENTATIONS MADE ABOUT MINORITIES, SUCH AS WOMEN, BLACKS, GAYS AND INDIGENOUS PEOPLE. THE RESEARCH RESULTED IN THE CONSTRUCTION OF A NEW THEORETICAL AND METHODOLOGICAL MODEL THAT EVALUATES THE SYMBOLIC ASPECTS THAT SHOW THE SOCIAL REPRESENTATIONS AMONG VIRTUAL MILITANTS. THE STUDY REVEALED THE CONSTRUCTION OF IDENTITY THROUGH OPPOSITION TO A SET OF COMMON IMAGINARY AND IMAGINED ENEMIES, RESULTING IN THE ELABORATION OF A NEW SPECIFIC FORM OF POLITICAL IDENTITY: BOLSONARISM.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>BNDES;PROSOFT;SETOR DE SOFTWARE E SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO;SOCIOLOGIA ECONÔMICA;ESTUDOS DE INOVAÇÃO</t>
+          <t>ETNOGRAFIA VIRTUAL;MINERAÇÃO DE DADOS;BOLSONARISMO;WHATSAPP;CULTURA POLÍTICA.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>BNDES;PROSOFT;SOFTWARE AND INFORMATION TECHNOLOGY SERVICE INDUSTRY;ECONOMIC SOCIOLOGY;INNOVATION STUDIES</t>
+          <t>VIRTUAL ETHNOGRAPHY;DATA MINING;BOLSONARISM;WHATSAPP;POLITICAL CULTURE.</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Modelos de linguagem &amp; IA generativa</t>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M49" t="b">
@@ -7269,14 +7269,14 @@
         <v>0</v>
       </c>
       <c r="P49" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="b">
         <v>1</v>
       </c>
-      <c r="Q49" t="b">
-        <v>0</v>
-      </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>SANDRO RUDUIT GARCIA</t>
+          <t>GEOVANI JACO DE FREITAS</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -7286,31 +7286,31 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DO RIO GRANDE DO SUL</t>
+          <t>UNIVERSIDADE ESTADUAL DO CEARÁ</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>UFRGS</t>
+          <t>UECE</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>SUL</t>
+          <t>NORDESTE</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>RIO GRANDE DO SUL</t>
+          <t>CEARÁ</t>
         </is>
       </c>
       <c r="Y49" t="n">
-        <v>559</v>
+        <v>198</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
@@ -7329,16 +7329,16 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11646370</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14809587</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>11646370</t>
+          <t>14809587</t>
         </is>
       </c>
       <c r="AE49" t="n">
-        <v>628150</v>
+        <v>386811</v>
       </c>
     </row>
     <row r="50">
@@ -7357,54 +7357,54 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>JULIO MARINHO FERREIRA</t>
+          <t>SARA RAQUEL DE ANDRADE SILVA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LECTOR DIGITALIS: A PRÁTICA BOOKTUBE, A CRIAÇÃO DE PÚBLICOS LEITORES NA INTERNET E A SUA RELAÇÃO COM O CAPITALISMO DE VIGILÂNCIA NA PRODUÇÃO DE SOCIABILIDADES LABORAIS</t>
+          <t>RELAÇÕES EMERGENTES ENTRE ARTE E EMPRESA: O PATROCÍNIO EMPRESARIAL NA ARTE CONTEMPORÂNEA BRASILEIRA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>A PRESENTE TESE DEBRUÇA-SE EM ANALISAR O PAPEL DE UM APARATO TECNOLÓGICO ALTAMENTE COMPLEXO QUE SE MOSTRA PRESENTE EM COMPUTADORES E SEUS SIMILARES, TAIS QUAIS SMARTPHONES, LAPTOPS ETC., EM PRODUZIR SUBJETIVIDADES LEITORAS, TENDO NA PLATAFORMA E MÍDIA SOCIAL DIGITAL YOUTUBE COMO UMA ESPÉCIE DE VETOR À PRODUÇÃO DESSAS AÇÕES. DESSE MODO, ATRAVÉS DE CRIADORES/AS DE CONTEÚDO SOBRE LIVROS E DERIVATIVOS NO REFERIDO YOUTUBE, OS/AS BOOKTUBERS, QUE SE MOSTRAM COMO UMA FORMA VARIANTE DE INFLUENCIADORES DIGITAIS, SE FAZ NECESSÁRIO UMA MIRADA SOCIOLÓGICA ACERCA DO ENTENDIMENTO DESSA PRÁTICA, QUE PODE SER, TANTO AMADORA QUANTO ESPECIALIZADA, E SUA RELAÇÃO COM O MODELO DE UMA SOCIEDADE INFORMATIZADA. E AO MESMO TEMPO, CONTROLADA POR FERRAMENTAS INTERATIVAS, QUE, PODERIAM IMPOR CERTOS ASPECTOS PROBLEMÁTICOS COMO REGULAGEM ALGORÍTMICA, EXPOSIÇÃO DO PRIVADO, CONTROLE, MANIPULAÇÃO DE DADOS E VIGILÂNCIA. NESSE SENTIDO, TENDO NOS LIVROS COMO SUAS FERRAMENTAS PARA PRODUÇÃO DE RESENHAS AMADORAS, CRÍTICAS LITERÁRIAS, OPINIÕES E TAMBÉM COMENTÁRIOS DIVERSOS, ESSAS PESSOAS QUE AGEM, NA MAIOR PARTE DE SEU TEMPO, COMO INFLUENCIADORES DIGITAIS PARA UMA GAMA DE SEGUIDORES E TAMBÉM CURIOSOS ACABAM TORNANDO-SE INDIVÍDUOS QUE PODEM GESTAR A SUA PRÓPRIA IMAGEM EM FUNÇÃO DO DIGITAL. E AO INFLUENCIAR DIGITALMENTE LEITORES A RESPEITO DE CERTAS OBRAS LITERÁRIAS, CRIARIAM VÍNCULOS DE SOCIABILIDADES QUE SE APRESENTAM COMO ELEMENTOS FUNDANTES PARA UMA RELAÇÃO LABORAL LATENTE NO DIGITAL, MAS NÃO APENAS, JÁ QUE ESSE MESMO ATO DE INFLUENCIAR PRESSUPÕE UMA GAMA DE RELAÇÕES QUE PODEM IR ALÉM DA CATEGORIA TRABALHO. DESSE MODO, A PESQUISA SE FIA NA PERCEPÇÃO TEÓRICA DO DIGITAL COMO UM TERRITÓRIO ESTÉTICO E PROBLEMÁTICO, SOMADA À UMA RETÓRICA DE ESPAÇO DE PROGRESSO SOCIAL E TAMBÉM DE LIBERDADE, ALÉM DA INTERAÇÃO E DE SUA RELAÇÃO COM INSTITUIÇÕES SOCIAIS, PRINCIPALMENTE O TRABALHO RECONFIGURADO – UMA DAS MARCAS DA GESTÃO LABORAL ATUAL. EM SEGUIDA, A PARTIR DE UMA PESQUISA TEÓRICA E EMPÍRICA EXECUTADA ATRAVÉS DE ENTREVISTAS, DE ACOMPANHAMENTOS, DE COLETA DE DADOS E DE PERCEPÇÕES MÚLTIPLAS SOMADAS ÀS ANÁLISES DESSES/AS CRIADORES/AS DE CONTEÚDO SOBRE LIVROS NO YT UM DEBATE ACABA SENDO PROPOSTO E DESMEMBRADO AO LONGO DOS CAPÍTULOS. ONDE O FOCO ANALÍTICO VISA PERCEBER SE BIG DATA, ALGORITMOS, BIG TECH, CAPITALISMO DE VIGILÂNCIA (ZUBOFF, 2021) E A CRIAÇÃO DE REPUTAÇÃO ATRAVÉS DA EXPOSIÇÃO DE SI, FUNDIDAS EM PROL DE UMA INTERAÇÃO DIGITAL TORNADA OBRIGATÓRIA NA SOCIEDADE, PODERIAM APRESENTAR, ELEMENTOS PARA UMA INVESTIGAÇÃO SOCIOLÓGICA SOBRE AS CAUSAS E OS EFEITOS SOBRE INDIVÍDUOS QUE PRECISAM ESTAR NESSE AMPLO TERRITÓRIO DIGITAL, PRIMEIRO COMO UMA FORMA DE EXISTÊNCIA REDEFINIDA, E DEPOIS COMO UMA PRODUTORA DE TRABALHO EM CONTEXTOS DE CRISES SOCIAIS, POLÍTICAS, SANITÁRIAS ETC.</t>
+          <t>ANDRADE SILVA, SARA RAQUEL. RELAÇÕES EMERGENTES ENTRE ARTE E EMPRESA: O PATROCÍNIO EMPRESARIAL NA ARTE CONTEMPORÂNEA BRASILEIRA. TESE (DOUTORADO EM SOCIOLOGIA) – INSTITUTO DE FILOSOFIA E CIÊNCIAS SOCIAIS, UNIVERSIDADE FEDERAL DO RIO DE JANEIRO, RIO DE JANEIRO, 2023. ESTA PESQUISA TEM COMO OBJETIVO CONSTRUIR UMA VISÃO GERAL DO PATROCÍNIO CORPORATIVO NA ARTE CONTEMPORÂNEA NO BRASIL E ENTENDER COMO O INTERESSE DE EMPRESAS PRIVADAS NA CULTURA AFETOU O FUNCIONAMENTO DAS INSTITUIÇÕES DE ARTE. MINHA HIPÓTESE SUGERE QUE TRANSFORMAÇÕES CULTURAIS QUE COLOCARAM A EMPRESA PRIVADA NO CENTRO DA VIDA SOCIAL E EPÍTOME DE EFICIÊNCIA DA ERA CONTEMPORÂNEA, LEVANDO ESSES ATORES A UM PAPEL DE DESTAQUE EM DIVERSOS SETORES, EM ESPECIAL, A DEFINIÇÃO DE POLÍTICAS CULTURAIS E LEIS DE INCENTIVOS FISCAIS PARA A CULTURA. ARGUMENTO QUE TAIS MUDANÇAS REORGANIZARAM OS CAMPOS DE PRODUÇÃO CULTURAL O QUE, PARA AS INSTITUIÇÕES DE ARTE RESULTOU NO ACÚMULO DE UMA FUNÇÃO DE RELAÇÕES PÚBLICAS PARA EMPRESAS PATROCINADORAS. USANDO DADOS DE FINANCIAMENTO PÚBLICO PARA AS ARTES NO BRASIL, DIFERENCIO PROJETOS CULTURAIS DE ARTE CONTEMPORÂNEA DE OUTRAS MANIFESTAÇÕES ARTÍSTICAS FINANCIADAS POR EMPRESAS NO PAÍS COM A AJUDA DE UMA INTELIGÊNCIA ARTIFICIAL DESENVOLVIDA PELA COMBINAÇÃO DE PROCESSAMENTO DE LINGUAGEM NATURAL E MÉTODOS DE APRENDIZADO DE MÁQUINA. A PARTIR DESSES DADOS, MAPEIO A DISTRIBUIÇÃO GEOGRÁFICA, O VOLUME DE RECURSOS E AS PRINCIPAIS INSTITUIÇÕES DE ARTE E EMPRESAS QUE PATROCINAM A ARTE CONTEMPORÂNEA BRASILEIRA. EM UMA SEGUNDA ETAPA, USO ESSE MAPEAMENTO PARA ENCONTRAR PESSOAS LIGADAS A ESSAS INSTITUIÇÕES E EMPRESAS PARA REALIZAR ENTREVISTAS SEMIESTRUTURADAS. O OBJETIVO DAS ENTREVISTAS É PREENCHER QUALITATIVAMENTE AS LACUNAS DEIXADAS PELOS DADOS QUANTITATIVOS E ENTENDER COMO E EM QUE MEDIDA AS RELAÇÕES ENTRE OS PROFISSIONAIS DE ARTE E AS EMPRESAS PATROCINADORAS PODEM ALTERAR O FUNCIONAMENTO DAS INSTITUIÇÕES DE ARTE CONTEMPORÂNEA E A PRODUÇÃO DE ARTE LEGITIMADA. OS DADOS SUGEREM UMA CONCENTRAÇÃO DE INSTITUIÇÕES BANCÁRIAS NO PATROCÍNIO DA ARTE CONTEMPORÂNEA E A INTERFERÊNCIA DOS PATROCINADORES CORPORATIVOS NAS ESCOLHAS ARTÍSTICAS/CURATORIAIS DOS MUSEUS.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>THIS THESIS FOCUSES ON ANALYZING THE ROLE OF A HIGHLY COMPLEX TECHNOLOGICAL APPARATUS THAT IS PRESENT IN COMPUTERS AND THEIR SIMILAR ONES, SUCH AS SMARTPHONES, LAPTOPS, ETC., IN PRODUCING READER SUBJECTIVITIES, HAVING YOUTUBE AS A KIND OF PLATFORM AND DIGITAL SOCIAL MEDIA. OF VECTOR TO THE PRODUCTION OF THESE ACTIONS. IN THIS WAY, THROUGH CREATORS OF CONTENT ABOUT BOOKS AND DERIVATIVES ON THE AFOREMENTIONED YOUTUBE, THE BOOKTUBERS, WHO SHOW THEMSELVES AS A VARIANT FORM OF DIGITAL INFLUENCERS, IT IS NECESSARY TO TAKE A SOCIOLOGICAL LOOK AT THE UNDERSTANDING OF THIS PRACTICE, WHICH CAN BE, BOTH AMATEUR AND SPECIALIZED, AND ITS RELATION TO THE MODEL OF A COMPUTERIZED SOCIETY. AND AT THE SAME TIME, CONTROLLED BY INTERACTIVE TOOLS, WHICH COULD IMPOSE CERTAIN PROBLEMATIC ASPECTS SUCH AS ALGORITHMIC REGULATION, EXPOSURE OF THE PRIVATE, CONTROL, DATA MANIPULATION AND SURVEILLANCE. IN THIS SENSE, HAVING BOOKS AS THEIR TOOLS FOR PRODUCING AMATEUR REVIEWS, LITERARY CRITICISM, OPINIONS AND ALSO VARIOUS COMMENTS, THESE PEOPLE WHO ACT, MOST OF THEIR TIME, AS DIGITAL INFLUENCERS FOR A RANGE OF FOLLOWERS AND ALSO CURIOUS PEOPLE END UP BECOMING IF INDIVIDUALS WHO CAN MANAGE THEIR OWN IMAGE IN TERMS OF DIGITAL. AND BY DIGITALLY INFLUENCING READERS ABOUT CERTAIN LITERARY WORKS, THEY WOULD CREATE SOCIABILITY LINKS THAT ARE PRESENTED AS FOUNDING ELEMENTS FOR A LATENT LABOR RELATIONSHIP IN DIGITAL, BUT NOT ONLY, SINCE THIS SAME ACT OF INFLUENCING PRESUPPOSES A RANGE OF RELATIONSHIPS THAT CAN GO BEYOND OF THE JOB CATEGORY. IN THIS WAY, THE RESEARCH IS BASED ON THE THEORETICAL PERCEPTION OF THE DIGITAL AS AN AESTHETIC AND PROBLEMATIC TERRITORY, ADDED TO A RHETORIC OF SPACE OF SOCIAL PROGRESS AND ALSO OF FREEDOM, IN ADDITION TO THE INTERACTION AND ITS RELATIONSHIP WITH SOCIAL INSTITUTIONS, MAINLY THE RECONFIGURED WORK – THE HALLMARKS OF CURRENT LABOR MANAGEMENT. THEN, FROM A THEORETICAL AND EMPIRICAL RESEARCH CARRIED OUT THROUGH INTERVIEWS, FOLLOW-UPS, DATA COLLECTION AND MULTIPLE PERCEPTIONS ADDED TO THE ANALYZES OF THESE CREATORS OF CONTENT ABOUT BOOKS ON YT, A DEBATE ENDS UP BEING PROPOSED AND BROKEN DOWN TO THE THROUGHOUT THE CHAPTERS. WHERE THE ANALYTICAL FOCUS AIMS TO UNDERSTAND IF BIG DATA, ALGORITHMS, BIG TECH, SURVEILLANCE CAPITALISM (ZUBOFF, 2021) AND THE CREATION OF REPUTATION THROUGH SELF-EXPOSURE, MERGED IN FAVOR OF A DIGITAL INTERACTION MADE MANDATORY IN SOCIETY, COULD PRESENT, ELEMENTS FOR A SOCIOLOGICAL INVESTIGATION INTO THE CAUSES AND EFFECTS ON INDIVIDUALS WHO NEED TO BE IN THIS VAST DIGITAL TERRITORY, FIRST AS A REDEFINED FORM OF EXISTENCE, AND THEN AS A PRODUCER OF WORK IN CONTEXTS OF SOCIAL, POLITICAL, HEALTH CRISES, ETC.</t>
+          <t>ANDRADE SILVA, SARA RAQUEL. RELAÇÕES EMERGENTES ENTRE ARTE E EMPRESA: O PATROCÍNIO EMPRESARIAL NA ARTE CONTEMPORÂNEA BRASILEIRA. TESE (DOUTORADO EM SOCIOLOGIA) – INSTITUTO DE FILOSOFIA E CIÊNCIAS SOCIAIS, UNIVERSIDADE FEDERAL DO RIO DE JANEIRO, RIO DE JANEIRO, 2023. THIS RESEARCH AIMS TO BUILD AN OVERVIEW OF CORPORATE SPONSORSHIP IN CONTEMPORARY ART IN BRAZIL AND TO UNDERSTAND HOW THE INTEREST OF PRIVATE COMPANIES IN CULTURE HAS AFFECTED THE FUNCTIONING OF ART INSTITUTIONS. MY HYPOTHESIS SUGGESTS THAT CULTURAL TRANSFORMATIONS THAT HAVE PLACED THE PRIVATE COMPANY AT THE CENTER OF SOCIAL LIFE AND THE EPITOME OF EFFICIENCY IN THE CONTEMPORARY ERA, LEADING THESE ACTORS TO A PROMINENT ROLE IN VARIOUS SECTORS, IN PARTICULAR, THE DEFINITION OF CULTURAL POLICIES AND TAX INCENTIVE LAWS FOR CULTURE. I ARGUE THAT THESE CHANGES HAVE REORGANIZED THE FIELDS OF CULTURAL PRODUCTION, WHICH FOR ART INSTITUTIONS HAS RESULTED IN THE ACCUMULATION OF A PUBLIC RELATIONS FUNCTION FOR SPONSORING COMPANIES. USING DATA ON PUBLIC FUNDING FOR THE ARTS IN BRAZIL, I DIFFERENTIATE CONTEMPORARY ART CULTURAL PROJECTS FROM OTHER ARTISTIC MANIFESTATIONS FUNDED BY COMPANIES IN THE COUNTRY WITH THE HELP OF AN ARTIFICIAL INTELLIGENCE DEVELOPED BY COMBINING NATURAL LANGUAGE PROCESSING AND MACHINE LEARNING METHODS. USING THIS DATA, I MAP THE GEOGRAPHICAL DISTRIBUTION, THE VOLUME OF RESOURCES AND THE MAIN ART INSTITUTIONS AND COMPANIES THAT SPONSOR CONTEMPORARY ART IN BRAZIL. IN A SECOND STAGE, I USE THIS MAPPING TO FIND PEOPLE LINKED TO THESE INSTITUTIONS AND COMPANIES TO CONDUCT SEMI-STRUCTURED INTERVIEWS. THE AIM OF THE INTERVIEWS IS TO QUALITATIVELY FILL IN THE GAPS LEFT BY THE QUANTITATIVE DATA IN ORDER TO UNDERSTAND HOW AND TO WHAT EXTENT THE RELATIONSHIPS BETWEEN ART PROFESSIONALS AND SPONSORING COMPANIES CAN ALTER THE FUNCTIONING OF CONTEMPORARY ART INSTITUTIONS AND THE PRODUCTION OF LEGITIMIZED ART. THE DATA SUGGESTS A CONCENTRATION OF BANKING INSTITUTIONS IN THE SPONSORSHIP OF CONTEMPORARY ART AND THE INTERFERENCE OF CORPORATE SPONSORS IN THE ARTISTIC/CURATORIAL CHOICES OF MUSEUMS.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SOCIOLOGIA;DIGITAL;LIVROS. BOOKTUBERS;CAPITALISMO DE VIGILÂNCIA</t>
+          <t>ARTE CONTEMPORÂNEA;PATROCÍNIO;EMPRESA;SOCIOLOGIA DA ARTE</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>SOCIOLOGY;DIGITAL;BOOKS;BOOKTUBERS;SURVEILLANCE CAPITALISM</t>
+          <t>CONTEMPORARY ART;SPONSORSHIP;COMPANY;SOCIOLOGY OF ART</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Correlato</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>Aprendizado de máquina (ML); IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" t="b">
         <v>0</v>
@@ -7417,69 +7417,69 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>ELAINE DA SILVEIRA LEITE</t>
+          <t>GLAUCIA KRUSE VILLAS BOAS</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
+          <t>SOCIOLOGIA E ANTROPOLOGIA</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE FEDERAL DO RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>UFRJ</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>SUDESTE</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="Y50" t="n">
+        <v>229</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>PORTUGUES</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>OUTRAS SOCIOLOGIAS ESPECÍFICAS</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>UNIVERSIDADE FEDERAL DE PELOTAS</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>UFPEL</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>SUL</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>RIO GRANDE DO SUL</t>
-        </is>
-      </c>
-      <c r="Y50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>PORTUGUES</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>NÃO SE APLICA</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>SOCIOLOGIA</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14897523</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14195351</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>14897523</t>
+          <t>14195351</t>
         </is>
       </c>
       <c r="AE50" t="n">
-        <v>1330676</v>
+        <v>1329593</v>
       </c>
     </row>
     <row r="51">
@@ -7494,55 +7494,55 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PEDRO JORGE CHAVES MOURAO</t>
+          <t>ALEXANDRE PILAN ZANONI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>REPÚBLICA DO ÓDIO: ETNOGRAFIA DIGITAL FUNDAMENTADA EM DADOS DOS GRUPOS BOLSONARISTAS NO WHATSAPP</t>
+          <t>O TRABALHO NO LAÇO: PLATAFORMAS DE MICROTRABALHO E A EMERGÊNCIA DE SOLIDARIEDADES RESTRITAS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>A PESQUISA TEVE COMO OBJETIVO COMPREENDER O UNIVERSO SIMBÓLICO DOS MILITANTES BOLSONARISTAS EM 59 GRUPOS PÚBLICOS DE WHATSAPP DURANTE A CAMPANHA ELEITORAL DE 2018 NO BRASIL. A INVESTIGAÇÃO OBSERVOU E ANALISOU PRÁTICAS POLÍTICAS E REPRESENTAÇÕES DISCURSIVAS ALIADAS A TÉCNICAS DE MINERAÇÃO DE DADOS E PROCESSAMENTO COMPUTACIONAL DE TEXTOS. O ESTUDO ANALISOU 59 GRUPOS PÚBLICOS DE WHATSAPP QUE COMPARTILHAVAM IDENTIDADE BOLSONARISTA, VISANDO COMPREENDER A RELAÇÃO CONSTRUÍDA NO ESPAÇO DIGITAL, A DEFESA DA IDEOLOGIA BOLSONARISTA E AS REPRESENTAÇÕES FEITAS SOBRE MINORIAS, COMO MULHERES, NEGROS, GAYS E INDÍGENAS. A PESQUISA RESULTOU NA CONSTRUÇÃO DE UM NOVA FERRAMENTA SOCIOTÉCNICA QUE AVALIA OS ASPECTOS SIMBÓLICOS QUE EVIDENCIAM AS REPRESENTAÇÕES SOCIAIS ENTRE MILITANTES VIRTUAIS. O ESTUDO REVELOU A CONSTRUÇÃO DA IDENTIDADE POR MEIO DA OPOSIÇÃO A UM CONJUNTO DE INIMIGOS COMUNS IMAGINÁRIOS E IMAGINADOS, RESULTANDO NA ELABORAÇÃO DE UMA NOVA FORMA ESPECÍFICA DE IDENTIDADE POLÍTICA: O BOLSONARISMO.</t>
+          <t>O TRABALHO EM DADOS SE CONFIGURA COMO UMA ATIVIDADE CENTRAL PARA O FUNCIONAMENTO DA ECONOMIA CONTEMPORÂNEA E ESTÁ NA BASE DAS MAIS AVANÇADAS TECNOLOGIAS, COMO AS "INTELIGÊNCIAS ARTIFICIAIS". NO CONTROLE E EXECUÇÃO DESSE TRABALHO PREDOMINAM, NO BRASIL, PLATAFORMAS DE MICROTRABALHO, EMPRESAS TRANSNACIONAIS QUE SERVEM A UMA REDE DE CLIENTES GLOBAIS. ESTA PESQUISA, COM FOCO ETNOGRÁFICO SOCIOLÓGICO, TEM COMO OBJETIVO COMPREENDER COMO UMA CONFIGURAÇÃO DE TRABALHO INSTÁVEL E DESPROTEGIDO, CONTROLADO POR EMPRESAS-PLATAFORMAS, IMPACTA A FORMAÇÃO DE REDES DE SOLIDARIEDADE E PERSPECTIVAS EM RELAÇÃO AO TRABALHO. O ESTUDO UTILIZOU UMA METODOLOGIA DE PESQUISA MISTA, POR MEIO DA COMBINAÇÃO DE TRÊS ABORDAGENS: I) ANÁLISE QUANTITATIVA COMPARADA DE QUESTIONÁRIO APLICADO A 207 TRABALHADORES, COM FOCO EM SEUS PERFIS, EXPERIÊNCIAS E PERCEPÇÕES SOBRE O TRABALHO CONTROLADO POR PLATAFORMAS DE MICROTRABALHO E DE ENTREGAS; II) OBSERVAÇÃO PARTICIPANTE, COM INSERÇÃO EM PLATAFORMAS DE MICROTRABALHO DURANTE 6 MESES, PARA COMPREENDER PRÁTICAS DE TRABALHO E SUAS ESTRUTURAÇÕES; E, III) ENTREVISTAS EM PROFUNDIDADE COM BASE NO MÉTODO DOS RELATOS DE VIDA E NA ANÁLISE TEMÁTICA FOCADA EM EIXOS E DIMENSÕES QUE COSTURAM UM MOSAICO DE PERFIS HETEROGÊNEOS. A ANÁLISE E INTEGRAÇÃO DOS DADOS COLETADOS PERMITIU A CONSTRUÇÃO DA NOÇÃO DE SOLIDARIEDADES RESTRITAS PARA DESCREVER E EXPLICAR AS CONSEQUÊNCIAS PESSOAIS E SOCIAIS DA CONFIGURAÇÃO DO TRABALHO CONTROLADO POR PLATAFORMAS DE MICROTRABALHO. ESSA FORMA DE SOCIALIDADE SE CONFIGURA NO CONTEXTO DE UMA CULTURA DO TRABALHO DA SOBREVIVÊNCIA E SE CARACTERIZA PELO CURTO ALCANCE DOS LAÇOS E VÍNCULOS SOCIAIS FORMADOS PELOS TRABALHADORES, COM TENDÊNCIA A SE LIMITAREM AO NÚCLEO FAMILIAR MAIS PRÓXIMO, O QUE SE DEVE PRINCIPALMENTE À DESESTRUTURAÇÃO DOS ESPAÇOS E DOS TEMPOS DE TRABALHO, À ASSIMETRIA DE PODER ENTRE TRABALHADORES E PLATAFORMAS E À ORGANIZAÇÃO FRAGMENTADA E INCERTA DO TRABALHO POR PROJETOS E TAREFAS SOB DEMANDA.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>THE RESEARCH AIMED TO UNDERSTAND THE SYMBOLIC UNIVERSE OF BOLSONARIST MILITANTS IN 59 PUBLIC WHATSAPP GROUPS DURING THE 2018 ELECTION CAMPAIGN IN BRAZIL. THE INVESTIGATION OBSERVED AND ANALYZED POLITICAL PRACTICES AND DISCURSIVE REPRESENTATIONS COMBINED WITH DATA MINING TECHNIQUES AND COMPUTATIONAL TEXT PROCESSING. THE STUDY ANALYZED 59 PUBLIC WHATSAPP GROUPS THAT SHARED BOLSONARIST IDENTITY, AIMING TO UNDERSTAND THE RELATIONSHIP BUILT IN THE DIGITAL SPACE, THE DEFENSE OF BOLSONARISTA IDEOLOGY AND THE REPRESENTATIONS MADE ABOUT MINORITIES, SUCH AS WOMEN, BLACKS, GAYS AND INDIGENOUS PEOPLE. THE RESEARCH RESULTED IN THE CONSTRUCTION OF A NEW THEORETICAL AND METHODOLOGICAL MODEL THAT EVALUATES THE SYMBOLIC ASPECTS THAT SHOW THE SOCIAL REPRESENTATIONS AMONG VIRTUAL MILITANTS. THE STUDY REVEALED THE CONSTRUCTION OF IDENTITY THROUGH OPPOSITION TO A SET OF COMMON IMAGINARY AND IMAGINED ENEMIES, RESULTING IN THE ELABORATION OF A NEW SPECIFIC FORM OF POLITICAL IDENTITY: BOLSONARISM.</t>
+          <t>DATA WORK IS A CENTRAL ACTIVITY FOR THE FUNCTIONING OF THE CONTEMPORARY ECONOMY AND UNDERLIES THE MOST ADVANCED TECHNOLOGIES, SUCH AS "ARTIFICIAL INTELLIGENCES". IN BRAZIL, MICROWORK PLATFORMS, TRANSNATIONAL COMPANIES SERVING A NETWORK OF GLOBAL CLIENTS, PREDOMINATE IN THE CONTROL AND EXECUTION OF THIS WORK. THIS RESEARCH, WITH A SOCIOLOGICAL ETHNOGRAPHIC FOCUS, AIMS TO UNDERSTAND HOW AN UNSTABLE AND UNPROTECTED WORK CONFIGURATION, CONTROLLED BY PLATFORM COMPANIES, IMPACTS THE FORMATION OF SOLIDARITY NETWORKS AND PERSPECTIVES ON WORK. THE STUDY EMPLOYED A MIXED RESEARCH METHODOLOGY, COMBINING THREE APPROACHES: I) COMPARATIVE QUANTITATIVE ANALYSIS OF A QUESTIONNAIRE APPLIED TO 207 WORKERS, FOCUSING ON THEIR PROFILES, EXPERIENCES, AND PERCEPTIONS OF WORK CONTROLLED BY MICROWORK AND DELIVERY PLATFORMS; II) PARTICIPANT OBSERVATION, WITH INSERTION IN MICROWORK PLATFORMS FOR SIX MONTHS, TO UNDERSTAND WORK PRACTICES AND THEIR STRUCTURATIONS; AND, III) IN-DEPTH INTERVIEWS BASED ON THE LIFE HISTORY METHOD AND THEMATIC ANALYSIS FOCUSED ON AXES AND DIMENSIONS THAT WEAVE TOGETHER A MOSAIC OF HETEROGENEOUS PROFILES. THE ANALYSIS AND INTEGRATION OF THE COLLECTED DATA ALLOWED FOR THE CONSTRUCTION OF THE NOTION OF RESTRICTED SOLIDARITIES TO DESCRIBE AND EXPLAIN THE PERSONAL AND SOCIAL CONSEQUENCES OF THE CONFIGURATION OF WORK CONTROLLED BY MICROWORK PLATFORMS. THIS FORM OF SOCIALITY IS CONFIGURED IN THE CONTEXT OF A WORK CULTURE OF SURVIVAL AND IS CHARACTERIZED BY THE SHORT REACH OF SOCIAL TIES AND BONDS FORMED BY WORKERS, TENDING TO BE LIMITED TO THE CLOSEST FAMILY NUCLEUS, WHICH IS MAINLY DUE TO THE DISRUPTION OF WORK SPACES AND TIMES, THE POWER ASYMMETRY BETWEEN WORKERS AND PLATFORMS, AND THE FRAGMENTED AND UNCERTAIN ORGANIZATION OF WORK BY PROJECTS AND ON-DEMAND TASKS.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ETNOGRAFIA VIRTUAL;MINERAÇÃO DE DADOS;BOLSONARISMO;WHATSAPP;CULTURA POLÍTICA.</t>
+          <t>PLATAFORMAS DIGITAIS;INTELIGÊNCIA ARTIFICIAL;ECONOMIA DIGITAL;MICROTRABALHO;SOLIDARIEDADE RESTRITA.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>VIRTUAL ETHNOGRAPHY;DATA MINING;BOLSONARISM;WHATSAPP;POLITICAL CULTURE.</t>
+          <t>DIGITAL PLATFORMS;ARTIFICIAL INTELLIGENCE;DIGITAL ECONOMY;MICROWORK;RESTRICTED SOLIDARITY.</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Correlato</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>IA em sentido estrito</t>
         </is>
       </c>
       <c r="M51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" t="b">
         <v>0</v>
@@ -7554,11 +7554,11 @@
         <v>0</v>
       </c>
       <c r="Q51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>GEOVANI JACO DE FREITAS</t>
+          <t>MARIA APARECIDA DA CRUZ BRIDI</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -7568,31 +7568,31 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DO CEARÁ</t>
+          <t>UNIVERSIDADE FEDERAL DO PARANÁ</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>UECE</t>
+          <t>UFPR</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>NORDESTE</t>
+          <t>SUL</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>CEARÁ</t>
+          <t>PARANÁ</t>
         </is>
       </c>
       <c r="Y51" t="n">
-        <v>198</v>
+        <v>400</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
@@ -7611,16 +7611,16 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14809587</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15589542</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>14809587</t>
+          <t>15589542</t>
         </is>
       </c>
       <c r="AE51" t="n">
-        <v>386811</v>
+        <v>2675408</v>
       </c>
     </row>
     <row r="52">
@@ -7635,58 +7635,58 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2023-12-11</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SARA RAQUEL DE ANDRADE SILVA</t>
+          <t>EVANDRO DE ALMEIDA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>RELAÇÕES EMERGENTES ENTRE ARTE E EMPRESA: O PATROCÍNIO EMPRESARIAL NA ARTE CONTEMPORÂNEA BRASILEIRA</t>
+          <t>NOVAS TECNOLOGIAS E COMPETÊNCIAS PROFISSIONAIS: IMPACTOS NO TRABALHO DE BANCÁRIOS</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ANDRADE SILVA, SARA RAQUEL. RELAÇÕES EMERGENTES ENTRE ARTE E EMPRESA: O PATROCÍNIO EMPRESARIAL NA ARTE CONTEMPORÂNEA BRASILEIRA. TESE (DOUTORADO EM SOCIOLOGIA) – INSTITUTO DE FILOSOFIA E CIÊNCIAS SOCIAIS, UNIVERSIDADE FEDERAL DO RIO DE JANEIRO, RIO DE JANEIRO, 2023. ESTA PESQUISA TEM COMO OBJETIVO CONSTRUIR UMA VISÃO GERAL DO PATROCÍNIO CORPORATIVO NA ARTE CONTEMPORÂNEA NO BRASIL E ENTENDER COMO O INTERESSE DE EMPRESAS PRIVADAS NA CULTURA AFETOU O FUNCIONAMENTO DAS INSTITUIÇÕES DE ARTE. MINHA HIPÓTESE SUGERE QUE TRANSFORMAÇÕES CULTURAIS QUE COLOCARAM A EMPRESA PRIVADA NO CENTRO DA VIDA SOCIAL E EPÍTOME DE EFICIÊNCIA DA ERA CONTEMPORÂNEA, LEVANDO ESSES ATORES A UM PAPEL DE DESTAQUE EM DIVERSOS SETORES, EM ESPECIAL, A DEFINIÇÃO DE POLÍTICAS CULTURAIS E LEIS DE INCENTIVOS FISCAIS PARA A CULTURA. ARGUMENTO QUE TAIS MUDANÇAS REORGANIZARAM OS CAMPOS DE PRODUÇÃO CULTURAL O QUE, PARA AS INSTITUIÇÕES DE ARTE RESULTOU NO ACÚMULO DE UMA FUNÇÃO DE RELAÇÕES PÚBLICAS PARA EMPRESAS PATROCINADORAS. USANDO DADOS DE FINANCIAMENTO PÚBLICO PARA AS ARTES NO BRASIL, DIFERENCIO PROJETOS CULTURAIS DE ARTE CONTEMPORÂNEA DE OUTRAS MANIFESTAÇÕES ARTÍSTICAS FINANCIADAS POR EMPRESAS NO PAÍS COM A AJUDA DE UMA INTELIGÊNCIA ARTIFICIAL DESENVOLVIDA PELA COMBINAÇÃO DE PROCESSAMENTO DE LINGUAGEM NATURAL E MÉTODOS DE APRENDIZADO DE MÁQUINA. A PARTIR DESSES DADOS, MAPEIO A DISTRIBUIÇÃO GEOGRÁFICA, O VOLUME DE RECURSOS E AS PRINCIPAIS INSTITUIÇÕES DE ARTE E EMPRESAS QUE PATROCINAM A ARTE CONTEMPORÂNEA BRASILEIRA. EM UMA SEGUNDA ETAPA, USO ESSE MAPEAMENTO PARA ENCONTRAR PESSOAS LIGADAS A ESSAS INSTITUIÇÕES E EMPRESAS PARA REALIZAR ENTREVISTAS SEMIESTRUTURADAS. O OBJETIVO DAS ENTREVISTAS É PREENCHER QUALITATIVAMENTE AS LACUNAS DEIXADAS PELOS DADOS QUANTITATIVOS E ENTENDER COMO E EM QUE MEDIDA AS RELAÇÕES ENTRE OS PROFISSIONAIS DE ARTE E AS EMPRESAS PATROCINADORAS PODEM ALTERAR O FUNCIONAMENTO DAS INSTITUIÇÕES DE ARTE CONTEMPORÂNEA E A PRODUÇÃO DE ARTE LEGITIMADA. OS DADOS SUGEREM UMA CONCENTRAÇÃO DE INSTITUIÇÕES BANCÁRIAS NO PATROCÍNIO DA ARTE CONTEMPORÂNEA E A INTERFERÊNCIA DOS PATROCINADORES CORPORATIVOS NAS ESCOLHAS ARTÍSTICAS/CURATORIAIS DOS MUSEUS.</t>
+          <t>ESTA TESE TEM POR OBJETIVO APRESENTAR O ENTENDIMENTO DE TRABALHADORES DO SETOR BANCÁRIO ACERCA DE SUAS COMPETÊNCIAS TÉCNICAS E SOCIOEMOCIONAIS, NO ÂMBITO DA INTERAÇÃO OU NÃO, PRESENCIAL E/OU VIRTUAL COM OS CLIENTES, CONTEXTUALIZADA PELA IMPLEMENTAÇÃO DE TECNOLOGIAS DIGITAIS EM SUAS ÁREAS DE ATUAÇÃO. A ESCOLHA POR ESSE PROFISSIONAL JUSTIFICA-SE EM RAZÃO DO ALTO INVESTIMENTO EM PROCESSOS DE AUTOMATIZAÇÃO E DIGITALIZAÇÃO, CUJOS EFEITOS IMEDIATOS SÃO SENTIDOS PRINCIPALMENTE NAS FORMAS DE ORGANIZAÇÃO DO TRABALHO DESSA CATEGORIA. AS HIPÓTESES LEVANTADAS FORAM QUE AS TECNOLOGIAS DIGITAIS IMPLEMENTADAS ATUAM DE MODO DUPLO, ELAS POSSUEM POTENCIAL PARA SUBSTITUIR OS TRABALHADORES DE ALGUNS SETORES POR MÁQUINAS E POR PROGRAMAS AUTOMATIZADOS, COM VISTAS À REDUÇÃO DE CUSTOS E AUMENTO DE PRODUTIVIDADE, AO MESMO TEMPO QUE PROPORCIONAM O SURGIMENTO DE NOVAS OCUPAÇÕES. PARA FAZER FRENTE A ESSA IMPOSIÇÃO DIGITAL, OBSERVA-SE A NECESSIDADE DE UM CONSTANTE APRIMORAMENTO E REQUALIFICAÇÃO PROFISSIONAL. A TESE, FUNDAMENTADA EM ESTUDOS DAS ÁREAS DA SOCIOLOGIA DO TRABALHO, ADMINISTRAÇÃO, TECNOLOGIAS DIGITAIS E BANCÁRIAS, CONFIGURA-SE EM UMA PESQUISA QUALITATIVA HIPOTÉTICO-DEDUTIVA, SUCEDIDA POR UMA PESQUISA BIBLIOGRÁFICA E UM ROTEIRO DE ENTREVISTAS. OS DADOS ANALISADOS FORAM COLETADOS JUNTO A 15 TRABALHADORES DE 6 INSTITUIÇÕES BANCÁRIAS, QUE CONTEMPLAVAM OS REQUISITOS EXIGIDOS, A SABER, A INTERAÇÃO OU NÃO COM CLIENTES NAS MODALIDADES, PRESENCIAL, VIRTUAL E OU HIBRIDA, E A VIVÊNCIA DA TRANSFORMAÇÃO DIGITAL NO AMBIENTE DE TRABALHO. OS RESULTADOS DA PESQUISA INDICAM QUE APESAR DAS MUDANÇAS OCORRIDAS NA PERSPECTIVA TECNOLÓGICA, AINDA HÁ NECESSIDADE DE CAPACITAÇÃO PARA O DESENVOLVIMENTO DE COMPETÊNCIAS, CONFIRMANDO AS HIPÓTESES ACERCA DOS IMPACTOS GERADOS PELAS TECNOLOGIAS DIGITAIS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ANDRADE SILVA, SARA RAQUEL. RELAÇÕES EMERGENTES ENTRE ARTE E EMPRESA: O PATROCÍNIO EMPRESARIAL NA ARTE CONTEMPORÂNEA BRASILEIRA. TESE (DOUTORADO EM SOCIOLOGIA) – INSTITUTO DE FILOSOFIA E CIÊNCIAS SOCIAIS, UNIVERSIDADE FEDERAL DO RIO DE JANEIRO, RIO DE JANEIRO, 2023. THIS RESEARCH AIMS TO BUILD AN OVERVIEW OF CORPORATE SPONSORSHIP IN CONTEMPORARY ART IN BRAZIL AND TO UNDERSTAND HOW THE INTEREST OF PRIVATE COMPANIES IN CULTURE HAS AFFECTED THE FUNCTIONING OF ART INSTITUTIONS. MY HYPOTHESIS SUGGESTS THAT CULTURAL TRANSFORMATIONS THAT HAVE PLACED THE PRIVATE COMPANY AT THE CENTER OF SOCIAL LIFE AND THE EPITOME OF EFFICIENCY IN THE CONTEMPORARY ERA, LEADING THESE ACTORS TO A PROMINENT ROLE IN VARIOUS SECTORS, IN PARTICULAR, THE DEFINITION OF CULTURAL POLICIES AND TAX INCENTIVE LAWS FOR CULTURE. I ARGUE THAT THESE CHANGES HAVE REORGANIZED THE FIELDS OF CULTURAL PRODUCTION, WHICH FOR ART INSTITUTIONS HAS RESULTED IN THE ACCUMULATION OF A PUBLIC RELATIONS FUNCTION FOR SPONSORING COMPANIES. USING DATA ON PUBLIC FUNDING FOR THE ARTS IN BRAZIL, I DIFFERENTIATE CONTEMPORARY ART CULTURAL PROJECTS FROM OTHER ARTISTIC MANIFESTATIONS FUNDED BY COMPANIES IN THE COUNTRY WITH THE HELP OF AN ARTIFICIAL INTELLIGENCE DEVELOPED BY COMBINING NATURAL LANGUAGE PROCESSING AND MACHINE LEARNING METHODS. USING THIS DATA, I MAP THE GEOGRAPHICAL DISTRIBUTION, THE VOLUME OF RESOURCES AND THE MAIN ART INSTITUTIONS AND COMPANIES THAT SPONSOR CONTEMPORARY ART IN BRAZIL. IN A SECOND STAGE, I USE THIS MAPPING TO FIND PEOPLE LINKED TO THESE INSTITUTIONS AND COMPANIES TO CONDUCT SEMI-STRUCTURED INTERVIEWS. THE AIM OF THE INTERVIEWS IS TO QUALITATIVELY FILL IN THE GAPS LEFT BY THE QUANTITATIVE DATA IN ORDER TO UNDERSTAND HOW AND TO WHAT EXTENT THE RELATIONSHIPS BETWEEN ART PROFESSIONALS AND SPONSORING COMPANIES CAN ALTER THE FUNCTIONING OF CONTEMPORARY ART INSTITUTIONS AND THE PRODUCTION OF LEGITIMIZED ART. THE DATA SUGGESTS A CONCENTRATION OF BANKING INSTITUTIONS IN THE SPONSORSHIP OF CONTEMPORARY ART AND THE INTERFERENCE OF CORPORATE SPONSORS IN THE ARTISTIC/CURATORIAL CHOICES OF MUSEUMS.</t>
+          <t>THIS THESIS AIMS TO PRESENT THE UNDERSTANDING OF WORKERS IN THE BANKING SECTOR ABOUT THEIR TECHNICAL AND SOCIO-EMOTIONAL SKILLS, WITHIN THE SCOPE OF REMOTE OR PERSONAL INTERACTION WITH CUSTOMERS, CONTEXTUALIZED BY THE IMPLEMENTATION OF DIGITAL TECHNOLOGIES IN THEIR AREAS OF ACTIVITY. THE CHOICE FOR THIS PROFESSIONAL IS JUSTIFIED DUE TO THE HIGH INVESTMENT IN AUTOMATION AND DIGITALIZATION PROCESSES, WHOSE IMMEDIATE EFFECTS ARE FELT MAINLY IN THE FORMS OF WORK ORGANIZATION IN THIS CATEGORY. THE HYPOTHESES RAISED WERE THE IMPLEMENTED DIGITAL TECHNOLOGIES FOLLOW THIS DOUBLE PROGRESSION, IN SOME SECTORS, THEY HAVE THE POTENTIAL TO REPLACE WORKERS BY MACHINES AND AUTOMATED PROGRAMS, WITH THE PURPOSE OF REDUCING COSTS AND INCREASING PRODUCTIVITY, WHILE PROVIDING THE EMERGENCE OF NEW OCCUPATIONS. IN ORDER TO FACE THIS DIGITAL IMPOSITION, THERE IS A NEED FOR CONSTANT PROFESSIONAL IMPROVEMENT AND RETRAINING. THE THESIS IS BASED ON STUDIES OF LABOUR SOCIOLOGY, ADMINISTRATION, DIGITAL AND BANKING TECHNOLOGIES; IT CONSISTS OF HYPOTHETICAL-DEDUCTIVE QUALITATIVE RESEARCH, FOLLOWED BY BIBLIOGRAPHICAL RESEARCH, A DOCUMENTARY ANALYSIS AND A QUESTIONNAIRE. THE ANALYZED DATA WERE COLLECTED FROM 15 WORKERS FROM 6 BANKING INSTITUTIONS, WHICH MET THE STANDARD REQUIREMENTS, NAMELY, INTERACTION WITH OR NOT CUSTOMERS, IN THE MODALITIES, IN-PERSON, VIRTUAL AND/OR HYBRID, AND THE EXPERIENCE OF DIGITAL TRANSFORMATION IN THE WORKPLACE. THE RESEARCH FINDINGS INDICATE THAT DESPITE THE CHANGES THAT HAVE OCCURRED FROM A TECHNOLOGICAL PERSPECTIVE, THERE IS STILL A NEED FOR TRAINING TO DEVELOP SKILLS, CONFIRMING THE HYPOTHESES ABOUT THE IMPACTS GENERATED BY DIGITAL TECHNOLOGIES</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ARTE CONTEMPORÂNEA;PATROCÍNIO;EMPRESA;SOCIOLOGIA DA ARTE</t>
+          <t>REESTRUTURAÇÃO PRODUTIVA;TECNOLOGIAS DIGITAIS;TECNOLOGIAS BANCÁRIAS;COMPETÊNCIAS TÉCNICAS E SOCIOEMOCIONAIS;QUALIFICAÇÃO PROFISSIONAL</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>CONTEMPORARY ART;SPONSORSHIP;COMPANY;SOCIOLOGY OF ART</t>
+          <t>PRODUCTIVE RESTRUCTURING;DIGITAL TECHNOLOGIES;BANKING TECHNOLOGIES;TECHNICAL AND SOCIO-EMOTIONAL SKILLS;PROFESSIONAL TRAINING</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Aprendizado de máquina (ML); IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52" t="b">
         <v>0</v>
@@ -7699,22 +7699,22 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>GLAUCIA KRUSE VILLAS BOAS</t>
+          <t>NOEMIA LAZZARESCHI</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>SOCIOLOGIA E ANTROPOLOGIA</t>
+          <t>CIÊNCIAS SOCIAIS</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DO RIO DE JANEIRO</t>
+          <t>PONTIFÍCIA UNIVERSIDADE CATÓLICA DE SÃO PAULO</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>UFRJ</t>
+          <t>PUCSP</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -7724,16 +7724,16 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>SÃO PAULO</t>
         </is>
       </c>
       <c r="Y52" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>OUTRAS SOCIOLOGIAS ESPECÍFICAS</t>
+          <t>NÃO SE APLICA</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -7752,16 +7752,16 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14195351</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15793149</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>14195351</t>
+          <t>15793149</t>
         </is>
       </c>
       <c r="AE52" t="n">
-        <v>1329593</v>
+        <v>2530079</v>
       </c>
     </row>
     <row r="53">
@@ -7780,64 +7780,64 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ALEXANDRE PILAN ZANONI</t>
+          <t>FERNANDA RIBAS BOHLER</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>O TRABALHO NO LAÇO: PLATAFORMAS DE MICROTRABALHO E A EMERGÊNCIA DE SOLIDARIEDADES RESTRITAS</t>
+          <t xml:space="preserve">BENEFÍCIO PARA QUEM? A REALIDADE DO TELETRABALHO NO INSTITUTO NACIONAL DO SEGURO SOCIAL A PARTIR DA PANDEMIA DA COVID-19. </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>O TRABALHO EM DADOS SE CONFIGURA COMO UMA ATIVIDADE CENTRAL PARA O FUNCIONAMENTO DA ECONOMIA CONTEMPORÂNEA E ESTÁ NA BASE DAS MAIS AVANÇADAS TECNOLOGIAS, COMO AS "INTELIGÊNCIAS ARTIFICIAIS". NO CONTROLE E EXECUÇÃO DESSE TRABALHO PREDOMINAM, NO BRASIL, PLATAFORMAS DE MICROTRABALHO, EMPRESAS TRANSNACIONAIS QUE SERVEM A UMA REDE DE CLIENTES GLOBAIS. ESTA PESQUISA, COM FOCO ETNOGRÁFICO SOCIOLÓGICO, TEM COMO OBJETIVO COMPREENDER COMO UMA CONFIGURAÇÃO DE TRABALHO INSTÁVEL E DESPROTEGIDO, CONTROLADO POR EMPRESAS-PLATAFORMAS, IMPACTA A FORMAÇÃO DE REDES DE SOLIDARIEDADE E PERSPECTIVAS EM RELAÇÃO AO TRABALHO. O ESTUDO UTILIZOU UMA METODOLOGIA DE PESQUISA MISTA, POR MEIO DA COMBINAÇÃO DE TRÊS ABORDAGENS: I) ANÁLISE QUANTITATIVA COMPARADA DE QUESTIONÁRIO APLICADO A 207 TRABALHADORES, COM FOCO EM SEUS PERFIS, EXPERIÊNCIAS E PERCEPÇÕES SOBRE O TRABALHO CONTROLADO POR PLATAFORMAS DE MICROTRABALHO E DE ENTREGAS; II) OBSERVAÇÃO PARTICIPANTE, COM INSERÇÃO EM PLATAFORMAS DE MICROTRABALHO DURANTE 6 MESES, PARA COMPREENDER PRÁTICAS DE TRABALHO E SUAS ESTRUTURAÇÕES; E, III) ENTREVISTAS EM PROFUNDIDADE COM BASE NO MÉTODO DOS RELATOS DE VIDA E NA ANÁLISE TEMÁTICA FOCADA EM EIXOS E DIMENSÕES QUE COSTURAM UM MOSAICO DE PERFIS HETEROGÊNEOS. A ANÁLISE E INTEGRAÇÃO DOS DADOS COLETADOS PERMITIU A CONSTRUÇÃO DA NOÇÃO DE SOLIDARIEDADES RESTRITAS PARA DESCREVER E EXPLICAR AS CONSEQUÊNCIAS PESSOAIS E SOCIAIS DA CONFIGURAÇÃO DO TRABALHO CONTROLADO POR PLATAFORMAS DE MICROTRABALHO. ESSA FORMA DE SOCIALIDADE SE CONFIGURA NO CONTEXTO DE UMA CULTURA DO TRABALHO DA SOBREVIVÊNCIA E SE CARACTERIZA PELO CURTO ALCANCE DOS LAÇOS E VÍNCULOS SOCIAIS FORMADOS PELOS TRABALHADORES, COM TENDÊNCIA A SE LIMITAREM AO NÚCLEO FAMILIAR MAIS PRÓXIMO, O QUE SE DEVE PRINCIPALMENTE À DESESTRUTURAÇÃO DOS ESPAÇOS E DOS TEMPOS DE TRABALHO, À ASSIMETRIA DE PODER ENTRE TRABALHADORES E PLATAFORMAS E À ORGANIZAÇÃO FRAGMENTADA E INCERTA DO TRABALHO POR PROJETOS E TAREFAS SOB DEMANDA.</t>
+          <t>O ANO DE 2020 TROUXE MUDANÇAS SEM PRECEDENTES PARA O MUNDO DO TRABALHO, SOBRETUDO PARA O TELETRABALHO, MODALIDADE QUE JÁ VINHA SENDO ADOTADA GRADUALMENTE, MAS QUE GANHOU RELEVÂNCIA NO CONTEXTO DA PANDEMIA DA COVID-19. NESSE CENÁRIO, O TRABALHO REMOTO FOI A ALTERNATIVA ENCONTRADA PELOS SETORES PÚBLICO E PRIVADO PARA A REDUÇÃO DO CONTÁGIO DA DOENÇA, BEM COMO PARA DAR CONTINUIDADE ÀS SUAS ATIVIDADES LABORAIS. NO INSTITUTO NACIONAL DO SEGURO SOCIAL (INSS), A MODALIDADE JÁ ERA UMA REALIDADE DESDE 2019, QUANDO FOI INSTITUÍDA A TÍTULO DE EXPERIÊNCIA-PILOTO NA INSTITUIÇÃO, PORÉM A PANDEMIA DA COVID-19 FORÇOU TODOS (AS) A SE ADAPTAREM COM O TELETRABALHO, TRAZENDO UMA NOVA CONDIÇÃO PARA OS (AS) SERVIDORES (AS), MESMO PARA AQUELES QUE JÁ TRABALHAVAM REMOTAMENTE. A PARTIR DESTE CONTEXTO, A PRESENTE TESE TEM COMO OBJETO DE ESTUDO A ANÁLISE DAS CONDIÇÕES DE TRABALHO DOS (AS) SERVIDORES (AS) DO INSS QUE TIVERAM QUE TRABALHAR REMOTAMENTE DURANTE O PERÍODO CRÍTICO DA PANDEMIA E OS QUE OPTARAM POR CONTINUAR NA MODALIDADE NO PERÍODO PÓS-PANDEMIA. A PESQUISA EMPÍRICA, COM ABORDAGEM QUANTI-QUALI, CONSISTIU NA ANÁLISE DE DADOS DA PESQUISA REALIZADA EM 2020, INTITULADA “O TRABALHO REMOTO/HOME OFFICE NO CONTEXTO DA PANDEMIA DA COVID-19”, REALIZADA POR INTEGRANTES DO GRUPO DE ESTUDOS TRABALHO E SOCIEDADE (GETS) DA UNIVERSIDADE FEDERAL DO PARANÁ (UFPR) COM PARCERIA DA REMIR (REDE DE ESTUDOS E MONITORAMENTO INTERDISCIPLINAR DA REFORMA TRABALHISTA), A QUAL OBTEVE O TOTAL DE 906 RESPOSTAS VÁLIDAS, SENDO 181 RESPOSTAS DE SERVIDORES (AS) DO INSS. EM 2023, APLICAMOS UM NOVO QUESTIONÁRIO ONLINE COM O FOCO EXCLUSIVO NO OBJETO DA PRESENTE TESE, O TELETRABALHO NO INSS, ATENTANDO PARA OS CONFLITOS QUE DESEMBOCARAM NA GREVE DE 2022 E SOBRE A RELAÇÃO DOS (AS) SERVIDORES (AS) COM O SINDICATO. NESSE SEGUNDO MOMENTO OBTIVEMOS NO TOTAL 24 QUESTIONÁRIOS RESPONDIDOS. AINDA, A FIM DE COMPREENDERMOS MELHOR AS DINÂMICAS DO TRABALHO DESENVOLVIDO PELOS SERVIDORES (AS), OS SISTEMAS PELOS QUAIS DESENVOLVEM SUAS ATIVIDADES REMOTAMENTE E A GESTÃO POR METAS APLICADAS A ELES (AS), ENTREVISTAMOS DOIS SERVIDORES, A PARTIR DE UM ROTEIRO DE ENTREVISTA SEMIESTRUTURADO. ATRAVÉS DOS DADOS COLETADOS, OBSERVAMOS QUE O TELETRABALHO COMO É INSTITUÍDO NO INSS CONTRIBUI PARA O DESMANTELAMENTO DO INSTITUTO, JÁ EM CURSO EM RAZÃO DAS POLÍTICAS NEOLIBERAIS DE ENXUGAMENTO ESTATAL E DA FINANCEIRIZAÇÃO DAS POLÍTICAS SOCIAIS QUE AGRAVAM AS CONDIÇÕES DE TRABALHO DOS (AS) SERVIDORES (AS), SEJA PELA NÃO REPOSIÇÃO DE PESSOAL AO QUADRO FUNCIONAL, SEJA POR MEIO DE REFORMAS QUE PREJUDICAM A MAIOR PARTE DA POPULAÇÃO QUE DEPENDE DO SISTEMA PREVIDENCIÁRIO. NUM CENÁRIO ONDE O QUADRO DE FUNCIONÁRIOS ESTÁ DEFASADO POR UM LADO, E A DEMANDA DE REQUERIMENTOS AUMENTA POR OUTRO, O INSS INSTITUI PARA OS SERVIDORES EM TELETRABALHO UM ADICIONAL DE METAS DE 30%, NÃO FORNECE ESTRUTURA ADEQUADA (EQUIPAMENTOS, CADEIRA ERGONÔMICA) E TAMPOUCO AJUDA COM OS CUSTOS COM INTERNET, LUZ ETC. OS (AS) SERVIDORES (AS) QUE JÁ SOFRIAM COM A ESTRUTURA PRECÁRIA DAS AGÊNCIAS PREVIDENCIÁRIAS, COM COMPUTADORES ANTIGOS, SISTEMA FALHO, INTERNET FRACA ETC., ALÉM DE TEREM QUE PRODUZIR MAIS, DEVEM ARCAR COM A RESPONSABILIDADE PELOS CUSTOS E RISCOS DO SEU TRABALHO. QUANTO AOS BENEFICIÁRIOS DO SISTEMA, EM ESPECIAL OS MAIS VULNERÁVEIS E OS MAIS IDOSOS, ESTÃO CADA VEZ MAIS AFASTADOS DELE EM VIRTUDE DA AUTOMATIZAÇÃO DOS REQUERIMENTOS, DA FALTA DE CONHECIMENTO E DE CONDIÇÕES DE EFETUAR UM PEDIDO DE BENEFÍCIO POR MEIO DIGITAL. O IMPACTO DESTE PROCESSO, PELO QUAL A GESTÃO DE METAS É IMPOSTA NO SETOR PÚBLICO, PREJUDICA AS CONDIÇÕES DE TRABALHO DOS SERVIDORES (AS) MAS, SOBRETUDO, ATINGE O DIREITO CONSTITUCIONAL À SEGURIDADE SOCIAL DA POPULAÇÃO.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>DATA WORK IS A CENTRAL ACTIVITY FOR THE FUNCTIONING OF THE CONTEMPORARY ECONOMY AND UNDERLIES THE MOST ADVANCED TECHNOLOGIES, SUCH AS "ARTIFICIAL INTELLIGENCES". IN BRAZIL, MICROWORK PLATFORMS, TRANSNATIONAL COMPANIES SERVING A NETWORK OF GLOBAL CLIENTS, PREDOMINATE IN THE CONTROL AND EXECUTION OF THIS WORK. THIS RESEARCH, WITH A SOCIOLOGICAL ETHNOGRAPHIC FOCUS, AIMS TO UNDERSTAND HOW AN UNSTABLE AND UNPROTECTED WORK CONFIGURATION, CONTROLLED BY PLATFORM COMPANIES, IMPACTS THE FORMATION OF SOLIDARITY NETWORKS AND PERSPECTIVES ON WORK. THE STUDY EMPLOYED A MIXED RESEARCH METHODOLOGY, COMBINING THREE APPROACHES: I) COMPARATIVE QUANTITATIVE ANALYSIS OF A QUESTIONNAIRE APPLIED TO 207 WORKERS, FOCUSING ON THEIR PROFILES, EXPERIENCES, AND PERCEPTIONS OF WORK CONTROLLED BY MICROWORK AND DELIVERY PLATFORMS; II) PARTICIPANT OBSERVATION, WITH INSERTION IN MICROWORK PLATFORMS FOR SIX MONTHS, TO UNDERSTAND WORK PRACTICES AND THEIR STRUCTURATIONS; AND, III) IN-DEPTH INTERVIEWS BASED ON THE LIFE HISTORY METHOD AND THEMATIC ANALYSIS FOCUSED ON AXES AND DIMENSIONS THAT WEAVE TOGETHER A MOSAIC OF HETEROGENEOUS PROFILES. THE ANALYSIS AND INTEGRATION OF THE COLLECTED DATA ALLOWED FOR THE CONSTRUCTION OF THE NOTION OF RESTRICTED SOLIDARITIES TO DESCRIBE AND EXPLAIN THE PERSONAL AND SOCIAL CONSEQUENCES OF THE CONFIGURATION OF WORK CONTROLLED BY MICROWORK PLATFORMS. THIS FORM OF SOCIALITY IS CONFIGURED IN THE CONTEXT OF A WORK CULTURE OF SURVIVAL AND IS CHARACTERIZED BY THE SHORT REACH OF SOCIAL TIES AND BONDS FORMED BY WORKERS, TENDING TO BE LIMITED TO THE CLOSEST FAMILY NUCLEUS, WHICH IS MAINLY DUE TO THE DISRUPTION OF WORK SPACES AND TIMES, THE POWER ASYMMETRY BETWEEN WORKERS AND PLATFORMS, AND THE FRAGMENTED AND UNCERTAIN ORGANIZATION OF WORK BY PROJECTS AND ON-DEMAND TASKS.</t>
+          <t>THE YEAR 2020 BROUGHT UNPRECEDENTED CHANGES TO THE WORLD OF WORK, ESPECIALLY FOR TELEWORKING, A MODALITY THAT HAD ALREADY BEEN GRADUALLY ADOPTED, BUT WHICH GAINED RELEVANCE IN THE CONTEXT OF THE COVID-19 PANDEMIC. IN THIS SCENARIO, REMOTE WORK WAS THE ALTERNATIVE FOUND BY THE PUBLIC AND PRIVATE SECTORS TO REDUCE THE SPREAD OF THE DISEASE, AS WELL AS TO CONTINUE THEIR WORK ACTIVITIES. AT THE NATIONAL SOCIAL SECURITY INSTITUTE (INSS), THE MODALITY HAS BEEN A REALITY SINCE 2019, WHEN IT WAS ESTABLISHED AS A PILOT EXPERIENCE AT THE INSTITUTION, BUT THE COVID-19 PANDEMIC FORCED EVERYONE TO ADAPT TO TELEWORKING, BRINGING A NEW CONDITION FOR THE PUBLIC SERVANTS, EVEN FOR THOSE WHO WERE ALREADY TELEWORKING BEFORE. FROM THIS CONTEXT, THE OBJECT OF STUDY OF THIS THESIS IS TO ANALYZE THE WORKING CONDITIONS OF INSS EMPLOYEES WHO HAD TO WORK REMOTELY DURING THE CRITICAL PERIOD OF THE PANDEMIC AND THOSE WHO CHOSE TO CONTINUE IN THE MODALITY DURING THE POST-PANDEMIC PERIOD. THE EMPIRICAL RESEARCH, WITH A QUANTITATIVEQUALITATIVE APPROACH, CONSISTED OF ANALYZING DATA FROM RESEARCH CARRIED OUT IN 2020, ENTITLED “REMOTE WORK/HOME OFFICE IN THE CONTEXT OF THE COVID-19 PANDEMIC”, CARRIED OUT BY MEMBERS OF THE WORK AND SOCIETY STUDY GROUP (GETS) FROM THE FEDERAL UNIVERSITY OF PARANÁ (UFPR) IN PARTNERSHIP WITH REMIR (NETWORK FOR STUDIES AND INTERDISCIPLINARY MONITORING OF LABOR REFORM), THAT OBTAINED A TOTAL OF 906 VALID RESPONSES, OF WHICH 181 FROM INSS PUBLIC EMPLOYEES. IN 2023, WE APPLIED A NEW ONLINE QUESTIONNAIRE WITH AN EXCLUSIVE FOCUS ON THE OBJECT OF THIS THESIS, TELEWORKING AT INSS, PAYING ATTENTION TO THE CONFLICTS THAT LED TO THE 2022 STRIKE AND TO THE RELATIONSHIP BETWEEN CIVIL SERVANTS AND THE UNION. IN THIS SECOND MOMENT, WE OBTAINED A TOTAL OF 24 COMPLETED QUESTIONNAIRES. FURTHERMORE, TO UNDERSTAND THE DYNAMICS OF THE WORK CARRIED OUT BY THE PUBLIC SERVERS, THE SYSTEMS THROUGH WHICH THEY CARRY OUT THEIR ACTIVITIES REMOTELY AND THE MANAGEMENT BY GOALS APPLIED TO THEM, WE INTERVIEWED TWO SERVERS, BASED ON A SEMI-STRUCTURED INTERVIEW SCRIPT. THROUGH THE DATA COLLECTED, WE OBSERVED THAT TELEWORKING AS ESTABLISHED IN THE INSS CONTRIBUTES TO THE DISMANTLING OF THE INSTITUTE, ALREADY UNDERWAY DUE TO NEOLIBERAL POLICIES OF STATE DOWNSIZING AND THE FINANCIALIZATION OF SOCIAL POLICIES THAT AGGRAVATE THE CONDITIONS OF THE PUBLIC EMPLOYEES, EITHER BY NOT REPLACING PERSONNEL LOSSES IN THE WORKFORCE, OR THROUGH REFORMS THAT HARM THE MAJORITY OF THE POPULATION THAT DEPENDS ON THE SOCIAL SECURITY SYSTEM. IN A SCENARIO WHERE THE NUMBER OF EMPLOYEES IS OUTDATED ON ONE HAND, AND THE DEMAND FOR APPLICATIONS INCREASES ON THE OTHER, THE INSS ESTABLISHES AN ADDITIONAL TARGET OF 30% FOR TELEWORKING EMPLOYEES, DOES NOT PROVIDE ADEQUATE STRUCTURE (EQUIPMENT, ERGONOMIC CHAIR) AND NEITHER HELP WITH INTERNET, ELECTRICITY COSTS, ETC. SERVERS WHO ALREADY SUFFERED FROM THE PRECARIOUS STRUCTURE OF SOCIAL SECURITY AGENCIES, WITH OLD COMPUTERS, FAULTY SYSTEMS, WEAK INTERNET, ETC., IN ADDITION TO HAVING TO PRODUCE MORE, MUST TAKE RESPONSIBILITY FOR THE COSTS AND RISKS OF THEIR WORK. THE SUPPOSED BENEFICIARIES OF THE SYSTEM, ESPECIALLY THE MOST VULNERABLE AND THE ELDERLY, ARE INCREASINGLY SEPARATED FROM IT DUE TO THE AUTOMATION OF APPLICATIONS AND THE LACK OF KNOWLEDGE AND CONDITIONS TO MAKE A BENEFIT REQUEST THROUGH TECHNOLOGICAL MEANS. THE IMPACT OF THIS PROCESS, BY WHICH MANAGEMENT BY GOALS IS IMPOSED IN THE PUBLIC SECTOR, HARMS THE WORKING CONDITIONS OF CIVIL SERVANTS BUT, ABOVE ALL, AFFECTS THE CONSTITUTIONAL RIGHT TO SOCIAL SECURITY OF THE POPULATION.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>PLATAFORMAS DIGITAIS;INTELIGÊNCIA ARTIFICIAL;ECONOMIA DIGITAL;MICROTRABALHO;SOLIDARIEDADE RESTRITA.</t>
+          <t>CONDIÇÕES DE TRABALHO;TELETRABALHO NO INSS;SETOR PÚBLICO;PANDEMIA.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>DIGITAL PLATFORMS;ARTIFICIAL INTELLIGENCE;DIGITAL ECONOMY;MICROWORK;RESTRICTED SOLIDARITY.</t>
+          <t>WORKING CONDITIONS;TELEWORKING AT INSS;PUBLIC SECTOR;PANDEMIC.</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>IA em sentido estrito</t>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M53" t="b">
+        <v>0</v>
+      </c>
+      <c r="N53" t="b">
+        <v>0</v>
+      </c>
+      <c r="O53" t="b">
+        <v>0</v>
+      </c>
+      <c r="P53" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="b">
         <v>1</v>
       </c>
-      <c r="N53" t="b">
-        <v>0</v>
-      </c>
-      <c r="O53" t="b">
-        <v>0</v>
-      </c>
-      <c r="P53" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="b">
-        <v>0</v>
-      </c>
       <c r="R53" t="inlineStr">
         <is>
           <t>MARIA APARECIDA DA CRUZ BRIDI</t>
@@ -7874,7 +7874,7 @@
         </is>
       </c>
       <c r="Y53" t="n">
-        <v>400</v>
+        <v>209</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
@@ -7893,16 +7893,16 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15589542</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15589576</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>15589542</t>
+          <t>15589576</t>
         </is>
       </c>
       <c r="AE53" t="n">
-        <v>2675408</v>
+        <v>2675423</v>
       </c>
     </row>
     <row r="54">
@@ -7921,37 +7921,37 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>EVANDRO DE ALMEIDA</t>
+          <t>MARCELO DA SILVA RIBEIRO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NOVAS TECNOLOGIAS E COMPETÊNCIAS PROFISSIONAIS: IMPACTOS NO TRABALHO DE BANCÁRIOS</t>
+          <t>“DO TECNOSOLUCIONISMO AO TECNOVIGILANTISMO”: UM ESTUDO SOCIOLÓGICO SOBRE OS USOS DE EMERGENTES TECNOLOGIAS PELAS FORÇAS DE SEGURANÇA DO CEARÁ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ESTA TESE TEM POR OBJETIVO APRESENTAR O ENTENDIMENTO DE TRABALHADORES DO SETOR BANCÁRIO ACERCA DE SUAS COMPETÊNCIAS TÉCNICAS E SOCIOEMOCIONAIS, NO ÂMBITO DA INTERAÇÃO OU NÃO, PRESENCIAL E/OU VIRTUAL COM OS CLIENTES, CONTEXTUALIZADA PELA IMPLEMENTAÇÃO DE TECNOLOGIAS DIGITAIS EM SUAS ÁREAS DE ATUAÇÃO. A ESCOLHA POR ESSE PROFISSIONAL JUSTIFICA-SE EM RAZÃO DO ALTO INVESTIMENTO EM PROCESSOS DE AUTOMATIZAÇÃO E DIGITALIZAÇÃO, CUJOS EFEITOS IMEDIATOS SÃO SENTIDOS PRINCIPALMENTE NAS FORMAS DE ORGANIZAÇÃO DO TRABALHO DESSA CATEGORIA. AS HIPÓTESES LEVANTADAS FORAM QUE AS TECNOLOGIAS DIGITAIS IMPLEMENTADAS ATUAM DE MODO DUPLO, ELAS POSSUEM POTENCIAL PARA SUBSTITUIR OS TRABALHADORES DE ALGUNS SETORES POR MÁQUINAS E POR PROGRAMAS AUTOMATIZADOS, COM VISTAS À REDUÇÃO DE CUSTOS E AUMENTO DE PRODUTIVIDADE, AO MESMO TEMPO QUE PROPORCIONAM O SURGIMENTO DE NOVAS OCUPAÇÕES. PARA FAZER FRENTE A ESSA IMPOSIÇÃO DIGITAL, OBSERVA-SE A NECESSIDADE DE UM CONSTANTE APRIMORAMENTO E REQUALIFICAÇÃO PROFISSIONAL. A TESE, FUNDAMENTADA EM ESTUDOS DAS ÁREAS DA SOCIOLOGIA DO TRABALHO, ADMINISTRAÇÃO, TECNOLOGIAS DIGITAIS E BANCÁRIAS, CONFIGURA-SE EM UMA PESQUISA QUALITATIVA HIPOTÉTICO-DEDUTIVA, SUCEDIDA POR UMA PESQUISA BIBLIOGRÁFICA E UM ROTEIRO DE ENTREVISTAS. OS DADOS ANALISADOS FORAM COLETADOS JUNTO A 15 TRABALHADORES DE 6 INSTITUIÇÕES BANCÁRIAS, QUE CONTEMPLAVAM OS REQUISITOS EXIGIDOS, A SABER, A INTERAÇÃO OU NÃO COM CLIENTES NAS MODALIDADES, PRESENCIAL, VIRTUAL E OU HIBRIDA, E A VIVÊNCIA DA TRANSFORMAÇÃO DIGITAL NO AMBIENTE DE TRABALHO. OS RESULTADOS DA PESQUISA INDICAM QUE APESAR DAS MUDANÇAS OCORRIDAS NA PERSPECTIVA TECNOLÓGICA, AINDA HÁ NECESSIDADE DE CAPACITAÇÃO PARA O DESENVOLVIMENTO DE COMPETÊNCIAS, CONFIRMANDO AS HIPÓTESES ACERCA DOS IMPACTOS GERADOS PELAS TECNOLOGIAS DIGITAIS</t>
+          <t>A PRESENTE TESE TEM POR OBJETIVO PRINCIPAL ANALISAR SOCIOLOGICAMENTE OS ARRANJOS SOCIAIS E POLÍTICOS ENVOLVENDO A RECENTE ADOÇÃO DE NOVOS APARATOS TECNOLÓGICOS DE CAPTAÇÃO, REGISTRO, ARMAZENAMENTO, CODIFICAÇÃO E VISUALIZAÇÃO ANALÍTICA DE IMAGENS E DADOS DIGITAIS POR PARTE DAS FORÇAS ESTADUAIS DE SEGURANÇA PÚBLICA NO CEARÁ. ATUALMENTE NO BRASIL, O USO DE NOVAS TECNOLOGIAS PARA OS FINS DE OPERAÇÕES POLICIAIS E DE INVESTIGAÇÕES CRIMINAIS RECEBEM MAIOR ATENÇÃO NO CAMPO INSTITUCIONAL DA SEGURANÇA PÚBLICA. NOS ÚLTIMOS CINCO ANOS, O ESTADO DO CEARÁ RECEBEU RELATIVA NOTABILIDADE NO CENÁRIO NACIONAL COMO UM DOS ESTADOS DO PAÍS QUE MAIS INVESTEM NA ADOÇÃO DE NOVOS EQUIPAMENTOS ELETRÔNICOS E DIGITAIS COMO CÂMERAS DE VIGILÂNCIA DE ÚLTIMA GERAÇÃO, TECNOLOGIAS DE RECONHECIMENTO FACIAL (TRF) E PLATAFORMAS DIGITAIS DE BIG DATA, PARA AUXÍLIO NO COMBATE ESTATAL À CRIMINALIDADE, SENDO A MAIOR PARTE DESSAS “FERRAMENTAS” PROJETADAS E DESENVOLVIDAS NO PRÓPRIO ESTADO POR MEIO DE PARCERIAS INSTITUCIONAIS ENTRE O GOVERNO E CENTROS DE PESQUISA DA ÁREA DA “CIÊNCIA DE DADOS”. ESSAS PARCERIAS SÃO UM DOS ELEMENTOS CONSTITUTIVOS DO QUE NOMEIO METODOLOGICAMENTE AQUI POR MOVIMENTO DE ATUALIZAÇÃO TECNOLÓGICA DA SEGURANÇA PÚBLICA CEARENSE, O QUAL SE CONFIGURA OBJETO DE ESTUDO DA PESQUISA DA QUAL RESULTA ESTA TESE. MEDIANTE UMA INVESTIGAÇÃO QUALITATIVA QUE CONTOU COM UM A PESQUISA DOCUMENTAL E BIBLIOGRÁFICA, COM UM LEVANTAMENTO DE MATÉRIAS JORNALÍSTICAS, ALÉM DE UM MONITORAMENTO NÃO-AUTOMATIZADO DE CONTEÚDOS DIGITAIS, COM OBSERVAÇÕES DIRETAS DECORRENTES DE UM TRABALHO DE CAMPO MULTISITUADO E ENTREVISTAS COM ATORES SOCIAIS IMPLICADOS DIRETA OU INDIRETAMENTE COM O DESENVOLVIMENTO E/OU OPERACIONALIZAÇÃO DESSAS TECNOLOGIAS. DESSE MODO, BUSCA-SE AQUI COMPREENDER QUAIS OS SIGNIFICADOS E SENTIDOS SOCIAIS E POLÍTICOS DOS USOS DAS EMERGENTES TECNOLOGIAS DE CAPTAÇÃO, REGISTRO, CODIFICAÇÃO, CRUZAMENTO E ANÁLISE DE IMAGENS E DADOS DIGITAIS POR PARTE DAS FORÇAS ESTADUAIS DE SEGURANÇA PÚBLICA DO CEARÁ, COM PRIVILÉGIO SOBRE O RECORTE TEMPORAL REFERENTE ÀS GESTÕES DO EX-GOVERNADOR CAMILO SANTANA (PT), DURANTE OS ANOS DE 2015-2022. OS USOS DESSAS TECNOLOGIAS REVELAM UMA COMPLEXA REDE DE ASSOCIAÇÕES HETEROGÊNEAS QUE MOBILIZAM INSTRUMENTOS TÉCNICOS, AÇÕES POLÍTICAS E DE GOVERNO, MOBILIZA APARATOS BUROCRÁTICOS E AGENTES PÚBLICOS.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>THIS THESIS AIMS TO PRESENT THE UNDERSTANDING OF WORKERS IN THE BANKING SECTOR ABOUT THEIR TECHNICAL AND SOCIO-EMOTIONAL SKILLS, WITHIN THE SCOPE OF REMOTE OR PERSONAL INTERACTION WITH CUSTOMERS, CONTEXTUALIZED BY THE IMPLEMENTATION OF DIGITAL TECHNOLOGIES IN THEIR AREAS OF ACTIVITY. THE CHOICE FOR THIS PROFESSIONAL IS JUSTIFIED DUE TO THE HIGH INVESTMENT IN AUTOMATION AND DIGITALIZATION PROCESSES, WHOSE IMMEDIATE EFFECTS ARE FELT MAINLY IN THE FORMS OF WORK ORGANIZATION IN THIS CATEGORY. THE HYPOTHESES RAISED WERE THE IMPLEMENTED DIGITAL TECHNOLOGIES FOLLOW THIS DOUBLE PROGRESSION, IN SOME SECTORS, THEY HAVE THE POTENTIAL TO REPLACE WORKERS BY MACHINES AND AUTOMATED PROGRAMS, WITH THE PURPOSE OF REDUCING COSTS AND INCREASING PRODUCTIVITY, WHILE PROVIDING THE EMERGENCE OF NEW OCCUPATIONS. IN ORDER TO FACE THIS DIGITAL IMPOSITION, THERE IS A NEED FOR CONSTANT PROFESSIONAL IMPROVEMENT AND RETRAINING. THE THESIS IS BASED ON STUDIES OF LABOUR SOCIOLOGY, ADMINISTRATION, DIGITAL AND BANKING TECHNOLOGIES; IT CONSISTS OF HYPOTHETICAL-DEDUCTIVE QUALITATIVE RESEARCH, FOLLOWED BY BIBLIOGRAPHICAL RESEARCH, A DOCUMENTARY ANALYSIS AND A QUESTIONNAIRE. THE ANALYZED DATA WERE COLLECTED FROM 15 WORKERS FROM 6 BANKING INSTITUTIONS, WHICH MET THE STANDARD REQUIREMENTS, NAMELY, INTERACTION WITH OR NOT CUSTOMERS, IN THE MODALITIES, IN-PERSON, VIRTUAL AND/OR HYBRID, AND THE EXPERIENCE OF DIGITAL TRANSFORMATION IN THE WORKPLACE. THE RESEARCH FINDINGS INDICATE THAT DESPITE THE CHANGES THAT HAVE OCCURRED FROM A TECHNOLOGICAL PERSPECTIVE, THERE IS STILL A NEED FOR TRAINING TO DEVELOP SKILLS, CONFIRMING THE HYPOTHESES ABOUT THE IMPACTS GENERATED BY DIGITAL TECHNOLOGIES</t>
+          <t>THE PRESENT THESIS AIMS PRIMARILY TO SOCIOLOGICALLY ANALYSE THE SOCIAL AND POLITICAL ARRANGEMENTS SURROUNDING THE RECENT ADOPTION OF NEW TECHNOLOGICAL APPARATUSES FOR CAPTURING, RECORDING, STORING, ENCODING, AND ANALYTICALLY VISUALISING IMAGES AND DIGITAL DATA BY STATE PUBLIC SECURITY FORCES IN CEARÁ. CURRENTLY IN BRAZIL, THE USE OF NEW TECHNOLOGIES FOR POLICE OPERATIONS AND CRIMINAL INVESTIGATIONS IS RECEIVING GREATER ATTENTION WITHIN THE INSTITUTIONAL FIELD OF PUBLIC SECURITY. OVER THE PAST FIVE YEARS, THE STATE OF CEARÁ HAS GAINED RELATIVE PROMINENCE ON THE NATIONAL SCENE AS ONE OF THE STATES IN THE COUNTRY THAT INVESTS MOST IN THE ADOPTION OF NEW ELECTRONIC AND DIGITAL EQUIPMENT, SUCH AS STATE-OF-THE-ART SURVEILLANCE CAMERAS, FACIAL RECOGNITION TECHNOLOGIES (FRT), AND DIGITAL BIG DATA PLATFORMS, TO ASSIST IN THE STATE'S FIGHT AGAINST CRIME. MOST OF THESE “TOOLS” HAVE BEEN DESIGNED AND DEVELOPED WITHIN THE STATE THROUGH INSTITUTIONAL PARTNERSHIPS BETWEEN THE GOVERNMENT AND RESEARCH CENTRES IN THE FIELD OF “DATA SCIENCE.” THESE PARTNERSHIPS ARE ONE OF THE CONSTITUTIVE ELEMENTS OF WHAT I METHODOLOGICALLY REFER TO AS THE TECHNOLOGICAL UPDATE MOVEMENT OF PUBLIC SECURITY IN CEARÁ, WHICH IS THE OBJECT OF STUDY OF THE RESEARCH THAT UNDERPINS THIS THESIS. THROUGH QUALITATIVE INVESTIGATION THAT INCLUDED DOCUMENTARY AND BIBLIOGRAPHIC RESEARCH, AS WELL AS A SURVEY OF JOURNALISTIC ARTICLES AND NON-AUTOMATED MONITORING OF DIGITAL CONTENT, THIS STUDY INVOLVED DIRECT OBSERVATIONS STEMMING FROM A MULTISITUATED FIELDWORK AND INTERVIEWS WITH SOCIAL ACTORS DIRECTLY OR INDIRECTLY INVOLVED IN THE DEVELOPMENT AND/OR OPERATIONALISATION OF THESE TECHNOLOGIES. IN THIS WAY, THE AIM IS TO UNDERSTAND THE SOCIAL AND POLITICAL MEANINGS AND IMPLICATIONS OF THE USE OF EMERGING TECHNOLOGIES FOR CAPTURING, RECORDING, ENCODING, CROSS-REFERENCING, AND ANALYSING IMAGES AND DIGITAL DATA BY THE STATE PUBLIC SECURITY FORCES OF CEARÁ, WITH A PARTICULAR FOCUS ON THE TEMPORAL FRAMEWORK PERTAINING TO THE ADMINISTRATIONS OF FORMER GOVERNOR CAMILO SANTANA (PT) FROM 2015 TO 2022. THE USE OF THESE TECHNOLOGIES REVEALS A COMPLEX NETWORK OF HETEROGENEOUS ASSOCIATIONS THAT MOBILISE TECHNICAL INSTRUMENTS, POLITICAL ACTIONS, GOVERNMENT INITIATIVES, BUREAUCRATIC APPARATUSES, AND PUBLIC AGENTS.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>REESTRUTURAÇÃO PRODUTIVA;TECNOLOGIAS DIGITAIS;TECNOLOGIAS BANCÁRIAS;COMPETÊNCIAS TÉCNICAS E SOCIOEMOCIONAIS;QUALIFICAÇÃO PROFISSIONAL</t>
+          <t>ATUALIZAÇÃO TECNOLÓGICA;TECNOSOLUCIONISMO;DADOS;FORÇAS DE SEGURANÇA;SEGURANÇA PÚBLICA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>PRODUCTIVE RESTRUCTURING;DIGITAL TECHNOLOGIES;BANKING TECHNOLOGIES;TECHNICAL AND SOCIO-EMOTIONAL SKILLS;PROFESSIONAL TRAINING</t>
+          <t>TECHNOLOGICAL UPGRADING;TECHNOSOLUTIONISM;DATA;SECURITY FORCES;PUBLIC SECURITY</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -7981,41 +7981,41 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>NOEMIA LAZZARESCHI</t>
+          <t>CESAR BARREIRA</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>CIÊNCIAS SOCIAIS</t>
+          <t>SOCIOLOGIA</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>PONTIFÍCIA UNIVERSIDADE CATÓLICA DE SÃO PAULO</t>
+          <t>UNIVERSIDADE FEDERAL DO CEARÁ</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>PUCSP</t>
+          <t>UFC</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>SUDESTE</t>
+          <t>NORDESTE</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>SÃO PAULO</t>
+          <t>CEARÁ</t>
         </is>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
@@ -8034,16 +8034,16 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15793149</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16174984</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>15793149</t>
+          <t>16174984</t>
         </is>
       </c>
       <c r="AE54" t="n">
-        <v>2530079</v>
+        <v>1177406</v>
       </c>
     </row>
     <row r="55">
@@ -8062,37 +8062,37 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FERNANDA RIBAS BOHLER</t>
+          <t>OSCAR ARRUDA D ALVA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">BENEFÍCIO PARA QUEM? A REALIDADE DO TELETRABALHO NO INSTITUTO NACIONAL DO SEGURO SOCIAL A PARTIR DA PANDEMIA DA COVID-19. </t>
+          <t>ESTATÍSTICAS OFICIAIS E CAPITALISMO DE PLATAFORMA: A TRANSIÇÃO PARA UM REGIME DE DATAFICAÇÃO NO BRASIL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>O ANO DE 2020 TROUXE MUDANÇAS SEM PRECEDENTES PARA O MUNDO DO TRABALHO, SOBRETUDO PARA O TELETRABALHO, MODALIDADE QUE JÁ VINHA SENDO ADOTADA GRADUALMENTE, MAS QUE GANHOU RELEVÂNCIA NO CONTEXTO DA PANDEMIA DA COVID-19. NESSE CENÁRIO, O TRABALHO REMOTO FOI A ALTERNATIVA ENCONTRADA PELOS SETORES PÚBLICO E PRIVADO PARA A REDUÇÃO DO CONTÁGIO DA DOENÇA, BEM COMO PARA DAR CONTINUIDADE ÀS SUAS ATIVIDADES LABORAIS. NO INSTITUTO NACIONAL DO SEGURO SOCIAL (INSS), A MODALIDADE JÁ ERA UMA REALIDADE DESDE 2019, QUANDO FOI INSTITUÍDA A TÍTULO DE EXPERIÊNCIA-PILOTO NA INSTITUIÇÃO, PORÉM A PANDEMIA DA COVID-19 FORÇOU TODOS (AS) A SE ADAPTAREM COM O TELETRABALHO, TRAZENDO UMA NOVA CONDIÇÃO PARA OS (AS) SERVIDORES (AS), MESMO PARA AQUELES QUE JÁ TRABALHAVAM REMOTAMENTE. A PARTIR DESTE CONTEXTO, A PRESENTE TESE TEM COMO OBJETO DE ESTUDO A ANÁLISE DAS CONDIÇÕES DE TRABALHO DOS (AS) SERVIDORES (AS) DO INSS QUE TIVERAM QUE TRABALHAR REMOTAMENTE DURANTE O PERÍODO CRÍTICO DA PANDEMIA E OS QUE OPTARAM POR CONTINUAR NA MODALIDADE NO PERÍODO PÓS-PANDEMIA. A PESQUISA EMPÍRICA, COM ABORDAGEM QUANTI-QUALI, CONSISTIU NA ANÁLISE DE DADOS DA PESQUISA REALIZADA EM 2020, INTITULADA “O TRABALHO REMOTO/HOME OFFICE NO CONTEXTO DA PANDEMIA DA COVID-19”, REALIZADA POR INTEGRANTES DO GRUPO DE ESTUDOS TRABALHO E SOCIEDADE (GETS) DA UNIVERSIDADE FEDERAL DO PARANÁ (UFPR) COM PARCERIA DA REMIR (REDE DE ESTUDOS E MONITORAMENTO INTERDISCIPLINAR DA REFORMA TRABALHISTA), A QUAL OBTEVE O TOTAL DE 906 RESPOSTAS VÁLIDAS, SENDO 181 RESPOSTAS DE SERVIDORES (AS) DO INSS. EM 2023, APLICAMOS UM NOVO QUESTIONÁRIO ONLINE COM O FOCO EXCLUSIVO NO OBJETO DA PRESENTE TESE, O TELETRABALHO NO INSS, ATENTANDO PARA OS CONFLITOS QUE DESEMBOCARAM NA GREVE DE 2022 E SOBRE A RELAÇÃO DOS (AS) SERVIDORES (AS) COM O SINDICATO. NESSE SEGUNDO MOMENTO OBTIVEMOS NO TOTAL 24 QUESTIONÁRIOS RESPONDIDOS. AINDA, A FIM DE COMPREENDERMOS MELHOR AS DINÂMICAS DO TRABALHO DESENVOLVIDO PELOS SERVIDORES (AS), OS SISTEMAS PELOS QUAIS DESENVOLVEM SUAS ATIVIDADES REMOTAMENTE E A GESTÃO POR METAS APLICADAS A ELES (AS), ENTREVISTAMOS DOIS SERVIDORES, A PARTIR DE UM ROTEIRO DE ENTREVISTA SEMIESTRUTURADO. ATRAVÉS DOS DADOS COLETADOS, OBSERVAMOS QUE O TELETRABALHO COMO É INSTITUÍDO NO INSS CONTRIBUI PARA O DESMANTELAMENTO DO INSTITUTO, JÁ EM CURSO EM RAZÃO DAS POLÍTICAS NEOLIBERAIS DE ENXUGAMENTO ESTATAL E DA FINANCEIRIZAÇÃO DAS POLÍTICAS SOCIAIS QUE AGRAVAM AS CONDIÇÕES DE TRABALHO DOS (AS) SERVIDORES (AS), SEJA PELA NÃO REPOSIÇÃO DE PESSOAL AO QUADRO FUNCIONAL, SEJA POR MEIO DE REFORMAS QUE PREJUDICAM A MAIOR PARTE DA POPULAÇÃO QUE DEPENDE DO SISTEMA PREVIDENCIÁRIO. NUM CENÁRIO ONDE O QUADRO DE FUNCIONÁRIOS ESTÁ DEFASADO POR UM LADO, E A DEMANDA DE REQUERIMENTOS AUMENTA POR OUTRO, O INSS INSTITUI PARA OS SERVIDORES EM TELETRABALHO UM ADICIONAL DE METAS DE 30%, NÃO FORNECE ESTRUTURA ADEQUADA (EQUIPAMENTOS, CADEIRA ERGONÔMICA) E TAMPOUCO AJUDA COM OS CUSTOS COM INTERNET, LUZ ETC. OS (AS) SERVIDORES (AS) QUE JÁ SOFRIAM COM A ESTRUTURA PRECÁRIA DAS AGÊNCIAS PREVIDENCIÁRIAS, COM COMPUTADORES ANTIGOS, SISTEMA FALHO, INTERNET FRACA ETC., ALÉM DE TEREM QUE PRODUZIR MAIS, DEVEM ARCAR COM A RESPONSABILIDADE PELOS CUSTOS E RISCOS DO SEU TRABALHO. QUANTO AOS BENEFICIÁRIOS DO SISTEMA, EM ESPECIAL OS MAIS VULNERÁVEIS E OS MAIS IDOSOS, ESTÃO CADA VEZ MAIS AFASTADOS DELE EM VIRTUDE DA AUTOMATIZAÇÃO DOS REQUERIMENTOS, DA FALTA DE CONHECIMENTO E DE CONDIÇÕES DE EFETUAR UM PEDIDO DE BENEFÍCIO POR MEIO DIGITAL. O IMPACTO DESTE PROCESSO, PELO QUAL A GESTÃO DE METAS É IMPOSTA NO SETOR PÚBLICO, PREJUDICA AS CONDIÇÕES DE TRABALHO DOS SERVIDORES (AS) MAS, SOBRETUDO, ATINGE O DIREITO CONSTITUCIONAL À SEGURIDADE SOCIAL DA POPULAÇÃO.</t>
+          <t>COM ESTE TRABALHO BUSCAMOS COMPREENDER EM QUE MEDIDA OS PROCESSOS CONTEMPORÂNEOS DE DATAFICAÇÃO E A INTRODUÇÃO DE BIG DATA E CIÊNCIA DE DADOS NO INSTITUTO BRASILEIRO DE GEOGRAFIA E ESTATÍSTICA (IBGE) RECONFIGURAM O CAMPO DE PRODUÇÃO E DISTRIBUIÇÃO DE ESTATÍSTICAS OFICIAIS NO BRASIL. UTILIZANDO FERRAMENTAS DO ESTRUTURALISMO GENÉTICO DE BOURDIEU E DA SOCIOLOGIA DA QUANTIFICAÇÃO CONDUZIMOS UMA INVESTIGAÇÃO COMPARATIVA QUE ABORDA A IMPLANTAÇÃO DO HUB REGIONAL DE BIG DATA PARA A AMÉRICA LATINA NO IBGE, À LUZ DOS PROCESSOS HISTÓRICOS DE ESTRUTURAÇÃO DO CAMPO ESTATÍSTICO E DE TRANSIÇÃO DE REGIMES ESTATÍSTICOS, NOS CONTEXTOS DO NORTE-GLOBAL E DO BRASIL. A PESQUISA CONSISTIU NA ANÁLISE DE DADOS SECUNDÁRIOS, COTEJADOS COM DADOS PRIMÁRIOS, OBTIDOS POR MEIO DE ENTREVISTAS E OBSERVAÇÃO NÃO PARTICIPANTE. O TEMA É RELEVANTE ENQUANTO, NO CONTEXTO DO CAPITALISMO DE PLATAFORMA, A INCIDÊNCIA DAS BIG TECH NO CAMPO ESTATÍSTICO TRANSNACIONAL IMPLICA EM RISCOS À SOBERANIA DOS PAÍSES DO SUL-GLOBAL. NOSSA HIPÓTESE É A DE QUE A INTRODUÇÃO DE NOVAS FONTES DE DADOS E MÉTODOS NAS ESTATÍSTICAS OFICIAIS IMPLICA EM UMA INTERSEÇÃO ENTRE O CAMPO ESTATÍSTICO, TRADICIONALMENTE VINCULADO AO ESTADO, E O CAMPO ALGORÍTMICO, ASSOCIADO A CORPORAÇÕES PRIVADAS. ESTE ENGAJAMENTO CONDUZ A UMA TRANSIÇÃO PARA UM NOVO REGIME DE DATAFICAÇÃO. NOSSA TESE É A DE QUE ESTA TRANSIÇÃO É CARACTERIZADA POR DOIS OBSTÁCULOS. UM OBSTÁCULO ONTOLÓGICO, RELACIONADO À ECONOMIA POLÍTICA DOS DADOS, TENSIONADA ENTRE AS CONCEPÇÕES DE BEM PÚBLICO E MERCADORIA. E UM OBSTÁCULO EPISTEMOLÓGICO, RELACIONADO AOS MÉTODOS, TENSIONADOS ENTRE AS INTERPRETAÇÕES FREQUENTISTA E BAYESIANA DA CIÊNCIA ESTATÍSTICA. ESTES OBSTÁCULOS CONDUZEM A UM DUPLO MOVIMENTO NO CAMPO ESTATÍSTICO. ESFORÇOS PARA CRIAR MERCADOS DE DADOS PARA ESTATÍSTICAS OFICIAIS E GESTAR CIENTISTAS DE DADOS NOS INSTITUTOS NACIONAIS DE ESTATÍSTICA SE CONTRAPÕE A INICIATIVAS QUE VISAM A REGULAMENTAÇÃO, PROTEÇÃO E ACESSO AOS DADOS COMO BENS PÚBLICOS, ASSEGURANDO A SUA INCORPORAÇÃO E A PRESERVAÇÃO DOS MÉTODOS E FONTES ESTATÍSTICAS TRADICIONAIS, SOB A GOVERNANÇA DOS ESTATÍSTICOS DE ESTADO. NO CASO DO BRASIL E PAÍSES DO SUL-GLOBAL, DESTACA-SE A RELEVÂNCIA DOS CONTRAMOVIMENTOS NACIONAIS, PROTETIVOS DO CARÁTER PÚBLICO DAS ESTATÍSTICAS OFICIAS E DA SOBERANIA DE DADOS, NA DETERMINAÇÃO DO GRAU DE AUTONOMIA OU DEPENDÊNCIA QUE SEUS SISTEMAS ESTATÍSTICOS PODERÃO ASSUMIR NA TRANSIÇÃO PARA UM NOVO REGIME DE DATAFICAÇÃO.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>THE YEAR 2020 BROUGHT UNPRECEDENTED CHANGES TO THE WORLD OF WORK, ESPECIALLY FOR TELEWORKING, A MODALITY THAT HAD ALREADY BEEN GRADUALLY ADOPTED, BUT WHICH GAINED RELEVANCE IN THE CONTEXT OF THE COVID-19 PANDEMIC. IN THIS SCENARIO, REMOTE WORK WAS THE ALTERNATIVE FOUND BY THE PUBLIC AND PRIVATE SECTORS TO REDUCE THE SPREAD OF THE DISEASE, AS WELL AS TO CONTINUE THEIR WORK ACTIVITIES. AT THE NATIONAL SOCIAL SECURITY INSTITUTE (INSS), THE MODALITY HAS BEEN A REALITY SINCE 2019, WHEN IT WAS ESTABLISHED AS A PILOT EXPERIENCE AT THE INSTITUTION, BUT THE COVID-19 PANDEMIC FORCED EVERYONE TO ADAPT TO TELEWORKING, BRINGING A NEW CONDITION FOR THE PUBLIC SERVANTS, EVEN FOR THOSE WHO WERE ALREADY TELEWORKING BEFORE. FROM THIS CONTEXT, THE OBJECT OF STUDY OF THIS THESIS IS TO ANALYZE THE WORKING CONDITIONS OF INSS EMPLOYEES WHO HAD TO WORK REMOTELY DURING THE CRITICAL PERIOD OF THE PANDEMIC AND THOSE WHO CHOSE TO CONTINUE IN THE MODALITY DURING THE POST-PANDEMIC PERIOD. THE EMPIRICAL RESEARCH, WITH A QUANTITATIVEQUALITATIVE APPROACH, CONSISTED OF ANALYZING DATA FROM RESEARCH CARRIED OUT IN 2020, ENTITLED “REMOTE WORK/HOME OFFICE IN THE CONTEXT OF THE COVID-19 PANDEMIC”, CARRIED OUT BY MEMBERS OF THE WORK AND SOCIETY STUDY GROUP (GETS) FROM THE FEDERAL UNIVERSITY OF PARANÁ (UFPR) IN PARTNERSHIP WITH REMIR (NETWORK FOR STUDIES AND INTERDISCIPLINARY MONITORING OF LABOR REFORM), THAT OBTAINED A TOTAL OF 906 VALID RESPONSES, OF WHICH 181 FROM INSS PUBLIC EMPLOYEES. IN 2023, WE APPLIED A NEW ONLINE QUESTIONNAIRE WITH AN EXCLUSIVE FOCUS ON THE OBJECT OF THIS THESIS, TELEWORKING AT INSS, PAYING ATTENTION TO THE CONFLICTS THAT LED TO THE 2022 STRIKE AND TO THE RELATIONSHIP BETWEEN CIVIL SERVANTS AND THE UNION. IN THIS SECOND MOMENT, WE OBTAINED A TOTAL OF 24 COMPLETED QUESTIONNAIRES. FURTHERMORE, TO UNDERSTAND THE DYNAMICS OF THE WORK CARRIED OUT BY THE PUBLIC SERVERS, THE SYSTEMS THROUGH WHICH THEY CARRY OUT THEIR ACTIVITIES REMOTELY AND THE MANAGEMENT BY GOALS APPLIED TO THEM, WE INTERVIEWED TWO SERVERS, BASED ON A SEMI-STRUCTURED INTERVIEW SCRIPT. THROUGH THE DATA COLLECTED, WE OBSERVED THAT TELEWORKING AS ESTABLISHED IN THE INSS CONTRIBUTES TO THE DISMANTLING OF THE INSTITUTE, ALREADY UNDERWAY DUE TO NEOLIBERAL POLICIES OF STATE DOWNSIZING AND THE FINANCIALIZATION OF SOCIAL POLICIES THAT AGGRAVATE THE CONDITIONS OF THE PUBLIC EMPLOYEES, EITHER BY NOT REPLACING PERSONNEL LOSSES IN THE WORKFORCE, OR THROUGH REFORMS THAT HARM THE MAJORITY OF THE POPULATION THAT DEPENDS ON THE SOCIAL SECURITY SYSTEM. IN A SCENARIO WHERE THE NUMBER OF EMPLOYEES IS OUTDATED ON ONE HAND, AND THE DEMAND FOR APPLICATIONS INCREASES ON THE OTHER, THE INSS ESTABLISHES AN ADDITIONAL TARGET OF 30% FOR TELEWORKING EMPLOYEES, DOES NOT PROVIDE ADEQUATE STRUCTURE (EQUIPMENT, ERGONOMIC CHAIR) AND NEITHER HELP WITH INTERNET, ELECTRICITY COSTS, ETC. SERVERS WHO ALREADY SUFFERED FROM THE PRECARIOUS STRUCTURE OF SOCIAL SECURITY AGENCIES, WITH OLD COMPUTERS, FAULTY SYSTEMS, WEAK INTERNET, ETC., IN ADDITION TO HAVING TO PRODUCE MORE, MUST TAKE RESPONSIBILITY FOR THE COSTS AND RISKS OF THEIR WORK. THE SUPPOSED BENEFICIARIES OF THE SYSTEM, ESPECIALLY THE MOST VULNERABLE AND THE ELDERLY, ARE INCREASINGLY SEPARATED FROM IT DUE TO THE AUTOMATION OF APPLICATIONS AND THE LACK OF KNOWLEDGE AND CONDITIONS TO MAKE A BENEFIT REQUEST THROUGH TECHNOLOGICAL MEANS. THE IMPACT OF THIS PROCESS, BY WHICH MANAGEMENT BY GOALS IS IMPOSED IN THE PUBLIC SECTOR, HARMS THE WORKING CONDITIONS OF CIVIL SERVANTS BUT, ABOVE ALL, AFFECTS THE CONSTITUTIONAL RIGHT TO SOCIAL SECURITY OF THE POPULATION.</t>
+          <t>WITH THIS WORK WE SEEK TO UNDERSTAND TO WHAT EXTENT CONTEMPORARY PROCESSES OF DATAFICATION AND THE INTRODUCTION OF BIG DATA AND DATA SCIENCE AT THE BRAZILIAN INSTITUTE OF GEOGRAPHY AND STATISTICS (IBGE) RECONFIGURE THE FIELD OF PRODUCTION AND DISTRIBUTION OF OFFICIAL STATISTICS IN BRAZIL. USING TOOLS FROM BOURDIEU'S GENETIC STRUCTURALISM AND FROM THE SOCIOLOGY OF QUANTIFICATION, WE CONDUCTED A COMPARATIVE INVESTIGATION THAT ADDRESSES THE IMPLEMENTATION OF THE REGIONAL BIG DATA HUB FOR LATIN AMERICA AT IBGE, IN LIGHT OF THE HISTORICAL PROCESSES OF STRUCTURING THE STATISTICAL FIELD AND TRANSITION OF STATISTICAL REGIMES, IN THE CONTEXTS OF THE GLOBAL NORTH AND BRAZIL. THE RESEARCH CONSISTED OF THE ANALYSIS OF SECONDARY DATA, COMPARED WITH PRIMARY DATA, OBTAINED THROUGH INTERVIEWS AND NON-PARTICIPANT OBSERVATION. THE TOPIC IS RELEVANT TO THE EXTENT THAT, IN THE CONTEXT OF PLATFORM CAPITALISM, THE INCIDENCE OF BIG TECH IN THE TRANSNATIONAL STATISTICAL FIELD IMPLIES RISKS TO THE SOVEREIGNTY OF COUNTRIES IN THE GLOBAL SOUTH. OUR HYPOTHESIS IS THAT THE INTRODUCTION OF NEW DATA SOURCES AND METHODS IN OFFICIAL STATISTICS IMPLIES AN INTERSECTION BETWEEN THE STATISTICAL FIELD, TRADITIONALLY LINKED TO THE STATE, AND THE ALGORITHMIC FIELD, ASSOCIATED TO PRIVATE CORPORATIONS. THIS ENGAGEMENT LEADS TO A TRANSITION TO A NEW DATAFICATION REGIME. OUR THESIS IS THAT THIS TRANSITION IS CHARACTERIZED BY TWO OBSTACLES. AN ONTOLOGICAL OBSTACLE, RELATED TO THE POLITICAL ECONOMY OF DATA, TENSIONED BETWEEN THE CONCEPTS OF PUBLIC GOOD AND COMMODITY. AND AN EPISTEMOLOGICAL OBSTACLE, RELATED TO THE METHODS, TENSIONED BETWEEN THE FREQUENTIST AND BAYESIAN INTERPRETATIONS OF STATISTICS. THESE OBSTACLES LEAD TO A DOUBLE MOVEMENT IN THE STATISTICAL FIELD. EFFORTS TO CREATE DATA MARKETS FOR OFFICIAL STATISTICS AND TO BREAD DATA SCIENTISTS AT NATIONAL STATISTICS OFFICES ARE OPPOSED TO INITIATIVES AIMED AT REGULATING, PROTECTING AND ACCESSING DATA AS PUBLIC GOODS, ENSURING THEIR INCORPORATION WITH THE PRESERVATION OF METHODS AND TRADITIONAL STATISTICAL SOURCES, UNDER THE GOVERNANCE OF STATE STATISTICIANS. IN THE CASE OF BRAZIL AND COUNTRIES IN THE GLOBAL SOUTH, THE RELEVANCE OF NATIONAL COUNTER-MOVEMENTS, PROTECTIVE OF THE PUBLIC NATURE OF OFFICIAL STATISTICS AND DATA SOVEREIGNTY, STANDS OUT IN DETERMINING THE DEGREE OF AUTONOMY OR DEPENDENCE THAT THEIR STATISTICAL SYSTEMS MAY ASSUME IN THE TRANSITION TO A NEW DATAFICATION REGIME.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CONDIÇÕES DE TRABALHO;TELETRABALHO NO INSS;SETOR PÚBLICO;PANDEMIA.</t>
+          <t>ESTATÍSTICAS OFICIAIS;PLATAFORMAS;BIG DATA;CIÊNCIA DE DADOS</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>WORKING CONDITIONS;TELEWORKING AT INSS;PUBLIC SECTOR;PANDEMIC.</t>
+          <t>OFFICIAL STATISTICS;PLATFORMS;DATA SCIENCE</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>MARIA APARECIDA DA CRUZ BRIDI</t>
+          <t>EDEMILSON CRUZ SANTANA JUNIOR</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -8132,31 +8132,31 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DO PARANÁ</t>
+          <t>UNIVERSIDADE FEDERAL DO CEARÁ</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>UFPR</t>
+          <t>UFC</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>SUL</t>
+          <t>NORDESTE</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>PARANÁ</t>
+          <t>CEARÁ</t>
         </is>
       </c>
       <c r="Y55" t="n">
-        <v>209</v>
+        <v>381</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
@@ -8175,16 +8175,16 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15589576</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16175018</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>15589576</t>
+          <t>16175018</t>
         </is>
       </c>
       <c r="AE55" t="n">
-        <v>2675423</v>
+        <v>1015048</v>
       </c>
     </row>
     <row r="56">
@@ -8195,45 +8195,45 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DOUTORADO</t>
+          <t>MESTRADO</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MARCELO DA SILVA RIBEIRO</t>
+          <t>LETICIA DE FRANCA PAES</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>“DO TECNOSOLUCIONISMO AO TECNOVIGILANTISMO”: UM ESTUDO SOCIOLÓGICO SOBRE OS USOS DE EMERGENTES TECNOLOGIAS PELAS FORÇAS DE SEGURANÇA DO CEARÁ</t>
+          <t>AUTOMÓVEIS VERSUS MOBILIDADE: UMA ANÁLISE SOCIOLÓGICA DO MERCADO”,</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>A PRESENTE TESE TEM POR OBJETIVO PRINCIPAL ANALISAR SOCIOLOGICAMENTE OS ARRANJOS SOCIAIS E POLÍTICOS ENVOLVENDO A RECENTE ADOÇÃO DE NOVOS APARATOS TECNOLÓGICOS DE CAPTAÇÃO, REGISTRO, ARMAZENAMENTO, CODIFICAÇÃO E VISUALIZAÇÃO ANALÍTICA DE IMAGENS E DADOS DIGITAIS POR PARTE DAS FORÇAS ESTADUAIS DE SEGURANÇA PÚBLICA NO CEARÁ. ATUALMENTE NO BRASIL, O USO DE NOVAS TECNOLOGIAS PARA OS FINS DE OPERAÇÕES POLICIAIS E DE INVESTIGAÇÕES CRIMINAIS RECEBEM MAIOR ATENÇÃO NO CAMPO INSTITUCIONAL DA SEGURANÇA PÚBLICA. NOS ÚLTIMOS CINCO ANOS, O ESTADO DO CEARÁ RECEBEU RELATIVA NOTABILIDADE NO CENÁRIO NACIONAL COMO UM DOS ESTADOS DO PAÍS QUE MAIS INVESTEM NA ADOÇÃO DE NOVOS EQUIPAMENTOS ELETRÔNICOS E DIGITAIS COMO CÂMERAS DE VIGILÂNCIA DE ÚLTIMA GERAÇÃO, TECNOLOGIAS DE RECONHECIMENTO FACIAL (TRF) E PLATAFORMAS DIGITAIS DE BIG DATA, PARA AUXÍLIO NO COMBATE ESTATAL À CRIMINALIDADE, SENDO A MAIOR PARTE DESSAS “FERRAMENTAS” PROJETADAS E DESENVOLVIDAS NO PRÓPRIO ESTADO POR MEIO DE PARCERIAS INSTITUCIONAIS ENTRE O GOVERNO E CENTROS DE PESQUISA DA ÁREA DA “CIÊNCIA DE DADOS”. ESSAS PARCERIAS SÃO UM DOS ELEMENTOS CONSTITUTIVOS DO QUE NOMEIO METODOLOGICAMENTE AQUI POR MOVIMENTO DE ATUALIZAÇÃO TECNOLÓGICA DA SEGURANÇA PÚBLICA CEARENSE, O QUAL SE CONFIGURA OBJETO DE ESTUDO DA PESQUISA DA QUAL RESULTA ESTA TESE. MEDIANTE UMA INVESTIGAÇÃO QUALITATIVA QUE CONTOU COM UM A PESQUISA DOCUMENTAL E BIBLIOGRÁFICA, COM UM LEVANTAMENTO DE MATÉRIAS JORNALÍSTICAS, ALÉM DE UM MONITORAMENTO NÃO-AUTOMATIZADO DE CONTEÚDOS DIGITAIS, COM OBSERVAÇÕES DIRETAS DECORRENTES DE UM TRABALHO DE CAMPO MULTISITUADO E ENTREVISTAS COM ATORES SOCIAIS IMPLICADOS DIRETA OU INDIRETAMENTE COM O DESENVOLVIMENTO E/OU OPERACIONALIZAÇÃO DESSAS TECNOLOGIAS. DESSE MODO, BUSCA-SE AQUI COMPREENDER QUAIS OS SIGNIFICADOS E SENTIDOS SOCIAIS E POLÍTICOS DOS USOS DAS EMERGENTES TECNOLOGIAS DE CAPTAÇÃO, REGISTRO, CODIFICAÇÃO, CRUZAMENTO E ANÁLISE DE IMAGENS E DADOS DIGITAIS POR PARTE DAS FORÇAS ESTADUAIS DE SEGURANÇA PÚBLICA DO CEARÁ, COM PRIVILÉGIO SOBRE O RECORTE TEMPORAL REFERENTE ÀS GESTÕES DO EX-GOVERNADOR CAMILO SANTANA (PT), DURANTE OS ANOS DE 2015-2022. OS USOS DESSAS TECNOLOGIAS REVELAM UMA COMPLEXA REDE DE ASSOCIAÇÕES HETEROGÊNEAS QUE MOBILIZAM INSTRUMENTOS TÉCNICOS, AÇÕES POLÍTICAS E DE GOVERNO, MOBILIZA APARATOS BUROCRÁTICOS E AGENTES PÚBLICOS.</t>
+          <t>O PRESENTE TRABALHO TEM COMO OBJETIVO COMPREENDER OS PROCESSOS E DINÂMICAS QUE TÊM OCORRIDO NO SETOR AUTOMOTIVO A PARTIR DO SURGIMENTO DE UMA SUB-INDÚSTRIA DA MOBILIDADE, QUE ALTERA OS MODELOS DE NEGÓCIOS DO MERCADO DE AUTOMÓVEIS COM A OFERTA DE SERVIÇOS DE MOBILIDADE; MODIFICA A ESTRUTURA PRODUTIVA COM O AUMENTO DA AUTOMATIZAÇÃO NAS PLANTAS; INSERE AS MONTADORAS EM ECOSSISTEMAS DIGITAIS COM TECNOLOGIAS COMO BIG DATA E INTERNET DAS COISAS; CRIA NOVAS FONTES DE VALOR AGREGADO A PARTIR DO MERCADO DE DADOS E INSERE NOVOS ATORES NAS DINÂMICAS DE CONCORRÊNCIA E PARCERIAS. A PESQUISA TEM COMO OBJETO A MONTADORA JAPONESA TOYOTA MOTOR CORPORATION, ENQUANTO ESTUDO DE CASO DE DIMENSÃO EXPLORATÓRIA, COM RECORTE DE TEMPO DE DOZE ANOS. NO TOCANTE ÀS ESCOLHAS METODOLÓGICAS DE COLETA DE DADOS, PRIORIZOU-SE A COLETA DOCUMENTAL, COM TRATAMENTO DE ANÁLISE DE CONTEÚDO. COMO PROPOSTA TEÓRICA, REALIZOU-SE A REVISÃO BIBLIOGRÁFICA DE VERTENTES DA SOCIOLOGIA ECONÔMICA SOB DUAS ÓTICAS: A ANÁLISE DOS MERCADOS A PARTIR DOS PROCESSOS DE QUALIFICAÇÃO E VALORAÇÃO DOS PRODUTOS; E A ANÁLISE DAS INSTITUIÇÕES E ESTRUTURAS DE PODER NAS ARENAS DE DISPUTAS DESSES MERCADOS. COMO PRINCIPAL RESULTADO, A ANÁLISE DO CASO DA TOYOTA SUGERE QUE OS PROCESSOS DE QUALIFICAÇÃO DO BEM, A MOBILIZAÇÃO DOS DISPOSITIVOS DE JULGAMENTO, DOS VALORES IMAGINATIVOS E A CONSTRUÇÃO DE PERFIS E IDENTIDADES TANTO DOS PRODUTOS QUANTO DA EMPRESA EM SI FUNCIONAM COMO FERRAMENTAS PARA MANUTENÇÃO DAS CONCEPÇÕES DE CONTROLE DA EMPRESA, UMA VEZ QUE A TOYOTA PASSOU A ATUAR EM NOVOS MERCADOS E SE REORGANIZOU PARA PROVER OS NOVOS PRODUTOS E SERVIÇOS SEM QUE ISSO SE PROVASSE ENQUANTO DESINSTITUCIONALIZAÇÃO DO MERCADO, SENDO A MANUTENÇÃO DO STATUS QUO SUA LUTA PRINCIPAL.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>THE PRESENT THESIS AIMS PRIMARILY TO SOCIOLOGICALLY ANALYSE THE SOCIAL AND POLITICAL ARRANGEMENTS SURROUNDING THE RECENT ADOPTION OF NEW TECHNOLOGICAL APPARATUSES FOR CAPTURING, RECORDING, STORING, ENCODING, AND ANALYTICALLY VISUALISING IMAGES AND DIGITAL DATA BY STATE PUBLIC SECURITY FORCES IN CEARÁ. CURRENTLY IN BRAZIL, THE USE OF NEW TECHNOLOGIES FOR POLICE OPERATIONS AND CRIMINAL INVESTIGATIONS IS RECEIVING GREATER ATTENTION WITHIN THE INSTITUTIONAL FIELD OF PUBLIC SECURITY. OVER THE PAST FIVE YEARS, THE STATE OF CEARÁ HAS GAINED RELATIVE PROMINENCE ON THE NATIONAL SCENE AS ONE OF THE STATES IN THE COUNTRY THAT INVESTS MOST IN THE ADOPTION OF NEW ELECTRONIC AND DIGITAL EQUIPMENT, SUCH AS STATE-OF-THE-ART SURVEILLANCE CAMERAS, FACIAL RECOGNITION TECHNOLOGIES (FRT), AND DIGITAL BIG DATA PLATFORMS, TO ASSIST IN THE STATE'S FIGHT AGAINST CRIME. MOST OF THESE “TOOLS” HAVE BEEN DESIGNED AND DEVELOPED WITHIN THE STATE THROUGH INSTITUTIONAL PARTNERSHIPS BETWEEN THE GOVERNMENT AND RESEARCH CENTRES IN THE FIELD OF “DATA SCIENCE.” THESE PARTNERSHIPS ARE ONE OF THE CONSTITUTIVE ELEMENTS OF WHAT I METHODOLOGICALLY REFER TO AS THE TECHNOLOGICAL UPDATE MOVEMENT OF PUBLIC SECURITY IN CEARÁ, WHICH IS THE OBJECT OF STUDY OF THE RESEARCH THAT UNDERPINS THIS THESIS. THROUGH QUALITATIVE INVESTIGATION THAT INCLUDED DOCUMENTARY AND BIBLIOGRAPHIC RESEARCH, AS WELL AS A SURVEY OF JOURNALISTIC ARTICLES AND NON-AUTOMATED MONITORING OF DIGITAL CONTENT, THIS STUDY INVOLVED DIRECT OBSERVATIONS STEMMING FROM A MULTISITUATED FIELDWORK AND INTERVIEWS WITH SOCIAL ACTORS DIRECTLY OR INDIRECTLY INVOLVED IN THE DEVELOPMENT AND/OR OPERATIONALISATION OF THESE TECHNOLOGIES. IN THIS WAY, THE AIM IS TO UNDERSTAND THE SOCIAL AND POLITICAL MEANINGS AND IMPLICATIONS OF THE USE OF EMERGING TECHNOLOGIES FOR CAPTURING, RECORDING, ENCODING, CROSS-REFERENCING, AND ANALYSING IMAGES AND DIGITAL DATA BY THE STATE PUBLIC SECURITY FORCES OF CEARÁ, WITH A PARTICULAR FOCUS ON THE TEMPORAL FRAMEWORK PERTAINING TO THE ADMINISTRATIONS OF FORMER GOVERNOR CAMILO SANTANA (PT) FROM 2015 TO 2022. THE USE OF THESE TECHNOLOGIES REVEALS A COMPLEX NETWORK OF HETEROGENEOUS ASSOCIATIONS THAT MOBILISE TECHNICAL INSTRUMENTS, POLITICAL ACTIONS, GOVERNMENT INITIATIVES, BUREAUCRATIC APPARATUSES, AND PUBLIC AGENTS.</t>
+          <t>THE PRESENT WORK AIMS TO COMPREHEND THE PROCESSES AND DYNAMICS THAT HAVE BEEN TAKING PLACE IN THE AUTOMOTIVE SECTOR FROM THE EMERGENCE OF A SUB-INDUSTRY OF MOBILITY, THAT MODIFIES THE BUSINESS MODELS OF THE CAR MARKET BASED ON THE OFFER OF MOBILITY SERVICES; IT ALSO ALTERS THE PRODUCTION STRUCTURE BY INCREASING THE PLANT AUTOMATION; INSERTS AUTOMAKERS IN DIGITAL ECOSYSTEMS WITH TECHNOLOGIES SUCH AS BIG DATA AND INTERNET OF THINGS; CREATES NEW SOURCES OF ADDED VALUE FROM THE DATA MARKET AND ALSO INSERTS NEW ACTORS IN THE DYNAMICS OF COMPETITION AND PARTNERSHIPS. THE OBJECT OF THIS RESEARCH IS ONE OF THESE MANUFACTURERS, THE JAPANESE AUTOMAKER TOYOTA MOTOR CORPORATION, AS A CASE STUDY OF AN EXPLORATORY DIMENSION, WITH A TWELVE-YEAR TIME FRAME. CONSIDERING METHODOLOGICAL CHOICES OF DATA COLLECTING, THE PRIORITY WAS THE DOCUMENTAL APPROACH, WITH CONTENT ANALYSIS TREATMENT. THE THEORETICAL PROPOSAL CHOSEN CONCERNED A BIBLIOGRAPHICAL REVIEW OF STRANDS OF THE ECONOMIC SOCIOLOGY FROM TWO PARTICULAR PERSPECTIVES: THE ANALYSIS OF MARKETS FROM THE QUALIFICATION AND VALUATION OF PRODUCTS; AND THE ANALYSIS OF INSTITUTIONS AND STRUCTURES OF POWER IN THE ARENAS OF DISPUTE OF THESE MARKETS. AS MAIN RESULT, THE ANALYSIS OF THE TOYOTA CASE SUGGESTS THAT THE PROPERTY QUALIFICATION PROCESSES, AS WELL AS THE MOBILIZATION OF JUDGMENT DEVICES, THE IMAGINATIVE VALUES AND THE CONSTRUCTION OF PROFILES AND IDENTITIES FOR BOTH THE PRODUCTS AND THE COMPANY ITSELF WORK AS TOOLS FOR MAINTAINING THE COMPANY’S CONCEPTS OF CONTROL, AS THE COMPANY STARTED TO ACT IN NEW MARKETS AND HAS REORGANIZED ITSELF TO SUPPLY NEW PRODUCTS AND SERVICES, EVEN THOUGH THIS DID NOT PROVE TO BE THE DEINSTITUTIONALIZATION OF THE MARKET, BEING THE MAINTENANCE OF THE STATUS QUO ITS MAIN STRUGGLE.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ATUALIZAÇÃO TECNOLÓGICA;TECNOSOLUCIONISMO;DADOS;FORÇAS DE SEGURANÇA;SEGURANÇA PÚBLICA</t>
+          <t>MERCADO DE AUTOMÓVEIS;SOCIOLOGIA ECONÔMICA;MOBILIDADE;TOYOTA.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>TECHNOLOGICAL UPGRADING;TECHNOSOLUTIONISM;DATA;SECURITY FORCES;PUBLIC SECURITY</t>
+          <t>AUTO MARKET;ECONOMIC SOCIOLOGY;MOBILITY;TOYOTA.</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>CESAR BARREIRA</t>
+          <t>RAPHAEL JONATHAS DA COSTA LIMA</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -8273,31 +8273,31 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DO CEARÁ</t>
+          <t>UNIVERSIDADE FEDERAL FLUMINENSE</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>UFC</t>
+          <t>UFF</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>NORDESTE</t>
+          <t>SUDESTE</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>CEARÁ</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="Y56" t="n">
-        <v>350</v>
+        <v>107</v>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
@@ -8316,16 +8316,16 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16174984</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11436964</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>16174984</t>
+          <t>11436964</t>
         </is>
       </c>
       <c r="AE56" t="n">
-        <v>1177406</v>
+        <v>2997668</v>
       </c>
     </row>
     <row r="57">
@@ -8336,45 +8336,45 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DOUTORADO</t>
+          <t>MESTRADO</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OSCAR ARRUDA D ALVA</t>
+          <t>MURILO APARECIDO GONCALVES</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ESTATÍSTICAS OFICIAIS E CAPITALISMO DE PLATAFORMA: A TRANSIÇÃO PARA UM REGIME DE DATAFICAÇÃO NO BRASIL</t>
+          <t>TECNOLOGIA ESPACIAL, RISCO E POLÍTICA: O CASO INPE SÃO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>COM ESTE TRABALHO BUSCAMOS COMPREENDER EM QUE MEDIDA OS PROCESSOS CONTEMPORÂNEOS DE DATAFICAÇÃO E A INTRODUÇÃO DE BIG DATA E CIÊNCIA DE DADOS NO INSTITUTO BRASILEIRO DE GEOGRAFIA E ESTATÍSTICA (IBGE) RECONFIGURAM O CAMPO DE PRODUÇÃO E DISTRIBUIÇÃO DE ESTATÍSTICAS OFICIAIS NO BRASIL. UTILIZANDO FERRAMENTAS DO ESTRUTURALISMO GENÉTICO DE BOURDIEU E DA SOCIOLOGIA DA QUANTIFICAÇÃO CONDUZIMOS UMA INVESTIGAÇÃO COMPARATIVA QUE ABORDA A IMPLANTAÇÃO DO HUB REGIONAL DE BIG DATA PARA A AMÉRICA LATINA NO IBGE, À LUZ DOS PROCESSOS HISTÓRICOS DE ESTRUTURAÇÃO DO CAMPO ESTATÍSTICO E DE TRANSIÇÃO DE REGIMES ESTATÍSTICOS, NOS CONTEXTOS DO NORTE-GLOBAL E DO BRASIL. A PESQUISA CONSISTIU NA ANÁLISE DE DADOS SECUNDÁRIOS, COTEJADOS COM DADOS PRIMÁRIOS, OBTIDOS POR MEIO DE ENTREVISTAS E OBSERVAÇÃO NÃO PARTICIPANTE. O TEMA É RELEVANTE ENQUANTO, NO CONTEXTO DO CAPITALISMO DE PLATAFORMA, A INCIDÊNCIA DAS BIG TECH NO CAMPO ESTATÍSTICO TRANSNACIONAL IMPLICA EM RISCOS À SOBERANIA DOS PAÍSES DO SUL-GLOBAL. NOSSA HIPÓTESE É A DE QUE A INTRODUÇÃO DE NOVAS FONTES DE DADOS E MÉTODOS NAS ESTATÍSTICAS OFICIAIS IMPLICA EM UMA INTERSEÇÃO ENTRE O CAMPO ESTATÍSTICO, TRADICIONALMENTE VINCULADO AO ESTADO, E O CAMPO ALGORÍTMICO, ASSOCIADO A CORPORAÇÕES PRIVADAS. ESTE ENGAJAMENTO CONDUZ A UMA TRANSIÇÃO PARA UM NOVO REGIME DE DATAFICAÇÃO. NOSSA TESE É A DE QUE ESTA TRANSIÇÃO É CARACTERIZADA POR DOIS OBSTÁCULOS. UM OBSTÁCULO ONTOLÓGICO, RELACIONADO À ECONOMIA POLÍTICA DOS DADOS, TENSIONADA ENTRE AS CONCEPÇÕES DE BEM PÚBLICO E MERCADORIA. E UM OBSTÁCULO EPISTEMOLÓGICO, RELACIONADO AOS MÉTODOS, TENSIONADOS ENTRE AS INTERPRETAÇÕES FREQUENTISTA E BAYESIANA DA CIÊNCIA ESTATÍSTICA. ESTES OBSTÁCULOS CONDUZEM A UM DUPLO MOVIMENTO NO CAMPO ESTATÍSTICO. ESFORÇOS PARA CRIAR MERCADOS DE DADOS PARA ESTATÍSTICAS OFICIAIS E GESTAR CIENTISTAS DE DADOS NOS INSTITUTOS NACIONAIS DE ESTATÍSTICA SE CONTRAPÕE A INICIATIVAS QUE VISAM A REGULAMENTAÇÃO, PROTEÇÃO E ACESSO AOS DADOS COMO BENS PÚBLICOS, ASSEGURANDO A SUA INCORPORAÇÃO E A PRESERVAÇÃO DOS MÉTODOS E FONTES ESTATÍSTICAS TRADICIONAIS, SOB A GOVERNANÇA DOS ESTATÍSTICOS DE ESTADO. NO CASO DO BRASIL E PAÍSES DO SUL-GLOBAL, DESTACA-SE A RELEVÂNCIA DOS CONTRAMOVIMENTOS NACIONAIS, PROTETIVOS DO CARÁTER PÚBLICO DAS ESTATÍSTICAS OFICIAS E DA SOBERANIA DE DADOS, NA DETERMINAÇÃO DO GRAU DE AUTONOMIA OU DEPENDÊNCIA QUE SEUS SISTEMAS ESTATÍSTICOS PODERÃO ASSUMIR NA TRANSIÇÃO PARA UM NOVO REGIME DE DATAFICAÇÃO.</t>
+          <t>ESTE TRABALHO PRODUZ UMA INVESTIGAÇÃO SOCIOLÓGICA ACERCA DAS DISPUTAS POLÍTICAS ENVOLVENDO O INPE (INSTITUTO NACIONAL DE PESQUISAS ESPACIAIS) E O PRESIDENTE JAIR MESSIAS BOLSONARO. APLICANDO CONCEITOS DE “RISCO” E “SOCIEDADE DE RISCO”, DE ULRICH BECK, O ESTUDO ESTABELECEU UMA RELAÇÃO DA PERSPECTIVA SOCIOLÓGICA COM ENFOQUE NA QUESTÃO AMBIENTAL, BEM COMO NAS POTENCIALIDADES DE NOVOS RECURSOS LIGADOS ÀS CIÊNCIAS ESPACIAIS E DA COMPUTAÇÃO, ESPECIALMENTE OS SATÉLITES E BANCOS DE DADOS. COM ESTES RECURSOS TECNOLÓGICOS, ARTICULA-SE UM COMPLEXO SISTEMA DE MINERAÇÃO DE DADOS, ONDE OS DADOS SÃO COLETADOS E CONVERTIDOS EM VALIOSAS INFORMAÇÕES. DESSE MODO, POSSUIR ESSES SISTEMAS SIGNIFICA MANTER SOB O CONTROLE, POR EXEMPLO, IMAGENS DA SUPERFÍCIE TERRESTRE DE DIVERSAS QUALIDADES TECNOLÓGICAS E FORMAS DE USO. SÃO INSTITUTOS LIGADOS A ESTADOS OU MESMO EMPRESAS PRIVADAS QUEM MAIS OS POSSUEM; CABE RESSALTAR, PORTANTO, QUE EXISTE CERTA EXCLUSIVIDADE DE ACESSO. NO CASO BRASILEIRO, O INPE É QUEM CONCENTRA TODOS OS ELEMENTOS APRESENTADOS, SEJA SUA DIMENSÃO TÉCNICA, SEJA NA DIMENSÃO POLÍTICA. O PERCURSO DE INSTITUCIONALIZAÇÃO DAS CIÊNCIAS ESPACIAIS NO BRASIL, ESPECIALMENTE ATRELADAS AO INPE, REPRESENTA AVANÇOS TECNOLÓGICOS PARADIGMÁTICOS NESTE SETOR. CONTUDO, A TRADIÇÃO DE PUBLICAR SEUS BANCOS DE DADOS ABERTAMENTE EM SEU SITE GEROU, NO ATUAL GOVERNO, FORTE REAÇÃO, POR DESTACAR A CRISE AMBIENTAL MOTIVADA PELO DESMATAMENTO. TENDO EM VISTA A EXPERIÊNCIA DO INSTITUTO SE CONSOLIDAR EM MEIO À DITADURA MILITAR, EVENTOS RECENTES ACENDEM O ALERTA DE UM PASSADO QUE VOLTA A ASSOMBRAR. PORTANTO, O TEMA DO RISCO SE REFERE AOS PROCESSOS QUE ESTÃO EM CURSO ENVOLVENDO O SUFOCAMENTO DOS HORIZONTES CIENTÍFICOS QUANDO EMPURRADOS A ESSA ARENA POLÍTICA IMPOSITIVA, COLOCANDO EM XEQUE A AUTONOMIA DE INSTITUTOS DE PESQUISA, BEM COMO INTERESSES DA SOCIEDADE CIVIL. ISSO NOS PERMITE CONSTATAR A DIMENSÃO POLÍTICA DESTES ARTEFATOS TÉCNICOS, SOBRETUDO QUANDO INTERESSES ESPECÍFICOS BUSCAM INCORPORAR ESTES BANCOS DE DADOS A PROJETOS DE PODER. TENDO EM VISTA UM CAMPO PRODUZIDO SOCIOLOGICAMENTE, BUSCA-SE CONTRIBUIR COM UM DEBATE INTERDISCIPLINAR QUE DEMONSTRE A DIMENSÃO POLÍTICA, ALÉM DE AMBIENTAL, DA NOÇÃO DE RISCO DE ULRICH BECK.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>WITH THIS WORK WE SEEK TO UNDERSTAND TO WHAT EXTENT CONTEMPORARY PROCESSES OF DATAFICATION AND THE INTRODUCTION OF BIG DATA AND DATA SCIENCE AT THE BRAZILIAN INSTITUTE OF GEOGRAPHY AND STATISTICS (IBGE) RECONFIGURE THE FIELD OF PRODUCTION AND DISTRIBUTION OF OFFICIAL STATISTICS IN BRAZIL. USING TOOLS FROM BOURDIEU'S GENETIC STRUCTURALISM AND FROM THE SOCIOLOGY OF QUANTIFICATION, WE CONDUCTED A COMPARATIVE INVESTIGATION THAT ADDRESSES THE IMPLEMENTATION OF THE REGIONAL BIG DATA HUB FOR LATIN AMERICA AT IBGE, IN LIGHT OF THE HISTORICAL PROCESSES OF STRUCTURING THE STATISTICAL FIELD AND TRANSITION OF STATISTICAL REGIMES, IN THE CONTEXTS OF THE GLOBAL NORTH AND BRAZIL. THE RESEARCH CONSISTED OF THE ANALYSIS OF SECONDARY DATA, COMPARED WITH PRIMARY DATA, OBTAINED THROUGH INTERVIEWS AND NON-PARTICIPANT OBSERVATION. THE TOPIC IS RELEVANT TO THE EXTENT THAT, IN THE CONTEXT OF PLATFORM CAPITALISM, THE INCIDENCE OF BIG TECH IN THE TRANSNATIONAL STATISTICAL FIELD IMPLIES RISKS TO THE SOVEREIGNTY OF COUNTRIES IN THE GLOBAL SOUTH. OUR HYPOTHESIS IS THAT THE INTRODUCTION OF NEW DATA SOURCES AND METHODS IN OFFICIAL STATISTICS IMPLIES AN INTERSECTION BETWEEN THE STATISTICAL FIELD, TRADITIONALLY LINKED TO THE STATE, AND THE ALGORITHMIC FIELD, ASSOCIATED TO PRIVATE CORPORATIONS. THIS ENGAGEMENT LEADS TO A TRANSITION TO A NEW DATAFICATION REGIME. OUR THESIS IS THAT THIS TRANSITION IS CHARACTERIZED BY TWO OBSTACLES. AN ONTOLOGICAL OBSTACLE, RELATED TO THE POLITICAL ECONOMY OF DATA, TENSIONED BETWEEN THE CONCEPTS OF PUBLIC GOOD AND COMMODITY. AND AN EPISTEMOLOGICAL OBSTACLE, RELATED TO THE METHODS, TENSIONED BETWEEN THE FREQUENTIST AND BAYESIAN INTERPRETATIONS OF STATISTICS. THESE OBSTACLES LEAD TO A DOUBLE MOVEMENT IN THE STATISTICAL FIELD. EFFORTS TO CREATE DATA MARKETS FOR OFFICIAL STATISTICS AND TO BREAD DATA SCIENTISTS AT NATIONAL STATISTICS OFFICES ARE OPPOSED TO INITIATIVES AIMED AT REGULATING, PROTECTING AND ACCESSING DATA AS PUBLIC GOODS, ENSURING THEIR INCORPORATION WITH THE PRESERVATION OF METHODS AND TRADITIONAL STATISTICAL SOURCES, UNDER THE GOVERNANCE OF STATE STATISTICIANS. IN THE CASE OF BRAZIL AND COUNTRIES IN THE GLOBAL SOUTH, THE RELEVANCE OF NATIONAL COUNTER-MOVEMENTS, PROTECTIVE OF THE PUBLIC NATURE OF OFFICIAL STATISTICS AND DATA SOVEREIGNTY, STANDS OUT IN DETERMINING THE DEGREE OF AUTONOMY OR DEPENDENCE THAT THEIR STATISTICAL SYSTEMS MAY ASSUME IN THE TRANSITION TO A NEW DATAFICATION REGIME.</t>
+          <t>THIS WORK PRODUCES A SOCIOLOGICAL INVESTIGATION ABOUT THE POLITICAL DISPUTES INVOLVING INPE (NATIONAL INSTITUTE FOR SPACE RESEARCH) AND PRESIDENT JAIR MESSIAS BOLSONARO. APPLYING CONCEPTS OF “RISK” AND “RISK SOCIETY” BY ULRICH BECK, THE STUDY ESTABLISHED A RELATIONSHIP FROM A SOCIOLOGICAL PERSPECTIVE WITH A FOCUS ON THE ENVIRONMENTAL ISSUE, AS WELL AS ON THE POTENTIAL OF NEW RESOURCES LINKED TO SPACE AND COMPUTER SCIENCES, ESPECIALLY SATELLITES AND DATABASES. WITH THESE TECHNOLOGICAL RESOURCES, A COMPLEX DATA MINING SYSTEM IS ARTICULATED, WHERE DATA IS COLLECTED AND CONVERTED INTO VALUABLE INFORMATION. THUS, HAVING THESE SYSTEMS MEANS KEEPING UNDER CONTROL, FOR EXAMPLE, IMAGES OF THE EARTH'S SURFACE OF VARIOUS TECHNOLOGICAL QUALITIES AND FORMS OF USE. IT IS INSTITUTES LINKED TO STATES OR EVEN PRIVATE COMPANIES THAT MOST HAVE THEM; IT IS WORTH EMPHASIZING, THEREFORE, THAT THERE IS A CERTAIN EXCLUSIVITY OF ACCESS. IN THE BRAZILIAN CASE, INPE IS THE ONE WHO CONCENTRATES ALL THE ELEMENTS PRESENTED, WHETHER ITS TECHNICAL DIMENSION OR ITS POLITICAL DIMENSION. THE PATH OF INSTITUTIONALIZATION OF SPACE SCIENCES IN BRAZIL, ESPECIALLY LINKED TO INPE, REPRESENTS PARADIGMATIC TECHNOLOGICAL ADVANCES IN THIS SECTOR. HOWEVER, THE TRADITION OF PUBLISHING ITS DATABASES OPENLY ON ITS WEBSITE GENERATED, IN THE CURRENT GOVERNMENT, A STRONG REACTION, FOR HIGHLIGHTING THE ENVIRONMENTAL CRISIS CAUSED BY DEFORESTATION. IN VIEW OF THE INSTITUTE'S EXPERIENCE CONSOLIDATING ITSELF IN THE MIDST OF THE MILITARY DICTATORSHIP, RECENT EVENTS RAISE THE ALERT OF A PAST THAT HAS COME BACK TO HAUNT. THEREFORE, THE THEME OF RISK REFERS TO ONGOING PROCESSES INVOLVING THE SUFFOCATION OF SCIENTIFIC HORIZONS WHEN PUSHED TO THIS IMPOSING POLITICAL ARENA, PUTTING THE AUTONOMY OF RESEARCH INSTITUTES IN CHECK, AS WELL AS THE INTERESTS OF CIVIL SOCIETY. THIS ALLOWS US TO SEE THE POLITICAL DIMENSION OF THESE TECHNICAL ARTIFACTS, ESPECIALLY WHEN SPECIFIC INTERESTS SEEK TO INCORPORATE THESE DATABASES INTO POWER PROJECTS. IN VIEW OF A SOCIOLOGICALLY PRODUCED FIELD, THE AIM IS TO CONTRIBUTE TO AN INTERDISCIPLINARY DEBATE THAT DEMONSTRATES THE POLITICAL DIMENSION, IN ADDITION TO THE ENVIRONMENTAL DIMENSION, OF ULRICH BECK'S NOTION OF RISK.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ESTATÍSTICAS OFICIAIS;PLATAFORMAS;BIG DATA;CIÊNCIA DE DADOS</t>
+          <t>INPE;TECNOLOGIA DIGITAL;TECNOLOGIA ESPACIAL;SOCIEDADE DE RISCO;BIG-DATAS;SATÉLITES;DISPUTAS POLÍTICAS</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>OFFICIAL STATISTICS;PLATFORMS;DATA SCIENCE</t>
+          <t>INPE;DIGITAL TECHNOLOGY;SPACEY TECHNOLOGY;RISK SOCIETY;BIG-DATES;SATELLITES;POLITICAL DISPUTES</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>EDEMILSON CRUZ SANTANA JUNIOR</t>
+          <t>SAMIRA FELDMAN MARZOCHI</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -8414,31 +8414,31 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DO CEARÁ</t>
+          <t>UNIVERSIDADE FEDERAL DE SÃO CARLOS</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>UFC</t>
+          <t>UFSCAR</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>NORDESTE</t>
+          <t>SUDESTE</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>CEARÁ</t>
+          <t>SÃO PAULO</t>
         </is>
       </c>
       <c r="Y57" t="n">
-        <v>381</v>
+        <v>124</v>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
@@ -8457,16 +8457,16 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16175018</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11254402</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>16175018</t>
+          <t>11254402</t>
         </is>
       </c>
       <c r="AE57" t="n">
-        <v>1015048</v>
+        <v>3328885</v>
       </c>
     </row>
     <row r="58">
@@ -8481,41 +8481,41 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>LETICIA DE FRANCA PAES</t>
+          <t>FABIO HENRIQUE BELINI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AUTOMÓVEIS VERSUS MOBILIDADE: UMA ANÁLISE SOCIOLÓGICA DO MERCADO”,</t>
+          <t>TRABALHO E AUTOMAÇÃO NA INDÚSTRIA FARMACÊUTICA DE ANÁPOLIS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>O PRESENTE TRABALHO TEM COMO OBJETIVO COMPREENDER OS PROCESSOS E DINÂMICAS QUE TÊM OCORRIDO NO SETOR AUTOMOTIVO A PARTIR DO SURGIMENTO DE UMA SUB-INDÚSTRIA DA MOBILIDADE, QUE ALTERA OS MODELOS DE NEGÓCIOS DO MERCADO DE AUTOMÓVEIS COM A OFERTA DE SERVIÇOS DE MOBILIDADE; MODIFICA A ESTRUTURA PRODUTIVA COM O AUMENTO DA AUTOMATIZAÇÃO NAS PLANTAS; INSERE AS MONTADORAS EM ECOSSISTEMAS DIGITAIS COM TECNOLOGIAS COMO BIG DATA E INTERNET DAS COISAS; CRIA NOVAS FONTES DE VALOR AGREGADO A PARTIR DO MERCADO DE DADOS E INSERE NOVOS ATORES NAS DINÂMICAS DE CONCORRÊNCIA E PARCERIAS. A PESQUISA TEM COMO OBJETO A MONTADORA JAPONESA TOYOTA MOTOR CORPORATION, ENQUANTO ESTUDO DE CASO DE DIMENSÃO EXPLORATÓRIA, COM RECORTE DE TEMPO DE DOZE ANOS. NO TOCANTE ÀS ESCOLHAS METODOLÓGICAS DE COLETA DE DADOS, PRIORIZOU-SE A COLETA DOCUMENTAL, COM TRATAMENTO DE ANÁLISE DE CONTEÚDO. COMO PROPOSTA TEÓRICA, REALIZOU-SE A REVISÃO BIBLIOGRÁFICA DE VERTENTES DA SOCIOLOGIA ECONÔMICA SOB DUAS ÓTICAS: A ANÁLISE DOS MERCADOS A PARTIR DOS PROCESSOS DE QUALIFICAÇÃO E VALORAÇÃO DOS PRODUTOS; E A ANÁLISE DAS INSTITUIÇÕES E ESTRUTURAS DE PODER NAS ARENAS DE DISPUTAS DESSES MERCADOS. COMO PRINCIPAL RESULTADO, A ANÁLISE DO CASO DA TOYOTA SUGERE QUE OS PROCESSOS DE QUALIFICAÇÃO DO BEM, A MOBILIZAÇÃO DOS DISPOSITIVOS DE JULGAMENTO, DOS VALORES IMAGINATIVOS E A CONSTRUÇÃO DE PERFIS E IDENTIDADES TANTO DOS PRODUTOS QUANTO DA EMPRESA EM SI FUNCIONAM COMO FERRAMENTAS PARA MANUTENÇÃO DAS CONCEPÇÕES DE CONTROLE DA EMPRESA, UMA VEZ QUE A TOYOTA PASSOU A ATUAR EM NOVOS MERCADOS E SE REORGANIZOU PARA PROVER OS NOVOS PRODUTOS E SERVIÇOS SEM QUE ISSO SE PROVASSE ENQUANTO DESINSTITUCIONALIZAÇÃO DO MERCADO, SENDO A MANUTENÇÃO DO STATUS QUO SUA LUTA PRINCIPAL.</t>
+          <t>O MERCADO DE TRABALHO BRASILEIRO SE DEPARA NA ATUALIDADE COM UM CENÁRIO DE DESINDUSTRIALIZAÇÃO E DESEMPREGO, RESULTADO DE UM PROCESSO GLOBAL DE REESTRUTURAÇÃO DO CAPITALISMO COM CRESCENTE PRECARIZAÇÃO DO TRABALHO. ESTA DISSERTAÇÃO PARTE DA INDÚSTRIA FARMACÊUTICA COMO UM CAMPO DE ESTUDO QUE SEGUE O CAMINHO OPOSTO AO CONTEXTO NACIONAL, APRESENTANDO AMPLIAÇÃO DE EMPREGOS FORMAIS. OBSERVA-SE QUE OS INVESTIMENTOS EM AUTOMAÇÃO NA INDÚSTRIA FARMACÊUTICA SÃO CONDICIONADOS PELA NECESSIDADE DE PRECISÃO NOS PROCESSOS E ATENDIMENTO DO NÍVEL DE QUALIDADE EXIGIDO PELA AGÊNCIA NACIONAL DE VIGILÂNCIA SANITÁRIA (ANVISA). FRENTE AO EXPOSTO, OBJETIVA-SE NESTE ESTUDO INVESTIGAR AS NOVAS CONFIGURAÇÕES DE TRABALHO DO OPERARIADO QUE ATUA NAS INDÚSTRIAS FARMACÊUTICAS DO DISTRITO AGROINDUSTRIAL DE ANÁPOLIS (DAIA). PRETENDE-SE COMPREENDER A IDENTIDADE E O PERFIL DESSES TRABALHADORES E ANALISAR COMO REPRESENTAM A AUTOMAÇÃO INDUSTRIAL E SUA RELAÇÃO COM A QUALIFICAÇÃO PROFISSIONAL. PARA TANTO, FOI REALIZADA UMA ANÁLISE QUANTITATIVA COM DADOS EXTRAÍDOS DA BASE DE DADOS GOVERNAMENTAIS DA RELAÇÃO ANUAL DE INFORMAÇÕES SOCIAIS (RAIS) PARA CARACTERIZAR O PERFIL DOS/AS TRABALHADORES/AS DA INDÚSTRIA FARMACÊUTICA DO BRASIL E DE ANÁPOLIS. OS DADOS APONTAM QUE HÁ UM CONTINGENTE SEMELHANTE DE HOMENS E MULHERES QUE COMPÕEM A FORÇA DE TRABALHO NESTE SEGMENTO DA INDÚSTRIA, O QUE DIFERE DA MÉDIA DO SETOR, PREDOMINANTEMENTE MASCULINO. ALÉM DISSO, FORAM REALIZADAS ENTREVISTAS SEMIESTRUTURADAS COM DEZ TRABALHADORES/AS DE DUAS FABRICANTES NACIONAIS DE MEDICAMENTOS GENÉRICOS LOCALIZADAS EM ANÁPOLIS PARA COMPREENDER SUA TRAJETÓRIA E AS CONDIÇÕES DE TRABALHO PELA PERSPECTIVA DOS/AS PRÓPRIOS/AS TRABALHADORES/AS. COMO RESULTADO DAS ENTREVISTAS, OBSERVASE QUE AS INDÚSTRIAS ESTUDADAS ESTÃO CONFIGURADAS A PARTIR DE FORMAS SOFISTICADAS DE CONTROLE E INTENSIFICAÇÃO DA PRODUÇÃO, DEFLAGRANDO UM AMBIENTE DE TRABALHO PASSÍVEL DE DEGRADAÇÃO DA SAÚDE FÍSICA E MENTAL. A RELAÇÃO ENTRE HUMANOS E MÁQUINAS FOI COMPREENDIDA COMO EIXO CENTRAL DA FABRICAÇÃO DE MEDICAMENTOS, DE MODO QUE A EXTRAÇÃO DO EMPENHO COGNITIVO DOS/AS TRABALHADORES/AS FRENTE À COMPLEXIDADE ESTABELECIDA PELOS DIFERENTES NÍVEIS DE AUTOMAÇÃO CONFIGURA O PROCESSO PRODUTIVO E DETERMINA SEU DESEMPENHO.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>THE PRESENT WORK AIMS TO COMPREHEND THE PROCESSES AND DYNAMICS THAT HAVE BEEN TAKING PLACE IN THE AUTOMOTIVE SECTOR FROM THE EMERGENCE OF A SUB-INDUSTRY OF MOBILITY, THAT MODIFIES THE BUSINESS MODELS OF THE CAR MARKET BASED ON THE OFFER OF MOBILITY SERVICES; IT ALSO ALTERS THE PRODUCTION STRUCTURE BY INCREASING THE PLANT AUTOMATION; INSERTS AUTOMAKERS IN DIGITAL ECOSYSTEMS WITH TECHNOLOGIES SUCH AS BIG DATA AND INTERNET OF THINGS; CREATES NEW SOURCES OF ADDED VALUE FROM THE DATA MARKET AND ALSO INSERTS NEW ACTORS IN THE DYNAMICS OF COMPETITION AND PARTNERSHIPS. THE OBJECT OF THIS RESEARCH IS ONE OF THESE MANUFACTURERS, THE JAPANESE AUTOMAKER TOYOTA MOTOR CORPORATION, AS A CASE STUDY OF AN EXPLORATORY DIMENSION, WITH A TWELVE-YEAR TIME FRAME. CONSIDERING METHODOLOGICAL CHOICES OF DATA COLLECTING, THE PRIORITY WAS THE DOCUMENTAL APPROACH, WITH CONTENT ANALYSIS TREATMENT. THE THEORETICAL PROPOSAL CHOSEN CONCERNED A BIBLIOGRAPHICAL REVIEW OF STRANDS OF THE ECONOMIC SOCIOLOGY FROM TWO PARTICULAR PERSPECTIVES: THE ANALYSIS OF MARKETS FROM THE QUALIFICATION AND VALUATION OF PRODUCTS; AND THE ANALYSIS OF INSTITUTIONS AND STRUCTURES OF POWER IN THE ARENAS OF DISPUTE OF THESE MARKETS. AS MAIN RESULT, THE ANALYSIS OF THE TOYOTA CASE SUGGESTS THAT THE PROPERTY QUALIFICATION PROCESSES, AS WELL AS THE MOBILIZATION OF JUDGMENT DEVICES, THE IMAGINATIVE VALUES AND THE CONSTRUCTION OF PROFILES AND IDENTITIES FOR BOTH THE PRODUCTS AND THE COMPANY ITSELF WORK AS TOOLS FOR MAINTAINING THE COMPANY’S CONCEPTS OF CONTROL, AS THE COMPANY STARTED TO ACT IN NEW MARKETS AND HAS REORGANIZED ITSELF TO SUPPLY NEW PRODUCTS AND SERVICES, EVEN THOUGH THIS DID NOT PROVE TO BE THE DEINSTITUTIONALIZATION OF THE MARKET, BEING THE MAINTENANCE OF THE STATUS QUO ITS MAIN STRUGGLE.</t>
+          <t>THE BRAZILIAN LABOR MARKET IS CURRENTLY FACING A SCENARIO OF DEINDUSTRIALIZATION AND UNEMPLOYMENT, AS THE RESULT OF A GLOBAL PROCESS OF CAPITALISM RESTRUCTURING WITH INCREASING JOB INSECURITY. THIS DISSERTATION FOCUSES ON THE PHARMACEUTICAL INDUSTRY AS A FIELD OF STUDY THAT IS ON THE OPPOSITE PATH OF THE NATIONAL CONTEXT, DISPLAYING AN INCREASE IN FORMAL JOBS. WE OBSERVE THAT THE INVESTMENTS IN AUTOMATION IN THE PHARMACEUTICAL INDUSTRY ARE CONDITIONED BY THE NEED FOR PRECISION IN THE PROCESSES AND FOR MEETING THE LEVEL OF QUALITY REQUIRED BY THE NATIONAL HEALTH SURVEILLANCE AGENCY (ANVISA). THUS, THIS STUDY AIMS TO INVESTIGATE THE NEW LABOR CONFIGURATIONS OF THE WORKERS WHO OPERATE IN THE PHARMACEUTICAL INDUSTRIES OF THE AGROINDUSTRIAL DISTRICT OF ANÁPOLIS (DAIA). WE INTEND TO UNDERSTAND THE IDENTITY AND THE PROFILE OF THESE WORKERS AND TO ANALYZE HOW THEY REPRESENT INDUSTRIAL AUTOMATION AND ITS RELATIONSHIP WITH PROFESSIONAL QUALIFICATION. THEREFORE, A QUANTITATIVE ANALYSIS WAS PERFORMED WITH DATA EXTRACTED FROM THE GOVERNMENTAL DATABASE OF THE ANNUAL SOCIAL INFORMATION REPORT (RAIS) TO CHARACTERIZE THE PROFILE OF THE WORKERS OF THE PHARMACEUTICAL INDUSTRY IN BRAZIL AND ANÁPOLIS. THE DATA SHOWS THAT THERE IS A SIMILAR CONTINGENT OF MEN AND WOMEN THAT COMPOSE THE WORKFORCE IN THIS SEGMENT OF THE INDUSTRY, WHICH DIFFERS FROM THE PREDOMINANTLY MALE SECTOR'S AVERAGE. IN ADDITION, SEMISTRUCTURED INTERVIEWS WERE CONDUCTED WITH TEN WORKERS FROM TWO NATIONAL MANUFACTURERS OF GENERIC DRUGS LOCATED IN ANÁPOLIS IN ORDER TO UNDERSTAND THEIR TRAJECTORY AND THE WORKING CONDITIONS FROM THE PERSPECTIVE OF THE WORKERS THEMSELVES. AS A RESULT OF THE INTERVIEWS, IT WAS OBSERVED THAT THE INDUSTRIES STUDIED ARE STRUCTURED BASED ON SOPHISTICATED FORMS OF CONTROL AND INTENSIFICATION OF PRODUCTION, TRIGGERING A WORK ENVIRONMENT THAT IS SUSCEPTIBLE TO THE DEGRADATION OF PHYSICAL AND MENTAL HEALTH. THE RELATIONSHIP BETWEEN HUMANS AND MACHINES WAS UNDERSTOOD AS THE CENTRAL AXIS OF DRUG MANUFACTURING, THUS THE EXTRACTION OF THE WORKERS' COGNITIVE ENGAGEMENT IN FACE OF THE COMPLEXITY ESTABLISHED BY THE DIFFERENT LEVELS OF AUTOMATION SHAPES THE PRODUCTIVE PROCESS AND DETERMINES ITS PERFORMANCE.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>MERCADO DE AUTOMÓVEIS;SOCIOLOGIA ECONÔMICA;MOBILIDADE;TOYOTA.</t>
+          <t>TRABALHO;INDÚSTRIA FARMACÊUTICA;TRABALHADORES DA INDÚSTRIA;AUTOMAÇÃO;CONTROLE.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>AUTO MARKET;ECONOMIC SOCIOLOGY;MOBILITY;TOYOTA.</t>
+          <t>WORK;PHARMACEUTICAL INDUSTRY;INDUSTRY WORKERS;AUTOMATION;CONTROL.</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>RAPHAEL JONATHAS DA COSTA LIMA</t>
+          <t>TANIA LUDMILA DIAS TOSTA</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -8555,31 +8555,31 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL FLUMINENSE</t>
+          <t>UNIVERSIDADE FEDERAL DE GOIÁS</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>UFF</t>
+          <t>UFG</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>SUDESTE</t>
+          <t>CENTRO-OESTE</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>GOIÁS</t>
         </is>
       </c>
       <c r="Y58" t="n">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
@@ -8598,16 +8598,16 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11436964</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13352420</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>11436964</t>
+          <t>13352420</t>
         </is>
       </c>
       <c r="AE58" t="n">
-        <v>2997668</v>
+        <v>3615926</v>
       </c>
     </row>
     <row r="59">
@@ -8622,71 +8622,71 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MURILO APARECIDO GONCALVES</t>
+          <t>JOAO RICARDO PENTEADO LOPES DA SILVA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TECNOLOGIA ESPACIAL, RISCO E POLÍTICA: O CASO INPE SÃO</t>
+          <t>TENDÊNCIAS DAS POLÍTICAS DO ESTADO BRASILEIRO PARA O DESENVOLVIMENTO DA INTELIGÊNCIA ARTIFICIAL: O CASO DOS CENTROS DE PESQUISA APLICADA EM INTELIGÊNCIA ARTIFICIAL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ESTE TRABALHO PRODUZ UMA INVESTIGAÇÃO SOCIOLÓGICA ACERCA DAS DISPUTAS POLÍTICAS ENVOLVENDO O INPE (INSTITUTO NACIONAL DE PESQUISAS ESPACIAIS) E O PRESIDENTE JAIR MESSIAS BOLSONARO. APLICANDO CONCEITOS DE “RISCO” E “SOCIEDADE DE RISCO”, DE ULRICH BECK, O ESTUDO ESTABELECEU UMA RELAÇÃO DA PERSPECTIVA SOCIOLÓGICA COM ENFOQUE NA QUESTÃO AMBIENTAL, BEM COMO NAS POTENCIALIDADES DE NOVOS RECURSOS LIGADOS ÀS CIÊNCIAS ESPACIAIS E DA COMPUTAÇÃO, ESPECIALMENTE OS SATÉLITES E BANCOS DE DADOS. COM ESTES RECURSOS TECNOLÓGICOS, ARTICULA-SE UM COMPLEXO SISTEMA DE MINERAÇÃO DE DADOS, ONDE OS DADOS SÃO COLETADOS E CONVERTIDOS EM VALIOSAS INFORMAÇÕES. DESSE MODO, POSSUIR ESSES SISTEMAS SIGNIFICA MANTER SOB O CONTROLE, POR EXEMPLO, IMAGENS DA SUPERFÍCIE TERRESTRE DE DIVERSAS QUALIDADES TECNOLÓGICAS E FORMAS DE USO. SÃO INSTITUTOS LIGADOS A ESTADOS OU MESMO EMPRESAS PRIVADAS QUEM MAIS OS POSSUEM; CABE RESSALTAR, PORTANTO, QUE EXISTE CERTA EXCLUSIVIDADE DE ACESSO. NO CASO BRASILEIRO, O INPE É QUEM CONCENTRA TODOS OS ELEMENTOS APRESENTADOS, SEJA SUA DIMENSÃO TÉCNICA, SEJA NA DIMENSÃO POLÍTICA. O PERCURSO DE INSTITUCIONALIZAÇÃO DAS CIÊNCIAS ESPACIAIS NO BRASIL, ESPECIALMENTE ATRELADAS AO INPE, REPRESENTA AVANÇOS TECNOLÓGICOS PARADIGMÁTICOS NESTE SETOR. CONTUDO, A TRADIÇÃO DE PUBLICAR SEUS BANCOS DE DADOS ABERTAMENTE EM SEU SITE GEROU, NO ATUAL GOVERNO, FORTE REAÇÃO, POR DESTACAR A CRISE AMBIENTAL MOTIVADA PELO DESMATAMENTO. TENDO EM VISTA A EXPERIÊNCIA DO INSTITUTO SE CONSOLIDAR EM MEIO À DITADURA MILITAR, EVENTOS RECENTES ACENDEM O ALERTA DE UM PASSADO QUE VOLTA A ASSOMBRAR. PORTANTO, O TEMA DO RISCO SE REFERE AOS PROCESSOS QUE ESTÃO EM CURSO ENVOLVENDO O SUFOCAMENTO DOS HORIZONTES CIENTÍFICOS QUANDO EMPURRADOS A ESSA ARENA POLÍTICA IMPOSITIVA, COLOCANDO EM XEQUE A AUTONOMIA DE INSTITUTOS DE PESQUISA, BEM COMO INTERESSES DA SOCIEDADE CIVIL. ISSO NOS PERMITE CONSTATAR A DIMENSÃO POLÍTICA DESTES ARTEFATOS TÉCNICOS, SOBRETUDO QUANDO INTERESSES ESPECÍFICOS BUSCAM INCORPORAR ESTES BANCOS DE DADOS A PROJETOS DE PODER. TENDO EM VISTA UM CAMPO PRODUZIDO SOCIOLOGICAMENTE, BUSCA-SE CONTRIBUIR COM UM DEBATE INTERDISCIPLINAR QUE DEMONSTRE A DIMENSÃO POLÍTICA, ALÉM DE AMBIENTAL, DA NOÇÃO DE RISCO DE ULRICH BECK.</t>
+          <t>DESDE O SURGIMENTO DE UMA NOVA TÉCNICA DE APRENDIZADO PROFUNDO, EM 2012, O INTERESSE PELA INTELIGÊNCIA ARTIFICIAL (IA) TEM AUMENTADO SENSIVELMENTE NA INDÚSTRIA, COMUNIDADE CIENTÍFICA E MÍDIA (LEE, 2018). COM O TEMPO, ESSA TECNOLOGIA TORNOU-SE ASSUNTO DE ESTADO A PONTO DE, NOS FINS DOS ANOS 2010, DIVERSOS PAÍSES TEREM PUBLICADO ESTRATÉGIAS NACIONAIS PARA O DESENVOLVIMENTO DA IA. ACOMPANHANDO ESSA TENDÊNCIA, O BRASIL PUBLICOU EM 2021 A ESTRATÉGIA BRASILEIRA DE INTELIGÊNCIA ARTIFICIAL. CURIOSAMENTE, PORÉM, O PAÍS JÁ HAVIA COLOCADO EM PRÁTICA TRÊS POLÍTICAS PARA O DESENVOLVIMENTO DA IA, SENDO UMA DELAS O PROGRAMA DOS CENTROS DE PESQUISA APLICADA EM INTELIGÊNCIA ARTIFICIAL (CPAS EM IA). EM NOSSA PESQUISA, BUSCAMOS EXAMINAR O ANDAMENTO DESSE PROGRAMA EM SEUS ESTÁGIOS INICIAIS, CONCEBENDO-O COMO UMA POLÍTICA DE ESTADO VOLTADA PARA O FOMENTO DA INOVAÇÃO E DESENVOLVIMENTO NACIONAL. PARA ISSO, ANALISAMOS DADOS LEVANTADOS COM BASE EM ENTREVISTAS, SEMINÁRIOS E DOCUMENTOS DOS ÓRGÃOS PÚBLICOS FINANCIADORES E DE CADA UM DOS SEIS CPAS CONTEMPLADOS NO PROGRAMA, AMPARANDO-SE AINDA EM PRODUÇÃO TEÓRICA SOBRE O PAPEL ECONÔMICO DA TECNOLOGIA, DESENVOLVIMENTO E SISTEMAS DE INOVAÇÃO. NOSSO TRABALHO APONTA QUE, TOMANDO O PROGRAMA DOS CPAS EM IA COMO REFERÊNCIA, A FORMULAÇÃO, O PLANEJAMENTO E A EXECUÇÃO DE UMA POLÍTICA PARA O DESENVOLVIMENTO DE INTELIGÊNCIA ARTIFICIAL NO BRASIL POSSUI LIMITAÇÕES E CONTRADIÇÕES BASTANTE VISÍVEIS, AINDA QUE CONFIGURE UMA INICIATIVA DE RELEVÂNCIA.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>THIS WORK PRODUCES A SOCIOLOGICAL INVESTIGATION ABOUT THE POLITICAL DISPUTES INVOLVING INPE (NATIONAL INSTITUTE FOR SPACE RESEARCH) AND PRESIDENT JAIR MESSIAS BOLSONARO. APPLYING CONCEPTS OF “RISK” AND “RISK SOCIETY” BY ULRICH BECK, THE STUDY ESTABLISHED A RELATIONSHIP FROM A SOCIOLOGICAL PERSPECTIVE WITH A FOCUS ON THE ENVIRONMENTAL ISSUE, AS WELL AS ON THE POTENTIAL OF NEW RESOURCES LINKED TO SPACE AND COMPUTER SCIENCES, ESPECIALLY SATELLITES AND DATABASES. WITH THESE TECHNOLOGICAL RESOURCES, A COMPLEX DATA MINING SYSTEM IS ARTICULATED, WHERE DATA IS COLLECTED AND CONVERTED INTO VALUABLE INFORMATION. THUS, HAVING THESE SYSTEMS MEANS KEEPING UNDER CONTROL, FOR EXAMPLE, IMAGES OF THE EARTH'S SURFACE OF VARIOUS TECHNOLOGICAL QUALITIES AND FORMS OF USE. IT IS INSTITUTES LINKED TO STATES OR EVEN PRIVATE COMPANIES THAT MOST HAVE THEM; IT IS WORTH EMPHASIZING, THEREFORE, THAT THERE IS A CERTAIN EXCLUSIVITY OF ACCESS. IN THE BRAZILIAN CASE, INPE IS THE ONE WHO CONCENTRATES ALL THE ELEMENTS PRESENTED, WHETHER ITS TECHNICAL DIMENSION OR ITS POLITICAL DIMENSION. THE PATH OF INSTITUTIONALIZATION OF SPACE SCIENCES IN BRAZIL, ESPECIALLY LINKED TO INPE, REPRESENTS PARADIGMATIC TECHNOLOGICAL ADVANCES IN THIS SECTOR. HOWEVER, THE TRADITION OF PUBLISHING ITS DATABASES OPENLY ON ITS WEBSITE GENERATED, IN THE CURRENT GOVERNMENT, A STRONG REACTION, FOR HIGHLIGHTING THE ENVIRONMENTAL CRISIS CAUSED BY DEFORESTATION. IN VIEW OF THE INSTITUTE'S EXPERIENCE CONSOLIDATING ITSELF IN THE MIDST OF THE MILITARY DICTATORSHIP, RECENT EVENTS RAISE THE ALERT OF A PAST THAT HAS COME BACK TO HAUNT. THEREFORE, THE THEME OF RISK REFERS TO ONGOING PROCESSES INVOLVING THE SUFFOCATION OF SCIENTIFIC HORIZONS WHEN PUSHED TO THIS IMPOSING POLITICAL ARENA, PUTTING THE AUTONOMY OF RESEARCH INSTITUTES IN CHECK, AS WELL AS THE INTERESTS OF CIVIL SOCIETY. THIS ALLOWS US TO SEE THE POLITICAL DIMENSION OF THESE TECHNICAL ARTIFACTS, ESPECIALLY WHEN SPECIFIC INTERESTS SEEK TO INCORPORATE THESE DATABASES INTO POWER PROJECTS. IN VIEW OF A SOCIOLOGICALLY PRODUCED FIELD, THE AIM IS TO CONTRIBUTE TO AN INTERDISCIPLINARY DEBATE THAT DEMONSTRATES THE POLITICAL DIMENSION, IN ADDITION TO THE ENVIRONMENTAL DIMENSION, OF ULRICH BECK'S NOTION OF RISK.</t>
+          <t>SINCE THE EMERGENCE OF A NEW DEEP LEARNING TECHNIQUE IN 2012, INTEREST IN ARTIFICIAL INTELLIGENCE (AI) HAS INCREASED SIGNIFICANTLY IN INDUSTRY, THE SCIENTIFIC COMMUNITY AND THE MEDIA (LEE, 2018). OVER TIME, TECHNOLOGY BECAME A STATE MATTER, TO THE POINT THAT, IN THE LATE 2010S, SEVERAL COUNTRIES PUBLISHED NATIONAL STRATEGIES FOR THE DEVELOPMENT OF AI. FOLLOWING THIS TREND, BRAZIL PUBLISHED IN 2021 THE BRAZILIAN ARTIFICIAL INTELLIGENCE STRATEGY. INTERESTINGLY, HOWEVER, THE COUNTRY HAD ALREADY PUT IN PLACE THREE POLICIES TO PROMOTE AI, ONE OF THEM BEING THE CENTERS FOR APPLIED RESEARCH IN ARTIFICIAL INTELLIGENCE PROGRAM. IN OUR RESEARCH, WE SOUGHT TO EXAMINE THE PROGRESS OF THIS PROGRAM IN ITS INITIAL STAGES, CONCEIVING IT AS A STATE POLICY AIMED AT FOSTERING INNOVATION AND NATIONAL DEVELOPMENT. FOR THIS, WE ANALYZED DATA COLLECTED ON INTERVIEWS, SEMINARS AND DOCUMENTS FROM ORGANS FUNDING BODIES AND FROM EACH OF THE SIX CENTERS CONTEMPLATED IN THE PROGRAM, WHILE SUPPORTED BY THEORETICAL PRODUCTION ON THE ECONOMIC ROLE OF TECHNOLOGY, DEVELOPMENT AND INNOVATION SYSTEMS. OUR WORK POINTS OUT THAT, TAKING THE PROGRAM AS A REFERENCE, THE FORMULATION, PLANNING AND EXECUTION OF A POLICY FOR THE DEVELOPMENT OF ARTIFICIAL INTELLIGENCE IN BRAZIL HAS VERY VISIBLE LIMITATIONS AND CONTRADICTIONS, EVEN THOUGH IT CONSTITUTES A RELEVANT INITIATIVE.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>INPE;TECNOLOGIA DIGITAL;TECNOLOGIA ESPACIAL;SOCIEDADE DE RISCO;BIG-DATAS;SATÉLITES;DISPUTAS POLÍTICAS</t>
+          <t>INTELIGÊNCIA ARTIFICIAL;CIÊNCIA E TECNOLOGIA;INOVAÇÃO;BRASIL</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>INPE;DIGITAL TECHNOLOGY;SPACEY TECHNOLOGY;RISK SOCIETY;BIG-DATES;SATELLITES;POLITICAL DISPUTES</t>
+          <t>ARTIFICIAL INTELLIGENCE;SCIENCE AND TECHNOLOGY;INNOVATION;BRAZIL</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Correlato</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>Aprendizado profundo &amp; redes neurais; IA em sentido estrito</t>
         </is>
       </c>
       <c r="M59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
       </c>
       <c r="O59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P59" t="b">
         <v>0</v>
       </c>
       <c r="Q59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>SAMIRA FELDMAN MARZOCHI</t>
+          <t>EDEMILSON CRUZ SANTANA JUNIOR</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -8696,31 +8696,31 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DE SÃO CARLOS</t>
+          <t>UNIVERSIDADE FEDERAL DO CEARÁ</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>UFSCAR</t>
+          <t>UFC</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>SUDESTE</t>
+          <t>NORDESTE</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>SÃO PAULO</t>
+          <t>CEARÁ</t>
         </is>
       </c>
       <c r="Y59" t="n">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
@@ -8739,16 +8739,16 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11254402</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13606356</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>11254402</t>
+          <t>13606356</t>
         </is>
       </c>
       <c r="AE59" t="n">
-        <v>3328885</v>
+        <v>3608423</v>
       </c>
     </row>
     <row r="60">
@@ -8767,54 +8767,54 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FABIO HENRIQUE BELINI</t>
+          <t>MAXIMO ITALO D ALMEIDA ATHAYDE AVILA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>TRABALHO E AUTOMAÇÃO NA INDÚSTRIA FARMACÊUTICA DE ANÁPOLIS</t>
+          <t>O PROCESSO DE ALGORITMIZAÇÃO DO ESTADO: UMA ANÁLISE DAS AGÊNCIAS PÚBLICAS DE INTERMEDIAÇÃO DE MÃO DE OBRA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>O MERCADO DE TRABALHO BRASILEIRO SE DEPARA NA ATUALIDADE COM UM CENÁRIO DE DESINDUSTRIALIZAÇÃO E DESEMPREGO, RESULTADO DE UM PROCESSO GLOBAL DE REESTRUTURAÇÃO DO CAPITALISMO COM CRESCENTE PRECARIZAÇÃO DO TRABALHO. ESTA DISSERTAÇÃO PARTE DA INDÚSTRIA FARMACÊUTICA COMO UM CAMPO DE ESTUDO QUE SEGUE O CAMINHO OPOSTO AO CONTEXTO NACIONAL, APRESENTANDO AMPLIAÇÃO DE EMPREGOS FORMAIS. OBSERVA-SE QUE OS INVESTIMENTOS EM AUTOMAÇÃO NA INDÚSTRIA FARMACÊUTICA SÃO CONDICIONADOS PELA NECESSIDADE DE PRECISÃO NOS PROCESSOS E ATENDIMENTO DO NÍVEL DE QUALIDADE EXIGIDO PELA AGÊNCIA NACIONAL DE VIGILÂNCIA SANITÁRIA (ANVISA). FRENTE AO EXPOSTO, OBJETIVA-SE NESTE ESTUDO INVESTIGAR AS NOVAS CONFIGURAÇÕES DE TRABALHO DO OPERARIADO QUE ATUA NAS INDÚSTRIAS FARMACÊUTICAS DO DISTRITO AGROINDUSTRIAL DE ANÁPOLIS (DAIA). PRETENDE-SE COMPREENDER A IDENTIDADE E O PERFIL DESSES TRABALHADORES E ANALISAR COMO REPRESENTAM A AUTOMAÇÃO INDUSTRIAL E SUA RELAÇÃO COM A QUALIFICAÇÃO PROFISSIONAL. PARA TANTO, FOI REALIZADA UMA ANÁLISE QUANTITATIVA COM DADOS EXTRAÍDOS DA BASE DE DADOS GOVERNAMENTAIS DA RELAÇÃO ANUAL DE INFORMAÇÕES SOCIAIS (RAIS) PARA CARACTERIZAR O PERFIL DOS/AS TRABALHADORES/AS DA INDÚSTRIA FARMACÊUTICA DO BRASIL E DE ANÁPOLIS. OS DADOS APONTAM QUE HÁ UM CONTINGENTE SEMELHANTE DE HOMENS E MULHERES QUE COMPÕEM A FORÇA DE TRABALHO NESTE SEGMENTO DA INDÚSTRIA, O QUE DIFERE DA MÉDIA DO SETOR, PREDOMINANTEMENTE MASCULINO. ALÉM DISSO, FORAM REALIZADAS ENTREVISTAS SEMIESTRUTURADAS COM DEZ TRABALHADORES/AS DE DUAS FABRICANTES NACIONAIS DE MEDICAMENTOS GENÉRICOS LOCALIZADAS EM ANÁPOLIS PARA COMPREENDER SUA TRAJETÓRIA E AS CONDIÇÕES DE TRABALHO PELA PERSPECTIVA DOS/AS PRÓPRIOS/AS TRABALHADORES/AS. COMO RESULTADO DAS ENTREVISTAS, OBSERVASE QUE AS INDÚSTRIAS ESTUDADAS ESTÃO CONFIGURADAS A PARTIR DE FORMAS SOFISTICADAS DE CONTROLE E INTENSIFICAÇÃO DA PRODUÇÃO, DEFLAGRANDO UM AMBIENTE DE TRABALHO PASSÍVEL DE DEGRADAÇÃO DA SAÚDE FÍSICA E MENTAL. A RELAÇÃO ENTRE HUMANOS E MÁQUINAS FOI COMPREENDIDA COMO EIXO CENTRAL DA FABRICAÇÃO DE MEDICAMENTOS, DE MODO QUE A EXTRAÇÃO DO EMPENHO COGNITIVO DOS/AS TRABALHADORES/AS FRENTE À COMPLEXIDADE ESTABELECIDA PELOS DIFERENTES NÍVEIS DE AUTOMAÇÃO CONFIGURA O PROCESSO PRODUTIVO E DETERMINA SEU DESEMPENHO.</t>
+          <t>A DISSERTAÇÃO SE PROPÕE A OBSERVAR OS INDÍCIOS CONTIDOS NO PROCESSO DE REESTRUTURAÇÃO NA ORGANIZAÇÃO DA POLÍTICA DE EMPREGO POSTOS SOB GERENCIAMENTO DE ALGORITMOS, EM ESPECÍFICO, NO SERVIÇO ESTATAL DE INTERMEDIAÇÃO DE MÃO DE OBRA. PARA TAL, REALIZA-SE UMA REVISÃO HISTÓRICA DA CONFORMAÇÃO DOS MERCADOS DE TRABALHO NO CONTEXTO CAPITALISTA, POSTERIORMENTE ABORDA-SE A QUESTÃO BRASILEIRA NA INSERÇÃO DE POLÍTICAS SOCIAIS PARA SER POSSÍVEL ANALISAR O TRAJETO DA POLÍTICA DO SINE NO ESTEIO DO MODO EMPRESA DE GERENCIAR O SOCIAL. A RENOVAÇÃO DESSA POLÍTICA CONTA COM A PARCERIA DE AGÊNCIAS INTERMEDIADORAS PRIVADAS, TORNA OS INTERMEDIADORES COMISSIONADOS E A REFAÇÃO DO SISTEMA DE ATENDIMENTO DIGITAL. TUDO EM NOME DA MODERNIZAÇÃO, DAS “BOAS PRÁTICAS GERENCIAIS” E DA EFICIÊNCIA NO GASTO PÚBLICO.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>THE BRAZILIAN LABOR MARKET IS CURRENTLY FACING A SCENARIO OF DEINDUSTRIALIZATION AND UNEMPLOYMENT, AS THE RESULT OF A GLOBAL PROCESS OF CAPITALISM RESTRUCTURING WITH INCREASING JOB INSECURITY. THIS DISSERTATION FOCUSES ON THE PHARMACEUTICAL INDUSTRY AS A FIELD OF STUDY THAT IS ON THE OPPOSITE PATH OF THE NATIONAL CONTEXT, DISPLAYING AN INCREASE IN FORMAL JOBS. WE OBSERVE THAT THE INVESTMENTS IN AUTOMATION IN THE PHARMACEUTICAL INDUSTRY ARE CONDITIONED BY THE NEED FOR PRECISION IN THE PROCESSES AND FOR MEETING THE LEVEL OF QUALITY REQUIRED BY THE NATIONAL HEALTH SURVEILLANCE AGENCY (ANVISA). THUS, THIS STUDY AIMS TO INVESTIGATE THE NEW LABOR CONFIGURATIONS OF THE WORKERS WHO OPERATE IN THE PHARMACEUTICAL INDUSTRIES OF THE AGROINDUSTRIAL DISTRICT OF ANÁPOLIS (DAIA). WE INTEND TO UNDERSTAND THE IDENTITY AND THE PROFILE OF THESE WORKERS AND TO ANALYZE HOW THEY REPRESENT INDUSTRIAL AUTOMATION AND ITS RELATIONSHIP WITH PROFESSIONAL QUALIFICATION. THEREFORE, A QUANTITATIVE ANALYSIS WAS PERFORMED WITH DATA EXTRACTED FROM THE GOVERNMENTAL DATABASE OF THE ANNUAL SOCIAL INFORMATION REPORT (RAIS) TO CHARACTERIZE THE PROFILE OF THE WORKERS OF THE PHARMACEUTICAL INDUSTRY IN BRAZIL AND ANÁPOLIS. THE DATA SHOWS THAT THERE IS A SIMILAR CONTINGENT OF MEN AND WOMEN THAT COMPOSE THE WORKFORCE IN THIS SEGMENT OF THE INDUSTRY, WHICH DIFFERS FROM THE PREDOMINANTLY MALE SECTOR'S AVERAGE. IN ADDITION, SEMISTRUCTURED INTERVIEWS WERE CONDUCTED WITH TEN WORKERS FROM TWO NATIONAL MANUFACTURERS OF GENERIC DRUGS LOCATED IN ANÁPOLIS IN ORDER TO UNDERSTAND THEIR TRAJECTORY AND THE WORKING CONDITIONS FROM THE PERSPECTIVE OF THE WORKERS THEMSELVES. AS A RESULT OF THE INTERVIEWS, IT WAS OBSERVED THAT THE INDUSTRIES STUDIED ARE STRUCTURED BASED ON SOPHISTICATED FORMS OF CONTROL AND INTENSIFICATION OF PRODUCTION, TRIGGERING A WORK ENVIRONMENT THAT IS SUSCEPTIBLE TO THE DEGRADATION OF PHYSICAL AND MENTAL HEALTH. THE RELATIONSHIP BETWEEN HUMANS AND MACHINES WAS UNDERSTOOD AS THE CENTRAL AXIS OF DRUG MANUFACTURING, THUS THE EXTRACTION OF THE WORKERS' COGNITIVE ENGAGEMENT IN FACE OF THE COMPLEXITY ESTABLISHED BY THE DIFFERENT LEVELS OF AUTOMATION SHAPES THE PRODUCTIVE PROCESS AND DETERMINES ITS PERFORMANCE.</t>
+          <t>THIS DISSERTATION PROPOSES TO OBSERVE THE EVIDENCE CONTAINED IN THE RESTRUCTURING PROCESS IN THE ORGANIZATION OF THE EMPLOYMENT POLICY PLACED UNDER THE ADMINISTRATION OF ALGORITHMS, SPECIFICALLY, IN THE STATE LABOR INTERMEDIATION SERVICE. TO THIS END, A HISTORICAL REVIEW OF THE CONFORMATION OF LABOR MARKETS IN THE CAPITALIST CONTEXT IS CARRIED OUT, LATER THE BRAZILIAN ISSUE IS ADDRESSED IN THE INSERTION OF SOCIAL POLICIES IN ORDER TO ANALYZE THE TRAJECTORY OF SINE'S POLICY ON THE SHOULDERS OF THE COMPANY FORM OF MANAGING THE SOCIAL. THE RENEWAL OF THIS POLICY COUNTS ON THE PARTNERSHIP OF PRIVATE INTERMEDIATION AGENCIES, MAKES THE INTERMEDIARIES COMMISSIONED AND, IN ITS WAY, REFINES THE DIGITAL INTERMEDIATION SERVICE SYSTEM. ALL IN THE NAME OF MODERNIZATION, “THE GOOD MANAGEMENT PRACTICES” AND EFFICIENCY IN PUBLIC SPENDING.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>TRABALHO;INDÚSTRIA FARMACÊUTICA;TRABALHADORES DA INDÚSTRIA;AUTOMAÇÃO;CONTROLE.</t>
+          <t>INTERMEDIAÇÃO DE MÃO DE OBRA;POLÍTICA DE EMPREGO;NEOLIBERALISMO;APRENDIZADO DE MÁQUINA;GOVERNANÇA ALGORÍTMICA.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>WORK;PHARMACEUTICAL INDUSTRY;INDUSTRY WORKERS;AUTOMATION;CONTROL.</t>
+          <t>INTERMEDIATION OF LABOR;EMPLOYMENT POLICY;NEOLIBERALISM;MACHINE LEARNING;ALGORITHMIC GOVERNANCE.</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Correlato</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>Aprendizado de máquina (ML)</t>
         </is>
       </c>
       <c r="M60" t="b">
         <v>0</v>
       </c>
       <c r="N60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" t="b">
         <v>0</v>
@@ -8823,11 +8823,11 @@
         <v>0</v>
       </c>
       <c r="Q60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>TANIA LUDMILA DIAS TOSTA</t>
+          <t>PEDRO ALCIDES ROBERTT NIZ</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -8837,31 +8837,31 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DE GOIÁS</t>
+          <t>UNIVERSIDADE FEDERAL DE PELOTAS</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>UFG</t>
+          <t>UFPEL</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>CENTRO-OESTE</t>
+          <t>SUL</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>GOIÁS</t>
+          <t>RIO GRANDE DO SUL</t>
         </is>
       </c>
       <c r="Y60" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
@@ -8880,16 +8880,16 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13352420</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11433364</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>13352420</t>
+          <t>11433364</t>
         </is>
       </c>
       <c r="AE60" t="n">
-        <v>3615926</v>
+        <v>668986</v>
       </c>
     </row>
     <row r="61">
@@ -8908,37 +8908,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>JOAO RICARDO PENTEADO LOPES DA SILVA</t>
+          <t>OLGA CHRISTINA DE OLIVEIRA ZUNINO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>TENDÊNCIAS DAS POLÍTICAS DO ESTADO BRASILEIRO PARA O DESENVOLVIMENTO DA INTELIGÊNCIA ARTIFICIAL: O CASO DOS CENTROS DE PESQUISA APLICADA EM INTELIGÊNCIA ARTIFICIAL</t>
+          <t>ROBÔS SOCIÁVEIS E ORGANIZAÇÕES EM MATURAÇÃO: O PROCESSO DE CRIAÇÃO DOS 'CHATBOTS' NO CONTEXTO COMERCIAL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DESDE O SURGIMENTO DE UMA NOVA TÉCNICA DE APRENDIZADO PROFUNDO, EM 2012, O INTERESSE PELA INTELIGÊNCIA ARTIFICIAL (IA) TEM AUMENTADO SENSIVELMENTE NA INDÚSTRIA, COMUNIDADE CIENTÍFICA E MÍDIA (LEE, 2018). COM O TEMPO, ESSA TECNOLOGIA TORNOU-SE ASSUNTO DE ESTADO A PONTO DE, NOS FINS DOS ANOS 2010, DIVERSOS PAÍSES TEREM PUBLICADO ESTRATÉGIAS NACIONAIS PARA O DESENVOLVIMENTO DA IA. ACOMPANHANDO ESSA TENDÊNCIA, O BRASIL PUBLICOU EM 2021 A ESTRATÉGIA BRASILEIRA DE INTELIGÊNCIA ARTIFICIAL. CURIOSAMENTE, PORÉM, O PAÍS JÁ HAVIA COLOCADO EM PRÁTICA TRÊS POLÍTICAS PARA O DESENVOLVIMENTO DA IA, SENDO UMA DELAS O PROGRAMA DOS CENTROS DE PESQUISA APLICADA EM INTELIGÊNCIA ARTIFICIAL (CPAS EM IA). EM NOSSA PESQUISA, BUSCAMOS EXAMINAR O ANDAMENTO DESSE PROGRAMA EM SEUS ESTÁGIOS INICIAIS, CONCEBENDO-O COMO UMA POLÍTICA DE ESTADO VOLTADA PARA O FOMENTO DA INOVAÇÃO E DESENVOLVIMENTO NACIONAL. PARA ISSO, ANALISAMOS DADOS LEVANTADOS COM BASE EM ENTREVISTAS, SEMINÁRIOS E DOCUMENTOS DOS ÓRGÃOS PÚBLICOS FINANCIADORES E DE CADA UM DOS SEIS CPAS CONTEMPLADOS NO PROGRAMA, AMPARANDO-SE AINDA EM PRODUÇÃO TEÓRICA SOBRE O PAPEL ECONÔMICO DA TECNOLOGIA, DESENVOLVIMENTO E SISTEMAS DE INOVAÇÃO. NOSSO TRABALHO APONTA QUE, TOMANDO O PROGRAMA DOS CPAS EM IA COMO REFERÊNCIA, A FORMULAÇÃO, O PLANEJAMENTO E A EXECUÇÃO DE UMA POLÍTICA PARA O DESENVOLVIMENTO DE INTELIGÊNCIA ARTIFICIAL NO BRASIL POSSUI LIMITAÇÕES E CONTRADIÇÕES BASTANTE VISÍVEIS, AINDA QUE CONFIGURE UMA INICIATIVA DE RELEVÂNCIA.</t>
+          <t>ESTA DISSERTAÇÃO PRETENDE ANALISAR O PROCESSO DE CRIAÇÃO DE CHATBOTS (TECNOLOGIAS DE PROGRAMAÇÃO COMPUTACIONAL DESENVOLVIDAS PARA A INTERAÇÃO COM O USUÁRIO) PARA O MEIO COMERCIAL A PARTIR, APOIADA EM UMA ABORDAGEM PRAGMATISTA, DA COMPREENSÃO DAS METAFÍSICAS MORAIS QUE ORIENTAM OS PRINCÍPIOS AVALIATIVOS DOS ESPECIALISTAS RESPONSÁVEIS E PELAS CARACTERÍSTICAS DA RELAÇÃO DESSES AGENTES EM SUA ROTINA DE TRABALHO. POR MEIO DA TÉCNICA DE ENTREVISTAS SEMIESTRUTURADAS COM OS ESPECIALISTAS FOI POSSÍVEL PRODUZIR O ENTENDIMENTO DE QUE ELES JUSTIFICAM SEUS PRINCÍPIOS AVALIATIVOS A PARTIR DA MOBILIZAÇÃO DE UMA METAFÍSICA SOBRE QUEM É ESSE USUÁRIO FINAL, ABSTRAÇÃO ESSA VARIÁVEL ENTRE DIFERENTES PROFISSIONAIS. ESSES MÚLTIPLOS PRINCÍPIOS AVALIATIVOS SÃO MOBILIZADOS DE FORMA A CRIAR FRICÇÕES PRODUTIVAS CAPAZES DE AUXILIAR NO PROCESSO DE DEPURAÇÃO SOBRE QUAL A MELHOR DECISÃO NA ARQUITETURA DA TECNOLOGIA. DESSA FORMA, A PESQUISA PROMOVE UM ESTUDO DA ORGANIZAÇÃO AO REDOR DO PROCESSO DE CRIAÇÃO DOS CHATBOTS PARA EM SEGUIDA COMPREENDER COMO ESSE CONTEXTO TÉCNICO IMPACTA NO DESENVOLVIMENTO DESSAS TECNOLOGIAS. ESSE EMPREENDIMENTO CONCLUIU QUE: (A) OS CHATBOTS SÃO O RESULTADO DE UM ACORDO DE COMPROMISSO ENTRE MÚLTIPLAS METAFÍSICAS MORAIS E QUE ESSE CARÁTER HETEROGÊNEO É BENÉFICO PARA O SEU FIM COMERCIAL; (B) ESTE BENEFÍCIO SE DEVE AO CARÁTER HÍBRIDO DA ORGANIZAÇÃO QUE, BASEANDO-ME EM NEFF E STARK, DESCREVO COMO O EMPREGO DE ASPECTOS TANTO DE ORGANIZAÇÕES ‘PERMANENTEMENTE BETA’ QUANTO DE ORGANIZAÇÕES TRADICIONAIS; (C) ESSES ESPECIALISTAS PROJETAM AS TECNOLOGIAS A PARTIR DA INCORPORAÇÃO DE UMA SOCIABILIDADE CORDIAL, PRODUZIDA POR MEIO DA ABERTURA EMOCIONAL COM O USUÁRIO, QUE AUXILIA NA DEFINIÇÃO DE UMA SITUAÇÃO FAVORECENDO A RECIPROCIDADE COM O USUÁRIO. POR FIM, PARA ANALISAR ESSE CAMPO PROPONHO O CONCEITO DE ORGANIZAÇÕES EM MATURAÇÃO, PARA DESCREVER ORGANIZAÇÕES QUE SE BENEFICIAM DESSE CARÁTER HÍBRIDO, E DE ROBÔS SOCIÁVEIS, BOTS SOCIAIS CRIADOS PARA SOCIALIZAR CORDIALMENTE COM O USUÁRIO.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SINCE THE EMERGENCE OF A NEW DEEP LEARNING TECHNIQUE IN 2012, INTEREST IN ARTIFICIAL INTELLIGENCE (AI) HAS INCREASED SIGNIFICANTLY IN INDUSTRY, THE SCIENTIFIC COMMUNITY AND THE MEDIA (LEE, 2018). OVER TIME, TECHNOLOGY BECAME A STATE MATTER, TO THE POINT THAT, IN THE LATE 2010S, SEVERAL COUNTRIES PUBLISHED NATIONAL STRATEGIES FOR THE DEVELOPMENT OF AI. FOLLOWING THIS TREND, BRAZIL PUBLISHED IN 2021 THE BRAZILIAN ARTIFICIAL INTELLIGENCE STRATEGY. INTERESTINGLY, HOWEVER, THE COUNTRY HAD ALREADY PUT IN PLACE THREE POLICIES TO PROMOTE AI, ONE OF THEM BEING THE CENTERS FOR APPLIED RESEARCH IN ARTIFICIAL INTELLIGENCE PROGRAM. IN OUR RESEARCH, WE SOUGHT TO EXAMINE THE PROGRESS OF THIS PROGRAM IN ITS INITIAL STAGES, CONCEIVING IT AS A STATE POLICY AIMED AT FOSTERING INNOVATION AND NATIONAL DEVELOPMENT. FOR THIS, WE ANALYZED DATA COLLECTED ON INTERVIEWS, SEMINARS AND DOCUMENTS FROM ORGANS FUNDING BODIES AND FROM EACH OF THE SIX CENTERS CONTEMPLATED IN THE PROGRAM, WHILE SUPPORTED BY THEORETICAL PRODUCTION ON THE ECONOMIC ROLE OF TECHNOLOGY, DEVELOPMENT AND INNOVATION SYSTEMS. OUR WORK POINTS OUT THAT, TAKING THE PROGRAM AS A REFERENCE, THE FORMULATION, PLANNING AND EXECUTION OF A POLICY FOR THE DEVELOPMENT OF ARTIFICIAL INTELLIGENCE IN BRAZIL HAS VERY VISIBLE LIMITATIONS AND CONTRADICTIONS, EVEN THOUGH IT CONSTITUTES A RELEVANT INITIATIVE.</t>
+          <t>THIS MASTER THESIS AIMS TO ANALYZE THE PROCESS OF CREATING CHATBOTS FOR THE COMMERCIAL ENVIRONMENT. CHATBOTS ARE COMPUTER PROGRAMMING TECHNOLOGIES DEVELOPED FOR INTERACTION WITH THE USER. BASED ON A PRAGMATIST APPROACH, THE WORK FOCUSES ON UNDERSTANDING THE MORAL METAPHYSICS THAT GUIDE THE EVALUATIVE PRINCIPLES OF THE RESPONSIBLE SPECIALISTS AND ON THE CHARACTERISTICS OF THE RELATIONSHIP OF THESE AGENTS IN THEIR WORK ROUTINE. BY DEPLOYING THE TECHNIQUE OF SEMI-STRUCTURED INTERVIEWS WITH EXPERTS, IT WAS POSSIBLE TO UNDERSTAND THAT THEY JUSTIFY THEIR EVALUATIVE PRINCIPLES BY MOBILIZING A METAPHYSICS ABOUT WHOM THIS END-USER IS - ABSTRACTION PROVED VARIABLE AMONG DIFFERENT PROFESSIONALS. THESE MULTIPLE EVALUATIVE PRINCIPLES ARE DEPLOYED IN ORDER TO CREATE PRODUCTIVE DISSONANCES CAPABLE OF ASSISTING IN DEBUGGING THE BEST DECISION IN TECHNOLOGY DESIGN. IN THIS WAY, THE RESEARCH PROMOTES A STUDY OF THE ORGANIZATION AROUND CREATING CHATBOTS TO UNDERSTAND HOW THIS TECHNICAL CONTEXT IMPACTS THE DEVELOPMENT OF THESE TECHNOLOGIES. THIS EFFORT CONCLUDED THAT: (A) CHATBOTS ARE THE RESULT OF A COMPROMISE AGREEMENT BETWEEN MULTIPLE MORAL METAPHYSICS AND THAT THIS HETEROGENEOUS CHARACTER IS BENEFICIAL FOR THEIR COMMERCIAL PURPOSE; (B) THIS BENEFIT IS DUE TO THE HYBRID CHARACTER OF THE ORGANIZATION WHICH, BASED ON NEFF AND STARK, I DESCRIBE AS EMPLOYING ASPECTS OF BOTH 'PERMANENTLY BETA' ORGANIZATIONS AND TRADITIONAL ORGANIZATIONS; (C) THESE SPECIALISTS DESIGN TECHNOLOGIES BASED ON THE INCORPORATION OF FRIENDLY SOCIABILITY, PRODUCED THROUGH EMOTIONAL OPENNESS WITH THE USER, WHICH HELPS TO DEFINE A SITUATION FAVORING RECIPROCITY WITH THE USER. FINALLY, TO ANALYZE THIS FIELD, I PROPOSE THE CONCEPT OF MATURING ORGANIZATIONS TO DESCRIBE ORGANIZATIONS THAT BENEFIT FROM THIS HYBRID CHARACTER. I ALSO SUGGEST THE CONCEPT OF SOCIABLE ROBOTS, SOCIAL BOTS CREATED TO FRIENDLY SOCIALIZE WITH THE USER.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>INTELIGÊNCIA ARTIFICIAL;CIÊNCIA E TECNOLOGIA;INOVAÇÃO;BRASIL</t>
+          <t>SOCIOLOGIA DA CRÍTICA;CHATBOTS;INTELIGÊNCIA ARTIFICIAL;SOCIOLOGIA DO VALOR</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>ARTIFICIAL INTELLIGENCE;SCIENCE AND TECHNOLOGY;INNOVATION;BRAZIL</t>
+          <t>SOCIOLOGY OF CRITIQUE;CHATBOTS;ARTIFICIAL INTELLIGENCE;SOCIOLOGY OF VALUE</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Aprendizado profundo &amp; redes neurais; IA em sentido estrito</t>
+          <t>IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M61" t="b">
@@ -8958,17 +8958,17 @@
         <v>0</v>
       </c>
       <c r="O61" t="b">
+        <v>0</v>
+      </c>
+      <c r="P61" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="b">
         <v>1</v>
       </c>
-      <c r="P61" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="b">
-        <v>0</v>
-      </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>EDEMILSON CRUZ SANTANA JUNIOR</t>
+          <t>EUGENIA DE SOUZA MELLO GUIMARAES MOTTA</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -8978,31 +8978,31 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DO CEARÁ</t>
+          <t>UNIVERSIDADE DO ESTADO DO RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>UFC</t>
+          <t>UERJ</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>NORDESTE</t>
+          <t>SUDESTE</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>CEARÁ</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="Y61" t="n">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
@@ -9021,16 +9021,16 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13606356</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12141694</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>13606356</t>
+          <t>12141694</t>
         </is>
       </c>
       <c r="AE61" t="n">
-        <v>3608423</v>
+        <v>3613835</v>
       </c>
     </row>
     <row r="62">
@@ -9049,37 +9049,37 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2022-02-15</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MAXIMO ITALO D ALMEIDA ATHAYDE AVILA</t>
+          <t>VITOR RODRIGUES FERREIRA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>O PROCESSO DE ALGORITMIZAÇÃO DO ESTADO: UMA ANÁLISE DAS AGÊNCIAS PÚBLICAS DE INTERMEDIAÇÃO DE MÃO DE OBRA</t>
+          <t>CONCEITOS, PROTÓTIPOS E IMAGENS: O NOVO PARADIGMA DE GESTÃO DE DADOS NAS REDES DE MARKETING DO SETOR AUTOMOBILÍSTICO BRASILEIRO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>A DISSERTAÇÃO SE PROPÕE A OBSERVAR OS INDÍCIOS CONTIDOS NO PROCESSO DE REESTRUTURAÇÃO NA ORGANIZAÇÃO DA POLÍTICA DE EMPREGO POSTOS SOB GERENCIAMENTO DE ALGORITMOS, EM ESPECÍFICO, NO SERVIÇO ESTATAL DE INTERMEDIAÇÃO DE MÃO DE OBRA. PARA TAL, REALIZA-SE UMA REVISÃO HISTÓRICA DA CONFORMAÇÃO DOS MERCADOS DE TRABALHO NO CONTEXTO CAPITALISTA, POSTERIORMENTE ABORDA-SE A QUESTÃO BRASILEIRA NA INSERÇÃO DE POLÍTICAS SOCIAIS PARA SER POSSÍVEL ANALISAR O TRAJETO DA POLÍTICA DO SINE NO ESTEIO DO MODO EMPRESA DE GERENCIAR O SOCIAL. A RENOVAÇÃO DESSA POLÍTICA CONTA COM A PARCERIA DE AGÊNCIAS INTERMEDIADORAS PRIVADAS, TORNA OS INTERMEDIADORES COMISSIONADOS E A REFAÇÃO DO SISTEMA DE ATENDIMENTO DIGITAL. TUDO EM NOME DA MODERNIZAÇÃO, DAS “BOAS PRÁTICAS GERENCIAIS” E DA EFICIÊNCIA NO GASTO PÚBLICO.</t>
+          <t>COM O ADVENTO DA INDÚSTRIA 4.0 E O DESENVOLVIMENTO DE NOVAS TECNOLOGIAS DA INFORMAÇÃO CALCADAS NA CIÊNCIA DE DADOS, A ATIVIDADE DE MARKETING, RESPONSÁVEL POR GERIR A COMUNICAÇÃO DA FIRMA COM O PÚBLICO, PASSA POR TRANSFORMAÇÕES RADICAIS. A PRESENTE PESQUISA DEFENDE QUE ESTE NOVO MODELO DE GESTÃO DA INFORMAÇÃO REORGANIZA O CONJUNTO DE RELAÇÕES CORPORATIVAS, ATIVIDADES DE TRABALHO E FORMAS DE CALCULAR MERCADOS E RELAÇÕES DE CONSUMO QUE COMPÕEM A REDE DE MARKETING. O TEXTO TAMBÉM SUSTENTA QUE TAL MUDANÇA IMPACTA A FORMA COMO MERCADORIAS SÃO MATERIAL E SIMBOLICAMENTE CRIADAS. ATRAVÉS DA REALIZAÇÃO DE ENTREVISTAS E DA ANÁLISE SISTEMÁTICA DAS INFORMAÇÕES PUBLICADAS POR MEMBROS DA REDE DE MARKETING DO SEGMENTO AUTOMOBILÍSTICO BRASILEIRO EM PLATAFORMAS DIGITAIS, É RECONSTITUÍDA A DIVISÃO DE ATRIBUIÇÕES, RECURSOS E FORMAS DE CÁLCULO ENTRE AS EQUIPES DE TRABALHO QUE COMPÕEM A REDE. O MARKETING AUTOMOTIVO UTILIZA DE TRABALHO INTENSIVO DE CAPTURA, PROCESSAMENTO E ANÁLISE DE GRANDES VOLUMES DE DADOS PROVENIENTES DA WEB PARA A DEFINIÇÃO DAS ESTRATÉGIAS DE CRIAÇÃO DE ANÚNCIOS E VEÍCULOS. ALÉM DISSO, O MARKETING DEPENDE DE MODELOS DE INTELIGÊNCIA ARTIFICIAL PARA DISTRIBUIR SEUS ANÚNCIOS AO PÚBLICO ALVO. A CRIAÇÃO DA MERCADORIA É ENRAIZADA A UMA CONFLUÊNCIA DE PROCESSOS: A CRIAÇÃO DE CONCEITOS DE NOVOS PRODUTOS A PARTIR DE PESQUISAS DE DADOS E DA SEGMENTAÇÃO DE PÚBLICO ALVO; DA ELABORAÇÃO DE PROTÓTIPOS COM VIABILIDADE FÍSICA E FINANCEIRA; E DA ASSOCIAÇÃO SIMBÓLICA DE MERCADORIAS A VALORES, IMAGENS E GRUPOS SOCIAIS, CORPORIFICADA ATRAVÉS DO ANÚNCIO.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>THIS DISSERTATION PROPOSES TO OBSERVE THE EVIDENCE CONTAINED IN THE RESTRUCTURING PROCESS IN THE ORGANIZATION OF THE EMPLOYMENT POLICY PLACED UNDER THE ADMINISTRATION OF ALGORITHMS, SPECIFICALLY, IN THE STATE LABOR INTERMEDIATION SERVICE. TO THIS END, A HISTORICAL REVIEW OF THE CONFORMATION OF LABOR MARKETS IN THE CAPITALIST CONTEXT IS CARRIED OUT, LATER THE BRAZILIAN ISSUE IS ADDRESSED IN THE INSERTION OF SOCIAL POLICIES IN ORDER TO ANALYZE THE TRAJECTORY OF SINE'S POLICY ON THE SHOULDERS OF THE COMPANY FORM OF MANAGING THE SOCIAL. THE RENEWAL OF THIS POLICY COUNTS ON THE PARTNERSHIP OF PRIVATE INTERMEDIATION AGENCIES, MAKES THE INTERMEDIARIES COMMISSIONED AND, IN ITS WAY, REFINES THE DIGITAL INTERMEDIATION SERVICE SYSTEM. ALL IN THE NAME OF MODERNIZATION, “THE GOOD MANAGEMENT PRACTICES” AND EFFICIENCY IN PUBLIC SPENDING.</t>
+          <t>WITH THE ADVENT OF INDUSTRY 4.0 AND THE DEVELOPMENT OF NEW INFORMATION TECHNOLOGIES BASED ON DATA SCIENCE, MARKETING ACTIVITY PASSAGES THROUGH RADICAL TRANSFORMATIONS. THE PRESENT RESEARCH ARGUES THAT THIS NEW INFORMATION MANAGEMENT MODEL REORGANIZES THE SET OF CORPORATE WORK RELATIONSHIPS, LABOUR ACTIVITIES AND WAYS OF CALCULATING MARKETS AND CONSUMER RELATIONS ALONG THE MARKETING NETWORK. THE TEXT ALSO MAINTAINS THAT SUCH A SHIFT IMPACTS THE WAY COMMODITIES ARE MATERIALLY AND SYMBOLICALLY CREATED. THROUGH INTERVIEWS AND THE SYSTEMATIC ANALYSIS OF INFORMATION PUBLISHED BY BRAZILIAN'S AUTOMOTIVE SEGMENT MARKETING NETWORK MEMBERS, THE DIVISION OF NETWORK ATTRIBUTIONS, RESOURCES, AND CALCULATION METHODS AMONG THE WORK ANALYSIS TEAMS THAT DEFINE A NETWORK IS RECONSTITUTED. AUTOMOTIVE MARKETING IS LABOR INTENSIVE IN CAPTURING, PROCESSING, AND ANALYZING LARGE VOLUMES OF DATA FROM THE WEB TO CREATE STRATEGIES FOR CREATING ADS AND VEHICLES. IN ADDITION, MARKETING RELIES ON ARTIFICIAL INTELLIGENCE MODELS TO DELIVER ITS ADS TO THE TARGET AUDIENCE. THE CREATION OF THE COMMODITY IS EMBEDDED TO A CONFLUENCE OF PROCESSES: THE CONCEPTUALIZON OF NEW PRODUCTS BASED ON DATA ANALYSIS AND THE ELABORATION OF TARGET RESEARCH; THE DESIGNING OF PROTOTYPES WITH PHYSICAL AND FINANCIAL VIABILITY; AND THE SYMBOLIC ASSOCIATION OF COMMODITIES TO VALUES, PUBLIC IMAGES AND SOCIAL GROUPES, WICH IS EMBODIED THROUGH THE ADVERTISEMENT.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>INTERMEDIAÇÃO DE MÃO DE OBRA;POLÍTICA DE EMPREGO;NEOLIBERALISMO;APRENDIZADO DE MÁQUINA;GOVERNANÇA ALGORÍTMICA.</t>
+          <t>SOCIOLOGIA ECONÔMICA;MARKETING;INDÚSTRIA AUTOMOTIVA;CIÊNCIA DE DADOS;REDES DIGITAIS.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>INTERMEDIATION OF LABOR;EMPLOYMENT POLICY;NEOLIBERALISM;MACHINE LEARNING;ALGORITHMIC GOVERNANCE.</t>
+          <t>ECONOMIC SOCIOLOGY;MARKETING;AUTOMOTIVE INDUSTRY;DATA SCIENCE;DIGITAL NETWORKS.</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -9089,14 +9089,14 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Aprendizado de máquina (ML)</t>
+          <t>IA em sentido estrito</t>
         </is>
       </c>
       <c r="M62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62" t="b">
         <v>0</v>
@@ -9109,69 +9109,69 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>PEDRO ALCIDES ROBERTT NIZ</t>
+          <t>RODRIGO SALLES PEREIRA DOS SANTOS</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
+          <t>SOCIOLOGIA E ANTROPOLOGIA</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE FEDERAL DO RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>UFRJ</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>SUDESTE</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="Y62" t="n">
+        <v>145</v>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>PORTUGUES</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>OUTRAS SOCIOLOGIAS ESPECÍFICAS</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>UNIVERSIDADE FEDERAL DE PELOTAS</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>UFPEL</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>SUL</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>RIO GRANDE DO SUL</t>
-        </is>
-      </c>
-      <c r="Y62" t="n">
-        <v>118</v>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>PORTUGUES</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>NÃO SE APLICA</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>SOCIOLOGIA</t>
-        </is>
-      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=11433364</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12879895</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>11433364</t>
+          <t>12879895</t>
         </is>
       </c>
       <c r="AE62" t="n">
-        <v>668986</v>
+        <v>3055993</v>
       </c>
     </row>
     <row r="63">
@@ -9186,55 +9186,55 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OLGA CHRISTINA DE OLIVEIRA ZUNINO</t>
+          <t>BARBARA BRUNA DA TRINDADE GOMES</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ROBÔS SOCIÁVEIS E ORGANIZAÇÕES EM MATURAÇÃO: O PROCESSO DE CRIAÇÃO DOS 'CHATBOTS' NO CONTEXTO COMERCIAL</t>
+          <t>JUVENTUDES PRECARIZADAS NO CAPITALISMO DE PLATAFORMA E SEU POTENCIAL EXPLOSIVO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>ESTA DISSERTAÇÃO PRETENDE ANALISAR O PROCESSO DE CRIAÇÃO DE CHATBOTS (TECNOLOGIAS DE PROGRAMAÇÃO COMPUTACIONAL DESENVOLVIDAS PARA A INTERAÇÃO COM O USUÁRIO) PARA O MEIO COMERCIAL A PARTIR, APOIADA EM UMA ABORDAGEM PRAGMATISTA, DA COMPREENSÃO DAS METAFÍSICAS MORAIS QUE ORIENTAM OS PRINCÍPIOS AVALIATIVOS DOS ESPECIALISTAS RESPONSÁVEIS E PELAS CARACTERÍSTICAS DA RELAÇÃO DESSES AGENTES EM SUA ROTINA DE TRABALHO. POR MEIO DA TÉCNICA DE ENTREVISTAS SEMIESTRUTURADAS COM OS ESPECIALISTAS FOI POSSÍVEL PRODUZIR O ENTENDIMENTO DE QUE ELES JUSTIFICAM SEUS PRINCÍPIOS AVALIATIVOS A PARTIR DA MOBILIZAÇÃO DE UMA METAFÍSICA SOBRE QUEM É ESSE USUÁRIO FINAL, ABSTRAÇÃO ESSA VARIÁVEL ENTRE DIFERENTES PROFISSIONAIS. ESSES MÚLTIPLOS PRINCÍPIOS AVALIATIVOS SÃO MOBILIZADOS DE FORMA A CRIAR FRICÇÕES PRODUTIVAS CAPAZES DE AUXILIAR NO PROCESSO DE DEPURAÇÃO SOBRE QUAL A MELHOR DECISÃO NA ARQUITETURA DA TECNOLOGIA. DESSA FORMA, A PESQUISA PROMOVE UM ESTUDO DA ORGANIZAÇÃO AO REDOR DO PROCESSO DE CRIAÇÃO DOS CHATBOTS PARA EM SEGUIDA COMPREENDER COMO ESSE CONTEXTO TÉCNICO IMPACTA NO DESENVOLVIMENTO DESSAS TECNOLOGIAS. ESSE EMPREENDIMENTO CONCLUIU QUE: (A) OS CHATBOTS SÃO O RESULTADO DE UM ACORDO DE COMPROMISSO ENTRE MÚLTIPLAS METAFÍSICAS MORAIS E QUE ESSE CARÁTER HETEROGÊNEO É BENÉFICO PARA O SEU FIM COMERCIAL; (B) ESTE BENEFÍCIO SE DEVE AO CARÁTER HÍBRIDO DA ORGANIZAÇÃO QUE, BASEANDO-ME EM NEFF E STARK, DESCREVO COMO O EMPREGO DE ASPECTOS TANTO DE ORGANIZAÇÕES ‘PERMANENTEMENTE BETA’ QUANTO DE ORGANIZAÇÕES TRADICIONAIS; (C) ESSES ESPECIALISTAS PROJETAM AS TECNOLOGIAS A PARTIR DA INCORPORAÇÃO DE UMA SOCIABILIDADE CORDIAL, PRODUZIDA POR MEIO DA ABERTURA EMOCIONAL COM O USUÁRIO, QUE AUXILIA NA DEFINIÇÃO DE UMA SITUAÇÃO FAVORECENDO A RECIPROCIDADE COM O USUÁRIO. POR FIM, PARA ANALISAR ESSE CAMPO PROPONHO O CONCEITO DE ORGANIZAÇÕES EM MATURAÇÃO, PARA DESCREVER ORGANIZAÇÕES QUE SE BENEFICIAM DESSE CARÁTER HÍBRIDO, E DE ROBÔS SOCIÁVEIS, BOTS SOCIAIS CRIADOS PARA SOCIALIZAR CORDIALMENTE COM O USUÁRIO.</t>
+          <t>O DESENVOLVIMENTO TECNOLÓGICO CONSTITUÍDO, SOBRETUDO, PELA NANOTECNOLOGIA, ROBÓTICA E TECNOLOGIA DA INFORMAÇÃO, TEM PROMOVIDO TRANSFORMAÇÕES SIGNIFICATIVAS NO MUNDO E NAS RELAÇÕES DE TRABALHO. ESPECIFICAMENTE NO BRASIL, ESSAS TRANSFORMAÇÕES FORAM ACENTUADAS A PARTIR DOS ANOS 90, COM A IMPLANTAÇÃO DAS POLÍTICAS NEOLIBERAIS DO GOVERNO COLLOR, GENERALIZANDO A PRECARIZAÇÃO E A FLEXIBILIZAÇÃO DO TRABALHO ATRAVÉS DO INCENTIVO DE CONTRATAÇÕES INFORMAIS E DESREGULAMENTADAS. HOJE, OS NOVOS CONTORNOS, ORGANIZAÇÃO E GESTÃO QUE VEM SE CONFIGURANDO NO MERCADO DE TRABALHO, ESTÃO SE TORNANDO MAIS RECONHECÍVEIS ATRAVÉS DO TRABALHO MEDIADO PELAS PLATAFORMAS DIGITAIS. NOS ÚLTIMOS ANOS, O CENÁRIO DAS CIDADES BRASILEIRAS PASSOU A CONTAR COM A FIGURA DOS ENTREGADORES POR APLICATIVO, NOTADAMENTE A PARTIR DE 2020 HOUVE UMA MAIOR PROLIFERAÇÃO DA CATEGORIA, EM VIRTUDE DA PANDEMIA DO VÍRUS COVID19, UMA VEZ QUE, COM A IMPOSSIBILIDADE DA LIVRE CIRCULAÇÃO DE PESSOAS, O SERVIÇO DE DELIVERY PASSOU A SER A ALTERNATIVA MAIS UTILIZADA COMO FORMA DE CONTINUIDADE DE PARCELA DO COMÉRCIO. NESSE SENTIDO, A PRESENTE DISSERTAÇÃO BUSCOU IDENTIFICAR A SITUAÇÃO DAS JUVENTUDES PRECARIZADAS QUE PRESTAM SERVIÇO POR DEMANDA DE APLICATIVO, ANALISANDO AS PECULIARIDADES DESSA FRAÇÃO DE TRABALHADORES, BEM COMO SEU POTENCIAL EXPLOSIVO PARA RESISTIR E REIVINDICAR. VERIFICOU-SE A PARTIR DA ANÁLISE E ESTUDOS DOS DADOS QUE ESSES JOVENS EM SUA MAIORIA SÃO PRETOS, POBRES E COM BAIXA ESCOLARIDADE. ALÉM DISSO, FOI CONSTATADO QUE APESAR DE FRAGILIZADA, ESSAS JUVENTUDES FAZEM PARTE DA FRAÇÃO DA CLASSE TRABALHADORA QUE TEM UM POTENCIAL DE TRANSFORMAÇÃO QUANDO SE PENSA EM LUTAR POR MELHORES CONDIÇÕES DE TRABALHO, BASTA OLHAR AS MANIFESTAÇÕES AO REDOR DO MUNDO E NO BRASIL, COMO EXEMPLO O BREQUE DOS APPS. CONTUDO, APESAR DE LUTAREM POR MELHORES CONDIÇÕES, AINDA NÃO EXISTE UM CONSENSO QUANDO SE TRATA DE TER VÍNCULOS EMPREGATÍCIOS E UM TRABALHO REGULAMENTADO, NOS MOLDES DA CLT.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>THIS MASTER THESIS AIMS TO ANALYZE THE PROCESS OF CREATING CHATBOTS FOR THE COMMERCIAL ENVIRONMENT. CHATBOTS ARE COMPUTER PROGRAMMING TECHNOLOGIES DEVELOPED FOR INTERACTION WITH THE USER. BASED ON A PRAGMATIST APPROACH, THE WORK FOCUSES ON UNDERSTANDING THE MORAL METAPHYSICS THAT GUIDE THE EVALUATIVE PRINCIPLES OF THE RESPONSIBLE SPECIALISTS AND ON THE CHARACTERISTICS OF THE RELATIONSHIP OF THESE AGENTS IN THEIR WORK ROUTINE. BY DEPLOYING THE TECHNIQUE OF SEMI-STRUCTURED INTERVIEWS WITH EXPERTS, IT WAS POSSIBLE TO UNDERSTAND THAT THEY JUSTIFY THEIR EVALUATIVE PRINCIPLES BY MOBILIZING A METAPHYSICS ABOUT WHOM THIS END-USER IS - ABSTRACTION PROVED VARIABLE AMONG DIFFERENT PROFESSIONALS. THESE MULTIPLE EVALUATIVE PRINCIPLES ARE DEPLOYED IN ORDER TO CREATE PRODUCTIVE DISSONANCES CAPABLE OF ASSISTING IN DEBUGGING THE BEST DECISION IN TECHNOLOGY DESIGN. IN THIS WAY, THE RESEARCH PROMOTES A STUDY OF THE ORGANIZATION AROUND CREATING CHATBOTS TO UNDERSTAND HOW THIS TECHNICAL CONTEXT IMPACTS THE DEVELOPMENT OF THESE TECHNOLOGIES. THIS EFFORT CONCLUDED THAT: (A) CHATBOTS ARE THE RESULT OF A COMPROMISE AGREEMENT BETWEEN MULTIPLE MORAL METAPHYSICS AND THAT THIS HETEROGENEOUS CHARACTER IS BENEFICIAL FOR THEIR COMMERCIAL PURPOSE; (B) THIS BENEFIT IS DUE TO THE HYBRID CHARACTER OF THE ORGANIZATION WHICH, BASED ON NEFF AND STARK, I DESCRIBE AS EMPLOYING ASPECTS OF BOTH 'PERMANENTLY BETA' ORGANIZATIONS AND TRADITIONAL ORGANIZATIONS; (C) THESE SPECIALISTS DESIGN TECHNOLOGIES BASED ON THE INCORPORATION OF FRIENDLY SOCIABILITY, PRODUCED THROUGH EMOTIONAL OPENNESS WITH THE USER, WHICH HELPS TO DEFINE A SITUATION FAVORING RECIPROCITY WITH THE USER. FINALLY, TO ANALYZE THIS FIELD, I PROPOSE THE CONCEPT OF MATURING ORGANIZATIONS TO DESCRIBE ORGANIZATIONS THAT BENEFIT FROM THIS HYBRID CHARACTER. I ALSO SUGGEST THE CONCEPT OF SOCIABLE ROBOTS, SOCIAL BOTS CREATED TO FRIENDLY SOCIALIZE WITH THE USER.</t>
+          <t>TECHNOLOGICAL DEVELOPMENT, CONSISTING MAINLY OF NANOTECHNOLOGY, ROBOTICS AND INFORMATION TECHNOLOGY, HAS PROMOTED SIGNIFICANT CHANGES IN THE WORLD AND IN LABOR RELATIONS. SPECIFICALLY IN BRAZIL, THESE TRANSFORMATIONS WERE ACCENTUATED FROM THE 1990S ONWARDS, WITH THE IMPLEMENTATION OF THE COLLOR GOVERNMENT'S NEOLIBERAL POLICIES, GENERALIZING MEASURES OF A LIBERAL NATURE FOR HIRING WORKERS IN WAYS THAT WERE BELOW WHAT WAS ESTABLISHED BY THE CLT. TODAY, THE NEW CONTOURS, ORGANIZATION AND MANAGEMENT THAT HAVE BEEN TAKING SHAPE IN THE LABOR MARKET ARE BECOMING MORE RECOGNIZABLE THROUGH WORK MEDIATED BY DIGITAL PLATFORMS. IN RECENT YEARS, THE SCENARIO OF BRAZILIAN CITIES HAS COME TO RELY ON THE FIGURE OF COURIERS BY APP, NOTABLY FROM 2020 THERE HAS BEEN A GREATER PROLIFERATION OF THE CATEGORY, DUE TO THE COVID19 VIRUS PANDEMIC, SINCE, WITH THE IMPOSSIBILITY OF FREE MOVEMENT OF PEOPLE, THE DELIVERY SERVICE HAS BECOME THE MOST USED ALTERNATIVE AS A WAY OF CONTINUING A PORTION OF TRADE. IN THIS SENSE, THIS DISSERTATION PROPOSES TO ANALYZE THE SITUATION OF PRECARIOUS YOUTHS WHO PROVIDE SERVICES BY APPLICATION DEMAND, SEEKING TO UNDERSTAND THE PECULIARITIES OF THIS FRACTION OF WORKERS, AS WELL AS THEIR EXPLOSIVE POTENTIAL TO RESIST AND CLAIM. IT WAS VERIFIED FROM THE ANALYSIS AND STUDIES OF THE DATA THAT THESE YOUNG PEOPLE ARE MOSTLY BLACK, POOR AND WITH LOW EDUCATION. IN ADDITION, IT WAS FOUND THAT DESPITE BEING FRAGILE, THESE YOUTHS ARE PART OF THE FRACTION OF THE WORKING CLASS THAT HAS A POTENTIAL FOR TRANSFORMATION WHEN THINKING ABOUT FIGHTING FOR BETTER CONDITIONS, JUST LOOK AT THE DEMONSTRATIONS AROUND THE WORLD AND IN BRAZIL, AS AN EXAMPLE OF THE BREQUE OF APPS. HOWEVER, DESPITE FIGHTING FOR BETTER CONDITIONS, THERE IS STILL NO CONSENSUS WHEN IT COMES TO HAVING LINKS WITH THE CLT.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SOCIOLOGIA DA CRÍTICA;CHATBOTS;INTELIGÊNCIA ARTIFICIAL;SOCIOLOGIA DO VALOR</t>
+          <t>DESENVOLVIMENTO TECNOLÓGICO;PLATAFORMAS DIGITAIS;ENTREGADORES POR APLICATIVO;BREQUE DOS APPS</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>SOCIOLOGY OF CRITIQUE;CHATBOTS;ARTIFICIAL INTELLIGENCE;SOCIOLOGY OF VALUE</t>
+          <t>TECHNOLOGICAL DEVELOPMENT;DIGITAL PLATFORMS;COURIERS BY APPLICATION;APPS BREAK.</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>IA em sentido estrito; Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N63" t="b">
         <v>0</v>
@@ -9250,69 +9250,69 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>EUGENIA DE SOUZA MELLO GUIMARAES MOTTA</t>
+          <t>GONZALO ADRIAN ROJAS</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
+          <t>CIÊNCIAS SOCIAIS</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE FEDERAL DE CAMPINA GRANDE</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>UFCG</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>NORDESTE</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>PARAÍBA</t>
+        </is>
+      </c>
+      <c r="Y63" t="n">
+        <v>117</v>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>PORTUGUES</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
           <t>SOCIOLOGIA</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>UNIVERSIDADE DO ESTADO DO RIO DE JANEIRO</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>UERJ</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>SUDESTE</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>RJ</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>RIO DE JANEIRO</t>
-        </is>
-      </c>
-      <c r="Y63" t="n">
-        <v>84</v>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>PORTUGUES</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>NÃO SE APLICA</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>SOCIOLOGIA</t>
-        </is>
-      </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12141694</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12825916</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>12141694</t>
+          <t>12825916</t>
         </is>
       </c>
       <c r="AE63" t="n">
-        <v>3613835</v>
+        <v>3876753</v>
       </c>
     </row>
     <row r="64">
@@ -9327,41 +9327,41 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>VITOR RODRIGUES FERREIRA</t>
+          <t>GUSTAVO DANIEL PRADO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CONCEITOS, PROTÓTIPOS E IMAGENS: O NOVO PARADIGMA DE GESTÃO DE DADOS NAS REDES DE MARKETING DO SETOR AUTOMOBILÍSTICO BRASILEIRO</t>
+          <t>DESAFIOS DA EMPREGABILIDADE ANTE O AVANÇO DA INTELIGÊNCIA ARTIFICIAL: O CASO IMPRENSA OFICIAL DE MG</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>COM O ADVENTO DA INDÚSTRIA 4.0 E O DESENVOLVIMENTO DE NOVAS TECNOLOGIAS DA INFORMAÇÃO CALCADAS NA CIÊNCIA DE DADOS, A ATIVIDADE DE MARKETING, RESPONSÁVEL POR GERIR A COMUNICAÇÃO DA FIRMA COM O PÚBLICO, PASSA POR TRANSFORMAÇÕES RADICAIS. A PRESENTE PESQUISA DEFENDE QUE ESTE NOVO MODELO DE GESTÃO DA INFORMAÇÃO REORGANIZA O CONJUNTO DE RELAÇÕES CORPORATIVAS, ATIVIDADES DE TRABALHO E FORMAS DE CALCULAR MERCADOS E RELAÇÕES DE CONSUMO QUE COMPÕEM A REDE DE MARKETING. O TEXTO TAMBÉM SUSTENTA QUE TAL MUDANÇA IMPACTA A FORMA COMO MERCADORIAS SÃO MATERIAL E SIMBOLICAMENTE CRIADAS. ATRAVÉS DA REALIZAÇÃO DE ENTREVISTAS E DA ANÁLISE SISTEMÁTICA DAS INFORMAÇÕES PUBLICADAS POR MEMBROS DA REDE DE MARKETING DO SEGMENTO AUTOMOBILÍSTICO BRASILEIRO EM PLATAFORMAS DIGITAIS, É RECONSTITUÍDA A DIVISÃO DE ATRIBUIÇÕES, RECURSOS E FORMAS DE CÁLCULO ENTRE AS EQUIPES DE TRABALHO QUE COMPÕEM A REDE. O MARKETING AUTOMOTIVO UTILIZA DE TRABALHO INTENSIVO DE CAPTURA, PROCESSAMENTO E ANÁLISE DE GRANDES VOLUMES DE DADOS PROVENIENTES DA WEB PARA A DEFINIÇÃO DAS ESTRATÉGIAS DE CRIAÇÃO DE ANÚNCIOS E VEÍCULOS. ALÉM DISSO, O MARKETING DEPENDE DE MODELOS DE INTELIGÊNCIA ARTIFICIAL PARA DISTRIBUIR SEUS ANÚNCIOS AO PÚBLICO ALVO. A CRIAÇÃO DA MERCADORIA É ENRAIZADA A UMA CONFLUÊNCIA DE PROCESSOS: A CRIAÇÃO DE CONCEITOS DE NOVOS PRODUTOS A PARTIR DE PESQUISAS DE DADOS E DA SEGMENTAÇÃO DE PÚBLICO ALVO; DA ELABORAÇÃO DE PROTÓTIPOS COM VIABILIDADE FÍSICA E FINANCEIRA; E DA ASSOCIAÇÃO SIMBÓLICA DE MERCADORIAS A VALORES, IMAGENS E GRUPOS SOCIAIS, CORPORIFICADA ATRAVÉS DO ANÚNCIO.</t>
+          <t>A HISTÓRIA DA HUMANIDADE É MARCADA POR INOVAÇÕES TECNOLÓGICAS, SERVINDO COMO CATALISADORES DE MUDANÇAS FUNDAMENTAIS NA FORMA COMO SOCIEDADES PERCEBEM E INTERAGEM COM O MUNDO. ATRAVÉS DAS ERAS, DESDE A INVENÇÃO DA MÁQUINA A VAPOR, QUE INICIOU A PRIMEIRA REVOLUÇÃO INDUSTRIAL, ATÉ OS AVANÇOS CONTEMPORÂNEOS DA CHAMADA REVOLUÇÃO 4.0, TECNOLOGIAS TÊM MOLDADO E REDEFINIDO O TECIDO SOCIOECONÔMICO DE MANEIRA PROFUNDA. AO EXAMINAR O IMPACTO DESSAS INOVAÇÕES, TORNA-SE EVIDENTE QUE NÃO SÃO MERAS ALTERAÇÕES TÉCNICAS, MAS SIM TRANSFORMAÇÕES QUE PERMEIAM TODOS OS ASPECTOS DA VIDA SOCIAL. ESSES AVANÇOS, PARTICULARMENTE NA ESFERA DA INTELIGÊNCIA ARTIFICIAL (IA), NÃO APENAS OFERECEM NOVAS CAPACIDADES TÉCNICAS, MAS TAMBÉM APRESENTAM DESAFIOS SIGNIFICATIVOS NO QUE DIZ RESPEITO À EMPREGABILIDADE, ESTRUTURAS ORGANIZACIONAIS E INTERAÇÕES HUMANAS. A IA, COM SUAS CAPACIDADES AVANÇADAS DE PROCESSAMENTO DE DADOS, ANÁLISE E GERAÇÃO DE CONTEÚDO, ESTÁ REDEFININDO O AMBIENTE DE TRABALHO, MUITAS VEZES TORNANDO FUNÇÕES TRADICIONAIS HUMANAS REDUNDANTES. TOMANDO A EXTINÇÃO DA IMPRENSA OFICIAL DE MINAS GERAIS COMO ESTUDO DE CASO, ESTA DISSERTAÇÃO BUSCA COMPREENDER AS RAMIFICAÇÕES REAIS E POTENCIAIS DOS AVANÇOS TECNOLÓGICOS SOBRE O EMPREGO. O FIM DA TRAJETÓRIA CENTENÁRIA DE PRODUÇÃO E IMPRESSÃO DO JORNAL FÍSICO NA IMPRENSA OFICIAL NÃO SÓ EXEMPLIFICA A TRANSIÇÃO PARA O DIGITAL, COMO DESTACA AS CONSEQUÊNCIAS SOCIAIS RESULTANTES. O DESLIGAMENTO DE MAIS DE 400 COLABORADORES E A ELIMINAÇÃO DE TODOS OS POSTOS DE TRABALHO ASSOCIADOS MOSTRAM A AMPLITUDE DO IMPACTO QUE INOVAÇÕES PODEM TER SOBRE SETORES TRADICIONAIS. ALÉM DE IDENTIFICAR OS DESAFIOS, É CRUCIAL ABORDAR AS OPORTUNIDADES QUE TAIS INOVAÇÕES APRESENTAM. A CAPACIDADE DA IA DE COLETAR E ANALISAR DADOS EM GRANDE ESCALA, POR EXEMPLO, OFERECE POTENCIAL PARA MELHORAR A EFICIÊNCIA, A PRECISÃO E A PERSONALIZAÇÃO EM VÁRIAS INDÚSTRIAS. NO ENTANTO, A QUESTÃO CENTRAL PERMANECE: COMO AS SOCIEDADES PODEM SE ADAPTAR A ESSA NOVA REALIDADE, GARANTINDO QUE OS AVANÇOS TECNOLÓGICOS BENEFICIEM A MAIORIA, E NÃO APENAS UMA ELITE? COMO PODEMOS ASSEGURAR UMA TRANSIÇÃO JUSTA PARA AQUELES AFETADOS POR MUDANÇAS TÃO DISRUPTIVAS? AO FINAL, ESTA PESQUISA DESTACA A IMPORTÂNCIA DE UMA ABORDAGEM EQUILIBRADA E PROATIVA. ENQUANTO OS AVANÇOS NA IA E NA TECNOLOGIA EM GERAL OFERECEM POSSIBILIDADES INCRÍVEIS, É FUNDAMENTAL QUE AS SOCIEDADES ESTEJAM PREPARADAS, SEJA POR MEIO DE POLÍTICAS DE REQUALIFICAÇÃO, SISTEMAS DE APOIO OU INOVAÇÕES EDUCACIONAIS, PARA GARANTIR QUE TODOS POSSAM SE BENEFICIAR DA ERA DA REVOLUÇÃO 4.0.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>WITH THE ADVENT OF INDUSTRY 4.0 AND THE DEVELOPMENT OF NEW INFORMATION TECHNOLOGIES BASED ON DATA SCIENCE, MARKETING ACTIVITY PASSAGES THROUGH RADICAL TRANSFORMATIONS. THE PRESENT RESEARCH ARGUES THAT THIS NEW INFORMATION MANAGEMENT MODEL REORGANIZES THE SET OF CORPORATE WORK RELATIONSHIPS, LABOUR ACTIVITIES AND WAYS OF CALCULATING MARKETS AND CONSUMER RELATIONS ALONG THE MARKETING NETWORK. THE TEXT ALSO MAINTAINS THAT SUCH A SHIFT IMPACTS THE WAY COMMODITIES ARE MATERIALLY AND SYMBOLICALLY CREATED. THROUGH INTERVIEWS AND THE SYSTEMATIC ANALYSIS OF INFORMATION PUBLISHED BY BRAZILIAN'S AUTOMOTIVE SEGMENT MARKETING NETWORK MEMBERS, THE DIVISION OF NETWORK ATTRIBUTIONS, RESOURCES, AND CALCULATION METHODS AMONG THE WORK ANALYSIS TEAMS THAT DEFINE A NETWORK IS RECONSTITUTED. AUTOMOTIVE MARKETING IS LABOR INTENSIVE IN CAPTURING, PROCESSING, AND ANALYZING LARGE VOLUMES OF DATA FROM THE WEB TO CREATE STRATEGIES FOR CREATING ADS AND VEHICLES. IN ADDITION, MARKETING RELIES ON ARTIFICIAL INTELLIGENCE MODELS TO DELIVER ITS ADS TO THE TARGET AUDIENCE. THE CREATION OF THE COMMODITY IS EMBEDDED TO A CONFLUENCE OF PROCESSES: THE CONCEPTUALIZON OF NEW PRODUCTS BASED ON DATA ANALYSIS AND THE ELABORATION OF TARGET RESEARCH; THE DESIGNING OF PROTOTYPES WITH PHYSICAL AND FINANCIAL VIABILITY; AND THE SYMBOLIC ASSOCIATION OF COMMODITIES TO VALUES, PUBLIC IMAGES AND SOCIAL GROUPES, WICH IS EMBODIED THROUGH THE ADVERTISEMENT.</t>
+          <t>HUMAN HISTORY IS PUNCTUATED BY TECHNOLOGICAL BREAKTHROUGHS, ACTING AS CATALYSTS FOR FOUNDATIONAL SHIFTS IN HOW SOCIETIES PERCEIVE AND ENGAGE WITH THEIR ENVIRONMENT. FROM THE INVENTION OF THE STEAM ENGINE, INITIATING THE FIRST INDUSTRIAL REVOLUTION, TO THE ADVANCEMENTS OF THE SO-CALLED 4.0 REVOLUTION, TECHNOLOGIES HAVE DEEPLY RESHAPED AND REDEFINED THE SOCIOECONOMIC FABRIC. WHEN EXAMINING THE IMPACT OF THESE INNOVATIONS, IT'S EVIDENT THAT THEY REPRESENT MORE THAN MERE TECHNICAL ADJUSTMENTS. THEY ENCOMPASS PROFOUND TRANSFORMATIONS THAT PERVADE ALL ASPECTS OF SOCIAL LIFE. SPECIFICALLY, ADVANCES IN ARTIFICIAL INTELLIGENCE (AI) NOT ONLY OFFER NEW TECHNICAL CAPABILITIES BUT ALSO PRESENT SIGNIFICANT CHALLENGES CONCERNING EMPLOYABILITY, ORGANIZATIONAL STRUCTURES, AND HUMAN INTERACTIONS. WITH ITS ADVANCED DATA PROCESSING, ANALYSIS, AND CONTENT GENERATION CAPABILITIES, AI IS REDEFINING THE WORKPLACE, OFTEN RENDERING TRADITIONAL HUMAN FUNCTIONS REDUNDANT. USING THE CESSATION OF THE OFFICIAL PRESS OF MINAS GERAIS AS A CASE STUDY, THIS DISSERTATION SEEKS TO UNDERSTAND THE REAL AND POTENTIAL RAMIFICATIONS OF SUCH TECHNOLOGICAL ADVANCEMENTS ON EMPLOYMENT. THE END OF THE CENTENNIAL TRAJECTORY OF PHYSICAL NEWSPAPER PRODUCTION AND PRINTING AT THE OFFICIAL PRESS NOT ONLY EXEMPLIFIES THE TRANSITION TO DIGITAL BUT ALSO UNDERSCORES THE RESULTANT SOCIAL REPERCUSSIONS. THE LAYOFF OF OVER 400 EMPLOYEES AND THE ELIMINATION OF ALL ASSOCIATED JOB ROLES SHOWCASES THE BREADTH OF THE IMPACT INNOVATIONS CAN HAVE ON TRADITIONAL SECTORS. BEYOND IDENTIFYING CHALLENGES, IT'S CRUCIAL TO DISCUSS THE OPPORTUNITIES THESE INNOVATIONS PRESENT. AI'S ABILITY TO COLLECT AND ANALYZE LARGE-SCALE DATA, FOR INSTANCE, OFFERS POTENTIAL TO ENHANCE EFFICIENCY, ACCURACY, AND CUSTOMIZATION ACROSS VARIOUS INDUSTRIES. YET, THE CENTRAL QUESTION REMAINS: HOW CAN SOCIETIES ADAPT TO THIS NEW REALITY, ENSURING TECHNOLOGICAL ADVANCEMENTS BENEFIT THE MANY, NOT JUST AN ELITE? HOW CAN A JUST TRANSITION FOR THOSE AFFECTED BY SUCH DISRUPTIVE SHIFTS BE ENSURED? IN CONCLUSION, THIS RESEARCH UNDERSCORES THE IMPORTANCE OF A BALANCED AND PROACTIVE APPROACH. WHILE ADVANCES IN AI AND TECHNOLOGY AT LARGE OFFER IMMENSE POSSIBILITIES, IT'S IMPERATIVE THAT SOCIETIES ARE PRIMED, WHETHER THROUGH RE-SKILLING POLICIES, SUPPORT SYSTEMS, OR EDUCATIONAL INNOVATIONS, TO ENSURE ALL CAN BENEFIT FROM THE 4.0 REVOLUTION ERA.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SOCIOLOGIA ECONÔMICA;MARKETING;INDÚSTRIA AUTOMOTIVA;CIÊNCIA DE DADOS;REDES DIGITAIS.</t>
+          <t>INTELIGÊNCIA ARTIFICIAL (IA);DIGITALIZAÇÃO;REVOLUÇÃO TECNOLÓGICA;EMPREGABILIDADE;IMPRENSA OFICIAL DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>ECONOMIC SOCIOLOGY;MARKETING;AUTOMOTIVE INDUSTRY;DATA SCIENCE;DIGITAL NETWORKS.</t>
+          <t>ARTIFICIAL INTELLIGENCE (AI);TECHNOLOGICAL REVOLUTIONS;DIGITALIZATION, EMPLOYABILITY;OFFICIAL PRESS OF MINAS GERAIS</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -9391,22 +9391,22 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>RODRIGO SALLES PEREIRA DOS SANTOS</t>
+          <t>DIOGO SILVA CORREA</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>SOCIOLOGIA E ANTROPOLOGIA</t>
+          <t>SOCIOLOGIA POLÍTICA</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DO RIO DE JANEIRO</t>
+          <t>UNIVERSIDADE VILA VELHA</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>UFRJ</t>
+          <t>UVV</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -9416,16 +9416,16 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>ESPÍRITO SANTO</t>
         </is>
       </c>
       <c r="Y64" t="n">
-        <v>145</v>
+        <v>98</v>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>OUTRAS SOCIOLOGIAS ESPECÍFICAS</t>
+          <t>NÃO SE APLICA</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -9444,16 +9444,16 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12879895</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14403191</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>12879895</t>
+          <t>14403191</t>
         </is>
       </c>
       <c r="AE64" t="n">
-        <v>3055993</v>
+        <v>1636325</v>
       </c>
     </row>
     <row r="65">
@@ -9472,37 +9472,37 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2023-03-07</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>BARBARA BRUNA DA TRINDADE GOMES</t>
+          <t>RAFAELA BUENO DA SILVA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>JUVENTUDES PRECARIZADAS NO CAPITALISMO DE PLATAFORMA E SEU POTENCIAL EXPLOSIVO</t>
+          <t>DISCURSOS PUNITIVOS EM REDES SOCIAIS: O FACEBOOK COMO MEIO DE CIRCULAÇÃO DA ‘FALA DO CRIME’ NO BRASIL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>O DESENVOLVIMENTO TECNOLÓGICO CONSTITUÍDO, SOBRETUDO, PELA NANOTECNOLOGIA, ROBÓTICA E TECNOLOGIA DA INFORMAÇÃO, TEM PROMOVIDO TRANSFORMAÇÕES SIGNIFICATIVAS NO MUNDO E NAS RELAÇÕES DE TRABALHO. ESPECIFICAMENTE NO BRASIL, ESSAS TRANSFORMAÇÕES FORAM ACENTUADAS A PARTIR DOS ANOS 90, COM A IMPLANTAÇÃO DAS POLÍTICAS NEOLIBERAIS DO GOVERNO COLLOR, GENERALIZANDO A PRECARIZAÇÃO E A FLEXIBILIZAÇÃO DO TRABALHO ATRAVÉS DO INCENTIVO DE CONTRATAÇÕES INFORMAIS E DESREGULAMENTADAS. HOJE, OS NOVOS CONTORNOS, ORGANIZAÇÃO E GESTÃO QUE VEM SE CONFIGURANDO NO MERCADO DE TRABALHO, ESTÃO SE TORNANDO MAIS RECONHECÍVEIS ATRAVÉS DO TRABALHO MEDIADO PELAS PLATAFORMAS DIGITAIS. NOS ÚLTIMOS ANOS, O CENÁRIO DAS CIDADES BRASILEIRAS PASSOU A CONTAR COM A FIGURA DOS ENTREGADORES POR APLICATIVO, NOTADAMENTE A PARTIR DE 2020 HOUVE UMA MAIOR PROLIFERAÇÃO DA CATEGORIA, EM VIRTUDE DA PANDEMIA DO VÍRUS COVID19, UMA VEZ QUE, COM A IMPOSSIBILIDADE DA LIVRE CIRCULAÇÃO DE PESSOAS, O SERVIÇO DE DELIVERY PASSOU A SER A ALTERNATIVA MAIS UTILIZADA COMO FORMA DE CONTINUIDADE DE PARCELA DO COMÉRCIO. NESSE SENTIDO, A PRESENTE DISSERTAÇÃO BUSCOU IDENTIFICAR A SITUAÇÃO DAS JUVENTUDES PRECARIZADAS QUE PRESTAM SERVIÇO POR DEMANDA DE APLICATIVO, ANALISANDO AS PECULIARIDADES DESSA FRAÇÃO DE TRABALHADORES, BEM COMO SEU POTENCIAL EXPLOSIVO PARA RESISTIR E REIVINDICAR. VERIFICOU-SE A PARTIR DA ANÁLISE E ESTUDOS DOS DADOS QUE ESSES JOVENS EM SUA MAIORIA SÃO PRETOS, POBRES E COM BAIXA ESCOLARIDADE. ALÉM DISSO, FOI CONSTATADO QUE APESAR DE FRAGILIZADA, ESSAS JUVENTUDES FAZEM PARTE DA FRAÇÃO DA CLASSE TRABALHADORA QUE TEM UM POTENCIAL DE TRANSFORMAÇÃO QUANDO SE PENSA EM LUTAR POR MELHORES CONDIÇÕES DE TRABALHO, BASTA OLHAR AS MANIFESTAÇÕES AO REDOR DO MUNDO E NO BRASIL, COMO EXEMPLO O BREQUE DOS APPS. CONTUDO, APESAR DE LUTAREM POR MELHORES CONDIÇÕES, AINDA NÃO EXISTE UM CONSENSO QUANDO SE TRATA DE TER VÍNCULOS EMPREGATÍCIOS E UM TRABALHO REGULAMENTADO, NOS MOLDES DA CLT.</t>
+          <t>ESTE ESTUDO TEM COMO OBJETIVO IDENTIFICAR E ANALISAR VOCABULÁRIOS E ENUNCIADOS EMITIDOS PELOS INTERNAUTAS BRASILEIROS NA REDE SOCIAL DIGITAL FACEBOOK A FIM DE COMPREENDER A PRODUÇÃO E A CIRCULAÇÃO DOS DISCURSOS SOBRE A PUNIÇÃO EM UM AMBIENTE DE MÍDIA COM UMA DINÂMICA DE FUNCIONAMENTO PRÓPRIA QUE É A INTERNET E, MAIS PRECISAMENTE, AS REDES SOCIAIS DIGITAIS. A PARTIR DA ANÁLISE DE UM CASO ESPECÍFICO - O DO SUPERMERCADO RICOY, NO QUAL UM ADOLESCENTE NEGRO FOI AMARRADO E CHICOTEADO PELOS SEGURANÇAS DO ESTABELECIMENTO; E TAMBÉM DE UM RECORTE ESPECÍFICO DE EMISSORES - O DAS PÁGINAS DOS VEÍCULOS DE COMUNICAÇÃO G1 E O R7, PERTENCENTES A DOIS DOS PRINCIPAIS CONGLOMERADOS DE MÍDIA DO BRASIL. FORAM ANALISADOS OS COMENTÁRIOS DOS INTERNAUTAS EM UMA COMBINAÇÃO DE MÉTODOS QUANTITATIVOS, COM O USO DE TÉCNICAS DE PROCESSAMENTO DE LINGUAGEM NATURAL, E QUALITATIVOS, VALENDO-SE DOS ESTUDOS DE MICHEL FOUCAULT SOBRE DISCURSO. COM ESTA COMBINAÇÃO METODOLÓGICA, FOI POSSÍVEL ANALISAR A EMERGÊNCIA DE UM DISCURSO QUE FORMA SUJEITOS, OBJETOS E ESTRATÉGIAS PARA LIDAR COM O CRIME, A CRIMINALIDADE E A VIOLÊNCIA URBANA – O QUE HAVIA SIDO IDENTIFICADO COMO ‘FALA DO CRIME’ POR TERESA CALDEIRA NO FINAL DA DÉCADA DE 1990. A DESCONTINUIDADE AQUI SE DÁ PRINCIPALMENTE PELO REGISTRO DAS FALAS EM UM AMBIENTE PÚBLICO, COM A ACELERAÇÃO DE TROCAS E DE INTERAÇÕES E A ELIMINAÇÃO DAS LIMITAÇÕES GEOGRÁFICAS. ALÉM DISSO, NOTA-SE UMA FORTE PRESENÇA DE UM CONTRADISCURSO NEUTRO OU NÃO PUNITIVISTA, QUE COLOCA EM CONFRONTO DIRETO OUTRAS PERSPECTIVAS SOBRE O SUJEITO CRIMINOSO, A LEGITIMIDADE DAS INSTITUIÇÕES E ABRE NOVAS PERSPECTIVAS SOBRE UMA SOCIEDADE DEMOCRÁTICA E UMA VISÃO UNIVERSAL DE CIDADANIA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>TECHNOLOGICAL DEVELOPMENT, CONSISTING MAINLY OF NANOTECHNOLOGY, ROBOTICS AND INFORMATION TECHNOLOGY, HAS PROMOTED SIGNIFICANT CHANGES IN THE WORLD AND IN LABOR RELATIONS. SPECIFICALLY IN BRAZIL, THESE TRANSFORMATIONS WERE ACCENTUATED FROM THE 1990S ONWARDS, WITH THE IMPLEMENTATION OF THE COLLOR GOVERNMENT'S NEOLIBERAL POLICIES, GENERALIZING MEASURES OF A LIBERAL NATURE FOR HIRING WORKERS IN WAYS THAT WERE BELOW WHAT WAS ESTABLISHED BY THE CLT. TODAY, THE NEW CONTOURS, ORGANIZATION AND MANAGEMENT THAT HAVE BEEN TAKING SHAPE IN THE LABOR MARKET ARE BECOMING MORE RECOGNIZABLE THROUGH WORK MEDIATED BY DIGITAL PLATFORMS. IN RECENT YEARS, THE SCENARIO OF BRAZILIAN CITIES HAS COME TO RELY ON THE FIGURE OF COURIERS BY APP, NOTABLY FROM 2020 THERE HAS BEEN A GREATER PROLIFERATION OF THE CATEGORY, DUE TO THE COVID19 VIRUS PANDEMIC, SINCE, WITH THE IMPOSSIBILITY OF FREE MOVEMENT OF PEOPLE, THE DELIVERY SERVICE HAS BECOME THE MOST USED ALTERNATIVE AS A WAY OF CONTINUING A PORTION OF TRADE. IN THIS SENSE, THIS DISSERTATION PROPOSES TO ANALYZE THE SITUATION OF PRECARIOUS YOUTHS WHO PROVIDE SERVICES BY APPLICATION DEMAND, SEEKING TO UNDERSTAND THE PECULIARITIES OF THIS FRACTION OF WORKERS, AS WELL AS THEIR EXPLOSIVE POTENTIAL TO RESIST AND CLAIM. IT WAS VERIFIED FROM THE ANALYSIS AND STUDIES OF THE DATA THAT THESE YOUNG PEOPLE ARE MOSTLY BLACK, POOR AND WITH LOW EDUCATION. IN ADDITION, IT WAS FOUND THAT DESPITE BEING FRAGILE, THESE YOUTHS ARE PART OF THE FRACTION OF THE WORKING CLASS THAT HAS A POTENTIAL FOR TRANSFORMATION WHEN THINKING ABOUT FIGHTING FOR BETTER CONDITIONS, JUST LOOK AT THE DEMONSTRATIONS AROUND THE WORLD AND IN BRAZIL, AS AN EXAMPLE OF THE BREQUE OF APPS. HOWEVER, DESPITE FIGHTING FOR BETTER CONDITIONS, THERE IS STILL NO CONSENSUS WHEN IT COMES TO HAVING LINKS WITH THE CLT.</t>
+          <t>THIS STUDY AIMS TO IDENTIFY AND ANALYZE VOCABULARIES AND STATEMENTS WRITTEN BY BRAZILIAN INTERNET USERS ON THE DIGITAL NETWORK FACEBOOK TO UNDERSTAND THE PRODUCTION AND CIRCULATION OF DISCOURSES ON PUNISHMENT IN A MEDIA ENVIRONMENT WITH A VERY SPECIFIC OPERATING DYNAMIC THAT IT IS INTERNET AND, MORE PRECISELY, THE SOCIAL NETWORKS. BASED ON THE ANALYSIS OF A SPECIFIC CASE, THE RICOY SUPERMARKET ONE, WHERE A BLACK TEENAGER WAS TIED UP AND WHIPPED BY THE ESTABLISHMENT'S SECURITY GUARDS, AND ALSO ON A SPECIFIC SET OF MEDIA, THE FACEBOOK PAGE OF THE COMMUNICATION VEHICLES G1 AND R7 THAT BELONG TO TWO OF THE MAIN MEDIA CONGLOMERATES IN BRAZIL, THE COMMENTS OF INTERNET USERS WERE ANALYZED USING A COMBINATION OF QUANTITATIVE METHODS, USING NATURAL LANGUAGE PROCESSING TECHNIQUES, AND QUALITATIVE METHODS, USING MICHEL FOUCAULT’S PERSPECTIVE OF DISCURSIVE ANALYSIS. THROUGH THIS METHODOLOGICAL APPROACH, IT WAS POSSIBLE TO ANALYZE THE EMERGENCE OF A DISCOURSE THAT FORMS SUBJECTS, OBJECTS, AND STRATEGIES TO DEAL WITH CRIME, CRIMINALITY, AND URBAN VIOLENCE – WHICH HAD ALREADY BEEN IDENTIFIED AS 'TALK OF CRIME' AT THE END OF THE 1990’S DECADE BY TERESA CALDEIRA. THE DISCURSIVE DISCONTINUITY HERE IS ENABLED BY THE INTERNET SPECIFICITIES: THE RECORDING OF SPEECHES IN A PUBLIC ENVIRONMENT, WITH THE ACCELERATION OF EXCHANGES AND INTERACTIONS AND THE ELIMINATION OF GEOGRAPHIC LIMITATIONS. IN ADDITION, THERE IS A STRONG PRESENCE OF A NEUTRAL OR NON-PUNITIVIST COUNTER-DISCOURSE THAT DIRECTLY CONFRONTS OTHER PERSPECTIVES ON THE CRIMINAL SUBJECT, THE LEGITIMACY OF INSTITUTIONS AND OPENS NEW PERSPECTIVES ON A DEMOCRATIC SOCIETY AND AN UNIVERSAL VISION OF CITIZENSHIP.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO TECNOLÓGICO;PLATAFORMAS DIGITAIS;ENTREGADORES POR APLICATIVO;BREQUE DOS APPS</t>
+          <t>FALA DO CRIME;DISCURSO PUNITIVISTA;PUNIÇÃO;REDES SOCIAIS DIGITAIS</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>TECHNOLOGICAL DEVELOPMENT;DIGITAL PLATFORMS;COURIERS BY APPLICATION;APPS BREAK.</t>
+          <t>TALK OF CRIME;PUNITIVE SPEECH;PUNISHMENT;DIGITAL NETWORKS</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -9532,41 +9532,41 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>GONZALO ADRIAN ROJAS</t>
+          <t>MARCOS CESAR ALVAREZ</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>CIÊNCIAS SOCIAIS</t>
+          <t>SOCIOLOGIA</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DE CAMPINA GRANDE</t>
+          <t>UNIVERSIDADE DE SÃO PAULO</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>UFCG</t>
+          <t>USP</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>NORDESTE</t>
+          <t>SUDESTE</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>PARAÍBA</t>
+          <t>SÃO PAULO</t>
         </is>
       </c>
       <c r="Y65" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
@@ -9585,16 +9585,16 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=12825916</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13882903</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>12825916</t>
+          <t>13882903</t>
         </is>
       </c>
       <c r="AE65" t="n">
-        <v>3876753</v>
+        <v>564924</v>
       </c>
     </row>
     <row r="66">
@@ -9609,41 +9609,41 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>GUSTAVO DANIEL PRADO</t>
+          <t>ADRIANA NUNES DE SOUZA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>DESAFIOS DA EMPREGABILIDADE ANTE O AVANÇO DA INTELIGÊNCIA ARTIFICIAL: O CASO IMPRENSA OFICIAL DE MG</t>
+          <t>VISIBILIDADE SURREAL: GÊNERO, MUNDOS DIGITAIS E NARRATIVAS DA VANGUARDA SURREALISTA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>A HISTÓRIA DA HUMANIDADE É MARCADA POR INOVAÇÕES TECNOLÓGICAS, SERVINDO COMO CATALISADORES DE MUDANÇAS FUNDAMENTAIS NA FORMA COMO SOCIEDADES PERCEBEM E INTERAGEM COM O MUNDO. ATRAVÉS DAS ERAS, DESDE A INVENÇÃO DA MÁQUINA A VAPOR, QUE INICIOU A PRIMEIRA REVOLUÇÃO INDUSTRIAL, ATÉ OS AVANÇOS CONTEMPORÂNEOS DA CHAMADA REVOLUÇÃO 4.0, TECNOLOGIAS TÊM MOLDADO E REDEFINIDO O TECIDO SOCIOECONÔMICO DE MANEIRA PROFUNDA. AO EXAMINAR O IMPACTO DESSAS INOVAÇÕES, TORNA-SE EVIDENTE QUE NÃO SÃO MERAS ALTERAÇÕES TÉCNICAS, MAS SIM TRANSFORMAÇÕES QUE PERMEIAM TODOS OS ASPECTOS DA VIDA SOCIAL. ESSES AVANÇOS, PARTICULARMENTE NA ESFERA DA INTELIGÊNCIA ARTIFICIAL (IA), NÃO APENAS OFERECEM NOVAS CAPACIDADES TÉCNICAS, MAS TAMBÉM APRESENTAM DESAFIOS SIGNIFICATIVOS NO QUE DIZ RESPEITO À EMPREGABILIDADE, ESTRUTURAS ORGANIZACIONAIS E INTERAÇÕES HUMANAS. A IA, COM SUAS CAPACIDADES AVANÇADAS DE PROCESSAMENTO DE DADOS, ANÁLISE E GERAÇÃO DE CONTEÚDO, ESTÁ REDEFININDO O AMBIENTE DE TRABALHO, MUITAS VEZES TORNANDO FUNÇÕES TRADICIONAIS HUMANAS REDUNDANTES. TOMANDO A EXTINÇÃO DA IMPRENSA OFICIAL DE MINAS GERAIS COMO ESTUDO DE CASO, ESTA DISSERTAÇÃO BUSCA COMPREENDER AS RAMIFICAÇÕES REAIS E POTENCIAIS DOS AVANÇOS TECNOLÓGICOS SOBRE O EMPREGO. O FIM DA TRAJETÓRIA CENTENÁRIA DE PRODUÇÃO E IMPRESSÃO DO JORNAL FÍSICO NA IMPRENSA OFICIAL NÃO SÓ EXEMPLIFICA A TRANSIÇÃO PARA O DIGITAL, COMO DESTACA AS CONSEQUÊNCIAS SOCIAIS RESULTANTES. O DESLIGAMENTO DE MAIS DE 400 COLABORADORES E A ELIMINAÇÃO DE TODOS OS POSTOS DE TRABALHO ASSOCIADOS MOSTRAM A AMPLITUDE DO IMPACTO QUE INOVAÇÕES PODEM TER SOBRE SETORES TRADICIONAIS. ALÉM DE IDENTIFICAR OS DESAFIOS, É CRUCIAL ABORDAR AS OPORTUNIDADES QUE TAIS INOVAÇÕES APRESENTAM. A CAPACIDADE DA IA DE COLETAR E ANALISAR DADOS EM GRANDE ESCALA, POR EXEMPLO, OFERECE POTENCIAL PARA MELHORAR A EFICIÊNCIA, A PRECISÃO E A PERSONALIZAÇÃO EM VÁRIAS INDÚSTRIAS. NO ENTANTO, A QUESTÃO CENTRAL PERMANECE: COMO AS SOCIEDADES PODEM SE ADAPTAR A ESSA NOVA REALIDADE, GARANTINDO QUE OS AVANÇOS TECNOLÓGICOS BENEFICIEM A MAIORIA, E NÃO APENAS UMA ELITE? COMO PODEMOS ASSEGURAR UMA TRANSIÇÃO JUSTA PARA AQUELES AFETADOS POR MUDANÇAS TÃO DISRUPTIVAS? AO FINAL, ESTA PESQUISA DESTACA A IMPORTÂNCIA DE UMA ABORDAGEM EQUILIBRADA E PROATIVA. ENQUANTO OS AVANÇOS NA IA E NA TECNOLOGIA EM GERAL OFERECEM POSSIBILIDADES INCRÍVEIS, É FUNDAMENTAL QUE AS SOCIEDADES ESTEJAM PREPARADAS, SEJA POR MEIO DE POLÍTICAS DE REQUALIFICAÇÃO, SISTEMAS DE APOIO OU INOVAÇÕES EDUCACIONAIS, PARA GARANTIR QUE TODOS POSSAM SE BENEFICIAR DA ERA DA REVOLUÇÃO 4.0.</t>
+          <t>NESTA OBRA, INVESTIGA-SE A RELEVÂNCIA DO SURREALISMO POR MEIO DE UMA ECOLOGIA DE MATERIAIS QUE VÃO DESDE OBRAS DE ARTE ATÉ ESBOÇOS E TEORIAS FEMINISTAS. TEMAS COMO SUBJETIVIDADE, REPRESENTAÇÃO FEMININA E A INTERSEÇÃO ENTRE TECNOLOGIA E IDENTIDADE EXPANDEM O DEBATE PARA ABARCAR A EXTENSÃO DA INTELIGÊNCIA ARTIFICIAL NO ANTROPOCENO, RESSALTANDO A IMPERATIVIDADE DE UMA ABORDAGEM ÉTICA COM OLHAR CIBORGUE. A DINÂMICA DAS REDES SOCIAIS, NA QUAL OS USUÁRIOS DESEMPENHAM PAPÉIS HÍBRIDOS DE PRODUTORES E CONSUMIDORES, CONTRIBUI PARA UMA CULTURA DE INCESSANTE ESPETACULARIZAÇÃO. LOGO, DÁ-SE ÊNFASE À ESTETIZAÇÃO DO COTIDIANO, EXPLORANDO A CIBERFLÂNERIE E A PARTICIPAÇÃO, TANTO CONSCIENTE QUANTO INCONSCIENTE, DOS INDIVÍDUOS NAS PERSONALIZAÇÕES ALGORÍTMICAS. A ESTÉTICA INSTAGRAMÁVEL É CONTRASTADA COM O SURREALISMO E JUNTAS CASAM O GROTESCO COM A GRAÇA, DESAFIANDO AS NORMAS EMOCIONAIS E DESTACANDO A IMPORTÂNCIA DO INSTAGRAM NA ESTILIZAÇÃO E NA FORMAÇÃO DE IDENTIDADES ESTÉTICAS. A CONTRIBUIÇÃO DESTE ESTUDO RESIDE NA ANÁLISE DO SURREALISMO COMO MOVIMENTO ARTÍSTICO E POLÍTICO, ALÉM DA EXPLORAÇÃO DAS POSSÍVEIS CONTINUIDADES DESSE MOVIMENTO NA CULTURA VISUAL DO INSTAGRAM. AS INSTÂNCIAS EMPÍRICAS ENGLOBAM ESTUDOS DE CASO DE ARTISTAS, ANÁLISES DE HASHTAGS E REFLEXÕES SOBRE ESTÉTICA, ALIANDO-SE ÀS ESCOLHAS METODOLÓGICAS QUE PRIVILEGIAM A AUTOETNOGRAFIA E UMA ABORDAGEM NÃO LINEAR NA ORGANIZAÇÃO DOS CAPÍTULOS, ALMEJANDO EXPANDIR A COMPREENSÃO DO SURREALISMO E SUAS RAMIFICAÇÕES.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>HUMAN HISTORY IS PUNCTUATED BY TECHNOLOGICAL BREAKTHROUGHS, ACTING AS CATALYSTS FOR FOUNDATIONAL SHIFTS IN HOW SOCIETIES PERCEIVE AND ENGAGE WITH THEIR ENVIRONMENT. FROM THE INVENTION OF THE STEAM ENGINE, INITIATING THE FIRST INDUSTRIAL REVOLUTION, TO THE ADVANCEMENTS OF THE SO-CALLED 4.0 REVOLUTION, TECHNOLOGIES HAVE DEEPLY RESHAPED AND REDEFINED THE SOCIOECONOMIC FABRIC. WHEN EXAMINING THE IMPACT OF THESE INNOVATIONS, IT'S EVIDENT THAT THEY REPRESENT MORE THAN MERE TECHNICAL ADJUSTMENTS. THEY ENCOMPASS PROFOUND TRANSFORMATIONS THAT PERVADE ALL ASPECTS OF SOCIAL LIFE. SPECIFICALLY, ADVANCES IN ARTIFICIAL INTELLIGENCE (AI) NOT ONLY OFFER NEW TECHNICAL CAPABILITIES BUT ALSO PRESENT SIGNIFICANT CHALLENGES CONCERNING EMPLOYABILITY, ORGANIZATIONAL STRUCTURES, AND HUMAN INTERACTIONS. WITH ITS ADVANCED DATA PROCESSING, ANALYSIS, AND CONTENT GENERATION CAPABILITIES, AI IS REDEFINING THE WORKPLACE, OFTEN RENDERING TRADITIONAL HUMAN FUNCTIONS REDUNDANT. USING THE CESSATION OF THE OFFICIAL PRESS OF MINAS GERAIS AS A CASE STUDY, THIS DISSERTATION SEEKS TO UNDERSTAND THE REAL AND POTENTIAL RAMIFICATIONS OF SUCH TECHNOLOGICAL ADVANCEMENTS ON EMPLOYMENT. THE END OF THE CENTENNIAL TRAJECTORY OF PHYSICAL NEWSPAPER PRODUCTION AND PRINTING AT THE OFFICIAL PRESS NOT ONLY EXEMPLIFIES THE TRANSITION TO DIGITAL BUT ALSO UNDERSCORES THE RESULTANT SOCIAL REPERCUSSIONS. THE LAYOFF OF OVER 400 EMPLOYEES AND THE ELIMINATION OF ALL ASSOCIATED JOB ROLES SHOWCASES THE BREADTH OF THE IMPACT INNOVATIONS CAN HAVE ON TRADITIONAL SECTORS. BEYOND IDENTIFYING CHALLENGES, IT'S CRUCIAL TO DISCUSS THE OPPORTUNITIES THESE INNOVATIONS PRESENT. AI'S ABILITY TO COLLECT AND ANALYZE LARGE-SCALE DATA, FOR INSTANCE, OFFERS POTENTIAL TO ENHANCE EFFICIENCY, ACCURACY, AND CUSTOMIZATION ACROSS VARIOUS INDUSTRIES. YET, THE CENTRAL QUESTION REMAINS: HOW CAN SOCIETIES ADAPT TO THIS NEW REALITY, ENSURING TECHNOLOGICAL ADVANCEMENTS BENEFIT THE MANY, NOT JUST AN ELITE? HOW CAN A JUST TRANSITION FOR THOSE AFFECTED BY SUCH DISRUPTIVE SHIFTS BE ENSURED? IN CONCLUSION, THIS RESEARCH UNDERSCORES THE IMPORTANCE OF A BALANCED AND PROACTIVE APPROACH. WHILE ADVANCES IN AI AND TECHNOLOGY AT LARGE OFFER IMMENSE POSSIBILITIES, IT'S IMPERATIVE THAT SOCIETIES ARE PRIMED, WHETHER THROUGH RE-SKILLING POLICIES, SUPPORT SYSTEMS, OR EDUCATIONAL INNOVATIONS, TO ENSURE ALL CAN BENEFIT FROM THE 4.0 REVOLUTION ERA.</t>
+          <t>IN THIS WORK, THE RELEVANCE OF SURREALISM IS INVESTIGATED THROUGH AN ECOLOGY OF MATERIALS RANGING FROM WORKS OF ART TO SKETCHES AND FEMINIST THEORIES. THEMES SUCH AS SUBJECTIVITY, FEMALE REPRESENTATION AND THE INTERSECTION BETWEEN TECHNOLOGY AND IDENTITY EXPAND THE DEBATE TO ENCOMPASS THE EXTENT OF ARTIFICIAL INTELLIGENCE IN THE ANTHROPOCENE, HIGHLIGHTING THE IMPERATIVE OF AN ETHICAL APPROACH WITH A CYBORG PERSPECTIVE. THE DYNAMICS OF SOCIAL NETWORKS, IN WHICH USERS PLAY HYBRID ROLES OF PRODUCERS AND CONSUMERS, CONTRIBUTES TO A CULTURE OF INCESSANT SPECTACULARIZATION. THEREFORE, EMPHASIS IS PLACED ON THE AESTHETICIZATION OF EVERYDAY LIFE, EXPLORING CYBER-FLÂNERIE AND THE PARTICIPATION, BOTH CONSCIOUS AND UNCONSCIOUS, OF INDIVIDUALS IN ALGORITHMIC PERSONALIZATIONS. INSTAGRAMMABLE AESTHETICS ARE CONTRASTED WITH SURREALISM AND TOGETHER THEY MARRY THE GROTESQUE WITH GRACE, CHALLENGING EMOTIONAL NORMS AND HIGHLIGHTING THE IMPORTANCE OF INSTAGRAM IN STYLIZATION AND THE FORMATION OF AESTHETIC IDENTITIES. THE CONTRIBUTION OF THIS STUDY LIES IN THE ANALYSIS OF SURREALISM AS AN ARTISTIC AND POLITICAL MOVEMENT, IN ADDITION TO EXPLORING THE POSSIBLE CONTINUITIES OF THIS MOVEMENT IN THE VISUAL CULTURE OF INSTAGRAM. THE EMPIRICAL INSTANCES INCLUDE CASE STUDIES OF ARTISTS, HASHTAG ANALYSIS AND REFLECTIONS ON AESTHETICS, COMBINED WITH METHODOLOGICAL CHOICES THAT FAVOR AUTOETHNOGRAPHY AND A NON-LINEAR APPROACH IN ORGANIZING THE CHAPTERS, AIMING TO EXPAND THE UNDERSTANDING OF SURREALISM AND ITS RAMIFICATIONS.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>INTELIGÊNCIA ARTIFICIAL (IA);DIGITALIZAÇÃO;REVOLUÇÃO TECNOLÓGICA;EMPREGABILIDADE;IMPRENSA OFICIAL DE MINAS GERAIS</t>
+          <t>SURREALISMO;SUBJETIVIDADE;REPRESENTAÇÃO FEMININA;INSTAGRAM;AUTOETNOGRAFIA.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>ARTIFICIAL INTELLIGENCE (AI);TECHNOLOGICAL REVOLUTIONS;DIGITALIZATION, EMPLOYABILITY;OFFICIAL PRESS OF MINAS GERAIS</t>
+          <t>SURREALISM;SUBJECTIVITY;FEMALE REPRESENTATION;INSTAGRAM;AUTOETHNOGRAPHY</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -9673,22 +9673,22 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>DIOGO SILVA CORREA</t>
+          <t>PATRICIA REINHEIMER</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>SOCIOLOGIA POLÍTICA</t>
+          <t>CIÊNCIAS SOCIAIS</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE VILA VELHA</t>
+          <t>UNIVERSIDADE FEDERAL RURAL DO RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>UVV</t>
+          <t>UFRRJ</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -9698,16 +9698,16 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>ESPÍRITO SANTO</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="Y66" t="n">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
@@ -9726,16 +9726,16 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=14403191</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15526518</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>14403191</t>
+          <t>15526518</t>
         </is>
       </c>
       <c r="AE66" t="n">
-        <v>1636325</v>
+        <v>4121197</v>
       </c>
     </row>
     <row r="67">
@@ -9750,55 +9750,55 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RAFAELA BUENO DA SILVA</t>
+          <t>BERNARDO MARTINHO BALLARDIN</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>DISCURSOS PUNITIVOS EM REDES SOCIAIS: O FACEBOOK COMO MEIO DE CIRCULAÇÃO DA ‘FALA DO CRIME’ NO BRASIL</t>
+          <t>"PARA ALÉM DA UBERIZAÇÃO: UMA INVESTIGAÇÃO DO TRABALHO DOCENTE NAS PLATAFORMAS DE AULAS PARTICULARES PROFES E SUPERPROF A PARTIR DOS PARADIGMAS DA PLATAFORMIZAÇÃO E DA ECONOMIA REPUTACIONAL"</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ESTE ESTUDO TEM COMO OBJETIVO IDENTIFICAR E ANALISAR VOCABULÁRIOS E ENUNCIADOS EMITIDOS PELOS INTERNAUTAS BRASILEIROS NA REDE SOCIAL DIGITAL FACEBOOK A FIM DE COMPREENDER A PRODUÇÃO E A CIRCULAÇÃO DOS DISCURSOS SOBRE A PUNIÇÃO EM UM AMBIENTE DE MÍDIA COM UMA DINÂMICA DE FUNCIONAMENTO PRÓPRIA QUE É A INTERNET E, MAIS PRECISAMENTE, AS REDES SOCIAIS DIGITAIS. A PARTIR DA ANÁLISE DE UM CASO ESPECÍFICO - O DO SUPERMERCADO RICOY, NO QUAL UM ADOLESCENTE NEGRO FOI AMARRADO E CHICOTEADO PELOS SEGURANÇAS DO ESTABELECIMENTO; E TAMBÉM DE UM RECORTE ESPECÍFICO DE EMISSORES - O DAS PÁGINAS DOS VEÍCULOS DE COMUNICAÇÃO G1 E O R7, PERTENCENTES A DOIS DOS PRINCIPAIS CONGLOMERADOS DE MÍDIA DO BRASIL. FORAM ANALISADOS OS COMENTÁRIOS DOS INTERNAUTAS EM UMA COMBINAÇÃO DE MÉTODOS QUANTITATIVOS, COM O USO DE TÉCNICAS DE PROCESSAMENTO DE LINGUAGEM NATURAL, E QUALITATIVOS, VALENDO-SE DOS ESTUDOS DE MICHEL FOUCAULT SOBRE DISCURSO. COM ESTA COMBINAÇÃO METODOLÓGICA, FOI POSSÍVEL ANALISAR A EMERGÊNCIA DE UM DISCURSO QUE FORMA SUJEITOS, OBJETOS E ESTRATÉGIAS PARA LIDAR COM O CRIME, A CRIMINALIDADE E A VIOLÊNCIA URBANA – O QUE HAVIA SIDO IDENTIFICADO COMO ‘FALA DO CRIME’ POR TERESA CALDEIRA NO FINAL DA DÉCADA DE 1990. A DESCONTINUIDADE AQUI SE DÁ PRINCIPALMENTE PELO REGISTRO DAS FALAS EM UM AMBIENTE PÚBLICO, COM A ACELERAÇÃO DE TROCAS E DE INTERAÇÕES E A ELIMINAÇÃO DAS LIMITAÇÕES GEOGRÁFICAS. ALÉM DISSO, NOTA-SE UMA FORTE PRESENÇA DE UM CONTRADISCURSO NEUTRO OU NÃO PUNITIVISTA, QUE COLOCA EM CONFRONTO DIRETO OUTRAS PERSPECTIVAS SOBRE O SUJEITO CRIMINOSO, A LEGITIMIDADE DAS INSTITUIÇÕES E ABRE NOVAS PERSPECTIVAS SOBRE UMA SOCIEDADE DEMOCRÁTICA E UMA VISÃO UNIVERSAL DE CIDADANIA</t>
+          <t>A PRESENTE DISSERTAÇÃO TEM POR OBJETIVO ANALISAR AS CONDIÇÕES DE CIRCULAÇÃO E REALIZAÇÃO DO TRABALHO NAS PLATAFORMAS DE AULAS PARTICULARES SUPERPROF E PROFES, AMBAS ATUANDO NO BRASIL, BEM COMO AS PERCEPÇÕES DOS DOCENTES SOBRE TAIS CONDIÇÕES. TAL ANÁLISE SE FUNDAMENTA EM TRÊS PARADIGMAS TEÓRICOS, A SABER, AS NOÇÕES – E OS DEBATES INERENTES A ELAS – DE ECONOMIA REPUTACIONAL, PLATAFORMIZAÇÃO E PLATAFORMIZAÇÃO DO TRABALHO. PARA ISSO, A PESQUISA SE VALE DE METODOLOGIAS DE RASPAGEM E ANÁLISE DE DADOS QUANTITATIVOS EM LARGA ESCALA, BEM COMO DE ENTREVISTAS SEMI-DIRETIVAS COM PROFESSORES ATUANDO NAS DUAS PLATAFORMAS. A PARTIR DESSAS, LEVANTA ELEMENTOS PARA O ENTENDIMENTO DA ESPECIFICIDADE DO TRABALHO DOCENTE DE AULAS PARTICULARES, BEM COMO PARA SUAS CARACTERÍSTICAS E ARTICULAÇÕES EM RELAÇÃO AO SEU PAR ANALÓGICO. TRAZ SUBSÍDIOS, TAMBÉM, PARA A REFLEXÃO ACERCA DA INFLUÊNCIA DE MECANISMOS DE INTELIGÊNCIA ARTIFICIAL NA CONSTITUIÇÃO DE MERCADOS DE TRABALHO, EM GERAL, E DO MERCADO DE TRABALHO DE AULAS PARTICULARES, ESPECIFICAMENTE, PROPONDO, COM ISSO, UM DEBATE SOBRE AS INTERSECÇÕES ENTRE AS PRÁTICAS DAS EMPRESAS-PLATAFORMA E AS CONDIÇÕES DE CIRCULAÇÃO DO TRABALHO NESSES CONTEXTOS.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>THIS STUDY AIMS TO IDENTIFY AND ANALYZE VOCABULARIES AND STATEMENTS WRITTEN BY BRAZILIAN INTERNET USERS ON THE DIGITAL NETWORK FACEBOOK TO UNDERSTAND THE PRODUCTION AND CIRCULATION OF DISCOURSES ON PUNISHMENT IN A MEDIA ENVIRONMENT WITH A VERY SPECIFIC OPERATING DYNAMIC THAT IT IS INTERNET AND, MORE PRECISELY, THE SOCIAL NETWORKS. BASED ON THE ANALYSIS OF A SPECIFIC CASE, THE RICOY SUPERMARKET ONE, WHERE A BLACK TEENAGER WAS TIED UP AND WHIPPED BY THE ESTABLISHMENT'S SECURITY GUARDS, AND ALSO ON A SPECIFIC SET OF MEDIA, THE FACEBOOK PAGE OF THE COMMUNICATION VEHICLES G1 AND R7 THAT BELONG TO TWO OF THE MAIN MEDIA CONGLOMERATES IN BRAZIL, THE COMMENTS OF INTERNET USERS WERE ANALYZED USING A COMBINATION OF QUANTITATIVE METHODS, USING NATURAL LANGUAGE PROCESSING TECHNIQUES, AND QUALITATIVE METHODS, USING MICHEL FOUCAULT’S PERSPECTIVE OF DISCURSIVE ANALYSIS. THROUGH THIS METHODOLOGICAL APPROACH, IT WAS POSSIBLE TO ANALYZE THE EMERGENCE OF A DISCOURSE THAT FORMS SUBJECTS, OBJECTS, AND STRATEGIES TO DEAL WITH CRIME, CRIMINALITY, AND URBAN VIOLENCE – WHICH HAD ALREADY BEEN IDENTIFIED AS 'TALK OF CRIME' AT THE END OF THE 1990’S DECADE BY TERESA CALDEIRA. THE DISCURSIVE DISCONTINUITY HERE IS ENABLED BY THE INTERNET SPECIFICITIES: THE RECORDING OF SPEECHES IN A PUBLIC ENVIRONMENT, WITH THE ACCELERATION OF EXCHANGES AND INTERACTIONS AND THE ELIMINATION OF GEOGRAPHIC LIMITATIONS. IN ADDITION, THERE IS A STRONG PRESENCE OF A NEUTRAL OR NON-PUNITIVIST COUNTER-DISCOURSE THAT DIRECTLY CONFRONTS OTHER PERSPECTIVES ON THE CRIMINAL SUBJECT, THE LEGITIMACY OF INSTITUTIONS AND OPENS NEW PERSPECTIVES ON A DEMOCRATIC SOCIETY AND AN UNIVERSAL VISION OF CITIZENSHIP.</t>
+          <t>THIS DISSERTATION AIMS TO ANALYZE THE CONDITIONS OF CIRCULATION AND REALIZATION OF I WORK ON THE PRIVATE TUTORING PLATFORMS SUPERPROF AND PROFES, BOTH ACTIVE IN BRAZIL, AS WELL AS TEACHERS' PERCEPTIONS ABOUT SUCH CONDITIONS. THIS ANALYSIS IS BASED ON THREE THEORETICAL PARADIGMS, NAMELY, THE NOTIONS – AND THE DEBATES INHERENT TO THEM – OF ECONOMICS REPUTATION, PLATFORMIZATION AND PLATFORMIZATION OF WORK. TO ACHIEVE THIS, RESEARCH USES LARGE-SCALE QUANTITATIVE DATA SCRAPING AND ANALYSIS METHODOLOGIES, AS WELL AS SEMI-DIRECTIVE INTERVIEWS WITH TEACHERS PRESENT ON BOTH PLATFORMS. FROM THAT, RAISES ELEMENTS FOR UNDERSTANDING THE SPECIFICITY OF TEACHING WORK IN CLASSES PARTICULAR, AS WELL AS FOR ITS CHARACTERISTICS AND ARTICULATIONS IN RELATION TO ITS ANALOGUE PAIR. IT ALSO PROVIDES SUPPORT FOR REFLECTION ON THE INFLUENCE OF INTELLIGENCE MECHANISMS ARTIFICIAL IN THE CONSTITUTION OF LABOR MARKETS, IN GENERAL, AND THE CLASSROOM LABOR MARKET SPECIFICALLY, PROPOSING, THEREFORE, A DEBATE ON THE INTERSECTIONS BETWEEN PRACTICES OF PLATFORM COMPANIES AND THE CONDITIONS OF LABOR CIRCULATION IN THESE CONTEXTS.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>FALA DO CRIME;DISCURSO PUNITIVISTA;PUNIÇÃO;REDES SOCIAIS DIGITAIS</t>
+          <t>INTELIGÊNCIA ARTIFICIAL;TRABALHO;PROFESSORES;PLATAFORMAS</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>TALK OF CRIME;PUNITIVE SPEECH;PUNISHMENT;DIGITAL NETWORKS</t>
+          <t>ARTIFICIAL INTELLIGENCE;WORK;TEACHERS;PLATFORMS</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Correlato</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>IA em sentido estrito</t>
         </is>
       </c>
       <c r="M67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N67" t="b">
         <v>0</v>
@@ -9810,11 +9810,11 @@
         <v>0</v>
       </c>
       <c r="Q67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>MARCOS CESAR ALVAREZ</t>
+          <t>ALVARO AUGUSTO COMIN</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -9848,7 +9848,7 @@
         </is>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
@@ -9867,16 +9867,16 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=13882903</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15426234</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>13882903</t>
+          <t>15426234</t>
         </is>
       </c>
       <c r="AE67" t="n">
-        <v>564924</v>
+        <v>3992079</v>
       </c>
     </row>
     <row r="68">
@@ -9895,67 +9895,67 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ADRIANA NUNES DE SOUZA</t>
+          <t>HELOISA HELENA SILVA CAVALCANTE</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>VISIBILIDADE SURREAL: GÊNERO, MUNDOS DIGITAIS E NARRATIVAS DA VANGUARDA SURREALISTA</t>
+          <t>BIG DATA E DEMOCRACIA: UMA ANÁLISE DA PARTICIPAÇÃO DO FACEBOOK NO 7 DE SETEMBRO DE 2021 NO BRASIL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>NESTA OBRA, INVESTIGA-SE A RELEVÂNCIA DO SURREALISMO POR MEIO DE UMA ECOLOGIA DE MATERIAIS QUE VÃO DESDE OBRAS DE ARTE ATÉ ESBOÇOS E TEORIAS FEMINISTAS. TEMAS COMO SUBJETIVIDADE, REPRESENTAÇÃO FEMININA E A INTERSEÇÃO ENTRE TECNOLOGIA E IDENTIDADE EXPANDEM O DEBATE PARA ABARCAR A EXTENSÃO DA INTELIGÊNCIA ARTIFICIAL NO ANTROPOCENO, RESSALTANDO A IMPERATIVIDADE DE UMA ABORDAGEM ÉTICA COM OLHAR CIBORGUE. A DINÂMICA DAS REDES SOCIAIS, NA QUAL OS USUÁRIOS DESEMPENHAM PAPÉIS HÍBRIDOS DE PRODUTORES E CONSUMIDORES, CONTRIBUI PARA UMA CULTURA DE INCESSANTE ESPETACULARIZAÇÃO. LOGO, DÁ-SE ÊNFASE À ESTETIZAÇÃO DO COTIDIANO, EXPLORANDO A CIBERFLÂNERIE E A PARTICIPAÇÃO, TANTO CONSCIENTE QUANTO INCONSCIENTE, DOS INDIVÍDUOS NAS PERSONALIZAÇÕES ALGORÍTMICAS. A ESTÉTICA INSTAGRAMÁVEL É CONTRASTADA COM O SURREALISMO E JUNTAS CASAM O GROTESCO COM A GRAÇA, DESAFIANDO AS NORMAS EMOCIONAIS E DESTACANDO A IMPORTÂNCIA DO INSTAGRAM NA ESTILIZAÇÃO E NA FORMAÇÃO DE IDENTIDADES ESTÉTICAS. A CONTRIBUIÇÃO DESTE ESTUDO RESIDE NA ANÁLISE DO SURREALISMO COMO MOVIMENTO ARTÍSTICO E POLÍTICO, ALÉM DA EXPLORAÇÃO DAS POSSÍVEIS CONTINUIDADES DESSE MOVIMENTO NA CULTURA VISUAL DO INSTAGRAM. AS INSTÂNCIAS EMPÍRICAS ENGLOBAM ESTUDOS DE CASO DE ARTISTAS, ANÁLISES DE HASHTAGS E REFLEXÕES SOBRE ESTÉTICA, ALIANDO-SE ÀS ESCOLHAS METODOLÓGICAS QUE PRIVILEGIAM A AUTOETNOGRAFIA E UMA ABORDAGEM NÃO LINEAR NA ORGANIZAÇÃO DOS CAPÍTULOS, ALMEJANDO EXPANDIR A COMPREENSÃO DO SURREALISMO E SUAS RAMIFICAÇÕES.</t>
+          <t>A PRESENTE PESQUISA BUSCA RESPONDER: COMO AS BIG TECHS PODEM INTERFERIR NA ADESÃO SOCIAL DE MOVIMENTOS POLÍTICOS AO UTILIZAREM A BIG DATA NO DESENVOLVIMENTO COMUNICACIONAL DE MANIFESTAÇÕES POPULARES, TRANSFIGURANDO SÍMBOLOS DA IDENTIDADE NACIONAL EM OBJETOS DE CAMPANHA POLÍTICA PARTIDÁRIA, MAIS ESPECIFICAMENTE O 7 DE SETEMBRO DE 2021 NO BRASIL? O OBJETIVO DESTA PESQUISA É IDENTIFICAR SE - E COMO - A BIG DATA FOI UTILIZADA PARA FINS DE INFLUÊNCIA SOBRE A ADESÃO SOCIAL DAS COMEMORAÇÕES DO 7 DE SETEMBRO DE 2021 E SEUS POSSÍVEIS REFLEXOS NA CAMPANHA PRESIDENCIAL PARA O PLEITO DE 2022 NO BRASIL. O CORPUS DA PESQUISA FOI COMPOSTO PELA ANÁLISE DO CASO QUE MARCOU A CAMPANHA ELEITORAL PRESIDENCIAL DE 2022: O USO POLÍTICO DO DIA DA INDEPENDÊNCIA DO BRASIL, O 07 DE SETEMBRO DE 2021. POR SE TRATAR DE UMA PESQUISA NO ÂMBITO DA COMUNICAÇÃO, OPTAMOS POR ANALISAR ESSE EVENTO A PARTIR DO MÉTODO METÁPORO, DE CIRO MARCONDES FILHO, CRIADO PARA “ACOMPANHAR A DINÂMICA, A VERSATILIDADE E A MUTABILIDADE CONTÍNUA” DESSA ÁREA, QUE IMPLICA AINDA NAS DEFINIÇÕES DE ACONTECIMENTO COMUNICACIONAL E CONTÍNUO ATMOSFÉRICO MEDIÁTICO, DO MESMO AUTOR. O ESTUDO SERÁ DESENVOLVIDO A PARTIR DA METODOLOGIA DE PESQUISA DA PSICOLOGIA DENOMINADA ANÁLISE TEMÁTICA, E SERÁ FEITO COM BASE NA INVESTIGAÇÃO DESSE EVENTO E DAS MÉTRICAS DE MENSURAÇÃO DE IMPACTO E ALCANCE DE ANÚNCIOS PATROCINADOS CRIADOS EM FUNÇÃO DELE E PRESENTES NA BIBLIOTECA DE ANÚNCIOS DA REDE SOCIAL META, ANTES FACEBOOK, APRESENTADOS NO RELATÓRIO PAREM O ROUBO 2.0: COMO O META ESTÁ SUBVERTENDO A DEMOCRACIA BRASILEIRA, DA ONG AMERICANA SUM OF US, QUE ESTÁ VINCULADA À UMA COMUNIDADE ONLINE INTERESSADA EM COBRAR DE GRANDES CORPORAÇÕES RESPONSABILIDADE DE SUAS AÇÕES SOBRE O MEIO AMBIENTE, OS DIREITOS DOS TRABALHADORES E A DEMOCRACIA, SEGUNDO SUA PRÓPRIA DEFINIÇÃO. O RELATÓRIO FOI DESENVOLVIDO ENTRE 20 A 26 DE AGOSTO DE 2022 E BUSCOU CHECAR O USO DO 7 DE SETEMBRO EM FAVOR DO ENTÃO CANDIDATO JAIR BOLSONARO NAS REDES SOCIAIS, NUMA ALUSÃO AO MOVIMENTO 'PARE O ROUBO', QUE CRESCEU EM 2020, NOS ESTADOS UNIDOS. O RESULTADO ESPERADO DESSA PESQUISA É COMPREENDER COMO O USO DA BIG DATA NO DESENVOLVIMENTO COMUNICACIONAL DAS COMEMORAÇÕES DO 7 DE SETEMBRO DE 2021 NO BRASIL PODE TER SIDO UTILIZADO PARA FINS DE CAMPANHA POLÍTICA NO PLEITO ELEITORAL PRESIDENCIAL DE 2022 NO BRASIL, BURLANDO AS REGRAS PRÉ-DEFINIDAS DE PERÍODO E FORMA COMO ESSAS CAMPANHAS DEVEM SER DESENVOLVIDAS.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>IN THIS WORK, THE RELEVANCE OF SURREALISM IS INVESTIGATED THROUGH AN ECOLOGY OF MATERIALS RANGING FROM WORKS OF ART TO SKETCHES AND FEMINIST THEORIES. THEMES SUCH AS SUBJECTIVITY, FEMALE REPRESENTATION AND THE INTERSECTION BETWEEN TECHNOLOGY AND IDENTITY EXPAND THE DEBATE TO ENCOMPASS THE EXTENT OF ARTIFICIAL INTELLIGENCE IN THE ANTHROPOCENE, HIGHLIGHTING THE IMPERATIVE OF AN ETHICAL APPROACH WITH A CYBORG PERSPECTIVE. THE DYNAMICS OF SOCIAL NETWORKS, IN WHICH USERS PLAY HYBRID ROLES OF PRODUCERS AND CONSUMERS, CONTRIBUTES TO A CULTURE OF INCESSANT SPECTACULARIZATION. THEREFORE, EMPHASIS IS PLACED ON THE AESTHETICIZATION OF EVERYDAY LIFE, EXPLORING CYBER-FLÂNERIE AND THE PARTICIPATION, BOTH CONSCIOUS AND UNCONSCIOUS, OF INDIVIDUALS IN ALGORITHMIC PERSONALIZATIONS. INSTAGRAMMABLE AESTHETICS ARE CONTRASTED WITH SURREALISM AND TOGETHER THEY MARRY THE GROTESQUE WITH GRACE, CHALLENGING EMOTIONAL NORMS AND HIGHLIGHTING THE IMPORTANCE OF INSTAGRAM IN STYLIZATION AND THE FORMATION OF AESTHETIC IDENTITIES. THE CONTRIBUTION OF THIS STUDY LIES IN THE ANALYSIS OF SURREALISM AS AN ARTISTIC AND POLITICAL MOVEMENT, IN ADDITION TO EXPLORING THE POSSIBLE CONTINUITIES OF THIS MOVEMENT IN THE VISUAL CULTURE OF INSTAGRAM. THE EMPIRICAL INSTANCES INCLUDE CASE STUDIES OF ARTISTS, HASHTAG ANALYSIS AND REFLECTIONS ON AESTHETICS, COMBINED WITH METHODOLOGICAL CHOICES THAT FAVOR AUTOETHNOGRAPHY AND A NON-LINEAR APPROACH IN ORGANIZING THE CHAPTERS, AIMING TO EXPAND THE UNDERSTANDING OF SURREALISM AND ITS RAMIFICATIONS.</t>
+          <t>THIS RESEARCH SEEKS TO ANSWER: HOW CAN BIG TECH INTERFERE IN THE SOCIAL ADHERENCE OF POLITICAL MOVEMENTS BY USING BIG DATA IN THE COMMUNICATIONAL DEVELOPMENT OF POPULAR DEMONSTRATIONS, TRANSFIGURING SYMBOLS OF NATIONAL IDENTITY INTO OBJECTS OF PARTISAN POLITICAL CAMPAIGNING, MORE SPECIFICALLY SEPTEMBER 7, 2021 IN BRAZIL? THE AIM OF THIS RESEARCH IS TO IDENTIFY WHETHER - AND HOW - BIG DATA WAS USED TO INFLUENCE SOCIAL ADHERENCE TO THE SEPTEMBER 7, 2021 CELEBRATIONS AND ITS POSSIBLE REPERCUSSIONS ON THE 2022 PRESIDENTIAL CAMPAIGN IN BRAZIL. THE CORPUS OF THE RESEARCH CONSISTED OF AN ANALYSIS OF THE CASE THAT MARKED THE 2022 PRESIDENTIAL ELECTION CAMPAIGN: THE POLITICAL USE OF BRAZIL'S INDEPENDENCE DAY, SEPTEMBER 7, 2021. AS THIS IS A RESEARCH PROJECT IN THE FIELD OF COMMUNICATION, WE CHOSE TO ANALYZE THIS EVENT USING CIRO MARCONDES FILHO'S METAPORO METHOD, CREATED TO “ACCOMPANY THE DYNAMICS, VERSATILITY AND CONTINUOUS MUTABILITY” OF THIS AREA, WHICH ALSO IMPLIES THE DEFINITIONS OF COMMUNICATIONAL EVENT AND CONTINUOUS ATMOSPHERIC MEDIA, BY THE SAME AUTHOR. THE STUDY WILL BE DEVELOPED USING THE PSYCHOLOGY RESEARCH METHODOLOGY CALLED THEMATIC ANALYSIS, AND WILL BE BASED ON THE INVESTIGATION OF THIS EVENT AND THE METRICS USED TO MEASURE THE IMPACT AND REACH OF SPONSORED ADS CREATED AS A RESULT OF IT AND PRESENT IN THE ADS LIBRARY OF THE SOCIAL NETWORK META, FORMERLY FACEBOOK, PRESENTED IN THE REPORT STOP THE THEFT 2.0: HOW META IS SUBVERTING BRAZILIAN DEMOCRACY, BY THE AMERICAN NGO SUM OF US, WHICH IS LINKED TO AN ONLINE COMMUNITY INTERESTED IN HOLDING LARGE CORPORATIONS ACCOUNTABLE FOR THEIR ACTIONS ON THE ENVIRONMENT, WORKERS' RIGHTS AND DEMOCRACY, ACCORDING TO ITS OWN DEFINITION. THE REPORT WAS DEVELOPED BETWEEN AUGUST 20 AND 26, 2022 AND SOUGHT TO CHECK THE USE OF SEPTEMBER 7 IN FAVOR OF THEN-CANDIDATE JAIR BOLSONARO ON SOCIAL NETWORKS, IN AN ALLUSION TO THE 'STOP THE ROBBERY' MOVEMENT, WHICH GREW IN 2020 IN THE UNITED STATES. THE EXPECTED RESULT OF THIS RESEARCH IS TO UNDERSTAND HOW THE USE OF BIG DATA IN THE COMMUNICATIONAL DEVELOPMENT OF THE SEPTEMBER 7, 2021 CELEBRATIONS IN BRAZIL MAY HAVE BEEN USED FOR POLITICAL CAMPAIGN PURPOSES IN THE 2022 PRESIDENTIAL ELECTION IN BRAZIL, CIRCUMVENTING THE PREDEFINED RULES OF PERIOD AND HOW THESE CAMPAIGNS SHOULD BE DEVELOPED.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>SURREALISMO;SUBJETIVIDADE;REPRESENTAÇÃO FEMININA;INSTAGRAM;AUTOETNOGRAFIA.</t>
+          <t>BIG DATA;ELEIÇÕES;BRASIL;META;HOMEM-MÁQUINA.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>SURREALISM;SUBJECTIVITY;FEMALE REPRESENTATION;INSTAGRAM;AUTOETHNOGRAPHY</t>
+          <t>BIG DATA;ELECTIONS;BRAZIL;META;HUMAN-MACHINE RELATION.</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>IA em sentido estrito</t>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M68" t="b">
+        <v>0</v>
+      </c>
+      <c r="N68" t="b">
+        <v>0</v>
+      </c>
+      <c r="O68" t="b">
+        <v>0</v>
+      </c>
+      <c r="P68" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="b">
         <v>1</v>
       </c>
-      <c r="N68" t="b">
-        <v>0</v>
-      </c>
-      <c r="O68" t="b">
-        <v>0</v>
-      </c>
-      <c r="P68" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="b">
-        <v>0</v>
-      </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>PATRICIA REINHEIMER</t>
+          <t>ALEXSANDRO GALENO ARAUJO DANTAS</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -9965,31 +9965,31 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL RURAL DO RIO DE JANEIRO</t>
+          <t>UNIVERSIDADE FEDERAL DO RIO GRANDE DO NORTE</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>UFRRJ</t>
+          <t>UFRN</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>SUDESTE</t>
+          <t>NORDESTE</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>RIO GRANDE DO NORTE</t>
         </is>
       </c>
       <c r="Y68" t="n">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>SOCIOLOGIA DO DESENVOLVIMENTO</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
@@ -10008,16 +10008,16 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15526518</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15936517</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>15526518</t>
+          <t>15936517</t>
         </is>
       </c>
       <c r="AE68" t="n">
-        <v>4121197</v>
+        <v>4322267</v>
       </c>
     </row>
     <row r="69">
@@ -10036,67 +10036,67 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>BERNARDO MARTINHO BALLARDIN</t>
+          <t>MARCUS ANGELO ALVES DA COSTA SILVA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>"PARA ALÉM DA UBERIZAÇÃO: UMA INVESTIGAÇÃO DO TRABALHO DOCENTE NAS PLATAFORMAS DE AULAS PARTICULARES PROFES E SUPERPROF A PARTIR DOS PARADIGMAS DA PLATAFORMIZAÇÃO E DA ECONOMIA REPUTACIONAL"</t>
+          <t>IMPLEMENTAÇÃO E USO DE TECNOLOGIAS PARA AUTOMAÇÃO DO ATENDIMENTO NOS SUPERMERCADOS DE FORTALEZA: UM OLHAR A PARTIR DA POSIÇÃO DOS AGENTES ENVOLVIDOS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>A PRESENTE DISSERTAÇÃO TEM POR OBJETIVO ANALISAR AS CONDIÇÕES DE CIRCULAÇÃO E REALIZAÇÃO DO TRABALHO NAS PLATAFORMAS DE AULAS PARTICULARES SUPERPROF E PROFES, AMBAS ATUANDO NO BRASIL, BEM COMO AS PERCEPÇÕES DOS DOCENTES SOBRE TAIS CONDIÇÕES. TAL ANÁLISE SE FUNDAMENTA EM TRÊS PARADIGMAS TEÓRICOS, A SABER, AS NOÇÕES – E OS DEBATES INERENTES A ELAS – DE ECONOMIA REPUTACIONAL, PLATAFORMIZAÇÃO E PLATAFORMIZAÇÃO DO TRABALHO. PARA ISSO, A PESQUISA SE VALE DE METODOLOGIAS DE RASPAGEM E ANÁLISE DE DADOS QUANTITATIVOS EM LARGA ESCALA, BEM COMO DE ENTREVISTAS SEMI-DIRETIVAS COM PROFESSORES ATUANDO NAS DUAS PLATAFORMAS. A PARTIR DESSAS, LEVANTA ELEMENTOS PARA O ENTENDIMENTO DA ESPECIFICIDADE DO TRABALHO DOCENTE DE AULAS PARTICULARES, BEM COMO PARA SUAS CARACTERÍSTICAS E ARTICULAÇÕES EM RELAÇÃO AO SEU PAR ANALÓGICO. TRAZ SUBSÍDIOS, TAMBÉM, PARA A REFLEXÃO ACERCA DA INFLUÊNCIA DE MECANISMOS DE INTELIGÊNCIA ARTIFICIAL NA CONSTITUIÇÃO DE MERCADOS DE TRABALHO, EM GERAL, E DO MERCADO DE TRABALHO DE AULAS PARTICULARES, ESPECIFICAMENTE, PROPONDO, COM ISSO, UM DEBATE SOBRE AS INTERSECÇÕES ENTRE AS PRÁTICAS DAS EMPRESAS-PLATAFORMA E AS CONDIÇÕES DE CIRCULAÇÃO DO TRABALHO NESSES CONTEXTOS.</t>
+          <t>A PRESENTE INVESTIGAÇÃO BUSCA RESPONDER QUE FATORES EXPLICAM A IMPLEMENTAÇÃO DE TECNOLOGIAS DE AUTOATENDIMENTO NOS SUPERMERCADOS DE FORTALEZA DA FORMA COMO ACONTECE. PARA TAL, UM ESTUDO DE CASO COM FINALIDADE EXPLICATIVA E ABORDAGEM QUALITATIVA FOI FEITO ESPECIALMENTE ORIENTADO POR ENTREVISTAS SEMIESTRUTURADAS, DE FORMA A NOTAR A POTENCIALIZAÇÃO DOS GANHOS, O CONTROLE DO TRABALHO E A MODIFICAÇÃO DO CONSUMO (PRESSUPOSTOS INICIALMENTE ELENCADOS). DEMONSTRA-SE QUE EM FORTALEZA HÁ BAIXA ADESÃO DESSAS MÁQUINAS POR SUPERMERCADO (INFERIOR A 15%), AINDA QUE A EFETIVIDADE DELAS SEJA RECONHECIDA POR TODOS OS AGENTES ENVOLVIDOS: CONSUMIDORES, FABRICANTES, GERENTES DOS SUPERMERCADOS QUE ADOTAM O SELF CHECKOUT E TAMBÉM DAQUELES NÃO ADERENTES. CONCLUI-SE, POIS, QUE A IMPLEMENTAÇÃO DO AUTOATENDIMENTO EM FORTALEZA DÁ-SE ESPECIALMENTE PELA CAPACIDADE DE INCIDIR SOBRE O TEMPO DA PRESTAÇÃO DO SERVIÇO, ISTO É: OS CONSUMIDORES PASSAM MENOS TEMPO NO SUPERMERCADO; O TEMPO DE TRABALHO DOS TRABALHADORES DO SUPERMERCADO É USADO EM OUTRAS ATIVIDADES; E O TEMPO DE ARRECADAÇÃO PROVENIENTE DA VENDA DO VOLUME DE MERCADORIAS TORNA-SE MAIS RÁPIDO. APESAR DISSO, A IMPLEMENTAÇÃO NÃO É MAIS EXPRESSIVA EM DECORRÊNCIA DE UMA CARACTERÍSTICA DE FORTALEZA QUE TAMBÉM É, DADAS AS PROPORÇÕES, CARACTERÍSTICA DO BRASIL E DO SUL GLOBAL: MÃO DE OBRA ABUNDANTE E BARATA.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>THIS DISSERTATION AIMS TO ANALYZE THE CONDITIONS OF CIRCULATION AND REALIZATION OF I WORK ON THE PRIVATE TUTORING PLATFORMS SUPERPROF AND PROFES, BOTH ACTIVE IN BRAZIL, AS WELL AS TEACHERS' PERCEPTIONS ABOUT SUCH CONDITIONS. THIS ANALYSIS IS BASED ON THREE THEORETICAL PARADIGMS, NAMELY, THE NOTIONS – AND THE DEBATES INHERENT TO THEM – OF ECONOMICS REPUTATION, PLATFORMIZATION AND PLATFORMIZATION OF WORK. TO ACHIEVE THIS, RESEARCH USES LARGE-SCALE QUANTITATIVE DATA SCRAPING AND ANALYSIS METHODOLOGIES, AS WELL AS SEMI-DIRECTIVE INTERVIEWS WITH TEACHERS PRESENT ON BOTH PLATFORMS. FROM THAT, RAISES ELEMENTS FOR UNDERSTANDING THE SPECIFICITY OF TEACHING WORK IN CLASSES PARTICULAR, AS WELL AS FOR ITS CHARACTERISTICS AND ARTICULATIONS IN RELATION TO ITS ANALOGUE PAIR. IT ALSO PROVIDES SUPPORT FOR REFLECTION ON THE INFLUENCE OF INTELLIGENCE MECHANISMS ARTIFICIAL IN THE CONSTITUTION OF LABOR MARKETS, IN GENERAL, AND THE CLASSROOM LABOR MARKET SPECIFICALLY, PROPOSING, THEREFORE, A DEBATE ON THE INTERSECTIONS BETWEEN PRACTICES OF PLATFORM COMPANIES AND THE CONDITIONS OF LABOR CIRCULATION IN THESE CONTEXTS.</t>
+          <t>THIS RESEARCH SEEKS TO ANSWER WHAT FACTORS HAVE CAUSED SELF-SERVICE TECHNOLOGIES TO BE IMPLEMENTED IN FORTALEZA SUPERMARKETS IN THE FORM THEY HAVE. TO THIS END, A CASE STUDY WITH AN EXPLANATORY PURPOSE AND A QUALITATIVE APPROACH WAS CARRIED OUT, ESPECIALLY GUIDED BY SEMI-STRUCTURED INTERVIEWS, IN ORDER TO NOTE THE POTENTIALIZATION OF GAINS, THE CONTROL OF WORK AND THE MODIFICATION OF CONSUMPTION (HYPOTHESES INITIALLY RAISED). IT SHOWS THAT IN FORTALEZA THERE IS LOW TAKE-UP OF THESE MACHINES BY SUPERMARKETS (LESS THAN 15%), EVEN THOUGH THEIR EFFECTIVENESS IS RECOGNIZED BY ALL THE AGENTS INVOLVED: CONSUMERS, MANUFACTURERS, MANAGERS OF SUPERMARKETS THAT HAVE ADOPTED SELF-CHECKOUT AND THOSE THAT HAVE NOT. IT CAN BE CONCLUDED, THEREFORE, THAT THE IMPLEMENTATION OF SELF-SERVICE IN FORTALEZA HAS A PARTICULAR IMPACT ON THE TIME TAKEN TO PROVIDE THE SERVICE, I.E.: CONSUMERS SPEND LESS TIME IN THE SUPERMARKET; SUPERMARKET WORKERS' WORKING TIME IS USED FOR OTHER ACTIVITIES; AND THE TIME TAKEN TO COLLECT REVENUE FROM THE SALE OF GOODS BECOMES FASTER. DESPITE THIS, THE IMPLEMENTATION IS NOT MORE SIGNIFICANT DUE TO A CHARACTERISTIC OF FORTALEZA THAT IS ALSO, GIVEN THE PROPORTIONS, CHARACTERISTIC OF BRAZIL AND THE GLOBAL SOUTH: ABUNDANT AND CHEAP LABOR</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>INTELIGÊNCIA ARTIFICIAL;TRABALHO;PROFESSORES;PLATAFORMAS</t>
+          <t>MAQUINAÇÃO;SUPERMERCADOS;TEMPO DE TRABALHO SOCIALMENTE NECESSÁRIO</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>ARTIFICIAL INTELLIGENCE;WORK;TEACHERS;PLATFORMS</t>
+          <t>MACHINING;SUPERMARKETS;SOCIALLY NECESSARY WORKING TIME</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Foco Central</t>
+          <t>Tecnologias IA/ML/DL - Correlato</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>IA em sentido estrito</t>
+          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
         </is>
       </c>
       <c r="M69" t="b">
+        <v>0</v>
+      </c>
+      <c r="N69" t="b">
+        <v>0</v>
+      </c>
+      <c r="O69" t="b">
+        <v>0</v>
+      </c>
+      <c r="P69" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="b">
         <v>1</v>
       </c>
-      <c r="N69" t="b">
-        <v>0</v>
-      </c>
-      <c r="O69" t="b">
-        <v>0</v>
-      </c>
-      <c r="P69" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="b">
-        <v>0</v>
-      </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>ALVARO AUGUSTO COMIN</t>
+          <t>EDEMILSON CRUZ SANTANA JUNIOR</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -10106,31 +10106,31 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DE SÃO PAULO</t>
+          <t>UNIVERSIDADE FEDERAL DO CEARÁ</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>USP</t>
+          <t>UFC</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>SUDESTE</t>
+          <t>NORDESTE</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>SÃO PAULO</t>
+          <t>CEARÁ</t>
         </is>
       </c>
       <c r="Y69" t="n">
-        <v>253</v>
+        <v>89</v>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
@@ -10149,16 +10149,16 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15426234</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16141494</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>15426234</t>
+          <t>16141494</t>
         </is>
       </c>
       <c r="AE69" t="n">
-        <v>3992079</v>
+        <v>4046589</v>
       </c>
     </row>
     <row r="70">
@@ -10177,51 +10177,51 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>HELOISA HELENA SILVA CAVALCANTE</t>
+          <t>VITOR MUSSA TAVARES GOMES</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>BIG DATA E DEMOCRACIA: UMA ANÁLISE DA PARTICIPAÇÃO DO FACEBOOK NO 7 DE SETEMBRO DE 2021 NO BRASIL</t>
+          <t>A CONSTRUÇÃO DA INDÚSTRIA 4.0 PELO MICROTRABALHO</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>A PRESENTE PESQUISA BUSCA RESPONDER: COMO AS BIG TECHS PODEM INTERFERIR NA ADESÃO SOCIAL DE MOVIMENTOS POLÍTICOS AO UTILIZAREM A BIG DATA NO DESENVOLVIMENTO COMUNICACIONAL DE MANIFESTAÇÕES POPULARES, TRANSFIGURANDO SÍMBOLOS DA IDENTIDADE NACIONAL EM OBJETOS DE CAMPANHA POLÍTICA PARTIDÁRIA, MAIS ESPECIFICAMENTE O 7 DE SETEMBRO DE 2021 NO BRASIL? O OBJETIVO DESTA PESQUISA É IDENTIFICAR SE - E COMO - A BIG DATA FOI UTILIZADA PARA FINS DE INFLUÊNCIA SOBRE A ADESÃO SOCIAL DAS COMEMORAÇÕES DO 7 DE SETEMBRO DE 2021 E SEUS POSSÍVEIS REFLEXOS NA CAMPANHA PRESIDENCIAL PARA O PLEITO DE 2022 NO BRASIL. O CORPUS DA PESQUISA FOI COMPOSTO PELA ANÁLISE DO CASO QUE MARCOU A CAMPANHA ELEITORAL PRESIDENCIAL DE 2022: O USO POLÍTICO DO DIA DA INDEPENDÊNCIA DO BRASIL, O 07 DE SETEMBRO DE 2021. POR SE TRATAR DE UMA PESQUISA NO ÂMBITO DA COMUNICAÇÃO, OPTAMOS POR ANALISAR ESSE EVENTO A PARTIR DO MÉTODO METÁPORO, DE CIRO MARCONDES FILHO, CRIADO PARA “ACOMPANHAR A DINÂMICA, A VERSATILIDADE E A MUTABILIDADE CONTÍNUA” DESSA ÁREA, QUE IMPLICA AINDA NAS DEFINIÇÕES DE ACONTECIMENTO COMUNICACIONAL E CONTÍNUO ATMOSFÉRICO MEDIÁTICO, DO MESMO AUTOR. O ESTUDO SERÁ DESENVOLVIDO A PARTIR DA METODOLOGIA DE PESQUISA DA PSICOLOGIA DENOMINADA ANÁLISE TEMÁTICA, E SERÁ FEITO COM BASE NA INVESTIGAÇÃO DESSE EVENTO E DAS MÉTRICAS DE MENSURAÇÃO DE IMPACTO E ALCANCE DE ANÚNCIOS PATROCINADOS CRIADOS EM FUNÇÃO DELE E PRESENTES NA BIBLIOTECA DE ANÚNCIOS DA REDE SOCIAL META, ANTES FACEBOOK, APRESENTADOS NO RELATÓRIO PAREM O ROUBO 2.0: COMO O META ESTÁ SUBVERTENDO A DEMOCRACIA BRASILEIRA, DA ONG AMERICANA SUM OF US, QUE ESTÁ VINCULADA À UMA COMUNIDADE ONLINE INTERESSADA EM COBRAR DE GRANDES CORPORAÇÕES RESPONSABILIDADE DE SUAS AÇÕES SOBRE O MEIO AMBIENTE, OS DIREITOS DOS TRABALHADORES E A DEMOCRACIA, SEGUNDO SUA PRÓPRIA DEFINIÇÃO. O RELATÓRIO FOI DESENVOLVIDO ENTRE 20 A 26 DE AGOSTO DE 2022 E BUSCOU CHECAR O USO DO 7 DE SETEMBRO EM FAVOR DO ENTÃO CANDIDATO JAIR BOLSONARO NAS REDES SOCIAIS, NUMA ALUSÃO AO MOVIMENTO 'PARE O ROUBO', QUE CRESCEU EM 2020, NOS ESTADOS UNIDOS. O RESULTADO ESPERADO DESSA PESQUISA É COMPREENDER COMO O USO DA BIG DATA NO DESENVOLVIMENTO COMUNICACIONAL DAS COMEMORAÇÕES DO 7 DE SETEMBRO DE 2021 NO BRASIL PODE TER SIDO UTILIZADO PARA FINS DE CAMPANHA POLÍTICA NO PLEITO ELEITORAL PRESIDENCIAL DE 2022 NO BRASIL, BURLANDO AS REGRAS PRÉ-DEFINIDAS DE PERÍODO E FORMA COMO ESSAS CAMPANHAS DEVEM SER DESENVOLVIDAS.</t>
+          <t>O OBJETIVO DESTA PESQUISA É RASTREAR A CONSTRUÇÃO SOCIOTÉCNICA DA INDÚSTRIA 4.0 PELO MICROTRABALHO. A INDÚSTRIA 4.0 DIZ RESPEITO A UMA AGENDA GLOBAL DE TRANSFORMAÇÕES NO ÂMBITO DA MANUFATURA INDUSTRIAL QUE COMPREENDE UMA SÉRIE DE NOVIDADES TÉCNICAS E ORGANIZACIONAIS, SENDO UMA DELAS A INTENSIFICAÇÃO DO USO DE TECNOLOGIAS DE INTELIGÊNCIA ARTIFICIAL (IA) NA PRODUÇÃO. O MICROTRABALHO, POR SUA VEZ, SE REFERE À ATIVIDADE DE PRODUÇÃO DE DADOS REALIZADA NA INTERNET ATRAVÉS DE PEQUENAS TAREFAS DE BAIXA REMUNERAÇÃO. DESSA FORMA, O QUE ESTE ESTUDO FAZ É VERIFICAR, ENTENDER E DESCREVER AS FORMAS DE PARTICIPAÇÃO DOS MICROTRABALHADORES, ATRAVÉS DA CURADORIA DE DADOS NECESSÁRIA PARA O ABASTECIMENTO DE MODELOS DE IA, NA CONSTITUIÇÃO DE TÉCNICAS DE INTELIGÊNCIA ARTIFICIAL CRUCIAIS PARA ESSE PROJETO DA INDÚSTRIA MANUFATUREIRA. ISSO É FEITO A PARTIR DE UMA METODOLOGIA MULTIFACETADA QUE COMBINA MÉTODOS QUALITATIVOS COM TÉCNICAS COMPUTACIONAIS, COMO O TRABALHO DE CAMPO DIGITAL E A MODELAGEM DE TÓPICOS. OS RESULTADOS INDICAM QUE O MICROTRABALHO É GERENCIADO INTENSAMENTE A PARTIR DE TÉCNICAS DIGITAIS – ALGORÍTMICAS E DE INTERFACE – E QUE DESEMPENHA UM PAPEL CONSTITUTIVO NO ECOSSISTEMA TECNOLÓGICO DA INDÚSTRIA 4.0.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>THIS RESEARCH SEEKS TO ANSWER: HOW CAN BIG TECH INTERFERE IN THE SOCIAL ADHERENCE OF POLITICAL MOVEMENTS BY USING BIG DATA IN THE COMMUNICATIONAL DEVELOPMENT OF POPULAR DEMONSTRATIONS, TRANSFIGURING SYMBOLS OF NATIONAL IDENTITY INTO OBJECTS OF PARTISAN POLITICAL CAMPAIGNING, MORE SPECIFICALLY SEPTEMBER 7, 2021 IN BRAZIL? THE AIM OF THIS RESEARCH IS TO IDENTIFY WHETHER - AND HOW - BIG DATA WAS USED TO INFLUENCE SOCIAL ADHERENCE TO THE SEPTEMBER 7, 2021 CELEBRATIONS AND ITS POSSIBLE REPERCUSSIONS ON THE 2022 PRESIDENTIAL CAMPAIGN IN BRAZIL. THE CORPUS OF THE RESEARCH CONSISTED OF AN ANALYSIS OF THE CASE THAT MARKED THE 2022 PRESIDENTIAL ELECTION CAMPAIGN: THE POLITICAL USE OF BRAZIL'S INDEPENDENCE DAY, SEPTEMBER 7, 2021. AS THIS IS A RESEARCH PROJECT IN THE FIELD OF COMMUNICATION, WE CHOSE TO ANALYZE THIS EVENT USING CIRO MARCONDES FILHO'S METAPORO METHOD, CREATED TO “ACCOMPANY THE DYNAMICS, VERSATILITY AND CONTINUOUS MUTABILITY” OF THIS AREA, WHICH ALSO IMPLIES THE DEFINITIONS OF COMMUNICATIONAL EVENT AND CONTINUOUS ATMOSPHERIC MEDIA, BY THE SAME AUTHOR. THE STUDY WILL BE DEVELOPED USING THE PSYCHOLOGY RESEARCH METHODOLOGY CALLED THEMATIC ANALYSIS, AND WILL BE BASED ON THE INVESTIGATION OF THIS EVENT AND THE METRICS USED TO MEASURE THE IMPACT AND REACH OF SPONSORED ADS CREATED AS A RESULT OF IT AND PRESENT IN THE ADS LIBRARY OF THE SOCIAL NETWORK META, FORMERLY FACEBOOK, PRESENTED IN THE REPORT STOP THE THEFT 2.0: HOW META IS SUBVERTING BRAZILIAN DEMOCRACY, BY THE AMERICAN NGO SUM OF US, WHICH IS LINKED TO AN ONLINE COMMUNITY INTERESTED IN HOLDING LARGE CORPORATIONS ACCOUNTABLE FOR THEIR ACTIONS ON THE ENVIRONMENT, WORKERS' RIGHTS AND DEMOCRACY, ACCORDING TO ITS OWN DEFINITION. THE REPORT WAS DEVELOPED BETWEEN AUGUST 20 AND 26, 2022 AND SOUGHT TO CHECK THE USE OF SEPTEMBER 7 IN FAVOR OF THEN-CANDIDATE JAIR BOLSONARO ON SOCIAL NETWORKS, IN AN ALLUSION TO THE 'STOP THE ROBBERY' MOVEMENT, WHICH GREW IN 2020 IN THE UNITED STATES. THE EXPECTED RESULT OF THIS RESEARCH IS TO UNDERSTAND HOW THE USE OF BIG DATA IN THE COMMUNICATIONAL DEVELOPMENT OF THE SEPTEMBER 7, 2021 CELEBRATIONS IN BRAZIL MAY HAVE BEEN USED FOR POLITICAL CAMPAIGN PURPOSES IN THE 2022 PRESIDENTIAL ELECTION IN BRAZIL, CIRCUMVENTING THE PREDEFINED RULES OF PERIOD AND HOW THESE CAMPAIGNS SHOULD BE DEVELOPED.</t>
+          <t>THE OBJECTIVE OF THIS RESEARCH IS TO TRACE THE SOCIOTECHNICAL CONSTRUCTION OF INDUSTRY 4.0 THROUGH MICROWORK. THE FIRST REFERS TO A GLOBAL AGENDA OF TRANSFORMATIONS IN INDUSTRIAL MANUFACTURING, ENCOMPASSING A SERIES OF TECHNICAL AND ORGANIZATIONAL INNOVATIONS, ONE OF WHICH IS THE INTENSIFIED USE OF ARTIFICIAL INTELLIGENCE (AI) TECHNOLOGIES IN PRODUCTION. THE SECOND REFERS TO THE ACTIVITY OF DATA PRODUCTION CARRIED OUT ONLINE THROUGH SMALL, LOW-PAID TASKS. THUS, THIS STUDY AIMS TO VERIFY, UNDERSTAND, AND DESCRIBE THE WAYS IN WHICH MICROWORKERS PARTICIPATE, THROUGH THE DATA CURATION NECESSARY TO TRAIN AI MODELS, IN THE DEVELOPMENT OF ARTIFICIAL INTELLIGENCE TECHNIQUES CRUCIAL TO THIS INDUSTRIAL MANUFACTURING PROJECT. THIS IS ACHIEVED THROUGH A MULTIFACETED METHODOLOGY THAT COMBINES QUALITATIVE METHODS WITH COMPUTATIONAL TECHNIQUES SUCH AS DIGITAL FIELDWORK AND TOPIC MODELING. THE RESULTS INDICATE THAT MICROWORK IS INTENSELY MANAGED THROUGH DIGITAL TECHNIQUES – BOTH ALGORITHMIC AND INTERFACE-BASED – AND THAT IT PLAYS A CONSTITUTIVE ROLE IN THE TECHNOLOGICAL ECOSYSTEM OF INDUSTRY 4.0.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>BIG DATA;ELEIÇÕES;BRASIL;META;HOMEM-MÁQUINA.</t>
+          <t>SOCIOLOGIA DO TRABALHO;SOCIOLOGIA DIGITAL;CIÊNCIA SOCIAL COMPUTACIONAL;TRABALHO EM PLATAFORMAS DIGITAIS;MICROTRABALHO;INDÚSTRIA 4.0.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>BIG DATA;ELECTIONS;BRAZIL;META;HUMAN-MACHINE RELATION.</t>
+          <t>LABOR SOCIOLOGY;DIGITAL SOCIOLOGY;COMPUTATIONAL SOCIAL SCIENCE;PLATFORM LABOR;MICROWORK;INDUSTRY 4.0.</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Tecnologias IA/ML/DL - Correlato</t>
+          <t>Tecnologias IA/ML/DL - Foco Central</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
+          <t>IA em sentido estrito</t>
         </is>
       </c>
       <c r="M70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N70" t="b">
         <v>0</v>
@@ -10233,45 +10233,45 @@
         <v>0</v>
       </c>
       <c r="Q70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>ALEXSANDRO GALENO ARAUJO DANTAS</t>
+          <t>JOSE RICARDO GARCIA PEREIRA RAMALHO</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>CIÊNCIAS SOCIAIS</t>
+          <t>SOCIOLOGIA E ANTROPOLOGIA</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE FEDERAL DO RIO GRANDE DO NORTE</t>
+          <t>UNIVERSIDADE FEDERAL DO RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>UFRN</t>
+          <t>UFRJ</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>NORDESTE</t>
+          <t>SUDESTE</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>RIO GRANDE DO NORTE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="Y70" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>SOCIOLOGIA DO DESENVOLVIMENTO</t>
+          <t>OUTRAS SOCIOLOGIAS ESPECÍFICAS</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
@@ -10290,297 +10290,15 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=15936517</t>
+          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16255791</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>15936517</t>
+          <t>16255791</t>
         </is>
       </c>
       <c r="AE70" t="n">
-        <v>4322267</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>SOCIOLOGIA</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>MESTRADO</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2024-08-23</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>MARCUS ANGELO ALVES DA COSTA SILVA</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>IMPLEMENTAÇÃO E USO DE TECNOLOGIAS PARA AUTOMAÇÃO DO ATENDIMENTO NOS SUPERMERCADOS DE FORTALEZA: UM OLHAR A PARTIR DA POSIÇÃO DOS AGENTES ENVOLVIDOS</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>A PRESENTE INVESTIGAÇÃO BUSCA RESPONDER QUE FATORES EXPLICAM A IMPLEMENTAÇÃO DE TECNOLOGIAS DE AUTOATENDIMENTO NOS SUPERMERCADOS DE FORTALEZA DA FORMA COMO ACONTECE. PARA TAL, UM ESTUDO DE CASO COM FINALIDADE EXPLICATIVA E ABORDAGEM QUALITATIVA FOI FEITO ESPECIALMENTE ORIENTADO POR ENTREVISTAS SEMIESTRUTURADAS, DE FORMA A NOTAR A POTENCIALIZAÇÃO DOS GANHOS, O CONTROLE DO TRABALHO E A MODIFICAÇÃO DO CONSUMO (PRESSUPOSTOS INICIALMENTE ELENCADOS). DEMONSTRA-SE QUE EM FORTALEZA HÁ BAIXA ADESÃO DESSAS MÁQUINAS POR SUPERMERCADO (INFERIOR A 15%), AINDA QUE A EFETIVIDADE DELAS SEJA RECONHECIDA POR TODOS OS AGENTES ENVOLVIDOS: CONSUMIDORES, FABRICANTES, GERENTES DOS SUPERMERCADOS QUE ADOTAM O SELF CHECKOUT E TAMBÉM DAQUELES NÃO ADERENTES. CONCLUI-SE, POIS, QUE A IMPLEMENTAÇÃO DO AUTOATENDIMENTO EM FORTALEZA DÁ-SE ESPECIALMENTE PELA CAPACIDADE DE INCIDIR SOBRE O TEMPO DA PRESTAÇÃO DO SERVIÇO, ISTO É: OS CONSUMIDORES PASSAM MENOS TEMPO NO SUPERMERCADO; O TEMPO DE TRABALHO DOS TRABALHADORES DO SUPERMERCADO É USADO EM OUTRAS ATIVIDADES; E O TEMPO DE ARRECADAÇÃO PROVENIENTE DA VENDA DO VOLUME DE MERCADORIAS TORNA-SE MAIS RÁPIDO. APESAR DISSO, A IMPLEMENTAÇÃO NÃO É MAIS EXPRESSIVA EM DECORRÊNCIA DE UMA CARACTERÍSTICA DE FORTALEZA QUE TAMBÉM É, DADAS AS PROPORÇÕES, CARACTERÍSTICA DO BRASIL E DO SUL GLOBAL: MÃO DE OBRA ABUNDANTE E BARATA.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>THIS RESEARCH SEEKS TO ANSWER WHAT FACTORS HAVE CAUSED SELF-SERVICE TECHNOLOGIES TO BE IMPLEMENTED IN FORTALEZA SUPERMARKETS IN THE FORM THEY HAVE. TO THIS END, A CASE STUDY WITH AN EXPLANATORY PURPOSE AND A QUALITATIVE APPROACH WAS CARRIED OUT, ESPECIALLY GUIDED BY SEMI-STRUCTURED INTERVIEWS, IN ORDER TO NOTE THE POTENTIALIZATION OF GAINS, THE CONTROL OF WORK AND THE MODIFICATION OF CONSUMPTION (HYPOTHESES INITIALLY RAISED). IT SHOWS THAT IN FORTALEZA THERE IS LOW TAKE-UP OF THESE MACHINES BY SUPERMARKETS (LESS THAN 15%), EVEN THOUGH THEIR EFFECTIVENESS IS RECOGNIZED BY ALL THE AGENTS INVOLVED: CONSUMERS, MANUFACTURERS, MANAGERS OF SUPERMARKETS THAT HAVE ADOPTED SELF-CHECKOUT AND THOSE THAT HAVE NOT. IT CAN BE CONCLUDED, THEREFORE, THAT THE IMPLEMENTATION OF SELF-SERVICE IN FORTALEZA HAS A PARTICULAR IMPACT ON THE TIME TAKEN TO PROVIDE THE SERVICE, I.E.: CONSUMERS SPEND LESS TIME IN THE SUPERMARKET; SUPERMARKET WORKERS' WORKING TIME IS USED FOR OTHER ACTIVITIES; AND THE TIME TAKEN TO COLLECT REVENUE FROM THE SALE OF GOODS BECOMES FASTER. DESPITE THIS, THE IMPLEMENTATION IS NOT MORE SIGNIFICANT DUE TO A CHARACTERISTIC OF FORTALEZA THAT IS ALSO, GIVEN THE PROPORTIONS, CHARACTERISTIC OF BRAZIL AND THE GLOBAL SOUTH: ABUNDANT AND CHEAP LABOR</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>MAQUINAÇÃO;SUPERMERCADOS;TEMPO DE TRABALHO SOCIALMENTE NECESSÁRIO</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>MACHINING;SUPERMARKETS;SOCIALLY NECESSARY WORKING TIME</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Tecnologias IA/ML/DL - Correlato</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Tecnologias correlatas (robótica, NLP, big data…)</t>
-        </is>
-      </c>
-      <c r="M71" t="b">
-        <v>0</v>
-      </c>
-      <c r="N71" t="b">
-        <v>0</v>
-      </c>
-      <c r="O71" t="b">
-        <v>0</v>
-      </c>
-      <c r="P71" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="b">
-        <v>1</v>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>EDEMILSON CRUZ SANTANA JUNIOR</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>SOCIOLOGIA</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>UNIVERSIDADE FEDERAL DO CEARÁ</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>UFC</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>NORDESTE</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>CE</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>CEARÁ</t>
-        </is>
-      </c>
-      <c r="Y71" t="n">
-        <v>89</v>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>PORTUGUES</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>NÃO SE APLICA</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>SOCIOLOGIA</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16141494</t>
-        </is>
-      </c>
-      <c r="AD71" t="inlineStr">
-        <is>
-          <t>16141494</t>
-        </is>
-      </c>
-      <c r="AE71" t="n">
-        <v>4046589</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>SOCIOLOGIA</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>MESTRADO</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>VITOR MUSSA TAVARES GOMES</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>A CONSTRUÇÃO DA INDÚSTRIA 4.0 PELO MICROTRABALHO</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>O OBJETIVO DESTA PESQUISA É RASTREAR A CONSTRUÇÃO SOCIOTÉCNICA DA INDÚSTRIA 4.0 PELO MICROTRABALHO. A INDÚSTRIA 4.0 DIZ RESPEITO A UMA AGENDA GLOBAL DE TRANSFORMAÇÕES NO ÂMBITO DA MANUFATURA INDUSTRIAL QUE COMPREENDE UMA SÉRIE DE NOVIDADES TÉCNICAS E ORGANIZACIONAIS, SENDO UMA DELAS A INTENSIFICAÇÃO DO USO DE TECNOLOGIAS DE INTELIGÊNCIA ARTIFICIAL (IA) NA PRODUÇÃO. O MICROTRABALHO, POR SUA VEZ, SE REFERE À ATIVIDADE DE PRODUÇÃO DE DADOS REALIZADA NA INTERNET ATRAVÉS DE PEQUENAS TAREFAS DE BAIXA REMUNERAÇÃO. DESSA FORMA, O QUE ESTE ESTUDO FAZ É VERIFICAR, ENTENDER E DESCREVER AS FORMAS DE PARTICIPAÇÃO DOS MICROTRABALHADORES, ATRAVÉS DA CURADORIA DE DADOS NECESSÁRIA PARA O ABASTECIMENTO DE MODELOS DE IA, NA CONSTITUIÇÃO DE TÉCNICAS DE INTELIGÊNCIA ARTIFICIAL CRUCIAIS PARA ESSE PROJETO DA INDÚSTRIA MANUFATUREIRA. ISSO É FEITO A PARTIR DE UMA METODOLOGIA MULTIFACETADA QUE COMBINA MÉTODOS QUALITATIVOS COM TÉCNICAS COMPUTACIONAIS, COMO O TRABALHO DE CAMPO DIGITAL E A MODELAGEM DE TÓPICOS. OS RESULTADOS INDICAM QUE O MICROTRABALHO É GERENCIADO INTENSAMENTE A PARTIR DE TÉCNICAS DIGITAIS – ALGORÍTMICAS E DE INTERFACE – E QUE DESEMPENHA UM PAPEL CONSTITUTIVO NO ECOSSISTEMA TECNOLÓGICO DA INDÚSTRIA 4.0.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>THE OBJECTIVE OF THIS RESEARCH IS TO TRACE THE SOCIOTECHNICAL CONSTRUCTION OF INDUSTRY 4.0 THROUGH MICROWORK. THE FIRST REFERS TO A GLOBAL AGENDA OF TRANSFORMATIONS IN INDUSTRIAL MANUFACTURING, ENCOMPASSING A SERIES OF TECHNICAL AND ORGANIZATIONAL INNOVATIONS, ONE OF WHICH IS THE INTENSIFIED USE OF ARTIFICIAL INTELLIGENCE (AI) TECHNOLOGIES IN PRODUCTION. THE SECOND REFERS TO THE ACTIVITY OF DATA PRODUCTION CARRIED OUT ONLINE THROUGH SMALL, LOW-PAID TASKS. THUS, THIS STUDY AIMS TO VERIFY, UNDERSTAND, AND DESCRIBE THE WAYS IN WHICH MICROWORKERS PARTICIPATE, THROUGH THE DATA CURATION NECESSARY TO TRAIN AI MODELS, IN THE DEVELOPMENT OF ARTIFICIAL INTELLIGENCE TECHNIQUES CRUCIAL TO THIS INDUSTRIAL MANUFACTURING PROJECT. THIS IS ACHIEVED THROUGH A MULTIFACETED METHODOLOGY THAT COMBINES QUALITATIVE METHODS WITH COMPUTATIONAL TECHNIQUES SUCH AS DIGITAL FIELDWORK AND TOPIC MODELING. THE RESULTS INDICATE THAT MICROWORK IS INTENSELY MANAGED THROUGH DIGITAL TECHNIQUES – BOTH ALGORITHMIC AND INTERFACE-BASED – AND THAT IT PLAYS A CONSTITUTIVE ROLE IN THE TECHNOLOGICAL ECOSYSTEM OF INDUSTRY 4.0.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>SOCIOLOGIA DO TRABALHO;SOCIOLOGIA DIGITAL;CIÊNCIA SOCIAL COMPUTACIONAL;TRABALHO EM PLATAFORMAS DIGITAIS;MICROTRABALHO;INDÚSTRIA 4.0.</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>LABOR SOCIOLOGY;DIGITAL SOCIOLOGY;COMPUTATIONAL SOCIAL SCIENCE;PLATFORM LABOR;MICROWORK;INDUSTRY 4.0.</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Tecnologias IA/ML/DL - Foco Central</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>IA em sentido estrito</t>
-        </is>
-      </c>
-      <c r="M72" t="b">
-        <v>1</v>
-      </c>
-      <c r="N72" t="b">
-        <v>0</v>
-      </c>
-      <c r="O72" t="b">
-        <v>0</v>
-      </c>
-      <c r="P72" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="b">
-        <v>0</v>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>JOSE RICARDO GARCIA PEREIRA RAMALHO</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>SOCIOLOGIA E ANTROPOLOGIA</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>UNIVERSIDADE FEDERAL DO RIO DE JANEIRO</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>UFRJ</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>SUDESTE</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>RJ</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>RIO DE JANEIRO</t>
-        </is>
-      </c>
-      <c r="Y72" t="n">
-        <v>78</v>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>PORTUGUES</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>OUTRAS SOCIOLOGIAS ESPECÍFICAS</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>SOCIOLOGIA</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>https://sucupira.capes.gov.br/sucupira/public/consultas/coleta/trabalhoConclusao/viewTrabalhoConclusao.jsf?popup=true&amp;id_trabalho=16255791</t>
-        </is>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>16255791</t>
-        </is>
-      </c>
-      <c r="AE72" t="n">
         <v>760300</v>
       </c>
     </row>
